--- a/artifacts/api-server/qa-output/Formula_Export_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Formula_Export_Charter_Public_Funding.xlsx
@@ -155,7 +155,7 @@
     <t>CSP Startup Grant</t>
   </si>
   <si>
-    <t>Grants &amp; Contributions</t>
+    <t>Philanthropy</t>
   </si>
   <si>
     <t>Annual Fixed</t>
@@ -675,7 +675,7 @@
     <font>
       <i/>
       <color rgb="FF666666"/>
-      <sz val="10"/>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -691,13 +691,13 @@
     <font>
       <i/>
       <color rgb="FF888888"/>
-      <sz val="10"/>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
       <i/>
       <color rgb="FF9CA3AF"/>
-      <sz val="9"/>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>

--- a/artifacts/api-server/qa-output/Formula_Export_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Formula_Export_Charter_Public_Funding.xlsx
@@ -23,7 +23,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="208">
   <si>
-    <t>Civic Scholars Charter — Financial Model Assumptions</t>
+    <t>Civic Scholars Charter - Financial Model Assumptions</t>
   </si>
   <si>
     <t>Yellow cells are editable inputs. All other cells in this workbook are formulas.</t>
@@ -371,7 +371,7 @@
     <t>Built by SchoolStack Budget  •  budget.schoolstack.ai</t>
   </si>
   <si>
-    <t>Civic Scholars Charter — 5-Year Financial Model</t>
+    <t>Civic Scholars Charter - 5-Year Financial Model</t>
   </si>
   <si>
     <t>REVENUE</t>
@@ -554,7 +554,7 @@
     <t>Break-Even Enrollment</t>
   </si>
   <si>
-    <t>Civic Scholars Charter — 2026-27 Pro Forma</t>
+    <t>Civic Scholars Charter - 2026-27 Pro Forma</t>
   </si>
   <si>
     <t>August</t>

--- a/artifacts/api-server/qa-output/Formula_Export_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Formula_Export_Charter_Public_Funding.xlsx
@@ -4,29 +4,104 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="Assumptions" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="5-Year Model" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="Year 1 Pro Forma" state="visible" r:id="rId6"/>
+    <sheet sheetId="1" name="Instructions" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Assumptions" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="5-Year Model" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="Year 1 Pro Forma" state="visible" r:id="rId7"/>
+    <sheet sheetId="5" name="Financial Health" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Assumptions'!$A1:$J70</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Assumptions'!$1:$3</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'5-Year Model'!$A1:$F89</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="1">'5-Year Model'!$1:$2</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Year 1 Pro Forma'!$A1:$N58</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Year 1 Pro Forma'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Instructions'!$A1:$B29</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Instructions'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Assumptions'!$A1:$J70</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Assumptions'!$1:$3</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'5-Year Model'!$A1:$F89</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'5-Year Model'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Year 1 Pro Forma'!$A1:$N58</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Year 1 Pro Forma'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Financial Health'!$A1:$G26</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Financial Health'!$1:$2</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="272">
+  <si>
+    <t>How to Use This Workbook</t>
+  </si>
+  <si>
+    <t>Cell Color Legend</t>
+  </si>
+  <si>
+    <t>Blue cells are editable inputs — change these to update your model.</t>
+  </si>
+  <si>
+    <t>White cells contain formulas — do not edit (they recalculate automatically).</t>
+  </si>
+  <si>
+    <t>Green cells are key outputs and summary metrics.</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Navigation</t>
+  </si>
+  <si>
+    <t>The Assumptions tab is the central control panel — all other tabs reference it.</t>
+  </si>
+  <si>
+    <t>Structure</t>
+  </si>
+  <si>
+    <t>5-Year Model: Detailed revenue, expense, and cash projections</t>
+  </si>
+  <si>
+    <t>Pro Forma: Consolidated income statement</t>
+  </si>
+  <si>
+    <t>Actuals vs Projections: Variance tracking</t>
+  </si>
+  <si>
+    <t>Financial Health: Key metrics dashboard</t>
+  </si>
+  <si>
+    <t>Debt Service Convention</t>
+  </si>
+  <si>
+    <t>operating expense on the Operating Statement. This is a standard</t>
+  </si>
+  <si>
+    <t>simplification used in school financial underwriting that ensures internal</t>
+  </si>
+  <si>
+    <t>consistency across all tabs.</t>
+  </si>
+  <si>
+    <t>Tips</t>
+  </si>
+  <si>
+    <t>Check the Financial Health dashboard for an at-a-glance assessment.</t>
+  </si>
+  <si>
+    <t>Review key metrics: net margin, cash runway, and DSCR.</t>
+  </si>
+  <si>
+    <t>Disclaimer</t>
+  </si>
+  <si>
+    <t>a loan commitment, or a guarantee of funding. All projections are based on</t>
+  </si>
+  <si>
+    <t>user-provided assumptions and should be independently verified.</t>
+  </si>
   <si>
     <t>Civic Scholars Charter - Financial Model Assumptions</t>
   </si>
   <si>
-    <t>Yellow cells are editable inputs. All other cells in this workbook are formulas.</t>
+    <t>Blue cells are editable inputs. All other cells in this workbook are formulas.</t>
   </si>
   <si>
     <t>SCHOOL PROFILE</t>
@@ -143,9 +218,6 @@
     <t>Per Student</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>Federal Title I</t>
   </si>
   <si>
@@ -645,6 +717,132 @@
   </si>
   <si>
     <t>Minimum Cash Month</t>
+  </si>
+  <si>
+    <t>Civic Scholars Charter — Financial Health Dashboard</t>
+  </si>
+  <si>
+    <t>Generated March 26, 2026</t>
+  </si>
+  <si>
+    <t>Metric</t>
+  </si>
+  <si>
+    <t>Year 1</t>
+  </si>
+  <si>
+    <t>Year 2</t>
+  </si>
+  <si>
+    <t>Year 3</t>
+  </si>
+  <si>
+    <t>Year 4</t>
+  </si>
+  <si>
+    <t>Year 5</t>
+  </si>
+  <si>
+    <t>Enrollment</t>
+  </si>
+  <si>
+    <t>Revenue</t>
+  </si>
+  <si>
+    <t>Personnel</t>
+  </si>
+  <si>
+    <t>Operating Expenses</t>
+  </si>
+  <si>
+    <t>Net Margin</t>
+  </si>
+  <si>
+    <t>FINANCIAL HEALTH SIGNALS</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Assessment</t>
+  </si>
+  <si>
+    <t>Watch Item</t>
+  </si>
+  <si>
+    <t>Viability</t>
+  </si>
+  <si>
+    <t>● Healthy</t>
+  </si>
+  <si>
+    <t>The model reaches net income early and sustains strong margins through Year 5.</t>
+  </si>
+  <si>
+    <t>Monitor enrollment actuals vs. projections in Year 1.</t>
+  </si>
+  <si>
+    <t>Liquidity</t>
+  </si>
+  <si>
+    <t>○ Needs attention</t>
+  </si>
+  <si>
+    <t>Cash goes negative in month 0. The school will need outside funding to continue operating.</t>
+  </si>
+  <si>
+    <t>Secure a line of credit or bridge funding before operations begin.</t>
+  </si>
+  <si>
+    <t>Staffing Burden</t>
+  </si>
+  <si>
+    <t>Staffing at 24% of revenue leaves room for facilities, programs, and reserves.</t>
+  </si>
+  <si>
+    <t>As you add staff, ensure staffing stays below 60% of revenue.</t>
+  </si>
+  <si>
+    <t>Facility Burden</t>
+  </si>
+  <si>
+    <t>Facility costs at 9% of revenue are well-managed and leave budget for programs.</t>
+  </si>
+  <si>
+    <t>Watch for rent escalation clauses that could push this higher over time.</t>
+  </si>
+  <si>
+    <t>Debt Affordability</t>
+  </si>
+  <si>
+    <t>DSCR of 48.12x provides comfortable coverage of debt payments with room to spare.</t>
+  </si>
+  <si>
+    <t>Maintain this ratio as you take on any additional debt.</t>
+  </si>
+  <si>
+    <t>Revenue Concentration</t>
+  </si>
+  <si>
+    <t>Revenue is anchored to enrollment-driven income — the strongest foundation for a school model. A focused revenue stream is a strength when backed by dependable demand.</t>
+  </si>
+  <si>
+    <t>Continue to pressure-test enrollment assumptions: recruitment pipeline, waitlist depth, retention rates, and collection reliability.</t>
+  </si>
+  <si>
+    <t>Reserve Strength</t>
+  </si>
+  <si>
+    <t>24.8 months of reserves by Year 5 — a strong buffer for unexpected costs.</t>
+  </si>
+  <si>
+    <t>Continue growing reserves toward 6 months for best-in-class financial health.</t>
+  </si>
+  <si>
+    <t>Summary</t>
+  </si>
+  <si>
+    <t>6 Healthy  |  0 Watch  |  1 Needs Attention</t>
   </si>
 </sst>
 </file>
@@ -658,11 +856,27 @@
     <numFmt numFmtId="167" formatCode="0.00x"/>
     <numFmt numFmtId="168" formatCode="0.0"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF1E293B"/>
+      <sz val="16"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF1E293B"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
@@ -679,12 +893,7 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <b/>
-      <color rgb="FF1E293B"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
+      <color rgb="FF1E3A5F"/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
@@ -723,8 +932,20 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <i/>
+      <color rgb="FF6B7280"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF16A34A"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -738,12 +959,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFDE8"/>
+        <fgColor rgb="FFDBEAFE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1E293B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE4EC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8F5E9"/>
       </patternFill>
     </fill>
   </fills>
@@ -789,46 +1020,84 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="10" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="10" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="10" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1171,6 +1440,163 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="B2:B29"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="4" customWidth="1"/>
+    <col min="2" max="2" width="80" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B4" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B5" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B6" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B7" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B8" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B9" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B10" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B11" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B12" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B13" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B14" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B15" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B16" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B17" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B18" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B19" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B20" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B21" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B22" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B23" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B24" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B25" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B26" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B27" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B28" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B29" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="portrait" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddHeader>&amp;L&amp;10&amp;BCivic Scholars Charter&amp;R&amp;8&amp;IInstructions</oddHeader>
+    <oddFooter>&amp;L&amp;8Built by SchoolStack Budget  •  budget.schoolstack.ai&amp;C&amp;8Page &amp;P of &amp;N&amp;R&amp;8&amp;D</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:J70"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
@@ -1181,1083 +1607,1083 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
+      <c r="A1" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" s="9">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="16" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="F16" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="G16" s="6"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B17" s="11">
+        <v>120</v>
+      </c>
+      <c r="C17" s="11">
+        <v>200</v>
+      </c>
+      <c r="D17" s="11">
+        <v>300</v>
+      </c>
+      <c r="E17" s="11">
+        <v>375</v>
+      </c>
+      <c r="F17" s="11">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="19" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="I19" s="6"/>
+      <c r="J19" s="6"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="D20" s="12">
+        <v>9500</v>
+      </c>
+      <c r="E20" s="13">
+        <v>0</v>
+      </c>
+      <c r="F20" s="9">
+        <v>12</v>
+      </c>
+      <c r="G20" s="13">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+      <c r="H20" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="D21" s="12">
+        <v>800</v>
+      </c>
+      <c r="E21" s="13">
+        <v>0</v>
+      </c>
+      <c r="F21" s="9">
+        <v>12</v>
+      </c>
+      <c r="G21" s="13">
+        <v>1</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="D22" s="12">
+        <v>1200</v>
+      </c>
+      <c r="E22" s="13">
+        <v>0</v>
+      </c>
+      <c r="F22" s="9">
+        <v>12</v>
+      </c>
+      <c r="G22" s="13">
+        <v>1</v>
+      </c>
+      <c r="H22" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="D23" s="12">
+        <v>100000</v>
+      </c>
+      <c r="E23" s="13">
+        <v>0</v>
+      </c>
+      <c r="F23" s="9">
+        <v>12</v>
+      </c>
+      <c r="G23" s="13">
+        <v>1</v>
+      </c>
+      <c r="H23" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="D24" s="12">
+        <v>30000</v>
+      </c>
+      <c r="E24" s="13">
+        <v>0</v>
+      </c>
+      <c r="F24" s="9">
+        <v>12</v>
+      </c>
+      <c r="G24" s="13">
+        <v>1</v>
+      </c>
+      <c r="H24" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="D25" s="12">
+        <v>300</v>
+      </c>
+      <c r="E25" s="13">
+        <v>0</v>
+      </c>
+      <c r="F25" s="9">
+        <v>12</v>
+      </c>
+      <c r="G25" s="13">
+        <v>1</v>
+      </c>
+      <c r="H25" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="G28" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="H28" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="I28" s="6" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D29" s="14">
+        <v>1</v>
+      </c>
+      <c r="E29" s="12">
+        <v>110000</v>
+      </c>
+      <c r="F29" s="13">
+        <v>0.28</v>
+      </c>
+      <c r="G29" s="13">
+        <v>0.0765</v>
+      </c>
+      <c r="H29" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="I29" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D30" s="14">
+        <v>1</v>
+      </c>
+      <c r="E30" s="12">
+        <v>90000</v>
+      </c>
+      <c r="F30" s="13">
+        <v>0.28</v>
+      </c>
+      <c r="G30" s="13">
+        <v>0.0765</v>
+      </c>
+      <c r="H30" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="I30" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D31" s="14">
+        <v>1</v>
+      </c>
+      <c r="E31" s="12">
+        <v>72000</v>
+      </c>
+      <c r="F31" s="13">
+        <v>0.28</v>
+      </c>
+      <c r="G31" s="13">
+        <v>0.0765</v>
+      </c>
+      <c r="H31" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="I31" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A32" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D32" s="14">
+        <v>6</v>
+      </c>
+      <c r="E32" s="12">
+        <v>52000</v>
+      </c>
+      <c r="F32" s="13">
+        <v>0.28</v>
+      </c>
+      <c r="G32" s="13">
+        <v>0.0765</v>
+      </c>
+      <c r="H32" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="I32" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A33" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D33" s="14">
+        <v>1</v>
+      </c>
+      <c r="E33" s="12">
+        <v>55000</v>
+      </c>
+      <c r="F33" s="13">
+        <v>0.28</v>
+      </c>
+      <c r="G33" s="13">
+        <v>0.0765</v>
+      </c>
+      <c r="H33" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="I33" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A34" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D34" s="14">
+        <v>3</v>
+      </c>
+      <c r="E34" s="12">
+        <v>30000</v>
+      </c>
+      <c r="F34" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="G34" s="13">
+        <v>0.0765</v>
+      </c>
+      <c r="H34" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="I34" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A35" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D35" s="14">
+        <v>1</v>
+      </c>
+      <c r="E35" s="12">
+        <v>55000</v>
+      </c>
+      <c r="F35" s="13">
+        <v>0.28</v>
+      </c>
+      <c r="G35" s="13">
+        <v>0.0765</v>
+      </c>
+      <c r="H35" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="I35" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A36" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D36" s="14">
         <v>2</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
+      <c r="E36" s="12">
+        <v>38000</v>
+      </c>
+      <c r="F36" s="13">
+        <v>0.25</v>
+      </c>
+      <c r="G36" s="13">
+        <v>0.0765</v>
+      </c>
+      <c r="H36" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="I36" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A37" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D37" s="14">
+        <v>1</v>
+      </c>
+      <c r="E37" s="12">
+        <v>55000</v>
+      </c>
+      <c r="F37" s="13">
+        <v>0.28</v>
+      </c>
+      <c r="G37" s="13">
+        <v>0.0765</v>
+      </c>
+      <c r="H37" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="I37" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="D39" s="6"/>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="B41" s="12">
+        <v>18000</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="B42" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="44" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="E44" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="F44" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="G44" s="6"/>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="D45" s="12">
+        <v>18000</v>
+      </c>
+      <c r="E45" s="13">
+        <v>0.03</v>
+      </c>
+      <c r="F45" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="D46" s="12">
+        <v>2500</v>
+      </c>
+      <c r="E46" s="13">
+        <v>0</v>
+      </c>
+      <c r="F46" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="D47" s="12">
+        <v>18000</v>
+      </c>
+      <c r="E47" s="13">
+        <v>0</v>
+      </c>
+      <c r="F47" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="B48" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="D48" s="12">
+        <v>1500</v>
+      </c>
+      <c r="E48" s="13">
+        <v>0</v>
+      </c>
+      <c r="F48" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="B49" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="D49" s="12">
+        <v>700</v>
+      </c>
+      <c r="E49" s="13">
+        <v>0</v>
+      </c>
+      <c r="F49" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="B50" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="D50" s="12">
+        <v>500</v>
+      </c>
+      <c r="E50" s="13">
+        <v>0</v>
+      </c>
+      <c r="F50" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="B51" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="D51" s="12">
+        <v>25000</v>
+      </c>
+      <c r="E51" s="13">
+        <v>0</v>
+      </c>
+      <c r="F51" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="B52" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="C52" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="D52" s="12">
+        <v>15000</v>
+      </c>
+      <c r="E52" s="13">
+        <v>0</v>
+      </c>
+      <c r="F52" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="B53" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="D53" s="12">
+        <v>20000</v>
+      </c>
+      <c r="E53" s="13">
+        <v>0</v>
+      </c>
+      <c r="F53" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="B54" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="C54" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="D54" s="12">
+        <v>800</v>
+      </c>
+      <c r="E54" s="13">
+        <v>0</v>
+      </c>
+      <c r="F54" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="B55" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="C55" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="D55" s="12">
+        <v>600</v>
+      </c>
+      <c r="E55" s="13">
+        <v>0</v>
+      </c>
+      <c r="F55" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="57" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="C57" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="D57" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="E57" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="F57" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="G57" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="H57" s="6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="B58" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C58" s="15">
+        <v>0</v>
+      </c>
+      <c r="D58" s="12">
+        <v>500000</v>
+      </c>
+      <c r="E58" s="16">
+        <v>0.0575</v>
+      </c>
+      <c r="F58" s="9">
         <v>15</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12" s="6">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="16" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="G16" s="3"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B17" s="8">
-        <v>120</v>
-      </c>
-      <c r="C17" s="8">
-        <v>200</v>
-      </c>
-      <c r="D17" s="8">
-        <v>300</v>
-      </c>
-      <c r="E17" s="8">
-        <v>375</v>
-      </c>
-      <c r="F17" s="8">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="19" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I19" s="3"/>
-      <c r="J19" s="3"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D20" s="9">
-        <v>9500</v>
-      </c>
-      <c r="E20" s="10">
-        <v>0</v>
-      </c>
-      <c r="F20" s="6">
-        <v>12</v>
-      </c>
-      <c r="G20" s="10">
-        <v>1</v>
-      </c>
-      <c r="H20" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D21" s="9">
-        <v>800</v>
-      </c>
-      <c r="E21" s="10">
-        <v>0</v>
-      </c>
-      <c r="F21" s="6">
-        <v>12</v>
-      </c>
-      <c r="G21" s="10">
-        <v>1</v>
-      </c>
-      <c r="H21" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D22" s="9">
-        <v>1200</v>
-      </c>
-      <c r="E22" s="10">
-        <v>0</v>
-      </c>
-      <c r="F22" s="6">
-        <v>12</v>
-      </c>
-      <c r="G22" s="10">
-        <v>1</v>
-      </c>
-      <c r="H22" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D23" s="9">
-        <v>100000</v>
-      </c>
-      <c r="E23" s="10">
-        <v>0</v>
-      </c>
-      <c r="F23" s="6">
-        <v>12</v>
-      </c>
-      <c r="G23" s="10">
-        <v>1</v>
-      </c>
-      <c r="H23" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D24" s="9">
-        <v>30000</v>
-      </c>
-      <c r="E24" s="10">
-        <v>0</v>
-      </c>
-      <c r="F24" s="6">
-        <v>12</v>
-      </c>
-      <c r="G24" s="10">
-        <v>1</v>
-      </c>
-      <c r="H24" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D25" s="9">
-        <v>300</v>
-      </c>
-      <c r="E25" s="10">
-        <v>0</v>
-      </c>
-      <c r="F25" s="6">
-        <v>12</v>
-      </c>
-      <c r="G25" s="10">
-        <v>1</v>
-      </c>
-      <c r="H25" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="28" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="I28" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D29" s="11">
-        <v>1</v>
-      </c>
-      <c r="E29" s="9">
-        <v>110000</v>
-      </c>
-      <c r="F29" s="10">
-        <v>0.28</v>
-      </c>
-      <c r="G29" s="10">
-        <v>0.0765</v>
-      </c>
-      <c r="H29" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="I29" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D30" s="11">
-        <v>1</v>
-      </c>
-      <c r="E30" s="9">
-        <v>90000</v>
-      </c>
-      <c r="F30" s="10">
-        <v>0.28</v>
-      </c>
-      <c r="G30" s="10">
-        <v>0.0765</v>
-      </c>
-      <c r="H30" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="I30" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D31" s="11">
-        <v>1</v>
-      </c>
-      <c r="E31" s="9">
-        <v>72000</v>
-      </c>
-      <c r="F31" s="10">
-        <v>0.28</v>
-      </c>
-      <c r="G31" s="10">
-        <v>0.0765</v>
-      </c>
-      <c r="H31" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="I31" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D32" s="11">
-        <v>6</v>
-      </c>
-      <c r="E32" s="9">
-        <v>52000</v>
-      </c>
-      <c r="F32" s="10">
-        <v>0.28</v>
-      </c>
-      <c r="G32" s="10">
-        <v>0.0765</v>
-      </c>
-      <c r="H32" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="I32" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A33" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D33" s="11">
-        <v>1</v>
-      </c>
-      <c r="E33" s="9">
-        <v>55000</v>
-      </c>
-      <c r="F33" s="10">
-        <v>0.28</v>
-      </c>
-      <c r="G33" s="10">
-        <v>0.0765</v>
-      </c>
-      <c r="H33" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="I33" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A34" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="B34" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D34" s="11">
-        <v>3</v>
-      </c>
-      <c r="E34" s="9">
-        <v>30000</v>
-      </c>
-      <c r="F34" s="10">
-        <v>0.2</v>
-      </c>
-      <c r="G34" s="10">
-        <v>0.0765</v>
-      </c>
-      <c r="H34" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="I34" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A35" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D35" s="11">
-        <v>1</v>
-      </c>
-      <c r="E35" s="9">
-        <v>55000</v>
-      </c>
-      <c r="F35" s="10">
-        <v>0.28</v>
-      </c>
-      <c r="G35" s="10">
-        <v>0.0765</v>
-      </c>
-      <c r="H35" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="I35" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A36" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D36" s="11">
-        <v>2</v>
-      </c>
-      <c r="E36" s="9">
-        <v>38000</v>
-      </c>
-      <c r="F36" s="10">
-        <v>0.25</v>
-      </c>
-      <c r="G36" s="10">
-        <v>0.0765</v>
-      </c>
-      <c r="H36" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="I36" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A37" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D37" s="11">
-        <v>1</v>
-      </c>
-      <c r="E37" s="9">
-        <v>55000</v>
-      </c>
-      <c r="F37" s="10">
-        <v>0.28</v>
-      </c>
-      <c r="G37" s="10">
-        <v>0.0765</v>
-      </c>
-      <c r="H37" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="I37" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="39" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="D39" s="3"/>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="B41" s="9">
-        <v>18000</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="B42" s="10">
+      <c r="G58" s="15">
+        <v>49825</v>
+      </c>
+      <c r="H58" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="B59" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="C59" s="12">
+        <v>75000</v>
+      </c>
+      <c r="D59" s="7">
+        <v>0</v>
+      </c>
+      <c r="E59" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="F59" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="G59" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="H59" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="B60" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="C60" s="12">
+        <v>40000</v>
+      </c>
+      <c r="D60" s="7">
+        <v>0</v>
+      </c>
+      <c r="E60" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="F60" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="G60" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="H60" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="62" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="B62" s="6"/>
+      <c r="C62" s="6"/>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="B63" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="B64" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="B65" s="14">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="C65" s="17" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="B66" s="13">
         <v>0.03</v>
       </c>
     </row>
-    <row r="44" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G44" s="3"/>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="B45" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="C45" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="D45" s="9">
-        <v>18000</v>
-      </c>
-      <c r="E45" s="10">
-        <v>0.03</v>
-      </c>
-      <c r="F45" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="B46" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="C46" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="D46" s="9">
-        <v>2500</v>
-      </c>
-      <c r="E46" s="10">
-        <v>0</v>
-      </c>
-      <c r="F46" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="B47" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="C47" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D47" s="9">
-        <v>18000</v>
-      </c>
-      <c r="E47" s="10">
-        <v>0</v>
-      </c>
-      <c r="F47" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B48" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="C48" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="D48" s="9">
-        <v>1500</v>
-      </c>
-      <c r="E48" s="10">
-        <v>0</v>
-      </c>
-      <c r="F48" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="B49" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="C49" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D49" s="9">
-        <v>700</v>
-      </c>
-      <c r="E49" s="10">
-        <v>0</v>
-      </c>
-      <c r="F49" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="B50" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="C50" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D50" s="9">
-        <v>500</v>
-      </c>
-      <c r="E50" s="10">
-        <v>0</v>
-      </c>
-      <c r="F50" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="B51" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="C51" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D51" s="9">
-        <v>25000</v>
-      </c>
-      <c r="E51" s="10">
-        <v>0</v>
-      </c>
-      <c r="F51" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="B52" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="C52" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D52" s="9">
-        <v>15000</v>
-      </c>
-      <c r="E52" s="10">
-        <v>0</v>
-      </c>
-      <c r="F52" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="B53" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="C53" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D53" s="9">
-        <v>20000</v>
-      </c>
-      <c r="E53" s="10">
-        <v>0</v>
-      </c>
-      <c r="F53" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="B54" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="C54" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D54" s="9">
-        <v>800</v>
-      </c>
-      <c r="E54" s="10">
-        <v>0</v>
-      </c>
-      <c r="F54" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="B55" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="C55" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D55" s="9">
-        <v>600</v>
-      </c>
-      <c r="E55" s="10">
-        <v>0</v>
-      </c>
-      <c r="F55" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="57" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D57" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="G57" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A58" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="B58" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="C58" s="12">
-        <v>0</v>
-      </c>
-      <c r="D58" s="9">
-        <v>500000</v>
-      </c>
-      <c r="E58" s="13">
-        <v>0.0575</v>
-      </c>
-      <c r="F58" s="6">
-        <v>15</v>
-      </c>
-      <c r="G58" s="12">
-        <v>49825</v>
-      </c>
-      <c r="H58" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A59" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="B59" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="C59" s="9">
-        <v>75000</v>
-      </c>
-      <c r="D59" s="4">
-        <v>0</v>
-      </c>
-      <c r="E59" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="F59" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="G59" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="H59" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A60" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="B60" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="C60" s="9">
-        <v>40000</v>
-      </c>
-      <c r="D60" s="4">
-        <v>0</v>
-      </c>
-      <c r="E60" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="F60" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="G60" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="H60" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="62" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="B62" s="3"/>
-      <c r="C62" s="3"/>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A63" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="B63" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A64" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="B64" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="B65" s="11">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="C65" s="14" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A66" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B66" s="10">
-        <v>0.03</v>
-      </c>
-    </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A67" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="B67" s="10">
+      <c r="A67" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B67" s="13">
         <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A68" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="B68" s="9">
+      <c r="A68" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="B68" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A70" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="B70" s="15"/>
-      <c r="C70" s="15"/>
-      <c r="D70" s="15"/>
-      <c r="E70" s="15"/>
-      <c r="F70" s="15"/>
-      <c r="G70" s="15"/>
+      <c r="A70" s="18" t="s">
+        <v>137</v>
+      </c>
+      <c r="B70" s="18"/>
+      <c r="C70" s="18"/>
+      <c r="D70" s="18"/>
+      <c r="E70" s="18"/>
+      <c r="F70" s="18"/>
+      <c r="G70" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -2275,7 +2701,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -2288,1604 +2714,1604 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
+      <c r="A1" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="B2" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="C2" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="D2" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="E2" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="F2" s="16" t="s">
-        <v>27</v>
+      <c r="A2" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="F2" s="19" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="B3" s="18">
+      <c r="A3" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="B3" s="21">
         <f>Assumptions!B17</f>
         <v>120</v>
       </c>
-      <c r="C3" s="18">
+      <c r="C3" s="21">
         <f>Assumptions!C17</f>
         <v>200</v>
       </c>
-      <c r="D3" s="18">
+      <c r="D3" s="21">
         <f>Assumptions!D17</f>
         <v>300</v>
       </c>
-      <c r="E3" s="18">
+      <c r="E3" s="21">
         <f>Assumptions!E17</f>
         <v>375</v>
       </c>
-      <c r="F3" s="18">
+      <c r="F3" s="21">
         <f>Assumptions!F17</f>
         <v>400</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
+      <c r="A5" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B6" s="12">
+      <c r="A6" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="15">
         <v>950000</v>
       </c>
-      <c r="C6" s="12">
+      <c r="C6" s="15">
         <v>1938000</v>
       </c>
-      <c r="D6" s="12">
+      <c r="D6" s="15">
         <v>2965200</v>
       </c>
-      <c r="E6" s="12">
+      <c r="E6" s="15">
         <v>3780375</v>
       </c>
-      <c r="F6" s="12">
+      <c r="F6" s="15">
         <v>4113200</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B7" s="12">
+      <c r="A7" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="B7" s="15">
         <v>80000</v>
       </c>
-      <c r="C7" s="12">
+      <c r="C7" s="15">
         <v>163200</v>
       </c>
-      <c r="D7" s="12">
+      <c r="D7" s="15">
         <v>249600</v>
       </c>
-      <c r="E7" s="12">
+      <c r="E7" s="15">
         <v>318375</v>
       </c>
-      <c r="F7" s="12">
+      <c r="F7" s="15">
         <v>346400</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B8" s="12">
+      <c r="A8" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="B8" s="15">
         <v>120000</v>
       </c>
-      <c r="C8" s="12">
+      <c r="C8" s="15">
         <v>244800</v>
       </c>
-      <c r="D8" s="12">
+      <c r="D8" s="15">
         <v>374400</v>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="15">
         <v>477375</v>
       </c>
-      <c r="F8" s="12">
+      <c r="F8" s="15">
         <v>519600</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B9" s="12">
+      <c r="A9" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="B9" s="15">
         <v>83333</v>
       </c>
-      <c r="C9" s="12">
+      <c r="C9" s="15">
         <v>75000</v>
       </c>
-      <c r="D9" s="12">
+      <c r="D9" s="15">
         <v>50000</v>
       </c>
-      <c r="E9" s="12">
-        <v>0</v>
-      </c>
-      <c r="F9" s="12">
+      <c r="E9" s="15">
+        <v>0</v>
+      </c>
+      <c r="F9" s="15">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B10" s="12">
+      <c r="A10" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="B10" s="15">
         <v>25000</v>
       </c>
-      <c r="C10" s="12">
+      <c r="C10" s="15">
         <v>40000</v>
       </c>
-      <c r="D10" s="12">
+      <c r="D10" s="15">
         <v>50000</v>
       </c>
-      <c r="E10" s="12">
+      <c r="E10" s="15">
         <v>60000</v>
       </c>
-      <c r="F10" s="12">
+      <c r="F10" s="15">
         <v>70000</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B11" s="12">
+      <c r="A11" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="B11" s="15">
         <v>30000</v>
       </c>
-      <c r="C11" s="12">
+      <c r="C11" s="15">
         <v>61800</v>
       </c>
-      <c r="D11" s="12">
+      <c r="D11" s="15">
         <v>95400</v>
       </c>
-      <c r="E11" s="12">
+      <c r="E11" s="15">
         <v>123000</v>
       </c>
-      <c r="F11" s="12">
+      <c r="F11" s="15">
         <v>135200</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="B12" s="19">
+      <c r="A12" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="B12" s="22">
         <f>SUM(B6:B11)</f>
         <v>1288333</v>
       </c>
-      <c r="C12" s="19">
+      <c r="C12" s="22">
         <f>SUM(C6:C11)</f>
         <v>2522800</v>
       </c>
-      <c r="D12" s="19">
+      <c r="D12" s="22">
         <f>SUM(D6:D11)</f>
         <v>3784600</v>
       </c>
-      <c r="E12" s="19">
+      <c r="E12" s="22">
         <f>SUM(E6:E11)</f>
         <v>4759125</v>
       </c>
-      <c r="F12" s="19">
+      <c r="F12" s="22">
         <f>SUM(F6:F11)</f>
         <v>5184400</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
+      <c r="A14" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="B15" s="12">
+      <c r="A15" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="B15" s="15">
         <v>124346</v>
       </c>
-      <c r="C15" s="12">
+      <c r="C15" s="15">
         <v>149215</v>
       </c>
-      <c r="D15" s="12">
+      <c r="D15" s="15">
         <v>149215</v>
       </c>
-      <c r="E15" s="12">
+      <c r="E15" s="15">
         <v>149215</v>
       </c>
-      <c r="F15" s="12">
+      <c r="F15" s="15">
         <v>149215</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="B16" s="12">
+      <c r="A16" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="B16" s="15">
         <v>101738</v>
       </c>
-      <c r="C16" s="12">
+      <c r="C16" s="15">
         <v>122085</v>
       </c>
-      <c r="D16" s="12">
+      <c r="D16" s="15">
         <v>122085</v>
       </c>
-      <c r="E16" s="12">
+      <c r="E16" s="15">
         <v>122085</v>
       </c>
-      <c r="F16" s="12">
+      <c r="F16" s="15">
         <v>122085</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="B17" s="12">
+      <c r="A17" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="B17" s="15">
         <v>81390</v>
       </c>
-      <c r="C17" s="12">
+      <c r="C17" s="15">
         <v>97668</v>
       </c>
-      <c r="D17" s="12">
+      <c r="D17" s="15">
         <v>97668</v>
       </c>
-      <c r="E17" s="12">
+      <c r="E17" s="15">
         <v>97668</v>
       </c>
-      <c r="F17" s="12">
+      <c r="F17" s="15">
         <v>97668</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="B18" s="12">
+      <c r="A18" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="B18" s="15">
         <v>352690</v>
       </c>
-      <c r="C18" s="12">
+      <c r="C18" s="15">
         <v>423228</v>
       </c>
-      <c r="D18" s="12">
+      <c r="D18" s="15">
         <v>423228</v>
       </c>
-      <c r="E18" s="12">
+      <c r="E18" s="15">
         <v>423228</v>
       </c>
-      <c r="F18" s="12">
+      <c r="F18" s="15">
         <v>423228</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="B19" s="12">
+      <c r="A19" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="B19" s="15">
         <v>62173</v>
       </c>
-      <c r="C19" s="12">
+      <c r="C19" s="15">
         <v>74608</v>
       </c>
-      <c r="D19" s="12">
+      <c r="D19" s="15">
         <v>74608</v>
       </c>
-      <c r="E19" s="12">
+      <c r="E19" s="15">
         <v>74608</v>
       </c>
-      <c r="F19" s="12">
+      <c r="F19" s="15">
         <v>74608</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="B20" s="12">
+      <c r="A20" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="B20" s="15">
         <v>95738</v>
       </c>
-      <c r="C20" s="12">
+      <c r="C20" s="15">
         <v>114885</v>
       </c>
-      <c r="D20" s="12">
+      <c r="D20" s="15">
         <v>114885</v>
       </c>
-      <c r="E20" s="12">
+      <c r="E20" s="15">
         <v>114885</v>
       </c>
-      <c r="F20" s="12">
+      <c r="F20" s="15">
         <v>114885</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="B21" s="12">
+      <c r="A21" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="B21" s="15">
         <v>62173</v>
       </c>
-      <c r="C21" s="12">
+      <c r="C21" s="15">
         <v>74608</v>
       </c>
-      <c r="D21" s="12">
+      <c r="D21" s="15">
         <v>74608</v>
       </c>
-      <c r="E21" s="12">
+      <c r="E21" s="15">
         <v>74608</v>
       </c>
-      <c r="F21" s="12">
+      <c r="F21" s="15">
         <v>74608</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="B22" s="12">
+      <c r="A22" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="B22" s="15">
         <v>84012</v>
       </c>
-      <c r="C22" s="12">
+      <c r="C22" s="15">
         <v>100814</v>
       </c>
-      <c r="D22" s="12">
+      <c r="D22" s="15">
         <v>100814</v>
       </c>
-      <c r="E22" s="12">
+      <c r="E22" s="15">
         <v>100814</v>
       </c>
-      <c r="F22" s="12">
+      <c r="F22" s="15">
         <v>100814</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="B23" s="12">
+      <c r="A23" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="B23" s="15">
         <v>62173</v>
       </c>
-      <c r="C23" s="12">
+      <c r="C23" s="15">
         <v>74608</v>
       </c>
-      <c r="D23" s="12">
+      <c r="D23" s="15">
         <v>74608</v>
       </c>
-      <c r="E23" s="12">
+      <c r="E23" s="15">
         <v>74608</v>
       </c>
-      <c r="F23" s="12">
+      <c r="F23" s="15">
         <v>74608</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="B24" s="19">
+      <c r="A24" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="B24" s="22">
         <f>SUM(B15:B23)</f>
         <v>1026431</v>
       </c>
-      <c r="C24" s="19">
+      <c r="C24" s="22">
         <f>SUM(C15:C23)</f>
         <v>1231718</v>
       </c>
-      <c r="D24" s="19">
+      <c r="D24" s="22">
         <f>SUM(D15:D23)</f>
         <v>1231718</v>
       </c>
-      <c r="E24" s="19">
+      <c r="E24" s="22">
         <f>SUM(E15:E23)</f>
         <v>1231718</v>
       </c>
-      <c r="F24" s="19">
+      <c r="F24" s="22">
         <f>SUM(F15:F23)</f>
         <v>1231718</v>
       </c>
     </row>
     <row r="26" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B26" s="3"/>
-      <c r="C26" s="3"/>
-      <c r="D26" s="3"/>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
+      <c r="A26" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B26" s="6"/>
+      <c r="C26" s="6"/>
+      <c r="D26" s="6"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="6"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B27" s="4"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4"/>
-      <c r="F27" s="4"/>
+      <c r="A27" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="B27" s="7"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
+      <c r="F27" s="7"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="B28" s="12">
+      <c r="A28" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="B28" s="15">
         <v>70000</v>
       </c>
-      <c r="C28" s="12">
+      <c r="C28" s="15">
         <v>144200</v>
       </c>
-      <c r="D28" s="12">
+      <c r="D28" s="15">
         <v>222900</v>
       </c>
-      <c r="E28" s="12">
+      <c r="E28" s="15">
         <v>286875</v>
       </c>
-      <c r="F28" s="12">
+      <c r="F28" s="15">
         <v>315200</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="20" t="s">
-        <v>131</v>
-      </c>
-      <c r="B29" s="21">
+      <c r="A29" s="23" t="s">
+        <v>153</v>
+      </c>
+      <c r="B29" s="24">
         <v>70000</v>
       </c>
-      <c r="C29" s="21">
+      <c r="C29" s="24">
         <v>144200</v>
       </c>
-      <c r="D29" s="21">
+      <c r="D29" s="24">
         <v>222900</v>
       </c>
-      <c r="E29" s="21">
+      <c r="E29" s="24">
         <v>286875</v>
       </c>
-      <c r="F29" s="21">
+      <c r="F29" s="24">
         <v>315200</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B30" s="4"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="4"/>
-      <c r="E30" s="4"/>
-      <c r="F30" s="4"/>
+      <c r="A30" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="B30" s="7"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
+      <c r="F30" s="7"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="B31" s="12">
+      <c r="A31" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="B31" s="15">
         <v>50000</v>
       </c>
-      <c r="C31" s="12">
+      <c r="C31" s="15">
         <v>103000</v>
       </c>
-      <c r="D31" s="12">
+      <c r="D31" s="15">
         <v>159000</v>
       </c>
-      <c r="E31" s="12">
+      <c r="E31" s="15">
         <v>204750</v>
       </c>
-      <c r="F31" s="12">
+      <c r="F31" s="15">
         <v>224800</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="20" t="s">
-        <v>133</v>
-      </c>
-      <c r="B32" s="21">
+      <c r="A32" s="23" t="s">
+        <v>155</v>
+      </c>
+      <c r="B32" s="24">
         <v>50000</v>
       </c>
-      <c r="C32" s="21">
+      <c r="C32" s="24">
         <v>103000</v>
       </c>
-      <c r="D32" s="21">
+      <c r="D32" s="24">
         <v>159000</v>
       </c>
-      <c r="E32" s="21">
+      <c r="E32" s="24">
         <v>204750</v>
       </c>
-      <c r="F32" s="21">
+      <c r="F32" s="24">
         <v>224800</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="B33" s="4"/>
-      <c r="C33" s="4"/>
-      <c r="D33" s="4"/>
-      <c r="E33" s="4"/>
-      <c r="F33" s="4"/>
+      <c r="A33" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="B33" s="7"/>
+      <c r="C33" s="7"/>
+      <c r="D33" s="7"/>
+      <c r="E33" s="7"/>
+      <c r="F33" s="7"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="B34" s="12">
+      <c r="A34" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="B34" s="15">
         <v>180000</v>
       </c>
-      <c r="C34" s="12">
+      <c r="C34" s="15">
         <v>222480</v>
       </c>
-      <c r="D34" s="12">
+      <c r="D34" s="15">
         <v>229154</v>
       </c>
-      <c r="E34" s="12">
+      <c r="E34" s="15">
         <v>236029</v>
       </c>
-      <c r="F34" s="12">
+      <c r="F34" s="15">
         <v>243110</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="B35" s="12">
+      <c r="A35" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="B35" s="15">
         <v>25000</v>
       </c>
-      <c r="C35" s="12">
+      <c r="C35" s="15">
         <v>30900</v>
       </c>
-      <c r="D35" s="12">
+      <c r="D35" s="15">
         <v>31824</v>
       </c>
-      <c r="E35" s="12">
+      <c r="E35" s="15">
         <v>32784</v>
       </c>
-      <c r="F35" s="12">
+      <c r="F35" s="15">
         <v>33768</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="B36" s="12">
+      <c r="A36" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="B36" s="15">
         <v>15000</v>
       </c>
-      <c r="C36" s="12">
+      <c r="C36" s="15">
         <v>18540</v>
       </c>
-      <c r="D36" s="12">
+      <c r="D36" s="15">
         <v>19096</v>
       </c>
-      <c r="E36" s="12">
+      <c r="E36" s="15">
         <v>19669</v>
       </c>
-      <c r="F36" s="12">
+      <c r="F36" s="15">
         <v>20259</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="B37" s="12">
+      <c r="A37" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="B37" s="15">
         <v>15000</v>
       </c>
-      <c r="C37" s="12">
+      <c r="C37" s="15">
         <v>18540</v>
       </c>
-      <c r="D37" s="12">
+      <c r="D37" s="15">
         <v>19092</v>
       </c>
-      <c r="E37" s="12">
+      <c r="E37" s="15">
         <v>19668</v>
       </c>
-      <c r="F37" s="12">
+      <c r="F37" s="15">
         <v>20256</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="20" t="s">
-        <v>138</v>
-      </c>
-      <c r="B38" s="21">
+      <c r="A38" s="23" t="s">
+        <v>160</v>
+      </c>
+      <c r="B38" s="24">
         <v>235000</v>
       </c>
-      <c r="C38" s="21">
+      <c r="C38" s="24">
         <v>290460</v>
       </c>
-      <c r="D38" s="21">
+      <c r="D38" s="24">
         <v>299166</v>
       </c>
-      <c r="E38" s="21">
+      <c r="E38" s="24">
         <v>308150</v>
       </c>
-      <c r="F38" s="21">
+      <c r="F38" s="24">
         <v>317393</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="B39" s="4"/>
-      <c r="C39" s="4"/>
-      <c r="D39" s="4"/>
-      <c r="E39" s="4"/>
-      <c r="F39" s="4"/>
+      <c r="A39" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="B39" s="7"/>
+      <c r="C39" s="7"/>
+      <c r="D39" s="7"/>
+      <c r="E39" s="7"/>
+      <c r="F39" s="7"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="B40" s="12">
+      <c r="A40" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="B40" s="15">
         <v>20833</v>
       </c>
-      <c r="C40" s="12">
+      <c r="C40" s="15">
         <v>25750</v>
       </c>
-      <c r="D40" s="12">
+      <c r="D40" s="15">
         <v>26523</v>
       </c>
-      <c r="E40" s="12">
+      <c r="E40" s="15">
         <v>27318</v>
       </c>
-      <c r="F40" s="12">
+      <c r="F40" s="15">
         <v>28138</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="B41" s="12">
+      <c r="A41" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="B41" s="15">
         <v>12500</v>
       </c>
-      <c r="C41" s="12">
+      <c r="C41" s="15">
         <v>15450</v>
       </c>
-      <c r="D41" s="12">
+      <c r="D41" s="15">
         <v>15914</v>
       </c>
-      <c r="E41" s="12">
+      <c r="E41" s="15">
         <v>16391</v>
       </c>
-      <c r="F41" s="12">
+      <c r="F41" s="15">
         <v>16883</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="B42" s="12">
+      <c r="A42" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="B42" s="15">
         <v>16667</v>
       </c>
-      <c r="C42" s="12">
+      <c r="C42" s="15">
         <v>20600</v>
       </c>
-      <c r="D42" s="12">
+      <c r="D42" s="15">
         <v>21218</v>
       </c>
-      <c r="E42" s="12">
+      <c r="E42" s="15">
         <v>21855</v>
       </c>
-      <c r="F42" s="12">
+      <c r="F42" s="15">
         <v>22510</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="B43" s="12">
+      <c r="A43" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="B43" s="15">
         <v>80000</v>
       </c>
-      <c r="C43" s="12">
+      <c r="C43" s="15">
         <v>164800</v>
       </c>
-      <c r="D43" s="12">
+      <c r="D43" s="15">
         <v>254700</v>
       </c>
-      <c r="E43" s="12">
+      <c r="E43" s="15">
         <v>327750</v>
       </c>
-      <c r="F43" s="12">
+      <c r="F43" s="15">
         <v>360000</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="B44" s="12">
+      <c r="A44" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="B44" s="15">
         <v>60000</v>
       </c>
-      <c r="C44" s="12">
+      <c r="C44" s="15">
         <v>123600</v>
       </c>
-      <c r="D44" s="12">
+      <c r="D44" s="15">
         <v>191100</v>
       </c>
-      <c r="E44" s="12">
+      <c r="E44" s="15">
         <v>246000</v>
       </c>
-      <c r="F44" s="12">
+      <c r="F44" s="15">
         <v>270000</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="20" t="s">
-        <v>144</v>
-      </c>
-      <c r="B45" s="21">
+      <c r="A45" s="23" t="s">
+        <v>166</v>
+      </c>
+      <c r="B45" s="24">
         <v>190000</v>
       </c>
-      <c r="C45" s="21">
+      <c r="C45" s="24">
         <v>350200</v>
       </c>
-      <c r="D45" s="21">
+      <c r="D45" s="24">
         <v>509455</v>
       </c>
-      <c r="E45" s="21">
+      <c r="E45" s="24">
         <v>639314</v>
       </c>
-      <c r="F45" s="21">
+      <c r="F45" s="24">
         <v>697531</v>
       </c>
     </row>
     <row r="46" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="B46" s="19">
+      <c r="A46" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="B46" s="22">
         <f>B29+B32+B38+B45</f>
         <v>545000</v>
       </c>
-      <c r="C46" s="19">
+      <c r="C46" s="22">
         <f>C29+C32+C38+C45</f>
         <v>887860</v>
       </c>
-      <c r="D46" s="19">
+      <c r="D46" s="22">
         <f>D29+D32+D38+D45</f>
         <v>1190521</v>
       </c>
-      <c r="E46" s="19">
+      <c r="E46" s="22">
         <f>E29+E32+E38+E45</f>
         <v>1439089</v>
       </c>
-      <c r="F46" s="19">
+      <c r="F46" s="22">
         <f>F29+F32+F38+F45</f>
         <v>1554924</v>
       </c>
     </row>
     <row r="48" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="B48" s="3"/>
-      <c r="C48" s="3"/>
-      <c r="D48" s="3"/>
-      <c r="E48" s="3"/>
-      <c r="F48" s="3"/>
+      <c r="A48" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="B48" s="6"/>
+      <c r="C48" s="6"/>
+      <c r="D48" s="6"/>
+      <c r="E48" s="6"/>
+      <c r="F48" s="6"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="B49" s="12">
+      <c r="A49" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="B49" s="15">
         <v>49825</v>
       </c>
-      <c r="C49" s="12">
+      <c r="C49" s="15">
         <v>49825</v>
       </c>
-      <c r="D49" s="12">
+      <c r="D49" s="15">
         <v>49825</v>
       </c>
-      <c r="E49" s="12">
+      <c r="E49" s="15">
         <v>49825</v>
       </c>
-      <c r="F49" s="12">
+      <c r="F49" s="15">
         <v>49825</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="B50" s="12">
+      <c r="A50" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="B50" s="15">
         <v>75000</v>
       </c>
-      <c r="C50" s="12">
+      <c r="C50" s="15">
         <v>25000</v>
       </c>
-      <c r="D50" s="12">
+      <c r="D50" s="15">
         <v>30000</v>
       </c>
-      <c r="E50" s="12">
+      <c r="E50" s="15">
         <v>15000</v>
       </c>
-      <c r="F50" s="12">
+      <c r="F50" s="15">
         <v>10000</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="B51" s="12">
+      <c r="A51" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="B51" s="15">
         <v>40000</v>
       </c>
-      <c r="C51" s="12">
+      <c r="C51" s="15">
         <v>15000</v>
       </c>
-      <c r="D51" s="12">
+      <c r="D51" s="15">
         <v>10000</v>
       </c>
-      <c r="E51" s="12">
+      <c r="E51" s="15">
         <v>10000</v>
       </c>
-      <c r="F51" s="12">
+      <c r="F51" s="15">
         <v>10000</v>
       </c>
     </row>
     <row r="52" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="B52" s="19">
+      <c r="A52" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="B52" s="22">
         <f>SUM(B49:B51)</f>
         <v>164825</v>
       </c>
-      <c r="C52" s="19">
+      <c r="C52" s="22">
         <f>SUM(C49:C51)</f>
         <v>89825</v>
       </c>
-      <c r="D52" s="19">
+      <c r="D52" s="22">
         <f>SUM(D49:D51)</f>
         <v>89825</v>
       </c>
-      <c r="E52" s="19">
+      <c r="E52" s="22">
         <f>SUM(E49:E51)</f>
         <v>74825</v>
       </c>
-      <c r="F52" s="19">
+      <c r="F52" s="22">
         <f>SUM(F49:F51)</f>
         <v>69825</v>
       </c>
     </row>
     <row r="54" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="B54" s="3"/>
-      <c r="C54" s="3"/>
-      <c r="D54" s="3"/>
-      <c r="E54" s="3"/>
-      <c r="F54" s="3"/>
+      <c r="A54" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="B54" s="6"/>
+      <c r="C54" s="6"/>
+      <c r="D54" s="6"/>
+      <c r="E54" s="6"/>
+      <c r="F54" s="6"/>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="17" t="s">
-        <v>149</v>
-      </c>
-      <c r="B55" s="21">
+      <c r="A55" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="B55" s="24">
         <f>B12</f>
         <v>1288333</v>
       </c>
-      <c r="C55" s="21">
+      <c r="C55" s="24">
         <f>C12</f>
         <v>2522800</v>
       </c>
-      <c r="D55" s="21">
+      <c r="D55" s="24">
         <f>D12</f>
         <v>3784600</v>
       </c>
-      <c r="E55" s="21">
+      <c r="E55" s="24">
         <f>E12</f>
         <v>4759125</v>
       </c>
-      <c r="F55" s="21">
+      <c r="F55" s="24">
         <f>F12</f>
         <v>5184400</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="B56" s="12">
+      <c r="A56" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="B56" s="15">
         <f>B24</f>
         <v>1026431</v>
       </c>
-      <c r="C56" s="12">
+      <c r="C56" s="15">
         <f>C24</f>
         <v>1231718</v>
       </c>
-      <c r="D56" s="12">
+      <c r="D56" s="15">
         <f>D24</f>
         <v>1231718</v>
       </c>
-      <c r="E56" s="12">
+      <c r="E56" s="15">
         <f>E24</f>
         <v>1231718</v>
       </c>
-      <c r="F56" s="12">
+      <c r="F56" s="15">
         <f>F24</f>
         <v>1231718</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="B57" s="12">
+      <c r="A57" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="B57" s="15">
         <f>B46</f>
         <v>545000</v>
       </c>
-      <c r="C57" s="12">
+      <c r="C57" s="15">
         <f>C46</f>
         <v>887860</v>
       </c>
-      <c r="D57" s="12">
+      <c r="D57" s="15">
         <f>D46</f>
         <v>1190521</v>
       </c>
-      <c r="E57" s="12">
+      <c r="E57" s="15">
         <f>E46</f>
         <v>1439089</v>
       </c>
-      <c r="F57" s="12">
+      <c r="F57" s="15">
         <f>F46</f>
         <v>1554924</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="B58" s="12">
+      <c r="A58" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="B58" s="15">
         <f>B52</f>
         <v>164825</v>
       </c>
-      <c r="C58" s="12">
+      <c r="C58" s="15">
         <f>C52</f>
         <v>89825</v>
       </c>
-      <c r="D58" s="12">
+      <c r="D58" s="15">
         <f>D52</f>
         <v>89825</v>
       </c>
-      <c r="E58" s="12">
+      <c r="E58" s="15">
         <f>E52</f>
         <v>74825</v>
       </c>
-      <c r="F58" s="12">
+      <c r="F58" s="15">
         <f>F52</f>
         <v>69825</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="17" t="s">
-        <v>153</v>
-      </c>
-      <c r="B59" s="21">
+      <c r="A59" s="20" t="s">
+        <v>175</v>
+      </c>
+      <c r="B59" s="24">
         <f>B56+B57+B58</f>
         <v>1736256</v>
       </c>
-      <c r="C59" s="21">
+      <c r="C59" s="24">
         <f>C56+C57+C58</f>
         <v>2209403</v>
       </c>
-      <c r="D59" s="21">
+      <c r="D59" s="24">
         <f>D56+D57+D58</f>
         <v>2512064</v>
       </c>
-      <c r="E59" s="21">
+      <c r="E59" s="24">
         <f>E56+E57+E58</f>
         <v>2745632</v>
       </c>
-      <c r="F59" s="21">
+      <c r="F59" s="24">
         <f>F56+F57+F58</f>
         <v>2856467</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>40</v>
+        <v>5</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="B61" s="23">
+      <c r="A61" s="25" t="s">
+        <v>176</v>
+      </c>
+      <c r="B61" s="26">
         <f>B55-B59</f>
         <v>-447923</v>
       </c>
-      <c r="C61" s="24">
+      <c r="C61" s="27">
         <f>C55-C59</f>
         <v>313397</v>
       </c>
-      <c r="D61" s="24">
+      <c r="D61" s="27">
         <f>D55-D59</f>
         <v>1272536</v>
       </c>
-      <c r="E61" s="24">
+      <c r="E61" s="27">
         <f>E55-E59</f>
         <v>2013493</v>
       </c>
-      <c r="F61" s="24">
+      <c r="F61" s="27">
         <f>F55-F59</f>
         <v>2327933</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="B62" s="25">
+      <c r="A62" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="B62" s="28">
         <f>IF(B55=0,"",B61/B55)</f>
         <v>-0.35</v>
       </c>
-      <c r="C62" s="25">
+      <c r="C62" s="28">
         <f>IF(C55=0,"",C61/C55)</f>
         <v>0.12</v>
       </c>
-      <c r="D62" s="25">
+      <c r="D62" s="28">
         <f>IF(D55=0,"",D61/D55)</f>
         <v>0.34</v>
       </c>
-      <c r="E62" s="25">
+      <c r="E62" s="28">
         <f>IF(E55=0,"",E61/E55)</f>
         <v>0.42</v>
       </c>
-      <c r="F62" s="25">
+      <c r="F62" s="28">
         <f>IF(F55=0,"",F61/F55)</f>
         <v>0.45</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="B63" s="12">
+      <c r="A63" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="B63" s="15">
         <f>B61</f>
         <v>-447923</v>
       </c>
-      <c r="C63" s="12">
+      <c r="C63" s="15">
         <f>B63+C61</f>
         <v>-134526</v>
       </c>
-      <c r="D63" s="12">
+      <c r="D63" s="15">
         <f>C63+D61</f>
         <v>1138010</v>
       </c>
-      <c r="E63" s="12">
+      <c r="E63" s="15">
         <f>D63+E61</f>
         <v>3151503</v>
       </c>
-      <c r="F63" s="12">
+      <c r="F63" s="15">
         <f>E63+F61</f>
         <v>5479436</v>
       </c>
     </row>
     <row r="65" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A65" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="B65" s="3"/>
-      <c r="C65" s="3"/>
-      <c r="D65" s="3"/>
-      <c r="E65" s="3"/>
-      <c r="F65" s="3"/>
+      <c r="A65" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="B65" s="6"/>
+      <c r="C65" s="6"/>
+      <c r="D65" s="6"/>
+      <c r="E65" s="6"/>
+      <c r="F65" s="6"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A66" s="17" t="s">
-        <v>158</v>
-      </c>
-      <c r="B66" s="21">
+      <c r="A66" s="20" t="s">
+        <v>180</v>
+      </c>
+      <c r="B66" s="24">
         <f>B55-B56-B57</f>
         <v>-283098</v>
       </c>
-      <c r="C66" s="21">
+      <c r="C66" s="24">
         <f>C55-C56-C57</f>
         <v>403222</v>
       </c>
-      <c r="D66" s="21">
+      <c r="D66" s="24">
         <f>D55-D56-D57</f>
         <v>1362361</v>
       </c>
-      <c r="E66" s="21">
+      <c r="E66" s="24">
         <f>E55-E56-E57</f>
         <v>2088318</v>
       </c>
-      <c r="F66" s="21">
+      <c r="F66" s="24">
         <f>F55-F56-F57</f>
         <v>2397758</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A67" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="B67" s="12">
+      <c r="A67" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="B67" s="15">
         <f>B58</f>
         <v>164825</v>
       </c>
-      <c r="C67" s="12">
+      <c r="C67" s="15">
         <f>C58</f>
         <v>89825</v>
       </c>
-      <c r="D67" s="12">
+      <c r="D67" s="15">
         <f>D58</f>
         <v>89825</v>
       </c>
-      <c r="E67" s="12">
+      <c r="E67" s="15">
         <f>E58</f>
         <v>74825</v>
       </c>
-      <c r="F67" s="12">
+      <c r="F67" s="15">
         <f>F58</f>
         <v>69825</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A68" s="17" t="s">
-        <v>160</v>
-      </c>
-      <c r="B68" s="26">
+      <c r="A68" s="20" t="s">
+        <v>182</v>
+      </c>
+      <c r="B68" s="29">
         <f>IF(B67=0,"N/A",B66/B67)</f>
         <v>-1.72</v>
       </c>
-      <c r="C68" s="26">
+      <c r="C68" s="29">
         <f>IF(C67=0,"N/A",C66/C67)</f>
         <v>4.49</v>
       </c>
-      <c r="D68" s="26">
+      <c r="D68" s="29">
         <f>IF(D67=0,"N/A",D66/D67)</f>
         <v>15.17</v>
       </c>
-      <c r="E68" s="26">
+      <c r="E68" s="29">
         <f>IF(E67=0,"N/A",E66/E67)</f>
         <v>27.91</v>
       </c>
-      <c r="F68" s="26">
+      <c r="F68" s="29">
         <f>IF(F67=0,"N/A",F66/F67)</f>
         <v>34.34</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A69" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="B69" s="12" t="str">
+      <c r="A69" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="B69" s="15" t="str">
         <f>Assumptions!B68</f>
         <v>0</v>
       </c>
-      <c r="C69" s="12">
+      <c r="C69" s="15">
         <f>B70</f>
         <v>-447923</v>
       </c>
-      <c r="D69" s="12">
+      <c r="D69" s="15">
         <f>C70</f>
         <v>-134526</v>
       </c>
-      <c r="E69" s="12">
+      <c r="E69" s="15">
         <f>D70</f>
         <v>1138010</v>
       </c>
-      <c r="F69" s="12">
+      <c r="F69" s="15">
         <f>E70</f>
         <v>3151503</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A70" s="17" t="s">
-        <v>161</v>
-      </c>
-      <c r="B70" s="21">
+      <c r="A70" s="20" t="s">
+        <v>183</v>
+      </c>
+      <c r="B70" s="24">
         <f>B69+B61</f>
         <v>-447923</v>
       </c>
-      <c r="C70" s="21">
+      <c r="C70" s="24">
         <f>C69+C61</f>
         <v>-134526</v>
       </c>
-      <c r="D70" s="21">
+      <c r="D70" s="24">
         <f>D69+D61</f>
         <v>1138010</v>
       </c>
-      <c r="E70" s="21">
+      <c r="E70" s="24">
         <f>E69+E61</f>
         <v>3151503</v>
       </c>
-      <c r="F70" s="21">
+      <c r="F70" s="24">
         <f>F69+F61</f>
         <v>5479436</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A71" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="B71" s="27">
+      <c r="A71" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="B71" s="30">
         <f>IF(B59=0,"",B70/B59*365)</f>
         <v>-94</v>
       </c>
-      <c r="C71" s="27">
+      <c r="C71" s="30">
         <f>IF(C59=0,"",C70/C59*365)</f>
         <v>-22</v>
       </c>
-      <c r="D71" s="27">
+      <c r="D71" s="30">
         <f>IF(D59=0,"",D70/D59*365)</f>
         <v>165</v>
       </c>
-      <c r="E71" s="27">
+      <c r="E71" s="30">
         <f>IF(E59=0,"",E70/E59*365)</f>
         <v>419</v>
       </c>
-      <c r="F71" s="27">
+      <c r="F71" s="30">
         <f>IF(F59=0,"",F70/F59*365)</f>
         <v>700</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A72" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="B72" s="28">
+      <c r="A72" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="B72" s="31">
         <f>IF(B59=0,"",B70/(B59/12))</f>
         <v>-3.1</v>
       </c>
-      <c r="C72" s="28">
+      <c r="C72" s="31">
         <f>IF(C59=0,"",C70/(C59/12))</f>
         <v>-0.7</v>
       </c>
-      <c r="D72" s="28">
+      <c r="D72" s="31">
         <f>IF(D59=0,"",D70/(D59/12))</f>
         <v>5.4</v>
       </c>
-      <c r="E72" s="28">
+      <c r="E72" s="31">
         <f>IF(E59=0,"",E70/(E59/12))</f>
         <v>13.8</v>
       </c>
-      <c r="F72" s="28">
+      <c r="F72" s="31">
         <f>IF(F59=0,"",F70/(F59/12))</f>
         <v>23</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A73" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="B73" s="25">
+      <c r="A73" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="B73" s="28">
         <f>IF(Assumptions!B12=0,"",B3/Assumptions!B12)</f>
         <v>0.3</v>
       </c>
-      <c r="C73" s="25">
+      <c r="C73" s="28">
         <f>IF(Assumptions!B12=0,"",C3/Assumptions!B12)</f>
         <v>0.5</v>
       </c>
-      <c r="D73" s="25">
+      <c r="D73" s="28">
         <f>IF(Assumptions!B12=0,"",D3/Assumptions!B12)</f>
         <v>0.75</v>
       </c>
-      <c r="E73" s="25">
+      <c r="E73" s="28">
         <f>IF(Assumptions!B12=0,"",E3/Assumptions!B12)</f>
         <v>0.94</v>
       </c>
-      <c r="F73" s="25">
+      <c r="F73" s="28">
         <f>IF(Assumptions!B12=0,"",F3/Assumptions!B12)</f>
         <v>1</v>
       </c>
     </row>
     <row r="75" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A75" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="B75" s="3"/>
-      <c r="C75" s="3"/>
-      <c r="D75" s="3"/>
-      <c r="E75" s="3"/>
-      <c r="F75" s="3"/>
+      <c r="A75" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="B75" s="6"/>
+      <c r="C75" s="6"/>
+      <c r="D75" s="6"/>
+      <c r="E75" s="6"/>
+      <c r="F75" s="6"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A76" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="B76" s="4" t="str">
+      <c r="A76" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="B76" s="7" t="str">
         <f>IF(B67=0,"N/A",IF(B68&gt;=1.2,"PASS","FAIL"))</f>
         <v>FAIL</v>
       </c>
-      <c r="C76" s="4" t="str">
+      <c r="C76" s="7" t="str">
         <f>IF(C67=0,"N/A",IF(C68&gt;=1.2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="D76" s="4" t="str">
+      <c r="D76" s="7" t="str">
         <f>IF(D67=0,"N/A",IF(D68&gt;=1.2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="E76" s="4" t="str">
+      <c r="E76" s="7" t="str">
         <f>IF(E67=0,"N/A",IF(E68&gt;=1.2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="F76" s="4" t="str">
+      <c r="F76" s="7" t="str">
         <f>IF(F67=0,"N/A",IF(F68&gt;=1.2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A77" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="B77" s="4" t="str">
+      <c r="A77" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="B77" s="7" t="str">
         <f>IF(B61&gt;0,"PASS","FAIL")</f>
         <v>FAIL</v>
       </c>
-      <c r="C77" s="4" t="str">
+      <c r="C77" s="7" t="str">
         <f>IF(C61&gt;0,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-      <c r="D77" s="4" t="str">
+      <c r="D77" s="7" t="str">
         <f>IF(D61&gt;0,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-      <c r="E77" s="4" t="str">
+      <c r="E77" s="7" t="str">
         <f>IF(E61&gt;0,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-      <c r="F77" s="4" t="str">
+      <c r="F77" s="7" t="str">
         <f>IF(F61&gt;0,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A78" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="B78" s="4" t="str">
+      <c r="A78" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="B78" s="7" t="str">
         <f>IF(Assumptions!B12=0,"N/A",IF(B3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
         <v>FAIL</v>
       </c>
-      <c r="C78" s="4" t="str">
+      <c r="C78" s="7" t="str">
         <f>IF(Assumptions!B12=0,"N/A",IF(C3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
         <v>FAIL</v>
       </c>
-      <c r="D78" s="4" t="str">
+      <c r="D78" s="7" t="str">
         <f>IF(Assumptions!B12=0,"N/A",IF(D3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="E78" s="4" t="str">
+      <c r="E78" s="7" t="str">
         <f>IF(Assumptions!B12=0,"N/A",IF(E3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="F78" s="4" t="str">
+      <c r="F78" s="7" t="str">
         <f>IF(Assumptions!B12=0,"N/A",IF(F3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A79" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="B79" s="4" t="str">
+      <c r="A79" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="B79" s="7" t="str">
         <f>IF(B59=0,"N/A",IF(B70/(B59/12)&gt;=2,"PASS","FAIL"))</f>
         <v>FAIL</v>
       </c>
-      <c r="C79" s="4" t="str">
+      <c r="C79" s="7" t="str">
         <f>IF(C59=0,"N/A",IF(C70/(C59/12)&gt;=2,"PASS","FAIL"))</f>
         <v>FAIL</v>
       </c>
-      <c r="D79" s="4" t="str">
+      <c r="D79" s="7" t="str">
         <f>IF(D59=0,"N/A",IF(D70/(D59/12)&gt;=2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="E79" s="4" t="str">
+      <c r="E79" s="7" t="str">
         <f>IF(E59=0,"N/A",IF(E70/(E59/12)&gt;=2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="F79" s="4" t="str">
+      <c r="F79" s="7" t="str">
         <f>IF(F59=0,"N/A",IF(F70/(F59/12)&gt;=2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="81" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A81" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="B81" s="3"/>
-      <c r="C81" s="3"/>
-      <c r="D81" s="3"/>
-      <c r="E81" s="3"/>
-      <c r="F81" s="3"/>
+      <c r="A81" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="B81" s="6"/>
+      <c r="C81" s="6"/>
+      <c r="D81" s="6"/>
+      <c r="E81" s="6"/>
+      <c r="F81" s="6"/>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A82" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="B82" s="12">
+      <c r="A82" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="B82" s="15">
         <f>IF(B3=0,"",B12/B3)</f>
         <v>10736</v>
       </c>
-      <c r="C82" s="12">
+      <c r="C82" s="15">
         <f>IF(C3=0,"",C12/C3)</f>
         <v>12614</v>
       </c>
-      <c r="D82" s="12">
+      <c r="D82" s="15">
         <f>IF(D3=0,"",D12/D3)</f>
         <v>12615</v>
       </c>
-      <c r="E82" s="12">
+      <c r="E82" s="15">
         <f>IF(E3=0,"",E12/E3)</f>
         <v>12691</v>
       </c>
-      <c r="F82" s="12">
+      <c r="F82" s="15">
         <f>IF(F3=0,"",F12/F3)</f>
         <v>12961</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A83" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="B83" s="12">
+      <c r="A83" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="B83" s="15">
         <f>IF(B3=0,"",B59/B3)</f>
         <v>14469</v>
       </c>
-      <c r="C83" s="12">
+      <c r="C83" s="15">
         <f>IF(C3=0,"",C59/C3)</f>
         <v>11047</v>
       </c>
-      <c r="D83" s="12">
+      <c r="D83" s="15">
         <f>IF(D3=0,"",D59/D3)</f>
         <v>8374</v>
       </c>
-      <c r="E83" s="12">
+      <c r="E83" s="15">
         <f>IF(E3=0,"",E59/E3)</f>
         <v>7322</v>
       </c>
-      <c r="F83" s="12">
+      <c r="F83" s="15">
         <f>IF(F3=0,"",F59/F3)</f>
         <v>7141</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A84" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="B84" s="12">
+      <c r="A84" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="B84" s="15">
         <f>B56+B58</f>
         <v>1191256</v>
       </c>
-      <c r="C84" s="12">
+      <c r="C84" s="15">
         <f>C56+C58</f>
         <v>1321543</v>
       </c>
-      <c r="D84" s="12">
+      <c r="D84" s="15">
         <f>D56+D58</f>
         <v>1321543</v>
       </c>
-      <c r="E84" s="12">
+      <c r="E84" s="15">
         <f>E56+E58</f>
         <v>1306543</v>
       </c>
-      <c r="F84" s="12">
+      <c r="F84" s="15">
         <f>F56+F58</f>
         <v>1301543</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A85" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="B85" s="12">
+      <c r="A85" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="B85" s="15">
         <f>IF(B3=0,"",B57/B3)</f>
         <v>4542</v>
       </c>
-      <c r="C85" s="12">
+      <c r="C85" s="15">
         <f>IF(C3=0,"",C57/C3)</f>
         <v>4439</v>
       </c>
-      <c r="D85" s="12">
+      <c r="D85" s="15">
         <f>IF(D3=0,"",D57/D3)</f>
         <v>3968</v>
       </c>
-      <c r="E85" s="12">
+      <c r="E85" s="15">
         <f>IF(E3=0,"",E57/E3)</f>
         <v>3838</v>
       </c>
-      <c r="F85" s="12">
+      <c r="F85" s="15">
         <f>IF(F3=0,"",F57/F3)</f>
         <v>3887</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A86" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="B86" s="12">
+      <c r="A86" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="B86" s="15">
         <f>IF(B3=0,"",B82-B85)</f>
         <v>6194</v>
       </c>
-      <c r="C86" s="12">
+      <c r="C86" s="15">
         <f>IF(C3=0,"",C82-C85)</f>
         <v>8175</v>
       </c>
-      <c r="D86" s="12">
+      <c r="D86" s="15">
         <f>IF(D3=0,"",D82-D85)</f>
         <v>8647</v>
       </c>
-      <c r="E86" s="12">
+      <c r="E86" s="15">
         <f>IF(E3=0,"",E82-E85)</f>
         <v>8853</v>
       </c>
-      <c r="F86" s="12">
+      <c r="F86" s="15">
         <f>IF(F3=0,"",F82-F85)</f>
         <v>9074</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A87" s="29" t="s">
-        <v>176</v>
-      </c>
-      <c r="B87" s="30">
+      <c r="A87" s="32" t="s">
+        <v>198</v>
+      </c>
+      <c r="B87" s="33">
         <f>IF(B86&lt;=0,"N/A",ROUNDUP(B84/B86,0))</f>
         <v>193</v>
       </c>
-      <c r="C87" s="30">
+      <c r="C87" s="33">
         <f>IF(C86&lt;=0,"N/A",ROUNDUP(C84/C86,0))</f>
         <v>162</v>
       </c>
-      <c r="D87" s="30">
+      <c r="D87" s="33">
         <f>IF(D86&lt;=0,"N/A",ROUNDUP(D84/D86,0))</f>
         <v>153</v>
       </c>
-      <c r="E87" s="30">
+      <c r="E87" s="33">
         <f>IF(E86&lt;=0,"N/A",ROUNDUP(E84/E86,0))</f>
         <v>148</v>
       </c>
-      <c r="F87" s="30">
+      <c r="F87" s="33">
         <f>IF(F86&lt;=0,"N/A",ROUNDUP(F84/F86,0))</f>
         <v>144</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A89" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="B89" s="15"/>
-      <c r="C89" s="15"/>
-      <c r="D89" s="15"/>
-      <c r="E89" s="15"/>
-      <c r="F89" s="15"/>
+      <c r="A89" s="18" t="s">
+        <v>137</v>
+      </c>
+      <c r="B89" s="18"/>
+      <c r="C89" s="18"/>
+      <c r="D89" s="18"/>
+      <c r="E89" s="18"/>
+      <c r="F89" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3901,7 +4327,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -3915,2018 +4341,2018 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
+      <c r="A1" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
+      <c r="N1" s="4"/>
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="B2" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" s="16" t="s">
-        <v>178</v>
-      </c>
-      <c r="D2" s="16" t="s">
-        <v>179</v>
-      </c>
-      <c r="E2" s="16" t="s">
-        <v>180</v>
-      </c>
-      <c r="F2" s="16" t="s">
-        <v>181</v>
-      </c>
-      <c r="G2" s="16" t="s">
-        <v>182</v>
-      </c>
-      <c r="H2" s="16" t="s">
-        <v>183</v>
-      </c>
-      <c r="I2" s="16" t="s">
-        <v>184</v>
-      </c>
-      <c r="J2" s="16" t="s">
-        <v>185</v>
-      </c>
-      <c r="K2" s="16" t="s">
-        <v>186</v>
-      </c>
-      <c r="L2" s="16" t="s">
-        <v>187</v>
-      </c>
-      <c r="M2" s="16" t="s">
-        <v>188</v>
-      </c>
-      <c r="N2" s="16" t="s">
-        <v>189</v>
+      <c r="A2" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2" s="19" t="s">
+        <v>200</v>
+      </c>
+      <c r="D2" s="19" t="s">
+        <v>201</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>202</v>
+      </c>
+      <c r="F2" s="19" t="s">
+        <v>203</v>
+      </c>
+      <c r="G2" s="19" t="s">
+        <v>204</v>
+      </c>
+      <c r="H2" s="19" t="s">
+        <v>205</v>
+      </c>
+      <c r="I2" s="19" t="s">
+        <v>206</v>
+      </c>
+      <c r="J2" s="19" t="s">
+        <v>207</v>
+      </c>
+      <c r="K2" s="19" t="s">
+        <v>208</v>
+      </c>
+      <c r="L2" s="19" t="s">
+        <v>209</v>
+      </c>
+      <c r="M2" s="19" t="s">
+        <v>210</v>
+      </c>
+      <c r="N2" s="19" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
-      <c r="M3" s="3"/>
-      <c r="N3" s="3"/>
+      <c r="A3" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="6"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B4" s="12">
+      <c r="A4" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="B4" s="15">
         <v>114000</v>
       </c>
-      <c r="C4" s="12">
+      <c r="C4" s="15">
         <v>114000</v>
       </c>
-      <c r="D4" s="12">
+      <c r="D4" s="15">
         <v>114000</v>
       </c>
-      <c r="E4" s="12">
+      <c r="E4" s="15">
         <v>114000</v>
       </c>
-      <c r="F4" s="12">
+      <c r="F4" s="15">
         <v>114000</v>
       </c>
-      <c r="G4" s="12">
+      <c r="G4" s="15">
         <v>114000</v>
       </c>
-      <c r="H4" s="12">
+      <c r="H4" s="15">
         <v>114000</v>
       </c>
-      <c r="I4" s="12">
+      <c r="I4" s="15">
         <v>114000</v>
       </c>
-      <c r="J4" s="12">
+      <c r="J4" s="15">
         <v>114000</v>
       </c>
-      <c r="K4" s="12">
+      <c r="K4" s="15">
         <v>114000</v>
       </c>
-      <c r="L4" s="12">
-        <v>0</v>
-      </c>
-      <c r="M4" s="12">
-        <v>0</v>
-      </c>
-      <c r="N4" s="12">
+      <c r="L4" s="15">
+        <v>0</v>
+      </c>
+      <c r="M4" s="15">
+        <v>0</v>
+      </c>
+      <c r="N4" s="15">
         <f>SUM(B4:M4)</f>
         <v>950000</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B5" s="12">
+      <c r="A5" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="B5" s="15">
         <v>9600</v>
       </c>
-      <c r="C5" s="12">
+      <c r="C5" s="15">
         <v>9600</v>
       </c>
-      <c r="D5" s="12">
+      <c r="D5" s="15">
         <v>9600</v>
       </c>
-      <c r="E5" s="12">
+      <c r="E5" s="15">
         <v>9600</v>
       </c>
-      <c r="F5" s="12">
+      <c r="F5" s="15">
         <v>9600</v>
       </c>
-      <c r="G5" s="12">
+      <c r="G5" s="15">
         <v>9600</v>
       </c>
-      <c r="H5" s="12">
+      <c r="H5" s="15">
         <v>9600</v>
       </c>
-      <c r="I5" s="12">
+      <c r="I5" s="15">
         <v>9600</v>
       </c>
-      <c r="J5" s="12">
+      <c r="J5" s="15">
         <v>9600</v>
       </c>
-      <c r="K5" s="12">
+      <c r="K5" s="15">
         <v>9600</v>
       </c>
-      <c r="L5" s="12">
-        <v>0</v>
-      </c>
-      <c r="M5" s="12">
-        <v>0</v>
-      </c>
-      <c r="N5" s="12">
+      <c r="L5" s="15">
+        <v>0</v>
+      </c>
+      <c r="M5" s="15">
+        <v>0</v>
+      </c>
+      <c r="N5" s="15">
         <f>SUM(B5:M5)</f>
         <v>80000</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B6" s="12">
+      <c r="A6" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="B6" s="15">
         <v>14400</v>
       </c>
-      <c r="C6" s="12">
+      <c r="C6" s="15">
         <v>14400</v>
       </c>
-      <c r="D6" s="12">
+      <c r="D6" s="15">
         <v>14400</v>
       </c>
-      <c r="E6" s="12">
+      <c r="E6" s="15">
         <v>14400</v>
       </c>
-      <c r="F6" s="12">
+      <c r="F6" s="15">
         <v>14400</v>
       </c>
-      <c r="G6" s="12">
+      <c r="G6" s="15">
         <v>14400</v>
       </c>
-      <c r="H6" s="12">
+      <c r="H6" s="15">
         <v>14400</v>
       </c>
-      <c r="I6" s="12">
+      <c r="I6" s="15">
         <v>14400</v>
       </c>
-      <c r="J6" s="12">
+      <c r="J6" s="15">
         <v>14400</v>
       </c>
-      <c r="K6" s="12">
+      <c r="K6" s="15">
         <v>14400</v>
       </c>
-      <c r="L6" s="12">
-        <v>0</v>
-      </c>
-      <c r="M6" s="12">
-        <v>0</v>
-      </c>
-      <c r="N6" s="12">
+      <c r="L6" s="15">
+        <v>0</v>
+      </c>
+      <c r="M6" s="15">
+        <v>0</v>
+      </c>
+      <c r="N6" s="15">
         <f>SUM(B6:M6)</f>
         <v>120000</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B7" s="12">
+      <c r="A7" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="B7" s="15">
         <v>10000</v>
       </c>
-      <c r="C7" s="12">
+      <c r="C7" s="15">
         <v>10000</v>
       </c>
-      <c r="D7" s="12">
+      <c r="D7" s="15">
         <v>10000</v>
       </c>
-      <c r="E7" s="12">
+      <c r="E7" s="15">
         <v>10000</v>
       </c>
-      <c r="F7" s="12">
+      <c r="F7" s="15">
         <v>10000</v>
       </c>
-      <c r="G7" s="12">
+      <c r="G7" s="15">
         <v>10000</v>
       </c>
-      <c r="H7" s="12">
+      <c r="H7" s="15">
         <v>10000</v>
       </c>
-      <c r="I7" s="12">
+      <c r="I7" s="15">
         <v>10000</v>
       </c>
-      <c r="J7" s="12">
+      <c r="J7" s="15">
         <v>10000</v>
       </c>
-      <c r="K7" s="12">
+      <c r="K7" s="15">
         <v>10000</v>
       </c>
-      <c r="L7" s="12">
-        <v>0</v>
-      </c>
-      <c r="M7" s="12">
-        <v>0</v>
-      </c>
-      <c r="N7" s="12">
+      <c r="L7" s="15">
+        <v>0</v>
+      </c>
+      <c r="M7" s="15">
+        <v>0</v>
+      </c>
+      <c r="N7" s="15">
         <f>SUM(B7:M7)</f>
         <v>83333</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B8" s="12">
+      <c r="A8" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="B8" s="15">
         <v>3000</v>
       </c>
-      <c r="C8" s="12">
+      <c r="C8" s="15">
         <v>3000</v>
       </c>
-      <c r="D8" s="12">
+      <c r="D8" s="15">
         <v>3000</v>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="15">
         <v>3000</v>
       </c>
-      <c r="F8" s="12">
+      <c r="F8" s="15">
         <v>3000</v>
       </c>
-      <c r="G8" s="12">
+      <c r="G8" s="15">
         <v>3000</v>
       </c>
-      <c r="H8" s="12">
+      <c r="H8" s="15">
         <v>3000</v>
       </c>
-      <c r="I8" s="12">
+      <c r="I8" s="15">
         <v>3000</v>
       </c>
-      <c r="J8" s="12">
+      <c r="J8" s="15">
         <v>3000</v>
       </c>
-      <c r="K8" s="12">
+      <c r="K8" s="15">
         <v>3000</v>
       </c>
-      <c r="L8" s="12">
-        <v>0</v>
-      </c>
-      <c r="M8" s="12">
-        <v>0</v>
-      </c>
-      <c r="N8" s="12">
+      <c r="L8" s="15">
+        <v>0</v>
+      </c>
+      <c r="M8" s="15">
+        <v>0</v>
+      </c>
+      <c r="N8" s="15">
         <f>SUM(B8:M8)</f>
         <v>25000</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B9" s="12">
+      <c r="A9" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="B9" s="15">
         <v>3600</v>
       </c>
-      <c r="C9" s="12">
+      <c r="C9" s="15">
         <v>3600</v>
       </c>
-      <c r="D9" s="12">
+      <c r="D9" s="15">
         <v>3600</v>
       </c>
-      <c r="E9" s="12">
+      <c r="E9" s="15">
         <v>3600</v>
       </c>
-      <c r="F9" s="12">
+      <c r="F9" s="15">
         <v>3600</v>
       </c>
-      <c r="G9" s="12">
+      <c r="G9" s="15">
         <v>3600</v>
       </c>
-      <c r="H9" s="12">
+      <c r="H9" s="15">
         <v>3600</v>
       </c>
-      <c r="I9" s="12">
+      <c r="I9" s="15">
         <v>3600</v>
       </c>
-      <c r="J9" s="12">
+      <c r="J9" s="15">
         <v>3600</v>
       </c>
-      <c r="K9" s="12">
+      <c r="K9" s="15">
         <v>3600</v>
       </c>
-      <c r="L9" s="12">
-        <v>0</v>
-      </c>
-      <c r="M9" s="12">
-        <v>0</v>
-      </c>
-      <c r="N9" s="12">
+      <c r="L9" s="15">
+        <v>0</v>
+      </c>
+      <c r="M9" s="15">
+        <v>0</v>
+      </c>
+      <c r="N9" s="15">
         <f>SUM(B9:M9)</f>
         <v>30000</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="B10" s="19">
+      <c r="A10" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="B10" s="22">
         <f>SUM(B4:B9)</f>
         <v>154600</v>
       </c>
-      <c r="C10" s="19">
+      <c r="C10" s="22">
         <f>SUM(C4:C9)</f>
         <v>154600</v>
       </c>
-      <c r="D10" s="19">
+      <c r="D10" s="22">
         <f>SUM(D4:D9)</f>
         <v>154600</v>
       </c>
-      <c r="E10" s="19">
+      <c r="E10" s="22">
         <f>SUM(E4:E9)</f>
         <v>154600</v>
       </c>
-      <c r="F10" s="19">
+      <c r="F10" s="22">
         <f>SUM(F4:F9)</f>
         <v>154600</v>
       </c>
-      <c r="G10" s="19">
+      <c r="G10" s="22">
         <f>SUM(G4:G9)</f>
         <v>154600</v>
       </c>
-      <c r="H10" s="19">
+      <c r="H10" s="22">
         <f>SUM(H4:H9)</f>
         <v>154600</v>
       </c>
-      <c r="I10" s="19">
+      <c r="I10" s="22">
         <f>SUM(I4:I9)</f>
         <v>154600</v>
       </c>
-      <c r="J10" s="19">
+      <c r="J10" s="22">
         <f>SUM(J4:J9)</f>
         <v>154600</v>
       </c>
-      <c r="K10" s="19">
+      <c r="K10" s="22">
         <f>SUM(K4:K9)</f>
         <v>154600</v>
       </c>
-      <c r="L10" s="19" t="str">
+      <c r="L10" s="22" t="str">
         <f>SUM(L4:L9)</f>
         <v>0</v>
       </c>
-      <c r="M10" s="19" t="str">
+      <c r="M10" s="22" t="str">
         <f>SUM(M4:M9)</f>
         <v>0</v>
       </c>
-      <c r="N10" s="19">
+      <c r="N10" s="22">
         <f>SUM(B10:M10)</f>
         <v>1546000</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>40</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
-      <c r="L12" s="3"/>
-      <c r="M12" s="3"/>
-      <c r="N12" s="3"/>
+      <c r="A12" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="B12" s="6"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6"/>
+      <c r="I12" s="6"/>
+      <c r="J12" s="6"/>
+      <c r="K12" s="6"/>
+      <c r="L12" s="6"/>
+      <c r="M12" s="6"/>
+      <c r="N12" s="6"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="B13" s="12">
+      <c r="A13" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="B13" s="15">
         <v>12435</v>
       </c>
-      <c r="C13" s="12">
+      <c r="C13" s="15">
         <v>12435</v>
       </c>
-      <c r="D13" s="12">
+      <c r="D13" s="15">
         <v>12435</v>
       </c>
-      <c r="E13" s="12">
+      <c r="E13" s="15">
         <v>12435</v>
       </c>
-      <c r="F13" s="12">
+      <c r="F13" s="15">
         <v>12435</v>
       </c>
-      <c r="G13" s="12">
+      <c r="G13" s="15">
         <v>12435</v>
       </c>
-      <c r="H13" s="12">
+      <c r="H13" s="15">
         <v>12435</v>
       </c>
-      <c r="I13" s="12">
+      <c r="I13" s="15">
         <v>12435</v>
       </c>
-      <c r="J13" s="12">
+      <c r="J13" s="15">
         <v>12435</v>
       </c>
-      <c r="K13" s="12">
+      <c r="K13" s="15">
         <v>12435</v>
       </c>
-      <c r="L13" s="12">
-        <v>0</v>
-      </c>
-      <c r="M13" s="12">
-        <v>0</v>
-      </c>
-      <c r="N13" s="12">
+      <c r="L13" s="15">
+        <v>0</v>
+      </c>
+      <c r="M13" s="15">
+        <v>0</v>
+      </c>
+      <c r="N13" s="15">
         <f>SUM(B13:M13)</f>
         <v>124346</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="B14" s="12">
+      <c r="A14" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="B14" s="15">
         <v>10174</v>
       </c>
-      <c r="C14" s="12">
+      <c r="C14" s="15">
         <v>10174</v>
       </c>
-      <c r="D14" s="12">
+      <c r="D14" s="15">
         <v>10174</v>
       </c>
-      <c r="E14" s="12">
+      <c r="E14" s="15">
         <v>10174</v>
       </c>
-      <c r="F14" s="12">
+      <c r="F14" s="15">
         <v>10174</v>
       </c>
-      <c r="G14" s="12">
+      <c r="G14" s="15">
         <v>10174</v>
       </c>
-      <c r="H14" s="12">
+      <c r="H14" s="15">
         <v>10174</v>
       </c>
-      <c r="I14" s="12">
+      <c r="I14" s="15">
         <v>10174</v>
       </c>
-      <c r="J14" s="12">
+      <c r="J14" s="15">
         <v>10174</v>
       </c>
-      <c r="K14" s="12">
+      <c r="K14" s="15">
         <v>10174</v>
       </c>
-      <c r="L14" s="12">
-        <v>0</v>
-      </c>
-      <c r="M14" s="12">
-        <v>0</v>
-      </c>
-      <c r="N14" s="12">
+      <c r="L14" s="15">
+        <v>0</v>
+      </c>
+      <c r="M14" s="15">
+        <v>0</v>
+      </c>
+      <c r="N14" s="15">
         <f>SUM(B14:M14)</f>
         <v>101738</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="B15" s="12">
+      <c r="A15" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="B15" s="15">
         <v>8139</v>
       </c>
-      <c r="C15" s="12">
+      <c r="C15" s="15">
         <v>8139</v>
       </c>
-      <c r="D15" s="12">
+      <c r="D15" s="15">
         <v>8139</v>
       </c>
-      <c r="E15" s="12">
+      <c r="E15" s="15">
         <v>8139</v>
       </c>
-      <c r="F15" s="12">
+      <c r="F15" s="15">
         <v>8139</v>
       </c>
-      <c r="G15" s="12">
+      <c r="G15" s="15">
         <v>8139</v>
       </c>
-      <c r="H15" s="12">
+      <c r="H15" s="15">
         <v>8139</v>
       </c>
-      <c r="I15" s="12">
+      <c r="I15" s="15">
         <v>8139</v>
       </c>
-      <c r="J15" s="12">
+      <c r="J15" s="15">
         <v>8139</v>
       </c>
-      <c r="K15" s="12">
+      <c r="K15" s="15">
         <v>8139</v>
       </c>
-      <c r="L15" s="12">
-        <v>0</v>
-      </c>
-      <c r="M15" s="12">
-        <v>0</v>
-      </c>
-      <c r="N15" s="12">
+      <c r="L15" s="15">
+        <v>0</v>
+      </c>
+      <c r="M15" s="15">
+        <v>0</v>
+      </c>
+      <c r="N15" s="15">
         <f>SUM(B15:M15)</f>
         <v>81390</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="B16" s="12">
+      <c r="A16" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="B16" s="15">
         <v>35269</v>
       </c>
-      <c r="C16" s="12">
+      <c r="C16" s="15">
         <v>35269</v>
       </c>
-      <c r="D16" s="12">
+      <c r="D16" s="15">
         <v>35269</v>
       </c>
-      <c r="E16" s="12">
+      <c r="E16" s="15">
         <v>35269</v>
       </c>
-      <c r="F16" s="12">
+      <c r="F16" s="15">
         <v>35269</v>
       </c>
-      <c r="G16" s="12">
+      <c r="G16" s="15">
         <v>35269</v>
       </c>
-      <c r="H16" s="12">
+      <c r="H16" s="15">
         <v>35269</v>
       </c>
-      <c r="I16" s="12">
+      <c r="I16" s="15">
         <v>35269</v>
       </c>
-      <c r="J16" s="12">
+      <c r="J16" s="15">
         <v>35269</v>
       </c>
-      <c r="K16" s="12">
+      <c r="K16" s="15">
         <v>35269</v>
       </c>
-      <c r="L16" s="12">
-        <v>0</v>
-      </c>
-      <c r="M16" s="12">
-        <v>0</v>
-      </c>
-      <c r="N16" s="12">
+      <c r="L16" s="15">
+        <v>0</v>
+      </c>
+      <c r="M16" s="15">
+        <v>0</v>
+      </c>
+      <c r="N16" s="15">
         <f>SUM(B16:M16)</f>
         <v>352690</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="B17" s="12">
+      <c r="A17" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="B17" s="15">
         <v>6217</v>
       </c>
-      <c r="C17" s="12">
+      <c r="C17" s="15">
         <v>6217</v>
       </c>
-      <c r="D17" s="12">
+      <c r="D17" s="15">
         <v>6217</v>
       </c>
-      <c r="E17" s="12">
+      <c r="E17" s="15">
         <v>6217</v>
       </c>
-      <c r="F17" s="12">
+      <c r="F17" s="15">
         <v>6217</v>
       </c>
-      <c r="G17" s="12">
+      <c r="G17" s="15">
         <v>6217</v>
       </c>
-      <c r="H17" s="12">
+      <c r="H17" s="15">
         <v>6217</v>
       </c>
-      <c r="I17" s="12">
+      <c r="I17" s="15">
         <v>6217</v>
       </c>
-      <c r="J17" s="12">
+      <c r="J17" s="15">
         <v>6217</v>
       </c>
-      <c r="K17" s="12">
+      <c r="K17" s="15">
         <v>6217</v>
       </c>
-      <c r="L17" s="12">
-        <v>0</v>
-      </c>
-      <c r="M17" s="12">
-        <v>0</v>
-      </c>
-      <c r="N17" s="12">
+      <c r="L17" s="15">
+        <v>0</v>
+      </c>
+      <c r="M17" s="15">
+        <v>0</v>
+      </c>
+      <c r="N17" s="15">
         <f>SUM(B17:M17)</f>
         <v>62173</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="B18" s="12">
+      <c r="A18" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="B18" s="15">
         <v>9574</v>
       </c>
-      <c r="C18" s="12">
+      <c r="C18" s="15">
         <v>9574</v>
       </c>
-      <c r="D18" s="12">
+      <c r="D18" s="15">
         <v>9574</v>
       </c>
-      <c r="E18" s="12">
+      <c r="E18" s="15">
         <v>9574</v>
       </c>
-      <c r="F18" s="12">
+      <c r="F18" s="15">
         <v>9574</v>
       </c>
-      <c r="G18" s="12">
+      <c r="G18" s="15">
         <v>9574</v>
       </c>
-      <c r="H18" s="12">
+      <c r="H18" s="15">
         <v>9574</v>
       </c>
-      <c r="I18" s="12">
+      <c r="I18" s="15">
         <v>9574</v>
       </c>
-      <c r="J18" s="12">
+      <c r="J18" s="15">
         <v>9574</v>
       </c>
-      <c r="K18" s="12">
+      <c r="K18" s="15">
         <v>9574</v>
       </c>
-      <c r="L18" s="12">
-        <v>0</v>
-      </c>
-      <c r="M18" s="12">
-        <v>0</v>
-      </c>
-      <c r="N18" s="12">
+      <c r="L18" s="15">
+        <v>0</v>
+      </c>
+      <c r="M18" s="15">
+        <v>0</v>
+      </c>
+      <c r="N18" s="15">
         <f>SUM(B18:M18)</f>
         <v>95738</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="B19" s="12">
+      <c r="A19" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="B19" s="15">
         <v>6217</v>
       </c>
-      <c r="C19" s="12">
+      <c r="C19" s="15">
         <v>6217</v>
       </c>
-      <c r="D19" s="12">
+      <c r="D19" s="15">
         <v>6217</v>
       </c>
-      <c r="E19" s="12">
+      <c r="E19" s="15">
         <v>6217</v>
       </c>
-      <c r="F19" s="12">
+      <c r="F19" s="15">
         <v>6217</v>
       </c>
-      <c r="G19" s="12">
+      <c r="G19" s="15">
         <v>6217</v>
       </c>
-      <c r="H19" s="12">
+      <c r="H19" s="15">
         <v>6217</v>
       </c>
-      <c r="I19" s="12">
+      <c r="I19" s="15">
         <v>6217</v>
       </c>
-      <c r="J19" s="12">
+      <c r="J19" s="15">
         <v>6217</v>
       </c>
-      <c r="K19" s="12">
+      <c r="K19" s="15">
         <v>6217</v>
       </c>
-      <c r="L19" s="12">
-        <v>0</v>
-      </c>
-      <c r="M19" s="12">
-        <v>0</v>
-      </c>
-      <c r="N19" s="12">
+      <c r="L19" s="15">
+        <v>0</v>
+      </c>
+      <c r="M19" s="15">
+        <v>0</v>
+      </c>
+      <c r="N19" s="15">
         <f>SUM(B19:M19)</f>
         <v>62173</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="B20" s="12">
+      <c r="A20" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="B20" s="15">
         <v>8401</v>
       </c>
-      <c r="C20" s="12">
+      <c r="C20" s="15">
         <v>8401</v>
       </c>
-      <c r="D20" s="12">
+      <c r="D20" s="15">
         <v>8401</v>
       </c>
-      <c r="E20" s="12">
+      <c r="E20" s="15">
         <v>8401</v>
       </c>
-      <c r="F20" s="12">
+      <c r="F20" s="15">
         <v>8401</v>
       </c>
-      <c r="G20" s="12">
+      <c r="G20" s="15">
         <v>8401</v>
       </c>
-      <c r="H20" s="12">
+      <c r="H20" s="15">
         <v>8401</v>
       </c>
-      <c r="I20" s="12">
+      <c r="I20" s="15">
         <v>8401</v>
       </c>
-      <c r="J20" s="12">
+      <c r="J20" s="15">
         <v>8401</v>
       </c>
-      <c r="K20" s="12">
+      <c r="K20" s="15">
         <v>8401</v>
       </c>
-      <c r="L20" s="12">
-        <v>0</v>
-      </c>
-      <c r="M20" s="12">
-        <v>0</v>
-      </c>
-      <c r="N20" s="12">
+      <c r="L20" s="15">
+        <v>0</v>
+      </c>
+      <c r="M20" s="15">
+        <v>0</v>
+      </c>
+      <c r="N20" s="15">
         <f>SUM(B20:M20)</f>
         <v>84012</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="B21" s="12">
+      <c r="A21" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="B21" s="15">
         <v>6217</v>
       </c>
-      <c r="C21" s="12">
+      <c r="C21" s="15">
         <v>6217</v>
       </c>
-      <c r="D21" s="12">
+      <c r="D21" s="15">
         <v>6217</v>
       </c>
-      <c r="E21" s="12">
+      <c r="E21" s="15">
         <v>6217</v>
       </c>
-      <c r="F21" s="12">
+      <c r="F21" s="15">
         <v>6217</v>
       </c>
-      <c r="G21" s="12">
+      <c r="G21" s="15">
         <v>6217</v>
       </c>
-      <c r="H21" s="12">
+      <c r="H21" s="15">
         <v>6217</v>
       </c>
-      <c r="I21" s="12">
+      <c r="I21" s="15">
         <v>6217</v>
       </c>
-      <c r="J21" s="12">
+      <c r="J21" s="15">
         <v>6217</v>
       </c>
-      <c r="K21" s="12">
+      <c r="K21" s="15">
         <v>6217</v>
       </c>
-      <c r="L21" s="12">
-        <v>0</v>
-      </c>
-      <c r="M21" s="12">
-        <v>0</v>
-      </c>
-      <c r="N21" s="12">
+      <c r="L21" s="15">
+        <v>0</v>
+      </c>
+      <c r="M21" s="15">
+        <v>0</v>
+      </c>
+      <c r="N21" s="15">
         <f>SUM(B21:M21)</f>
         <v>62173</v>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="B22" s="19">
+      <c r="A22" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="B22" s="22">
         <f>SUM(B13:B21)</f>
         <v>102643</v>
       </c>
-      <c r="C22" s="19">
+      <c r="C22" s="22">
         <f>SUM(C13:C21)</f>
         <v>102643</v>
       </c>
-      <c r="D22" s="19">
+      <c r="D22" s="22">
         <f>SUM(D13:D21)</f>
         <v>102643</v>
       </c>
-      <c r="E22" s="19">
+      <c r="E22" s="22">
         <f>SUM(E13:E21)</f>
         <v>102643</v>
       </c>
-      <c r="F22" s="19">
+      <c r="F22" s="22">
         <f>SUM(F13:F21)</f>
         <v>102643</v>
       </c>
-      <c r="G22" s="19">
+      <c r="G22" s="22">
         <f>SUM(G13:G21)</f>
         <v>102643</v>
       </c>
-      <c r="H22" s="19">
+      <c r="H22" s="22">
         <f>SUM(H13:H21)</f>
         <v>102643</v>
       </c>
-      <c r="I22" s="19">
+      <c r="I22" s="22">
         <f>SUM(I13:I21)</f>
         <v>102643</v>
       </c>
-      <c r="J22" s="19">
+      <c r="J22" s="22">
         <f>SUM(J13:J21)</f>
         <v>102643</v>
       </c>
-      <c r="K22" s="19">
+      <c r="K22" s="22">
         <f>SUM(K13:K21)</f>
         <v>102643</v>
       </c>
-      <c r="L22" s="19" t="str">
+      <c r="L22" s="22" t="str">
         <f>SUM(L13:L21)</f>
         <v>0</v>
       </c>
-      <c r="M22" s="19" t="str">
+      <c r="M22" s="22" t="str">
         <f>SUM(M13:M21)</f>
         <v>0</v>
       </c>
-      <c r="N22" s="19">
+      <c r="N22" s="22">
         <f>SUM(B22:M22)</f>
         <v>1026431</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>40</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
-      <c r="I24" s="3"/>
-      <c r="J24" s="3"/>
-      <c r="K24" s="3"/>
-      <c r="L24" s="3"/>
-      <c r="M24" s="3"/>
-      <c r="N24" s="3"/>
+      <c r="A24" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B24" s="6"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="6"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="6"/>
+      <c r="G24" s="6"/>
+      <c r="H24" s="6"/>
+      <c r="I24" s="6"/>
+      <c r="J24" s="6"/>
+      <c r="K24" s="6"/>
+      <c r="L24" s="6"/>
+      <c r="M24" s="6"/>
+      <c r="N24" s="6"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B25" s="4"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4"/>
-      <c r="F25" s="4"/>
-      <c r="G25" s="4"/>
-      <c r="H25" s="4"/>
-      <c r="I25" s="4"/>
-      <c r="J25" s="4"/>
-      <c r="K25" s="4"/>
-      <c r="L25" s="4"/>
-      <c r="M25" s="4"/>
-      <c r="N25" s="4"/>
+      <c r="A25" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="7"/>
+      <c r="H25" s="7"/>
+      <c r="I25" s="7"/>
+      <c r="J25" s="7"/>
+      <c r="K25" s="7"/>
+      <c r="L25" s="7"/>
+      <c r="M25" s="7"/>
+      <c r="N25" s="7"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="B26" s="12">
+      <c r="A26" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="B26" s="15">
         <v>7000</v>
       </c>
-      <c r="C26" s="12">
+      <c r="C26" s="15">
         <v>7000</v>
       </c>
-      <c r="D26" s="12">
+      <c r="D26" s="15">
         <v>7000</v>
       </c>
-      <c r="E26" s="12">
+      <c r="E26" s="15">
         <v>7000</v>
       </c>
-      <c r="F26" s="12">
+      <c r="F26" s="15">
         <v>7000</v>
       </c>
-      <c r="G26" s="12">
+      <c r="G26" s="15">
         <v>7000</v>
       </c>
-      <c r="H26" s="12">
+      <c r="H26" s="15">
         <v>7000</v>
       </c>
-      <c r="I26" s="12">
+      <c r="I26" s="15">
         <v>7000</v>
       </c>
-      <c r="J26" s="12">
+      <c r="J26" s="15">
         <v>7000</v>
       </c>
-      <c r="K26" s="12">
+      <c r="K26" s="15">
         <v>7000</v>
       </c>
-      <c r="L26" s="12">
-        <v>0</v>
-      </c>
-      <c r="M26" s="12">
-        <v>0</v>
-      </c>
-      <c r="N26" s="12">
+      <c r="L26" s="15">
+        <v>0</v>
+      </c>
+      <c r="M26" s="15">
+        <v>0</v>
+      </c>
+      <c r="N26" s="15">
         <f>SUM(B26:M26)</f>
         <v>70000</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A27" s="20" t="s">
-        <v>131</v>
-      </c>
-      <c r="B27" s="21">
+      <c r="A27" s="23" t="s">
+        <v>153</v>
+      </c>
+      <c r="B27" s="24">
         <v>7000</v>
       </c>
-      <c r="C27" s="21">
+      <c r="C27" s="24">
         <v>7000</v>
       </c>
-      <c r="D27" s="21">
+      <c r="D27" s="24">
         <v>7000</v>
       </c>
-      <c r="E27" s="21">
+      <c r="E27" s="24">
         <v>7000</v>
       </c>
-      <c r="F27" s="21">
+      <c r="F27" s="24">
         <v>7000</v>
       </c>
-      <c r="G27" s="21">
+      <c r="G27" s="24">
         <v>7000</v>
       </c>
-      <c r="H27" s="21">
+      <c r="H27" s="24">
         <v>7000</v>
       </c>
-      <c r="I27" s="21">
+      <c r="I27" s="24">
         <v>7000</v>
       </c>
-      <c r="J27" s="21">
+      <c r="J27" s="24">
         <v>7000</v>
       </c>
-      <c r="K27" s="21">
+      <c r="K27" s="24">
         <v>7000</v>
       </c>
-      <c r="L27" s="21">
-        <v>0</v>
-      </c>
-      <c r="M27" s="21">
-        <v>0</v>
-      </c>
-      <c r="N27" s="21">
+      <c r="L27" s="24">
+        <v>0</v>
+      </c>
+      <c r="M27" s="24">
+        <v>0</v>
+      </c>
+      <c r="N27" s="24">
         <f>SUM(B27:M27)</f>
         <v>70000</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A28" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B28" s="4"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="4"/>
-      <c r="E28" s="4"/>
-      <c r="F28" s="4"/>
-      <c r="G28" s="4"/>
-      <c r="H28" s="4"/>
-      <c r="I28" s="4"/>
-      <c r="J28" s="4"/>
-      <c r="K28" s="4"/>
-      <c r="L28" s="4"/>
-      <c r="M28" s="4"/>
-      <c r="N28" s="4"/>
+      <c r="A28" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="7"/>
+      <c r="G28" s="7"/>
+      <c r="H28" s="7"/>
+      <c r="I28" s="7"/>
+      <c r="J28" s="7"/>
+      <c r="K28" s="7"/>
+      <c r="L28" s="7"/>
+      <c r="M28" s="7"/>
+      <c r="N28" s="7"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A29" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="B29" s="12">
+      <c r="A29" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="B29" s="15">
         <v>5000</v>
       </c>
-      <c r="C29" s="12">
+      <c r="C29" s="15">
         <v>5000</v>
       </c>
-      <c r="D29" s="12">
+      <c r="D29" s="15">
         <v>5000</v>
       </c>
-      <c r="E29" s="12">
+      <c r="E29" s="15">
         <v>5000</v>
       </c>
-      <c r="F29" s="12">
+      <c r="F29" s="15">
         <v>5000</v>
       </c>
-      <c r="G29" s="12">
+      <c r="G29" s="15">
         <v>5000</v>
       </c>
-      <c r="H29" s="12">
+      <c r="H29" s="15">
         <v>5000</v>
       </c>
-      <c r="I29" s="12">
+      <c r="I29" s="15">
         <v>5000</v>
       </c>
-      <c r="J29" s="12">
+      <c r="J29" s="15">
         <v>5000</v>
       </c>
-      <c r="K29" s="12">
+      <c r="K29" s="15">
         <v>5000</v>
       </c>
-      <c r="L29" s="12">
-        <v>0</v>
-      </c>
-      <c r="M29" s="12">
-        <v>0</v>
-      </c>
-      <c r="N29" s="12">
+      <c r="L29" s="15">
+        <v>0</v>
+      </c>
+      <c r="M29" s="15">
+        <v>0</v>
+      </c>
+      <c r="N29" s="15">
         <f>SUM(B29:M29)</f>
         <v>50000</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A30" s="20" t="s">
-        <v>133</v>
-      </c>
-      <c r="B30" s="21">
+      <c r="A30" s="23" t="s">
+        <v>155</v>
+      </c>
+      <c r="B30" s="24">
         <v>5000</v>
       </c>
-      <c r="C30" s="21">
+      <c r="C30" s="24">
         <v>5000</v>
       </c>
-      <c r="D30" s="21">
+      <c r="D30" s="24">
         <v>5000</v>
       </c>
-      <c r="E30" s="21">
+      <c r="E30" s="24">
         <v>5000</v>
       </c>
-      <c r="F30" s="21">
+      <c r="F30" s="24">
         <v>5000</v>
       </c>
-      <c r="G30" s="21">
+      <c r="G30" s="24">
         <v>5000</v>
       </c>
-      <c r="H30" s="21">
+      <c r="H30" s="24">
         <v>5000</v>
       </c>
-      <c r="I30" s="21">
+      <c r="I30" s="24">
         <v>5000</v>
       </c>
-      <c r="J30" s="21">
+      <c r="J30" s="24">
         <v>5000</v>
       </c>
-      <c r="K30" s="21">
+      <c r="K30" s="24">
         <v>5000</v>
       </c>
-      <c r="L30" s="21">
-        <v>0</v>
-      </c>
-      <c r="M30" s="21">
-        <v>0</v>
-      </c>
-      <c r="N30" s="21">
+      <c r="L30" s="24">
+        <v>0</v>
+      </c>
+      <c r="M30" s="24">
+        <v>0</v>
+      </c>
+      <c r="N30" s="24">
         <f>SUM(B30:M30)</f>
         <v>50000</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A31" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="B31" s="4"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="4"/>
-      <c r="E31" s="4"/>
-      <c r="F31" s="4"/>
-      <c r="G31" s="4"/>
-      <c r="H31" s="4"/>
-      <c r="I31" s="4"/>
-      <c r="J31" s="4"/>
-      <c r="K31" s="4"/>
-      <c r="L31" s="4"/>
-      <c r="M31" s="4"/>
-      <c r="N31" s="4"/>
+      <c r="A31" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="B31" s="7"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
+      <c r="F31" s="7"/>
+      <c r="G31" s="7"/>
+      <c r="H31" s="7"/>
+      <c r="I31" s="7"/>
+      <c r="J31" s="7"/>
+      <c r="K31" s="7"/>
+      <c r="L31" s="7"/>
+      <c r="M31" s="7"/>
+      <c r="N31" s="7"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A32" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="B32" s="12">
+      <c r="A32" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B32" s="15">
         <v>18000</v>
       </c>
-      <c r="C32" s="12">
+      <c r="C32" s="15">
         <v>18000</v>
       </c>
-      <c r="D32" s="12">
+      <c r="D32" s="15">
         <v>18000</v>
       </c>
-      <c r="E32" s="12">
+      <c r="E32" s="15">
         <v>18000</v>
       </c>
-      <c r="F32" s="12">
+      <c r="F32" s="15">
         <v>18000</v>
       </c>
-      <c r="G32" s="12">
+      <c r="G32" s="15">
         <v>18000</v>
       </c>
-      <c r="H32" s="12">
+      <c r="H32" s="15">
         <v>18000</v>
       </c>
-      <c r="I32" s="12">
+      <c r="I32" s="15">
         <v>18000</v>
       </c>
-      <c r="J32" s="12">
+      <c r="J32" s="15">
         <v>18000</v>
       </c>
-      <c r="K32" s="12">
+      <c r="K32" s="15">
         <v>18000</v>
       </c>
-      <c r="L32" s="12">
-        <v>0</v>
-      </c>
-      <c r="M32" s="12">
-        <v>0</v>
-      </c>
-      <c r="N32" s="12">
+      <c r="L32" s="15">
+        <v>0</v>
+      </c>
+      <c r="M32" s="15">
+        <v>0</v>
+      </c>
+      <c r="N32" s="15">
         <f>SUM(B32:M32)</f>
         <v>180000</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A33" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="B33" s="12">
+      <c r="A33" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="B33" s="15">
         <v>2500</v>
       </c>
-      <c r="C33" s="12">
+      <c r="C33" s="15">
         <v>2500</v>
       </c>
-      <c r="D33" s="12">
+      <c r="D33" s="15">
         <v>2500</v>
       </c>
-      <c r="E33" s="12">
+      <c r="E33" s="15">
         <v>2500</v>
       </c>
-      <c r="F33" s="12">
+      <c r="F33" s="15">
         <v>2500</v>
       </c>
-      <c r="G33" s="12">
+      <c r="G33" s="15">
         <v>2500</v>
       </c>
-      <c r="H33" s="12">
+      <c r="H33" s="15">
         <v>2500</v>
       </c>
-      <c r="I33" s="12">
+      <c r="I33" s="15">
         <v>2500</v>
       </c>
-      <c r="J33" s="12">
+      <c r="J33" s="15">
         <v>2500</v>
       </c>
-      <c r="K33" s="12">
+      <c r="K33" s="15">
         <v>2500</v>
       </c>
-      <c r="L33" s="12">
-        <v>0</v>
-      </c>
-      <c r="M33" s="12">
-        <v>0</v>
-      </c>
-      <c r="N33" s="12">
+      <c r="L33" s="15">
+        <v>0</v>
+      </c>
+      <c r="M33" s="15">
+        <v>0</v>
+      </c>
+      <c r="N33" s="15">
         <f>SUM(B33:M33)</f>
         <v>25000</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A34" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="B34" s="12">
+      <c r="A34" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="B34" s="15">
         <v>1500</v>
       </c>
-      <c r="C34" s="12">
+      <c r="C34" s="15">
         <v>1500</v>
       </c>
-      <c r="D34" s="12">
+      <c r="D34" s="15">
         <v>1500</v>
       </c>
-      <c r="E34" s="12">
+      <c r="E34" s="15">
         <v>1500</v>
       </c>
-      <c r="F34" s="12">
+      <c r="F34" s="15">
         <v>1500</v>
       </c>
-      <c r="G34" s="12">
+      <c r="G34" s="15">
         <v>1500</v>
       </c>
-      <c r="H34" s="12">
+      <c r="H34" s="15">
         <v>1500</v>
       </c>
-      <c r="I34" s="12">
+      <c r="I34" s="15">
         <v>1500</v>
       </c>
-      <c r="J34" s="12">
+      <c r="J34" s="15">
         <v>1500</v>
       </c>
-      <c r="K34" s="12">
+      <c r="K34" s="15">
         <v>1500</v>
       </c>
-      <c r="L34" s="12">
-        <v>0</v>
-      </c>
-      <c r="M34" s="12">
-        <v>0</v>
-      </c>
-      <c r="N34" s="12">
+      <c r="L34" s="15">
+        <v>0</v>
+      </c>
+      <c r="M34" s="15">
+        <v>0</v>
+      </c>
+      <c r="N34" s="15">
         <f>SUM(B34:M34)</f>
         <v>15000</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A35" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="B35" s="12">
+      <c r="A35" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="B35" s="15">
         <v>1500</v>
       </c>
-      <c r="C35" s="12">
+      <c r="C35" s="15">
         <v>1500</v>
       </c>
-      <c r="D35" s="12">
+      <c r="D35" s="15">
         <v>1500</v>
       </c>
-      <c r="E35" s="12">
+      <c r="E35" s="15">
         <v>1500</v>
       </c>
-      <c r="F35" s="12">
+      <c r="F35" s="15">
         <v>1500</v>
       </c>
-      <c r="G35" s="12">
+      <c r="G35" s="15">
         <v>1500</v>
       </c>
-      <c r="H35" s="12">
+      <c r="H35" s="15">
         <v>1500</v>
       </c>
-      <c r="I35" s="12">
+      <c r="I35" s="15">
         <v>1500</v>
       </c>
-      <c r="J35" s="12">
+      <c r="J35" s="15">
         <v>1500</v>
       </c>
-      <c r="K35" s="12">
+      <c r="K35" s="15">
         <v>1500</v>
       </c>
-      <c r="L35" s="12">
-        <v>0</v>
-      </c>
-      <c r="M35" s="12">
-        <v>0</v>
-      </c>
-      <c r="N35" s="12">
+      <c r="L35" s="15">
+        <v>0</v>
+      </c>
+      <c r="M35" s="15">
+        <v>0</v>
+      </c>
+      <c r="N35" s="15">
         <f>SUM(B35:M35)</f>
         <v>15000</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A36" s="20" t="s">
-        <v>138</v>
-      </c>
-      <c r="B36" s="21">
+      <c r="A36" s="23" t="s">
+        <v>160</v>
+      </c>
+      <c r="B36" s="24">
         <v>23500</v>
       </c>
-      <c r="C36" s="21">
+      <c r="C36" s="24">
         <v>23500</v>
       </c>
-      <c r="D36" s="21">
+      <c r="D36" s="24">
         <v>23500</v>
       </c>
-      <c r="E36" s="21">
+      <c r="E36" s="24">
         <v>23500</v>
       </c>
-      <c r="F36" s="21">
+      <c r="F36" s="24">
         <v>23500</v>
       </c>
-      <c r="G36" s="21">
+      <c r="G36" s="24">
         <v>23500</v>
       </c>
-      <c r="H36" s="21">
+      <c r="H36" s="24">
         <v>23500</v>
       </c>
-      <c r="I36" s="21">
+      <c r="I36" s="24">
         <v>23500</v>
       </c>
-      <c r="J36" s="21">
+      <c r="J36" s="24">
         <v>23500</v>
       </c>
-      <c r="K36" s="21">
+      <c r="K36" s="24">
         <v>23500</v>
       </c>
-      <c r="L36" s="21">
-        <v>0</v>
-      </c>
-      <c r="M36" s="21">
-        <v>0</v>
-      </c>
-      <c r="N36" s="21">
+      <c r="L36" s="24">
+        <v>0</v>
+      </c>
+      <c r="M36" s="24">
+        <v>0</v>
+      </c>
+      <c r="N36" s="24">
         <f>SUM(B36:M36)</f>
         <v>235000</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A37" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="B37" s="4"/>
-      <c r="C37" s="4"/>
-      <c r="D37" s="4"/>
-      <c r="E37" s="4"/>
-      <c r="F37" s="4"/>
-      <c r="G37" s="4"/>
-      <c r="H37" s="4"/>
-      <c r="I37" s="4"/>
-      <c r="J37" s="4"/>
-      <c r="K37" s="4"/>
-      <c r="L37" s="4"/>
-      <c r="M37" s="4"/>
-      <c r="N37" s="4"/>
+      <c r="A37" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="B37" s="7"/>
+      <c r="C37" s="7"/>
+      <c r="D37" s="7"/>
+      <c r="E37" s="7"/>
+      <c r="F37" s="7"/>
+      <c r="G37" s="7"/>
+      <c r="H37" s="7"/>
+      <c r="I37" s="7"/>
+      <c r="J37" s="7"/>
+      <c r="K37" s="7"/>
+      <c r="L37" s="7"/>
+      <c r="M37" s="7"/>
+      <c r="N37" s="7"/>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A38" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="B38" s="12">
+      <c r="A38" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="B38" s="15">
         <v>2083</v>
       </c>
-      <c r="C38" s="12">
+      <c r="C38" s="15">
         <v>2083</v>
       </c>
-      <c r="D38" s="12">
+      <c r="D38" s="15">
         <v>2083</v>
       </c>
-      <c r="E38" s="12">
+      <c r="E38" s="15">
         <v>2083</v>
       </c>
-      <c r="F38" s="12">
+      <c r="F38" s="15">
         <v>2083</v>
       </c>
-      <c r="G38" s="12">
+      <c r="G38" s="15">
         <v>2083</v>
       </c>
-      <c r="H38" s="12">
+      <c r="H38" s="15">
         <v>2083</v>
       </c>
-      <c r="I38" s="12">
+      <c r="I38" s="15">
         <v>2083</v>
       </c>
-      <c r="J38" s="12">
+      <c r="J38" s="15">
         <v>2083</v>
       </c>
-      <c r="K38" s="12">
+      <c r="K38" s="15">
         <v>2083</v>
       </c>
-      <c r="L38" s="12">
-        <v>0</v>
-      </c>
-      <c r="M38" s="12">
-        <v>0</v>
-      </c>
-      <c r="N38" s="12">
+      <c r="L38" s="15">
+        <v>0</v>
+      </c>
+      <c r="M38" s="15">
+        <v>0</v>
+      </c>
+      <c r="N38" s="15">
         <f>SUM(B38:M38)</f>
         <v>20833</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A39" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="B39" s="12">
+      <c r="A39" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="B39" s="15">
         <v>1250</v>
       </c>
-      <c r="C39" s="12">
+      <c r="C39" s="15">
         <v>1250</v>
       </c>
-      <c r="D39" s="12">
+      <c r="D39" s="15">
         <v>1250</v>
       </c>
-      <c r="E39" s="12">
+      <c r="E39" s="15">
         <v>1250</v>
       </c>
-      <c r="F39" s="12">
+      <c r="F39" s="15">
         <v>1250</v>
       </c>
-      <c r="G39" s="12">
+      <c r="G39" s="15">
         <v>1250</v>
       </c>
-      <c r="H39" s="12">
+      <c r="H39" s="15">
         <v>1250</v>
       </c>
-      <c r="I39" s="12">
+      <c r="I39" s="15">
         <v>1250</v>
       </c>
-      <c r="J39" s="12">
+      <c r="J39" s="15">
         <v>1250</v>
       </c>
-      <c r="K39" s="12">
+      <c r="K39" s="15">
         <v>1250</v>
       </c>
-      <c r="L39" s="12">
-        <v>0</v>
-      </c>
-      <c r="M39" s="12">
-        <v>0</v>
-      </c>
-      <c r="N39" s="12">
+      <c r="L39" s="15">
+        <v>0</v>
+      </c>
+      <c r="M39" s="15">
+        <v>0</v>
+      </c>
+      <c r="N39" s="15">
         <f>SUM(B39:M39)</f>
         <v>12500</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A40" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="B40" s="12">
+      <c r="A40" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="B40" s="15">
         <v>1667</v>
       </c>
-      <c r="C40" s="12">
+      <c r="C40" s="15">
         <v>1667</v>
       </c>
-      <c r="D40" s="12">
+      <c r="D40" s="15">
         <v>1667</v>
       </c>
-      <c r="E40" s="12">
+      <c r="E40" s="15">
         <v>1667</v>
       </c>
-      <c r="F40" s="12">
+      <c r="F40" s="15">
         <v>1667</v>
       </c>
-      <c r="G40" s="12">
+      <c r="G40" s="15">
         <v>1667</v>
       </c>
-      <c r="H40" s="12">
+      <c r="H40" s="15">
         <v>1667</v>
       </c>
-      <c r="I40" s="12">
+      <c r="I40" s="15">
         <v>1667</v>
       </c>
-      <c r="J40" s="12">
+      <c r="J40" s="15">
         <v>1667</v>
       </c>
-      <c r="K40" s="12">
+      <c r="K40" s="15">
         <v>1667</v>
       </c>
-      <c r="L40" s="12">
-        <v>0</v>
-      </c>
-      <c r="M40" s="12">
-        <v>0</v>
-      </c>
-      <c r="N40" s="12">
+      <c r="L40" s="15">
+        <v>0</v>
+      </c>
+      <c r="M40" s="15">
+        <v>0</v>
+      </c>
+      <c r="N40" s="15">
         <f>SUM(B40:M40)</f>
         <v>16667</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A41" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="B41" s="12">
+      <c r="A41" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="B41" s="15">
         <v>8000</v>
       </c>
-      <c r="C41" s="12">
+      <c r="C41" s="15">
         <v>8000</v>
       </c>
-      <c r="D41" s="12">
+      <c r="D41" s="15">
         <v>8000</v>
       </c>
-      <c r="E41" s="12">
+      <c r="E41" s="15">
         <v>8000</v>
       </c>
-      <c r="F41" s="12">
+      <c r="F41" s="15">
         <v>8000</v>
       </c>
-      <c r="G41" s="12">
+      <c r="G41" s="15">
         <v>8000</v>
       </c>
-      <c r="H41" s="12">
+      <c r="H41" s="15">
         <v>8000</v>
       </c>
-      <c r="I41" s="12">
+      <c r="I41" s="15">
         <v>8000</v>
       </c>
-      <c r="J41" s="12">
+      <c r="J41" s="15">
         <v>8000</v>
       </c>
-      <c r="K41" s="12">
+      <c r="K41" s="15">
         <v>8000</v>
       </c>
-      <c r="L41" s="12">
-        <v>0</v>
-      </c>
-      <c r="M41" s="12">
-        <v>0</v>
-      </c>
-      <c r="N41" s="12">
+      <c r="L41" s="15">
+        <v>0</v>
+      </c>
+      <c r="M41" s="15">
+        <v>0</v>
+      </c>
+      <c r="N41" s="15">
         <f>SUM(B41:M41)</f>
         <v>80000</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A42" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="B42" s="12">
+      <c r="A42" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="B42" s="15">
         <v>6000</v>
       </c>
-      <c r="C42" s="12">
+      <c r="C42" s="15">
         <v>6000</v>
       </c>
-      <c r="D42" s="12">
+      <c r="D42" s="15">
         <v>6000</v>
       </c>
-      <c r="E42" s="12">
+      <c r="E42" s="15">
         <v>6000</v>
       </c>
-      <c r="F42" s="12">
+      <c r="F42" s="15">
         <v>6000</v>
       </c>
-      <c r="G42" s="12">
+      <c r="G42" s="15">
         <v>6000</v>
       </c>
-      <c r="H42" s="12">
+      <c r="H42" s="15">
         <v>6000</v>
       </c>
-      <c r="I42" s="12">
+      <c r="I42" s="15">
         <v>6000</v>
       </c>
-      <c r="J42" s="12">
+      <c r="J42" s="15">
         <v>6000</v>
       </c>
-      <c r="K42" s="12">
+      <c r="K42" s="15">
         <v>6000</v>
       </c>
-      <c r="L42" s="12">
-        <v>0</v>
-      </c>
-      <c r="M42" s="12">
-        <v>0</v>
-      </c>
-      <c r="N42" s="12">
+      <c r="L42" s="15">
+        <v>0</v>
+      </c>
+      <c r="M42" s="15">
+        <v>0</v>
+      </c>
+      <c r="N42" s="15">
         <f>SUM(B42:M42)</f>
         <v>60000</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A43" s="20" t="s">
-        <v>144</v>
-      </c>
-      <c r="B43" s="21">
+      <c r="A43" s="23" t="s">
+        <v>166</v>
+      </c>
+      <c r="B43" s="24">
         <v>19000</v>
       </c>
-      <c r="C43" s="21">
+      <c r="C43" s="24">
         <v>19000</v>
       </c>
-      <c r="D43" s="21">
+      <c r="D43" s="24">
         <v>19000</v>
       </c>
-      <c r="E43" s="21">
+      <c r="E43" s="24">
         <v>19000</v>
       </c>
-      <c r="F43" s="21">
+      <c r="F43" s="24">
         <v>19000</v>
       </c>
-      <c r="G43" s="21">
+      <c r="G43" s="24">
         <v>19000</v>
       </c>
-      <c r="H43" s="21">
+      <c r="H43" s="24">
         <v>19000</v>
       </c>
-      <c r="I43" s="21">
+      <c r="I43" s="24">
         <v>19000</v>
       </c>
-      <c r="J43" s="21">
+      <c r="J43" s="24">
         <v>19000</v>
       </c>
-      <c r="K43" s="21">
+      <c r="K43" s="24">
         <v>19000</v>
       </c>
-      <c r="L43" s="21">
-        <v>0</v>
-      </c>
-      <c r="M43" s="21">
-        <v>0</v>
-      </c>
-      <c r="N43" s="21">
+      <c r="L43" s="24">
+        <v>0</v>
+      </c>
+      <c r="M43" s="24">
+        <v>0</v>
+      </c>
+      <c r="N43" s="24">
         <f>SUM(B43:M43)</f>
         <v>190000</v>
       </c>
     </row>
     <row r="44" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A44" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="B44" s="19">
+      <c r="A44" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="B44" s="22">
         <f>B27+B30+B36+B43</f>
         <v>54500</v>
       </c>
-      <c r="C44" s="19">
+      <c r="C44" s="22">
         <f>C27+C30+C36+C43</f>
         <v>54500</v>
       </c>
-      <c r="D44" s="19">
+      <c r="D44" s="22">
         <f>D27+D30+D36+D43</f>
         <v>54500</v>
       </c>
-      <c r="E44" s="19">
+      <c r="E44" s="22">
         <f>E27+E30+E36+E43</f>
         <v>54500</v>
       </c>
-      <c r="F44" s="19">
+      <c r="F44" s="22">
         <f>F27+F30+F36+F43</f>
         <v>54500</v>
       </c>
-      <c r="G44" s="19">
+      <c r="G44" s="22">
         <f>G27+G30+G36+G43</f>
         <v>54500</v>
       </c>
-      <c r="H44" s="19">
+      <c r="H44" s="22">
         <f>H27+H30+H36+H43</f>
         <v>54500</v>
       </c>
-      <c r="I44" s="19">
+      <c r="I44" s="22">
         <f>I27+I30+I36+I43</f>
         <v>54500</v>
       </c>
-      <c r="J44" s="19">
+      <c r="J44" s="22">
         <f>J27+J30+J36+J43</f>
         <v>54500</v>
       </c>
-      <c r="K44" s="19">
+      <c r="K44" s="22">
         <f>K27+K30+K36+K43</f>
         <v>54500</v>
       </c>
-      <c r="L44" s="19" t="str">
+      <c r="L44" s="22" t="str">
         <f>L27+L30+L36+L43</f>
         <v>0</v>
       </c>
-      <c r="M44" s="19" t="str">
+      <c r="M44" s="22" t="str">
         <f>M27+M30+M36+M43</f>
         <v>0</v>
       </c>
-      <c r="N44" s="19">
+      <c r="N44" s="22">
         <f>SUM(B44:M44)</f>
         <v>545000</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>40</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A46" s="17" t="s">
-        <v>201</v>
-      </c>
-      <c r="B46" s="12">
+      <c r="A46" s="20" t="s">
+        <v>223</v>
+      </c>
+      <c r="B46" s="15">
         <v>13735</v>
       </c>
-      <c r="C46" s="12">
+      <c r="C46" s="15">
         <v>13735</v>
       </c>
-      <c r="D46" s="12">
+      <c r="D46" s="15">
         <v>13735</v>
       </c>
-      <c r="E46" s="12">
+      <c r="E46" s="15">
         <v>13735</v>
       </c>
-      <c r="F46" s="12">
+      <c r="F46" s="15">
         <v>13735</v>
       </c>
-      <c r="G46" s="12">
+      <c r="G46" s="15">
         <v>13735</v>
       </c>
-      <c r="H46" s="12">
+      <c r="H46" s="15">
         <v>13735</v>
       </c>
-      <c r="I46" s="12">
+      <c r="I46" s="15">
         <v>13735</v>
       </c>
-      <c r="J46" s="12">
+      <c r="J46" s="15">
         <v>13735</v>
       </c>
-      <c r="K46" s="12">
+      <c r="K46" s="15">
         <v>13735</v>
       </c>
-      <c r="L46" s="12">
+      <c r="L46" s="15">
         <v>13735</v>
       </c>
-      <c r="M46" s="12">
+      <c r="M46" s="15">
         <v>13735</v>
       </c>
-      <c r="N46" s="12">
+      <c r="N46" s="15">
         <f>SUM(B46:M46)</f>
         <v>164825</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>40</v>
+        <v>5</v>
       </c>
     </row>
     <row r="48" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A48" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="B48" s="3"/>
-      <c r="C48" s="3"/>
-      <c r="D48" s="3"/>
-      <c r="E48" s="3"/>
-      <c r="F48" s="3"/>
-      <c r="G48" s="3"/>
-      <c r="H48" s="3"/>
-      <c r="I48" s="3"/>
-      <c r="J48" s="3"/>
-      <c r="K48" s="3"/>
-      <c r="L48" s="3"/>
-      <c r="M48" s="3"/>
-      <c r="N48" s="3"/>
+      <c r="A48" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="B48" s="6"/>
+      <c r="C48" s="6"/>
+      <c r="D48" s="6"/>
+      <c r="E48" s="6"/>
+      <c r="F48" s="6"/>
+      <c r="G48" s="6"/>
+      <c r="H48" s="6"/>
+      <c r="I48" s="6"/>
+      <c r="J48" s="6"/>
+      <c r="K48" s="6"/>
+      <c r="L48" s="6"/>
+      <c r="M48" s="6"/>
+      <c r="N48" s="6"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A49" s="17" t="s">
-        <v>153</v>
-      </c>
-      <c r="B49" s="21">
+      <c r="A49" s="20" t="s">
+        <v>175</v>
+      </c>
+      <c r="B49" s="24">
         <f>B22+B44+B46</f>
         <v>170878</v>
       </c>
-      <c r="C49" s="21">
+      <c r="C49" s="24">
         <f>C22+C44+C46</f>
         <v>170878</v>
       </c>
-      <c r="D49" s="21">
+      <c r="D49" s="24">
         <f>D22+D44+D46</f>
         <v>170878</v>
       </c>
-      <c r="E49" s="21">
+      <c r="E49" s="24">
         <f>E22+E44+E46</f>
         <v>170878</v>
       </c>
-      <c r="F49" s="21">
+      <c r="F49" s="24">
         <f>F22+F44+F46</f>
         <v>170878</v>
       </c>
-      <c r="G49" s="21">
+      <c r="G49" s="24">
         <f>G22+G44+G46</f>
         <v>170878</v>
       </c>
-      <c r="H49" s="21">
+      <c r="H49" s="24">
         <f>H22+H44+H46</f>
         <v>170878</v>
       </c>
-      <c r="I49" s="21">
+      <c r="I49" s="24">
         <f>I22+I44+I46</f>
         <v>170878</v>
       </c>
-      <c r="J49" s="21">
+      <c r="J49" s="24">
         <f>J22+J44+J46</f>
         <v>170878</v>
       </c>
-      <c r="K49" s="21">
+      <c r="K49" s="24">
         <f>K22+K44+K46</f>
         <v>170878</v>
       </c>
-      <c r="L49" s="21">
+      <c r="L49" s="24">
         <f>L22+L44+L46</f>
         <v>13735</v>
       </c>
-      <c r="M49" s="21">
+      <c r="M49" s="24">
         <f>M22+M44+M46</f>
         <v>13735</v>
       </c>
-      <c r="N49" s="21">
+      <c r="N49" s="24">
         <f>SUM(B49:M49)</f>
         <v>1736250</v>
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A50" s="17" t="s">
-        <v>203</v>
-      </c>
-      <c r="B50" s="21">
+      <c r="A50" s="20" t="s">
+        <v>225</v>
+      </c>
+      <c r="B50" s="24">
         <f>B10-B49</f>
         <v>-16278</v>
       </c>
-      <c r="C50" s="21">
+      <c r="C50" s="24">
         <f>C10-C49</f>
         <v>-16278</v>
       </c>
-      <c r="D50" s="21">
+      <c r="D50" s="24">
         <f>D10-D49</f>
         <v>-16278</v>
       </c>
-      <c r="E50" s="21">
+      <c r="E50" s="24">
         <f>E10-E49</f>
         <v>-16278</v>
       </c>
-      <c r="F50" s="21">
+      <c r="F50" s="24">
         <f>F10-F49</f>
         <v>-16278</v>
       </c>
-      <c r="G50" s="21">
+      <c r="G50" s="24">
         <f>G10-G49</f>
         <v>-16278</v>
       </c>
-      <c r="H50" s="21">
+      <c r="H50" s="24">
         <f>H10-H49</f>
         <v>-16278</v>
       </c>
-      <c r="I50" s="21">
+      <c r="I50" s="24">
         <f>I10-I49</f>
         <v>-16278</v>
       </c>
-      <c r="J50" s="21">
+      <c r="J50" s="24">
         <f>J10-J49</f>
         <v>-16278</v>
       </c>
-      <c r="K50" s="21">
+      <c r="K50" s="24">
         <f>K10-K49</f>
         <v>-16278</v>
       </c>
-      <c r="L50" s="21">
+      <c r="L50" s="24">
         <f>L10-L49</f>
         <v>-13735</v>
       </c>
-      <c r="M50" s="21">
+      <c r="M50" s="24">
         <f>M10-M49</f>
         <v>-13735</v>
       </c>
-      <c r="N50" s="21">
+      <c r="N50" s="24">
         <f>SUM(B50:M50)</f>
         <v>-190250</v>
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A51" s="17" t="s">
-        <v>204</v>
-      </c>
-      <c r="B51" s="21">
+      <c r="A51" s="20" t="s">
+        <v>226</v>
+      </c>
+      <c r="B51" s="24">
         <f>0+B50</f>
         <v>-16278</v>
       </c>
-      <c r="C51" s="21">
+      <c r="C51" s="24">
         <f>B51+C50</f>
         <v>-32556</v>
       </c>
-      <c r="D51" s="21">
+      <c r="D51" s="24">
         <f>C51+D50</f>
         <v>-48834</v>
       </c>
-      <c r="E51" s="21">
+      <c r="E51" s="24">
         <f>D51+E50</f>
         <v>-65112</v>
       </c>
-      <c r="F51" s="21">
+      <c r="F51" s="24">
         <f>E51+F50</f>
         <v>-81390</v>
       </c>
-      <c r="G51" s="21">
+      <c r="G51" s="24">
         <f>F51+G50</f>
         <v>-97668</v>
       </c>
-      <c r="H51" s="21">
+      <c r="H51" s="24">
         <f>G51+H50</f>
         <v>-113946</v>
       </c>
-      <c r="I51" s="21">
+      <c r="I51" s="24">
         <f>H51+I50</f>
         <v>-130224</v>
       </c>
-      <c r="J51" s="21">
+      <c r="J51" s="24">
         <f>I51+J50</f>
         <v>-146502</v>
       </c>
-      <c r="K51" s="21">
+      <c r="K51" s="24">
         <f>J51+K50</f>
         <v>-162780</v>
       </c>
-      <c r="L51" s="21">
+      <c r="L51" s="24">
         <f>K51+L50</f>
         <v>-176515</v>
       </c>
-      <c r="M51" s="21">
+      <c r="M51" s="24">
         <f>L51+M50</f>
         <v>-190250</v>
       </c>
-      <c r="N51" s="21">
+      <c r="N51" s="24">
         <f>M51</f>
         <v>-190250</v>
       </c>
     </row>
     <row r="53" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="B53" s="3"/>
-      <c r="C53" s="3"/>
+      <c r="A53" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="B53" s="6"/>
+      <c r="C53" s="6"/>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="B54" s="12">
+      <c r="A54" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="B54" s="15">
         <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A55" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="B55" s="21">
+      <c r="A55" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="B55" s="24">
         <f>M51</f>
         <v>-190250</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A56" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="B56" s="12">
+      <c r="A56" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="B56" s="15">
         <f>MIN(B51:M51)</f>
         <v>-190250</v>
       </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A58" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="B58" s="15"/>
-      <c r="C58" s="15"/>
-      <c r="D58" s="15"/>
-      <c r="E58" s="15"/>
-      <c r="F58" s="15"/>
-      <c r="G58" s="15"/>
-      <c r="H58" s="15"/>
-      <c r="I58" s="15"/>
-      <c r="J58" s="15"/>
-      <c r="K58" s="15"/>
-      <c r="L58" s="15"/>
-      <c r="M58" s="15"/>
-      <c r="N58" s="15"/>
+      <c r="A58" s="18" t="s">
+        <v>137</v>
+      </c>
+      <c r="B58" s="18"/>
+      <c r="C58" s="18"/>
+      <c r="D58" s="18"/>
+      <c r="E58" s="18"/>
+      <c r="F58" s="18"/>
+      <c r="G58" s="18"/>
+      <c r="H58" s="18"/>
+      <c r="I58" s="18"/>
+      <c r="J58" s="18"/>
+      <c r="K58" s="18"/>
+      <c r="L58" s="18"/>
+      <c r="M58" s="18"/>
+      <c r="N58" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -5940,4 +6366,398 @@
     <oddFooter>&amp;L&amp;8Built by SchoolStack Budget  •  budget.schoolstack.ai&amp;C&amp;8Page &amp;P of &amp;N&amp;R&amp;8&amp;D</oddFooter>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B2:G26"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="4" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="3" max="7" width="16" customWidth="1"/>
+    <col min="8" max="8" width="40" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" ht="30" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B2" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+    </row>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B3" s="34" t="s">
+        <v>231</v>
+      </c>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="34"/>
+      <c r="G3" s="34"/>
+    </row>
+    <row r="5" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B5" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>233</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B6" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="C6" s="35">
+        <v>120</v>
+      </c>
+      <c r="D6" s="35">
+        <v>200</v>
+      </c>
+      <c r="E6" s="35">
+        <v>300</v>
+      </c>
+      <c r="F6" s="35">
+        <v>375</v>
+      </c>
+      <c r="G6" s="35">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B7" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="C7" s="36">
+        <v>1546000</v>
+      </c>
+      <c r="D7" s="36">
+        <v>2522800</v>
+      </c>
+      <c r="E7" s="36">
+        <v>3784600</v>
+      </c>
+      <c r="F7" s="36">
+        <v>4759125</v>
+      </c>
+      <c r="G7" s="36">
+        <v>5184400</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B8" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="C8" s="36">
+        <v>1026431.25</v>
+      </c>
+      <c r="D8" s="36">
+        <v>1231717.5</v>
+      </c>
+      <c r="E8" s="36">
+        <v>1231717.5</v>
+      </c>
+      <c r="F8" s="36">
+        <v>1231717.5</v>
+      </c>
+      <c r="G8" s="36">
+        <v>1231717.5</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B9" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="C9" s="36">
+        <v>654000</v>
+      </c>
+      <c r="D9" s="36">
+        <v>887860</v>
+      </c>
+      <c r="E9" s="36">
+        <v>1190521.4</v>
+      </c>
+      <c r="F9" s="36">
+        <v>1439089.0320000001</v>
+      </c>
+      <c r="G9" s="36">
+        <v>1554923.90296</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B10" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="C10" s="36">
+        <v>49824.605221179416</v>
+      </c>
+      <c r="D10" s="36">
+        <v>49824.605221179416</v>
+      </c>
+      <c r="E10" s="36">
+        <v>49824.605221179416</v>
+      </c>
+      <c r="F10" s="36">
+        <v>49824.605221179416</v>
+      </c>
+      <c r="G10" s="36">
+        <v>49824.605221179416</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B11" s="20" t="s">
+        <v>176</v>
+      </c>
+      <c r="C11" s="37">
+        <v>-184255.85522117943</v>
+      </c>
+      <c r="D11" s="38">
+        <v>353397.89477882057</v>
+      </c>
+      <c r="E11" s="38">
+        <v>1312536.4947788208</v>
+      </c>
+      <c r="F11" s="38">
+        <v>2038493.8627788206</v>
+      </c>
+      <c r="G11" s="38">
+        <v>2347933.9918188206</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B12" s="20" t="s">
+        <v>183</v>
+      </c>
+      <c r="C12" s="37">
+        <v>-184255.85522117943</v>
+      </c>
+      <c r="D12" s="38">
+        <v>169142.03955764114</v>
+      </c>
+      <c r="E12" s="38">
+        <v>1481678.534336462</v>
+      </c>
+      <c r="F12" s="38">
+        <v>3520172.3971152827</v>
+      </c>
+      <c r="G12" s="38">
+        <v>5868106.388934104</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B13" s="20" t="s">
+        <v>242</v>
+      </c>
+      <c r="C13" s="39">
+        <v>-0.11918231256221179</v>
+      </c>
+      <c r="D13" s="40">
+        <v>0.14008161359553692</v>
+      </c>
+      <c r="E13" s="40">
+        <v>0.34680983321323805</v>
+      </c>
+      <c r="F13" s="40">
+        <v>0.4283337510107048</v>
+      </c>
+      <c r="G13" s="40">
+        <v>0.4528844209202262</v>
+      </c>
+    </row>
+    <row r="15" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B15" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="G15" s="6"/>
+    </row>
+    <row r="16" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B16" s="41" t="s">
+        <v>247</v>
+      </c>
+      <c r="C16" s="42" t="s">
+        <v>248</v>
+      </c>
+      <c r="D16" s="43" t="s">
+        <v>249</v>
+      </c>
+      <c r="E16" s="43"/>
+      <c r="F16" s="44" t="s">
+        <v>250</v>
+      </c>
+      <c r="G16" s="44"/>
+    </row>
+    <row r="17" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="41" t="s">
+        <v>251</v>
+      </c>
+      <c r="C17" s="45" t="s">
+        <v>252</v>
+      </c>
+      <c r="D17" s="43" t="s">
+        <v>253</v>
+      </c>
+      <c r="E17" s="43"/>
+      <c r="F17" s="44" t="s">
+        <v>254</v>
+      </c>
+      <c r="G17" s="44"/>
+    </row>
+    <row r="18" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B18" s="41" t="s">
+        <v>255</v>
+      </c>
+      <c r="C18" s="42" t="s">
+        <v>248</v>
+      </c>
+      <c r="D18" s="43" t="s">
+        <v>256</v>
+      </c>
+      <c r="E18" s="43"/>
+      <c r="F18" s="44" t="s">
+        <v>257</v>
+      </c>
+      <c r="G18" s="44"/>
+    </row>
+    <row r="19" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B19" s="41" t="s">
+        <v>258</v>
+      </c>
+      <c r="C19" s="42" t="s">
+        <v>248</v>
+      </c>
+      <c r="D19" s="43" t="s">
+        <v>259</v>
+      </c>
+      <c r="E19" s="43"/>
+      <c r="F19" s="44" t="s">
+        <v>260</v>
+      </c>
+      <c r="G19" s="44"/>
+    </row>
+    <row r="20" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B20" s="41" t="s">
+        <v>261</v>
+      </c>
+      <c r="C20" s="42" t="s">
+        <v>248</v>
+      </c>
+      <c r="D20" s="43" t="s">
+        <v>262</v>
+      </c>
+      <c r="E20" s="43"/>
+      <c r="F20" s="44" t="s">
+        <v>263</v>
+      </c>
+      <c r="G20" s="44"/>
+    </row>
+    <row r="21" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B21" s="41" t="s">
+        <v>264</v>
+      </c>
+      <c r="C21" s="42" t="s">
+        <v>248</v>
+      </c>
+      <c r="D21" s="43" t="s">
+        <v>265</v>
+      </c>
+      <c r="E21" s="43"/>
+      <c r="F21" s="44" t="s">
+        <v>266</v>
+      </c>
+      <c r="G21" s="44"/>
+    </row>
+    <row r="22" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B22" s="41" t="s">
+        <v>267</v>
+      </c>
+      <c r="C22" s="42" t="s">
+        <v>248</v>
+      </c>
+      <c r="D22" s="43" t="s">
+        <v>268</v>
+      </c>
+      <c r="E22" s="43"/>
+      <c r="F22" s="44" t="s">
+        <v>269</v>
+      </c>
+      <c r="G22" s="44"/>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B24" s="41" t="s">
+        <v>270</v>
+      </c>
+      <c r="C24" s="20" t="s">
+        <v>271</v>
+      </c>
+      <c r="D24" s="20"/>
+      <c r="E24" s="20"/>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B26" s="46" t="s">
+        <v>137</v>
+      </c>
+      <c r="C26" s="46"/>
+      <c r="D26" s="46"/>
+      <c r="E26" s="46"/>
+      <c r="F26" s="46"/>
+      <c r="G26" s="46"/>
+    </row>
+  </sheetData>
+  <mergeCells count="20">
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="B26:G26"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddHeader>&amp;L&amp;10&amp;BCivic Scholars Charter&amp;R&amp;8&amp;IFinancial Health</oddHeader>
+    <oddFooter>&amp;L&amp;8Built by SchoolStack Budget  •  budget.schoolstack.ai&amp;C&amp;8Page &amp;P of &amp;N&amp;R&amp;8&amp;D</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>
--- a/artifacts/api-server/qa-output/Formula_Export_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Formula_Export_Charter_Public_Funding.xlsx
@@ -19,7 +19,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'5-Year Model'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Year 1 Pro Forma'!$A1:$N58</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Year 1 Pro Forma'!$1:$2</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'Financial Health'!$A1:$G26</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Financial Health'!$A1:$G33</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Financial Health'!$1:$2</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="280">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -756,6 +756,30 @@
   </si>
   <si>
     <t>Net Margin</t>
+  </si>
+  <si>
+    <t>Revenue per Student</t>
+  </si>
+  <si>
+    <t>Payroll %</t>
+  </si>
+  <si>
+    <t>Facility %</t>
+  </si>
+  <si>
+    <t>Operating Margin</t>
+  </si>
+  <si>
+    <t>DSCR</t>
+  </si>
+  <si>
+    <t>Break-even Year</t>
+  </si>
+  <si>
+    <t>Cash Runway</t>
+  </si>
+  <si>
+    <t>0 months</t>
   </si>
   <si>
     <t>FINANCIAL HEALTH SIGNALS</t>
@@ -1020,7 +1044,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1082,6 +1106,14 @@
     <xf numFmtId="166" fontId="10" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="167" fontId="10" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="167" fontId="10" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -6373,7 +6405,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:G26"/>
+  <dimension ref="B2:G33"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -6582,176 +6614,302 @@
         <v>0.4528844209202262</v>
       </c>
     </row>
-    <row r="15" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="6" t="s">
+    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B14" s="20" t="s">
         <v>243</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C14" s="36">
+        <v>12883.333333333334</v>
+      </c>
+      <c r="D14" s="36">
+        <v>12614</v>
+      </c>
+      <c r="E14" s="36">
+        <v>12615.333333333334</v>
+      </c>
+      <c r="F14" s="36">
+        <v>12691</v>
+      </c>
+      <c r="G14" s="36">
+        <v>12961</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B15" s="20" t="s">
         <v>244</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="C15" s="39">
+        <v>0.6639270698576973</v>
+      </c>
+      <c r="D15" s="40">
+        <v>0.48823430315522437</v>
+      </c>
+      <c r="E15" s="40">
+        <v>0.3254551339639592</v>
+      </c>
+      <c r="F15" s="40">
+        <v>0.25881175636277676</v>
+      </c>
+      <c r="G15" s="40">
+        <v>0.23758149448345034</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B16" s="20" t="s">
         <v>245</v>
       </c>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6" t="s">
+      <c r="C16" s="40">
+        <v>0.12690815006468306</v>
+      </c>
+      <c r="D16" s="40">
+        <v>0.10558030759473601</v>
+      </c>
+      <c r="E16" s="40">
+        <v>0.09437098240236748</v>
+      </c>
+      <c r="F16" s="40">
+        <v>0.09071556422661729</v>
+      </c>
+      <c r="G16" s="40">
+        <v>0.08997707948615076</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="20" t="s">
         <v>246</v>
       </c>
-      <c r="G15" s="6"/>
-    </row>
-    <row r="16" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="41" t="s">
+      <c r="C17" s="39">
+        <v>-0.08695423673997413</v>
+      </c>
+      <c r="D17" s="40">
+        <v>0.15983133819565562</v>
+      </c>
+      <c r="E17" s="40">
+        <v>0.35997492469481585</v>
+      </c>
+      <c r="F17" s="40">
+        <v>0.4388030295484989</v>
+      </c>
+      <c r="G17" s="40">
+        <v>0.4624949072293804</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B18" s="20" t="s">
         <v>247</v>
       </c>
-      <c r="C16" s="42" t="s">
+      <c r="C18" s="41">
+        <v>-2.698089616630942</v>
+      </c>
+      <c r="D18" s="42">
+        <v>8.092838833544805</v>
+      </c>
+      <c r="E18" s="42">
+        <v>27.34313887590801</v>
+      </c>
+      <c r="F18" s="42">
+        <v>41.91339718056208</v>
+      </c>
+      <c r="G18" s="42">
+        <v>48.12398585791026</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B19" s="20" t="s">
         <v>248</v>
       </c>
-      <c r="D16" s="43" t="s">
+      <c r="C19" s="43" t="s">
+        <v>234</v>
+      </c>
+      <c r="D19" s="43"/>
+      <c r="E19" s="43"/>
+      <c r="F19" s="43"/>
+      <c r="G19" s="43"/>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B20" s="20" t="s">
         <v>249</v>
       </c>
-      <c r="E16" s="43"/>
-      <c r="F16" s="44" t="s">
+      <c r="C20" s="44" t="s">
         <v>250</v>
       </c>
-      <c r="G16" s="44"/>
-    </row>
-    <row r="17" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="41" t="s">
+      <c r="D20" s="44"/>
+      <c r="E20" s="44"/>
+      <c r="F20" s="44"/>
+      <c r="G20" s="44"/>
+    </row>
+    <row r="22" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B22" s="6" t="s">
         <v>251</v>
       </c>
-      <c r="C17" s="45" t="s">
+      <c r="C22" s="6" t="s">
         <v>252</v>
       </c>
-      <c r="D17" s="43" t="s">
+      <c r="D22" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="E17" s="43"/>
-      <c r="F17" s="44" t="s">
+      <c r="E22" s="6"/>
+      <c r="F22" s="6" t="s">
         <v>254</v>
       </c>
-      <c r="G17" s="44"/>
-    </row>
-    <row r="18" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B18" s="41" t="s">
+      <c r="G22" s="6"/>
+    </row>
+    <row r="23" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B23" s="45" t="s">
         <v>255</v>
       </c>
-      <c r="C18" s="42" t="s">
-        <v>248</v>
-      </c>
-      <c r="D18" s="43" t="s">
+      <c r="C23" s="46" t="s">
         <v>256</v>
       </c>
-      <c r="E18" s="43"/>
-      <c r="F18" s="44" t="s">
+      <c r="D23" s="47" t="s">
         <v>257</v>
       </c>
-      <c r="G18" s="44"/>
-    </row>
-    <row r="19" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="41" t="s">
+      <c r="E23" s="47"/>
+      <c r="F23" s="48" t="s">
         <v>258</v>
       </c>
-      <c r="C19" s="42" t="s">
-        <v>248</v>
-      </c>
-      <c r="D19" s="43" t="s">
+      <c r="G23" s="48"/>
+    </row>
+    <row r="24" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B24" s="45" t="s">
         <v>259</v>
       </c>
-      <c r="E19" s="43"/>
-      <c r="F19" s="44" t="s">
+      <c r="C24" s="49" t="s">
         <v>260</v>
       </c>
-      <c r="G19" s="44"/>
-    </row>
-    <row r="20" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B20" s="41" t="s">
+      <c r="D24" s="47" t="s">
         <v>261</v>
       </c>
-      <c r="C20" s="42" t="s">
-        <v>248</v>
-      </c>
-      <c r="D20" s="43" t="s">
+      <c r="E24" s="47"/>
+      <c r="F24" s="48" t="s">
         <v>262</v>
       </c>
-      <c r="E20" s="43"/>
-      <c r="F20" s="44" t="s">
+      <c r="G24" s="48"/>
+    </row>
+    <row r="25" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B25" s="45" t="s">
         <v>263</v>
       </c>
-      <c r="G20" s="44"/>
-    </row>
-    <row r="21" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B21" s="41" t="s">
+      <c r="C25" s="46" t="s">
+        <v>256</v>
+      </c>
+      <c r="D25" s="47" t="s">
         <v>264</v>
       </c>
-      <c r="C21" s="42" t="s">
-        <v>248</v>
-      </c>
-      <c r="D21" s="43" t="s">
+      <c r="E25" s="47"/>
+      <c r="F25" s="48" t="s">
         <v>265</v>
       </c>
-      <c r="E21" s="43"/>
-      <c r="F21" s="44" t="s">
+      <c r="G25" s="48"/>
+    </row>
+    <row r="26" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B26" s="45" t="s">
         <v>266</v>
       </c>
-      <c r="G21" s="44"/>
-    </row>
-    <row r="22" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B22" s="41" t="s">
+      <c r="C26" s="46" t="s">
+        <v>256</v>
+      </c>
+      <c r="D26" s="47" t="s">
         <v>267</v>
       </c>
-      <c r="C22" s="42" t="s">
-        <v>248</v>
-      </c>
-      <c r="D22" s="43" t="s">
+      <c r="E26" s="47"/>
+      <c r="F26" s="48" t="s">
         <v>268</v>
       </c>
-      <c r="E22" s="43"/>
-      <c r="F22" s="44" t="s">
+      <c r="G26" s="48"/>
+    </row>
+    <row r="27" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B27" s="45" t="s">
         <v>269</v>
       </c>
-      <c r="G22" s="44"/>
-    </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B24" s="41" t="s">
+      <c r="C27" s="46" t="s">
+        <v>256</v>
+      </c>
+      <c r="D27" s="47" t="s">
         <v>270</v>
       </c>
-      <c r="C24" s="20" t="s">
+      <c r="E27" s="47"/>
+      <c r="F27" s="48" t="s">
         <v>271</v>
       </c>
-      <c r="D24" s="20"/>
-      <c r="E24" s="20"/>
-    </row>
-    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B26" s="46" t="s">
+      <c r="G27" s="48"/>
+    </row>
+    <row r="28" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B28" s="45" t="s">
+        <v>272</v>
+      </c>
+      <c r="C28" s="46" t="s">
+        <v>256</v>
+      </c>
+      <c r="D28" s="47" t="s">
+        <v>273</v>
+      </c>
+      <c r="E28" s="47"/>
+      <c r="F28" s="48" t="s">
+        <v>274</v>
+      </c>
+      <c r="G28" s="48"/>
+    </row>
+    <row r="29" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B29" s="45" t="s">
+        <v>275</v>
+      </c>
+      <c r="C29" s="46" t="s">
+        <v>256</v>
+      </c>
+      <c r="D29" s="47" t="s">
+        <v>276</v>
+      </c>
+      <c r="E29" s="47"/>
+      <c r="F29" s="48" t="s">
+        <v>277</v>
+      </c>
+      <c r="G29" s="48"/>
+    </row>
+    <row r="31" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B31" s="45" t="s">
+        <v>278</v>
+      </c>
+      <c r="C31" s="20" t="s">
+        <v>279</v>
+      </c>
+      <c r="D31" s="20"/>
+      <c r="E31" s="20"/>
+    </row>
+    <row r="33" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B33" s="50" t="s">
         <v>137</v>
       </c>
-      <c r="C26" s="46"/>
-      <c r="D26" s="46"/>
-      <c r="E26" s="46"/>
-      <c r="F26" s="46"/>
-      <c r="G26" s="46"/>
+      <c r="C33" s="50"/>
+      <c r="D33" s="50"/>
+      <c r="E33" s="50"/>
+      <c r="F33" s="50"/>
+      <c r="G33" s="50"/>
     </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="22">
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="B3:G3"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="C20:G20"/>
     <mergeCell ref="D22:E22"/>
     <mergeCell ref="F22:G22"/>
-    <mergeCell ref="C24:E24"/>
-    <mergeCell ref="B26:G26"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="C31:E31"/>
+    <mergeCell ref="B33:G33"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>

--- a/artifacts/api-server/qa-output/Formula_Export_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Formula_Export_Charter_Public_Funding.xlsx
@@ -11,7 +11,7 @@
     <sheet sheetId="5" name="Financial Health" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Instructions'!$A1:$B29</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Instructions'!$A1:$B37</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Instructions'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Assumptions'!$A1:$J70</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Assumptions'!$1:$3</definedName>
@@ -27,21 +27,27 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="286">
   <si>
     <t>How to Use This Workbook</t>
   </si>
   <si>
+    <t>Civic Scholars Charter</t>
+  </si>
+  <si>
+    <t>Generated March 26, 2026 · nonprofit_501c3</t>
+  </si>
+  <si>
     <t>Cell Color Legend</t>
   </si>
   <si>
-    <t>Blue cells are editable inputs — change these to update your model.</t>
-  </si>
-  <si>
-    <t>White cells contain formulas — do not edit (they recalculate automatically).</t>
-  </si>
-  <si>
-    <t>Green cells are key outputs and summary metrics.</t>
+    <t xml:space="preserve">  Blue cells are editable inputs — change these to update your model.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  White cells contain formulas — do not edit (they recalculate automatically).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Green cells are key outputs and summary metrics.</t>
   </si>
   <si>
     <t/>
@@ -89,6 +95,21 @@
     <t>Review key metrics: net margin, cash runway, and DSCR.</t>
   </si>
   <si>
+    <t>Next Steps</t>
+  </si>
+  <si>
+    <t>2. Verify enrollment and revenue projections match your plan.</t>
+  </si>
+  <si>
+    <t>3. Check the Financial Health dashboard for risk signals.</t>
+  </si>
+  <si>
+    <t>4. Share this workbook with your lender or financial advisor.</t>
+  </si>
+  <si>
+    <t>5. Update inputs as your school's plan evolves.</t>
+  </si>
+  <si>
     <t>Disclaimer</t>
   </si>
   <si>
@@ -108,9 +129,6 @@
   </si>
   <si>
     <t>School Name</t>
-  </si>
-  <si>
-    <t>Civic Scholars Charter</t>
   </si>
   <si>
     <t>State</t>
@@ -880,7 +898,7 @@
     <numFmt numFmtId="167" formatCode="0.00x"/>
     <numFmt numFmtId="168" formatCode="0.0"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -895,8 +913,24 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <color rgb="FF1E293B"/>
+      <sz val="12"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="FF6B7280"/>
+      <sz val="10"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <b/>
       <color rgb="FF1E293B"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <color rgb="FF1E3A5F"/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
@@ -913,11 +947,6 @@
     <font>
       <i/>
       <color rgb="FF666666"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <color rgb="FF1E3A5F"/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
@@ -978,12 +1007,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE8EDF2"/>
+        <fgColor rgb="FFDBEAFE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDBEAFE"/>
+        <fgColor rgb="FFE8F5E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8EDF2"/>
       </patternFill>
     </fill>
     <fill>
@@ -994,11 +1028,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFCE4EC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE8F5E9"/>
       </patternFill>
     </fill>
   </fills>
@@ -1044,97 +1073,249 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="10" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="12" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="12" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="12" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="12" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="12" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="10" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="12" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="10" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="12" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="21">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1470,9 +1651,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
+    <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B29"/>
+  <dimension ref="B2:B37"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -1484,134 +1666,174 @@
         <v>0</v>
       </c>
     </row>
+    <row r="3" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B3" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
     <row r="4" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B4" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B5" s="3" t="s">
+      <c r="B4" s="3" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="6" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="7" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="8" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="6" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="9" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="7" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="10" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="6" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="11" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B11" s="3" t="s">
-        <v>5</v>
+      <c r="B11" s="4" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B12" s="2" t="s">
-        <v>8</v>
+      <c r="B12" s="6" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B13" s="3" t="s">
-        <v>9</v>
+      <c r="B13" s="6" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="4" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="15" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="6" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="16" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B17" s="3" t="s">
-        <v>5</v>
+      <c r="B17" s="6" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B18" s="2" t="s">
-        <v>13</v>
+      <c r="B18" s="6" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="19" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B19" s="3" t="s">
-        <v>14</v>
+      <c r="B19" s="6" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="21" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="6" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="22" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B22" s="3" t="s">
-        <v>5</v>
+      <c r="B22" s="6" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="23" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B23" s="2" t="s">
-        <v>17</v>
+      <c r="B23" s="6" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="24" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B24" s="3" t="s">
-        <v>18</v>
+      <c r="B24" s="6" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="4" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="26" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B26" s="3" t="s">
-        <v>5</v>
+      <c r="B26" s="6" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="27" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B27" s="2" t="s">
-        <v>20</v>
+      <c r="B27" s="6" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="28" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B28" s="3" t="s">
-        <v>21</v>
+      <c r="B28" s="6" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B29" s="3" t="s">
+      <c r="B29" s="4" t="s">
         <v>22</v>
+      </c>
+    </row>
+    <row r="30" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B30" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="31" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B31" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="32" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B32" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B33" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="34" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B34" s="6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B35" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="36" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B36" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="37" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B37" s="6" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -1639,1083 +1861,1083 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
+      <c r="A1" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
-        <v>24</v>
+      <c r="A2" s="9" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
+      <c r="A4" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
+      <c r="A5" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="12"/>
+      <c r="D5" s="12"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>29</v>
+      <c r="A6" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>31</v>
+      <c r="A7" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>33</v>
+      <c r="A8" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>35</v>
+      <c r="A9" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
+      <c r="A10" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>39</v>
+      <c r="A11" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B12" s="9">
+      <c r="A12" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="B12" s="13">
         <v>400</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>42</v>
+      <c r="A13" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>44</v>
+      <c r="A14" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B16" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="C16" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D16" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="E16" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="F16" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="G16" s="6"/>
+      <c r="A16" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="C16" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="D16" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="E16" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="F16" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="G16" s="10"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="B17" s="11">
+      <c r="A17" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="B17" s="15">
         <v>120</v>
       </c>
-      <c r="C17" s="11">
+      <c r="C17" s="15">
         <v>200</v>
       </c>
-      <c r="D17" s="11">
+      <c r="D17" s="15">
         <v>300</v>
       </c>
-      <c r="E17" s="11">
+      <c r="E17" s="15">
         <v>375</v>
       </c>
-      <c r="F17" s="11">
+      <c r="F17" s="15">
         <v>400</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="F19" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="G19" s="6" t="s">
+      <c r="A19" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="H19" s="6" t="s">
+      <c r="B19" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="I19" s="6"/>
-      <c r="J19" s="6"/>
+      <c r="C19" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="G19" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="H19" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="I19" s="10"/>
+      <c r="J19" s="10"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="7" t="s">
+      <c r="A20" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="D20" s="16">
+        <v>9500</v>
+      </c>
+      <c r="E20" s="17">
+        <v>0</v>
+      </c>
+      <c r="F20" s="13">
+        <v>12</v>
+      </c>
+      <c r="G20" s="17">
+        <v>1</v>
+      </c>
+      <c r="H20" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="D21" s="16">
+        <v>800</v>
+      </c>
+      <c r="E21" s="17">
+        <v>0</v>
+      </c>
+      <c r="F21" s="13">
+        <v>12</v>
+      </c>
+      <c r="G21" s="17">
+        <v>1</v>
+      </c>
+      <c r="H21" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="D22" s="16">
+        <v>1200</v>
+      </c>
+      <c r="E22" s="17">
+        <v>0</v>
+      </c>
+      <c r="F22" s="13">
+        <v>12</v>
+      </c>
+      <c r="G22" s="17">
+        <v>1</v>
+      </c>
+      <c r="H22" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="D23" s="16">
+        <v>100000</v>
+      </c>
+      <c r="E23" s="17">
+        <v>0</v>
+      </c>
+      <c r="F23" s="13">
+        <v>12</v>
+      </c>
+      <c r="G23" s="17">
+        <v>1</v>
+      </c>
+      <c r="H23" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="D24" s="16">
+        <v>30000</v>
+      </c>
+      <c r="E24" s="17">
+        <v>0</v>
+      </c>
+      <c r="F24" s="13">
+        <v>12</v>
+      </c>
+      <c r="G24" s="17">
+        <v>1</v>
+      </c>
+      <c r="H24" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="D25" s="16">
+        <v>300</v>
+      </c>
+      <c r="E25" s="17">
+        <v>0</v>
+      </c>
+      <c r="F25" s="13">
+        <v>12</v>
+      </c>
+      <c r="G25" s="17">
+        <v>1</v>
+      </c>
+      <c r="H25" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="B28" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="C28" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="D28" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="E28" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="F28" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="G28" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="H28" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="I28" s="10" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="B29" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="D29" s="18">
+        <v>1</v>
+      </c>
+      <c r="E29" s="16">
+        <v>110000</v>
+      </c>
+      <c r="F29" s="17">
+        <v>0.28</v>
+      </c>
+      <c r="G29" s="17">
+        <v>0.0765</v>
+      </c>
+      <c r="H29" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="I29" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="B30" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="C30" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="D30" s="18">
+        <v>1</v>
+      </c>
+      <c r="E30" s="16">
+        <v>90000</v>
+      </c>
+      <c r="F30" s="17">
+        <v>0.28</v>
+      </c>
+      <c r="G30" s="17">
+        <v>0.0765</v>
+      </c>
+      <c r="H30" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="I30" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="B31" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="C31" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="D31" s="18">
+        <v>1</v>
+      </c>
+      <c r="E31" s="16">
+        <v>72000</v>
+      </c>
+      <c r="F31" s="17">
+        <v>0.28</v>
+      </c>
+      <c r="G31" s="17">
+        <v>0.0765</v>
+      </c>
+      <c r="H31" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="I31" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A32" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="B32" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="C32" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="D32" s="18">
+        <v>6</v>
+      </c>
+      <c r="E32" s="16">
+        <v>52000</v>
+      </c>
+      <c r="F32" s="17">
+        <v>0.28</v>
+      </c>
+      <c r="G32" s="17">
+        <v>0.0765</v>
+      </c>
+      <c r="H32" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="I32" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A33" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="B33" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="C33" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="D33" s="18">
+        <v>1</v>
+      </c>
+      <c r="E33" s="16">
+        <v>55000</v>
+      </c>
+      <c r="F33" s="17">
+        <v>0.28</v>
+      </c>
+      <c r="G33" s="17">
+        <v>0.0765</v>
+      </c>
+      <c r="H33" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="I33" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A34" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="B34" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="C34" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="D34" s="18">
+        <v>3</v>
+      </c>
+      <c r="E34" s="16">
+        <v>30000</v>
+      </c>
+      <c r="F34" s="17">
+        <v>0.2</v>
+      </c>
+      <c r="G34" s="17">
+        <v>0.0765</v>
+      </c>
+      <c r="H34" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="I34" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A35" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="B35" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="C35" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="D35" s="18">
+        <v>1</v>
+      </c>
+      <c r="E35" s="16">
+        <v>55000</v>
+      </c>
+      <c r="F35" s="17">
+        <v>0.28</v>
+      </c>
+      <c r="G35" s="17">
+        <v>0.0765</v>
+      </c>
+      <c r="H35" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="I35" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A36" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="B36" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="C36" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="D36" s="18">
+        <v>2</v>
+      </c>
+      <c r="E36" s="16">
+        <v>38000</v>
+      </c>
+      <c r="F36" s="17">
+        <v>0.25</v>
+      </c>
+      <c r="G36" s="17">
+        <v>0.0765</v>
+      </c>
+      <c r="H36" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="I36" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A37" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="B37" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="C37" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="D37" s="18">
+        <v>1</v>
+      </c>
+      <c r="E37" s="16">
+        <v>55000</v>
+      </c>
+      <c r="F37" s="17">
+        <v>0.28</v>
+      </c>
+      <c r="G37" s="17">
+        <v>0.0765</v>
+      </c>
+      <c r="H37" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="I37" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="39" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="B39" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="C39" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="D39" s="10"/>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="B40" s="12" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="B41" s="16">
+        <v>18000</v>
+      </c>
+      <c r="C41" s="11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="B42" s="17">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="44" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="B44" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="C44" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="B20" s="7" t="s">
+      <c r="D44" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="E44" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="D20" s="12">
-        <v>9500</v>
-      </c>
-      <c r="E20" s="13">
-        <v>0</v>
-      </c>
-      <c r="F20" s="9">
-        <v>12</v>
-      </c>
-      <c r="G20" s="13">
-        <v>1</v>
-      </c>
-      <c r="H20" s="7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B21" s="7" t="s">
+      <c r="F44" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="G44" s="10"/>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="B45" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="C45" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="D45" s="16">
+        <v>18000</v>
+      </c>
+      <c r="E45" s="17">
+        <v>0.03</v>
+      </c>
+      <c r="F45" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="B46" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="C46" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="D46" s="16">
+        <v>2500</v>
+      </c>
+      <c r="E46" s="17">
+        <v>0</v>
+      </c>
+      <c r="F46" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="B47" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="C47" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="D47" s="16">
+        <v>18000</v>
+      </c>
+      <c r="E47" s="17">
+        <v>0</v>
+      </c>
+      <c r="F47" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="B48" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="C48" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="D48" s="16">
+        <v>1500</v>
+      </c>
+      <c r="E48" s="17">
+        <v>0</v>
+      </c>
+      <c r="F48" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="B49" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="C49" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="D49" s="16">
+        <v>700</v>
+      </c>
+      <c r="E49" s="17">
+        <v>0</v>
+      </c>
+      <c r="F49" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="B50" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="C50" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="D50" s="16">
+        <v>500</v>
+      </c>
+      <c r="E50" s="17">
+        <v>0</v>
+      </c>
+      <c r="F50" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="B51" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="C51" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="D51" s="16">
+        <v>25000</v>
+      </c>
+      <c r="E51" s="17">
+        <v>0</v>
+      </c>
+      <c r="F51" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="B52" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="C52" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="D52" s="16">
+        <v>15000</v>
+      </c>
+      <c r="E52" s="17">
+        <v>0</v>
+      </c>
+      <c r="F52" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="B53" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="C53" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="D53" s="16">
+        <v>20000</v>
+      </c>
+      <c r="E53" s="17">
+        <v>0</v>
+      </c>
+      <c r="F53" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="B54" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="C54" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="D54" s="16">
+        <v>800</v>
+      </c>
+      <c r="E54" s="17">
+        <v>0</v>
+      </c>
+      <c r="F54" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="B55" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="C55" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="D55" s="16">
+        <v>600</v>
+      </c>
+      <c r="E55" s="17">
+        <v>0</v>
+      </c>
+      <c r="F55" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="57" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="B57" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="C57" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="C21" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="D21" s="12">
-        <v>800</v>
-      </c>
-      <c r="E21" s="13">
-        <v>0</v>
-      </c>
-      <c r="F21" s="9">
-        <v>12</v>
-      </c>
-      <c r="G21" s="13">
-        <v>1</v>
-      </c>
-      <c r="H21" s="7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="D22" s="12">
-        <v>1200</v>
-      </c>
-      <c r="E22" s="13">
-        <v>0</v>
-      </c>
-      <c r="F22" s="9">
-        <v>12</v>
-      </c>
-      <c r="G22" s="13">
-        <v>1</v>
-      </c>
-      <c r="H22" s="7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="7" t="s">
+      <c r="D57" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="E57" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="F57" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="G57" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="H57" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="B23" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="D23" s="12">
-        <v>100000</v>
-      </c>
-      <c r="E23" s="13">
-        <v>0</v>
-      </c>
-      <c r="F23" s="9">
-        <v>12</v>
-      </c>
-      <c r="G23" s="13">
-        <v>1</v>
-      </c>
-      <c r="H23" s="7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="D24" s="12">
-        <v>30000</v>
-      </c>
-      <c r="E24" s="13">
-        <v>0</v>
-      </c>
-      <c r="F24" s="9">
-        <v>12</v>
-      </c>
-      <c r="G24" s="13">
-        <v>1</v>
-      </c>
-      <c r="H24" s="7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="D25" s="12">
-        <v>300</v>
-      </c>
-      <c r="E25" s="13">
-        <v>0</v>
-      </c>
-      <c r="F25" s="9">
-        <v>12</v>
-      </c>
-      <c r="G25" s="13">
-        <v>1</v>
-      </c>
-      <c r="H25" s="7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="28" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="D28" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="E28" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="F28" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="G28" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="I28" s="6" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="B29" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="D29" s="14">
-        <v>1</v>
-      </c>
-      <c r="E29" s="12">
-        <v>110000</v>
-      </c>
-      <c r="F29" s="13">
-        <v>0.28</v>
-      </c>
-      <c r="G29" s="13">
-        <v>0.0765</v>
-      </c>
-      <c r="H29" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="I29" s="7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="B30" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="C30" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="D30" s="14">
-        <v>1</v>
-      </c>
-      <c r="E30" s="12">
-        <v>90000</v>
-      </c>
-      <c r="F30" s="13">
-        <v>0.28</v>
-      </c>
-      <c r="G30" s="13">
-        <v>0.0765</v>
-      </c>
-      <c r="H30" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="I30" s="7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="B31" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="C31" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="D31" s="14">
-        <v>1</v>
-      </c>
-      <c r="E31" s="12">
-        <v>72000</v>
-      </c>
-      <c r="F31" s="13">
-        <v>0.28</v>
-      </c>
-      <c r="G31" s="13">
-        <v>0.0765</v>
-      </c>
-      <c r="H31" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="I31" s="7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="C32" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="D32" s="14">
-        <v>6</v>
-      </c>
-      <c r="E32" s="12">
-        <v>52000</v>
-      </c>
-      <c r="F32" s="13">
-        <v>0.28</v>
-      </c>
-      <c r="G32" s="13">
-        <v>0.0765</v>
-      </c>
-      <c r="H32" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="I32" s="7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A33" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="B33" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="C33" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="D33" s="14">
-        <v>1</v>
-      </c>
-      <c r="E33" s="12">
-        <v>55000</v>
-      </c>
-      <c r="F33" s="13">
-        <v>0.28</v>
-      </c>
-      <c r="G33" s="13">
-        <v>0.0765</v>
-      </c>
-      <c r="H33" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="I33" s="7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A34" s="7" t="s">
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="B58" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="B34" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="C34" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="D34" s="14">
-        <v>3</v>
-      </c>
-      <c r="E34" s="12">
-        <v>30000</v>
-      </c>
-      <c r="F34" s="13">
-        <v>0.2</v>
-      </c>
-      <c r="G34" s="13">
-        <v>0.0765</v>
-      </c>
-      <c r="H34" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="I34" s="7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A35" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="B35" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="C35" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="D35" s="14">
-        <v>1</v>
-      </c>
-      <c r="E35" s="12">
-        <v>55000</v>
-      </c>
-      <c r="F35" s="13">
-        <v>0.28</v>
-      </c>
-      <c r="G35" s="13">
-        <v>0.0765</v>
-      </c>
-      <c r="H35" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="I35" s="7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A36" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="B36" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C36" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="D36" s="14">
-        <v>2</v>
-      </c>
-      <c r="E36" s="12">
-        <v>38000</v>
-      </c>
-      <c r="F36" s="13">
-        <v>0.25</v>
-      </c>
-      <c r="G36" s="13">
-        <v>0.0765</v>
-      </c>
-      <c r="H36" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="I36" s="7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A37" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="B37" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="C37" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="D37" s="14">
-        <v>1</v>
-      </c>
-      <c r="E37" s="12">
-        <v>55000</v>
-      </c>
-      <c r="F37" s="13">
-        <v>0.28</v>
-      </c>
-      <c r="G37" s="13">
-        <v>0.0765</v>
-      </c>
-      <c r="H37" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="I37" s="7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="39" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="C39" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="D39" s="6"/>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="B40" s="8" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="B41" s="12">
-        <v>18000</v>
-      </c>
-      <c r="C41" s="7" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="B42" s="13">
+      <c r="C58" s="19">
+        <v>0</v>
+      </c>
+      <c r="D58" s="16">
+        <v>500000</v>
+      </c>
+      <c r="E58" s="20">
+        <v>0.0575</v>
+      </c>
+      <c r="F58" s="13">
+        <v>15</v>
+      </c>
+      <c r="G58" s="19">
+        <v>49825</v>
+      </c>
+      <c r="H58" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="B59" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="C59" s="16">
+        <v>75000</v>
+      </c>
+      <c r="D59" s="11">
+        <v>0</v>
+      </c>
+      <c r="E59" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="F59" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="G59" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="H59" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="B60" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="C60" s="16">
+        <v>40000</v>
+      </c>
+      <c r="D60" s="11">
+        <v>0</v>
+      </c>
+      <c r="E60" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="F60" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="G60" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="H60" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="62" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="B62" s="10"/>
+      <c r="C62" s="10"/>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="B63" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="B64" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="B65" s="18">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="C65" s="21" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="B66" s="17">
         <v>0.03</v>
       </c>
     </row>
-    <row r="44" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="C44" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="D44" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="E44" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="F44" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="G44" s="6"/>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="B45" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="C45" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="D45" s="12">
-        <v>18000</v>
-      </c>
-      <c r="E45" s="13">
-        <v>0.03</v>
-      </c>
-      <c r="F45" s="7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="B46" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="C46" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="D46" s="12">
-        <v>2500</v>
-      </c>
-      <c r="E46" s="13">
-        <v>0</v>
-      </c>
-      <c r="F46" s="7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="B47" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="C47" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="D47" s="12">
-        <v>18000</v>
-      </c>
-      <c r="E47" s="13">
-        <v>0</v>
-      </c>
-      <c r="F47" s="7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="B48" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="C48" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="D48" s="12">
-        <v>1500</v>
-      </c>
-      <c r="E48" s="13">
-        <v>0</v>
-      </c>
-      <c r="F48" s="7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="B49" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="C49" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="D49" s="12">
-        <v>700</v>
-      </c>
-      <c r="E49" s="13">
-        <v>0</v>
-      </c>
-      <c r="F49" s="7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="B50" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="C50" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="D50" s="12">
-        <v>500</v>
-      </c>
-      <c r="E50" s="13">
-        <v>0</v>
-      </c>
-      <c r="F50" s="7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="B51" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="C51" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="D51" s="12">
-        <v>25000</v>
-      </c>
-      <c r="E51" s="13">
-        <v>0</v>
-      </c>
-      <c r="F51" s="7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="B52" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="C52" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="D52" s="12">
-        <v>15000</v>
-      </c>
-      <c r="E52" s="13">
-        <v>0</v>
-      </c>
-      <c r="F52" s="7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="B53" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="C53" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="D53" s="12">
-        <v>20000</v>
-      </c>
-      <c r="E53" s="13">
-        <v>0</v>
-      </c>
-      <c r="F53" s="7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="B54" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="C54" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="D54" s="12">
-        <v>800</v>
-      </c>
-      <c r="E54" s="13">
-        <v>0</v>
-      </c>
-      <c r="F54" s="7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="B55" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="C55" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="D55" s="12">
-        <v>600</v>
-      </c>
-      <c r="E55" s="13">
-        <v>0</v>
-      </c>
-      <c r="F55" s="7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="57" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="B57" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="C57" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="D57" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="E57" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="F57" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="G57" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="H57" s="6" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A58" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="B58" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="C58" s="15">
-        <v>0</v>
-      </c>
-      <c r="D58" s="12">
-        <v>500000</v>
-      </c>
-      <c r="E58" s="16">
-        <v>0.0575</v>
-      </c>
-      <c r="F58" s="9">
-        <v>15</v>
-      </c>
-      <c r="G58" s="15">
-        <v>49825</v>
-      </c>
-      <c r="H58" s="7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A59" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="B59" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="C59" s="12">
-        <v>75000</v>
-      </c>
-      <c r="D59" s="7">
-        <v>0</v>
-      </c>
-      <c r="E59" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="F59" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="G59" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="H59" s="7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A60" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="B60" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="C60" s="12">
-        <v>40000</v>
-      </c>
-      <c r="D60" s="7">
-        <v>0</v>
-      </c>
-      <c r="E60" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="F60" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="G60" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="H60" s="7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="62" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="B62" s="6"/>
-      <c r="C62" s="6"/>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A63" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="B63" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A64" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="B64" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="B65" s="14">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="C65" s="17" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A66" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="B66" s="13">
-        <v>0.03</v>
-      </c>
-    </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A67" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="B67" s="13">
+      <c r="A67" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="B67" s="17">
         <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A68" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="B68" s="12">
+      <c r="A68" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="B68" s="16">
         <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A70" s="18" t="s">
-        <v>137</v>
-      </c>
-      <c r="B70" s="18"/>
-      <c r="C70" s="18"/>
-      <c r="D70" s="18"/>
-      <c r="E70" s="18"/>
-      <c r="F70" s="18"/>
-      <c r="G70" s="18"/>
+      <c r="A70" s="22" t="s">
+        <v>143</v>
+      </c>
+      <c r="B70" s="22"/>
+      <c r="C70" s="22"/>
+      <c r="D70" s="22"/>
+      <c r="E70" s="22"/>
+      <c r="F70" s="22"/>
+      <c r="G70" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -2746,1604 +2968,1604 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
+      <c r="A1" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="C2" s="19" t="s">
-        <v>47</v>
-      </c>
-      <c r="D2" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="E2" s="19" t="s">
-        <v>49</v>
-      </c>
-      <c r="F2" s="19" t="s">
-        <v>50</v>
+      <c r="A2" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="D2" s="23" t="s">
+        <v>54</v>
+      </c>
+      <c r="E2" s="23" t="s">
+        <v>55</v>
+      </c>
+      <c r="F2" s="23" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="B3" s="21">
+      <c r="A3" s="24" t="s">
+        <v>57</v>
+      </c>
+      <c r="B3" s="25">
         <f>Assumptions!B17</f>
         <v>120</v>
       </c>
-      <c r="C3" s="21">
+      <c r="C3" s="25">
         <f>Assumptions!C17</f>
         <v>200</v>
       </c>
-      <c r="D3" s="21">
+      <c r="D3" s="25">
         <f>Assumptions!D17</f>
         <v>300</v>
       </c>
-      <c r="E3" s="21">
+      <c r="E3" s="25">
         <f>Assumptions!E17</f>
         <v>375</v>
       </c>
-      <c r="F3" s="21">
+      <c r="F3" s="25">
         <f>Assumptions!F17</f>
         <v>400</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="B5" s="6"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
+      <c r="A5" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="B5" s="10"/>
+      <c r="C5" s="10"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="10"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="B6" s="15">
+      <c r="A6" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="B6" s="19">
         <v>950000</v>
       </c>
-      <c r="C6" s="15">
+      <c r="C6" s="19">
         <v>1938000</v>
       </c>
-      <c r="D6" s="15">
+      <c r="D6" s="19">
         <v>2965200</v>
       </c>
-      <c r="E6" s="15">
+      <c r="E6" s="19">
         <v>3780375</v>
       </c>
-      <c r="F6" s="15">
+      <c r="F6" s="19">
         <v>4113200</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B7" s="15">
+      <c r="A7" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="B7" s="19">
         <v>80000</v>
       </c>
-      <c r="C7" s="15">
+      <c r="C7" s="19">
         <v>163200</v>
       </c>
-      <c r="D7" s="15">
+      <c r="D7" s="19">
         <v>249600</v>
       </c>
-      <c r="E7" s="15">
+      <c r="E7" s="19">
         <v>318375</v>
       </c>
-      <c r="F7" s="15">
+      <c r="F7" s="19">
         <v>346400</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="B8" s="15">
+      <c r="A8" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="B8" s="19">
         <v>120000</v>
       </c>
-      <c r="C8" s="15">
+      <c r="C8" s="19">
         <v>244800</v>
       </c>
-      <c r="D8" s="15">
+      <c r="D8" s="19">
         <v>374400</v>
       </c>
-      <c r="E8" s="15">
+      <c r="E8" s="19">
         <v>477375</v>
       </c>
-      <c r="F8" s="15">
+      <c r="F8" s="19">
         <v>519600</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="B9" s="15">
+      <c r="A9" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="B9" s="19">
         <v>83333</v>
       </c>
-      <c r="C9" s="15">
+      <c r="C9" s="19">
         <v>75000</v>
       </c>
-      <c r="D9" s="15">
+      <c r="D9" s="19">
         <v>50000</v>
       </c>
-      <c r="E9" s="15">
-        <v>0</v>
-      </c>
-      <c r="F9" s="15">
+      <c r="E9" s="19">
+        <v>0</v>
+      </c>
+      <c r="F9" s="19">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="B10" s="15">
+      <c r="A10" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="B10" s="19">
         <v>25000</v>
       </c>
-      <c r="C10" s="15">
+      <c r="C10" s="19">
         <v>40000</v>
       </c>
-      <c r="D10" s="15">
+      <c r="D10" s="19">
         <v>50000</v>
       </c>
-      <c r="E10" s="15">
+      <c r="E10" s="19">
         <v>60000</v>
       </c>
-      <c r="F10" s="15">
+      <c r="F10" s="19">
         <v>70000</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="B11" s="15">
+      <c r="A11" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="B11" s="19">
         <v>30000</v>
       </c>
-      <c r="C11" s="15">
+      <c r="C11" s="19">
         <v>61800</v>
       </c>
-      <c r="D11" s="15">
+      <c r="D11" s="19">
         <v>95400</v>
       </c>
-      <c r="E11" s="15">
+      <c r="E11" s="19">
         <v>123000</v>
       </c>
-      <c r="F11" s="15">
+      <c r="F11" s="19">
         <v>135200</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="B12" s="22">
+      <c r="A12" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="B12" s="26">
         <f>SUM(B6:B11)</f>
         <v>1288333</v>
       </c>
-      <c r="C12" s="22">
+      <c r="C12" s="26">
         <f>SUM(C6:C11)</f>
         <v>2522800</v>
       </c>
-      <c r="D12" s="22">
+      <c r="D12" s="26">
         <f>SUM(D6:D11)</f>
         <v>3784600</v>
       </c>
-      <c r="E12" s="22">
+      <c r="E12" s="26">
         <f>SUM(E6:E11)</f>
         <v>4759125</v>
       </c>
-      <c r="F12" s="22">
+      <c r="F12" s="26">
         <f>SUM(F6:F11)</f>
         <v>5184400</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
+      <c r="A14" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="B14" s="10"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="10"/>
+      <c r="F14" s="10"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="B15" s="15">
+      <c r="A15" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="B15" s="19">
         <v>124346</v>
       </c>
-      <c r="C15" s="15">
+      <c r="C15" s="19">
         <v>149215</v>
       </c>
-      <c r="D15" s="15">
+      <c r="D15" s="19">
         <v>149215</v>
       </c>
-      <c r="E15" s="15">
+      <c r="E15" s="19">
         <v>149215</v>
       </c>
-      <c r="F15" s="15">
+      <c r="F15" s="19">
         <v>149215</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="B16" s="15">
+      <c r="A16" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="B16" s="19">
         <v>101738</v>
       </c>
-      <c r="C16" s="15">
+      <c r="C16" s="19">
         <v>122085</v>
       </c>
-      <c r="D16" s="15">
+      <c r="D16" s="19">
         <v>122085</v>
       </c>
-      <c r="E16" s="15">
+      <c r="E16" s="19">
         <v>122085</v>
       </c>
-      <c r="F16" s="15">
+      <c r="F16" s="19">
         <v>122085</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="B17" s="15">
+      <c r="A17" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="B17" s="19">
         <v>81390</v>
       </c>
-      <c r="C17" s="15">
+      <c r="C17" s="19">
         <v>97668</v>
       </c>
-      <c r="D17" s="15">
+      <c r="D17" s="19">
         <v>97668</v>
       </c>
-      <c r="E17" s="15">
+      <c r="E17" s="19">
         <v>97668</v>
       </c>
-      <c r="F17" s="15">
+      <c r="F17" s="19">
         <v>97668</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="B18" s="15">
+      <c r="A18" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="B18" s="19">
         <v>352690</v>
       </c>
-      <c r="C18" s="15">
+      <c r="C18" s="19">
         <v>423228</v>
       </c>
-      <c r="D18" s="15">
+      <c r="D18" s="19">
         <v>423228</v>
       </c>
-      <c r="E18" s="15">
+      <c r="E18" s="19">
         <v>423228</v>
       </c>
-      <c r="F18" s="15">
+      <c r="F18" s="19">
         <v>423228</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="B19" s="15">
+      <c r="A19" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="B19" s="19">
         <v>62173</v>
       </c>
-      <c r="C19" s="15">
+      <c r="C19" s="19">
         <v>74608</v>
       </c>
-      <c r="D19" s="15">
+      <c r="D19" s="19">
         <v>74608</v>
       </c>
-      <c r="E19" s="15">
+      <c r="E19" s="19">
         <v>74608</v>
       </c>
-      <c r="F19" s="15">
+      <c r="F19" s="19">
         <v>74608</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="B20" s="15">
+      <c r="A20" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="B20" s="19">
         <v>95738</v>
       </c>
-      <c r="C20" s="15">
+      <c r="C20" s="19">
         <v>114885</v>
       </c>
-      <c r="D20" s="15">
+      <c r="D20" s="19">
         <v>114885</v>
       </c>
-      <c r="E20" s="15">
+      <c r="E20" s="19">
         <v>114885</v>
       </c>
-      <c r="F20" s="15">
+      <c r="F20" s="19">
         <v>114885</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="B21" s="15">
+      <c r="A21" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="B21" s="19">
         <v>62173</v>
       </c>
-      <c r="C21" s="15">
+      <c r="C21" s="19">
         <v>74608</v>
       </c>
-      <c r="D21" s="15">
+      <c r="D21" s="19">
         <v>74608</v>
       </c>
-      <c r="E21" s="15">
+      <c r="E21" s="19">
         <v>74608</v>
       </c>
-      <c r="F21" s="15">
+      <c r="F21" s="19">
         <v>74608</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="B22" s="15">
+      <c r="A22" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="B22" s="19">
         <v>84012</v>
       </c>
-      <c r="C22" s="15">
+      <c r="C22" s="19">
         <v>100814</v>
       </c>
-      <c r="D22" s="15">
+      <c r="D22" s="19">
         <v>100814</v>
       </c>
-      <c r="E22" s="15">
+      <c r="E22" s="19">
         <v>100814</v>
       </c>
-      <c r="F22" s="15">
+      <c r="F22" s="19">
         <v>100814</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="B23" s="15">
+      <c r="A23" s="11" t="s">
+        <v>156</v>
+      </c>
+      <c r="B23" s="19">
         <v>62173</v>
       </c>
-      <c r="C23" s="15">
+      <c r="C23" s="19">
         <v>74608</v>
       </c>
-      <c r="D23" s="15">
+      <c r="D23" s="19">
         <v>74608</v>
       </c>
-      <c r="E23" s="15">
+      <c r="E23" s="19">
         <v>74608</v>
       </c>
-      <c r="F23" s="15">
+      <c r="F23" s="19">
         <v>74608</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="B24" s="22">
+      <c r="A24" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="B24" s="26">
         <f>SUM(B15:B23)</f>
         <v>1026431</v>
       </c>
-      <c r="C24" s="22">
+      <c r="C24" s="26">
         <f>SUM(C15:C23)</f>
         <v>1231718</v>
       </c>
-      <c r="D24" s="22">
+      <c r="D24" s="26">
         <f>SUM(D15:D23)</f>
         <v>1231718</v>
       </c>
-      <c r="E24" s="22">
+      <c r="E24" s="26">
         <f>SUM(E15:E23)</f>
         <v>1231718</v>
       </c>
-      <c r="F24" s="22">
+      <c r="F24" s="26">
         <f>SUM(F15:F23)</f>
         <v>1231718</v>
       </c>
     </row>
     <row r="26" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="B26" s="6"/>
-      <c r="C26" s="6"/>
-      <c r="D26" s="6"/>
-      <c r="E26" s="6"/>
-      <c r="F26" s="6"/>
+      <c r="A26" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="B26" s="10"/>
+      <c r="C26" s="10"/>
+      <c r="D26" s="10"/>
+      <c r="E26" s="10"/>
+      <c r="F26" s="10"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="B27" s="7"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="7"/>
+      <c r="A27" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="B27" s="11"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="11"/>
+      <c r="F27" s="11"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="B28" s="15">
+      <c r="A28" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="B28" s="19">
         <v>70000</v>
       </c>
-      <c r="C28" s="15">
+      <c r="C28" s="19">
         <v>144200</v>
       </c>
-      <c r="D28" s="15">
+      <c r="D28" s="19">
         <v>222900</v>
       </c>
-      <c r="E28" s="15">
+      <c r="E28" s="19">
         <v>286875</v>
       </c>
-      <c r="F28" s="15">
+      <c r="F28" s="19">
         <v>315200</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="23" t="s">
-        <v>153</v>
-      </c>
-      <c r="B29" s="24">
+      <c r="A29" s="27" t="s">
+        <v>159</v>
+      </c>
+      <c r="B29" s="28">
         <v>70000</v>
       </c>
-      <c r="C29" s="24">
+      <c r="C29" s="28">
         <v>144200</v>
       </c>
-      <c r="D29" s="24">
+      <c r="D29" s="28">
         <v>222900</v>
       </c>
-      <c r="E29" s="24">
+      <c r="E29" s="28">
         <v>286875</v>
       </c>
-      <c r="F29" s="24">
+      <c r="F29" s="28">
         <v>315200</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="B30" s="7"/>
-      <c r="C30" s="7"/>
-      <c r="D30" s="7"/>
-      <c r="E30" s="7"/>
-      <c r="F30" s="7"/>
+      <c r="A30" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="B30" s="11"/>
+      <c r="C30" s="11"/>
+      <c r="D30" s="11"/>
+      <c r="E30" s="11"/>
+      <c r="F30" s="11"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="B31" s="15">
+      <c r="A31" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="B31" s="19">
         <v>50000</v>
       </c>
-      <c r="C31" s="15">
+      <c r="C31" s="19">
         <v>103000</v>
       </c>
-      <c r="D31" s="15">
+      <c r="D31" s="19">
         <v>159000</v>
       </c>
-      <c r="E31" s="15">
+      <c r="E31" s="19">
         <v>204750</v>
       </c>
-      <c r="F31" s="15">
+      <c r="F31" s="19">
         <v>224800</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="23" t="s">
-        <v>155</v>
-      </c>
-      <c r="B32" s="24">
+      <c r="A32" s="27" t="s">
+        <v>161</v>
+      </c>
+      <c r="B32" s="28">
         <v>50000</v>
       </c>
-      <c r="C32" s="24">
+      <c r="C32" s="28">
         <v>103000</v>
       </c>
-      <c r="D32" s="24">
+      <c r="D32" s="28">
         <v>159000</v>
       </c>
-      <c r="E32" s="24">
+      <c r="E32" s="28">
         <v>204750</v>
       </c>
-      <c r="F32" s="24">
+      <c r="F32" s="28">
         <v>224800</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="B33" s="7"/>
-      <c r="C33" s="7"/>
-      <c r="D33" s="7"/>
-      <c r="E33" s="7"/>
-      <c r="F33" s="7"/>
+      <c r="A33" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="B33" s="11"/>
+      <c r="C33" s="11"/>
+      <c r="D33" s="11"/>
+      <c r="E33" s="11"/>
+      <c r="F33" s="11"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="B34" s="15">
+      <c r="A34" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="B34" s="19">
         <v>180000</v>
       </c>
-      <c r="C34" s="15">
+      <c r="C34" s="19">
         <v>222480</v>
       </c>
-      <c r="D34" s="15">
+      <c r="D34" s="19">
         <v>229154</v>
       </c>
-      <c r="E34" s="15">
+      <c r="E34" s="19">
         <v>236029</v>
       </c>
-      <c r="F34" s="15">
+      <c r="F34" s="19">
         <v>243110</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="B35" s="15">
+      <c r="A35" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="B35" s="19">
         <v>25000</v>
       </c>
-      <c r="C35" s="15">
+      <c r="C35" s="19">
         <v>30900</v>
       </c>
-      <c r="D35" s="15">
+      <c r="D35" s="19">
         <v>31824</v>
       </c>
-      <c r="E35" s="15">
+      <c r="E35" s="19">
         <v>32784</v>
       </c>
-      <c r="F35" s="15">
+      <c r="F35" s="19">
         <v>33768</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="B36" s="15">
+      <c r="A36" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="B36" s="19">
         <v>15000</v>
       </c>
-      <c r="C36" s="15">
+      <c r="C36" s="19">
         <v>18540</v>
       </c>
-      <c r="D36" s="15">
+      <c r="D36" s="19">
         <v>19096</v>
       </c>
-      <c r="E36" s="15">
+      <c r="E36" s="19">
         <v>19669</v>
       </c>
-      <c r="F36" s="15">
+      <c r="F36" s="19">
         <v>20259</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="B37" s="15">
+      <c r="A37" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="B37" s="19">
         <v>15000</v>
       </c>
-      <c r="C37" s="15">
+      <c r="C37" s="19">
         <v>18540</v>
       </c>
-      <c r="D37" s="15">
+      <c r="D37" s="19">
         <v>19092</v>
       </c>
-      <c r="E37" s="15">
+      <c r="E37" s="19">
         <v>19668</v>
       </c>
-      <c r="F37" s="15">
+      <c r="F37" s="19">
         <v>20256</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="23" t="s">
-        <v>160</v>
-      </c>
-      <c r="B38" s="24">
+      <c r="A38" s="27" t="s">
+        <v>166</v>
+      </c>
+      <c r="B38" s="28">
         <v>235000</v>
       </c>
-      <c r="C38" s="24">
+      <c r="C38" s="28">
         <v>290460</v>
       </c>
-      <c r="D38" s="24">
+      <c r="D38" s="28">
         <v>299166</v>
       </c>
-      <c r="E38" s="24">
+      <c r="E38" s="28">
         <v>308150</v>
       </c>
-      <c r="F38" s="24">
+      <c r="F38" s="28">
         <v>317393</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="B39" s="7"/>
-      <c r="C39" s="7"/>
-      <c r="D39" s="7"/>
-      <c r="E39" s="7"/>
-      <c r="F39" s="7"/>
+      <c r="A39" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="B39" s="11"/>
+      <c r="C39" s="11"/>
+      <c r="D39" s="11"/>
+      <c r="E39" s="11"/>
+      <c r="F39" s="11"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="B40" s="15">
+      <c r="A40" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="B40" s="19">
         <v>20833</v>
       </c>
-      <c r="C40" s="15">
+      <c r="C40" s="19">
         <v>25750</v>
       </c>
-      <c r="D40" s="15">
+      <c r="D40" s="19">
         <v>26523</v>
       </c>
-      <c r="E40" s="15">
+      <c r="E40" s="19">
         <v>27318</v>
       </c>
-      <c r="F40" s="15">
+      <c r="F40" s="19">
         <v>28138</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="B41" s="15">
+      <c r="A41" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="B41" s="19">
         <v>12500</v>
       </c>
-      <c r="C41" s="15">
+      <c r="C41" s="19">
         <v>15450</v>
       </c>
-      <c r="D41" s="15">
+      <c r="D41" s="19">
         <v>15914</v>
       </c>
-      <c r="E41" s="15">
+      <c r="E41" s="19">
         <v>16391</v>
       </c>
-      <c r="F41" s="15">
+      <c r="F41" s="19">
         <v>16883</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="B42" s="15">
+      <c r="A42" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="B42" s="19">
         <v>16667</v>
       </c>
-      <c r="C42" s="15">
+      <c r="C42" s="19">
         <v>20600</v>
       </c>
-      <c r="D42" s="15">
+      <c r="D42" s="19">
         <v>21218</v>
       </c>
-      <c r="E42" s="15">
+      <c r="E42" s="19">
         <v>21855</v>
       </c>
-      <c r="F42" s="15">
+      <c r="F42" s="19">
         <v>22510</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="B43" s="15">
+      <c r="A43" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="B43" s="19">
         <v>80000</v>
       </c>
-      <c r="C43" s="15">
+      <c r="C43" s="19">
         <v>164800</v>
       </c>
-      <c r="D43" s="15">
+      <c r="D43" s="19">
         <v>254700</v>
       </c>
-      <c r="E43" s="15">
+      <c r="E43" s="19">
         <v>327750</v>
       </c>
-      <c r="F43" s="15">
+      <c r="F43" s="19">
         <v>360000</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="B44" s="15">
+      <c r="A44" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="B44" s="19">
         <v>60000</v>
       </c>
-      <c r="C44" s="15">
+      <c r="C44" s="19">
         <v>123600</v>
       </c>
-      <c r="D44" s="15">
+      <c r="D44" s="19">
         <v>191100</v>
       </c>
-      <c r="E44" s="15">
+      <c r="E44" s="19">
         <v>246000</v>
       </c>
-      <c r="F44" s="15">
+      <c r="F44" s="19">
         <v>270000</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="23" t="s">
-        <v>166</v>
-      </c>
-      <c r="B45" s="24">
+      <c r="A45" s="27" t="s">
+        <v>172</v>
+      </c>
+      <c r="B45" s="28">
         <v>190000</v>
       </c>
-      <c r="C45" s="24">
+      <c r="C45" s="28">
         <v>350200</v>
       </c>
-      <c r="D45" s="24">
+      <c r="D45" s="28">
         <v>509455</v>
       </c>
-      <c r="E45" s="24">
+      <c r="E45" s="28">
         <v>639314</v>
       </c>
-      <c r="F45" s="24">
+      <c r="F45" s="28">
         <v>697531</v>
       </c>
     </row>
     <row r="46" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="B46" s="22">
+      <c r="A46" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="B46" s="26">
         <f>B29+B32+B38+B45</f>
         <v>545000</v>
       </c>
-      <c r="C46" s="22">
+      <c r="C46" s="26">
         <f>C29+C32+C38+C45</f>
         <v>887860</v>
       </c>
-      <c r="D46" s="22">
+      <c r="D46" s="26">
         <f>D29+D32+D38+D45</f>
         <v>1190521</v>
       </c>
-      <c r="E46" s="22">
+      <c r="E46" s="26">
         <f>E29+E32+E38+E45</f>
         <v>1439089</v>
       </c>
-      <c r="F46" s="22">
+      <c r="F46" s="26">
         <f>F29+F32+F38+F45</f>
         <v>1554924</v>
       </c>
     </row>
     <row r="48" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="B48" s="6"/>
-      <c r="C48" s="6"/>
-      <c r="D48" s="6"/>
-      <c r="E48" s="6"/>
-      <c r="F48" s="6"/>
+      <c r="A48" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="B48" s="10"/>
+      <c r="C48" s="10"/>
+      <c r="D48" s="10"/>
+      <c r="E48" s="10"/>
+      <c r="F48" s="10"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="B49" s="15">
+      <c r="A49" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="B49" s="19">
         <v>49825</v>
       </c>
-      <c r="C49" s="15">
+      <c r="C49" s="19">
         <v>49825</v>
       </c>
-      <c r="D49" s="15">
+      <c r="D49" s="19">
         <v>49825</v>
       </c>
-      <c r="E49" s="15">
+      <c r="E49" s="19">
         <v>49825</v>
       </c>
-      <c r="F49" s="15">
+      <c r="F49" s="19">
         <v>49825</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="B50" s="15">
+      <c r="A50" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="B50" s="19">
         <v>75000</v>
       </c>
-      <c r="C50" s="15">
+      <c r="C50" s="19">
         <v>25000</v>
       </c>
-      <c r="D50" s="15">
+      <c r="D50" s="19">
         <v>30000</v>
       </c>
-      <c r="E50" s="15">
+      <c r="E50" s="19">
         <v>15000</v>
       </c>
-      <c r="F50" s="15">
+      <c r="F50" s="19">
         <v>10000</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="B51" s="15">
+      <c r="A51" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="B51" s="19">
         <v>40000</v>
       </c>
-      <c r="C51" s="15">
+      <c r="C51" s="19">
         <v>15000</v>
       </c>
-      <c r="D51" s="15">
+      <c r="D51" s="19">
         <v>10000</v>
       </c>
-      <c r="E51" s="15">
+      <c r="E51" s="19">
         <v>10000</v>
       </c>
-      <c r="F51" s="15">
+      <c r="F51" s="19">
         <v>10000</v>
       </c>
     </row>
     <row r="52" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="B52" s="22">
+      <c r="A52" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="B52" s="26">
         <f>SUM(B49:B51)</f>
         <v>164825</v>
       </c>
-      <c r="C52" s="22">
+      <c r="C52" s="26">
         <f>SUM(C49:C51)</f>
         <v>89825</v>
       </c>
-      <c r="D52" s="22">
+      <c r="D52" s="26">
         <f>SUM(D49:D51)</f>
         <v>89825</v>
       </c>
-      <c r="E52" s="22">
+      <c r="E52" s="26">
         <f>SUM(E49:E51)</f>
         <v>74825</v>
       </c>
-      <c r="F52" s="22">
+      <c r="F52" s="26">
         <f>SUM(F49:F51)</f>
         <v>69825</v>
       </c>
     </row>
     <row r="54" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="B54" s="6"/>
-      <c r="C54" s="6"/>
-      <c r="D54" s="6"/>
-      <c r="E54" s="6"/>
-      <c r="F54" s="6"/>
+      <c r="A54" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="B54" s="10"/>
+      <c r="C54" s="10"/>
+      <c r="D54" s="10"/>
+      <c r="E54" s="10"/>
+      <c r="F54" s="10"/>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="20" t="s">
-        <v>171</v>
-      </c>
-      <c r="B55" s="24">
+      <c r="A55" s="24" t="s">
+        <v>177</v>
+      </c>
+      <c r="B55" s="28">
         <f>B12</f>
         <v>1288333</v>
       </c>
-      <c r="C55" s="24">
+      <c r="C55" s="28">
         <f>C12</f>
         <v>2522800</v>
       </c>
-      <c r="D55" s="24">
+      <c r="D55" s="28">
         <f>D12</f>
         <v>3784600</v>
       </c>
-      <c r="E55" s="24">
+      <c r="E55" s="28">
         <f>E12</f>
         <v>4759125</v>
       </c>
-      <c r="F55" s="24">
+      <c r="F55" s="28">
         <f>F12</f>
         <v>5184400</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="7" t="s">
-        <v>172</v>
-      </c>
-      <c r="B56" s="15">
+      <c r="A56" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="B56" s="19">
         <f>B24</f>
         <v>1026431</v>
       </c>
-      <c r="C56" s="15">
+      <c r="C56" s="19">
         <f>C24</f>
         <v>1231718</v>
       </c>
-      <c r="D56" s="15">
+      <c r="D56" s="19">
         <f>D24</f>
         <v>1231718</v>
       </c>
-      <c r="E56" s="15">
+      <c r="E56" s="19">
         <f>E24</f>
         <v>1231718</v>
       </c>
-      <c r="F56" s="15">
+      <c r="F56" s="19">
         <f>F24</f>
         <v>1231718</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="B57" s="15">
+      <c r="A57" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="B57" s="19">
         <f>B46</f>
         <v>545000</v>
       </c>
-      <c r="C57" s="15">
+      <c r="C57" s="19">
         <f>C46</f>
         <v>887860</v>
       </c>
-      <c r="D57" s="15">
+      <c r="D57" s="19">
         <f>D46</f>
         <v>1190521</v>
       </c>
-      <c r="E57" s="15">
+      <c r="E57" s="19">
         <f>E46</f>
         <v>1439089</v>
       </c>
-      <c r="F57" s="15">
+      <c r="F57" s="19">
         <f>F46</f>
         <v>1554924</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="B58" s="15">
+      <c r="A58" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="B58" s="19">
         <f>B52</f>
         <v>164825</v>
       </c>
-      <c r="C58" s="15">
+      <c r="C58" s="19">
         <f>C52</f>
         <v>89825</v>
       </c>
-      <c r="D58" s="15">
+      <c r="D58" s="19">
         <f>D52</f>
         <v>89825</v>
       </c>
-      <c r="E58" s="15">
+      <c r="E58" s="19">
         <f>E52</f>
         <v>74825</v>
       </c>
-      <c r="F58" s="15">
+      <c r="F58" s="19">
         <f>F52</f>
         <v>69825</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="20" t="s">
-        <v>175</v>
-      </c>
-      <c r="B59" s="24">
+      <c r="A59" s="24" t="s">
+        <v>181</v>
+      </c>
+      <c r="B59" s="28">
         <f>B56+B57+B58</f>
         <v>1736256</v>
       </c>
-      <c r="C59" s="24">
+      <c r="C59" s="28">
         <f>C56+C57+C58</f>
         <v>2209403</v>
       </c>
-      <c r="D59" s="24">
+      <c r="D59" s="28">
         <f>D56+D57+D58</f>
         <v>2512064</v>
       </c>
-      <c r="E59" s="24">
+      <c r="E59" s="28">
         <f>E56+E57+E58</f>
         <v>2745632</v>
       </c>
-      <c r="F59" s="24">
+      <c r="F59" s="28">
         <f>F56+F57+F58</f>
         <v>2856467</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="25" t="s">
-        <v>176</v>
-      </c>
-      <c r="B61" s="26">
+      <c r="A61" s="29" t="s">
+        <v>182</v>
+      </c>
+      <c r="B61" s="30">
         <f>B55-B59</f>
         <v>-447923</v>
       </c>
-      <c r="C61" s="27">
+      <c r="C61" s="31">
         <f>C55-C59</f>
         <v>313397</v>
       </c>
-      <c r="D61" s="27">
+      <c r="D61" s="31">
         <f>D55-D59</f>
         <v>1272536</v>
       </c>
-      <c r="E61" s="27">
+      <c r="E61" s="31">
         <f>E55-E59</f>
         <v>2013493</v>
       </c>
-      <c r="F61" s="27">
+      <c r="F61" s="31">
         <f>F55-F59</f>
         <v>2327933</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="B62" s="28">
+      <c r="A62" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="B62" s="32">
         <f>IF(B55=0,"",B61/B55)</f>
         <v>-0.35</v>
       </c>
-      <c r="C62" s="28">
+      <c r="C62" s="32">
         <f>IF(C55=0,"",C61/C55)</f>
         <v>0.12</v>
       </c>
-      <c r="D62" s="28">
+      <c r="D62" s="32">
         <f>IF(D55=0,"",D61/D55)</f>
         <v>0.34</v>
       </c>
-      <c r="E62" s="28">
+      <c r="E62" s="32">
         <f>IF(E55=0,"",E61/E55)</f>
         <v>0.42</v>
       </c>
-      <c r="F62" s="28">
+      <c r="F62" s="32">
         <f>IF(F55=0,"",F61/F55)</f>
         <v>0.45</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="B63" s="15">
+      <c r="A63" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="B63" s="19">
         <f>B61</f>
         <v>-447923</v>
       </c>
-      <c r="C63" s="15">
+      <c r="C63" s="19">
         <f>B63+C61</f>
         <v>-134526</v>
       </c>
-      <c r="D63" s="15">
+      <c r="D63" s="19">
         <f>C63+D61</f>
         <v>1138010</v>
       </c>
-      <c r="E63" s="15">
+      <c r="E63" s="19">
         <f>D63+E61</f>
         <v>3151503</v>
       </c>
-      <c r="F63" s="15">
+      <c r="F63" s="19">
         <f>E63+F61</f>
         <v>5479436</v>
       </c>
     </row>
     <row r="65" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A65" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="B65" s="6"/>
-      <c r="C65" s="6"/>
-      <c r="D65" s="6"/>
-      <c r="E65" s="6"/>
-      <c r="F65" s="6"/>
+      <c r="A65" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="B65" s="10"/>
+      <c r="C65" s="10"/>
+      <c r="D65" s="10"/>
+      <c r="E65" s="10"/>
+      <c r="F65" s="10"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A66" s="20" t="s">
-        <v>180</v>
-      </c>
-      <c r="B66" s="24">
+      <c r="A66" s="24" t="s">
+        <v>186</v>
+      </c>
+      <c r="B66" s="28">
         <f>B55-B56-B57</f>
         <v>-283098</v>
       </c>
-      <c r="C66" s="24">
+      <c r="C66" s="28">
         <f>C55-C56-C57</f>
         <v>403222</v>
       </c>
-      <c r="D66" s="24">
+      <c r="D66" s="28">
         <f>D55-D56-D57</f>
         <v>1362361</v>
       </c>
-      <c r="E66" s="24">
+      <c r="E66" s="28">
         <f>E55-E56-E57</f>
         <v>2088318</v>
       </c>
-      <c r="F66" s="24">
+      <c r="F66" s="28">
         <f>F55-F56-F57</f>
         <v>2397758</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A67" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="B67" s="15">
+      <c r="A67" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="B67" s="19">
         <f>B58</f>
         <v>164825</v>
       </c>
-      <c r="C67" s="15">
+      <c r="C67" s="19">
         <f>C58</f>
         <v>89825</v>
       </c>
-      <c r="D67" s="15">
+      <c r="D67" s="19">
         <f>D58</f>
         <v>89825</v>
       </c>
-      <c r="E67" s="15">
+      <c r="E67" s="19">
         <f>E58</f>
         <v>74825</v>
       </c>
-      <c r="F67" s="15">
+      <c r="F67" s="19">
         <f>F58</f>
         <v>69825</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A68" s="20" t="s">
-        <v>182</v>
-      </c>
-      <c r="B68" s="29">
+      <c r="A68" s="24" t="s">
+        <v>188</v>
+      </c>
+      <c r="B68" s="33">
         <f>IF(B67=0,"N/A",B66/B67)</f>
         <v>-1.72</v>
       </c>
-      <c r="C68" s="29">
+      <c r="C68" s="33">
         <f>IF(C67=0,"N/A",C66/C67)</f>
         <v>4.49</v>
       </c>
-      <c r="D68" s="29">
+      <c r="D68" s="33">
         <f>IF(D67=0,"N/A",D66/D67)</f>
         <v>15.17</v>
       </c>
-      <c r="E68" s="29">
+      <c r="E68" s="33">
         <f>IF(E67=0,"N/A",E66/E67)</f>
         <v>27.91</v>
       </c>
-      <c r="F68" s="29">
+      <c r="F68" s="33">
         <f>IF(F67=0,"N/A",F66/F67)</f>
         <v>34.34</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A69" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="B69" s="15" t="str">
+      <c r="A69" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="B69" s="19" t="str">
         <f>Assumptions!B68</f>
         <v>0</v>
       </c>
-      <c r="C69" s="15">
+      <c r="C69" s="19">
         <f>B70</f>
         <v>-447923</v>
       </c>
-      <c r="D69" s="15">
+      <c r="D69" s="19">
         <f>C70</f>
         <v>-134526</v>
       </c>
-      <c r="E69" s="15">
+      <c r="E69" s="19">
         <f>D70</f>
         <v>1138010</v>
       </c>
-      <c r="F69" s="15">
+      <c r="F69" s="19">
         <f>E70</f>
         <v>3151503</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A70" s="20" t="s">
-        <v>183</v>
-      </c>
-      <c r="B70" s="24">
+      <c r="A70" s="24" t="s">
+        <v>189</v>
+      </c>
+      <c r="B70" s="28">
         <f>B69+B61</f>
         <v>-447923</v>
       </c>
-      <c r="C70" s="24">
+      <c r="C70" s="28">
         <f>C69+C61</f>
         <v>-134526</v>
       </c>
-      <c r="D70" s="24">
+      <c r="D70" s="28">
         <f>D69+D61</f>
         <v>1138010</v>
       </c>
-      <c r="E70" s="24">
+      <c r="E70" s="28">
         <f>E69+E61</f>
         <v>3151503</v>
       </c>
-      <c r="F70" s="24">
+      <c r="F70" s="28">
         <f>F69+F61</f>
         <v>5479436</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A71" s="7" t="s">
-        <v>184</v>
-      </c>
-      <c r="B71" s="30">
+      <c r="A71" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="B71" s="34">
         <f>IF(B59=0,"",B70/B59*365)</f>
         <v>-94</v>
       </c>
-      <c r="C71" s="30">
+      <c r="C71" s="34">
         <f>IF(C59=0,"",C70/C59*365)</f>
         <v>-22</v>
       </c>
-      <c r="D71" s="30">
+      <c r="D71" s="34">
         <f>IF(D59=0,"",D70/D59*365)</f>
         <v>165</v>
       </c>
-      <c r="E71" s="30">
+      <c r="E71" s="34">
         <f>IF(E59=0,"",E70/E59*365)</f>
         <v>419</v>
       </c>
-      <c r="F71" s="30">
+      <c r="F71" s="34">
         <f>IF(F59=0,"",F70/F59*365)</f>
         <v>700</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A72" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="B72" s="31">
+      <c r="A72" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="B72" s="35">
         <f>IF(B59=0,"",B70/(B59/12))</f>
         <v>-3.1</v>
       </c>
-      <c r="C72" s="31">
+      <c r="C72" s="35">
         <f>IF(C59=0,"",C70/(C59/12))</f>
         <v>-0.7</v>
       </c>
-      <c r="D72" s="31">
+      <c r="D72" s="35">
         <f>IF(D59=0,"",D70/(D59/12))</f>
         <v>5.4</v>
       </c>
-      <c r="E72" s="31">
+      <c r="E72" s="35">
         <f>IF(E59=0,"",E70/(E59/12))</f>
         <v>13.8</v>
       </c>
-      <c r="F72" s="31">
+      <c r="F72" s="35">
         <f>IF(F59=0,"",F70/(F59/12))</f>
         <v>23</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A73" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="B73" s="28">
+      <c r="A73" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="B73" s="32">
         <f>IF(Assumptions!B12=0,"",B3/Assumptions!B12)</f>
         <v>0.3</v>
       </c>
-      <c r="C73" s="28">
+      <c r="C73" s="32">
         <f>IF(Assumptions!B12=0,"",C3/Assumptions!B12)</f>
         <v>0.5</v>
       </c>
-      <c r="D73" s="28">
+      <c r="D73" s="32">
         <f>IF(Assumptions!B12=0,"",D3/Assumptions!B12)</f>
         <v>0.75</v>
       </c>
-      <c r="E73" s="28">
+      <c r="E73" s="32">
         <f>IF(Assumptions!B12=0,"",E3/Assumptions!B12)</f>
         <v>0.94</v>
       </c>
-      <c r="F73" s="28">
+      <c r="F73" s="32">
         <f>IF(Assumptions!B12=0,"",F3/Assumptions!B12)</f>
         <v>1</v>
       </c>
     </row>
     <row r="75" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A75" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="B75" s="6"/>
-      <c r="C75" s="6"/>
-      <c r="D75" s="6"/>
-      <c r="E75" s="6"/>
-      <c r="F75" s="6"/>
+      <c r="A75" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="B75" s="10"/>
+      <c r="C75" s="10"/>
+      <c r="D75" s="10"/>
+      <c r="E75" s="10"/>
+      <c r="F75" s="10"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A76" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="B76" s="7" t="str">
+      <c r="A76" s="11" t="s">
+        <v>194</v>
+      </c>
+      <c r="B76" s="11" t="str">
         <f>IF(B67=0,"N/A",IF(B68&gt;=1.2,"PASS","FAIL"))</f>
         <v>FAIL</v>
       </c>
-      <c r="C76" s="7" t="str">
+      <c r="C76" s="11" t="str">
         <f>IF(C67=0,"N/A",IF(C68&gt;=1.2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="D76" s="7" t="str">
+      <c r="D76" s="11" t="str">
         <f>IF(D67=0,"N/A",IF(D68&gt;=1.2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="E76" s="7" t="str">
+      <c r="E76" s="11" t="str">
         <f>IF(E67=0,"N/A",IF(E68&gt;=1.2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="F76" s="7" t="str">
+      <c r="F76" s="11" t="str">
         <f>IF(F67=0,"N/A",IF(F68&gt;=1.2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A77" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="B77" s="7" t="str">
+      <c r="A77" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="B77" s="11" t="str">
         <f>IF(B61&gt;0,"PASS","FAIL")</f>
         <v>FAIL</v>
       </c>
-      <c r="C77" s="7" t="str">
+      <c r="C77" s="11" t="str">
         <f>IF(C61&gt;0,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-      <c r="D77" s="7" t="str">
+      <c r="D77" s="11" t="str">
         <f>IF(D61&gt;0,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-      <c r="E77" s="7" t="str">
+      <c r="E77" s="11" t="str">
         <f>IF(E61&gt;0,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-      <c r="F77" s="7" t="str">
+      <c r="F77" s="11" t="str">
         <f>IF(F61&gt;0,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A78" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="B78" s="7" t="str">
+      <c r="A78" s="11" t="s">
+        <v>196</v>
+      </c>
+      <c r="B78" s="11" t="str">
         <f>IF(Assumptions!B12=0,"N/A",IF(B3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
         <v>FAIL</v>
       </c>
-      <c r="C78" s="7" t="str">
+      <c r="C78" s="11" t="str">
         <f>IF(Assumptions!B12=0,"N/A",IF(C3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
         <v>FAIL</v>
       </c>
-      <c r="D78" s="7" t="str">
+      <c r="D78" s="11" t="str">
         <f>IF(Assumptions!B12=0,"N/A",IF(D3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="E78" s="7" t="str">
+      <c r="E78" s="11" t="str">
         <f>IF(Assumptions!B12=0,"N/A",IF(E3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="F78" s="7" t="str">
+      <c r="F78" s="11" t="str">
         <f>IF(Assumptions!B12=0,"N/A",IF(F3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A79" s="7" t="s">
-        <v>191</v>
-      </c>
-      <c r="B79" s="7" t="str">
+      <c r="A79" s="11" t="s">
+        <v>197</v>
+      </c>
+      <c r="B79" s="11" t="str">
         <f>IF(B59=0,"N/A",IF(B70/(B59/12)&gt;=2,"PASS","FAIL"))</f>
         <v>FAIL</v>
       </c>
-      <c r="C79" s="7" t="str">
+      <c r="C79" s="11" t="str">
         <f>IF(C59=0,"N/A",IF(C70/(C59/12)&gt;=2,"PASS","FAIL"))</f>
         <v>FAIL</v>
       </c>
-      <c r="D79" s="7" t="str">
+      <c r="D79" s="11" t="str">
         <f>IF(D59=0,"N/A",IF(D70/(D59/12)&gt;=2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="E79" s="7" t="str">
+      <c r="E79" s="11" t="str">
         <f>IF(E59=0,"N/A",IF(E70/(E59/12)&gt;=2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="F79" s="7" t="str">
+      <c r="F79" s="11" t="str">
         <f>IF(F59=0,"N/A",IF(F70/(F59/12)&gt;=2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="81" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A81" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="B81" s="6"/>
-      <c r="C81" s="6"/>
-      <c r="D81" s="6"/>
-      <c r="E81" s="6"/>
-      <c r="F81" s="6"/>
+      <c r="A81" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="B81" s="10"/>
+      <c r="C81" s="10"/>
+      <c r="D81" s="10"/>
+      <c r="E81" s="10"/>
+      <c r="F81" s="10"/>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A82" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="B82" s="15">
+      <c r="A82" s="11" t="s">
+        <v>199</v>
+      </c>
+      <c r="B82" s="19">
         <f>IF(B3=0,"",B12/B3)</f>
         <v>10736</v>
       </c>
-      <c r="C82" s="15">
+      <c r="C82" s="19">
         <f>IF(C3=0,"",C12/C3)</f>
         <v>12614</v>
       </c>
-      <c r="D82" s="15">
+      <c r="D82" s="19">
         <f>IF(D3=0,"",D12/D3)</f>
         <v>12615</v>
       </c>
-      <c r="E82" s="15">
+      <c r="E82" s="19">
         <f>IF(E3=0,"",E12/E3)</f>
         <v>12691</v>
       </c>
-      <c r="F82" s="15">
+      <c r="F82" s="19">
         <f>IF(F3=0,"",F12/F3)</f>
         <v>12961</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A83" s="7" t="s">
-        <v>194</v>
-      </c>
-      <c r="B83" s="15">
+      <c r="A83" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="B83" s="19">
         <f>IF(B3=0,"",B59/B3)</f>
         <v>14469</v>
       </c>
-      <c r="C83" s="15">
+      <c r="C83" s="19">
         <f>IF(C3=0,"",C59/C3)</f>
         <v>11047</v>
       </c>
-      <c r="D83" s="15">
+      <c r="D83" s="19">
         <f>IF(D3=0,"",D59/D3)</f>
         <v>8374</v>
       </c>
-      <c r="E83" s="15">
+      <c r="E83" s="19">
         <f>IF(E3=0,"",E59/E3)</f>
         <v>7322</v>
       </c>
-      <c r="F83" s="15">
+      <c r="F83" s="19">
         <f>IF(F3=0,"",F59/F3)</f>
         <v>7141</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A84" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="B84" s="15">
+      <c r="A84" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="B84" s="19">
         <f>B56+B58</f>
         <v>1191256</v>
       </c>
-      <c r="C84" s="15">
+      <c r="C84" s="19">
         <f>C56+C58</f>
         <v>1321543</v>
       </c>
-      <c r="D84" s="15">
+      <c r="D84" s="19">
         <f>D56+D58</f>
         <v>1321543</v>
       </c>
-      <c r="E84" s="15">
+      <c r="E84" s="19">
         <f>E56+E58</f>
         <v>1306543</v>
       </c>
-      <c r="F84" s="15">
+      <c r="F84" s="19">
         <f>F56+F58</f>
         <v>1301543</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A85" s="7" t="s">
-        <v>196</v>
-      </c>
-      <c r="B85" s="15">
+      <c r="A85" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="B85" s="19">
         <f>IF(B3=0,"",B57/B3)</f>
         <v>4542</v>
       </c>
-      <c r="C85" s="15">
+      <c r="C85" s="19">
         <f>IF(C3=0,"",C57/C3)</f>
         <v>4439</v>
       </c>
-      <c r="D85" s="15">
+      <c r="D85" s="19">
         <f>IF(D3=0,"",D57/D3)</f>
         <v>3968</v>
       </c>
-      <c r="E85" s="15">
+      <c r="E85" s="19">
         <f>IF(E3=0,"",E57/E3)</f>
         <v>3838</v>
       </c>
-      <c r="F85" s="15">
+      <c r="F85" s="19">
         <f>IF(F3=0,"",F57/F3)</f>
         <v>3887</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A86" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="B86" s="15">
+      <c r="A86" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="B86" s="19">
         <f>IF(B3=0,"",B82-B85)</f>
         <v>6194</v>
       </c>
-      <c r="C86" s="15">
+      <c r="C86" s="19">
         <f>IF(C3=0,"",C82-C85)</f>
         <v>8175</v>
       </c>
-      <c r="D86" s="15">
+      <c r="D86" s="19">
         <f>IF(D3=0,"",D82-D85)</f>
         <v>8647</v>
       </c>
-      <c r="E86" s="15">
+      <c r="E86" s="19">
         <f>IF(E3=0,"",E82-E85)</f>
         <v>8853</v>
       </c>
-      <c r="F86" s="15">
+      <c r="F86" s="19">
         <f>IF(F3=0,"",F82-F85)</f>
         <v>9074</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A87" s="32" t="s">
-        <v>198</v>
-      </c>
-      <c r="B87" s="33">
+      <c r="A87" s="36" t="s">
+        <v>204</v>
+      </c>
+      <c r="B87" s="37">
         <f>IF(B86&lt;=0,"N/A",ROUNDUP(B84/B86,0))</f>
         <v>193</v>
       </c>
-      <c r="C87" s="33">
+      <c r="C87" s="37">
         <f>IF(C86&lt;=0,"N/A",ROUNDUP(C84/C86,0))</f>
         <v>162</v>
       </c>
-      <c r="D87" s="33">
+      <c r="D87" s="37">
         <f>IF(D86&lt;=0,"N/A",ROUNDUP(D84/D86,0))</f>
         <v>153</v>
       </c>
-      <c r="E87" s="33">
+      <c r="E87" s="37">
         <f>IF(E86&lt;=0,"N/A",ROUNDUP(E84/E86,0))</f>
         <v>148</v>
       </c>
-      <c r="F87" s="33">
+      <c r="F87" s="37">
         <f>IF(F86&lt;=0,"N/A",ROUNDUP(F84/F86,0))</f>
         <v>144</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A89" s="18" t="s">
-        <v>137</v>
-      </c>
-      <c r="B89" s="18"/>
-      <c r="C89" s="18"/>
-      <c r="D89" s="18"/>
-      <c r="E89" s="18"/>
-      <c r="F89" s="18"/>
+      <c r="A89" s="22" t="s">
+        <v>143</v>
+      </c>
+      <c r="B89" s="22"/>
+      <c r="C89" s="22"/>
+      <c r="D89" s="22"/>
+      <c r="E89" s="22"/>
+      <c r="F89" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -4373,2018 +4595,2018 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
-      <c r="M1" s="4"/>
-      <c r="N1" s="4"/>
+      <c r="A1" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
+      <c r="M1" s="8"/>
+      <c r="N1" s="8"/>
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="19" t="s">
-        <v>39</v>
-      </c>
-      <c r="C2" s="19" t="s">
-        <v>200</v>
-      </c>
-      <c r="D2" s="19" t="s">
-        <v>201</v>
-      </c>
-      <c r="E2" s="19" t="s">
-        <v>202</v>
-      </c>
-      <c r="F2" s="19" t="s">
-        <v>203</v>
-      </c>
-      <c r="G2" s="19" t="s">
-        <v>204</v>
-      </c>
-      <c r="H2" s="19" t="s">
-        <v>205</v>
-      </c>
-      <c r="I2" s="19" t="s">
+      <c r="A2" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2" s="23" t="s">
         <v>206</v>
       </c>
-      <c r="J2" s="19" t="s">
+      <c r="D2" s="23" t="s">
         <v>207</v>
       </c>
-      <c r="K2" s="19" t="s">
+      <c r="E2" s="23" t="s">
         <v>208</v>
       </c>
-      <c r="L2" s="19" t="s">
+      <c r="F2" s="23" t="s">
         <v>209</v>
       </c>
-      <c r="M2" s="19" t="s">
+      <c r="G2" s="23" t="s">
         <v>210</v>
       </c>
-      <c r="N2" s="19" t="s">
+      <c r="H2" s="23" t="s">
         <v>211</v>
       </c>
+      <c r="I2" s="23" t="s">
+        <v>212</v>
+      </c>
+      <c r="J2" s="23" t="s">
+        <v>213</v>
+      </c>
+      <c r="K2" s="23" t="s">
+        <v>214</v>
+      </c>
+      <c r="L2" s="23" t="s">
+        <v>215</v>
+      </c>
+      <c r="M2" s="23" t="s">
+        <v>216</v>
+      </c>
+      <c r="N2" s="23" t="s">
+        <v>217</v>
+      </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="6"/>
-      <c r="K3" s="6"/>
-      <c r="L3" s="6"/>
-      <c r="M3" s="6"/>
-      <c r="N3" s="6"/>
+      <c r="A3" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="10"/>
+      <c r="N3" s="10"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="B4" s="15">
+      <c r="A4" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="B4" s="19">
         <v>114000</v>
       </c>
-      <c r="C4" s="15">
+      <c r="C4" s="19">
         <v>114000</v>
       </c>
-      <c r="D4" s="15">
+      <c r="D4" s="19">
         <v>114000</v>
       </c>
-      <c r="E4" s="15">
+      <c r="E4" s="19">
         <v>114000</v>
       </c>
-      <c r="F4" s="15">
+      <c r="F4" s="19">
         <v>114000</v>
       </c>
-      <c r="G4" s="15">
+      <c r="G4" s="19">
         <v>114000</v>
       </c>
-      <c r="H4" s="15">
+      <c r="H4" s="19">
         <v>114000</v>
       </c>
-      <c r="I4" s="15">
+      <c r="I4" s="19">
         <v>114000</v>
       </c>
-      <c r="J4" s="15">
+      <c r="J4" s="19">
         <v>114000</v>
       </c>
-      <c r="K4" s="15">
+      <c r="K4" s="19">
         <v>114000</v>
       </c>
-      <c r="L4" s="15">
-        <v>0</v>
-      </c>
-      <c r="M4" s="15">
-        <v>0</v>
-      </c>
-      <c r="N4" s="15">
+      <c r="L4" s="19">
+        <v>0</v>
+      </c>
+      <c r="M4" s="19">
+        <v>0</v>
+      </c>
+      <c r="N4" s="19">
         <f>SUM(B4:M4)</f>
         <v>950000</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B5" s="15">
+      <c r="A5" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="B5" s="19">
         <v>9600</v>
       </c>
-      <c r="C5" s="15">
+      <c r="C5" s="19">
         <v>9600</v>
       </c>
-      <c r="D5" s="15">
+      <c r="D5" s="19">
         <v>9600</v>
       </c>
-      <c r="E5" s="15">
+      <c r="E5" s="19">
         <v>9600</v>
       </c>
-      <c r="F5" s="15">
+      <c r="F5" s="19">
         <v>9600</v>
       </c>
-      <c r="G5" s="15">
+      <c r="G5" s="19">
         <v>9600</v>
       </c>
-      <c r="H5" s="15">
+      <c r="H5" s="19">
         <v>9600</v>
       </c>
-      <c r="I5" s="15">
+      <c r="I5" s="19">
         <v>9600</v>
       </c>
-      <c r="J5" s="15">
+      <c r="J5" s="19">
         <v>9600</v>
       </c>
-      <c r="K5" s="15">
+      <c r="K5" s="19">
         <v>9600</v>
       </c>
-      <c r="L5" s="15">
-        <v>0</v>
-      </c>
-      <c r="M5" s="15">
-        <v>0</v>
-      </c>
-      <c r="N5" s="15">
+      <c r="L5" s="19">
+        <v>0</v>
+      </c>
+      <c r="M5" s="19">
+        <v>0</v>
+      </c>
+      <c r="N5" s="19">
         <f>SUM(B5:M5)</f>
         <v>80000</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="B6" s="15">
+      <c r="A6" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="B6" s="19">
         <v>14400</v>
       </c>
-      <c r="C6" s="15">
+      <c r="C6" s="19">
         <v>14400</v>
       </c>
-      <c r="D6" s="15">
+      <c r="D6" s="19">
         <v>14400</v>
       </c>
-      <c r="E6" s="15">
+      <c r="E6" s="19">
         <v>14400</v>
       </c>
-      <c r="F6" s="15">
+      <c r="F6" s="19">
         <v>14400</v>
       </c>
-      <c r="G6" s="15">
+      <c r="G6" s="19">
         <v>14400</v>
       </c>
-      <c r="H6" s="15">
+      <c r="H6" s="19">
         <v>14400</v>
       </c>
-      <c r="I6" s="15">
+      <c r="I6" s="19">
         <v>14400</v>
       </c>
-      <c r="J6" s="15">
+      <c r="J6" s="19">
         <v>14400</v>
       </c>
-      <c r="K6" s="15">
+      <c r="K6" s="19">
         <v>14400</v>
       </c>
-      <c r="L6" s="15">
-        <v>0</v>
-      </c>
-      <c r="M6" s="15">
-        <v>0</v>
-      </c>
-      <c r="N6" s="15">
+      <c r="L6" s="19">
+        <v>0</v>
+      </c>
+      <c r="M6" s="19">
+        <v>0</v>
+      </c>
+      <c r="N6" s="19">
         <f>SUM(B6:M6)</f>
         <v>120000</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="B7" s="15">
+      <c r="A7" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="B7" s="19">
         <v>10000</v>
       </c>
-      <c r="C7" s="15">
+      <c r="C7" s="19">
         <v>10000</v>
       </c>
-      <c r="D7" s="15">
+      <c r="D7" s="19">
         <v>10000</v>
       </c>
-      <c r="E7" s="15">
+      <c r="E7" s="19">
         <v>10000</v>
       </c>
-      <c r="F7" s="15">
+      <c r="F7" s="19">
         <v>10000</v>
       </c>
-      <c r="G7" s="15">
+      <c r="G7" s="19">
         <v>10000</v>
       </c>
-      <c r="H7" s="15">
+      <c r="H7" s="19">
         <v>10000</v>
       </c>
-      <c r="I7" s="15">
+      <c r="I7" s="19">
         <v>10000</v>
       </c>
-      <c r="J7" s="15">
+      <c r="J7" s="19">
         <v>10000</v>
       </c>
-      <c r="K7" s="15">
+      <c r="K7" s="19">
         <v>10000</v>
       </c>
-      <c r="L7" s="15">
-        <v>0</v>
-      </c>
-      <c r="M7" s="15">
-        <v>0</v>
-      </c>
-      <c r="N7" s="15">
+      <c r="L7" s="19">
+        <v>0</v>
+      </c>
+      <c r="M7" s="19">
+        <v>0</v>
+      </c>
+      <c r="N7" s="19">
         <f>SUM(B7:M7)</f>
         <v>83333</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="B8" s="15">
+      <c r="A8" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="B8" s="19">
         <v>3000</v>
       </c>
-      <c r="C8" s="15">
+      <c r="C8" s="19">
         <v>3000</v>
       </c>
-      <c r="D8" s="15">
+      <c r="D8" s="19">
         <v>3000</v>
       </c>
-      <c r="E8" s="15">
+      <c r="E8" s="19">
         <v>3000</v>
       </c>
-      <c r="F8" s="15">
+      <c r="F8" s="19">
         <v>3000</v>
       </c>
-      <c r="G8" s="15">
+      <c r="G8" s="19">
         <v>3000</v>
       </c>
-      <c r="H8" s="15">
+      <c r="H8" s="19">
         <v>3000</v>
       </c>
-      <c r="I8" s="15">
+      <c r="I8" s="19">
         <v>3000</v>
       </c>
-      <c r="J8" s="15">
+      <c r="J8" s="19">
         <v>3000</v>
       </c>
-      <c r="K8" s="15">
+      <c r="K8" s="19">
         <v>3000</v>
       </c>
-      <c r="L8" s="15">
-        <v>0</v>
-      </c>
-      <c r="M8" s="15">
-        <v>0</v>
-      </c>
-      <c r="N8" s="15">
+      <c r="L8" s="19">
+        <v>0</v>
+      </c>
+      <c r="M8" s="19">
+        <v>0</v>
+      </c>
+      <c r="N8" s="19">
         <f>SUM(B8:M8)</f>
         <v>25000</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="B9" s="15">
+      <c r="A9" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="B9" s="19">
         <v>3600</v>
       </c>
-      <c r="C9" s="15">
+      <c r="C9" s="19">
         <v>3600</v>
       </c>
-      <c r="D9" s="15">
+      <c r="D9" s="19">
         <v>3600</v>
       </c>
-      <c r="E9" s="15">
+      <c r="E9" s="19">
         <v>3600</v>
       </c>
-      <c r="F9" s="15">
+      <c r="F9" s="19">
         <v>3600</v>
       </c>
-      <c r="G9" s="15">
+      <c r="G9" s="19">
         <v>3600</v>
       </c>
-      <c r="H9" s="15">
+      <c r="H9" s="19">
         <v>3600</v>
       </c>
-      <c r="I9" s="15">
+      <c r="I9" s="19">
         <v>3600</v>
       </c>
-      <c r="J9" s="15">
+      <c r="J9" s="19">
         <v>3600</v>
       </c>
-      <c r="K9" s="15">
+      <c r="K9" s="19">
         <v>3600</v>
       </c>
-      <c r="L9" s="15">
-        <v>0</v>
-      </c>
-      <c r="M9" s="15">
-        <v>0</v>
-      </c>
-      <c r="N9" s="15">
+      <c r="L9" s="19">
+        <v>0</v>
+      </c>
+      <c r="M9" s="19">
+        <v>0</v>
+      </c>
+      <c r="N9" s="19">
         <f>SUM(B9:M9)</f>
         <v>30000</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="B10" s="22">
+      <c r="A10" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="B10" s="26">
         <f>SUM(B4:B9)</f>
         <v>154600</v>
       </c>
-      <c r="C10" s="22">
+      <c r="C10" s="26">
         <f>SUM(C4:C9)</f>
         <v>154600</v>
       </c>
-      <c r="D10" s="22">
+      <c r="D10" s="26">
         <f>SUM(D4:D9)</f>
         <v>154600</v>
       </c>
-      <c r="E10" s="22">
+      <c r="E10" s="26">
         <f>SUM(E4:E9)</f>
         <v>154600</v>
       </c>
-      <c r="F10" s="22">
+      <c r="F10" s="26">
         <f>SUM(F4:F9)</f>
         <v>154600</v>
       </c>
-      <c r="G10" s="22">
+      <c r="G10" s="26">
         <f>SUM(G4:G9)</f>
         <v>154600</v>
       </c>
-      <c r="H10" s="22">
+      <c r="H10" s="26">
         <f>SUM(H4:H9)</f>
         <v>154600</v>
       </c>
-      <c r="I10" s="22">
+      <c r="I10" s="26">
         <f>SUM(I4:I9)</f>
         <v>154600</v>
       </c>
-      <c r="J10" s="22">
+      <c r="J10" s="26">
         <f>SUM(J4:J9)</f>
         <v>154600</v>
       </c>
-      <c r="K10" s="22">
+      <c r="K10" s="26">
         <f>SUM(K4:K9)</f>
         <v>154600</v>
       </c>
-      <c r="L10" s="22" t="str">
+      <c r="L10" s="26" t="str">
         <f>SUM(L4:L9)</f>
         <v>0</v>
       </c>
-      <c r="M10" s="22" t="str">
+      <c r="M10" s="26" t="str">
         <f>SUM(M4:M9)</f>
         <v>0</v>
       </c>
-      <c r="N10" s="22">
+      <c r="N10" s="26">
         <f>SUM(B10:M10)</f>
         <v>1546000</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6"/>
-      <c r="J12" s="6"/>
-      <c r="K12" s="6"/>
-      <c r="L12" s="6"/>
-      <c r="M12" s="6"/>
-      <c r="N12" s="6"/>
+      <c r="A12" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="B12" s="10"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="10"/>
+      <c r="H12" s="10"/>
+      <c r="I12" s="10"/>
+      <c r="J12" s="10"/>
+      <c r="K12" s="10"/>
+      <c r="L12" s="10"/>
+      <c r="M12" s="10"/>
+      <c r="N12" s="10"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="B13" s="15">
+      <c r="A13" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="B13" s="19">
         <v>12435</v>
       </c>
-      <c r="C13" s="15">
+      <c r="C13" s="19">
         <v>12435</v>
       </c>
-      <c r="D13" s="15">
+      <c r="D13" s="19">
         <v>12435</v>
       </c>
-      <c r="E13" s="15">
+      <c r="E13" s="19">
         <v>12435</v>
       </c>
-      <c r="F13" s="15">
+      <c r="F13" s="19">
         <v>12435</v>
       </c>
-      <c r="G13" s="15">
+      <c r="G13" s="19">
         <v>12435</v>
       </c>
-      <c r="H13" s="15">
+      <c r="H13" s="19">
         <v>12435</v>
       </c>
-      <c r="I13" s="15">
+      <c r="I13" s="19">
         <v>12435</v>
       </c>
-      <c r="J13" s="15">
+      <c r="J13" s="19">
         <v>12435</v>
       </c>
-      <c r="K13" s="15">
+      <c r="K13" s="19">
         <v>12435</v>
       </c>
-      <c r="L13" s="15">
-        <v>0</v>
-      </c>
-      <c r="M13" s="15">
-        <v>0</v>
-      </c>
-      <c r="N13" s="15">
+      <c r="L13" s="19">
+        <v>0</v>
+      </c>
+      <c r="M13" s="19">
+        <v>0</v>
+      </c>
+      <c r="N13" s="19">
         <f>SUM(B13:M13)</f>
         <v>124346</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="B14" s="15">
+      <c r="A14" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="B14" s="19">
         <v>10174</v>
       </c>
-      <c r="C14" s="15">
+      <c r="C14" s="19">
         <v>10174</v>
       </c>
-      <c r="D14" s="15">
+      <c r="D14" s="19">
         <v>10174</v>
       </c>
-      <c r="E14" s="15">
+      <c r="E14" s="19">
         <v>10174</v>
       </c>
-      <c r="F14" s="15">
+      <c r="F14" s="19">
         <v>10174</v>
       </c>
-      <c r="G14" s="15">
+      <c r="G14" s="19">
         <v>10174</v>
       </c>
-      <c r="H14" s="15">
+      <c r="H14" s="19">
         <v>10174</v>
       </c>
-      <c r="I14" s="15">
+      <c r="I14" s="19">
         <v>10174</v>
       </c>
-      <c r="J14" s="15">
+      <c r="J14" s="19">
         <v>10174</v>
       </c>
-      <c r="K14" s="15">
+      <c r="K14" s="19">
         <v>10174</v>
       </c>
-      <c r="L14" s="15">
-        <v>0</v>
-      </c>
-      <c r="M14" s="15">
-        <v>0</v>
-      </c>
-      <c r="N14" s="15">
+      <c r="L14" s="19">
+        <v>0</v>
+      </c>
+      <c r="M14" s="19">
+        <v>0</v>
+      </c>
+      <c r="N14" s="19">
         <f>SUM(B14:M14)</f>
         <v>101738</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="B15" s="15">
+      <c r="A15" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="B15" s="19">
         <v>8139</v>
       </c>
-      <c r="C15" s="15">
+      <c r="C15" s="19">
         <v>8139</v>
       </c>
-      <c r="D15" s="15">
+      <c r="D15" s="19">
         <v>8139</v>
       </c>
-      <c r="E15" s="15">
+      <c r="E15" s="19">
         <v>8139</v>
       </c>
-      <c r="F15" s="15">
+      <c r="F15" s="19">
         <v>8139</v>
       </c>
-      <c r="G15" s="15">
+      <c r="G15" s="19">
         <v>8139</v>
       </c>
-      <c r="H15" s="15">
+      <c r="H15" s="19">
         <v>8139</v>
       </c>
-      <c r="I15" s="15">
+      <c r="I15" s="19">
         <v>8139</v>
       </c>
-      <c r="J15" s="15">
+      <c r="J15" s="19">
         <v>8139</v>
       </c>
-      <c r="K15" s="15">
+      <c r="K15" s="19">
         <v>8139</v>
       </c>
-      <c r="L15" s="15">
-        <v>0</v>
-      </c>
-      <c r="M15" s="15">
-        <v>0</v>
-      </c>
-      <c r="N15" s="15">
+      <c r="L15" s="19">
+        <v>0</v>
+      </c>
+      <c r="M15" s="19">
+        <v>0</v>
+      </c>
+      <c r="N15" s="19">
         <f>SUM(B15:M15)</f>
         <v>81390</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A16" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="B16" s="15">
+      <c r="A16" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="B16" s="19">
         <v>35269</v>
       </c>
-      <c r="C16" s="15">
+      <c r="C16" s="19">
         <v>35269</v>
       </c>
-      <c r="D16" s="15">
+      <c r="D16" s="19">
         <v>35269</v>
       </c>
-      <c r="E16" s="15">
+      <c r="E16" s="19">
         <v>35269</v>
       </c>
-      <c r="F16" s="15">
+      <c r="F16" s="19">
         <v>35269</v>
       </c>
-      <c r="G16" s="15">
+      <c r="G16" s="19">
         <v>35269</v>
       </c>
-      <c r="H16" s="15">
+      <c r="H16" s="19">
         <v>35269</v>
       </c>
-      <c r="I16" s="15">
+      <c r="I16" s="19">
         <v>35269</v>
       </c>
-      <c r="J16" s="15">
+      <c r="J16" s="19">
         <v>35269</v>
       </c>
-      <c r="K16" s="15">
+      <c r="K16" s="19">
         <v>35269</v>
       </c>
-      <c r="L16" s="15">
-        <v>0</v>
-      </c>
-      <c r="M16" s="15">
-        <v>0</v>
-      </c>
-      <c r="N16" s="15">
+      <c r="L16" s="19">
+        <v>0</v>
+      </c>
+      <c r="M16" s="19">
+        <v>0</v>
+      </c>
+      <c r="N16" s="19">
         <f>SUM(B16:M16)</f>
         <v>352690</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="B17" s="15">
+      <c r="A17" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="B17" s="19">
         <v>6217</v>
       </c>
-      <c r="C17" s="15">
+      <c r="C17" s="19">
         <v>6217</v>
       </c>
-      <c r="D17" s="15">
+      <c r="D17" s="19">
         <v>6217</v>
       </c>
-      <c r="E17" s="15">
+      <c r="E17" s="19">
         <v>6217</v>
       </c>
-      <c r="F17" s="15">
+      <c r="F17" s="19">
         <v>6217</v>
       </c>
-      <c r="G17" s="15">
+      <c r="G17" s="19">
         <v>6217</v>
       </c>
-      <c r="H17" s="15">
+      <c r="H17" s="19">
         <v>6217</v>
       </c>
-      <c r="I17" s="15">
+      <c r="I17" s="19">
         <v>6217</v>
       </c>
-      <c r="J17" s="15">
+      <c r="J17" s="19">
         <v>6217</v>
       </c>
-      <c r="K17" s="15">
+      <c r="K17" s="19">
         <v>6217</v>
       </c>
-      <c r="L17" s="15">
-        <v>0</v>
-      </c>
-      <c r="M17" s="15">
-        <v>0</v>
-      </c>
-      <c r="N17" s="15">
+      <c r="L17" s="19">
+        <v>0</v>
+      </c>
+      <c r="M17" s="19">
+        <v>0</v>
+      </c>
+      <c r="N17" s="19">
         <f>SUM(B17:M17)</f>
         <v>62173</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="B18" s="15">
+      <c r="A18" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="B18" s="19">
         <v>9574</v>
       </c>
-      <c r="C18" s="15">
+      <c r="C18" s="19">
         <v>9574</v>
       </c>
-      <c r="D18" s="15">
+      <c r="D18" s="19">
         <v>9574</v>
       </c>
-      <c r="E18" s="15">
+      <c r="E18" s="19">
         <v>9574</v>
       </c>
-      <c r="F18" s="15">
+      <c r="F18" s="19">
         <v>9574</v>
       </c>
-      <c r="G18" s="15">
+      <c r="G18" s="19">
         <v>9574</v>
       </c>
-      <c r="H18" s="15">
+      <c r="H18" s="19">
         <v>9574</v>
       </c>
-      <c r="I18" s="15">
+      <c r="I18" s="19">
         <v>9574</v>
       </c>
-      <c r="J18" s="15">
+      <c r="J18" s="19">
         <v>9574</v>
       </c>
-      <c r="K18" s="15">
+      <c r="K18" s="19">
         <v>9574</v>
       </c>
-      <c r="L18" s="15">
-        <v>0</v>
-      </c>
-      <c r="M18" s="15">
-        <v>0</v>
-      </c>
-      <c r="N18" s="15">
+      <c r="L18" s="19">
+        <v>0</v>
+      </c>
+      <c r="M18" s="19">
+        <v>0</v>
+      </c>
+      <c r="N18" s="19">
         <f>SUM(B18:M18)</f>
         <v>95738</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A19" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="B19" s="15">
+      <c r="A19" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="B19" s="19">
         <v>6217</v>
       </c>
-      <c r="C19" s="15">
+      <c r="C19" s="19">
         <v>6217</v>
       </c>
-      <c r="D19" s="15">
+      <c r="D19" s="19">
         <v>6217</v>
       </c>
-      <c r="E19" s="15">
+      <c r="E19" s="19">
         <v>6217</v>
       </c>
-      <c r="F19" s="15">
+      <c r="F19" s="19">
         <v>6217</v>
       </c>
-      <c r="G19" s="15">
+      <c r="G19" s="19">
         <v>6217</v>
       </c>
-      <c r="H19" s="15">
+      <c r="H19" s="19">
         <v>6217</v>
       </c>
-      <c r="I19" s="15">
+      <c r="I19" s="19">
         <v>6217</v>
       </c>
-      <c r="J19" s="15">
+      <c r="J19" s="19">
         <v>6217</v>
       </c>
-      <c r="K19" s="15">
+      <c r="K19" s="19">
         <v>6217</v>
       </c>
-      <c r="L19" s="15">
-        <v>0</v>
-      </c>
-      <c r="M19" s="15">
-        <v>0</v>
-      </c>
-      <c r="N19" s="15">
+      <c r="L19" s="19">
+        <v>0</v>
+      </c>
+      <c r="M19" s="19">
+        <v>0</v>
+      </c>
+      <c r="N19" s="19">
         <f>SUM(B19:M19)</f>
         <v>62173</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A20" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="B20" s="15">
+      <c r="A20" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="B20" s="19">
         <v>8401</v>
       </c>
-      <c r="C20" s="15">
+      <c r="C20" s="19">
         <v>8401</v>
       </c>
-      <c r="D20" s="15">
+      <c r="D20" s="19">
         <v>8401</v>
       </c>
-      <c r="E20" s="15">
+      <c r="E20" s="19">
         <v>8401</v>
       </c>
-      <c r="F20" s="15">
+      <c r="F20" s="19">
         <v>8401</v>
       </c>
-      <c r="G20" s="15">
+      <c r="G20" s="19">
         <v>8401</v>
       </c>
-      <c r="H20" s="15">
+      <c r="H20" s="19">
         <v>8401</v>
       </c>
-      <c r="I20" s="15">
+      <c r="I20" s="19">
         <v>8401</v>
       </c>
-      <c r="J20" s="15">
+      <c r="J20" s="19">
         <v>8401</v>
       </c>
-      <c r="K20" s="15">
+      <c r="K20" s="19">
         <v>8401</v>
       </c>
-      <c r="L20" s="15">
-        <v>0</v>
-      </c>
-      <c r="M20" s="15">
-        <v>0</v>
-      </c>
-      <c r="N20" s="15">
+      <c r="L20" s="19">
+        <v>0</v>
+      </c>
+      <c r="M20" s="19">
+        <v>0</v>
+      </c>
+      <c r="N20" s="19">
         <f>SUM(B20:M20)</f>
         <v>84012</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A21" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="B21" s="15">
+      <c r="A21" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="B21" s="19">
         <v>6217</v>
       </c>
-      <c r="C21" s="15">
+      <c r="C21" s="19">
         <v>6217</v>
       </c>
-      <c r="D21" s="15">
+      <c r="D21" s="19">
         <v>6217</v>
       </c>
-      <c r="E21" s="15">
+      <c r="E21" s="19">
         <v>6217</v>
       </c>
-      <c r="F21" s="15">
+      <c r="F21" s="19">
         <v>6217</v>
       </c>
-      <c r="G21" s="15">
+      <c r="G21" s="19">
         <v>6217</v>
       </c>
-      <c r="H21" s="15">
+      <c r="H21" s="19">
         <v>6217</v>
       </c>
-      <c r="I21" s="15">
+      <c r="I21" s="19">
         <v>6217</v>
       </c>
-      <c r="J21" s="15">
+      <c r="J21" s="19">
         <v>6217</v>
       </c>
-      <c r="K21" s="15">
+      <c r="K21" s="19">
         <v>6217</v>
       </c>
-      <c r="L21" s="15">
-        <v>0</v>
-      </c>
-      <c r="M21" s="15">
-        <v>0</v>
-      </c>
-      <c r="N21" s="15">
+      <c r="L21" s="19">
+        <v>0</v>
+      </c>
+      <c r="M21" s="19">
+        <v>0</v>
+      </c>
+      <c r="N21" s="19">
         <f>SUM(B21:M21)</f>
         <v>62173</v>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A22" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="B22" s="22">
+      <c r="A22" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="B22" s="26">
         <f>SUM(B13:B21)</f>
         <v>102643</v>
       </c>
-      <c r="C22" s="22">
+      <c r="C22" s="26">
         <f>SUM(C13:C21)</f>
         <v>102643</v>
       </c>
-      <c r="D22" s="22">
+      <c r="D22" s="26">
         <f>SUM(D13:D21)</f>
         <v>102643</v>
       </c>
-      <c r="E22" s="22">
+      <c r="E22" s="26">
         <f>SUM(E13:E21)</f>
         <v>102643</v>
       </c>
-      <c r="F22" s="22">
+      <c r="F22" s="26">
         <f>SUM(F13:F21)</f>
         <v>102643</v>
       </c>
-      <c r="G22" s="22">
+      <c r="G22" s="26">
         <f>SUM(G13:G21)</f>
         <v>102643</v>
       </c>
-      <c r="H22" s="22">
+      <c r="H22" s="26">
         <f>SUM(H13:H21)</f>
         <v>102643</v>
       </c>
-      <c r="I22" s="22">
+      <c r="I22" s="26">
         <f>SUM(I13:I21)</f>
         <v>102643</v>
       </c>
-      <c r="J22" s="22">
+      <c r="J22" s="26">
         <f>SUM(J13:J21)</f>
         <v>102643</v>
       </c>
-      <c r="K22" s="22">
+      <c r="K22" s="26">
         <f>SUM(K13:K21)</f>
         <v>102643</v>
       </c>
-      <c r="L22" s="22" t="str">
+      <c r="L22" s="26" t="str">
         <f>SUM(L13:L21)</f>
         <v>0</v>
       </c>
-      <c r="M22" s="22" t="str">
+      <c r="M22" s="26" t="str">
         <f>SUM(M13:M21)</f>
         <v>0</v>
       </c>
-      <c r="N22" s="22">
+      <c r="N22" s="26">
         <f>SUM(B22:M22)</f>
         <v>1026431</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A24" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="B24" s="6"/>
-      <c r="C24" s="6"/>
-      <c r="D24" s="6"/>
-      <c r="E24" s="6"/>
-      <c r="F24" s="6"/>
-      <c r="G24" s="6"/>
-      <c r="H24" s="6"/>
-      <c r="I24" s="6"/>
-      <c r="J24" s="6"/>
-      <c r="K24" s="6"/>
-      <c r="L24" s="6"/>
-      <c r="M24" s="6"/>
-      <c r="N24" s="6"/>
+      <c r="A24" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="B24" s="10"/>
+      <c r="C24" s="10"/>
+      <c r="D24" s="10"/>
+      <c r="E24" s="10"/>
+      <c r="F24" s="10"/>
+      <c r="G24" s="10"/>
+      <c r="H24" s="10"/>
+      <c r="I24" s="10"/>
+      <c r="J24" s="10"/>
+      <c r="K24" s="10"/>
+      <c r="L24" s="10"/>
+      <c r="M24" s="10"/>
+      <c r="N24" s="10"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A25" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
-      <c r="G25" s="7"/>
-      <c r="H25" s="7"/>
-      <c r="I25" s="7"/>
-      <c r="J25" s="7"/>
-      <c r="K25" s="7"/>
-      <c r="L25" s="7"/>
-      <c r="M25" s="7"/>
-      <c r="N25" s="7"/>
+      <c r="A25" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="B25" s="11"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="11"/>
+      <c r="I25" s="11"/>
+      <c r="J25" s="11"/>
+      <c r="K25" s="11"/>
+      <c r="L25" s="11"/>
+      <c r="M25" s="11"/>
+      <c r="N25" s="11"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A26" s="7" t="s">
-        <v>212</v>
-      </c>
-      <c r="B26" s="15">
+      <c r="A26" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="B26" s="19">
         <v>7000</v>
       </c>
-      <c r="C26" s="15">
+      <c r="C26" s="19">
         <v>7000</v>
       </c>
-      <c r="D26" s="15">
+      <c r="D26" s="19">
         <v>7000</v>
       </c>
-      <c r="E26" s="15">
+      <c r="E26" s="19">
         <v>7000</v>
       </c>
-      <c r="F26" s="15">
+      <c r="F26" s="19">
         <v>7000</v>
       </c>
-      <c r="G26" s="15">
+      <c r="G26" s="19">
         <v>7000</v>
       </c>
-      <c r="H26" s="15">
+      <c r="H26" s="19">
         <v>7000</v>
       </c>
-      <c r="I26" s="15">
+      <c r="I26" s="19">
         <v>7000</v>
       </c>
-      <c r="J26" s="15">
+      <c r="J26" s="19">
         <v>7000</v>
       </c>
-      <c r="K26" s="15">
+      <c r="K26" s="19">
         <v>7000</v>
       </c>
-      <c r="L26" s="15">
-        <v>0</v>
-      </c>
-      <c r="M26" s="15">
-        <v>0</v>
-      </c>
-      <c r="N26" s="15">
+      <c r="L26" s="19">
+        <v>0</v>
+      </c>
+      <c r="M26" s="19">
+        <v>0</v>
+      </c>
+      <c r="N26" s="19">
         <f>SUM(B26:M26)</f>
         <v>70000</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A27" s="23" t="s">
-        <v>153</v>
-      </c>
-      <c r="B27" s="24">
+      <c r="A27" s="27" t="s">
+        <v>159</v>
+      </c>
+      <c r="B27" s="28">
         <v>7000</v>
       </c>
-      <c r="C27" s="24">
+      <c r="C27" s="28">
         <v>7000</v>
       </c>
-      <c r="D27" s="24">
+      <c r="D27" s="28">
         <v>7000</v>
       </c>
-      <c r="E27" s="24">
+      <c r="E27" s="28">
         <v>7000</v>
       </c>
-      <c r="F27" s="24">
+      <c r="F27" s="28">
         <v>7000</v>
       </c>
-      <c r="G27" s="24">
+      <c r="G27" s="28">
         <v>7000</v>
       </c>
-      <c r="H27" s="24">
+      <c r="H27" s="28">
         <v>7000</v>
       </c>
-      <c r="I27" s="24">
+      <c r="I27" s="28">
         <v>7000</v>
       </c>
-      <c r="J27" s="24">
+      <c r="J27" s="28">
         <v>7000</v>
       </c>
-      <c r="K27" s="24">
+      <c r="K27" s="28">
         <v>7000</v>
       </c>
-      <c r="L27" s="24">
-        <v>0</v>
-      </c>
-      <c r="M27" s="24">
-        <v>0</v>
-      </c>
-      <c r="N27" s="24">
+      <c r="L27" s="28">
+        <v>0</v>
+      </c>
+      <c r="M27" s="28">
+        <v>0</v>
+      </c>
+      <c r="N27" s="28">
         <f>SUM(B27:M27)</f>
         <v>70000</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A28" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="B28" s="7"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="7"/>
-      <c r="F28" s="7"/>
-      <c r="G28" s="7"/>
-      <c r="H28" s="7"/>
-      <c r="I28" s="7"/>
-      <c r="J28" s="7"/>
-      <c r="K28" s="7"/>
-      <c r="L28" s="7"/>
-      <c r="M28" s="7"/>
-      <c r="N28" s="7"/>
+      <c r="A28" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="B28" s="11"/>
+      <c r="C28" s="11"/>
+      <c r="D28" s="11"/>
+      <c r="E28" s="11"/>
+      <c r="F28" s="11"/>
+      <c r="G28" s="11"/>
+      <c r="H28" s="11"/>
+      <c r="I28" s="11"/>
+      <c r="J28" s="11"/>
+      <c r="K28" s="11"/>
+      <c r="L28" s="11"/>
+      <c r="M28" s="11"/>
+      <c r="N28" s="11"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A29" s="7" t="s">
-        <v>213</v>
-      </c>
-      <c r="B29" s="15">
+      <c r="A29" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="B29" s="19">
         <v>5000</v>
       </c>
-      <c r="C29" s="15">
+      <c r="C29" s="19">
         <v>5000</v>
       </c>
-      <c r="D29" s="15">
+      <c r="D29" s="19">
         <v>5000</v>
       </c>
-      <c r="E29" s="15">
+      <c r="E29" s="19">
         <v>5000</v>
       </c>
-      <c r="F29" s="15">
+      <c r="F29" s="19">
         <v>5000</v>
       </c>
-      <c r="G29" s="15">
+      <c r="G29" s="19">
         <v>5000</v>
       </c>
-      <c r="H29" s="15">
+      <c r="H29" s="19">
         <v>5000</v>
       </c>
-      <c r="I29" s="15">
+      <c r="I29" s="19">
         <v>5000</v>
       </c>
-      <c r="J29" s="15">
+      <c r="J29" s="19">
         <v>5000</v>
       </c>
-      <c r="K29" s="15">
+      <c r="K29" s="19">
         <v>5000</v>
       </c>
-      <c r="L29" s="15">
-        <v>0</v>
-      </c>
-      <c r="M29" s="15">
-        <v>0</v>
-      </c>
-      <c r="N29" s="15">
+      <c r="L29" s="19">
+        <v>0</v>
+      </c>
+      <c r="M29" s="19">
+        <v>0</v>
+      </c>
+      <c r="N29" s="19">
         <f>SUM(B29:M29)</f>
         <v>50000</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A30" s="23" t="s">
-        <v>155</v>
-      </c>
-      <c r="B30" s="24">
+      <c r="A30" s="27" t="s">
+        <v>161</v>
+      </c>
+      <c r="B30" s="28">
         <v>5000</v>
       </c>
-      <c r="C30" s="24">
+      <c r="C30" s="28">
         <v>5000</v>
       </c>
-      <c r="D30" s="24">
+      <c r="D30" s="28">
         <v>5000</v>
       </c>
-      <c r="E30" s="24">
+      <c r="E30" s="28">
         <v>5000</v>
       </c>
-      <c r="F30" s="24">
+      <c r="F30" s="28">
         <v>5000</v>
       </c>
-      <c r="G30" s="24">
+      <c r="G30" s="28">
         <v>5000</v>
       </c>
-      <c r="H30" s="24">
+      <c r="H30" s="28">
         <v>5000</v>
       </c>
-      <c r="I30" s="24">
+      <c r="I30" s="28">
         <v>5000</v>
       </c>
-      <c r="J30" s="24">
+      <c r="J30" s="28">
         <v>5000</v>
       </c>
-      <c r="K30" s="24">
+      <c r="K30" s="28">
         <v>5000</v>
       </c>
-      <c r="L30" s="24">
-        <v>0</v>
-      </c>
-      <c r="M30" s="24">
-        <v>0</v>
-      </c>
-      <c r="N30" s="24">
+      <c r="L30" s="28">
+        <v>0</v>
+      </c>
+      <c r="M30" s="28">
+        <v>0</v>
+      </c>
+      <c r="N30" s="28">
         <f>SUM(B30:M30)</f>
         <v>50000</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A31" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="B31" s="7"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="7"/>
-      <c r="E31" s="7"/>
-      <c r="F31" s="7"/>
-      <c r="G31" s="7"/>
-      <c r="H31" s="7"/>
-      <c r="I31" s="7"/>
-      <c r="J31" s="7"/>
-      <c r="K31" s="7"/>
-      <c r="L31" s="7"/>
-      <c r="M31" s="7"/>
-      <c r="N31" s="7"/>
+      <c r="A31" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="B31" s="11"/>
+      <c r="C31" s="11"/>
+      <c r="D31" s="11"/>
+      <c r="E31" s="11"/>
+      <c r="F31" s="11"/>
+      <c r="G31" s="11"/>
+      <c r="H31" s="11"/>
+      <c r="I31" s="11"/>
+      <c r="J31" s="11"/>
+      <c r="K31" s="11"/>
+      <c r="L31" s="11"/>
+      <c r="M31" s="11"/>
+      <c r="N31" s="11"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A32" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="B32" s="15">
+      <c r="A32" s="11" t="s">
+        <v>220</v>
+      </c>
+      <c r="B32" s="19">
         <v>18000</v>
       </c>
-      <c r="C32" s="15">
+      <c r="C32" s="19">
         <v>18000</v>
       </c>
-      <c r="D32" s="15">
+      <c r="D32" s="19">
         <v>18000</v>
       </c>
-      <c r="E32" s="15">
+      <c r="E32" s="19">
         <v>18000</v>
       </c>
-      <c r="F32" s="15">
+      <c r="F32" s="19">
         <v>18000</v>
       </c>
-      <c r="G32" s="15">
+      <c r="G32" s="19">
         <v>18000</v>
       </c>
-      <c r="H32" s="15">
+      <c r="H32" s="19">
         <v>18000</v>
       </c>
-      <c r="I32" s="15">
+      <c r="I32" s="19">
         <v>18000</v>
       </c>
-      <c r="J32" s="15">
+      <c r="J32" s="19">
         <v>18000</v>
       </c>
-      <c r="K32" s="15">
+      <c r="K32" s="19">
         <v>18000</v>
       </c>
-      <c r="L32" s="15">
-        <v>0</v>
-      </c>
-      <c r="M32" s="15">
-        <v>0</v>
-      </c>
-      <c r="N32" s="15">
+      <c r="L32" s="19">
+        <v>0</v>
+      </c>
+      <c r="M32" s="19">
+        <v>0</v>
+      </c>
+      <c r="N32" s="19">
         <f>SUM(B32:M32)</f>
         <v>180000</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A33" s="7" t="s">
-        <v>215</v>
-      </c>
-      <c r="B33" s="15">
+      <c r="A33" s="11" t="s">
+        <v>221</v>
+      </c>
+      <c r="B33" s="19">
         <v>2500</v>
       </c>
-      <c r="C33" s="15">
+      <c r="C33" s="19">
         <v>2500</v>
       </c>
-      <c r="D33" s="15">
+      <c r="D33" s="19">
         <v>2500</v>
       </c>
-      <c r="E33" s="15">
+      <c r="E33" s="19">
         <v>2500</v>
       </c>
-      <c r="F33" s="15">
+      <c r="F33" s="19">
         <v>2500</v>
       </c>
-      <c r="G33" s="15">
+      <c r="G33" s="19">
         <v>2500</v>
       </c>
-      <c r="H33" s="15">
+      <c r="H33" s="19">
         <v>2500</v>
       </c>
-      <c r="I33" s="15">
+      <c r="I33" s="19">
         <v>2500</v>
       </c>
-      <c r="J33" s="15">
+      <c r="J33" s="19">
         <v>2500</v>
       </c>
-      <c r="K33" s="15">
+      <c r="K33" s="19">
         <v>2500</v>
       </c>
-      <c r="L33" s="15">
-        <v>0</v>
-      </c>
-      <c r="M33" s="15">
-        <v>0</v>
-      </c>
-      <c r="N33" s="15">
+      <c r="L33" s="19">
+        <v>0</v>
+      </c>
+      <c r="M33" s="19">
+        <v>0</v>
+      </c>
+      <c r="N33" s="19">
         <f>SUM(B33:M33)</f>
         <v>25000</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A34" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="B34" s="15">
+      <c r="A34" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="B34" s="19">
         <v>1500</v>
       </c>
-      <c r="C34" s="15">
+      <c r="C34" s="19">
         <v>1500</v>
       </c>
-      <c r="D34" s="15">
+      <c r="D34" s="19">
         <v>1500</v>
       </c>
-      <c r="E34" s="15">
+      <c r="E34" s="19">
         <v>1500</v>
       </c>
-      <c r="F34" s="15">
+      <c r="F34" s="19">
         <v>1500</v>
       </c>
-      <c r="G34" s="15">
+      <c r="G34" s="19">
         <v>1500</v>
       </c>
-      <c r="H34" s="15">
+      <c r="H34" s="19">
         <v>1500</v>
       </c>
-      <c r="I34" s="15">
+      <c r="I34" s="19">
         <v>1500</v>
       </c>
-      <c r="J34" s="15">
+      <c r="J34" s="19">
         <v>1500</v>
       </c>
-      <c r="K34" s="15">
+      <c r="K34" s="19">
         <v>1500</v>
       </c>
-      <c r="L34" s="15">
-        <v>0</v>
-      </c>
-      <c r="M34" s="15">
-        <v>0</v>
-      </c>
-      <c r="N34" s="15">
+      <c r="L34" s="19">
+        <v>0</v>
+      </c>
+      <c r="M34" s="19">
+        <v>0</v>
+      </c>
+      <c r="N34" s="19">
         <f>SUM(B34:M34)</f>
         <v>15000</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A35" s="7" t="s">
-        <v>217</v>
-      </c>
-      <c r="B35" s="15">
+      <c r="A35" s="11" t="s">
+        <v>223</v>
+      </c>
+      <c r="B35" s="19">
         <v>1500</v>
       </c>
-      <c r="C35" s="15">
+      <c r="C35" s="19">
         <v>1500</v>
       </c>
-      <c r="D35" s="15">
+      <c r="D35" s="19">
         <v>1500</v>
       </c>
-      <c r="E35" s="15">
+      <c r="E35" s="19">
         <v>1500</v>
       </c>
-      <c r="F35" s="15">
+      <c r="F35" s="19">
         <v>1500</v>
       </c>
-      <c r="G35" s="15">
+      <c r="G35" s="19">
         <v>1500</v>
       </c>
-      <c r="H35" s="15">
+      <c r="H35" s="19">
         <v>1500</v>
       </c>
-      <c r="I35" s="15">
+      <c r="I35" s="19">
         <v>1500</v>
       </c>
-      <c r="J35" s="15">
+      <c r="J35" s="19">
         <v>1500</v>
       </c>
-      <c r="K35" s="15">
+      <c r="K35" s="19">
         <v>1500</v>
       </c>
-      <c r="L35" s="15">
-        <v>0</v>
-      </c>
-      <c r="M35" s="15">
-        <v>0</v>
-      </c>
-      <c r="N35" s="15">
+      <c r="L35" s="19">
+        <v>0</v>
+      </c>
+      <c r="M35" s="19">
+        <v>0</v>
+      </c>
+      <c r="N35" s="19">
         <f>SUM(B35:M35)</f>
         <v>15000</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A36" s="23" t="s">
-        <v>160</v>
-      </c>
-      <c r="B36" s="24">
+      <c r="A36" s="27" t="s">
+        <v>166</v>
+      </c>
+      <c r="B36" s="28">
         <v>23500</v>
       </c>
-      <c r="C36" s="24">
+      <c r="C36" s="28">
         <v>23500</v>
       </c>
-      <c r="D36" s="24">
+      <c r="D36" s="28">
         <v>23500</v>
       </c>
-      <c r="E36" s="24">
+      <c r="E36" s="28">
         <v>23500</v>
       </c>
-      <c r="F36" s="24">
+      <c r="F36" s="28">
         <v>23500</v>
       </c>
-      <c r="G36" s="24">
+      <c r="G36" s="28">
         <v>23500</v>
       </c>
-      <c r="H36" s="24">
+      <c r="H36" s="28">
         <v>23500</v>
       </c>
-      <c r="I36" s="24">
+      <c r="I36" s="28">
         <v>23500</v>
       </c>
-      <c r="J36" s="24">
+      <c r="J36" s="28">
         <v>23500</v>
       </c>
-      <c r="K36" s="24">
+      <c r="K36" s="28">
         <v>23500</v>
       </c>
-      <c r="L36" s="24">
-        <v>0</v>
-      </c>
-      <c r="M36" s="24">
-        <v>0</v>
-      </c>
-      <c r="N36" s="24">
+      <c r="L36" s="28">
+        <v>0</v>
+      </c>
+      <c r="M36" s="28">
+        <v>0</v>
+      </c>
+      <c r="N36" s="28">
         <f>SUM(B36:M36)</f>
         <v>235000</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A37" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="B37" s="7"/>
-      <c r="C37" s="7"/>
-      <c r="D37" s="7"/>
-      <c r="E37" s="7"/>
-      <c r="F37" s="7"/>
-      <c r="G37" s="7"/>
-      <c r="H37" s="7"/>
-      <c r="I37" s="7"/>
-      <c r="J37" s="7"/>
-      <c r="K37" s="7"/>
-      <c r="L37" s="7"/>
-      <c r="M37" s="7"/>
-      <c r="N37" s="7"/>
+      <c r="A37" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="B37" s="11"/>
+      <c r="C37" s="11"/>
+      <c r="D37" s="11"/>
+      <c r="E37" s="11"/>
+      <c r="F37" s="11"/>
+      <c r="G37" s="11"/>
+      <c r="H37" s="11"/>
+      <c r="I37" s="11"/>
+      <c r="J37" s="11"/>
+      <c r="K37" s="11"/>
+      <c r="L37" s="11"/>
+      <c r="M37" s="11"/>
+      <c r="N37" s="11"/>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A38" s="7" t="s">
-        <v>218</v>
-      </c>
-      <c r="B38" s="15">
+      <c r="A38" s="11" t="s">
+        <v>224</v>
+      </c>
+      <c r="B38" s="19">
         <v>2083</v>
       </c>
-      <c r="C38" s="15">
+      <c r="C38" s="19">
         <v>2083</v>
       </c>
-      <c r="D38" s="15">
+      <c r="D38" s="19">
         <v>2083</v>
       </c>
-      <c r="E38" s="15">
+      <c r="E38" s="19">
         <v>2083</v>
       </c>
-      <c r="F38" s="15">
+      <c r="F38" s="19">
         <v>2083</v>
       </c>
-      <c r="G38" s="15">
+      <c r="G38" s="19">
         <v>2083</v>
       </c>
-      <c r="H38" s="15">
+      <c r="H38" s="19">
         <v>2083</v>
       </c>
-      <c r="I38" s="15">
+      <c r="I38" s="19">
         <v>2083</v>
       </c>
-      <c r="J38" s="15">
+      <c r="J38" s="19">
         <v>2083</v>
       </c>
-      <c r="K38" s="15">
+      <c r="K38" s="19">
         <v>2083</v>
       </c>
-      <c r="L38" s="15">
-        <v>0</v>
-      </c>
-      <c r="M38" s="15">
-        <v>0</v>
-      </c>
-      <c r="N38" s="15">
+      <c r="L38" s="19">
+        <v>0</v>
+      </c>
+      <c r="M38" s="19">
+        <v>0</v>
+      </c>
+      <c r="N38" s="19">
         <f>SUM(B38:M38)</f>
         <v>20833</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A39" s="7" t="s">
-        <v>219</v>
-      </c>
-      <c r="B39" s="15">
+      <c r="A39" s="11" t="s">
+        <v>225</v>
+      </c>
+      <c r="B39" s="19">
         <v>1250</v>
       </c>
-      <c r="C39" s="15">
+      <c r="C39" s="19">
         <v>1250</v>
       </c>
-      <c r="D39" s="15">
+      <c r="D39" s="19">
         <v>1250</v>
       </c>
-      <c r="E39" s="15">
+      <c r="E39" s="19">
         <v>1250</v>
       </c>
-      <c r="F39" s="15">
+      <c r="F39" s="19">
         <v>1250</v>
       </c>
-      <c r="G39" s="15">
+      <c r="G39" s="19">
         <v>1250</v>
       </c>
-      <c r="H39" s="15">
+      <c r="H39" s="19">
         <v>1250</v>
       </c>
-      <c r="I39" s="15">
+      <c r="I39" s="19">
         <v>1250</v>
       </c>
-      <c r="J39" s="15">
+      <c r="J39" s="19">
         <v>1250</v>
       </c>
-      <c r="K39" s="15">
+      <c r="K39" s="19">
         <v>1250</v>
       </c>
-      <c r="L39" s="15">
-        <v>0</v>
-      </c>
-      <c r="M39" s="15">
-        <v>0</v>
-      </c>
-      <c r="N39" s="15">
+      <c r="L39" s="19">
+        <v>0</v>
+      </c>
+      <c r="M39" s="19">
+        <v>0</v>
+      </c>
+      <c r="N39" s="19">
         <f>SUM(B39:M39)</f>
         <v>12500</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A40" s="7" t="s">
-        <v>220</v>
-      </c>
-      <c r="B40" s="15">
+      <c r="A40" s="11" t="s">
+        <v>226</v>
+      </c>
+      <c r="B40" s="19">
         <v>1667</v>
       </c>
-      <c r="C40" s="15">
+      <c r="C40" s="19">
         <v>1667</v>
       </c>
-      <c r="D40" s="15">
+      <c r="D40" s="19">
         <v>1667</v>
       </c>
-      <c r="E40" s="15">
+      <c r="E40" s="19">
         <v>1667</v>
       </c>
-      <c r="F40" s="15">
+      <c r="F40" s="19">
         <v>1667</v>
       </c>
-      <c r="G40" s="15">
+      <c r="G40" s="19">
         <v>1667</v>
       </c>
-      <c r="H40" s="15">
+      <c r="H40" s="19">
         <v>1667</v>
       </c>
-      <c r="I40" s="15">
+      <c r="I40" s="19">
         <v>1667</v>
       </c>
-      <c r="J40" s="15">
+      <c r="J40" s="19">
         <v>1667</v>
       </c>
-      <c r="K40" s="15">
+      <c r="K40" s="19">
         <v>1667</v>
       </c>
-      <c r="L40" s="15">
-        <v>0</v>
-      </c>
-      <c r="M40" s="15">
-        <v>0</v>
-      </c>
-      <c r="N40" s="15">
+      <c r="L40" s="19">
+        <v>0</v>
+      </c>
+      <c r="M40" s="19">
+        <v>0</v>
+      </c>
+      <c r="N40" s="19">
         <f>SUM(B40:M40)</f>
         <v>16667</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A41" s="7" t="s">
-        <v>221</v>
-      </c>
-      <c r="B41" s="15">
+      <c r="A41" s="11" t="s">
+        <v>227</v>
+      </c>
+      <c r="B41" s="19">
         <v>8000</v>
       </c>
-      <c r="C41" s="15">
+      <c r="C41" s="19">
         <v>8000</v>
       </c>
-      <c r="D41" s="15">
+      <c r="D41" s="19">
         <v>8000</v>
       </c>
-      <c r="E41" s="15">
+      <c r="E41" s="19">
         <v>8000</v>
       </c>
-      <c r="F41" s="15">
+      <c r="F41" s="19">
         <v>8000</v>
       </c>
-      <c r="G41" s="15">
+      <c r="G41" s="19">
         <v>8000</v>
       </c>
-      <c r="H41" s="15">
+      <c r="H41" s="19">
         <v>8000</v>
       </c>
-      <c r="I41" s="15">
+      <c r="I41" s="19">
         <v>8000</v>
       </c>
-      <c r="J41" s="15">
+      <c r="J41" s="19">
         <v>8000</v>
       </c>
-      <c r="K41" s="15">
+      <c r="K41" s="19">
         <v>8000</v>
       </c>
-      <c r="L41" s="15">
-        <v>0</v>
-      </c>
-      <c r="M41" s="15">
-        <v>0</v>
-      </c>
-      <c r="N41" s="15">
+      <c r="L41" s="19">
+        <v>0</v>
+      </c>
+      <c r="M41" s="19">
+        <v>0</v>
+      </c>
+      <c r="N41" s="19">
         <f>SUM(B41:M41)</f>
         <v>80000</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A42" s="7" t="s">
-        <v>222</v>
-      </c>
-      <c r="B42" s="15">
+      <c r="A42" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="B42" s="19">
         <v>6000</v>
       </c>
-      <c r="C42" s="15">
+      <c r="C42" s="19">
         <v>6000</v>
       </c>
-      <c r="D42" s="15">
+      <c r="D42" s="19">
         <v>6000</v>
       </c>
-      <c r="E42" s="15">
+      <c r="E42" s="19">
         <v>6000</v>
       </c>
-      <c r="F42" s="15">
+      <c r="F42" s="19">
         <v>6000</v>
       </c>
-      <c r="G42" s="15">
+      <c r="G42" s="19">
         <v>6000</v>
       </c>
-      <c r="H42" s="15">
+      <c r="H42" s="19">
         <v>6000</v>
       </c>
-      <c r="I42" s="15">
+      <c r="I42" s="19">
         <v>6000</v>
       </c>
-      <c r="J42" s="15">
+      <c r="J42" s="19">
         <v>6000</v>
       </c>
-      <c r="K42" s="15">
+      <c r="K42" s="19">
         <v>6000</v>
       </c>
-      <c r="L42" s="15">
-        <v>0</v>
-      </c>
-      <c r="M42" s="15">
-        <v>0</v>
-      </c>
-      <c r="N42" s="15">
+      <c r="L42" s="19">
+        <v>0</v>
+      </c>
+      <c r="M42" s="19">
+        <v>0</v>
+      </c>
+      <c r="N42" s="19">
         <f>SUM(B42:M42)</f>
         <v>60000</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A43" s="23" t="s">
-        <v>166</v>
-      </c>
-      <c r="B43" s="24">
+      <c r="A43" s="27" t="s">
+        <v>172</v>
+      </c>
+      <c r="B43" s="28">
         <v>19000</v>
       </c>
-      <c r="C43" s="24">
+      <c r="C43" s="28">
         <v>19000</v>
       </c>
-      <c r="D43" s="24">
+      <c r="D43" s="28">
         <v>19000</v>
       </c>
-      <c r="E43" s="24">
+      <c r="E43" s="28">
         <v>19000</v>
       </c>
-      <c r="F43" s="24">
+      <c r="F43" s="28">
         <v>19000</v>
       </c>
-      <c r="G43" s="24">
+      <c r="G43" s="28">
         <v>19000</v>
       </c>
-      <c r="H43" s="24">
+      <c r="H43" s="28">
         <v>19000</v>
       </c>
-      <c r="I43" s="24">
+      <c r="I43" s="28">
         <v>19000</v>
       </c>
-      <c r="J43" s="24">
+      <c r="J43" s="28">
         <v>19000</v>
       </c>
-      <c r="K43" s="24">
+      <c r="K43" s="28">
         <v>19000</v>
       </c>
-      <c r="L43" s="24">
-        <v>0</v>
-      </c>
-      <c r="M43" s="24">
-        <v>0</v>
-      </c>
-      <c r="N43" s="24">
+      <c r="L43" s="28">
+        <v>0</v>
+      </c>
+      <c r="M43" s="28">
+        <v>0</v>
+      </c>
+      <c r="N43" s="28">
         <f>SUM(B43:M43)</f>
         <v>190000</v>
       </c>
     </row>
     <row r="44" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A44" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="B44" s="22">
+      <c r="A44" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="B44" s="26">
         <f>B27+B30+B36+B43</f>
         <v>54500</v>
       </c>
-      <c r="C44" s="22">
+      <c r="C44" s="26">
         <f>C27+C30+C36+C43</f>
         <v>54500</v>
       </c>
-      <c r="D44" s="22">
+      <c r="D44" s="26">
         <f>D27+D30+D36+D43</f>
         <v>54500</v>
       </c>
-      <c r="E44" s="22">
+      <c r="E44" s="26">
         <f>E27+E30+E36+E43</f>
         <v>54500</v>
       </c>
-      <c r="F44" s="22">
+      <c r="F44" s="26">
         <f>F27+F30+F36+F43</f>
         <v>54500</v>
       </c>
-      <c r="G44" s="22">
+      <c r="G44" s="26">
         <f>G27+G30+G36+G43</f>
         <v>54500</v>
       </c>
-      <c r="H44" s="22">
+      <c r="H44" s="26">
         <f>H27+H30+H36+H43</f>
         <v>54500</v>
       </c>
-      <c r="I44" s="22">
+      <c r="I44" s="26">
         <f>I27+I30+I36+I43</f>
         <v>54500</v>
       </c>
-      <c r="J44" s="22">
+      <c r="J44" s="26">
         <f>J27+J30+J36+J43</f>
         <v>54500</v>
       </c>
-      <c r="K44" s="22">
+      <c r="K44" s="26">
         <f>K27+K30+K36+K43</f>
         <v>54500</v>
       </c>
-      <c r="L44" s="22" t="str">
+      <c r="L44" s="26" t="str">
         <f>L27+L30+L36+L43</f>
         <v>0</v>
       </c>
-      <c r="M44" s="22" t="str">
+      <c r="M44" s="26" t="str">
         <f>M27+M30+M36+M43</f>
         <v>0</v>
       </c>
-      <c r="N44" s="22">
+      <c r="N44" s="26">
         <f>SUM(B44:M44)</f>
         <v>545000</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A46" s="20" t="s">
-        <v>223</v>
-      </c>
-      <c r="B46" s="15">
+      <c r="A46" s="24" t="s">
+        <v>229</v>
+      </c>
+      <c r="B46" s="19">
         <v>13735</v>
       </c>
-      <c r="C46" s="15">
+      <c r="C46" s="19">
         <v>13735</v>
       </c>
-      <c r="D46" s="15">
+      <c r="D46" s="19">
         <v>13735</v>
       </c>
-      <c r="E46" s="15">
+      <c r="E46" s="19">
         <v>13735</v>
       </c>
-      <c r="F46" s="15">
+      <c r="F46" s="19">
         <v>13735</v>
       </c>
-      <c r="G46" s="15">
+      <c r="G46" s="19">
         <v>13735</v>
       </c>
-      <c r="H46" s="15">
+      <c r="H46" s="19">
         <v>13735</v>
       </c>
-      <c r="I46" s="15">
+      <c r="I46" s="19">
         <v>13735</v>
       </c>
-      <c r="J46" s="15">
+      <c r="J46" s="19">
         <v>13735</v>
       </c>
-      <c r="K46" s="15">
+      <c r="K46" s="19">
         <v>13735</v>
       </c>
-      <c r="L46" s="15">
+      <c r="L46" s="19">
         <v>13735</v>
       </c>
-      <c r="M46" s="15">
+      <c r="M46" s="19">
         <v>13735</v>
       </c>
-      <c r="N46" s="15">
+      <c r="N46" s="19">
         <f>SUM(B46:M46)</f>
         <v>164825</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="48" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A48" s="6" t="s">
-        <v>224</v>
-      </c>
-      <c r="B48" s="6"/>
-      <c r="C48" s="6"/>
-      <c r="D48" s="6"/>
-      <c r="E48" s="6"/>
-      <c r="F48" s="6"/>
-      <c r="G48" s="6"/>
-      <c r="H48" s="6"/>
-      <c r="I48" s="6"/>
-      <c r="J48" s="6"/>
-      <c r="K48" s="6"/>
-      <c r="L48" s="6"/>
-      <c r="M48" s="6"/>
-      <c r="N48" s="6"/>
+      <c r="A48" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="B48" s="10"/>
+      <c r="C48" s="10"/>
+      <c r="D48" s="10"/>
+      <c r="E48" s="10"/>
+      <c r="F48" s="10"/>
+      <c r="G48" s="10"/>
+      <c r="H48" s="10"/>
+      <c r="I48" s="10"/>
+      <c r="J48" s="10"/>
+      <c r="K48" s="10"/>
+      <c r="L48" s="10"/>
+      <c r="M48" s="10"/>
+      <c r="N48" s="10"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A49" s="20" t="s">
-        <v>175</v>
-      </c>
-      <c r="B49" s="24">
+      <c r="A49" s="24" t="s">
+        <v>181</v>
+      </c>
+      <c r="B49" s="28">
         <f>B22+B44+B46</f>
         <v>170878</v>
       </c>
-      <c r="C49" s="24">
+      <c r="C49" s="28">
         <f>C22+C44+C46</f>
         <v>170878</v>
       </c>
-      <c r="D49" s="24">
+      <c r="D49" s="28">
         <f>D22+D44+D46</f>
         <v>170878</v>
       </c>
-      <c r="E49" s="24">
+      <c r="E49" s="28">
         <f>E22+E44+E46</f>
         <v>170878</v>
       </c>
-      <c r="F49" s="24">
+      <c r="F49" s="28">
         <f>F22+F44+F46</f>
         <v>170878</v>
       </c>
-      <c r="G49" s="24">
+      <c r="G49" s="28">
         <f>G22+G44+G46</f>
         <v>170878</v>
       </c>
-      <c r="H49" s="24">
+      <c r="H49" s="28">
         <f>H22+H44+H46</f>
         <v>170878</v>
       </c>
-      <c r="I49" s="24">
+      <c r="I49" s="28">
         <f>I22+I44+I46</f>
         <v>170878</v>
       </c>
-      <c r="J49" s="24">
+      <c r="J49" s="28">
         <f>J22+J44+J46</f>
         <v>170878</v>
       </c>
-      <c r="K49" s="24">
+      <c r="K49" s="28">
         <f>K22+K44+K46</f>
         <v>170878</v>
       </c>
-      <c r="L49" s="24">
+      <c r="L49" s="28">
         <f>L22+L44+L46</f>
         <v>13735</v>
       </c>
-      <c r="M49" s="24">
+      <c r="M49" s="28">
         <f>M22+M44+M46</f>
         <v>13735</v>
       </c>
-      <c r="N49" s="24">
+      <c r="N49" s="28">
         <f>SUM(B49:M49)</f>
         <v>1736250</v>
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A50" s="20" t="s">
-        <v>225</v>
-      </c>
-      <c r="B50" s="24">
+      <c r="A50" s="24" t="s">
+        <v>231</v>
+      </c>
+      <c r="B50" s="28">
         <f>B10-B49</f>
         <v>-16278</v>
       </c>
-      <c r="C50" s="24">
+      <c r="C50" s="28">
         <f>C10-C49</f>
         <v>-16278</v>
       </c>
-      <c r="D50" s="24">
+      <c r="D50" s="28">
         <f>D10-D49</f>
         <v>-16278</v>
       </c>
-      <c r="E50" s="24">
+      <c r="E50" s="28">
         <f>E10-E49</f>
         <v>-16278</v>
       </c>
-      <c r="F50" s="24">
+      <c r="F50" s="28">
         <f>F10-F49</f>
         <v>-16278</v>
       </c>
-      <c r="G50" s="24">
+      <c r="G50" s="28">
         <f>G10-G49</f>
         <v>-16278</v>
       </c>
-      <c r="H50" s="24">
+      <c r="H50" s="28">
         <f>H10-H49</f>
         <v>-16278</v>
       </c>
-      <c r="I50" s="24">
+      <c r="I50" s="28">
         <f>I10-I49</f>
         <v>-16278</v>
       </c>
-      <c r="J50" s="24">
+      <c r="J50" s="28">
         <f>J10-J49</f>
         <v>-16278</v>
       </c>
-      <c r="K50" s="24">
+      <c r="K50" s="28">
         <f>K10-K49</f>
         <v>-16278</v>
       </c>
-      <c r="L50" s="24">
+      <c r="L50" s="28">
         <f>L10-L49</f>
         <v>-13735</v>
       </c>
-      <c r="M50" s="24">
+      <c r="M50" s="28">
         <f>M10-M49</f>
         <v>-13735</v>
       </c>
-      <c r="N50" s="24">
+      <c r="N50" s="28">
         <f>SUM(B50:M50)</f>
         <v>-190250</v>
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A51" s="20" t="s">
-        <v>226</v>
-      </c>
-      <c r="B51" s="24">
+      <c r="A51" s="24" t="s">
+        <v>232</v>
+      </c>
+      <c r="B51" s="28">
         <f>0+B50</f>
         <v>-16278</v>
       </c>
-      <c r="C51" s="24">
+      <c r="C51" s="28">
         <f>B51+C50</f>
         <v>-32556</v>
       </c>
-      <c r="D51" s="24">
+      <c r="D51" s="28">
         <f>C51+D50</f>
         <v>-48834</v>
       </c>
-      <c r="E51" s="24">
+      <c r="E51" s="28">
         <f>D51+E50</f>
         <v>-65112</v>
       </c>
-      <c r="F51" s="24">
+      <c r="F51" s="28">
         <f>E51+F50</f>
         <v>-81390</v>
       </c>
-      <c r="G51" s="24">
+      <c r="G51" s="28">
         <f>F51+G50</f>
         <v>-97668</v>
       </c>
-      <c r="H51" s="24">
+      <c r="H51" s="28">
         <f>G51+H50</f>
         <v>-113946</v>
       </c>
-      <c r="I51" s="24">
+      <c r="I51" s="28">
         <f>H51+I50</f>
         <v>-130224</v>
       </c>
-      <c r="J51" s="24">
+      <c r="J51" s="28">
         <f>I51+J50</f>
         <v>-146502</v>
       </c>
-      <c r="K51" s="24">
+      <c r="K51" s="28">
         <f>J51+K50</f>
         <v>-162780</v>
       </c>
-      <c r="L51" s="24">
+      <c r="L51" s="28">
         <f>K51+L50</f>
         <v>-176515</v>
       </c>
-      <c r="M51" s="24">
+      <c r="M51" s="28">
         <f>L51+M50</f>
         <v>-190250</v>
       </c>
-      <c r="N51" s="24">
+      <c r="N51" s="28">
         <f>M51</f>
         <v>-190250</v>
       </c>
     </row>
     <row r="53" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" s="6" t="s">
-        <v>227</v>
-      </c>
-      <c r="B53" s="6"/>
-      <c r="C53" s="6"/>
+      <c r="A53" s="10" t="s">
+        <v>233</v>
+      </c>
+      <c r="B53" s="10"/>
+      <c r="C53" s="10"/>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="B54" s="15">
+      <c r="A54" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="B54" s="19">
         <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A55" s="7" t="s">
-        <v>228</v>
-      </c>
-      <c r="B55" s="24">
+      <c r="A55" s="11" t="s">
+        <v>234</v>
+      </c>
+      <c r="B55" s="28">
         <f>M51</f>
         <v>-190250</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A56" s="7" t="s">
-        <v>229</v>
-      </c>
-      <c r="B56" s="15">
+      <c r="A56" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="B56" s="19">
         <f>MIN(B51:M51)</f>
         <v>-190250</v>
       </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A58" s="18" t="s">
-        <v>137</v>
-      </c>
-      <c r="B58" s="18"/>
-      <c r="C58" s="18"/>
-      <c r="D58" s="18"/>
-      <c r="E58" s="18"/>
-      <c r="F58" s="18"/>
-      <c r="G58" s="18"/>
-      <c r="H58" s="18"/>
-      <c r="I58" s="18"/>
-      <c r="J58" s="18"/>
-      <c r="K58" s="18"/>
-      <c r="L58" s="18"/>
-      <c r="M58" s="18"/>
-      <c r="N58" s="18"/>
+      <c r="A58" s="22" t="s">
+        <v>143</v>
+      </c>
+      <c r="B58" s="22"/>
+      <c r="C58" s="22"/>
+      <c r="D58" s="22"/>
+      <c r="E58" s="22"/>
+      <c r="F58" s="22"/>
+      <c r="G58" s="22"/>
+      <c r="H58" s="22"/>
+      <c r="I58" s="22"/>
+      <c r="J58" s="22"/>
+      <c r="K58" s="22"/>
+      <c r="L58" s="22"/>
+      <c r="M58" s="22"/>
+      <c r="N58" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -6403,6 +6625,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
+    <tabColor rgb="FF0D9488"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B2:G33"/>
@@ -6416,7 +6639,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -6425,466 +6648,466 @@
       <c r="G2" s="1"/>
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="34" t="s">
-        <v>231</v>
-      </c>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
+      <c r="B3" s="38" t="s">
+        <v>237</v>
+      </c>
+      <c r="C3" s="38"/>
+      <c r="D3" s="38"/>
+      <c r="E3" s="38"/>
+      <c r="F3" s="38"/>
+      <c r="G3" s="38"/>
     </row>
     <row r="5" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="6" t="s">
-        <v>232</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>233</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>234</v>
-      </c>
-      <c r="E5" s="10" t="s">
-        <v>235</v>
-      </c>
-      <c r="F5" s="10" t="s">
-        <v>236</v>
-      </c>
-      <c r="G5" s="10" t="s">
-        <v>237</v>
+      <c r="B5" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>239</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>240</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>241</v>
+      </c>
+      <c r="F5" s="14" t="s">
+        <v>242</v>
+      </c>
+      <c r="G5" s="14" t="s">
+        <v>243</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="7" t="s">
-        <v>238</v>
-      </c>
-      <c r="C6" s="35">
+      <c r="B6" s="11" t="s">
+        <v>244</v>
+      </c>
+      <c r="C6" s="39">
         <v>120</v>
       </c>
-      <c r="D6" s="35">
+      <c r="D6" s="39">
         <v>200</v>
       </c>
-      <c r="E6" s="35">
+      <c r="E6" s="39">
         <v>300</v>
       </c>
-      <c r="F6" s="35">
+      <c r="F6" s="39">
         <v>375</v>
       </c>
-      <c r="G6" s="35">
+      <c r="G6" s="39">
         <v>400</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="7" t="s">
-        <v>239</v>
-      </c>
-      <c r="C7" s="36">
+      <c r="B7" s="11" t="s">
+        <v>245</v>
+      </c>
+      <c r="C7" s="40">
         <v>1546000</v>
       </c>
-      <c r="D7" s="36">
+      <c r="D7" s="40">
         <v>2522800</v>
       </c>
-      <c r="E7" s="36">
+      <c r="E7" s="40">
         <v>3784600</v>
       </c>
-      <c r="F7" s="36">
+      <c r="F7" s="40">
         <v>4759125</v>
       </c>
-      <c r="G7" s="36">
+      <c r="G7" s="40">
         <v>5184400</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="11" t="s">
+        <v>246</v>
+      </c>
+      <c r="C8" s="40">
+        <v>1026431.25</v>
+      </c>
+      <c r="D8" s="40">
+        <v>1231717.5</v>
+      </c>
+      <c r="E8" s="40">
+        <v>1231717.5</v>
+      </c>
+      <c r="F8" s="40">
+        <v>1231717.5</v>
+      </c>
+      <c r="G8" s="40">
+        <v>1231717.5</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B9" s="11" t="s">
+        <v>247</v>
+      </c>
+      <c r="C9" s="40">
+        <v>654000</v>
+      </c>
+      <c r="D9" s="40">
+        <v>887860</v>
+      </c>
+      <c r="E9" s="40">
+        <v>1190521.4</v>
+      </c>
+      <c r="F9" s="40">
+        <v>1439089.0320000001</v>
+      </c>
+      <c r="G9" s="40">
+        <v>1554923.90296</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B10" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="C10" s="40">
+        <v>49824.605221179416</v>
+      </c>
+      <c r="D10" s="40">
+        <v>49824.605221179416</v>
+      </c>
+      <c r="E10" s="40">
+        <v>49824.605221179416</v>
+      </c>
+      <c r="F10" s="40">
+        <v>49824.605221179416</v>
+      </c>
+      <c r="G10" s="40">
+        <v>49824.605221179416</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B11" s="24" t="s">
+        <v>182</v>
+      </c>
+      <c r="C11" s="41">
+        <v>-184255.85522117943</v>
+      </c>
+      <c r="D11" s="42">
+        <v>353397.89477882057</v>
+      </c>
+      <c r="E11" s="42">
+        <v>1312536.4947788208</v>
+      </c>
+      <c r="F11" s="42">
+        <v>2038493.8627788206</v>
+      </c>
+      <c r="G11" s="42">
+        <v>2347933.9918188206</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B12" s="24" t="s">
+        <v>189</v>
+      </c>
+      <c r="C12" s="41">
+        <v>-184255.85522117943</v>
+      </c>
+      <c r="D12" s="42">
+        <v>169142.03955764114</v>
+      </c>
+      <c r="E12" s="42">
+        <v>1481678.534336462</v>
+      </c>
+      <c r="F12" s="42">
+        <v>3520172.3971152827</v>
+      </c>
+      <c r="G12" s="42">
+        <v>5868106.388934104</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B13" s="24" t="s">
+        <v>248</v>
+      </c>
+      <c r="C13" s="43">
+        <v>-0.11918231256221179</v>
+      </c>
+      <c r="D13" s="44">
+        <v>0.14008161359553692</v>
+      </c>
+      <c r="E13" s="44">
+        <v>0.34680983321323805</v>
+      </c>
+      <c r="F13" s="44">
+        <v>0.4283337510107048</v>
+      </c>
+      <c r="G13" s="44">
+        <v>0.4528844209202262</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B14" s="24" t="s">
+        <v>249</v>
+      </c>
+      <c r="C14" s="40">
+        <v>12883.333333333334</v>
+      </c>
+      <c r="D14" s="40">
+        <v>12614</v>
+      </c>
+      <c r="E14" s="40">
+        <v>12615.333333333334</v>
+      </c>
+      <c r="F14" s="40">
+        <v>12691</v>
+      </c>
+      <c r="G14" s="40">
+        <v>12961</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B15" s="24" t="s">
+        <v>250</v>
+      </c>
+      <c r="C15" s="43">
+        <v>0.6639270698576973</v>
+      </c>
+      <c r="D15" s="44">
+        <v>0.48823430315522437</v>
+      </c>
+      <c r="E15" s="44">
+        <v>0.3254551339639592</v>
+      </c>
+      <c r="F15" s="44">
+        <v>0.25881175636277676</v>
+      </c>
+      <c r="G15" s="44">
+        <v>0.23758149448345034</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B16" s="24" t="s">
+        <v>251</v>
+      </c>
+      <c r="C16" s="44">
+        <v>0.12690815006468306</v>
+      </c>
+      <c r="D16" s="44">
+        <v>0.10558030759473601</v>
+      </c>
+      <c r="E16" s="44">
+        <v>0.09437098240236748</v>
+      </c>
+      <c r="F16" s="44">
+        <v>0.09071556422661729</v>
+      </c>
+      <c r="G16" s="44">
+        <v>0.08997707948615076</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="24" t="s">
+        <v>252</v>
+      </c>
+      <c r="C17" s="43">
+        <v>-0.08695423673997413</v>
+      </c>
+      <c r="D17" s="44">
+        <v>0.15983133819565562</v>
+      </c>
+      <c r="E17" s="44">
+        <v>0.35997492469481585</v>
+      </c>
+      <c r="F17" s="44">
+        <v>0.4388030295484989</v>
+      </c>
+      <c r="G17" s="44">
+        <v>0.4624949072293804</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B18" s="24" t="s">
+        <v>253</v>
+      </c>
+      <c r="C18" s="45">
+        <v>-2.698089616630942</v>
+      </c>
+      <c r="D18" s="46">
+        <v>8.092838833544805</v>
+      </c>
+      <c r="E18" s="46">
+        <v>27.34313887590801</v>
+      </c>
+      <c r="F18" s="46">
+        <v>41.91339718056208</v>
+      </c>
+      <c r="G18" s="46">
+        <v>48.12398585791026</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B19" s="24" t="s">
+        <v>254</v>
+      </c>
+      <c r="C19" s="47" t="s">
         <v>240</v>
       </c>
-      <c r="C8" s="36">
-        <v>1026431.25</v>
-      </c>
-      <c r="D8" s="36">
-        <v>1231717.5</v>
-      </c>
-      <c r="E8" s="36">
-        <v>1231717.5</v>
-      </c>
-      <c r="F8" s="36">
-        <v>1231717.5</v>
-      </c>
-      <c r="G8" s="36">
-        <v>1231717.5</v>
-      </c>
-    </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="7" t="s">
-        <v>241</v>
-      </c>
-      <c r="C9" s="36">
-        <v>654000</v>
-      </c>
-      <c r="D9" s="36">
-        <v>887860</v>
-      </c>
-      <c r="E9" s="36">
-        <v>1190521.4</v>
-      </c>
-      <c r="F9" s="36">
-        <v>1439089.0320000001</v>
-      </c>
-      <c r="G9" s="36">
-        <v>1554923.90296</v>
-      </c>
-    </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="C10" s="36">
-        <v>49824.605221179416</v>
-      </c>
-      <c r="D10" s="36">
-        <v>49824.605221179416</v>
-      </c>
-      <c r="E10" s="36">
-        <v>49824.605221179416</v>
-      </c>
-      <c r="F10" s="36">
-        <v>49824.605221179416</v>
-      </c>
-      <c r="G10" s="36">
-        <v>49824.605221179416</v>
-      </c>
-    </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B11" s="20" t="s">
-        <v>176</v>
-      </c>
-      <c r="C11" s="37">
-        <v>-184255.85522117943</v>
-      </c>
-      <c r="D11" s="38">
-        <v>353397.89477882057</v>
-      </c>
-      <c r="E11" s="38">
-        <v>1312536.4947788208</v>
-      </c>
-      <c r="F11" s="38">
-        <v>2038493.8627788206</v>
-      </c>
-      <c r="G11" s="38">
-        <v>2347933.9918188206</v>
-      </c>
-    </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="20" t="s">
-        <v>183</v>
-      </c>
-      <c r="C12" s="37">
-        <v>-184255.85522117943</v>
-      </c>
-      <c r="D12" s="38">
-        <v>169142.03955764114</v>
-      </c>
-      <c r="E12" s="38">
-        <v>1481678.534336462</v>
-      </c>
-      <c r="F12" s="38">
-        <v>3520172.3971152827</v>
-      </c>
-      <c r="G12" s="38">
-        <v>5868106.388934104</v>
-      </c>
-    </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="20" t="s">
-        <v>242</v>
-      </c>
-      <c r="C13" s="39">
-        <v>-0.11918231256221179</v>
-      </c>
-      <c r="D13" s="40">
-        <v>0.14008161359553692</v>
-      </c>
-      <c r="E13" s="40">
-        <v>0.34680983321323805</v>
-      </c>
-      <c r="F13" s="40">
-        <v>0.4283337510107048</v>
-      </c>
-      <c r="G13" s="40">
-        <v>0.4528844209202262</v>
-      </c>
-    </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="20" t="s">
-        <v>243</v>
-      </c>
-      <c r="C14" s="36">
-        <v>12883.333333333334</v>
-      </c>
-      <c r="D14" s="36">
-        <v>12614</v>
-      </c>
-      <c r="E14" s="36">
-        <v>12615.333333333334</v>
-      </c>
-      <c r="F14" s="36">
-        <v>12691</v>
-      </c>
-      <c r="G14" s="36">
-        <v>12961</v>
-      </c>
-    </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="20" t="s">
-        <v>244</v>
-      </c>
-      <c r="C15" s="39">
-        <v>0.6639270698576973</v>
-      </c>
-      <c r="D15" s="40">
-        <v>0.48823430315522437</v>
-      </c>
-      <c r="E15" s="40">
-        <v>0.3254551339639592</v>
-      </c>
-      <c r="F15" s="40">
-        <v>0.25881175636277676</v>
-      </c>
-      <c r="G15" s="40">
-        <v>0.23758149448345034</v>
-      </c>
-    </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="20" t="s">
-        <v>245</v>
-      </c>
-      <c r="C16" s="40">
-        <v>0.12690815006468306</v>
-      </c>
-      <c r="D16" s="40">
-        <v>0.10558030759473601</v>
-      </c>
-      <c r="E16" s="40">
-        <v>0.09437098240236748</v>
-      </c>
-      <c r="F16" s="40">
-        <v>0.09071556422661729</v>
-      </c>
-      <c r="G16" s="40">
-        <v>0.08997707948615076</v>
-      </c>
-    </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="20" t="s">
-        <v>246</v>
-      </c>
-      <c r="C17" s="39">
-        <v>-0.08695423673997413</v>
-      </c>
-      <c r="D17" s="40">
-        <v>0.15983133819565562</v>
-      </c>
-      <c r="E17" s="40">
-        <v>0.35997492469481585</v>
-      </c>
-      <c r="F17" s="40">
-        <v>0.4388030295484989</v>
-      </c>
-      <c r="G17" s="40">
-        <v>0.4624949072293804</v>
-      </c>
-    </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B18" s="20" t="s">
-        <v>247</v>
-      </c>
-      <c r="C18" s="41">
-        <v>-2.698089616630942</v>
-      </c>
-      <c r="D18" s="42">
-        <v>8.092838833544805</v>
-      </c>
-      <c r="E18" s="42">
-        <v>27.34313887590801</v>
-      </c>
-      <c r="F18" s="42">
-        <v>41.91339718056208</v>
-      </c>
-      <c r="G18" s="42">
-        <v>48.12398585791026</v>
-      </c>
-    </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="20" t="s">
-        <v>248</v>
-      </c>
-      <c r="C19" s="43" t="s">
-        <v>234</v>
-      </c>
-      <c r="D19" s="43"/>
-      <c r="E19" s="43"/>
-      <c r="F19" s="43"/>
-      <c r="G19" s="43"/>
+      <c r="D19" s="47"/>
+      <c r="E19" s="47"/>
+      <c r="F19" s="47"/>
+      <c r="G19" s="47"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B20" s="20" t="s">
-        <v>249</v>
-      </c>
-      <c r="C20" s="44" t="s">
-        <v>250</v>
-      </c>
-      <c r="D20" s="44"/>
-      <c r="E20" s="44"/>
-      <c r="F20" s="44"/>
-      <c r="G20" s="44"/>
+      <c r="B20" s="24" t="s">
+        <v>255</v>
+      </c>
+      <c r="C20" s="48" t="s">
+        <v>256</v>
+      </c>
+      <c r="D20" s="48"/>
+      <c r="E20" s="48"/>
+      <c r="F20" s="48"/>
+      <c r="G20" s="48"/>
     </row>
     <row r="22" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B22" s="6" t="s">
-        <v>251</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>253</v>
-      </c>
-      <c r="E22" s="6"/>
-      <c r="F22" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="G22" s="6"/>
+      <c r="B22" s="10" t="s">
+        <v>257</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>258</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>259</v>
+      </c>
+      <c r="E22" s="10"/>
+      <c r="F22" s="10" t="s">
+        <v>260</v>
+      </c>
+      <c r="G22" s="10"/>
     </row>
     <row r="23" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B23" s="45" t="s">
-        <v>255</v>
-      </c>
-      <c r="C23" s="46" t="s">
-        <v>256</v>
-      </c>
-      <c r="D23" s="47" t="s">
-        <v>257</v>
-      </c>
-      <c r="E23" s="47"/>
-      <c r="F23" s="48" t="s">
-        <v>258</v>
-      </c>
-      <c r="G23" s="48"/>
+      <c r="B23" s="49" t="s">
+        <v>261</v>
+      </c>
+      <c r="C23" s="50" t="s">
+        <v>262</v>
+      </c>
+      <c r="D23" s="51" t="s">
+        <v>263</v>
+      </c>
+      <c r="E23" s="51"/>
+      <c r="F23" s="52" t="s">
+        <v>264</v>
+      </c>
+      <c r="G23" s="52"/>
     </row>
     <row r="24" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B24" s="45" t="s">
-        <v>259</v>
-      </c>
-      <c r="C24" s="49" t="s">
-        <v>260</v>
-      </c>
-      <c r="D24" s="47" t="s">
-        <v>261</v>
-      </c>
-      <c r="E24" s="47"/>
-      <c r="F24" s="48" t="s">
+      <c r="B24" s="49" t="s">
+        <v>265</v>
+      </c>
+      <c r="C24" s="53" t="s">
+        <v>266</v>
+      </c>
+      <c r="D24" s="51" t="s">
+        <v>267</v>
+      </c>
+      <c r="E24" s="51"/>
+      <c r="F24" s="52" t="s">
+        <v>268</v>
+      </c>
+      <c r="G24" s="52"/>
+    </row>
+    <row r="25" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B25" s="49" t="s">
+        <v>269</v>
+      </c>
+      <c r="C25" s="50" t="s">
         <v>262</v>
       </c>
-      <c r="G24" s="48"/>
-    </row>
-    <row r="25" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B25" s="45" t="s">
-        <v>263</v>
-      </c>
-      <c r="C25" s="46" t="s">
-        <v>256</v>
-      </c>
-      <c r="D25" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="E25" s="47"/>
-      <c r="F25" s="48" t="s">
-        <v>265</v>
-      </c>
-      <c r="G25" s="48"/>
+      <c r="D25" s="51" t="s">
+        <v>270</v>
+      </c>
+      <c r="E25" s="51"/>
+      <c r="F25" s="52" t="s">
+        <v>271</v>
+      </c>
+      <c r="G25" s="52"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B26" s="45" t="s">
-        <v>266</v>
-      </c>
-      <c r="C26" s="46" t="s">
-        <v>256</v>
-      </c>
-      <c r="D26" s="47" t="s">
-        <v>267</v>
-      </c>
-      <c r="E26" s="47"/>
-      <c r="F26" s="48" t="s">
-        <v>268</v>
-      </c>
-      <c r="G26" s="48"/>
+      <c r="B26" s="49" t="s">
+        <v>272</v>
+      </c>
+      <c r="C26" s="50" t="s">
+        <v>262</v>
+      </c>
+      <c r="D26" s="51" t="s">
+        <v>273</v>
+      </c>
+      <c r="E26" s="51"/>
+      <c r="F26" s="52" t="s">
+        <v>274</v>
+      </c>
+      <c r="G26" s="52"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B27" s="45" t="s">
-        <v>269</v>
-      </c>
-      <c r="C27" s="46" t="s">
-        <v>256</v>
-      </c>
-      <c r="D27" s="47" t="s">
-        <v>270</v>
-      </c>
-      <c r="E27" s="47"/>
-      <c r="F27" s="48" t="s">
-        <v>271</v>
-      </c>
-      <c r="G27" s="48"/>
+      <c r="B27" s="49" t="s">
+        <v>275</v>
+      </c>
+      <c r="C27" s="50" t="s">
+        <v>262</v>
+      </c>
+      <c r="D27" s="51" t="s">
+        <v>276</v>
+      </c>
+      <c r="E27" s="51"/>
+      <c r="F27" s="52" t="s">
+        <v>277</v>
+      </c>
+      <c r="G27" s="52"/>
     </row>
     <row r="28" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B28" s="45" t="s">
-        <v>272</v>
-      </c>
-      <c r="C28" s="46" t="s">
-        <v>256</v>
-      </c>
-      <c r="D28" s="47" t="s">
-        <v>273</v>
-      </c>
-      <c r="E28" s="47"/>
-      <c r="F28" s="48" t="s">
-        <v>274</v>
-      </c>
-      <c r="G28" s="48"/>
+      <c r="B28" s="49" t="s">
+        <v>278</v>
+      </c>
+      <c r="C28" s="50" t="s">
+        <v>262</v>
+      </c>
+      <c r="D28" s="51" t="s">
+        <v>279</v>
+      </c>
+      <c r="E28" s="51"/>
+      <c r="F28" s="52" t="s">
+        <v>280</v>
+      </c>
+      <c r="G28" s="52"/>
     </row>
     <row r="29" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B29" s="45" t="s">
-        <v>275</v>
-      </c>
-      <c r="C29" s="46" t="s">
-        <v>256</v>
-      </c>
-      <c r="D29" s="47" t="s">
-        <v>276</v>
-      </c>
-      <c r="E29" s="47"/>
-      <c r="F29" s="48" t="s">
-        <v>277</v>
-      </c>
-      <c r="G29" s="48"/>
+      <c r="B29" s="49" t="s">
+        <v>281</v>
+      </c>
+      <c r="C29" s="50" t="s">
+        <v>262</v>
+      </c>
+      <c r="D29" s="51" t="s">
+        <v>282</v>
+      </c>
+      <c r="E29" s="51"/>
+      <c r="F29" s="52" t="s">
+        <v>283</v>
+      </c>
+      <c r="G29" s="52"/>
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B31" s="45" t="s">
-        <v>278</v>
-      </c>
-      <c r="C31" s="20" t="s">
-        <v>279</v>
-      </c>
-      <c r="D31" s="20"/>
-      <c r="E31" s="20"/>
+      <c r="B31" s="49" t="s">
+        <v>284</v>
+      </c>
+      <c r="C31" s="24" t="s">
+        <v>285</v>
+      </c>
+      <c r="D31" s="24"/>
+      <c r="E31" s="24"/>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B33" s="50" t="s">
-        <v>137</v>
-      </c>
-      <c r="C33" s="50"/>
-      <c r="D33" s="50"/>
-      <c r="E33" s="50"/>
-      <c r="F33" s="50"/>
-      <c r="G33" s="50"/>
+      <c r="B33" s="54" t="s">
+        <v>143</v>
+      </c>
+      <c r="C33" s="54"/>
+      <c r="D33" s="54"/>
+      <c r="E33" s="54"/>
+      <c r="F33" s="54"/>
+      <c r="G33" s="54"/>
     </row>
   </sheetData>
   <mergeCells count="22">
@@ -6911,6 +7134,83 @@
     <mergeCell ref="C31:E31"/>
     <mergeCell ref="B33:G33"/>
   </mergeCells>
+  <conditionalFormatting sqref="C11:G11">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>C11&gt;=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>C11&gt;=-1</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="3">
+      <formula>C11&lt;-1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C12:G12">
+    <cfRule type="expression" dxfId="3" priority="1">
+      <formula>C12&gt;=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="4" priority="2">
+      <formula>C12&gt;=-1</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="5" priority="3">
+      <formula>C12&lt;-1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C13:G13">
+    <cfRule type="expression" dxfId="6" priority="1">
+      <formula>C13&gt;=0.05</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="7" priority="2">
+      <formula>C13&gt;=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="8" priority="3">
+      <formula>C13&lt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C15:G15">
+    <cfRule type="expression" dxfId="9" priority="1">
+      <formula>C15&lt;=0.55</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="10" priority="2">
+      <formula>C15&lt;=0.65</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="11" priority="3">
+      <formula>C15&gt;0.65</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C16:G16">
+    <cfRule type="expression" dxfId="12" priority="1">
+      <formula>C16&lt;=0.15</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="13" priority="2">
+      <formula>C16&lt;=0.25</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="14" priority="3">
+      <formula>C16&gt;0.25</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C17:G17">
+    <cfRule type="expression" dxfId="15" priority="1">
+      <formula>C17&gt;=0.10</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="16" priority="2">
+      <formula>C17&gt;=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="17" priority="3">
+      <formula>C17&lt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C18:G18">
+    <cfRule type="expression" dxfId="18" priority="1">
+      <formula>C18&gt;=1.25</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="19" priority="2">
+      <formula>C18&gt;=1.0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="20" priority="3">
+      <formula>C18&lt;1.0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>

--- a/artifacts/api-server/qa-output/Formula_Export_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Formula_Export_Charter_Public_Funding.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="286">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -1073,7 +1073,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1085,6 +1085,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1871,1073 +1872,1076 @@
       <c r="F1" s="8"/>
       <c r="G1" s="8"/>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="10" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="11"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="11" t="s">
+      <c r="A5" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="12"/>
-      <c r="D5" s="12"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="13"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="13" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="13" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="13" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="11" t="s">
+      <c r="A9" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="13" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="13"/>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="11" t="s">
+      <c r="A11" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="13" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="11" t="s">
+      <c r="A12" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="B12" s="13">
+      <c r="B12" s="14">
         <v>400</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="11" t="s">
+      <c r="A13" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="B13" s="12" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="11" t="s">
+      <c r="A14" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="B14" s="12" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="10" t="s">
+      <c r="A16" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="B16" s="14" t="s">
+      <c r="B16" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="C16" s="14" t="s">
+      <c r="C16" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="D16" s="14" t="s">
+      <c r="D16" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="E16" s="14" t="s">
+      <c r="E16" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="F16" s="14" t="s">
+      <c r="F16" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="G16" s="10"/>
+      <c r="G16" s="11"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="11" t="s">
+      <c r="A17" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="B17" s="15">
+      <c r="B17" s="16">
         <v>120</v>
       </c>
-      <c r="C17" s="15">
+      <c r="C17" s="16">
         <v>200</v>
       </c>
-      <c r="D17" s="15">
+      <c r="D17" s="16">
         <v>300</v>
       </c>
-      <c r="E17" s="15">
+      <c r="E17" s="16">
         <v>375</v>
       </c>
-      <c r="F17" s="15">
+      <c r="F17" s="16">
         <v>400</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="10" t="s">
+      <c r="A19" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="B19" s="10" t="s">
+      <c r="B19" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="C19" s="10" t="s">
+      <c r="C19" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="D19" s="10" t="s">
+      <c r="D19" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="E19" s="10" t="s">
+      <c r="E19" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="F19" s="10" t="s">
+      <c r="F19" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="G19" s="10" t="s">
+      <c r="G19" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="H19" s="10" t="s">
+      <c r="H19" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="I19" s="10"/>
-      <c r="J19" s="10"/>
+      <c r="I19" s="11"/>
+      <c r="J19" s="11"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="11" t="s">
+      <c r="A20" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="B20" s="11" t="s">
+      <c r="B20" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="C20" s="11" t="s">
+      <c r="C20" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="D20" s="16">
+      <c r="D20" s="17">
         <v>9500</v>
       </c>
-      <c r="E20" s="17">
-        <v>0</v>
-      </c>
-      <c r="F20" s="13">
+      <c r="E20" s="18">
+        <v>0</v>
+      </c>
+      <c r="F20" s="14">
         <v>12</v>
       </c>
-      <c r="G20" s="17">
+      <c r="G20" s="18">
         <v>1</v>
       </c>
-      <c r="H20" s="11" t="s">
+      <c r="H20" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="11" t="s">
+      <c r="A21" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="B21" s="11" t="s">
+      <c r="B21" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="C21" s="11" t="s">
+      <c r="C21" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="D21" s="16">
+      <c r="D21" s="17">
         <v>800</v>
       </c>
-      <c r="E21" s="17">
-        <v>0</v>
-      </c>
-      <c r="F21" s="13">
+      <c r="E21" s="18">
+        <v>0</v>
+      </c>
+      <c r="F21" s="14">
         <v>12</v>
       </c>
-      <c r="G21" s="17">
+      <c r="G21" s="18">
         <v>1</v>
       </c>
-      <c r="H21" s="11" t="s">
+      <c r="H21" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="11" t="s">
+      <c r="A22" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="B22" s="11" t="s">
+      <c r="B22" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="C22" s="11" t="s">
+      <c r="C22" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="D22" s="16">
+      <c r="D22" s="17">
         <v>1200</v>
       </c>
-      <c r="E22" s="17">
-        <v>0</v>
-      </c>
-      <c r="F22" s="13">
+      <c r="E22" s="18">
+        <v>0</v>
+      </c>
+      <c r="F22" s="14">
         <v>12</v>
       </c>
-      <c r="G22" s="17">
+      <c r="G22" s="18">
         <v>1</v>
       </c>
-      <c r="H22" s="11" t="s">
+      <c r="H22" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="11" t="s">
+      <c r="A23" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="B23" s="11" t="s">
+      <c r="B23" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="C23" s="11" t="s">
+      <c r="C23" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="D23" s="16">
+      <c r="D23" s="17">
         <v>100000</v>
       </c>
-      <c r="E23" s="17">
-        <v>0</v>
-      </c>
-      <c r="F23" s="13">
+      <c r="E23" s="18">
+        <v>0</v>
+      </c>
+      <c r="F23" s="14">
         <v>12</v>
       </c>
-      <c r="G23" s="17">
+      <c r="G23" s="18">
         <v>1</v>
       </c>
-      <c r="H23" s="11" t="s">
+      <c r="H23" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="11" t="s">
+      <c r="A24" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="B24" s="11" t="s">
+      <c r="B24" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="C24" s="11" t="s">
+      <c r="C24" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="D24" s="16">
+      <c r="D24" s="17">
         <v>30000</v>
       </c>
-      <c r="E24" s="17">
-        <v>0</v>
-      </c>
-      <c r="F24" s="13">
+      <c r="E24" s="18">
+        <v>0</v>
+      </c>
+      <c r="F24" s="14">
         <v>12</v>
       </c>
-      <c r="G24" s="17">
+      <c r="G24" s="18">
         <v>1</v>
       </c>
-      <c r="H24" s="11" t="s">
+      <c r="H24" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="11" t="s">
+      <c r="A25" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="B25" s="11" t="s">
+      <c r="B25" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="C25" s="11" t="s">
+      <c r="C25" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="D25" s="16">
+      <c r="D25" s="17">
         <v>300</v>
       </c>
-      <c r="E25" s="17">
-        <v>0</v>
-      </c>
-      <c r="F25" s="13">
+      <c r="E25" s="18">
+        <v>0</v>
+      </c>
+      <c r="F25" s="14">
         <v>12</v>
       </c>
-      <c r="G25" s="17">
+      <c r="G25" s="18">
         <v>1</v>
       </c>
-      <c r="H25" s="11" t="s">
+      <c r="H25" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="28" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" s="10" t="s">
+      <c r="A28" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="B28" s="10" t="s">
+      <c r="B28" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="C28" s="10" t="s">
+      <c r="C28" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="D28" s="10" t="s">
+      <c r="D28" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="E28" s="10" t="s">
+      <c r="E28" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="F28" s="10" t="s">
+      <c r="F28" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="G28" s="10" t="s">
+      <c r="G28" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="H28" s="10" t="s">
+      <c r="H28" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="I28" s="10" t="s">
+      <c r="I28" s="11" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" s="11" t="s">
+      <c r="A29" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="B29" s="11" t="s">
+      <c r="B29" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="C29" s="11" t="s">
+      <c r="C29" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="D29" s="18">
+      <c r="D29" s="19">
         <v>1</v>
       </c>
-      <c r="E29" s="16">
+      <c r="E29" s="17">
         <v>110000</v>
       </c>
-      <c r="F29" s="17">
+      <c r="F29" s="18">
         <v>0.28</v>
       </c>
-      <c r="G29" s="17">
+      <c r="G29" s="18">
         <v>0.0765</v>
       </c>
-      <c r="H29" s="11" t="s">
+      <c r="H29" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="I29" s="11" t="s">
+      <c r="I29" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30" s="11" t="s">
+      <c r="A30" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="B30" s="11" t="s">
+      <c r="B30" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="C30" s="11" t="s">
+      <c r="C30" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="D30" s="18">
+      <c r="D30" s="19">
         <v>1</v>
       </c>
-      <c r="E30" s="16">
+      <c r="E30" s="17">
         <v>90000</v>
       </c>
-      <c r="F30" s="17">
+      <c r="F30" s="18">
         <v>0.28</v>
       </c>
-      <c r="G30" s="17">
+      <c r="G30" s="18">
         <v>0.0765</v>
       </c>
-      <c r="H30" s="11" t="s">
+      <c r="H30" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="I30" s="11" t="s">
+      <c r="I30" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" s="11" t="s">
+      <c r="A31" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="B31" s="11" t="s">
+      <c r="B31" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="C31" s="11" t="s">
+      <c r="C31" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="D31" s="18">
+      <c r="D31" s="19">
         <v>1</v>
       </c>
-      <c r="E31" s="16">
+      <c r="E31" s="17">
         <v>72000</v>
       </c>
-      <c r="F31" s="17">
+      <c r="F31" s="18">
         <v>0.28</v>
       </c>
-      <c r="G31" s="17">
+      <c r="G31" s="18">
         <v>0.0765</v>
       </c>
-      <c r="H31" s="11" t="s">
+      <c r="H31" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="I31" s="11" t="s">
+      <c r="I31" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32" s="11" t="s">
+      <c r="A32" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="B32" s="11" t="s">
+      <c r="B32" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="C32" s="11" t="s">
+      <c r="C32" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="D32" s="18">
+      <c r="D32" s="19">
         <v>6</v>
       </c>
-      <c r="E32" s="16">
+      <c r="E32" s="17">
         <v>52000</v>
       </c>
-      <c r="F32" s="17">
+      <c r="F32" s="18">
         <v>0.28</v>
       </c>
-      <c r="G32" s="17">
+      <c r="G32" s="18">
         <v>0.0765</v>
       </c>
-      <c r="H32" s="11" t="s">
+      <c r="H32" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="I32" s="11" t="s">
+      <c r="I32" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A33" s="11" t="s">
+      <c r="A33" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="B33" s="11" t="s">
+      <c r="B33" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="C33" s="11" t="s">
+      <c r="C33" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="D33" s="18">
+      <c r="D33" s="19">
         <v>1</v>
       </c>
-      <c r="E33" s="16">
+      <c r="E33" s="17">
         <v>55000</v>
       </c>
-      <c r="F33" s="17">
+      <c r="F33" s="18">
         <v>0.28</v>
       </c>
-      <c r="G33" s="17">
+      <c r="G33" s="18">
         <v>0.0765</v>
       </c>
-      <c r="H33" s="11" t="s">
+      <c r="H33" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="I33" s="11" t="s">
+      <c r="I33" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A34" s="11" t="s">
+      <c r="A34" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="B34" s="11" t="s">
+      <c r="B34" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="C34" s="11" t="s">
+      <c r="C34" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="D34" s="18">
+      <c r="D34" s="19">
         <v>3</v>
       </c>
-      <c r="E34" s="16">
+      <c r="E34" s="17">
         <v>30000</v>
       </c>
-      <c r="F34" s="17">
+      <c r="F34" s="18">
         <v>0.2</v>
       </c>
-      <c r="G34" s="17">
+      <c r="G34" s="18">
         <v>0.0765</v>
       </c>
-      <c r="H34" s="11" t="s">
+      <c r="H34" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="I34" s="11" t="s">
+      <c r="I34" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A35" s="11" t="s">
+      <c r="A35" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="B35" s="11" t="s">
+      <c r="B35" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="C35" s="11" t="s">
+      <c r="C35" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="D35" s="18">
+      <c r="D35" s="19">
         <v>1</v>
       </c>
-      <c r="E35" s="16">
+      <c r="E35" s="17">
         <v>55000</v>
       </c>
-      <c r="F35" s="17">
+      <c r="F35" s="18">
         <v>0.28</v>
       </c>
-      <c r="G35" s="17">
+      <c r="G35" s="18">
         <v>0.0765</v>
       </c>
-      <c r="H35" s="11" t="s">
+      <c r="H35" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="I35" s="11" t="s">
+      <c r="I35" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A36" s="11" t="s">
+      <c r="A36" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="B36" s="11" t="s">
+      <c r="B36" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="C36" s="11" t="s">
+      <c r="C36" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="D36" s="18">
+      <c r="D36" s="19">
         <v>2</v>
       </c>
-      <c r="E36" s="16">
+      <c r="E36" s="17">
         <v>38000</v>
       </c>
-      <c r="F36" s="17">
+      <c r="F36" s="18">
         <v>0.25</v>
       </c>
-      <c r="G36" s="17">
+      <c r="G36" s="18">
         <v>0.0765</v>
       </c>
-      <c r="H36" s="11" t="s">
+      <c r="H36" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="I36" s="11" t="s">
+      <c r="I36" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A37" s="11" t="s">
+      <c r="A37" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="B37" s="11" t="s">
+      <c r="B37" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="C37" s="11" t="s">
+      <c r="C37" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="D37" s="18">
+      <c r="D37" s="19">
         <v>1</v>
       </c>
-      <c r="E37" s="16">
+      <c r="E37" s="17">
         <v>55000</v>
       </c>
-      <c r="F37" s="17">
+      <c r="F37" s="18">
         <v>0.28</v>
       </c>
-      <c r="G37" s="17">
+      <c r="G37" s="18">
         <v>0.0765</v>
       </c>
-      <c r="H37" s="11" t="s">
+      <c r="H37" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="I37" s="11" t="s">
+      <c r="I37" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="39" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="10" t="s">
+      <c r="A39" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="B39" s="10" t="s">
+      <c r="B39" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="C39" s="10" t="s">
+      <c r="C39" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="D39" s="10"/>
+      <c r="D39" s="11"/>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="11" t="s">
+      <c r="A40" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="B40" s="12" t="s">
+      <c r="B40" s="13" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="11" t="s">
+      <c r="A41" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="B41" s="16">
+      <c r="B41" s="17">
         <v>18000</v>
       </c>
-      <c r="C41" s="11" t="s">
+      <c r="C41" s="12" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" s="11" t="s">
+      <c r="A42" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="B42" s="17">
+      <c r="B42" s="18">
         <v>0.03</v>
       </c>
     </row>
     <row r="44" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="10" t="s">
+      <c r="A44" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="B44" s="10" t="s">
+      <c r="B44" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="C44" s="10" t="s">
+      <c r="C44" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="D44" s="10" t="s">
+      <c r="D44" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="E44" s="10" t="s">
+      <c r="E44" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="F44" s="10" t="s">
+      <c r="F44" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="G44" s="10"/>
+      <c r="G44" s="11"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="11" t="s">
+      <c r="A45" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="B45" s="11" t="s">
+      <c r="B45" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="C45" s="11" t="s">
+      <c r="C45" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="D45" s="16">
+      <c r="D45" s="17">
         <v>18000</v>
       </c>
-      <c r="E45" s="17">
+      <c r="E45" s="18">
         <v>0.03</v>
       </c>
-      <c r="F45" s="11" t="s">
+      <c r="F45" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="11" t="s">
+      <c r="A46" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="B46" s="11" t="s">
+      <c r="B46" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="C46" s="11" t="s">
+      <c r="C46" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="D46" s="16">
+      <c r="D46" s="17">
         <v>2500</v>
       </c>
-      <c r="E46" s="17">
-        <v>0</v>
-      </c>
-      <c r="F46" s="11" t="s">
+      <c r="E46" s="18">
+        <v>0</v>
+      </c>
+      <c r="F46" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="11" t="s">
+      <c r="A47" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="B47" s="11" t="s">
+      <c r="B47" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="C47" s="11" t="s">
+      <c r="C47" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="D47" s="16">
+      <c r="D47" s="17">
         <v>18000</v>
       </c>
-      <c r="E47" s="17">
-        <v>0</v>
-      </c>
-      <c r="F47" s="11" t="s">
+      <c r="E47" s="18">
+        <v>0</v>
+      </c>
+      <c r="F47" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="11" t="s">
+      <c r="A48" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="B48" s="11" t="s">
+      <c r="B48" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="C48" s="11" t="s">
+      <c r="C48" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="D48" s="16">
+      <c r="D48" s="17">
         <v>1500</v>
       </c>
-      <c r="E48" s="17">
-        <v>0</v>
-      </c>
-      <c r="F48" s="11" t="s">
+      <c r="E48" s="18">
+        <v>0</v>
+      </c>
+      <c r="F48" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="11" t="s">
+      <c r="A49" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="B49" s="11" t="s">
+      <c r="B49" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="C49" s="11" t="s">
+      <c r="C49" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="D49" s="16">
+      <c r="D49" s="17">
         <v>700</v>
       </c>
-      <c r="E49" s="17">
-        <v>0</v>
-      </c>
-      <c r="F49" s="11" t="s">
+      <c r="E49" s="18">
+        <v>0</v>
+      </c>
+      <c r="F49" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="11" t="s">
+      <c r="A50" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="B50" s="11" t="s">
+      <c r="B50" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="C50" s="11" t="s">
+      <c r="C50" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="D50" s="16">
+      <c r="D50" s="17">
         <v>500</v>
       </c>
-      <c r="E50" s="17">
-        <v>0</v>
-      </c>
-      <c r="F50" s="11" t="s">
+      <c r="E50" s="18">
+        <v>0</v>
+      </c>
+      <c r="F50" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="11" t="s">
+      <c r="A51" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="B51" s="11" t="s">
+      <c r="B51" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="C51" s="11" t="s">
+      <c r="C51" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="D51" s="16">
+      <c r="D51" s="17">
         <v>25000</v>
       </c>
-      <c r="E51" s="17">
-        <v>0</v>
-      </c>
-      <c r="F51" s="11" t="s">
+      <c r="E51" s="18">
+        <v>0</v>
+      </c>
+      <c r="F51" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="11" t="s">
+      <c r="A52" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="B52" s="11" t="s">
+      <c r="B52" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="C52" s="11" t="s">
+      <c r="C52" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="D52" s="16">
+      <c r="D52" s="17">
         <v>15000</v>
       </c>
-      <c r="E52" s="17">
-        <v>0</v>
-      </c>
-      <c r="F52" s="11" t="s">
+      <c r="E52" s="18">
+        <v>0</v>
+      </c>
+      <c r="F52" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="11" t="s">
+      <c r="A53" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="B53" s="11" t="s">
+      <c r="B53" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="C53" s="11" t="s">
+      <c r="C53" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="D53" s="16">
+      <c r="D53" s="17">
         <v>20000</v>
       </c>
-      <c r="E53" s="17">
-        <v>0</v>
-      </c>
-      <c r="F53" s="11" t="s">
+      <c r="E53" s="18">
+        <v>0</v>
+      </c>
+      <c r="F53" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="11" t="s">
+      <c r="A54" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="B54" s="11" t="s">
+      <c r="B54" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="C54" s="11" t="s">
+      <c r="C54" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="D54" s="16">
+      <c r="D54" s="17">
         <v>800</v>
       </c>
-      <c r="E54" s="17">
-        <v>0</v>
-      </c>
-      <c r="F54" s="11" t="s">
+      <c r="E54" s="18">
+        <v>0</v>
+      </c>
+      <c r="F54" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="11" t="s">
+      <c r="A55" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="B55" s="11" t="s">
+      <c r="B55" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="C55" s="11" t="s">
+      <c r="C55" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="D55" s="16">
+      <c r="D55" s="17">
         <v>600</v>
       </c>
-      <c r="E55" s="17">
-        <v>0</v>
-      </c>
-      <c r="F55" s="11" t="s">
+      <c r="E55" s="18">
+        <v>0</v>
+      </c>
+      <c r="F55" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="57" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" s="10" t="s">
+      <c r="A57" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="B57" s="10" t="s">
+      <c r="B57" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="C57" s="10" t="s">
+      <c r="C57" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="D57" s="10" t="s">
+      <c r="D57" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="E57" s="10" t="s">
+      <c r="E57" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="F57" s="10" t="s">
+      <c r="F57" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="G57" s="10" t="s">
+      <c r="G57" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="H57" s="10" t="s">
+      <c r="H57" s="11" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A58" s="11" t="s">
+      <c r="A58" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="B58" s="11" t="s">
+      <c r="B58" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="C58" s="19">
-        <v>0</v>
-      </c>
-      <c r="D58" s="16">
+      <c r="C58" s="20">
+        <v>0</v>
+      </c>
+      <c r="D58" s="17">
         <v>500000</v>
       </c>
-      <c r="E58" s="20">
+      <c r="E58" s="21">
         <v>0.0575</v>
       </c>
-      <c r="F58" s="13">
+      <c r="F58" s="14">
         <v>15</v>
       </c>
-      <c r="G58" s="19">
+      <c r="G58" s="20">
         <v>49825</v>
       </c>
-      <c r="H58" s="11" t="s">
+      <c r="H58" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A59" s="11" t="s">
+      <c r="A59" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="B59" s="11" t="s">
+      <c r="B59" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="C59" s="16">
+      <c r="C59" s="17">
         <v>75000</v>
       </c>
-      <c r="D59" s="11">
-        <v>0</v>
-      </c>
-      <c r="E59" s="11" t="s">
+      <c r="D59" s="12">
+        <v>0</v>
+      </c>
+      <c r="E59" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="F59" s="11" t="s">
+      <c r="F59" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="G59" s="11" t="s">
+      <c r="G59" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H59" s="11" t="s">
+      <c r="H59" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A60" s="11" t="s">
+      <c r="A60" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="B60" s="11" t="s">
+      <c r="B60" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="C60" s="16">
+      <c r="C60" s="17">
         <v>40000</v>
       </c>
-      <c r="D60" s="11">
-        <v>0</v>
-      </c>
-      <c r="E60" s="11" t="s">
+      <c r="D60" s="12">
+        <v>0</v>
+      </c>
+      <c r="E60" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="F60" s="11" t="s">
+      <c r="F60" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="G60" s="11" t="s">
+      <c r="G60" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H60" s="11" t="s">
+      <c r="H60" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="62" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" s="10" t="s">
+      <c r="A62" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="B62" s="10"/>
-      <c r="C62" s="10"/>
+      <c r="B62" s="11"/>
+      <c r="C62" s="11"/>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A63" s="11" t="s">
+      <c r="A63" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="B63" s="17">
+      <c r="B63" s="18">
         <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A64" s="11" t="s">
+      <c r="A64" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="B64" s="17">
+      <c r="B64" s="18">
         <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" s="11" t="s">
+      <c r="A65" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="B65" s="18">
+      <c r="B65" s="19">
         <v>0.8333333333333334</v>
       </c>
-      <c r="C65" s="21" t="s">
+      <c r="C65" s="22" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A66" s="11" t="s">
+      <c r="A66" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="B66" s="17">
+      <c r="B66" s="18">
         <v>0.03</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A67" s="11" t="s">
+      <c r="A67" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="B67" s="17">
+      <c r="B67" s="18">
         <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A68" s="11" t="s">
+      <c r="A68" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="B68" s="16">
+      <c r="B68" s="17">
         <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A70" s="22" t="s">
+      <c r="A70" s="23" t="s">
         <v>143</v>
       </c>
-      <c r="B70" s="22"/>
-      <c r="C70" s="22"/>
-      <c r="D70" s="22"/>
-      <c r="E70" s="22"/>
-      <c r="F70" s="22"/>
-      <c r="G70" s="22"/>
+      <c r="B70" s="23"/>
+      <c r="C70" s="23"/>
+      <c r="D70" s="23"/>
+      <c r="E70" s="23"/>
+      <c r="F70" s="23"/>
+      <c r="G70" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -2978,1021 +2982,1021 @@
       <c r="F1" s="8"/>
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="23" t="s">
+      <c r="B2" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="C2" s="23" t="s">
+      <c r="C2" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="D2" s="23" t="s">
+      <c r="D2" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="E2" s="23" t="s">
+      <c r="E2" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="F2" s="23" t="s">
+      <c r="F2" s="24" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="24" t="s">
+      <c r="A3" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="B3" s="25">
+      <c r="B3" s="26">
         <f>Assumptions!B17</f>
         <v>120</v>
       </c>
-      <c r="C3" s="25">
+      <c r="C3" s="26">
         <f>Assumptions!C17</f>
         <v>200</v>
       </c>
-      <c r="D3" s="25">
+      <c r="D3" s="26">
         <f>Assumptions!D17</f>
         <v>300</v>
       </c>
-      <c r="E3" s="25">
+      <c r="E3" s="26">
         <f>Assumptions!E17</f>
         <v>375</v>
       </c>
-      <c r="F3" s="25">
+      <c r="F3" s="26">
         <f>Assumptions!F17</f>
         <v>400</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="11" t="s">
         <v>145</v>
       </c>
-      <c r="B5" s="10"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="B6" s="19">
+      <c r="B6" s="20">
         <v>950000</v>
       </c>
-      <c r="C6" s="19">
+      <c r="C6" s="20">
         <v>1938000</v>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="20">
         <v>2965200</v>
       </c>
-      <c r="E6" s="19">
+      <c r="E6" s="20">
         <v>3780375</v>
       </c>
-      <c r="F6" s="19">
+      <c r="F6" s="20">
         <v>4113200</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="B7" s="19">
+      <c r="B7" s="20">
         <v>80000</v>
       </c>
-      <c r="C7" s="19">
+      <c r="C7" s="20">
         <v>163200</v>
       </c>
-      <c r="D7" s="19">
+      <c r="D7" s="20">
         <v>249600</v>
       </c>
-      <c r="E7" s="19">
+      <c r="E7" s="20">
         <v>318375</v>
       </c>
-      <c r="F7" s="19">
+      <c r="F7" s="20">
         <v>346400</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="B8" s="19">
+      <c r="B8" s="20">
         <v>120000</v>
       </c>
-      <c r="C8" s="19">
+      <c r="C8" s="20">
         <v>244800</v>
       </c>
-      <c r="D8" s="19">
+      <c r="D8" s="20">
         <v>374400</v>
       </c>
-      <c r="E8" s="19">
+      <c r="E8" s="20">
         <v>477375</v>
       </c>
-      <c r="F8" s="19">
+      <c r="F8" s="20">
         <v>519600</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="11" t="s">
+      <c r="A9" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="B9" s="19">
+      <c r="B9" s="20">
         <v>83333</v>
       </c>
-      <c r="C9" s="19">
+      <c r="C9" s="20">
         <v>75000</v>
       </c>
-      <c r="D9" s="19">
+      <c r="D9" s="20">
         <v>50000</v>
       </c>
-      <c r="E9" s="19">
-        <v>0</v>
-      </c>
-      <c r="F9" s="19">
+      <c r="E9" s="20">
+        <v>0</v>
+      </c>
+      <c r="F9" s="20">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="B10" s="19">
+      <c r="B10" s="20">
         <v>25000</v>
       </c>
-      <c r="C10" s="19">
+      <c r="C10" s="20">
         <v>40000</v>
       </c>
-      <c r="D10" s="19">
+      <c r="D10" s="20">
         <v>50000</v>
       </c>
-      <c r="E10" s="19">
+      <c r="E10" s="20">
         <v>60000</v>
       </c>
-      <c r="F10" s="19">
+      <c r="F10" s="20">
         <v>70000</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="11" t="s">
+      <c r="A11" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="B11" s="19">
+      <c r="B11" s="20">
         <v>30000</v>
       </c>
-      <c r="C11" s="19">
+      <c r="C11" s="20">
         <v>61800</v>
       </c>
-      <c r="D11" s="19">
+      <c r="D11" s="20">
         <v>95400</v>
       </c>
-      <c r="E11" s="19">
+      <c r="E11" s="20">
         <v>123000</v>
       </c>
-      <c r="F11" s="19">
+      <c r="F11" s="20">
         <v>135200</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="10" t="s">
+      <c r="A12" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="B12" s="26">
+      <c r="B12" s="27">
         <f>SUM(B6:B11)</f>
         <v>1288333</v>
       </c>
-      <c r="C12" s="26">
+      <c r="C12" s="27">
         <f>SUM(C6:C11)</f>
         <v>2522800</v>
       </c>
-      <c r="D12" s="26">
+      <c r="D12" s="27">
         <f>SUM(D6:D11)</f>
         <v>3784600</v>
       </c>
-      <c r="E12" s="26">
+      <c r="E12" s="27">
         <f>SUM(E6:E11)</f>
         <v>4759125</v>
       </c>
-      <c r="F12" s="26">
+      <c r="F12" s="27">
         <f>SUM(F6:F11)</f>
         <v>5184400</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="10" t="s">
+      <c r="A14" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="11" t="s">
+      <c r="A15" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="B15" s="19">
+      <c r="B15" s="20">
         <v>124346</v>
       </c>
-      <c r="C15" s="19">
+      <c r="C15" s="20">
         <v>149215</v>
       </c>
-      <c r="D15" s="19">
+      <c r="D15" s="20">
         <v>149215</v>
       </c>
-      <c r="E15" s="19">
+      <c r="E15" s="20">
         <v>149215</v>
       </c>
-      <c r="F15" s="19">
+      <c r="F15" s="20">
         <v>149215</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="11" t="s">
+      <c r="A16" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="B16" s="19">
+      <c r="B16" s="20">
         <v>101738</v>
       </c>
-      <c r="C16" s="19">
+      <c r="C16" s="20">
         <v>122085</v>
       </c>
-      <c r="D16" s="19">
+      <c r="D16" s="20">
         <v>122085</v>
       </c>
-      <c r="E16" s="19">
+      <c r="E16" s="20">
         <v>122085</v>
       </c>
-      <c r="F16" s="19">
+      <c r="F16" s="20">
         <v>122085</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="11" t="s">
+      <c r="A17" s="12" t="s">
         <v>150</v>
       </c>
-      <c r="B17" s="19">
+      <c r="B17" s="20">
         <v>81390</v>
       </c>
-      <c r="C17" s="19">
+      <c r="C17" s="20">
         <v>97668</v>
       </c>
-      <c r="D17" s="19">
+      <c r="D17" s="20">
         <v>97668</v>
       </c>
-      <c r="E17" s="19">
+      <c r="E17" s="20">
         <v>97668</v>
       </c>
-      <c r="F17" s="19">
+      <c r="F17" s="20">
         <v>97668</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="11" t="s">
+      <c r="A18" s="12" t="s">
         <v>151</v>
       </c>
-      <c r="B18" s="19">
+      <c r="B18" s="20">
         <v>352690</v>
       </c>
-      <c r="C18" s="19">
+      <c r="C18" s="20">
         <v>423228</v>
       </c>
-      <c r="D18" s="19">
+      <c r="D18" s="20">
         <v>423228</v>
       </c>
-      <c r="E18" s="19">
+      <c r="E18" s="20">
         <v>423228</v>
       </c>
-      <c r="F18" s="19">
+      <c r="F18" s="20">
         <v>423228</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="11" t="s">
+      <c r="A19" s="12" t="s">
         <v>152</v>
       </c>
-      <c r="B19" s="19">
+      <c r="B19" s="20">
         <v>62173</v>
       </c>
-      <c r="C19" s="19">
+      <c r="C19" s="20">
         <v>74608</v>
       </c>
-      <c r="D19" s="19">
+      <c r="D19" s="20">
         <v>74608</v>
       </c>
-      <c r="E19" s="19">
+      <c r="E19" s="20">
         <v>74608</v>
       </c>
-      <c r="F19" s="19">
+      <c r="F19" s="20">
         <v>74608</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="11" t="s">
+      <c r="A20" s="12" t="s">
         <v>153</v>
       </c>
-      <c r="B20" s="19">
+      <c r="B20" s="20">
         <v>95738</v>
       </c>
-      <c r="C20" s="19">
+      <c r="C20" s="20">
         <v>114885</v>
       </c>
-      <c r="D20" s="19">
+      <c r="D20" s="20">
         <v>114885</v>
       </c>
-      <c r="E20" s="19">
+      <c r="E20" s="20">
         <v>114885</v>
       </c>
-      <c r="F20" s="19">
+      <c r="F20" s="20">
         <v>114885</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="11" t="s">
+      <c r="A21" s="12" t="s">
         <v>154</v>
       </c>
-      <c r="B21" s="19">
+      <c r="B21" s="20">
         <v>62173</v>
       </c>
-      <c r="C21" s="19">
+      <c r="C21" s="20">
         <v>74608</v>
       </c>
-      <c r="D21" s="19">
+      <c r="D21" s="20">
         <v>74608</v>
       </c>
-      <c r="E21" s="19">
+      <c r="E21" s="20">
         <v>74608</v>
       </c>
-      <c r="F21" s="19">
+      <c r="F21" s="20">
         <v>74608</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="11" t="s">
+      <c r="A22" s="12" t="s">
         <v>155</v>
       </c>
-      <c r="B22" s="19">
+      <c r="B22" s="20">
         <v>84012</v>
       </c>
-      <c r="C22" s="19">
+      <c r="C22" s="20">
         <v>100814</v>
       </c>
-      <c r="D22" s="19">
+      <c r="D22" s="20">
         <v>100814</v>
       </c>
-      <c r="E22" s="19">
+      <c r="E22" s="20">
         <v>100814</v>
       </c>
-      <c r="F22" s="19">
+      <c r="F22" s="20">
         <v>100814</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="11" t="s">
+      <c r="A23" s="12" t="s">
         <v>156</v>
       </c>
-      <c r="B23" s="19">
+      <c r="B23" s="20">
         <v>62173</v>
       </c>
-      <c r="C23" s="19">
+      <c r="C23" s="20">
         <v>74608</v>
       </c>
-      <c r="D23" s="19">
+      <c r="D23" s="20">
         <v>74608</v>
       </c>
-      <c r="E23" s="19">
+      <c r="E23" s="20">
         <v>74608</v>
       </c>
-      <c r="F23" s="19">
+      <c r="F23" s="20">
         <v>74608</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="10" t="s">
+      <c r="A24" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="B24" s="26">
+      <c r="B24" s="27">
         <f>SUM(B15:B23)</f>
         <v>1026431</v>
       </c>
-      <c r="C24" s="26">
+      <c r="C24" s="27">
         <f>SUM(C15:C23)</f>
         <v>1231718</v>
       </c>
-      <c r="D24" s="26">
+      <c r="D24" s="27">
         <f>SUM(D15:D23)</f>
         <v>1231718</v>
       </c>
-      <c r="E24" s="26">
+      <c r="E24" s="27">
         <f>SUM(E15:E23)</f>
         <v>1231718</v>
       </c>
-      <c r="F24" s="26">
+      <c r="F24" s="27">
         <f>SUM(F15:F23)</f>
         <v>1231718</v>
       </c>
     </row>
     <row r="26" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="10" t="s">
+      <c r="A26" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="B26" s="10"/>
-      <c r="C26" s="10"/>
-      <c r="D26" s="10"/>
-      <c r="E26" s="10"/>
-      <c r="F26" s="10"/>
+      <c r="B26" s="11"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="11"/>
+      <c r="E26" s="11"/>
+      <c r="F26" s="11"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="11" t="s">
+      <c r="A27" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="B27" s="11"/>
-      <c r="C27" s="11"/>
-      <c r="D27" s="11"/>
-      <c r="E27" s="11"/>
-      <c r="F27" s="11"/>
+      <c r="B27" s="12"/>
+      <c r="C27" s="12"/>
+      <c r="D27" s="12"/>
+      <c r="E27" s="12"/>
+      <c r="F27" s="12"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="11" t="s">
+      <c r="A28" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="B28" s="19">
+      <c r="B28" s="20">
         <v>70000</v>
       </c>
-      <c r="C28" s="19">
+      <c r="C28" s="20">
         <v>144200</v>
       </c>
-      <c r="D28" s="19">
+      <c r="D28" s="20">
         <v>222900</v>
       </c>
-      <c r="E28" s="19">
+      <c r="E28" s="20">
         <v>286875</v>
       </c>
-      <c r="F28" s="19">
+      <c r="F28" s="20">
         <v>315200</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="27" t="s">
+      <c r="A29" s="28" t="s">
         <v>159</v>
       </c>
-      <c r="B29" s="28">
+      <c r="B29" s="29">
         <v>70000</v>
       </c>
-      <c r="C29" s="28">
+      <c r="C29" s="29">
         <v>144200</v>
       </c>
-      <c r="D29" s="28">
+      <c r="D29" s="29">
         <v>222900</v>
       </c>
-      <c r="E29" s="28">
+      <c r="E29" s="29">
         <v>286875</v>
       </c>
-      <c r="F29" s="28">
+      <c r="F29" s="29">
         <v>315200</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="11" t="s">
+      <c r="A30" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="B30" s="11"/>
-      <c r="C30" s="11"/>
-      <c r="D30" s="11"/>
-      <c r="E30" s="11"/>
-      <c r="F30" s="11"/>
+      <c r="B30" s="12"/>
+      <c r="C30" s="12"/>
+      <c r="D30" s="12"/>
+      <c r="E30" s="12"/>
+      <c r="F30" s="12"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="11" t="s">
+      <c r="A31" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="B31" s="19">
+      <c r="B31" s="20">
         <v>50000</v>
       </c>
-      <c r="C31" s="19">
+      <c r="C31" s="20">
         <v>103000</v>
       </c>
-      <c r="D31" s="19">
+      <c r="D31" s="20">
         <v>159000</v>
       </c>
-      <c r="E31" s="19">
+      <c r="E31" s="20">
         <v>204750</v>
       </c>
-      <c r="F31" s="19">
+      <c r="F31" s="20">
         <v>224800</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="27" t="s">
+      <c r="A32" s="28" t="s">
         <v>161</v>
       </c>
-      <c r="B32" s="28">
+      <c r="B32" s="29">
         <v>50000</v>
       </c>
-      <c r="C32" s="28">
+      <c r="C32" s="29">
         <v>103000</v>
       </c>
-      <c r="D32" s="28">
+      <c r="D32" s="29">
         <v>159000</v>
       </c>
-      <c r="E32" s="28">
+      <c r="E32" s="29">
         <v>204750</v>
       </c>
-      <c r="F32" s="28">
+      <c r="F32" s="29">
         <v>224800</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="11" t="s">
+      <c r="A33" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="B33" s="11"/>
-      <c r="C33" s="11"/>
-      <c r="D33" s="11"/>
-      <c r="E33" s="11"/>
-      <c r="F33" s="11"/>
+      <c r="B33" s="12"/>
+      <c r="C33" s="12"/>
+      <c r="D33" s="12"/>
+      <c r="E33" s="12"/>
+      <c r="F33" s="12"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="11" t="s">
+      <c r="A34" s="12" t="s">
         <v>162</v>
       </c>
-      <c r="B34" s="19">
+      <c r="B34" s="20">
         <v>180000</v>
       </c>
-      <c r="C34" s="19">
+      <c r="C34" s="20">
         <v>222480</v>
       </c>
-      <c r="D34" s="19">
+      <c r="D34" s="20">
         <v>229154</v>
       </c>
-      <c r="E34" s="19">
+      <c r="E34" s="20">
         <v>236029</v>
       </c>
-      <c r="F34" s="19">
+      <c r="F34" s="20">
         <v>243110</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="11" t="s">
+      <c r="A35" s="12" t="s">
         <v>163</v>
       </c>
-      <c r="B35" s="19">
+      <c r="B35" s="20">
         <v>25000</v>
       </c>
-      <c r="C35" s="19">
+      <c r="C35" s="20">
         <v>30900</v>
       </c>
-      <c r="D35" s="19">
+      <c r="D35" s="20">
         <v>31824</v>
       </c>
-      <c r="E35" s="19">
+      <c r="E35" s="20">
         <v>32784</v>
       </c>
-      <c r="F35" s="19">
+      <c r="F35" s="20">
         <v>33768</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="11" t="s">
+      <c r="A36" s="12" t="s">
         <v>164</v>
       </c>
-      <c r="B36" s="19">
+      <c r="B36" s="20">
         <v>15000</v>
       </c>
-      <c r="C36" s="19">
+      <c r="C36" s="20">
         <v>18540</v>
       </c>
-      <c r="D36" s="19">
+      <c r="D36" s="20">
         <v>19096</v>
       </c>
-      <c r="E36" s="19">
+      <c r="E36" s="20">
         <v>19669</v>
       </c>
-      <c r="F36" s="19">
+      <c r="F36" s="20">
         <v>20259</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="11" t="s">
+      <c r="A37" s="12" t="s">
         <v>165</v>
       </c>
-      <c r="B37" s="19">
+      <c r="B37" s="20">
         <v>15000</v>
       </c>
-      <c r="C37" s="19">
+      <c r="C37" s="20">
         <v>18540</v>
       </c>
-      <c r="D37" s="19">
+      <c r="D37" s="20">
         <v>19092</v>
       </c>
-      <c r="E37" s="19">
+      <c r="E37" s="20">
         <v>19668</v>
       </c>
-      <c r="F37" s="19">
+      <c r="F37" s="20">
         <v>20256</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="27" t="s">
+      <c r="A38" s="28" t="s">
         <v>166</v>
       </c>
-      <c r="B38" s="28">
+      <c r="B38" s="29">
         <v>235000</v>
       </c>
-      <c r="C38" s="28">
+      <c r="C38" s="29">
         <v>290460</v>
       </c>
-      <c r="D38" s="28">
+      <c r="D38" s="29">
         <v>299166</v>
       </c>
-      <c r="E38" s="28">
+      <c r="E38" s="29">
         <v>308150</v>
       </c>
-      <c r="F38" s="28">
+      <c r="F38" s="29">
         <v>317393</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="11" t="s">
+      <c r="A39" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="B39" s="11"/>
-      <c r="C39" s="11"/>
-      <c r="D39" s="11"/>
-      <c r="E39" s="11"/>
-      <c r="F39" s="11"/>
+      <c r="B39" s="12"/>
+      <c r="C39" s="12"/>
+      <c r="D39" s="12"/>
+      <c r="E39" s="12"/>
+      <c r="F39" s="12"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="11" t="s">
+      <c r="A40" s="12" t="s">
         <v>167</v>
       </c>
-      <c r="B40" s="19">
+      <c r="B40" s="20">
         <v>20833</v>
       </c>
-      <c r="C40" s="19">
+      <c r="C40" s="20">
         <v>25750</v>
       </c>
-      <c r="D40" s="19">
+      <c r="D40" s="20">
         <v>26523</v>
       </c>
-      <c r="E40" s="19">
+      <c r="E40" s="20">
         <v>27318</v>
       </c>
-      <c r="F40" s="19">
+      <c r="F40" s="20">
         <v>28138</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="11" t="s">
+      <c r="A41" s="12" t="s">
         <v>168</v>
       </c>
-      <c r="B41" s="19">
+      <c r="B41" s="20">
         <v>12500</v>
       </c>
-      <c r="C41" s="19">
+      <c r="C41" s="20">
         <v>15450</v>
       </c>
-      <c r="D41" s="19">
+      <c r="D41" s="20">
         <v>15914</v>
       </c>
-      <c r="E41" s="19">
+      <c r="E41" s="20">
         <v>16391</v>
       </c>
-      <c r="F41" s="19">
+      <c r="F41" s="20">
         <v>16883</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="11" t="s">
+      <c r="A42" s="12" t="s">
         <v>169</v>
       </c>
-      <c r="B42" s="19">
+      <c r="B42" s="20">
         <v>16667</v>
       </c>
-      <c r="C42" s="19">
+      <c r="C42" s="20">
         <v>20600</v>
       </c>
-      <c r="D42" s="19">
+      <c r="D42" s="20">
         <v>21218</v>
       </c>
-      <c r="E42" s="19">
+      <c r="E42" s="20">
         <v>21855</v>
       </c>
-      <c r="F42" s="19">
+      <c r="F42" s="20">
         <v>22510</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="11" t="s">
+      <c r="A43" s="12" t="s">
         <v>170</v>
       </c>
-      <c r="B43" s="19">
+      <c r="B43" s="20">
         <v>80000</v>
       </c>
-      <c r="C43" s="19">
+      <c r="C43" s="20">
         <v>164800</v>
       </c>
-      <c r="D43" s="19">
+      <c r="D43" s="20">
         <v>254700</v>
       </c>
-      <c r="E43" s="19">
+      <c r="E43" s="20">
         <v>327750</v>
       </c>
-      <c r="F43" s="19">
+      <c r="F43" s="20">
         <v>360000</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="11" t="s">
+      <c r="A44" s="12" t="s">
         <v>171</v>
       </c>
-      <c r="B44" s="19">
+      <c r="B44" s="20">
         <v>60000</v>
       </c>
-      <c r="C44" s="19">
+      <c r="C44" s="20">
         <v>123600</v>
       </c>
-      <c r="D44" s="19">
+      <c r="D44" s="20">
         <v>191100</v>
       </c>
-      <c r="E44" s="19">
+      <c r="E44" s="20">
         <v>246000</v>
       </c>
-      <c r="F44" s="19">
+      <c r="F44" s="20">
         <v>270000</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="27" t="s">
+      <c r="A45" s="28" t="s">
         <v>172</v>
       </c>
-      <c r="B45" s="28">
+      <c r="B45" s="29">
         <v>190000</v>
       </c>
-      <c r="C45" s="28">
+      <c r="C45" s="29">
         <v>350200</v>
       </c>
-      <c r="D45" s="28">
+      <c r="D45" s="29">
         <v>509455</v>
       </c>
-      <c r="E45" s="28">
+      <c r="E45" s="29">
         <v>639314</v>
       </c>
-      <c r="F45" s="28">
+      <c r="F45" s="29">
         <v>697531</v>
       </c>
     </row>
     <row r="46" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="10" t="s">
+      <c r="A46" s="11" t="s">
         <v>173</v>
       </c>
-      <c r="B46" s="26">
+      <c r="B46" s="27">
         <f>B29+B32+B38+B45</f>
         <v>545000</v>
       </c>
-      <c r="C46" s="26">
+      <c r="C46" s="27">
         <f>C29+C32+C38+C45</f>
         <v>887860</v>
       </c>
-      <c r="D46" s="26">
+      <c r="D46" s="27">
         <f>D29+D32+D38+D45</f>
         <v>1190521</v>
       </c>
-      <c r="E46" s="26">
+      <c r="E46" s="27">
         <f>E29+E32+E38+E45</f>
         <v>1439089</v>
       </c>
-      <c r="F46" s="26">
+      <c r="F46" s="27">
         <f>F29+F32+F38+F45</f>
         <v>1554924</v>
       </c>
     </row>
     <row r="48" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="10" t="s">
+      <c r="A48" s="11" t="s">
         <v>174</v>
       </c>
-      <c r="B48" s="10"/>
-      <c r="C48" s="10"/>
-      <c r="D48" s="10"/>
-      <c r="E48" s="10"/>
-      <c r="F48" s="10"/>
+      <c r="B48" s="11"/>
+      <c r="C48" s="11"/>
+      <c r="D48" s="11"/>
+      <c r="E48" s="11"/>
+      <c r="F48" s="11"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="11" t="s">
+      <c r="A49" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="B49" s="19">
+      <c r="B49" s="20">
         <v>49825</v>
       </c>
-      <c r="C49" s="19">
+      <c r="C49" s="20">
         <v>49825</v>
       </c>
-      <c r="D49" s="19">
+      <c r="D49" s="20">
         <v>49825</v>
       </c>
-      <c r="E49" s="19">
+      <c r="E49" s="20">
         <v>49825</v>
       </c>
-      <c r="F49" s="19">
+      <c r="F49" s="20">
         <v>49825</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="11" t="s">
+      <c r="A50" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="B50" s="19">
+      <c r="B50" s="20">
         <v>75000</v>
       </c>
-      <c r="C50" s="19">
+      <c r="C50" s="20">
         <v>25000</v>
       </c>
-      <c r="D50" s="19">
+      <c r="D50" s="20">
         <v>30000</v>
       </c>
-      <c r="E50" s="19">
+      <c r="E50" s="20">
         <v>15000</v>
       </c>
-      <c r="F50" s="19">
+      <c r="F50" s="20">
         <v>10000</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="11" t="s">
+      <c r="A51" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="B51" s="19">
+      <c r="B51" s="20">
         <v>40000</v>
       </c>
-      <c r="C51" s="19">
+      <c r="C51" s="20">
         <v>15000</v>
       </c>
-      <c r="D51" s="19">
+      <c r="D51" s="20">
         <v>10000</v>
       </c>
-      <c r="E51" s="19">
+      <c r="E51" s="20">
         <v>10000</v>
       </c>
-      <c r="F51" s="19">
+      <c r="F51" s="20">
         <v>10000</v>
       </c>
     </row>
     <row r="52" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="10" t="s">
+      <c r="A52" s="11" t="s">
         <v>175</v>
       </c>
-      <c r="B52" s="26">
+      <c r="B52" s="27">
         <f>SUM(B49:B51)</f>
         <v>164825</v>
       </c>
-      <c r="C52" s="26">
+      <c r="C52" s="27">
         <f>SUM(C49:C51)</f>
         <v>89825</v>
       </c>
-      <c r="D52" s="26">
+      <c r="D52" s="27">
         <f>SUM(D49:D51)</f>
         <v>89825</v>
       </c>
-      <c r="E52" s="26">
+      <c r="E52" s="27">
         <f>SUM(E49:E51)</f>
         <v>74825</v>
       </c>
-      <c r="F52" s="26">
+      <c r="F52" s="27">
         <f>SUM(F49:F51)</f>
         <v>69825</v>
       </c>
     </row>
     <row r="54" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="10" t="s">
+      <c r="A54" s="11" t="s">
         <v>176</v>
       </c>
-      <c r="B54" s="10"/>
-      <c r="C54" s="10"/>
-      <c r="D54" s="10"/>
-      <c r="E54" s="10"/>
-      <c r="F54" s="10"/>
+      <c r="B54" s="11"/>
+      <c r="C54" s="11"/>
+      <c r="D54" s="11"/>
+      <c r="E54" s="11"/>
+      <c r="F54" s="11"/>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="24" t="s">
+      <c r="A55" s="25" t="s">
         <v>177</v>
       </c>
-      <c r="B55" s="28">
+      <c r="B55" s="29">
         <f>B12</f>
         <v>1288333</v>
       </c>
-      <c r="C55" s="28">
+      <c r="C55" s="29">
         <f>C12</f>
         <v>2522800</v>
       </c>
-      <c r="D55" s="28">
+      <c r="D55" s="29">
         <f>D12</f>
         <v>3784600</v>
       </c>
-      <c r="E55" s="28">
+      <c r="E55" s="29">
         <f>E12</f>
         <v>4759125</v>
       </c>
-      <c r="F55" s="28">
+      <c r="F55" s="29">
         <f>F12</f>
         <v>5184400</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="11" t="s">
+      <c r="A56" s="12" t="s">
         <v>178</v>
       </c>
-      <c r="B56" s="19">
+      <c r="B56" s="20">
         <f>B24</f>
         <v>1026431</v>
       </c>
-      <c r="C56" s="19">
+      <c r="C56" s="20">
         <f>C24</f>
         <v>1231718</v>
       </c>
-      <c r="D56" s="19">
+      <c r="D56" s="20">
         <f>D24</f>
         <v>1231718</v>
       </c>
-      <c r="E56" s="19">
+      <c r="E56" s="20">
         <f>E24</f>
         <v>1231718</v>
       </c>
-      <c r="F56" s="19">
+      <c r="F56" s="20">
         <f>F24</f>
         <v>1231718</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="11" t="s">
+      <c r="A57" s="12" t="s">
         <v>179</v>
       </c>
-      <c r="B57" s="19">
+      <c r="B57" s="20">
         <f>B46</f>
         <v>545000</v>
       </c>
-      <c r="C57" s="19">
+      <c r="C57" s="20">
         <f>C46</f>
         <v>887860</v>
       </c>
-      <c r="D57" s="19">
+      <c r="D57" s="20">
         <f>D46</f>
         <v>1190521</v>
       </c>
-      <c r="E57" s="19">
+      <c r="E57" s="20">
         <f>E46</f>
         <v>1439089</v>
       </c>
-      <c r="F57" s="19">
+      <c r="F57" s="20">
         <f>F46</f>
         <v>1554924</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="11" t="s">
+      <c r="A58" s="12" t="s">
         <v>180</v>
       </c>
-      <c r="B58" s="19">
+      <c r="B58" s="20">
         <f>B52</f>
         <v>164825</v>
       </c>
-      <c r="C58" s="19">
+      <c r="C58" s="20">
         <f>C52</f>
         <v>89825</v>
       </c>
-      <c r="D58" s="19">
+      <c r="D58" s="20">
         <f>D52</f>
         <v>89825</v>
       </c>
-      <c r="E58" s="19">
+      <c r="E58" s="20">
         <f>E52</f>
         <v>74825</v>
       </c>
-      <c r="F58" s="19">
+      <c r="F58" s="20">
         <f>F52</f>
         <v>69825</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="24" t="s">
+      <c r="A59" s="25" t="s">
         <v>181</v>
       </c>
-      <c r="B59" s="28">
+      <c r="B59" s="29">
         <f>B56+B57+B58</f>
         <v>1736256</v>
       </c>
-      <c r="C59" s="28">
+      <c r="C59" s="29">
         <f>C56+C57+C58</f>
         <v>2209403</v>
       </c>
-      <c r="D59" s="28">
+      <c r="D59" s="29">
         <f>D56+D57+D58</f>
         <v>2512064</v>
       </c>
-      <c r="E59" s="28">
+      <c r="E59" s="29">
         <f>E56+E57+E58</f>
         <v>2745632</v>
       </c>
-      <c r="F59" s="28">
+      <c r="F59" s="29">
         <f>F56+F57+F58</f>
         <v>2856467</v>
       </c>
@@ -4003,569 +4007,569 @@
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="29" t="s">
+      <c r="A61" s="30" t="s">
         <v>182</v>
       </c>
-      <c r="B61" s="30">
+      <c r="B61" s="31">
         <f>B55-B59</f>
         <v>-447923</v>
       </c>
-      <c r="C61" s="31">
+      <c r="C61" s="32">
         <f>C55-C59</f>
         <v>313397</v>
       </c>
-      <c r="D61" s="31">
+      <c r="D61" s="32">
         <f>D55-D59</f>
         <v>1272536</v>
       </c>
-      <c r="E61" s="31">
+      <c r="E61" s="32">
         <f>E55-E59</f>
         <v>2013493</v>
       </c>
-      <c r="F61" s="31">
+      <c r="F61" s="32">
         <f>F55-F59</f>
         <v>2327933</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="11" t="s">
+      <c r="A62" s="12" t="s">
         <v>183</v>
       </c>
-      <c r="B62" s="32">
+      <c r="B62" s="33">
         <f>IF(B55=0,"",B61/B55)</f>
         <v>-0.35</v>
       </c>
-      <c r="C62" s="32">
+      <c r="C62" s="33">
         <f>IF(C55=0,"",C61/C55)</f>
         <v>0.12</v>
       </c>
-      <c r="D62" s="32">
+      <c r="D62" s="33">
         <f>IF(D55=0,"",D61/D55)</f>
         <v>0.34</v>
       </c>
-      <c r="E62" s="32">
+      <c r="E62" s="33">
         <f>IF(E55=0,"",E61/E55)</f>
         <v>0.42</v>
       </c>
-      <c r="F62" s="32">
+      <c r="F62" s="33">
         <f>IF(F55=0,"",F61/F55)</f>
         <v>0.45</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" s="11" t="s">
+      <c r="A63" s="12" t="s">
         <v>184</v>
       </c>
-      <c r="B63" s="19">
+      <c r="B63" s="20">
         <f>B61</f>
         <v>-447923</v>
       </c>
-      <c r="C63" s="19">
+      <c r="C63" s="20">
         <f>B63+C61</f>
         <v>-134526</v>
       </c>
-      <c r="D63" s="19">
+      <c r="D63" s="20">
         <f>C63+D61</f>
         <v>1138010</v>
       </c>
-      <c r="E63" s="19">
+      <c r="E63" s="20">
         <f>D63+E61</f>
         <v>3151503</v>
       </c>
-      <c r="F63" s="19">
+      <c r="F63" s="20">
         <f>E63+F61</f>
         <v>5479436</v>
       </c>
     </row>
     <row r="65" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A65" s="10" t="s">
+      <c r="A65" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="B65" s="10"/>
-      <c r="C65" s="10"/>
-      <c r="D65" s="10"/>
-      <c r="E65" s="10"/>
-      <c r="F65" s="10"/>
+      <c r="B65" s="11"/>
+      <c r="C65" s="11"/>
+      <c r="D65" s="11"/>
+      <c r="E65" s="11"/>
+      <c r="F65" s="11"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A66" s="24" t="s">
+      <c r="A66" s="25" t="s">
         <v>186</v>
       </c>
-      <c r="B66" s="28">
+      <c r="B66" s="29">
         <f>B55-B56-B57</f>
         <v>-283098</v>
       </c>
-      <c r="C66" s="28">
+      <c r="C66" s="29">
         <f>C55-C56-C57</f>
         <v>403222</v>
       </c>
-      <c r="D66" s="28">
+      <c r="D66" s="29">
         <f>D55-D56-D57</f>
         <v>1362361</v>
       </c>
-      <c r="E66" s="28">
+      <c r="E66" s="29">
         <f>E55-E56-E57</f>
         <v>2088318</v>
       </c>
-      <c r="F66" s="28">
+      <c r="F66" s="29">
         <f>F55-F56-F57</f>
         <v>2397758</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A67" s="11" t="s">
+      <c r="A67" s="12" t="s">
         <v>187</v>
       </c>
-      <c r="B67" s="19">
+      <c r="B67" s="20">
         <f>B58</f>
         <v>164825</v>
       </c>
-      <c r="C67" s="19">
+      <c r="C67" s="20">
         <f>C58</f>
         <v>89825</v>
       </c>
-      <c r="D67" s="19">
+      <c r="D67" s="20">
         <f>D58</f>
         <v>89825</v>
       </c>
-      <c r="E67" s="19">
+      <c r="E67" s="20">
         <f>E58</f>
         <v>74825</v>
       </c>
-      <c r="F67" s="19">
+      <c r="F67" s="20">
         <f>F58</f>
         <v>69825</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A68" s="24" t="s">
+      <c r="A68" s="25" t="s">
         <v>188</v>
       </c>
-      <c r="B68" s="33">
+      <c r="B68" s="34">
         <f>IF(B67=0,"N/A",B66/B67)</f>
         <v>-1.72</v>
       </c>
-      <c r="C68" s="33">
+      <c r="C68" s="34">
         <f>IF(C67=0,"N/A",C66/C67)</f>
         <v>4.49</v>
       </c>
-      <c r="D68" s="33">
+      <c r="D68" s="34">
         <f>IF(D67=0,"N/A",D66/D67)</f>
         <v>15.17</v>
       </c>
-      <c r="E68" s="33">
+      <c r="E68" s="34">
         <f>IF(E67=0,"N/A",E66/E67)</f>
         <v>27.91</v>
       </c>
-      <c r="F68" s="33">
+      <c r="F68" s="34">
         <f>IF(F67=0,"N/A",F66/F67)</f>
         <v>34.34</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A69" s="11" t="s">
+      <c r="A69" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="B69" s="19" t="str">
+      <c r="B69" s="20" t="str">
         <f>Assumptions!B68</f>
         <v>0</v>
       </c>
-      <c r="C69" s="19">
+      <c r="C69" s="20">
         <f>B70</f>
         <v>-447923</v>
       </c>
-      <c r="D69" s="19">
+      <c r="D69" s="20">
         <f>C70</f>
         <v>-134526</v>
       </c>
-      <c r="E69" s="19">
+      <c r="E69" s="20">
         <f>D70</f>
         <v>1138010</v>
       </c>
-      <c r="F69" s="19">
+      <c r="F69" s="20">
         <f>E70</f>
         <v>3151503</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A70" s="24" t="s">
+      <c r="A70" s="25" t="s">
         <v>189</v>
       </c>
-      <c r="B70" s="28">
+      <c r="B70" s="29">
         <f>B69+B61</f>
         <v>-447923</v>
       </c>
-      <c r="C70" s="28">
+      <c r="C70" s="29">
         <f>C69+C61</f>
         <v>-134526</v>
       </c>
-      <c r="D70" s="28">
+      <c r="D70" s="29">
         <f>D69+D61</f>
         <v>1138010</v>
       </c>
-      <c r="E70" s="28">
+      <c r="E70" s="29">
         <f>E69+E61</f>
         <v>3151503</v>
       </c>
-      <c r="F70" s="28">
+      <c r="F70" s="29">
         <f>F69+F61</f>
         <v>5479436</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A71" s="11" t="s">
+      <c r="A71" s="12" t="s">
         <v>190</v>
       </c>
-      <c r="B71" s="34">
+      <c r="B71" s="35">
         <f>IF(B59=0,"",B70/B59*365)</f>
         <v>-94</v>
       </c>
-      <c r="C71" s="34">
+      <c r="C71" s="35">
         <f>IF(C59=0,"",C70/C59*365)</f>
         <v>-22</v>
       </c>
-      <c r="D71" s="34">
+      <c r="D71" s="35">
         <f>IF(D59=0,"",D70/D59*365)</f>
         <v>165</v>
       </c>
-      <c r="E71" s="34">
+      <c r="E71" s="35">
         <f>IF(E59=0,"",E70/E59*365)</f>
         <v>419</v>
       </c>
-      <c r="F71" s="34">
+      <c r="F71" s="35">
         <f>IF(F59=0,"",F70/F59*365)</f>
         <v>700</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A72" s="11" t="s">
+      <c r="A72" s="12" t="s">
         <v>191</v>
       </c>
-      <c r="B72" s="35">
+      <c r="B72" s="36">
         <f>IF(B59=0,"",B70/(B59/12))</f>
         <v>-3.1</v>
       </c>
-      <c r="C72" s="35">
+      <c r="C72" s="36">
         <f>IF(C59=0,"",C70/(C59/12))</f>
         <v>-0.7</v>
       </c>
-      <c r="D72" s="35">
+      <c r="D72" s="36">
         <f>IF(D59=0,"",D70/(D59/12))</f>
         <v>5.4</v>
       </c>
-      <c r="E72" s="35">
+      <c r="E72" s="36">
         <f>IF(E59=0,"",E70/(E59/12))</f>
         <v>13.8</v>
       </c>
-      <c r="F72" s="35">
+      <c r="F72" s="36">
         <f>IF(F59=0,"",F70/(F59/12))</f>
         <v>23</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A73" s="11" t="s">
+      <c r="A73" s="12" t="s">
         <v>192</v>
       </c>
-      <c r="B73" s="32">
+      <c r="B73" s="33">
         <f>IF(Assumptions!B12=0,"",B3/Assumptions!B12)</f>
         <v>0.3</v>
       </c>
-      <c r="C73" s="32">
+      <c r="C73" s="33">
         <f>IF(Assumptions!B12=0,"",C3/Assumptions!B12)</f>
         <v>0.5</v>
       </c>
-      <c r="D73" s="32">
+      <c r="D73" s="33">
         <f>IF(Assumptions!B12=0,"",D3/Assumptions!B12)</f>
         <v>0.75</v>
       </c>
-      <c r="E73" s="32">
+      <c r="E73" s="33">
         <f>IF(Assumptions!B12=0,"",E3/Assumptions!B12)</f>
         <v>0.94</v>
       </c>
-      <c r="F73" s="32">
+      <c r="F73" s="33">
         <f>IF(Assumptions!B12=0,"",F3/Assumptions!B12)</f>
         <v>1</v>
       </c>
     </row>
     <row r="75" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A75" s="10" t="s">
+      <c r="A75" s="11" t="s">
         <v>193</v>
       </c>
-      <c r="B75" s="10"/>
-      <c r="C75" s="10"/>
-      <c r="D75" s="10"/>
-      <c r="E75" s="10"/>
-      <c r="F75" s="10"/>
+      <c r="B75" s="11"/>
+      <c r="C75" s="11"/>
+      <c r="D75" s="11"/>
+      <c r="E75" s="11"/>
+      <c r="F75" s="11"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A76" s="11" t="s">
+      <c r="A76" s="12" t="s">
         <v>194</v>
       </c>
-      <c r="B76" s="11" t="str">
+      <c r="B76" s="12" t="str">
         <f>IF(B67=0,"N/A",IF(B68&gt;=1.2,"PASS","FAIL"))</f>
         <v>FAIL</v>
       </c>
-      <c r="C76" s="11" t="str">
+      <c r="C76" s="12" t="str">
         <f>IF(C67=0,"N/A",IF(C68&gt;=1.2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="D76" s="11" t="str">
+      <c r="D76" s="12" t="str">
         <f>IF(D67=0,"N/A",IF(D68&gt;=1.2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="E76" s="11" t="str">
+      <c r="E76" s="12" t="str">
         <f>IF(E67=0,"N/A",IF(E68&gt;=1.2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="F76" s="11" t="str">
+      <c r="F76" s="12" t="str">
         <f>IF(F67=0,"N/A",IF(F68&gt;=1.2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A77" s="11" t="s">
+      <c r="A77" s="12" t="s">
         <v>195</v>
       </c>
-      <c r="B77" s="11" t="str">
+      <c r="B77" s="12" t="str">
         <f>IF(B61&gt;0,"PASS","FAIL")</f>
         <v>FAIL</v>
       </c>
-      <c r="C77" s="11" t="str">
+      <c r="C77" s="12" t="str">
         <f>IF(C61&gt;0,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-      <c r="D77" s="11" t="str">
+      <c r="D77" s="12" t="str">
         <f>IF(D61&gt;0,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-      <c r="E77" s="11" t="str">
+      <c r="E77" s="12" t="str">
         <f>IF(E61&gt;0,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-      <c r="F77" s="11" t="str">
+      <c r="F77" s="12" t="str">
         <f>IF(F61&gt;0,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A78" s="11" t="s">
+      <c r="A78" s="12" t="s">
         <v>196</v>
       </c>
-      <c r="B78" s="11" t="str">
+      <c r="B78" s="12" t="str">
         <f>IF(Assumptions!B12=0,"N/A",IF(B3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
         <v>FAIL</v>
       </c>
-      <c r="C78" s="11" t="str">
+      <c r="C78" s="12" t="str">
         <f>IF(Assumptions!B12=0,"N/A",IF(C3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
         <v>FAIL</v>
       </c>
-      <c r="D78" s="11" t="str">
+      <c r="D78" s="12" t="str">
         <f>IF(Assumptions!B12=0,"N/A",IF(D3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="E78" s="11" t="str">
+      <c r="E78" s="12" t="str">
         <f>IF(Assumptions!B12=0,"N/A",IF(E3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="F78" s="11" t="str">
+      <c r="F78" s="12" t="str">
         <f>IF(Assumptions!B12=0,"N/A",IF(F3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A79" s="11" t="s">
+      <c r="A79" s="12" t="s">
         <v>197</v>
       </c>
-      <c r="B79" s="11" t="str">
+      <c r="B79" s="12" t="str">
         <f>IF(B59=0,"N/A",IF(B70/(B59/12)&gt;=2,"PASS","FAIL"))</f>
         <v>FAIL</v>
       </c>
-      <c r="C79" s="11" t="str">
+      <c r="C79" s="12" t="str">
         <f>IF(C59=0,"N/A",IF(C70/(C59/12)&gt;=2,"PASS","FAIL"))</f>
         <v>FAIL</v>
       </c>
-      <c r="D79" s="11" t="str">
+      <c r="D79" s="12" t="str">
         <f>IF(D59=0,"N/A",IF(D70/(D59/12)&gt;=2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="E79" s="11" t="str">
+      <c r="E79" s="12" t="str">
         <f>IF(E59=0,"N/A",IF(E70/(E59/12)&gt;=2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="F79" s="11" t="str">
+      <c r="F79" s="12" t="str">
         <f>IF(F59=0,"N/A",IF(F70/(F59/12)&gt;=2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="81" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A81" s="10" t="s">
+      <c r="A81" s="11" t="s">
         <v>198</v>
       </c>
-      <c r="B81" s="10"/>
-      <c r="C81" s="10"/>
-      <c r="D81" s="10"/>
-      <c r="E81" s="10"/>
-      <c r="F81" s="10"/>
+      <c r="B81" s="11"/>
+      <c r="C81" s="11"/>
+      <c r="D81" s="11"/>
+      <c r="E81" s="11"/>
+      <c r="F81" s="11"/>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A82" s="11" t="s">
+      <c r="A82" s="12" t="s">
         <v>199</v>
       </c>
-      <c r="B82" s="19">
+      <c r="B82" s="20">
         <f>IF(B3=0,"",B12/B3)</f>
         <v>10736</v>
       </c>
-      <c r="C82" s="19">
+      <c r="C82" s="20">
         <f>IF(C3=0,"",C12/C3)</f>
         <v>12614</v>
       </c>
-      <c r="D82" s="19">
+      <c r="D82" s="20">
         <f>IF(D3=0,"",D12/D3)</f>
         <v>12615</v>
       </c>
-      <c r="E82" s="19">
+      <c r="E82" s="20">
         <f>IF(E3=0,"",E12/E3)</f>
         <v>12691</v>
       </c>
-      <c r="F82" s="19">
+      <c r="F82" s="20">
         <f>IF(F3=0,"",F12/F3)</f>
         <v>12961</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A83" s="11" t="s">
+      <c r="A83" s="12" t="s">
         <v>200</v>
       </c>
-      <c r="B83" s="19">
+      <c r="B83" s="20">
         <f>IF(B3=0,"",B59/B3)</f>
         <v>14469</v>
       </c>
-      <c r="C83" s="19">
+      <c r="C83" s="20">
         <f>IF(C3=0,"",C59/C3)</f>
         <v>11047</v>
       </c>
-      <c r="D83" s="19">
+      <c r="D83" s="20">
         <f>IF(D3=0,"",D59/D3)</f>
         <v>8374</v>
       </c>
-      <c r="E83" s="19">
+      <c r="E83" s="20">
         <f>IF(E3=0,"",E59/E3)</f>
         <v>7322</v>
       </c>
-      <c r="F83" s="19">
+      <c r="F83" s="20">
         <f>IF(F3=0,"",F59/F3)</f>
         <v>7141</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A84" s="11" t="s">
+      <c r="A84" s="12" t="s">
         <v>201</v>
       </c>
-      <c r="B84" s="19">
+      <c r="B84" s="20">
         <f>B56+B58</f>
         <v>1191256</v>
       </c>
-      <c r="C84" s="19">
+      <c r="C84" s="20">
         <f>C56+C58</f>
         <v>1321543</v>
       </c>
-      <c r="D84" s="19">
+      <c r="D84" s="20">
         <f>D56+D58</f>
         <v>1321543</v>
       </c>
-      <c r="E84" s="19">
+      <c r="E84" s="20">
         <f>E56+E58</f>
         <v>1306543</v>
       </c>
-      <c r="F84" s="19">
+      <c r="F84" s="20">
         <f>F56+F58</f>
         <v>1301543</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A85" s="11" t="s">
+      <c r="A85" s="12" t="s">
         <v>202</v>
       </c>
-      <c r="B85" s="19">
+      <c r="B85" s="20">
         <f>IF(B3=0,"",B57/B3)</f>
         <v>4542</v>
       </c>
-      <c r="C85" s="19">
+      <c r="C85" s="20">
         <f>IF(C3=0,"",C57/C3)</f>
         <v>4439</v>
       </c>
-      <c r="D85" s="19">
+      <c r="D85" s="20">
         <f>IF(D3=0,"",D57/D3)</f>
         <v>3968</v>
       </c>
-      <c r="E85" s="19">
+      <c r="E85" s="20">
         <f>IF(E3=0,"",E57/E3)</f>
         <v>3838</v>
       </c>
-      <c r="F85" s="19">
+      <c r="F85" s="20">
         <f>IF(F3=0,"",F57/F3)</f>
         <v>3887</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A86" s="11" t="s">
+      <c r="A86" s="12" t="s">
         <v>203</v>
       </c>
-      <c r="B86" s="19">
+      <c r="B86" s="20">
         <f>IF(B3=0,"",B82-B85)</f>
         <v>6194</v>
       </c>
-      <c r="C86" s="19">
+      <c r="C86" s="20">
         <f>IF(C3=0,"",C82-C85)</f>
         <v>8175</v>
       </c>
-      <c r="D86" s="19">
+      <c r="D86" s="20">
         <f>IF(D3=0,"",D82-D85)</f>
         <v>8647</v>
       </c>
-      <c r="E86" s="19">
+      <c r="E86" s="20">
         <f>IF(E3=0,"",E82-E85)</f>
         <v>8853</v>
       </c>
-      <c r="F86" s="19">
+      <c r="F86" s="20">
         <f>IF(F3=0,"",F82-F85)</f>
         <v>9074</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A87" s="36" t="s">
+      <c r="A87" s="37" t="s">
         <v>204</v>
       </c>
-      <c r="B87" s="37">
+      <c r="B87" s="38">
         <f>IF(B86&lt;=0,"N/A",ROUNDUP(B84/B86,0))</f>
         <v>193</v>
       </c>
-      <c r="C87" s="37">
+      <c r="C87" s="38">
         <f>IF(C86&lt;=0,"N/A",ROUNDUP(C84/C86,0))</f>
         <v>162</v>
       </c>
-      <c r="D87" s="37">
+      <c r="D87" s="38">
         <f>IF(D86&lt;=0,"N/A",ROUNDUP(D84/D86,0))</f>
         <v>153</v>
       </c>
-      <c r="E87" s="37">
+      <c r="E87" s="38">
         <f>IF(E86&lt;=0,"N/A",ROUNDUP(E84/E86,0))</f>
         <v>148</v>
       </c>
-      <c r="F87" s="37">
+      <c r="F87" s="38">
         <f>IF(F86&lt;=0,"N/A",ROUNDUP(F84/F86,0))</f>
         <v>144</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A89" s="22" t="s">
+      <c r="A89" s="23" t="s">
         <v>143</v>
       </c>
-      <c r="B89" s="22"/>
-      <c r="C89" s="22"/>
-      <c r="D89" s="22"/>
-      <c r="E89" s="22"/>
-      <c r="F89" s="22"/>
+      <c r="B89" s="23"/>
+      <c r="C89" s="23"/>
+      <c r="D89" s="23"/>
+      <c r="E89" s="23"/>
+      <c r="F89" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -4613,390 +4617,390 @@
       <c r="N1" s="8"/>
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="23" t="s">
+      <c r="B2" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="C2" s="23" t="s">
+      <c r="C2" s="24" t="s">
         <v>206</v>
       </c>
-      <c r="D2" s="23" t="s">
+      <c r="D2" s="24" t="s">
         <v>207</v>
       </c>
-      <c r="E2" s="23" t="s">
+      <c r="E2" s="24" t="s">
         <v>208</v>
       </c>
-      <c r="F2" s="23" t="s">
+      <c r="F2" s="24" t="s">
         <v>209</v>
       </c>
-      <c r="G2" s="23" t="s">
+      <c r="G2" s="24" t="s">
         <v>210</v>
       </c>
-      <c r="H2" s="23" t="s">
+      <c r="H2" s="24" t="s">
         <v>211</v>
       </c>
-      <c r="I2" s="23" t="s">
+      <c r="I2" s="24" t="s">
         <v>212</v>
       </c>
-      <c r="J2" s="23" t="s">
+      <c r="J2" s="24" t="s">
         <v>213</v>
       </c>
-      <c r="K2" s="23" t="s">
+      <c r="K2" s="24" t="s">
         <v>214</v>
       </c>
-      <c r="L2" s="23" t="s">
+      <c r="L2" s="24" t="s">
         <v>215</v>
       </c>
-      <c r="M2" s="23" t="s">
+      <c r="M2" s="24" t="s">
         <v>216</v>
       </c>
-      <c r="N2" s="23" t="s">
+      <c r="N2" s="24" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="11" t="s">
         <v>145</v>
       </c>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10"/>
-      <c r="H3" s="10"/>
-      <c r="I3" s="10"/>
-      <c r="J3" s="10"/>
-      <c r="K3" s="10"/>
-      <c r="L3" s="10"/>
-      <c r="M3" s="10"/>
-      <c r="N3" s="10"/>
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11"/>
+      <c r="J3" s="11"/>
+      <c r="K3" s="11"/>
+      <c r="L3" s="11"/>
+      <c r="M3" s="11"/>
+      <c r="N3" s="11"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="B4" s="19">
+      <c r="B4" s="20">
         <v>114000</v>
       </c>
-      <c r="C4" s="19">
+      <c r="C4" s="20">
         <v>114000</v>
       </c>
-      <c r="D4" s="19">
+      <c r="D4" s="20">
         <v>114000</v>
       </c>
-      <c r="E4" s="19">
+      <c r="E4" s="20">
         <v>114000</v>
       </c>
-      <c r="F4" s="19">
+      <c r="F4" s="20">
         <v>114000</v>
       </c>
-      <c r="G4" s="19">
+      <c r="G4" s="20">
         <v>114000</v>
       </c>
-      <c r="H4" s="19">
+      <c r="H4" s="20">
         <v>114000</v>
       </c>
-      <c r="I4" s="19">
+      <c r="I4" s="20">
         <v>114000</v>
       </c>
-      <c r="J4" s="19">
+      <c r="J4" s="20">
         <v>114000</v>
       </c>
-      <c r="K4" s="19">
+      <c r="K4" s="20">
         <v>114000</v>
       </c>
-      <c r="L4" s="19">
-        <v>0</v>
-      </c>
-      <c r="M4" s="19">
-        <v>0</v>
-      </c>
-      <c r="N4" s="19">
+      <c r="L4" s="20">
+        <v>0</v>
+      </c>
+      <c r="M4" s="20">
+        <v>0</v>
+      </c>
+      <c r="N4" s="20">
         <f>SUM(B4:M4)</f>
         <v>950000</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" s="11" t="s">
+      <c r="A5" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="B5" s="19">
+      <c r="B5" s="20">
         <v>9600</v>
       </c>
-      <c r="C5" s="19">
+      <c r="C5" s="20">
         <v>9600</v>
       </c>
-      <c r="D5" s="19">
+      <c r="D5" s="20">
         <v>9600</v>
       </c>
-      <c r="E5" s="19">
+      <c r="E5" s="20">
         <v>9600</v>
       </c>
-      <c r="F5" s="19">
+      <c r="F5" s="20">
         <v>9600</v>
       </c>
-      <c r="G5" s="19">
+      <c r="G5" s="20">
         <v>9600</v>
       </c>
-      <c r="H5" s="19">
+      <c r="H5" s="20">
         <v>9600</v>
       </c>
-      <c r="I5" s="19">
+      <c r="I5" s="20">
         <v>9600</v>
       </c>
-      <c r="J5" s="19">
+      <c r="J5" s="20">
         <v>9600</v>
       </c>
-      <c r="K5" s="19">
+      <c r="K5" s="20">
         <v>9600</v>
       </c>
-      <c r="L5" s="19">
-        <v>0</v>
-      </c>
-      <c r="M5" s="19">
-        <v>0</v>
-      </c>
-      <c r="N5" s="19">
+      <c r="L5" s="20">
+        <v>0</v>
+      </c>
+      <c r="M5" s="20">
+        <v>0</v>
+      </c>
+      <c r="N5" s="20">
         <f>SUM(B5:M5)</f>
         <v>80000</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="B6" s="19">
+      <c r="B6" s="20">
         <v>14400</v>
       </c>
-      <c r="C6" s="19">
+      <c r="C6" s="20">
         <v>14400</v>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="20">
         <v>14400</v>
       </c>
-      <c r="E6" s="19">
+      <c r="E6" s="20">
         <v>14400</v>
       </c>
-      <c r="F6" s="19">
+      <c r="F6" s="20">
         <v>14400</v>
       </c>
-      <c r="G6" s="19">
+      <c r="G6" s="20">
         <v>14400</v>
       </c>
-      <c r="H6" s="19">
+      <c r="H6" s="20">
         <v>14400</v>
       </c>
-      <c r="I6" s="19">
+      <c r="I6" s="20">
         <v>14400</v>
       </c>
-      <c r="J6" s="19">
+      <c r="J6" s="20">
         <v>14400</v>
       </c>
-      <c r="K6" s="19">
+      <c r="K6" s="20">
         <v>14400</v>
       </c>
-      <c r="L6" s="19">
-        <v>0</v>
-      </c>
-      <c r="M6" s="19">
-        <v>0</v>
-      </c>
-      <c r="N6" s="19">
+      <c r="L6" s="20">
+        <v>0</v>
+      </c>
+      <c r="M6" s="20">
+        <v>0</v>
+      </c>
+      <c r="N6" s="20">
         <f>SUM(B6:M6)</f>
         <v>120000</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="B7" s="19">
+      <c r="B7" s="20">
         <v>10000</v>
       </c>
-      <c r="C7" s="19">
+      <c r="C7" s="20">
         <v>10000</v>
       </c>
-      <c r="D7" s="19">
+      <c r="D7" s="20">
         <v>10000</v>
       </c>
-      <c r="E7" s="19">
+      <c r="E7" s="20">
         <v>10000</v>
       </c>
-      <c r="F7" s="19">
+      <c r="F7" s="20">
         <v>10000</v>
       </c>
-      <c r="G7" s="19">
+      <c r="G7" s="20">
         <v>10000</v>
       </c>
-      <c r="H7" s="19">
+      <c r="H7" s="20">
         <v>10000</v>
       </c>
-      <c r="I7" s="19">
+      <c r="I7" s="20">
         <v>10000</v>
       </c>
-      <c r="J7" s="19">
+      <c r="J7" s="20">
         <v>10000</v>
       </c>
-      <c r="K7" s="19">
+      <c r="K7" s="20">
         <v>10000</v>
       </c>
-      <c r="L7" s="19">
-        <v>0</v>
-      </c>
-      <c r="M7" s="19">
-        <v>0</v>
-      </c>
-      <c r="N7" s="19">
+      <c r="L7" s="20">
+        <v>0</v>
+      </c>
+      <c r="M7" s="20">
+        <v>0</v>
+      </c>
+      <c r="N7" s="20">
         <f>SUM(B7:M7)</f>
         <v>83333</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="B8" s="19">
+      <c r="B8" s="20">
         <v>3000</v>
       </c>
-      <c r="C8" s="19">
+      <c r="C8" s="20">
         <v>3000</v>
       </c>
-      <c r="D8" s="19">
+      <c r="D8" s="20">
         <v>3000</v>
       </c>
-      <c r="E8" s="19">
+      <c r="E8" s="20">
         <v>3000</v>
       </c>
-      <c r="F8" s="19">
+      <c r="F8" s="20">
         <v>3000</v>
       </c>
-      <c r="G8" s="19">
+      <c r="G8" s="20">
         <v>3000</v>
       </c>
-      <c r="H8" s="19">
+      <c r="H8" s="20">
         <v>3000</v>
       </c>
-      <c r="I8" s="19">
+      <c r="I8" s="20">
         <v>3000</v>
       </c>
-      <c r="J8" s="19">
+      <c r="J8" s="20">
         <v>3000</v>
       </c>
-      <c r="K8" s="19">
+      <c r="K8" s="20">
         <v>3000</v>
       </c>
-      <c r="L8" s="19">
-        <v>0</v>
-      </c>
-      <c r="M8" s="19">
-        <v>0</v>
-      </c>
-      <c r="N8" s="19">
+      <c r="L8" s="20">
+        <v>0</v>
+      </c>
+      <c r="M8" s="20">
+        <v>0</v>
+      </c>
+      <c r="N8" s="20">
         <f>SUM(B8:M8)</f>
         <v>25000</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="11" t="s">
+      <c r="A9" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="B9" s="19">
+      <c r="B9" s="20">
         <v>3600</v>
       </c>
-      <c r="C9" s="19">
+      <c r="C9" s="20">
         <v>3600</v>
       </c>
-      <c r="D9" s="19">
+      <c r="D9" s="20">
         <v>3600</v>
       </c>
-      <c r="E9" s="19">
+      <c r="E9" s="20">
         <v>3600</v>
       </c>
-      <c r="F9" s="19">
+      <c r="F9" s="20">
         <v>3600</v>
       </c>
-      <c r="G9" s="19">
+      <c r="G9" s="20">
         <v>3600</v>
       </c>
-      <c r="H9" s="19">
+      <c r="H9" s="20">
         <v>3600</v>
       </c>
-      <c r="I9" s="19">
+      <c r="I9" s="20">
         <v>3600</v>
       </c>
-      <c r="J9" s="19">
+      <c r="J9" s="20">
         <v>3600</v>
       </c>
-      <c r="K9" s="19">
+      <c r="K9" s="20">
         <v>3600</v>
       </c>
-      <c r="L9" s="19">
-        <v>0</v>
-      </c>
-      <c r="M9" s="19">
-        <v>0</v>
-      </c>
-      <c r="N9" s="19">
+      <c r="L9" s="20">
+        <v>0</v>
+      </c>
+      <c r="M9" s="20">
+        <v>0</v>
+      </c>
+      <c r="N9" s="20">
         <f>SUM(B9:M9)</f>
         <v>30000</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="10" t="s">
+      <c r="A10" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="B10" s="26">
+      <c r="B10" s="27">
         <f>SUM(B4:B9)</f>
         <v>154600</v>
       </c>
-      <c r="C10" s="26">
+      <c r="C10" s="27">
         <f>SUM(C4:C9)</f>
         <v>154600</v>
       </c>
-      <c r="D10" s="26">
+      <c r="D10" s="27">
         <f>SUM(D4:D9)</f>
         <v>154600</v>
       </c>
-      <c r="E10" s="26">
+      <c r="E10" s="27">
         <f>SUM(E4:E9)</f>
         <v>154600</v>
       </c>
-      <c r="F10" s="26">
+      <c r="F10" s="27">
         <f>SUM(F4:F9)</f>
         <v>154600</v>
       </c>
-      <c r="G10" s="26">
+      <c r="G10" s="27">
         <f>SUM(G4:G9)</f>
         <v>154600</v>
       </c>
-      <c r="H10" s="26">
+      <c r="H10" s="27">
         <f>SUM(H4:H9)</f>
         <v>154600</v>
       </c>
-      <c r="I10" s="26">
+      <c r="I10" s="27">
         <f>SUM(I4:I9)</f>
         <v>154600</v>
       </c>
-      <c r="J10" s="26">
+      <c r="J10" s="27">
         <f>SUM(J4:J9)</f>
         <v>154600</v>
       </c>
-      <c r="K10" s="26">
+      <c r="K10" s="27">
         <f>SUM(K4:K9)</f>
         <v>154600</v>
       </c>
-      <c r="L10" s="26" t="str">
+      <c r="L10" s="27" t="str">
         <f>SUM(L4:L9)</f>
         <v>0</v>
       </c>
-      <c r="M10" s="26" t="str">
+      <c r="M10" s="27" t="str">
         <f>SUM(M4:M9)</f>
         <v>0</v>
       </c>
-      <c r="N10" s="26">
+      <c r="N10" s="27">
         <f>SUM(B10:M10)</f>
         <v>1546000</v>
       </c>
@@ -5007,481 +5011,481 @@
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" s="10" t="s">
+      <c r="A12" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="B12" s="10"/>
-      <c r="C12" s="10"/>
-      <c r="D12" s="10"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="10"/>
-      <c r="H12" s="10"/>
-      <c r="I12" s="10"/>
-      <c r="J12" s="10"/>
-      <c r="K12" s="10"/>
-      <c r="L12" s="10"/>
-      <c r="M12" s="10"/>
-      <c r="N12" s="10"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="11"/>
+      <c r="J12" s="11"/>
+      <c r="K12" s="11"/>
+      <c r="L12" s="11"/>
+      <c r="M12" s="11"/>
+      <c r="N12" s="11"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" s="11" t="s">
+      <c r="A13" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="B13" s="19">
+      <c r="B13" s="20">
         <v>12435</v>
       </c>
-      <c r="C13" s="19">
+      <c r="C13" s="20">
         <v>12435</v>
       </c>
-      <c r="D13" s="19">
+      <c r="D13" s="20">
         <v>12435</v>
       </c>
-      <c r="E13" s="19">
+      <c r="E13" s="20">
         <v>12435</v>
       </c>
-      <c r="F13" s="19">
+      <c r="F13" s="20">
         <v>12435</v>
       </c>
-      <c r="G13" s="19">
+      <c r="G13" s="20">
         <v>12435</v>
       </c>
-      <c r="H13" s="19">
+      <c r="H13" s="20">
         <v>12435</v>
       </c>
-      <c r="I13" s="19">
+      <c r="I13" s="20">
         <v>12435</v>
       </c>
-      <c r="J13" s="19">
+      <c r="J13" s="20">
         <v>12435</v>
       </c>
-      <c r="K13" s="19">
+      <c r="K13" s="20">
         <v>12435</v>
       </c>
-      <c r="L13" s="19">
-        <v>0</v>
-      </c>
-      <c r="M13" s="19">
-        <v>0</v>
-      </c>
-      <c r="N13" s="19">
+      <c r="L13" s="20">
+        <v>0</v>
+      </c>
+      <c r="M13" s="20">
+        <v>0</v>
+      </c>
+      <c r="N13" s="20">
         <f>SUM(B13:M13)</f>
         <v>124346</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A14" s="11" t="s">
+      <c r="A14" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="B14" s="19">
+      <c r="B14" s="20">
         <v>10174</v>
       </c>
-      <c r="C14" s="19">
+      <c r="C14" s="20">
         <v>10174</v>
       </c>
-      <c r="D14" s="19">
+      <c r="D14" s="20">
         <v>10174</v>
       </c>
-      <c r="E14" s="19">
+      <c r="E14" s="20">
         <v>10174</v>
       </c>
-      <c r="F14" s="19">
+      <c r="F14" s="20">
         <v>10174</v>
       </c>
-      <c r="G14" s="19">
+      <c r="G14" s="20">
         <v>10174</v>
       </c>
-      <c r="H14" s="19">
+      <c r="H14" s="20">
         <v>10174</v>
       </c>
-      <c r="I14" s="19">
+      <c r="I14" s="20">
         <v>10174</v>
       </c>
-      <c r="J14" s="19">
+      <c r="J14" s="20">
         <v>10174</v>
       </c>
-      <c r="K14" s="19">
+      <c r="K14" s="20">
         <v>10174</v>
       </c>
-      <c r="L14" s="19">
-        <v>0</v>
-      </c>
-      <c r="M14" s="19">
-        <v>0</v>
-      </c>
-      <c r="N14" s="19">
+      <c r="L14" s="20">
+        <v>0</v>
+      </c>
+      <c r="M14" s="20">
+        <v>0</v>
+      </c>
+      <c r="N14" s="20">
         <f>SUM(B14:M14)</f>
         <v>101738</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" s="11" t="s">
+      <c r="A15" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="B15" s="19">
+      <c r="B15" s="20">
         <v>8139</v>
       </c>
-      <c r="C15" s="19">
+      <c r="C15" s="20">
         <v>8139</v>
       </c>
-      <c r="D15" s="19">
+      <c r="D15" s="20">
         <v>8139</v>
       </c>
-      <c r="E15" s="19">
+      <c r="E15" s="20">
         <v>8139</v>
       </c>
-      <c r="F15" s="19">
+      <c r="F15" s="20">
         <v>8139</v>
       </c>
-      <c r="G15" s="19">
+      <c r="G15" s="20">
         <v>8139</v>
       </c>
-      <c r="H15" s="19">
+      <c r="H15" s="20">
         <v>8139</v>
       </c>
-      <c r="I15" s="19">
+      <c r="I15" s="20">
         <v>8139</v>
       </c>
-      <c r="J15" s="19">
+      <c r="J15" s="20">
         <v>8139</v>
       </c>
-      <c r="K15" s="19">
+      <c r="K15" s="20">
         <v>8139</v>
       </c>
-      <c r="L15" s="19">
-        <v>0</v>
-      </c>
-      <c r="M15" s="19">
-        <v>0</v>
-      </c>
-      <c r="N15" s="19">
+      <c r="L15" s="20">
+        <v>0</v>
+      </c>
+      <c r="M15" s="20">
+        <v>0</v>
+      </c>
+      <c r="N15" s="20">
         <f>SUM(B15:M15)</f>
         <v>81390</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A16" s="11" t="s">
+      <c r="A16" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="B16" s="19">
+      <c r="B16" s="20">
         <v>35269</v>
       </c>
-      <c r="C16" s="19">
+      <c r="C16" s="20">
         <v>35269</v>
       </c>
-      <c r="D16" s="19">
+      <c r="D16" s="20">
         <v>35269</v>
       </c>
-      <c r="E16" s="19">
+      <c r="E16" s="20">
         <v>35269</v>
       </c>
-      <c r="F16" s="19">
+      <c r="F16" s="20">
         <v>35269</v>
       </c>
-      <c r="G16" s="19">
+      <c r="G16" s="20">
         <v>35269</v>
       </c>
-      <c r="H16" s="19">
+      <c r="H16" s="20">
         <v>35269</v>
       </c>
-      <c r="I16" s="19">
+      <c r="I16" s="20">
         <v>35269</v>
       </c>
-      <c r="J16" s="19">
+      <c r="J16" s="20">
         <v>35269</v>
       </c>
-      <c r="K16" s="19">
+      <c r="K16" s="20">
         <v>35269</v>
       </c>
-      <c r="L16" s="19">
-        <v>0</v>
-      </c>
-      <c r="M16" s="19">
-        <v>0</v>
-      </c>
-      <c r="N16" s="19">
+      <c r="L16" s="20">
+        <v>0</v>
+      </c>
+      <c r="M16" s="20">
+        <v>0</v>
+      </c>
+      <c r="N16" s="20">
         <f>SUM(B16:M16)</f>
         <v>352690</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A17" s="11" t="s">
+      <c r="A17" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="B17" s="19">
+      <c r="B17" s="20">
         <v>6217</v>
       </c>
-      <c r="C17" s="19">
+      <c r="C17" s="20">
         <v>6217</v>
       </c>
-      <c r="D17" s="19">
+      <c r="D17" s="20">
         <v>6217</v>
       </c>
-      <c r="E17" s="19">
+      <c r="E17" s="20">
         <v>6217</v>
       </c>
-      <c r="F17" s="19">
+      <c r="F17" s="20">
         <v>6217</v>
       </c>
-      <c r="G17" s="19">
+      <c r="G17" s="20">
         <v>6217</v>
       </c>
-      <c r="H17" s="19">
+      <c r="H17" s="20">
         <v>6217</v>
       </c>
-      <c r="I17" s="19">
+      <c r="I17" s="20">
         <v>6217</v>
       </c>
-      <c r="J17" s="19">
+      <c r="J17" s="20">
         <v>6217</v>
       </c>
-      <c r="K17" s="19">
+      <c r="K17" s="20">
         <v>6217</v>
       </c>
-      <c r="L17" s="19">
-        <v>0</v>
-      </c>
-      <c r="M17" s="19">
-        <v>0</v>
-      </c>
-      <c r="N17" s="19">
+      <c r="L17" s="20">
+        <v>0</v>
+      </c>
+      <c r="M17" s="20">
+        <v>0</v>
+      </c>
+      <c r="N17" s="20">
         <f>SUM(B17:M17)</f>
         <v>62173</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" s="11" t="s">
+      <c r="A18" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="B18" s="19">
+      <c r="B18" s="20">
         <v>9574</v>
       </c>
-      <c r="C18" s="19">
+      <c r="C18" s="20">
         <v>9574</v>
       </c>
-      <c r="D18" s="19">
+      <c r="D18" s="20">
         <v>9574</v>
       </c>
-      <c r="E18" s="19">
+      <c r="E18" s="20">
         <v>9574</v>
       </c>
-      <c r="F18" s="19">
+      <c r="F18" s="20">
         <v>9574</v>
       </c>
-      <c r="G18" s="19">
+      <c r="G18" s="20">
         <v>9574</v>
       </c>
-      <c r="H18" s="19">
+      <c r="H18" s="20">
         <v>9574</v>
       </c>
-      <c r="I18" s="19">
+      <c r="I18" s="20">
         <v>9574</v>
       </c>
-      <c r="J18" s="19">
+      <c r="J18" s="20">
         <v>9574</v>
       </c>
-      <c r="K18" s="19">
+      <c r="K18" s="20">
         <v>9574</v>
       </c>
-      <c r="L18" s="19">
-        <v>0</v>
-      </c>
-      <c r="M18" s="19">
-        <v>0</v>
-      </c>
-      <c r="N18" s="19">
+      <c r="L18" s="20">
+        <v>0</v>
+      </c>
+      <c r="M18" s="20">
+        <v>0</v>
+      </c>
+      <c r="N18" s="20">
         <f>SUM(B18:M18)</f>
         <v>95738</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A19" s="11" t="s">
+      <c r="A19" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="B19" s="19">
+      <c r="B19" s="20">
         <v>6217</v>
       </c>
-      <c r="C19" s="19">
+      <c r="C19" s="20">
         <v>6217</v>
       </c>
-      <c r="D19" s="19">
+      <c r="D19" s="20">
         <v>6217</v>
       </c>
-      <c r="E19" s="19">
+      <c r="E19" s="20">
         <v>6217</v>
       </c>
-      <c r="F19" s="19">
+      <c r="F19" s="20">
         <v>6217</v>
       </c>
-      <c r="G19" s="19">
+      <c r="G19" s="20">
         <v>6217</v>
       </c>
-      <c r="H19" s="19">
+      <c r="H19" s="20">
         <v>6217</v>
       </c>
-      <c r="I19" s="19">
+      <c r="I19" s="20">
         <v>6217</v>
       </c>
-      <c r="J19" s="19">
+      <c r="J19" s="20">
         <v>6217</v>
       </c>
-      <c r="K19" s="19">
+      <c r="K19" s="20">
         <v>6217</v>
       </c>
-      <c r="L19" s="19">
-        <v>0</v>
-      </c>
-      <c r="M19" s="19">
-        <v>0</v>
-      </c>
-      <c r="N19" s="19">
+      <c r="L19" s="20">
+        <v>0</v>
+      </c>
+      <c r="M19" s="20">
+        <v>0</v>
+      </c>
+      <c r="N19" s="20">
         <f>SUM(B19:M19)</f>
         <v>62173</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A20" s="11" t="s">
+      <c r="A20" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="B20" s="19">
+      <c r="B20" s="20">
         <v>8401</v>
       </c>
-      <c r="C20" s="19">
+      <c r="C20" s="20">
         <v>8401</v>
       </c>
-      <c r="D20" s="19">
+      <c r="D20" s="20">
         <v>8401</v>
       </c>
-      <c r="E20" s="19">
+      <c r="E20" s="20">
         <v>8401</v>
       </c>
-      <c r="F20" s="19">
+      <c r="F20" s="20">
         <v>8401</v>
       </c>
-      <c r="G20" s="19">
+      <c r="G20" s="20">
         <v>8401</v>
       </c>
-      <c r="H20" s="19">
+      <c r="H20" s="20">
         <v>8401</v>
       </c>
-      <c r="I20" s="19">
+      <c r="I20" s="20">
         <v>8401</v>
       </c>
-      <c r="J20" s="19">
+      <c r="J20" s="20">
         <v>8401</v>
       </c>
-      <c r="K20" s="19">
+      <c r="K20" s="20">
         <v>8401</v>
       </c>
-      <c r="L20" s="19">
-        <v>0</v>
-      </c>
-      <c r="M20" s="19">
-        <v>0</v>
-      </c>
-      <c r="N20" s="19">
+      <c r="L20" s="20">
+        <v>0</v>
+      </c>
+      <c r="M20" s="20">
+        <v>0</v>
+      </c>
+      <c r="N20" s="20">
         <f>SUM(B20:M20)</f>
         <v>84012</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A21" s="11" t="s">
+      <c r="A21" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="B21" s="19">
+      <c r="B21" s="20">
         <v>6217</v>
       </c>
-      <c r="C21" s="19">
+      <c r="C21" s="20">
         <v>6217</v>
       </c>
-      <c r="D21" s="19">
+      <c r="D21" s="20">
         <v>6217</v>
       </c>
-      <c r="E21" s="19">
+      <c r="E21" s="20">
         <v>6217</v>
       </c>
-      <c r="F21" s="19">
+      <c r="F21" s="20">
         <v>6217</v>
       </c>
-      <c r="G21" s="19">
+      <c r="G21" s="20">
         <v>6217</v>
       </c>
-      <c r="H21" s="19">
+      <c r="H21" s="20">
         <v>6217</v>
       </c>
-      <c r="I21" s="19">
+      <c r="I21" s="20">
         <v>6217</v>
       </c>
-      <c r="J21" s="19">
+      <c r="J21" s="20">
         <v>6217</v>
       </c>
-      <c r="K21" s="19">
+      <c r="K21" s="20">
         <v>6217</v>
       </c>
-      <c r="L21" s="19">
-        <v>0</v>
-      </c>
-      <c r="M21" s="19">
-        <v>0</v>
-      </c>
-      <c r="N21" s="19">
+      <c r="L21" s="20">
+        <v>0</v>
+      </c>
+      <c r="M21" s="20">
+        <v>0</v>
+      </c>
+      <c r="N21" s="20">
         <f>SUM(B21:M21)</f>
         <v>62173</v>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A22" s="10" t="s">
+      <c r="A22" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="B22" s="26">
+      <c r="B22" s="27">
         <f>SUM(B13:B21)</f>
         <v>102643</v>
       </c>
-      <c r="C22" s="26">
+      <c r="C22" s="27">
         <f>SUM(C13:C21)</f>
         <v>102643</v>
       </c>
-      <c r="D22" s="26">
+      <c r="D22" s="27">
         <f>SUM(D13:D21)</f>
         <v>102643</v>
       </c>
-      <c r="E22" s="26">
+      <c r="E22" s="27">
         <f>SUM(E13:E21)</f>
         <v>102643</v>
       </c>
-      <c r="F22" s="26">
+      <c r="F22" s="27">
         <f>SUM(F13:F21)</f>
         <v>102643</v>
       </c>
-      <c r="G22" s="26">
+      <c r="G22" s="27">
         <f>SUM(G13:G21)</f>
         <v>102643</v>
       </c>
-      <c r="H22" s="26">
+      <c r="H22" s="27">
         <f>SUM(H13:H21)</f>
         <v>102643</v>
       </c>
-      <c r="I22" s="26">
+      <c r="I22" s="27">
         <f>SUM(I13:I21)</f>
         <v>102643</v>
       </c>
-      <c r="J22" s="26">
+      <c r="J22" s="27">
         <f>SUM(J13:J21)</f>
         <v>102643</v>
       </c>
-      <c r="K22" s="26">
+      <c r="K22" s="27">
         <f>SUM(K13:K21)</f>
         <v>102643</v>
       </c>
-      <c r="L22" s="26" t="str">
+      <c r="L22" s="27" t="str">
         <f>SUM(L13:L21)</f>
         <v>0</v>
       </c>
-      <c r="M22" s="26" t="str">
+      <c r="M22" s="27" t="str">
         <f>SUM(M13:M21)</f>
         <v>0</v>
       </c>
-      <c r="N22" s="26">
+      <c r="N22" s="27">
         <f>SUM(B22:M22)</f>
         <v>1026431</v>
       </c>
@@ -5492,823 +5496,823 @@
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A24" s="10" t="s">
+      <c r="A24" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="B24" s="10"/>
-      <c r="C24" s="10"/>
-      <c r="D24" s="10"/>
-      <c r="E24" s="10"/>
-      <c r="F24" s="10"/>
-      <c r="G24" s="10"/>
-      <c r="H24" s="10"/>
-      <c r="I24" s="10"/>
-      <c r="J24" s="10"/>
-      <c r="K24" s="10"/>
-      <c r="L24" s="10"/>
-      <c r="M24" s="10"/>
-      <c r="N24" s="10"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="11"/>
+      <c r="H24" s="11"/>
+      <c r="I24" s="11"/>
+      <c r="J24" s="11"/>
+      <c r="K24" s="11"/>
+      <c r="L24" s="11"/>
+      <c r="M24" s="11"/>
+      <c r="N24" s="11"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A25" s="11" t="s">
+      <c r="A25" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="B25" s="11"/>
-      <c r="C25" s="11"/>
-      <c r="D25" s="11"/>
-      <c r="E25" s="11"/>
-      <c r="F25" s="11"/>
-      <c r="G25" s="11"/>
-      <c r="H25" s="11"/>
-      <c r="I25" s="11"/>
-      <c r="J25" s="11"/>
-      <c r="K25" s="11"/>
-      <c r="L25" s="11"/>
-      <c r="M25" s="11"/>
-      <c r="N25" s="11"/>
+      <c r="B25" s="12"/>
+      <c r="C25" s="12"/>
+      <c r="D25" s="12"/>
+      <c r="E25" s="12"/>
+      <c r="F25" s="12"/>
+      <c r="G25" s="12"/>
+      <c r="H25" s="12"/>
+      <c r="I25" s="12"/>
+      <c r="J25" s="12"/>
+      <c r="K25" s="12"/>
+      <c r="L25" s="12"/>
+      <c r="M25" s="12"/>
+      <c r="N25" s="12"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A26" s="11" t="s">
+      <c r="A26" s="12" t="s">
         <v>218</v>
       </c>
-      <c r="B26" s="19">
+      <c r="B26" s="20">
         <v>7000</v>
       </c>
-      <c r="C26" s="19">
+      <c r="C26" s="20">
         <v>7000</v>
       </c>
-      <c r="D26" s="19">
+      <c r="D26" s="20">
         <v>7000</v>
       </c>
-      <c r="E26" s="19">
+      <c r="E26" s="20">
         <v>7000</v>
       </c>
-      <c r="F26" s="19">
+      <c r="F26" s="20">
         <v>7000</v>
       </c>
-      <c r="G26" s="19">
+      <c r="G26" s="20">
         <v>7000</v>
       </c>
-      <c r="H26" s="19">
+      <c r="H26" s="20">
         <v>7000</v>
       </c>
-      <c r="I26" s="19">
+      <c r="I26" s="20">
         <v>7000</v>
       </c>
-      <c r="J26" s="19">
+      <c r="J26" s="20">
         <v>7000</v>
       </c>
-      <c r="K26" s="19">
+      <c r="K26" s="20">
         <v>7000</v>
       </c>
-      <c r="L26" s="19">
-        <v>0</v>
-      </c>
-      <c r="M26" s="19">
-        <v>0</v>
-      </c>
-      <c r="N26" s="19">
+      <c r="L26" s="20">
+        <v>0</v>
+      </c>
+      <c r="M26" s="20">
+        <v>0</v>
+      </c>
+      <c r="N26" s="20">
         <f>SUM(B26:M26)</f>
         <v>70000</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A27" s="27" t="s">
+      <c r="A27" s="28" t="s">
         <v>159</v>
       </c>
-      <c r="B27" s="28">
+      <c r="B27" s="29">
         <v>7000</v>
       </c>
-      <c r="C27" s="28">
+      <c r="C27" s="29">
         <v>7000</v>
       </c>
-      <c r="D27" s="28">
+      <c r="D27" s="29">
         <v>7000</v>
       </c>
-      <c r="E27" s="28">
+      <c r="E27" s="29">
         <v>7000</v>
       </c>
-      <c r="F27" s="28">
+      <c r="F27" s="29">
         <v>7000</v>
       </c>
-      <c r="G27" s="28">
+      <c r="G27" s="29">
         <v>7000</v>
       </c>
-      <c r="H27" s="28">
+      <c r="H27" s="29">
         <v>7000</v>
       </c>
-      <c r="I27" s="28">
+      <c r="I27" s="29">
         <v>7000</v>
       </c>
-      <c r="J27" s="28">
+      <c r="J27" s="29">
         <v>7000</v>
       </c>
-      <c r="K27" s="28">
+      <c r="K27" s="29">
         <v>7000</v>
       </c>
-      <c r="L27" s="28">
-        <v>0</v>
-      </c>
-      <c r="M27" s="28">
-        <v>0</v>
-      </c>
-      <c r="N27" s="28">
+      <c r="L27" s="29">
+        <v>0</v>
+      </c>
+      <c r="M27" s="29">
+        <v>0</v>
+      </c>
+      <c r="N27" s="29">
         <f>SUM(B27:M27)</f>
         <v>70000</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A28" s="11" t="s">
+      <c r="A28" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="B28" s="11"/>
-      <c r="C28" s="11"/>
-      <c r="D28" s="11"/>
-      <c r="E28" s="11"/>
-      <c r="F28" s="11"/>
-      <c r="G28" s="11"/>
-      <c r="H28" s="11"/>
-      <c r="I28" s="11"/>
-      <c r="J28" s="11"/>
-      <c r="K28" s="11"/>
-      <c r="L28" s="11"/>
-      <c r="M28" s="11"/>
-      <c r="N28" s="11"/>
+      <c r="B28" s="12"/>
+      <c r="C28" s="12"/>
+      <c r="D28" s="12"/>
+      <c r="E28" s="12"/>
+      <c r="F28" s="12"/>
+      <c r="G28" s="12"/>
+      <c r="H28" s="12"/>
+      <c r="I28" s="12"/>
+      <c r="J28" s="12"/>
+      <c r="K28" s="12"/>
+      <c r="L28" s="12"/>
+      <c r="M28" s="12"/>
+      <c r="N28" s="12"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A29" s="11" t="s">
+      <c r="A29" s="12" t="s">
         <v>219</v>
       </c>
-      <c r="B29" s="19">
+      <c r="B29" s="20">
         <v>5000</v>
       </c>
-      <c r="C29" s="19">
+      <c r="C29" s="20">
         <v>5000</v>
       </c>
-      <c r="D29" s="19">
+      <c r="D29" s="20">
         <v>5000</v>
       </c>
-      <c r="E29" s="19">
+      <c r="E29" s="20">
         <v>5000</v>
       </c>
-      <c r="F29" s="19">
+      <c r="F29" s="20">
         <v>5000</v>
       </c>
-      <c r="G29" s="19">
+      <c r="G29" s="20">
         <v>5000</v>
       </c>
-      <c r="H29" s="19">
+      <c r="H29" s="20">
         <v>5000</v>
       </c>
-      <c r="I29" s="19">
+      <c r="I29" s="20">
         <v>5000</v>
       </c>
-      <c r="J29" s="19">
+      <c r="J29" s="20">
         <v>5000</v>
       </c>
-      <c r="K29" s="19">
+      <c r="K29" s="20">
         <v>5000</v>
       </c>
-      <c r="L29" s="19">
-        <v>0</v>
-      </c>
-      <c r="M29" s="19">
-        <v>0</v>
-      </c>
-      <c r="N29" s="19">
+      <c r="L29" s="20">
+        <v>0</v>
+      </c>
+      <c r="M29" s="20">
+        <v>0</v>
+      </c>
+      <c r="N29" s="20">
         <f>SUM(B29:M29)</f>
         <v>50000</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A30" s="27" t="s">
+      <c r="A30" s="28" t="s">
         <v>161</v>
       </c>
-      <c r="B30" s="28">
+      <c r="B30" s="29">
         <v>5000</v>
       </c>
-      <c r="C30" s="28">
+      <c r="C30" s="29">
         <v>5000</v>
       </c>
-      <c r="D30" s="28">
+      <c r="D30" s="29">
         <v>5000</v>
       </c>
-      <c r="E30" s="28">
+      <c r="E30" s="29">
         <v>5000</v>
       </c>
-      <c r="F30" s="28">
+      <c r="F30" s="29">
         <v>5000</v>
       </c>
-      <c r="G30" s="28">
+      <c r="G30" s="29">
         <v>5000</v>
       </c>
-      <c r="H30" s="28">
+      <c r="H30" s="29">
         <v>5000</v>
       </c>
-      <c r="I30" s="28">
+      <c r="I30" s="29">
         <v>5000</v>
       </c>
-      <c r="J30" s="28">
+      <c r="J30" s="29">
         <v>5000</v>
       </c>
-      <c r="K30" s="28">
+      <c r="K30" s="29">
         <v>5000</v>
       </c>
-      <c r="L30" s="28">
-        <v>0</v>
-      </c>
-      <c r="M30" s="28">
-        <v>0</v>
-      </c>
-      <c r="N30" s="28">
+      <c r="L30" s="29">
+        <v>0</v>
+      </c>
+      <c r="M30" s="29">
+        <v>0</v>
+      </c>
+      <c r="N30" s="29">
         <f>SUM(B30:M30)</f>
         <v>50000</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A31" s="11" t="s">
+      <c r="A31" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="B31" s="11"/>
-      <c r="C31" s="11"/>
-      <c r="D31" s="11"/>
-      <c r="E31" s="11"/>
-      <c r="F31" s="11"/>
-      <c r="G31" s="11"/>
-      <c r="H31" s="11"/>
-      <c r="I31" s="11"/>
-      <c r="J31" s="11"/>
-      <c r="K31" s="11"/>
-      <c r="L31" s="11"/>
-      <c r="M31" s="11"/>
-      <c r="N31" s="11"/>
+      <c r="B31" s="12"/>
+      <c r="C31" s="12"/>
+      <c r="D31" s="12"/>
+      <c r="E31" s="12"/>
+      <c r="F31" s="12"/>
+      <c r="G31" s="12"/>
+      <c r="H31" s="12"/>
+      <c r="I31" s="12"/>
+      <c r="J31" s="12"/>
+      <c r="K31" s="12"/>
+      <c r="L31" s="12"/>
+      <c r="M31" s="12"/>
+      <c r="N31" s="12"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A32" s="11" t="s">
+      <c r="A32" s="12" t="s">
         <v>220</v>
       </c>
-      <c r="B32" s="19">
+      <c r="B32" s="20">
         <v>18000</v>
       </c>
-      <c r="C32" s="19">
+      <c r="C32" s="20">
         <v>18000</v>
       </c>
-      <c r="D32" s="19">
+      <c r="D32" s="20">
         <v>18000</v>
       </c>
-      <c r="E32" s="19">
+      <c r="E32" s="20">
         <v>18000</v>
       </c>
-      <c r="F32" s="19">
+      <c r="F32" s="20">
         <v>18000</v>
       </c>
-      <c r="G32" s="19">
+      <c r="G32" s="20">
         <v>18000</v>
       </c>
-      <c r="H32" s="19">
+      <c r="H32" s="20">
         <v>18000</v>
       </c>
-      <c r="I32" s="19">
+      <c r="I32" s="20">
         <v>18000</v>
       </c>
-      <c r="J32" s="19">
+      <c r="J32" s="20">
         <v>18000</v>
       </c>
-      <c r="K32" s="19">
+      <c r="K32" s="20">
         <v>18000</v>
       </c>
-      <c r="L32" s="19">
-        <v>0</v>
-      </c>
-      <c r="M32" s="19">
-        <v>0</v>
-      </c>
-      <c r="N32" s="19">
+      <c r="L32" s="20">
+        <v>0</v>
+      </c>
+      <c r="M32" s="20">
+        <v>0</v>
+      </c>
+      <c r="N32" s="20">
         <f>SUM(B32:M32)</f>
         <v>180000</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A33" s="11" t="s">
+      <c r="A33" s="12" t="s">
         <v>221</v>
       </c>
-      <c r="B33" s="19">
+      <c r="B33" s="20">
         <v>2500</v>
       </c>
-      <c r="C33" s="19">
+      <c r="C33" s="20">
         <v>2500</v>
       </c>
-      <c r="D33" s="19">
+      <c r="D33" s="20">
         <v>2500</v>
       </c>
-      <c r="E33" s="19">
+      <c r="E33" s="20">
         <v>2500</v>
       </c>
-      <c r="F33" s="19">
+      <c r="F33" s="20">
         <v>2500</v>
       </c>
-      <c r="G33" s="19">
+      <c r="G33" s="20">
         <v>2500</v>
       </c>
-      <c r="H33" s="19">
+      <c r="H33" s="20">
         <v>2500</v>
       </c>
-      <c r="I33" s="19">
+      <c r="I33" s="20">
         <v>2500</v>
       </c>
-      <c r="J33" s="19">
+      <c r="J33" s="20">
         <v>2500</v>
       </c>
-      <c r="K33" s="19">
+      <c r="K33" s="20">
         <v>2500</v>
       </c>
-      <c r="L33" s="19">
-        <v>0</v>
-      </c>
-      <c r="M33" s="19">
-        <v>0</v>
-      </c>
-      <c r="N33" s="19">
+      <c r="L33" s="20">
+        <v>0</v>
+      </c>
+      <c r="M33" s="20">
+        <v>0</v>
+      </c>
+      <c r="N33" s="20">
         <f>SUM(B33:M33)</f>
         <v>25000</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A34" s="11" t="s">
+      <c r="A34" s="12" t="s">
         <v>222</v>
       </c>
-      <c r="B34" s="19">
+      <c r="B34" s="20">
         <v>1500</v>
       </c>
-      <c r="C34" s="19">
+      <c r="C34" s="20">
         <v>1500</v>
       </c>
-      <c r="D34" s="19">
+      <c r="D34" s="20">
         <v>1500</v>
       </c>
-      <c r="E34" s="19">
+      <c r="E34" s="20">
         <v>1500</v>
       </c>
-      <c r="F34" s="19">
+      <c r="F34" s="20">
         <v>1500</v>
       </c>
-      <c r="G34" s="19">
+      <c r="G34" s="20">
         <v>1500</v>
       </c>
-      <c r="H34" s="19">
+      <c r="H34" s="20">
         <v>1500</v>
       </c>
-      <c r="I34" s="19">
+      <c r="I34" s="20">
         <v>1500</v>
       </c>
-      <c r="J34" s="19">
+      <c r="J34" s="20">
         <v>1500</v>
       </c>
-      <c r="K34" s="19">
+      <c r="K34" s="20">
         <v>1500</v>
       </c>
-      <c r="L34" s="19">
-        <v>0</v>
-      </c>
-      <c r="M34" s="19">
-        <v>0</v>
-      </c>
-      <c r="N34" s="19">
+      <c r="L34" s="20">
+        <v>0</v>
+      </c>
+      <c r="M34" s="20">
+        <v>0</v>
+      </c>
+      <c r="N34" s="20">
         <f>SUM(B34:M34)</f>
         <v>15000</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A35" s="11" t="s">
+      <c r="A35" s="12" t="s">
         <v>223</v>
       </c>
-      <c r="B35" s="19">
+      <c r="B35" s="20">
         <v>1500</v>
       </c>
-      <c r="C35" s="19">
+      <c r="C35" s="20">
         <v>1500</v>
       </c>
-      <c r="D35" s="19">
+      <c r="D35" s="20">
         <v>1500</v>
       </c>
-      <c r="E35" s="19">
+      <c r="E35" s="20">
         <v>1500</v>
       </c>
-      <c r="F35" s="19">
+      <c r="F35" s="20">
         <v>1500</v>
       </c>
-      <c r="G35" s="19">
+      <c r="G35" s="20">
         <v>1500</v>
       </c>
-      <c r="H35" s="19">
+      <c r="H35" s="20">
         <v>1500</v>
       </c>
-      <c r="I35" s="19">
+      <c r="I35" s="20">
         <v>1500</v>
       </c>
-      <c r="J35" s="19">
+      <c r="J35" s="20">
         <v>1500</v>
       </c>
-      <c r="K35" s="19">
+      <c r="K35" s="20">
         <v>1500</v>
       </c>
-      <c r="L35" s="19">
-        <v>0</v>
-      </c>
-      <c r="M35" s="19">
-        <v>0</v>
-      </c>
-      <c r="N35" s="19">
+      <c r="L35" s="20">
+        <v>0</v>
+      </c>
+      <c r="M35" s="20">
+        <v>0</v>
+      </c>
+      <c r="N35" s="20">
         <f>SUM(B35:M35)</f>
         <v>15000</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A36" s="27" t="s">
+      <c r="A36" s="28" t="s">
         <v>166</v>
       </c>
-      <c r="B36" s="28">
+      <c r="B36" s="29">
         <v>23500</v>
       </c>
-      <c r="C36" s="28">
+      <c r="C36" s="29">
         <v>23500</v>
       </c>
-      <c r="D36" s="28">
+      <c r="D36" s="29">
         <v>23500</v>
       </c>
-      <c r="E36" s="28">
+      <c r="E36" s="29">
         <v>23500</v>
       </c>
-      <c r="F36" s="28">
+      <c r="F36" s="29">
         <v>23500</v>
       </c>
-      <c r="G36" s="28">
+      <c r="G36" s="29">
         <v>23500</v>
       </c>
-      <c r="H36" s="28">
+      <c r="H36" s="29">
         <v>23500</v>
       </c>
-      <c r="I36" s="28">
+      <c r="I36" s="29">
         <v>23500</v>
       </c>
-      <c r="J36" s="28">
+      <c r="J36" s="29">
         <v>23500</v>
       </c>
-      <c r="K36" s="28">
+      <c r="K36" s="29">
         <v>23500</v>
       </c>
-      <c r="L36" s="28">
-        <v>0</v>
-      </c>
-      <c r="M36" s="28">
-        <v>0</v>
-      </c>
-      <c r="N36" s="28">
+      <c r="L36" s="29">
+        <v>0</v>
+      </c>
+      <c r="M36" s="29">
+        <v>0</v>
+      </c>
+      <c r="N36" s="29">
         <f>SUM(B36:M36)</f>
         <v>235000</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A37" s="11" t="s">
+      <c r="A37" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="B37" s="11"/>
-      <c r="C37" s="11"/>
-      <c r="D37" s="11"/>
-      <c r="E37" s="11"/>
-      <c r="F37" s="11"/>
-      <c r="G37" s="11"/>
-      <c r="H37" s="11"/>
-      <c r="I37" s="11"/>
-      <c r="J37" s="11"/>
-      <c r="K37" s="11"/>
-      <c r="L37" s="11"/>
-      <c r="M37" s="11"/>
-      <c r="N37" s="11"/>
+      <c r="B37" s="12"/>
+      <c r="C37" s="12"/>
+      <c r="D37" s="12"/>
+      <c r="E37" s="12"/>
+      <c r="F37" s="12"/>
+      <c r="G37" s="12"/>
+      <c r="H37" s="12"/>
+      <c r="I37" s="12"/>
+      <c r="J37" s="12"/>
+      <c r="K37" s="12"/>
+      <c r="L37" s="12"/>
+      <c r="M37" s="12"/>
+      <c r="N37" s="12"/>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A38" s="11" t="s">
+      <c r="A38" s="12" t="s">
         <v>224</v>
       </c>
-      <c r="B38" s="19">
+      <c r="B38" s="20">
         <v>2083</v>
       </c>
-      <c r="C38" s="19">
+      <c r="C38" s="20">
         <v>2083</v>
       </c>
-      <c r="D38" s="19">
+      <c r="D38" s="20">
         <v>2083</v>
       </c>
-      <c r="E38" s="19">
+      <c r="E38" s="20">
         <v>2083</v>
       </c>
-      <c r="F38" s="19">
+      <c r="F38" s="20">
         <v>2083</v>
       </c>
-      <c r="G38" s="19">
+      <c r="G38" s="20">
         <v>2083</v>
       </c>
-      <c r="H38" s="19">
+      <c r="H38" s="20">
         <v>2083</v>
       </c>
-      <c r="I38" s="19">
+      <c r="I38" s="20">
         <v>2083</v>
       </c>
-      <c r="J38" s="19">
+      <c r="J38" s="20">
         <v>2083</v>
       </c>
-      <c r="K38" s="19">
+      <c r="K38" s="20">
         <v>2083</v>
       </c>
-      <c r="L38" s="19">
-        <v>0</v>
-      </c>
-      <c r="M38" s="19">
-        <v>0</v>
-      </c>
-      <c r="N38" s="19">
+      <c r="L38" s="20">
+        <v>0</v>
+      </c>
+      <c r="M38" s="20">
+        <v>0</v>
+      </c>
+      <c r="N38" s="20">
         <f>SUM(B38:M38)</f>
         <v>20833</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A39" s="11" t="s">
+      <c r="A39" s="12" t="s">
         <v>225</v>
       </c>
-      <c r="B39" s="19">
+      <c r="B39" s="20">
         <v>1250</v>
       </c>
-      <c r="C39" s="19">
+      <c r="C39" s="20">
         <v>1250</v>
       </c>
-      <c r="D39" s="19">
+      <c r="D39" s="20">
         <v>1250</v>
       </c>
-      <c r="E39" s="19">
+      <c r="E39" s="20">
         <v>1250</v>
       </c>
-      <c r="F39" s="19">
+      <c r="F39" s="20">
         <v>1250</v>
       </c>
-      <c r="G39" s="19">
+      <c r="G39" s="20">
         <v>1250</v>
       </c>
-      <c r="H39" s="19">
+      <c r="H39" s="20">
         <v>1250</v>
       </c>
-      <c r="I39" s="19">
+      <c r="I39" s="20">
         <v>1250</v>
       </c>
-      <c r="J39" s="19">
+      <c r="J39" s="20">
         <v>1250</v>
       </c>
-      <c r="K39" s="19">
+      <c r="K39" s="20">
         <v>1250</v>
       </c>
-      <c r="L39" s="19">
-        <v>0</v>
-      </c>
-      <c r="M39" s="19">
-        <v>0</v>
-      </c>
-      <c r="N39" s="19">
+      <c r="L39" s="20">
+        <v>0</v>
+      </c>
+      <c r="M39" s="20">
+        <v>0</v>
+      </c>
+      <c r="N39" s="20">
         <f>SUM(B39:M39)</f>
         <v>12500</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A40" s="11" t="s">
+      <c r="A40" s="12" t="s">
         <v>226</v>
       </c>
-      <c r="B40" s="19">
+      <c r="B40" s="20">
         <v>1667</v>
       </c>
-      <c r="C40" s="19">
+      <c r="C40" s="20">
         <v>1667</v>
       </c>
-      <c r="D40" s="19">
+      <c r="D40" s="20">
         <v>1667</v>
       </c>
-      <c r="E40" s="19">
+      <c r="E40" s="20">
         <v>1667</v>
       </c>
-      <c r="F40" s="19">
+      <c r="F40" s="20">
         <v>1667</v>
       </c>
-      <c r="G40" s="19">
+      <c r="G40" s="20">
         <v>1667</v>
       </c>
-      <c r="H40" s="19">
+      <c r="H40" s="20">
         <v>1667</v>
       </c>
-      <c r="I40" s="19">
+      <c r="I40" s="20">
         <v>1667</v>
       </c>
-      <c r="J40" s="19">
+      <c r="J40" s="20">
         <v>1667</v>
       </c>
-      <c r="K40" s="19">
+      <c r="K40" s="20">
         <v>1667</v>
       </c>
-      <c r="L40" s="19">
-        <v>0</v>
-      </c>
-      <c r="M40" s="19">
-        <v>0</v>
-      </c>
-      <c r="N40" s="19">
+      <c r="L40" s="20">
+        <v>0</v>
+      </c>
+      <c r="M40" s="20">
+        <v>0</v>
+      </c>
+      <c r="N40" s="20">
         <f>SUM(B40:M40)</f>
         <v>16667</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A41" s="11" t="s">
+      <c r="A41" s="12" t="s">
         <v>227</v>
       </c>
-      <c r="B41" s="19">
+      <c r="B41" s="20">
         <v>8000</v>
       </c>
-      <c r="C41" s="19">
+      <c r="C41" s="20">
         <v>8000</v>
       </c>
-      <c r="D41" s="19">
+      <c r="D41" s="20">
         <v>8000</v>
       </c>
-      <c r="E41" s="19">
+      <c r="E41" s="20">
         <v>8000</v>
       </c>
-      <c r="F41" s="19">
+      <c r="F41" s="20">
         <v>8000</v>
       </c>
-      <c r="G41" s="19">
+      <c r="G41" s="20">
         <v>8000</v>
       </c>
-      <c r="H41" s="19">
+      <c r="H41" s="20">
         <v>8000</v>
       </c>
-      <c r="I41" s="19">
+      <c r="I41" s="20">
         <v>8000</v>
       </c>
-      <c r="J41" s="19">
+      <c r="J41" s="20">
         <v>8000</v>
       </c>
-      <c r="K41" s="19">
+      <c r="K41" s="20">
         <v>8000</v>
       </c>
-      <c r="L41" s="19">
-        <v>0</v>
-      </c>
-      <c r="M41" s="19">
-        <v>0</v>
-      </c>
-      <c r="N41" s="19">
+      <c r="L41" s="20">
+        <v>0</v>
+      </c>
+      <c r="M41" s="20">
+        <v>0</v>
+      </c>
+      <c r="N41" s="20">
         <f>SUM(B41:M41)</f>
         <v>80000</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A42" s="11" t="s">
+      <c r="A42" s="12" t="s">
         <v>228</v>
       </c>
-      <c r="B42" s="19">
+      <c r="B42" s="20">
         <v>6000</v>
       </c>
-      <c r="C42" s="19">
+      <c r="C42" s="20">
         <v>6000</v>
       </c>
-      <c r="D42" s="19">
+      <c r="D42" s="20">
         <v>6000</v>
       </c>
-      <c r="E42" s="19">
+      <c r="E42" s="20">
         <v>6000</v>
       </c>
-      <c r="F42" s="19">
+      <c r="F42" s="20">
         <v>6000</v>
       </c>
-      <c r="G42" s="19">
+      <c r="G42" s="20">
         <v>6000</v>
       </c>
-      <c r="H42" s="19">
+      <c r="H42" s="20">
         <v>6000</v>
       </c>
-      <c r="I42" s="19">
+      <c r="I42" s="20">
         <v>6000</v>
       </c>
-      <c r="J42" s="19">
+      <c r="J42" s="20">
         <v>6000</v>
       </c>
-      <c r="K42" s="19">
+      <c r="K42" s="20">
         <v>6000</v>
       </c>
-      <c r="L42" s="19">
-        <v>0</v>
-      </c>
-      <c r="M42" s="19">
-        <v>0</v>
-      </c>
-      <c r="N42" s="19">
+      <c r="L42" s="20">
+        <v>0</v>
+      </c>
+      <c r="M42" s="20">
+        <v>0</v>
+      </c>
+      <c r="N42" s="20">
         <f>SUM(B42:M42)</f>
         <v>60000</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A43" s="27" t="s">
+      <c r="A43" s="28" t="s">
         <v>172</v>
       </c>
-      <c r="B43" s="28">
+      <c r="B43" s="29">
         <v>19000</v>
       </c>
-      <c r="C43" s="28">
+      <c r="C43" s="29">
         <v>19000</v>
       </c>
-      <c r="D43" s="28">
+      <c r="D43" s="29">
         <v>19000</v>
       </c>
-      <c r="E43" s="28">
+      <c r="E43" s="29">
         <v>19000</v>
       </c>
-      <c r="F43" s="28">
+      <c r="F43" s="29">
         <v>19000</v>
       </c>
-      <c r="G43" s="28">
+      <c r="G43" s="29">
         <v>19000</v>
       </c>
-      <c r="H43" s="28">
+      <c r="H43" s="29">
         <v>19000</v>
       </c>
-      <c r="I43" s="28">
+      <c r="I43" s="29">
         <v>19000</v>
       </c>
-      <c r="J43" s="28">
+      <c r="J43" s="29">
         <v>19000</v>
       </c>
-      <c r="K43" s="28">
+      <c r="K43" s="29">
         <v>19000</v>
       </c>
-      <c r="L43" s="28">
-        <v>0</v>
-      </c>
-      <c r="M43" s="28">
-        <v>0</v>
-      </c>
-      <c r="N43" s="28">
+      <c r="L43" s="29">
+        <v>0</v>
+      </c>
+      <c r="M43" s="29">
+        <v>0</v>
+      </c>
+      <c r="N43" s="29">
         <f>SUM(B43:M43)</f>
         <v>190000</v>
       </c>
     </row>
     <row r="44" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A44" s="10" t="s">
+      <c r="A44" s="11" t="s">
         <v>173</v>
       </c>
-      <c r="B44" s="26">
+      <c r="B44" s="27">
         <f>B27+B30+B36+B43</f>
         <v>54500</v>
       </c>
-      <c r="C44" s="26">
+      <c r="C44" s="27">
         <f>C27+C30+C36+C43</f>
         <v>54500</v>
       </c>
-      <c r="D44" s="26">
+      <c r="D44" s="27">
         <f>D27+D30+D36+D43</f>
         <v>54500</v>
       </c>
-      <c r="E44" s="26">
+      <c r="E44" s="27">
         <f>E27+E30+E36+E43</f>
         <v>54500</v>
       </c>
-      <c r="F44" s="26">
+      <c r="F44" s="27">
         <f>F27+F30+F36+F43</f>
         <v>54500</v>
       </c>
-      <c r="G44" s="26">
+      <c r="G44" s="27">
         <f>G27+G30+G36+G43</f>
         <v>54500</v>
       </c>
-      <c r="H44" s="26">
+      <c r="H44" s="27">
         <f>H27+H30+H36+H43</f>
         <v>54500</v>
       </c>
-      <c r="I44" s="26">
+      <c r="I44" s="27">
         <f>I27+I30+I36+I43</f>
         <v>54500</v>
       </c>
-      <c r="J44" s="26">
+      <c r="J44" s="27">
         <f>J27+J30+J36+J43</f>
         <v>54500</v>
       </c>
-      <c r="K44" s="26">
+      <c r="K44" s="27">
         <f>K27+K30+K36+K43</f>
         <v>54500</v>
       </c>
-      <c r="L44" s="26" t="str">
+      <c r="L44" s="27" t="str">
         <f>L27+L30+L36+L43</f>
         <v>0</v>
       </c>
-      <c r="M44" s="26" t="str">
+      <c r="M44" s="27" t="str">
         <f>M27+M30+M36+M43</f>
         <v>0</v>
       </c>
-      <c r="N44" s="26">
+      <c r="N44" s="27">
         <f>SUM(B44:M44)</f>
         <v>545000</v>
       </c>
@@ -6319,46 +6323,46 @@
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A46" s="24" t="s">
+      <c r="A46" s="25" t="s">
         <v>229</v>
       </c>
-      <c r="B46" s="19">
+      <c r="B46" s="20">
         <v>13735</v>
       </c>
-      <c r="C46" s="19">
+      <c r="C46" s="20">
         <v>13735</v>
       </c>
-      <c r="D46" s="19">
+      <c r="D46" s="20">
         <v>13735</v>
       </c>
-      <c r="E46" s="19">
+      <c r="E46" s="20">
         <v>13735</v>
       </c>
-      <c r="F46" s="19">
+      <c r="F46" s="20">
         <v>13735</v>
       </c>
-      <c r="G46" s="19">
+      <c r="G46" s="20">
         <v>13735</v>
       </c>
-      <c r="H46" s="19">
+      <c r="H46" s="20">
         <v>13735</v>
       </c>
-      <c r="I46" s="19">
+      <c r="I46" s="20">
         <v>13735</v>
       </c>
-      <c r="J46" s="19">
+      <c r="J46" s="20">
         <v>13735</v>
       </c>
-      <c r="K46" s="19">
+      <c r="K46" s="20">
         <v>13735</v>
       </c>
-      <c r="L46" s="19">
+      <c r="L46" s="20">
         <v>13735</v>
       </c>
-      <c r="M46" s="19">
+      <c r="M46" s="20">
         <v>13735</v>
       </c>
-      <c r="N46" s="19">
+      <c r="N46" s="20">
         <f>SUM(B46:M46)</f>
         <v>164825</v>
       </c>
@@ -6369,244 +6373,244 @@
       </c>
     </row>
     <row r="48" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A48" s="10" t="s">
+      <c r="A48" s="11" t="s">
         <v>230</v>
       </c>
-      <c r="B48" s="10"/>
-      <c r="C48" s="10"/>
-      <c r="D48" s="10"/>
-      <c r="E48" s="10"/>
-      <c r="F48" s="10"/>
-      <c r="G48" s="10"/>
-      <c r="H48" s="10"/>
-      <c r="I48" s="10"/>
-      <c r="J48" s="10"/>
-      <c r="K48" s="10"/>
-      <c r="L48" s="10"/>
-      <c r="M48" s="10"/>
-      <c r="N48" s="10"/>
+      <c r="B48" s="11"/>
+      <c r="C48" s="11"/>
+      <c r="D48" s="11"/>
+      <c r="E48" s="11"/>
+      <c r="F48" s="11"/>
+      <c r="G48" s="11"/>
+      <c r="H48" s="11"/>
+      <c r="I48" s="11"/>
+      <c r="J48" s="11"/>
+      <c r="K48" s="11"/>
+      <c r="L48" s="11"/>
+      <c r="M48" s="11"/>
+      <c r="N48" s="11"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A49" s="24" t="s">
+      <c r="A49" s="25" t="s">
         <v>181</v>
       </c>
-      <c r="B49" s="28">
+      <c r="B49" s="29">
         <f>B22+B44+B46</f>
         <v>170878</v>
       </c>
-      <c r="C49" s="28">
+      <c r="C49" s="29">
         <f>C22+C44+C46</f>
         <v>170878</v>
       </c>
-      <c r="D49" s="28">
+      <c r="D49" s="29">
         <f>D22+D44+D46</f>
         <v>170878</v>
       </c>
-      <c r="E49" s="28">
+      <c r="E49" s="29">
         <f>E22+E44+E46</f>
         <v>170878</v>
       </c>
-      <c r="F49" s="28">
+      <c r="F49" s="29">
         <f>F22+F44+F46</f>
         <v>170878</v>
       </c>
-      <c r="G49" s="28">
+      <c r="G49" s="29">
         <f>G22+G44+G46</f>
         <v>170878</v>
       </c>
-      <c r="H49" s="28">
+      <c r="H49" s="29">
         <f>H22+H44+H46</f>
         <v>170878</v>
       </c>
-      <c r="I49" s="28">
+      <c r="I49" s="29">
         <f>I22+I44+I46</f>
         <v>170878</v>
       </c>
-      <c r="J49" s="28">
+      <c r="J49" s="29">
         <f>J22+J44+J46</f>
         <v>170878</v>
       </c>
-      <c r="K49" s="28">
+      <c r="K49" s="29">
         <f>K22+K44+K46</f>
         <v>170878</v>
       </c>
-      <c r="L49" s="28">
+      <c r="L49" s="29">
         <f>L22+L44+L46</f>
         <v>13735</v>
       </c>
-      <c r="M49" s="28">
+      <c r="M49" s="29">
         <f>M22+M44+M46</f>
         <v>13735</v>
       </c>
-      <c r="N49" s="28">
+      <c r="N49" s="29">
         <f>SUM(B49:M49)</f>
         <v>1736250</v>
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A50" s="24" t="s">
+      <c r="A50" s="25" t="s">
         <v>231</v>
       </c>
-      <c r="B50" s="28">
+      <c r="B50" s="29">
         <f>B10-B49</f>
         <v>-16278</v>
       </c>
-      <c r="C50" s="28">
+      <c r="C50" s="29">
         <f>C10-C49</f>
         <v>-16278</v>
       </c>
-      <c r="D50" s="28">
+      <c r="D50" s="29">
         <f>D10-D49</f>
         <v>-16278</v>
       </c>
-      <c r="E50" s="28">
+      <c r="E50" s="29">
         <f>E10-E49</f>
         <v>-16278</v>
       </c>
-      <c r="F50" s="28">
+      <c r="F50" s="29">
         <f>F10-F49</f>
         <v>-16278</v>
       </c>
-      <c r="G50" s="28">
+      <c r="G50" s="29">
         <f>G10-G49</f>
         <v>-16278</v>
       </c>
-      <c r="H50" s="28">
+      <c r="H50" s="29">
         <f>H10-H49</f>
         <v>-16278</v>
       </c>
-      <c r="I50" s="28">
+      <c r="I50" s="29">
         <f>I10-I49</f>
         <v>-16278</v>
       </c>
-      <c r="J50" s="28">
+      <c r="J50" s="29">
         <f>J10-J49</f>
         <v>-16278</v>
       </c>
-      <c r="K50" s="28">
+      <c r="K50" s="29">
         <f>K10-K49</f>
         <v>-16278</v>
       </c>
-      <c r="L50" s="28">
+      <c r="L50" s="29">
         <f>L10-L49</f>
         <v>-13735</v>
       </c>
-      <c r="M50" s="28">
+      <c r="M50" s="29">
         <f>M10-M49</f>
         <v>-13735</v>
       </c>
-      <c r="N50" s="28">
+      <c r="N50" s="29">
         <f>SUM(B50:M50)</f>
         <v>-190250</v>
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A51" s="24" t="s">
+      <c r="A51" s="25" t="s">
         <v>232</v>
       </c>
-      <c r="B51" s="28">
+      <c r="B51" s="29">
         <f>0+B50</f>
         <v>-16278</v>
       </c>
-      <c r="C51" s="28">
+      <c r="C51" s="29">
         <f>B51+C50</f>
         <v>-32556</v>
       </c>
-      <c r="D51" s="28">
+      <c r="D51" s="29">
         <f>C51+D50</f>
         <v>-48834</v>
       </c>
-      <c r="E51" s="28">
+      <c r="E51" s="29">
         <f>D51+E50</f>
         <v>-65112</v>
       </c>
-      <c r="F51" s="28">
+      <c r="F51" s="29">
         <f>E51+F50</f>
         <v>-81390</v>
       </c>
-      <c r="G51" s="28">
+      <c r="G51" s="29">
         <f>F51+G50</f>
         <v>-97668</v>
       </c>
-      <c r="H51" s="28">
+      <c r="H51" s="29">
         <f>G51+H50</f>
         <v>-113946</v>
       </c>
-      <c r="I51" s="28">
+      <c r="I51" s="29">
         <f>H51+I50</f>
         <v>-130224</v>
       </c>
-      <c r="J51" s="28">
+      <c r="J51" s="29">
         <f>I51+J50</f>
         <v>-146502</v>
       </c>
-      <c r="K51" s="28">
+      <c r="K51" s="29">
         <f>J51+K50</f>
         <v>-162780</v>
       </c>
-      <c r="L51" s="28">
+      <c r="L51" s="29">
         <f>K51+L50</f>
         <v>-176515</v>
       </c>
-      <c r="M51" s="28">
+      <c r="M51" s="29">
         <f>L51+M50</f>
         <v>-190250</v>
       </c>
-      <c r="N51" s="28">
+      <c r="N51" s="29">
         <f>M51</f>
         <v>-190250</v>
       </c>
     </row>
     <row r="53" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" s="10" t="s">
+      <c r="A53" s="11" t="s">
         <v>233</v>
       </c>
-      <c r="B53" s="10"/>
-      <c r="C53" s="10"/>
+      <c r="B53" s="11"/>
+      <c r="C53" s="11"/>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" s="11" t="s">
+      <c r="A54" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="B54" s="19">
+      <c r="B54" s="20">
         <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A55" s="11" t="s">
+      <c r="A55" s="12" t="s">
         <v>234</v>
       </c>
-      <c r="B55" s="28">
+      <c r="B55" s="29">
         <f>M51</f>
         <v>-190250</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A56" s="11" t="s">
+      <c r="A56" s="12" t="s">
         <v>235</v>
       </c>
-      <c r="B56" s="19">
+      <c r="B56" s="20">
         <f>MIN(B51:M51)</f>
         <v>-190250</v>
       </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A58" s="22" t="s">
+      <c r="A58" s="23" t="s">
         <v>143</v>
       </c>
-      <c r="B58" s="22"/>
-      <c r="C58" s="22"/>
-      <c r="D58" s="22"/>
-      <c r="E58" s="22"/>
-      <c r="F58" s="22"/>
-      <c r="G58" s="22"/>
-      <c r="H58" s="22"/>
-      <c r="I58" s="22"/>
-      <c r="J58" s="22"/>
-      <c r="K58" s="22"/>
-      <c r="L58" s="22"/>
-      <c r="M58" s="22"/>
-      <c r="N58" s="22"/>
+      <c r="B58" s="23"/>
+      <c r="C58" s="23"/>
+      <c r="D58" s="23"/>
+      <c r="E58" s="23"/>
+      <c r="F58" s="23"/>
+      <c r="G58" s="23"/>
+      <c r="H58" s="23"/>
+      <c r="I58" s="23"/>
+      <c r="J58" s="23"/>
+      <c r="K58" s="23"/>
+      <c r="L58" s="23"/>
+      <c r="M58" s="23"/>
+      <c r="N58" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -6648,466 +6652,466 @@
       <c r="G2" s="1"/>
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="38" t="s">
+      <c r="B3" s="39" t="s">
         <v>237</v>
       </c>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="39"/>
+      <c r="E3" s="39"/>
+      <c r="F3" s="39"/>
+      <c r="G3" s="39"/>
     </row>
     <row r="5" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="11" t="s">
         <v>238</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="15" t="s">
         <v>239</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="D5" s="15" t="s">
         <v>240</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="E5" s="15" t="s">
         <v>241</v>
       </c>
-      <c r="F5" s="14" t="s">
+      <c r="F5" s="15" t="s">
         <v>242</v>
       </c>
-      <c r="G5" s="14" t="s">
+      <c r="G5" s="15" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="12" t="s">
         <v>244</v>
       </c>
-      <c r="C6" s="39">
+      <c r="C6" s="40">
         <v>120</v>
       </c>
-      <c r="D6" s="39">
+      <c r="D6" s="40">
         <v>200</v>
       </c>
-      <c r="E6" s="39">
+      <c r="E6" s="40">
         <v>300</v>
       </c>
-      <c r="F6" s="39">
+      <c r="F6" s="40">
         <v>375</v>
       </c>
-      <c r="G6" s="39">
+      <c r="G6" s="40">
         <v>400</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="C7" s="40">
+      <c r="C7" s="41">
         <v>1546000</v>
       </c>
-      <c r="D7" s="40">
+      <c r="D7" s="41">
         <v>2522800</v>
       </c>
-      <c r="E7" s="40">
+      <c r="E7" s="41">
         <v>3784600</v>
       </c>
-      <c r="F7" s="40">
+      <c r="F7" s="41">
         <v>4759125</v>
       </c>
-      <c r="G7" s="40">
+      <c r="G7" s="41">
         <v>5184400</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="12" t="s">
         <v>246</v>
       </c>
-      <c r="C8" s="40">
+      <c r="C8" s="41">
         <v>1026431.25</v>
       </c>
-      <c r="D8" s="40">
+      <c r="D8" s="41">
         <v>1231717.5</v>
       </c>
-      <c r="E8" s="40">
+      <c r="E8" s="41">
         <v>1231717.5</v>
       </c>
-      <c r="F8" s="40">
+      <c r="F8" s="41">
         <v>1231717.5</v>
       </c>
-      <c r="G8" s="40">
+      <c r="G8" s="41">
         <v>1231717.5</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="12" t="s">
         <v>247</v>
       </c>
-      <c r="C9" s="40">
+      <c r="C9" s="41">
         <v>654000</v>
       </c>
-      <c r="D9" s="40">
+      <c r="D9" s="41">
         <v>887860</v>
       </c>
-      <c r="E9" s="40">
+      <c r="E9" s="41">
         <v>1190521.4</v>
       </c>
-      <c r="F9" s="40">
+      <c r="F9" s="41">
         <v>1439089.0320000001</v>
       </c>
-      <c r="G9" s="40">
+      <c r="G9" s="41">
         <v>1554923.90296</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="12" t="s">
         <v>187</v>
       </c>
-      <c r="C10" s="40">
+      <c r="C10" s="41">
         <v>49824.605221179416</v>
       </c>
-      <c r="D10" s="40">
+      <c r="D10" s="41">
         <v>49824.605221179416</v>
       </c>
-      <c r="E10" s="40">
+      <c r="E10" s="41">
         <v>49824.605221179416</v>
       </c>
-      <c r="F10" s="40">
+      <c r="F10" s="41">
         <v>49824.605221179416</v>
       </c>
-      <c r="G10" s="40">
+      <c r="G10" s="41">
         <v>49824.605221179416</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B11" s="24" t="s">
+      <c r="B11" s="25" t="s">
         <v>182</v>
       </c>
-      <c r="C11" s="41">
+      <c r="C11" s="42">
         <v>-184255.85522117943</v>
       </c>
-      <c r="D11" s="42">
+      <c r="D11" s="43">
         <v>353397.89477882057</v>
       </c>
-      <c r="E11" s="42">
+      <c r="E11" s="43">
         <v>1312536.4947788208</v>
       </c>
-      <c r="F11" s="42">
+      <c r="F11" s="43">
         <v>2038493.8627788206</v>
       </c>
-      <c r="G11" s="42">
+      <c r="G11" s="43">
         <v>2347933.9918188206</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="24" t="s">
+      <c r="B12" s="25" t="s">
         <v>189</v>
       </c>
-      <c r="C12" s="41">
+      <c r="C12" s="42">
         <v>-184255.85522117943</v>
       </c>
-      <c r="D12" s="42">
+      <c r="D12" s="43">
         <v>169142.03955764114</v>
       </c>
-      <c r="E12" s="42">
+      <c r="E12" s="43">
         <v>1481678.534336462</v>
       </c>
-      <c r="F12" s="42">
+      <c r="F12" s="43">
         <v>3520172.3971152827</v>
       </c>
-      <c r="G12" s="42">
+      <c r="G12" s="43">
         <v>5868106.388934104</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="24" t="s">
+      <c r="B13" s="25" t="s">
         <v>248</v>
       </c>
-      <c r="C13" s="43">
+      <c r="C13" s="44">
         <v>-0.11918231256221179</v>
       </c>
-      <c r="D13" s="44">
+      <c r="D13" s="45">
         <v>0.14008161359553692</v>
       </c>
-      <c r="E13" s="44">
+      <c r="E13" s="45">
         <v>0.34680983321323805</v>
       </c>
-      <c r="F13" s="44">
+      <c r="F13" s="45">
         <v>0.4283337510107048</v>
       </c>
-      <c r="G13" s="44">
+      <c r="G13" s="45">
         <v>0.4528844209202262</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="24" t="s">
+      <c r="B14" s="25" t="s">
         <v>249</v>
       </c>
-      <c r="C14" s="40">
+      <c r="C14" s="41">
         <v>12883.333333333334</v>
       </c>
-      <c r="D14" s="40">
+      <c r="D14" s="41">
         <v>12614</v>
       </c>
-      <c r="E14" s="40">
+      <c r="E14" s="41">
         <v>12615.333333333334</v>
       </c>
-      <c r="F14" s="40">
+      <c r="F14" s="41">
         <v>12691</v>
       </c>
-      <c r="G14" s="40">
+      <c r="G14" s="41">
         <v>12961</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="24" t="s">
+      <c r="B15" s="25" t="s">
         <v>250</v>
       </c>
-      <c r="C15" s="43">
+      <c r="C15" s="44">
         <v>0.6639270698576973</v>
       </c>
-      <c r="D15" s="44">
+      <c r="D15" s="45">
         <v>0.48823430315522437</v>
       </c>
-      <c r="E15" s="44">
+      <c r="E15" s="45">
         <v>0.3254551339639592</v>
       </c>
-      <c r="F15" s="44">
+      <c r="F15" s="45">
         <v>0.25881175636277676</v>
       </c>
-      <c r="G15" s="44">
+      <c r="G15" s="45">
         <v>0.23758149448345034</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="24" t="s">
+      <c r="B16" s="25" t="s">
         <v>251</v>
       </c>
-      <c r="C16" s="44">
+      <c r="C16" s="45">
         <v>0.12690815006468306</v>
       </c>
-      <c r="D16" s="44">
+      <c r="D16" s="45">
         <v>0.10558030759473601</v>
       </c>
-      <c r="E16" s="44">
+      <c r="E16" s="45">
         <v>0.09437098240236748</v>
       </c>
-      <c r="F16" s="44">
+      <c r="F16" s="45">
         <v>0.09071556422661729</v>
       </c>
-      <c r="G16" s="44">
+      <c r="G16" s="45">
         <v>0.08997707948615076</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="24" t="s">
+      <c r="B17" s="25" t="s">
         <v>252</v>
       </c>
-      <c r="C17" s="43">
+      <c r="C17" s="44">
         <v>-0.08695423673997413</v>
       </c>
-      <c r="D17" s="44">
+      <c r="D17" s="45">
         <v>0.15983133819565562</v>
       </c>
-      <c r="E17" s="44">
+      <c r="E17" s="45">
         <v>0.35997492469481585</v>
       </c>
-      <c r="F17" s="44">
+      <c r="F17" s="45">
         <v>0.4388030295484989</v>
       </c>
-      <c r="G17" s="44">
+      <c r="G17" s="45">
         <v>0.4624949072293804</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B18" s="24" t="s">
+      <c r="B18" s="25" t="s">
         <v>253</v>
       </c>
-      <c r="C18" s="45">
+      <c r="C18" s="46">
         <v>-2.698089616630942</v>
       </c>
-      <c r="D18" s="46">
+      <c r="D18" s="47">
         <v>8.092838833544805</v>
       </c>
-      <c r="E18" s="46">
+      <c r="E18" s="47">
         <v>27.34313887590801</v>
       </c>
-      <c r="F18" s="46">
+      <c r="F18" s="47">
         <v>41.91339718056208</v>
       </c>
-      <c r="G18" s="46">
+      <c r="G18" s="47">
         <v>48.12398585791026</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="24" t="s">
+      <c r="B19" s="25" t="s">
         <v>254</v>
       </c>
-      <c r="C19" s="47" t="s">
+      <c r="C19" s="48" t="s">
         <v>240</v>
       </c>
-      <c r="D19" s="47"/>
-      <c r="E19" s="47"/>
-      <c r="F19" s="47"/>
-      <c r="G19" s="47"/>
+      <c r="D19" s="48"/>
+      <c r="E19" s="48"/>
+      <c r="F19" s="48"/>
+      <c r="G19" s="48"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B20" s="24" t="s">
+      <c r="B20" s="25" t="s">
         <v>255</v>
       </c>
-      <c r="C20" s="48" t="s">
+      <c r="C20" s="49" t="s">
         <v>256</v>
       </c>
-      <c r="D20" s="48"/>
-      <c r="E20" s="48"/>
-      <c r="F20" s="48"/>
-      <c r="G20" s="48"/>
+      <c r="D20" s="49"/>
+      <c r="E20" s="49"/>
+      <c r="F20" s="49"/>
+      <c r="G20" s="49"/>
     </row>
     <row r="22" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B22" s="10" t="s">
+      <c r="B22" s="11" t="s">
         <v>257</v>
       </c>
-      <c r="C22" s="10" t="s">
+      <c r="C22" s="11" t="s">
         <v>258</v>
       </c>
-      <c r="D22" s="10" t="s">
+      <c r="D22" s="11" t="s">
         <v>259</v>
       </c>
-      <c r="E22" s="10"/>
-      <c r="F22" s="10" t="s">
+      <c r="E22" s="11"/>
+      <c r="F22" s="11" t="s">
         <v>260</v>
       </c>
-      <c r="G22" s="10"/>
+      <c r="G22" s="11"/>
     </row>
     <row r="23" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B23" s="49" t="s">
+      <c r="B23" s="50" t="s">
         <v>261</v>
       </c>
-      <c r="C23" s="50" t="s">
+      <c r="C23" s="51" t="s">
         <v>262</v>
       </c>
-      <c r="D23" s="51" t="s">
+      <c r="D23" s="52" t="s">
         <v>263</v>
       </c>
-      <c r="E23" s="51"/>
-      <c r="F23" s="52" t="s">
+      <c r="E23" s="52"/>
+      <c r="F23" s="53" t="s">
         <v>264</v>
       </c>
-      <c r="G23" s="52"/>
+      <c r="G23" s="53"/>
     </row>
     <row r="24" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B24" s="49" t="s">
+      <c r="B24" s="50" t="s">
         <v>265</v>
       </c>
-      <c r="C24" s="53" t="s">
+      <c r="C24" s="54" t="s">
         <v>266</v>
       </c>
-      <c r="D24" s="51" t="s">
+      <c r="D24" s="52" t="s">
         <v>267</v>
       </c>
-      <c r="E24" s="51"/>
-      <c r="F24" s="52" t="s">
+      <c r="E24" s="52"/>
+      <c r="F24" s="53" t="s">
         <v>268</v>
       </c>
-      <c r="G24" s="52"/>
+      <c r="G24" s="53"/>
     </row>
     <row r="25" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B25" s="49" t="s">
+      <c r="B25" s="50" t="s">
         <v>269</v>
       </c>
-      <c r="C25" s="50" t="s">
+      <c r="C25" s="51" t="s">
         <v>262</v>
       </c>
-      <c r="D25" s="51" t="s">
+      <c r="D25" s="52" t="s">
         <v>270</v>
       </c>
-      <c r="E25" s="51"/>
-      <c r="F25" s="52" t="s">
+      <c r="E25" s="52"/>
+      <c r="F25" s="53" t="s">
         <v>271</v>
       </c>
-      <c r="G25" s="52"/>
+      <c r="G25" s="53"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B26" s="49" t="s">
+      <c r="B26" s="50" t="s">
         <v>272</v>
       </c>
-      <c r="C26" s="50" t="s">
+      <c r="C26" s="51" t="s">
         <v>262</v>
       </c>
-      <c r="D26" s="51" t="s">
+      <c r="D26" s="52" t="s">
         <v>273</v>
       </c>
-      <c r="E26" s="51"/>
-      <c r="F26" s="52" t="s">
+      <c r="E26" s="52"/>
+      <c r="F26" s="53" t="s">
         <v>274</v>
       </c>
-      <c r="G26" s="52"/>
+      <c r="G26" s="53"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B27" s="49" t="s">
+      <c r="B27" s="50" t="s">
         <v>275</v>
       </c>
-      <c r="C27" s="50" t="s">
+      <c r="C27" s="51" t="s">
         <v>262</v>
       </c>
-      <c r="D27" s="51" t="s">
+      <c r="D27" s="52" t="s">
         <v>276</v>
       </c>
-      <c r="E27" s="51"/>
-      <c r="F27" s="52" t="s">
+      <c r="E27" s="52"/>
+      <c r="F27" s="53" t="s">
         <v>277</v>
       </c>
-      <c r="G27" s="52"/>
+      <c r="G27" s="53"/>
     </row>
     <row r="28" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B28" s="49" t="s">
+      <c r="B28" s="50" t="s">
         <v>278</v>
       </c>
-      <c r="C28" s="50" t="s">
+      <c r="C28" s="51" t="s">
         <v>262</v>
       </c>
-      <c r="D28" s="51" t="s">
+      <c r="D28" s="52" t="s">
         <v>279</v>
       </c>
-      <c r="E28" s="51"/>
-      <c r="F28" s="52" t="s">
+      <c r="E28" s="52"/>
+      <c r="F28" s="53" t="s">
         <v>280</v>
       </c>
-      <c r="G28" s="52"/>
+      <c r="G28" s="53"/>
     </row>
     <row r="29" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B29" s="49" t="s">
+      <c r="B29" s="50" t="s">
         <v>281</v>
       </c>
-      <c r="C29" s="50" t="s">
+      <c r="C29" s="51" t="s">
         <v>262</v>
       </c>
-      <c r="D29" s="51" t="s">
+      <c r="D29" s="52" t="s">
         <v>282</v>
       </c>
-      <c r="E29" s="51"/>
-      <c r="F29" s="52" t="s">
+      <c r="E29" s="52"/>
+      <c r="F29" s="53" t="s">
         <v>283</v>
       </c>
-      <c r="G29" s="52"/>
+      <c r="G29" s="53"/>
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B31" s="49" t="s">
+      <c r="B31" s="50" t="s">
         <v>284</v>
       </c>
-      <c r="C31" s="24" t="s">
+      <c r="C31" s="25" t="s">
         <v>285</v>
       </c>
-      <c r="D31" s="24"/>
-      <c r="E31" s="24"/>
+      <c r="D31" s="25"/>
+      <c r="E31" s="25"/>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B33" s="54" t="s">
+      <c r="B33" s="55" t="s">
         <v>143</v>
       </c>
-      <c r="C33" s="54"/>
-      <c r="D33" s="54"/>
-      <c r="E33" s="54"/>
-      <c r="F33" s="54"/>
-      <c r="G33" s="54"/>
+      <c r="C33" s="55"/>
+      <c r="D33" s="55"/>
+      <c r="E33" s="55"/>
+      <c r="F33" s="55"/>
+      <c r="G33" s="55"/>
     </row>
   </sheetData>
   <mergeCells count="22">

--- a/artifacts/api-server/qa-output/Formula_Export_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Formula_Export_Charter_Public_Funding.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="287">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -122,7 +122,10 @@
     <t>Civic Scholars Charter - Financial Model Assumptions</t>
   </si>
   <si>
-    <t>Blue cells are editable inputs. All other cells in this workbook are formulas.</t>
+    <t>Editable assumption — change this value</t>
+  </si>
+  <si>
+    <t>Calculated — driven by formula</t>
   </si>
   <si>
     <t>SCHOOL PROFILE</t>
@@ -998,7 +1001,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1017,6 +1020,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFE8EDF2"/>
       </patternFill>
     </fill>
@@ -1031,12 +1039,21 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD0D0D0"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1073,7 +1090,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1087,78 +1104,79 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="12" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="12" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="12" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="12" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="12" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="12" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="12" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="12" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1872,1076 +1890,1082 @@
       <c r="F1" s="8"/>
       <c r="G1" s="8"/>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
         <v>7</v>
       </c>
       <c r="B2" s="10" t="s">
         <v>31</v>
       </c>
+      <c r="D2" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="B4" s="11"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="11"/>
+      <c r="A4" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" s="12"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="B5" s="13" t="s">
+      <c r="A5" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="13"/>
-      <c r="D5" s="13"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="14"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="B6" s="13" t="s">
+      <c r="A6" s="13" t="s">
         <v>35</v>
       </c>
+      <c r="B6" s="14" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="B7" s="13" t="s">
+      <c r="A7" s="13" t="s">
         <v>37</v>
       </c>
+      <c r="B7" s="14" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="B8" s="13" t="s">
+      <c r="A8" s="13" t="s">
         <v>39</v>
       </c>
+      <c r="B8" s="14" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="B9" s="13" t="s">
+      <c r="A9" s="13" t="s">
         <v>41</v>
       </c>
+      <c r="B9" s="14" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="B10" s="13" t="s">
+      <c r="A10" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13"/>
+      <c r="B10" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" s="14"/>
+      <c r="D10" s="14"/>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="B11" s="13" t="s">
+      <c r="A11" s="13" t="s">
         <v>45</v>
       </c>
+      <c r="B11" s="14" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="B12" s="14">
+      <c r="A12" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="B12" s="15">
         <v>400</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="B13" s="12" t="s">
+      <c r="A13" s="13" t="s">
         <v>48</v>
       </c>
+      <c r="B13" s="13" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="B14" s="12" t="s">
+      <c r="A14" s="13" t="s">
         <v>50</v>
       </c>
+      <c r="B14" s="13" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="B16" s="15" t="s">
+      <c r="A16" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="C16" s="15" t="s">
+      <c r="B16" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="D16" s="15" t="s">
+      <c r="C16" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="E16" s="15" t="s">
+      <c r="D16" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="F16" s="15" t="s">
+      <c r="E16" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="G16" s="11"/>
+      <c r="F16" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="G16" s="12"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="B17" s="16">
+      <c r="A17" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="B17" s="17">
         <v>120</v>
       </c>
-      <c r="C17" s="16">
+      <c r="C17" s="17">
         <v>200</v>
       </c>
-      <c r="D17" s="16">
+      <c r="D17" s="17">
         <v>300</v>
       </c>
-      <c r="E17" s="16">
+      <c r="E17" s="17">
         <v>375</v>
       </c>
-      <c r="F17" s="16">
+      <c r="F17" s="17">
         <v>400</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="B19" s="11" t="s">
+      <c r="A19" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="C19" s="11" t="s">
+      <c r="B19" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="D19" s="11" t="s">
+      <c r="C19" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="E19" s="11" t="s">
+      <c r="D19" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="F19" s="11" t="s">
+      <c r="E19" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="G19" s="11" t="s">
+      <c r="F19" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="H19" s="11" t="s">
+      <c r="G19" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="I19" s="11"/>
-      <c r="J19" s="11"/>
+      <c r="H19" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="I19" s="12"/>
+      <c r="J19" s="12"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="12" t="s">
+      <c r="A20" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="B20" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="C20" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="D20" s="18">
+        <v>9500</v>
+      </c>
+      <c r="E20" s="19">
+        <v>0</v>
+      </c>
+      <c r="F20" s="15">
+        <v>12</v>
+      </c>
+      <c r="G20" s="19">
+        <v>1</v>
+      </c>
+      <c r="H20" s="13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="C21" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="D21" s="18">
+        <v>800</v>
+      </c>
+      <c r="E21" s="19">
+        <v>0</v>
+      </c>
+      <c r="F21" s="15">
+        <v>12</v>
+      </c>
+      <c r="G21" s="19">
+        <v>1</v>
+      </c>
+      <c r="H21" s="13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="C22" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="D22" s="18">
+        <v>1200</v>
+      </c>
+      <c r="E22" s="19">
+        <v>0</v>
+      </c>
+      <c r="F22" s="15">
+        <v>12</v>
+      </c>
+      <c r="G22" s="19">
+        <v>1</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="C23" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="D23" s="18">
+        <v>100000</v>
+      </c>
+      <c r="E23" s="19">
+        <v>0</v>
+      </c>
+      <c r="F23" s="15">
+        <v>12</v>
+      </c>
+      <c r="G23" s="19">
+        <v>1</v>
+      </c>
+      <c r="H23" s="13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="C24" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="D24" s="18">
+        <v>30000</v>
+      </c>
+      <c r="E24" s="19">
+        <v>0</v>
+      </c>
+      <c r="F24" s="15">
+        <v>12</v>
+      </c>
+      <c r="G24" s="19">
+        <v>1</v>
+      </c>
+      <c r="H24" s="13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="C25" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="D25" s="18">
+        <v>300</v>
+      </c>
+      <c r="E25" s="19">
+        <v>0</v>
+      </c>
+      <c r="F25" s="15">
+        <v>12</v>
+      </c>
+      <c r="G25" s="19">
+        <v>1</v>
+      </c>
+      <c r="H25" s="13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="B28" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="C28" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="D28" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="E28" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="F28" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="G28" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="H28" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="I28" s="12" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="B29" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="C29" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="D29" s="20">
+        <v>1</v>
+      </c>
+      <c r="E29" s="18">
+        <v>110000</v>
+      </c>
+      <c r="F29" s="19">
+        <v>0.28</v>
+      </c>
+      <c r="G29" s="19">
+        <v>0.0765</v>
+      </c>
+      <c r="H29" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="I29" s="13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="B30" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="C30" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="D30" s="20">
+        <v>1</v>
+      </c>
+      <c r="E30" s="18">
+        <v>90000</v>
+      </c>
+      <c r="F30" s="19">
+        <v>0.28</v>
+      </c>
+      <c r="G30" s="19">
+        <v>0.0765</v>
+      </c>
+      <c r="H30" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="I30" s="13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="B31" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="C31" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="D31" s="20">
+        <v>1</v>
+      </c>
+      <c r="E31" s="18">
+        <v>72000</v>
+      </c>
+      <c r="F31" s="19">
+        <v>0.28</v>
+      </c>
+      <c r="G31" s="19">
+        <v>0.0765</v>
+      </c>
+      <c r="H31" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="I31" s="13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A32" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="B32" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="C32" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="D32" s="20">
+        <v>6</v>
+      </c>
+      <c r="E32" s="18">
+        <v>52000</v>
+      </c>
+      <c r="F32" s="19">
+        <v>0.28</v>
+      </c>
+      <c r="G32" s="19">
+        <v>0.0765</v>
+      </c>
+      <c r="H32" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="I32" s="13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A33" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="B33" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="C33" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="D33" s="20">
+        <v>1</v>
+      </c>
+      <c r="E33" s="18">
+        <v>55000</v>
+      </c>
+      <c r="F33" s="19">
+        <v>0.28</v>
+      </c>
+      <c r="G33" s="19">
+        <v>0.0765</v>
+      </c>
+      <c r="H33" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="I33" s="13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A34" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="B34" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="C34" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="D34" s="20">
+        <v>3</v>
+      </c>
+      <c r="E34" s="18">
+        <v>30000</v>
+      </c>
+      <c r="F34" s="19">
+        <v>0.2</v>
+      </c>
+      <c r="G34" s="19">
+        <v>0.0765</v>
+      </c>
+      <c r="H34" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="I34" s="13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A35" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="B35" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="C35" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="D35" s="20">
+        <v>1</v>
+      </c>
+      <c r="E35" s="18">
+        <v>55000</v>
+      </c>
+      <c r="F35" s="19">
+        <v>0.28</v>
+      </c>
+      <c r="G35" s="19">
+        <v>0.0765</v>
+      </c>
+      <c r="H35" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="I35" s="13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A36" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="B36" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="C36" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="D36" s="20">
+        <v>2</v>
+      </c>
+      <c r="E36" s="18">
+        <v>38000</v>
+      </c>
+      <c r="F36" s="19">
+        <v>0.25</v>
+      </c>
+      <c r="G36" s="19">
+        <v>0.0765</v>
+      </c>
+      <c r="H36" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="I36" s="13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A37" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="B37" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="C37" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="D37" s="20">
+        <v>1</v>
+      </c>
+      <c r="E37" s="18">
+        <v>55000</v>
+      </c>
+      <c r="F37" s="19">
+        <v>0.28</v>
+      </c>
+      <c r="G37" s="19">
+        <v>0.0765</v>
+      </c>
+      <c r="H37" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="I37" s="13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="39" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="B39" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="C39" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="D39" s="12"/>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="B40" s="14" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="B41" s="18">
+        <v>18000</v>
+      </c>
+      <c r="C41" s="13" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="B42" s="19">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="44" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="B44" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="C44" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="D44" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="E44" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="F44" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="B20" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="C20" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="D20" s="17">
-        <v>9500</v>
-      </c>
-      <c r="E20" s="18">
-        <v>0</v>
-      </c>
-      <c r="F20" s="14">
-        <v>12</v>
-      </c>
-      <c r="G20" s="18">
-        <v>1</v>
-      </c>
-      <c r="H20" s="12" t="s">
+      <c r="G44" s="12"/>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="B45" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="C45" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="D45" s="18">
+        <v>18000</v>
+      </c>
+      <c r="E45" s="19">
+        <v>0.03</v>
+      </c>
+      <c r="F45" s="13" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="12" t="s">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="B46" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="C46" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="D46" s="18">
+        <v>2500</v>
+      </c>
+      <c r="E46" s="19">
+        <v>0</v>
+      </c>
+      <c r="F46" s="13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="B47" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="C47" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="D47" s="18">
+        <v>18000</v>
+      </c>
+      <c r="E47" s="19">
+        <v>0</v>
+      </c>
+      <c r="F47" s="13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="B48" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="C48" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="D48" s="18">
+        <v>1500</v>
+      </c>
+      <c r="E48" s="19">
+        <v>0</v>
+      </c>
+      <c r="F48" s="13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="B49" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="C49" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="B21" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="C21" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="D21" s="17">
+      <c r="D49" s="18">
+        <v>700</v>
+      </c>
+      <c r="E49" s="19">
+        <v>0</v>
+      </c>
+      <c r="F49" s="13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="B50" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="C50" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="D50" s="18">
+        <v>500</v>
+      </c>
+      <c r="E50" s="19">
+        <v>0</v>
+      </c>
+      <c r="F50" s="13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="B51" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="C51" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="D51" s="18">
+        <v>25000</v>
+      </c>
+      <c r="E51" s="19">
+        <v>0</v>
+      </c>
+      <c r="F51" s="13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="B52" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="C52" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="D52" s="18">
+        <v>15000</v>
+      </c>
+      <c r="E52" s="19">
+        <v>0</v>
+      </c>
+      <c r="F52" s="13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="B53" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="C53" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="D53" s="18">
+        <v>20000</v>
+      </c>
+      <c r="E53" s="19">
+        <v>0</v>
+      </c>
+      <c r="F53" s="13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="B54" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="C54" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="D54" s="18">
         <v>800</v>
       </c>
-      <c r="E21" s="18">
-        <v>0</v>
-      </c>
-      <c r="F21" s="14">
-        <v>12</v>
-      </c>
-      <c r="G21" s="18">
-        <v>1</v>
-      </c>
-      <c r="H21" s="12" t="s">
+      <c r="E54" s="19">
+        <v>0</v>
+      </c>
+      <c r="F54" s="13" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="B22" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="C22" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="D22" s="17">
-        <v>1200</v>
-      </c>
-      <c r="E22" s="18">
-        <v>0</v>
-      </c>
-      <c r="F22" s="14">
-        <v>12</v>
-      </c>
-      <c r="G22" s="18">
-        <v>1</v>
-      </c>
-      <c r="H22" s="12" t="s">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="B55" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="C55" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="D55" s="18">
+        <v>600</v>
+      </c>
+      <c r="E55" s="19">
+        <v>0</v>
+      </c>
+      <c r="F55" s="13" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="B23" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="C23" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="D23" s="17">
-        <v>100000</v>
-      </c>
-      <c r="E23" s="18">
-        <v>0</v>
-      </c>
-      <c r="F23" s="14">
-        <v>12</v>
-      </c>
-      <c r="G23" s="18">
-        <v>1</v>
-      </c>
-      <c r="H23" s="12" t="s">
+    <row r="57" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="B57" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="C57" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="D57" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="E57" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="F57" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="G57" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="H57" s="12" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="B58" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="C58" s="21">
+        <v>0</v>
+      </c>
+      <c r="D58" s="18">
+        <v>500000</v>
+      </c>
+      <c r="E58" s="22">
+        <v>0.0575</v>
+      </c>
+      <c r="F58" s="15">
+        <v>15</v>
+      </c>
+      <c r="G58" s="21">
+        <v>49825</v>
+      </c>
+      <c r="H58" s="13" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="B24" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="C24" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="D24" s="17">
-        <v>30000</v>
-      </c>
-      <c r="E24" s="18">
-        <v>0</v>
-      </c>
-      <c r="F24" s="14">
-        <v>12</v>
-      </c>
-      <c r="G24" s="18">
-        <v>1</v>
-      </c>
-      <c r="H24" s="12" t="s">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="B59" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="C59" s="18">
+        <v>75000</v>
+      </c>
+      <c r="D59" s="13">
+        <v>0</v>
+      </c>
+      <c r="E59" s="13" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="B25" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="C25" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="D25" s="17">
-        <v>300</v>
-      </c>
-      <c r="E25" s="18">
-        <v>0</v>
-      </c>
-      <c r="F25" s="14">
-        <v>12</v>
-      </c>
-      <c r="G25" s="18">
-        <v>1</v>
-      </c>
-      <c r="H25" s="12" t="s">
+      <c r="F59" s="13" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="28" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="B28" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="C28" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="D28" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="E28" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="F28" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="G28" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="H28" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="I28" s="11" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="B29" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="C29" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="D29" s="19">
-        <v>1</v>
-      </c>
-      <c r="E29" s="17">
-        <v>110000</v>
-      </c>
-      <c r="F29" s="18">
-        <v>0.28</v>
-      </c>
-      <c r="G29" s="18">
-        <v>0.0765</v>
-      </c>
-      <c r="H29" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="I29" s="12" t="s">
+      <c r="G59" s="13" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="B30" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="C30" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="D30" s="19">
-        <v>1</v>
-      </c>
-      <c r="E30" s="17">
-        <v>90000</v>
-      </c>
-      <c r="F30" s="18">
-        <v>0.28</v>
-      </c>
-      <c r="G30" s="18">
-        <v>0.0765</v>
-      </c>
-      <c r="H30" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="I30" s="12" t="s">
+      <c r="H59" s="13" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="B31" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="C31" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="D31" s="19">
-        <v>1</v>
-      </c>
-      <c r="E31" s="17">
-        <v>72000</v>
-      </c>
-      <c r="F31" s="18">
-        <v>0.28</v>
-      </c>
-      <c r="G31" s="18">
-        <v>0.0765</v>
-      </c>
-      <c r="H31" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="I31" s="12" t="s">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="B60" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="C60" s="18">
+        <v>40000</v>
+      </c>
+      <c r="D60" s="13">
+        <v>0</v>
+      </c>
+      <c r="E60" s="13" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="B32" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="C32" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="D32" s="19">
-        <v>6</v>
-      </c>
-      <c r="E32" s="17">
-        <v>52000</v>
-      </c>
-      <c r="F32" s="18">
-        <v>0.28</v>
-      </c>
-      <c r="G32" s="18">
-        <v>0.0765</v>
-      </c>
-      <c r="H32" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="I32" s="12" t="s">
+      <c r="F60" s="13" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A33" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="B33" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="C33" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="D33" s="19">
-        <v>1</v>
-      </c>
-      <c r="E33" s="17">
-        <v>55000</v>
-      </c>
-      <c r="F33" s="18">
-        <v>0.28</v>
-      </c>
-      <c r="G33" s="18">
-        <v>0.0765</v>
-      </c>
-      <c r="H33" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="I33" s="12" t="s">
+      <c r="G60" s="13" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A34" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="B34" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="C34" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="D34" s="19">
-        <v>3</v>
-      </c>
-      <c r="E34" s="17">
-        <v>30000</v>
-      </c>
-      <c r="F34" s="18">
-        <v>0.2</v>
-      </c>
-      <c r="G34" s="18">
-        <v>0.0765</v>
-      </c>
-      <c r="H34" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="I34" s="12" t="s">
+      <c r="H60" s="13" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A35" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="B35" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="C35" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="D35" s="19">
-        <v>1</v>
-      </c>
-      <c r="E35" s="17">
-        <v>55000</v>
-      </c>
-      <c r="F35" s="18">
-        <v>0.28</v>
-      </c>
-      <c r="G35" s="18">
-        <v>0.0765</v>
-      </c>
-      <c r="H35" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="I35" s="12" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A36" s="12" t="s">
-        <v>98</v>
-      </c>
-      <c r="B36" s="12" t="s">
-        <v>99</v>
-      </c>
-      <c r="C36" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="D36" s="19">
-        <v>2</v>
-      </c>
-      <c r="E36" s="17">
-        <v>38000</v>
-      </c>
-      <c r="F36" s="18">
-        <v>0.25</v>
-      </c>
-      <c r="G36" s="18">
-        <v>0.0765</v>
-      </c>
-      <c r="H36" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="I36" s="12" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A37" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="B37" s="12" t="s">
-        <v>101</v>
-      </c>
-      <c r="C37" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="D37" s="19">
-        <v>1</v>
-      </c>
-      <c r="E37" s="17">
-        <v>55000</v>
-      </c>
-      <c r="F37" s="18">
-        <v>0.28</v>
-      </c>
-      <c r="G37" s="18">
-        <v>0.0765</v>
-      </c>
-      <c r="H37" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="I37" s="12" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="39" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="B39" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="C39" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="D39" s="11"/>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="B40" s="13" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="B41" s="17">
-        <v>18000</v>
-      </c>
-      <c r="C41" s="12" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="B42" s="18">
+    <row r="62" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="B62" s="12"/>
+      <c r="C62" s="12"/>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="B63" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="B64" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="B65" s="20">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="C65" s="23" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="B66" s="19">
         <v>0.03</v>
       </c>
     </row>
-    <row r="44" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="11" t="s">
-        <v>110</v>
-      </c>
-      <c r="B44" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="C44" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="D44" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="E44" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="F44" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="G44" s="11"/>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="B45" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="C45" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="D45" s="17">
-        <v>18000</v>
-      </c>
-      <c r="E45" s="18">
-        <v>0.03</v>
-      </c>
-      <c r="F45" s="12" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="B46" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="C46" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="D46" s="17">
-        <v>2500</v>
-      </c>
-      <c r="E46" s="18">
-        <v>0</v>
-      </c>
-      <c r="F46" s="12" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="B47" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="C47" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="D47" s="17">
-        <v>18000</v>
-      </c>
-      <c r="E47" s="18">
-        <v>0</v>
-      </c>
-      <c r="F47" s="12" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="B48" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="C48" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="D48" s="17">
-        <v>1500</v>
-      </c>
-      <c r="E48" s="18">
-        <v>0</v>
-      </c>
-      <c r="F48" s="12" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="12" t="s">
-        <v>116</v>
-      </c>
-      <c r="B49" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="C49" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="D49" s="17">
-        <v>700</v>
-      </c>
-      <c r="E49" s="18">
-        <v>0</v>
-      </c>
-      <c r="F49" s="12" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="B50" s="12" t="s">
-        <v>119</v>
-      </c>
-      <c r="C50" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="D50" s="17">
-        <v>500</v>
-      </c>
-      <c r="E50" s="18">
-        <v>0</v>
-      </c>
-      <c r="F50" s="12" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="B51" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="C51" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="D51" s="17">
-        <v>25000</v>
-      </c>
-      <c r="E51" s="18">
-        <v>0</v>
-      </c>
-      <c r="F51" s="12" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="12" t="s">
-        <v>122</v>
-      </c>
-      <c r="B52" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="C52" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="D52" s="17">
-        <v>15000</v>
-      </c>
-      <c r="E52" s="18">
-        <v>0</v>
-      </c>
-      <c r="F52" s="12" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="12" t="s">
-        <v>123</v>
-      </c>
-      <c r="B53" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="C53" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="D53" s="17">
-        <v>20000</v>
-      </c>
-      <c r="E53" s="18">
-        <v>0</v>
-      </c>
-      <c r="F53" s="12" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="12" t="s">
-        <v>124</v>
-      </c>
-      <c r="B54" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="C54" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="D54" s="17">
-        <v>800</v>
-      </c>
-      <c r="E54" s="18">
-        <v>0</v>
-      </c>
-      <c r="F54" s="12" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="12" t="s">
-        <v>125</v>
-      </c>
-      <c r="B55" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="C55" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="D55" s="17">
-        <v>600</v>
-      </c>
-      <c r="E55" s="18">
-        <v>0</v>
-      </c>
-      <c r="F55" s="12" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="57" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="B57" s="11" t="s">
-        <v>127</v>
-      </c>
-      <c r="C57" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="D57" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="E57" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="F57" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="G57" s="11" t="s">
-        <v>130</v>
-      </c>
-      <c r="H57" s="11" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A58" s="12" t="s">
-        <v>131</v>
-      </c>
-      <c r="B58" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="C58" s="20">
-        <v>0</v>
-      </c>
-      <c r="D58" s="17">
-        <v>500000</v>
-      </c>
-      <c r="E58" s="21">
-        <v>0.0575</v>
-      </c>
-      <c r="F58" s="14">
-        <v>15</v>
-      </c>
-      <c r="G58" s="20">
-        <v>49825</v>
-      </c>
-      <c r="H58" s="12" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A59" s="12" t="s">
-        <v>132</v>
-      </c>
-      <c r="B59" s="12" t="s">
-        <v>133</v>
-      </c>
-      <c r="C59" s="17">
-        <v>75000</v>
-      </c>
-      <c r="D59" s="12">
-        <v>0</v>
-      </c>
-      <c r="E59" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F59" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="G59" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="H59" s="12" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A60" s="12" t="s">
-        <v>134</v>
-      </c>
-      <c r="B60" s="12" t="s">
-        <v>133</v>
-      </c>
-      <c r="C60" s="17">
-        <v>40000</v>
-      </c>
-      <c r="D60" s="12">
-        <v>0</v>
-      </c>
-      <c r="E60" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F60" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="G60" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="H60" s="12" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="62" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="B62" s="11"/>
-      <c r="C62" s="11"/>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A63" s="12" t="s">
-        <v>136</v>
-      </c>
-      <c r="B63" s="18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A64" s="12" t="s">
-        <v>137</v>
-      </c>
-      <c r="B64" s="18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" s="12" t="s">
-        <v>138</v>
-      </c>
-      <c r="B65" s="19">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="C65" s="22" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A66" s="12" t="s">
-        <v>140</v>
-      </c>
-      <c r="B66" s="18">
-        <v>0.03</v>
-      </c>
-    </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A67" s="12" t="s">
-        <v>141</v>
-      </c>
-      <c r="B67" s="18">
+      <c r="A67" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="B67" s="19">
         <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A68" s="12" t="s">
-        <v>142</v>
-      </c>
-      <c r="B68" s="17">
+      <c r="A68" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="B68" s="18">
         <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A70" s="23" t="s">
-        <v>143</v>
-      </c>
-      <c r="B70" s="23"/>
-      <c r="C70" s="23"/>
-      <c r="D70" s="23"/>
-      <c r="E70" s="23"/>
-      <c r="F70" s="23"/>
-      <c r="G70" s="23"/>
+      <c r="A70" s="24" t="s">
+        <v>144</v>
+      </c>
+      <c r="B70" s="24"/>
+      <c r="C70" s="24"/>
+      <c r="D70" s="24"/>
+      <c r="E70" s="24"/>
+      <c r="F70" s="24"/>
+      <c r="G70" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -2973,7 +2997,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -2982,1021 +3006,1021 @@
       <c r="F1" s="8"/>
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="24" t="s">
-        <v>52</v>
-      </c>
-      <c r="C2" s="24" t="s">
+      <c r="B2" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="D2" s="24" t="s">
+      <c r="C2" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="E2" s="24" t="s">
+      <c r="D2" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="F2" s="24" t="s">
+      <c r="E2" s="25" t="s">
         <v>56</v>
       </c>
+      <c r="F2" s="25" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="25" t="s">
-        <v>57</v>
-      </c>
-      <c r="B3" s="26">
+      <c r="A3" s="26" t="s">
+        <v>58</v>
+      </c>
+      <c r="B3" s="27">
         <f>Assumptions!B17</f>
         <v>120</v>
       </c>
-      <c r="C3" s="26">
+      <c r="C3" s="27">
         <f>Assumptions!C17</f>
         <v>200</v>
       </c>
-      <c r="D3" s="26">
+      <c r="D3" s="27">
         <f>Assumptions!D17</f>
         <v>300</v>
       </c>
-      <c r="E3" s="26">
+      <c r="E3" s="27">
         <f>Assumptions!E17</f>
         <v>375</v>
       </c>
-      <c r="F3" s="26">
+      <c r="F3" s="27">
         <f>Assumptions!F17</f>
         <v>400</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="11" t="s">
-        <v>145</v>
-      </c>
-      <c r="B5" s="11"/>
-      <c r="C5" s="11"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
+      <c r="A5" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="B5" s="12"/>
+      <c r="C5" s="12"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="B6" s="20">
+      <c r="A6" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="B6" s="21">
         <v>950000</v>
       </c>
-      <c r="C6" s="20">
+      <c r="C6" s="21">
         <v>1938000</v>
       </c>
-      <c r="D6" s="20">
+      <c r="D6" s="21">
         <v>2965200</v>
       </c>
-      <c r="E6" s="20">
+      <c r="E6" s="21">
         <v>3780375</v>
       </c>
-      <c r="F6" s="20">
+      <c r="F6" s="21">
         <v>4113200</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="B7" s="20">
+      <c r="A7" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="B7" s="21">
         <v>80000</v>
       </c>
-      <c r="C7" s="20">
+      <c r="C7" s="21">
         <v>163200</v>
       </c>
-      <c r="D7" s="20">
+      <c r="D7" s="21">
         <v>249600</v>
       </c>
-      <c r="E7" s="20">
+      <c r="E7" s="21">
         <v>318375</v>
       </c>
-      <c r="F7" s="20">
+      <c r="F7" s="21">
         <v>346400</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="B8" s="20">
+      <c r="A8" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="B8" s="21">
         <v>120000</v>
       </c>
-      <c r="C8" s="20">
+      <c r="C8" s="21">
         <v>244800</v>
       </c>
-      <c r="D8" s="20">
+      <c r="D8" s="21">
         <v>374400</v>
       </c>
-      <c r="E8" s="20">
+      <c r="E8" s="21">
         <v>477375</v>
       </c>
-      <c r="F8" s="20">
+      <c r="F8" s="21">
         <v>519600</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="B9" s="20">
+      <c r="A9" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="B9" s="21">
         <v>83333</v>
       </c>
-      <c r="C9" s="20">
+      <c r="C9" s="21">
         <v>75000</v>
       </c>
-      <c r="D9" s="20">
+      <c r="D9" s="21">
         <v>50000</v>
       </c>
-      <c r="E9" s="20">
-        <v>0</v>
-      </c>
-      <c r="F9" s="20">
+      <c r="E9" s="21">
+        <v>0</v>
+      </c>
+      <c r="F9" s="21">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="B10" s="20">
+      <c r="A10" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="B10" s="21">
         <v>25000</v>
       </c>
-      <c r="C10" s="20">
+      <c r="C10" s="21">
         <v>40000</v>
       </c>
-      <c r="D10" s="20">
+      <c r="D10" s="21">
         <v>50000</v>
       </c>
-      <c r="E10" s="20">
+      <c r="E10" s="21">
         <v>60000</v>
       </c>
-      <c r="F10" s="20">
+      <c r="F10" s="21">
         <v>70000</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="B11" s="20">
+      <c r="A11" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="B11" s="21">
         <v>30000</v>
       </c>
-      <c r="C11" s="20">
+      <c r="C11" s="21">
         <v>61800</v>
       </c>
-      <c r="D11" s="20">
+      <c r="D11" s="21">
         <v>95400</v>
       </c>
-      <c r="E11" s="20">
+      <c r="E11" s="21">
         <v>123000</v>
       </c>
-      <c r="F11" s="20">
+      <c r="F11" s="21">
         <v>135200</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="B12" s="27">
+      <c r="A12" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="B12" s="28">
         <f>SUM(B6:B11)</f>
         <v>1288333</v>
       </c>
-      <c r="C12" s="27">
+      <c r="C12" s="28">
         <f>SUM(C6:C11)</f>
         <v>2522800</v>
       </c>
-      <c r="D12" s="27">
+      <c r="D12" s="28">
         <f>SUM(D6:D11)</f>
         <v>3784600</v>
       </c>
-      <c r="E12" s="27">
+      <c r="E12" s="28">
         <f>SUM(E6:E11)</f>
         <v>4759125</v>
       </c>
-      <c r="F12" s="27">
+      <c r="F12" s="28">
         <f>SUM(F6:F11)</f>
         <v>5184400</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="11" t="s">
-        <v>147</v>
-      </c>
-      <c r="B14" s="11"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="11"/>
+      <c r="A14" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="B14" s="12"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="12"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="12" t="s">
-        <v>148</v>
-      </c>
-      <c r="B15" s="20">
+      <c r="A15" s="13" t="s">
+        <v>149</v>
+      </c>
+      <c r="B15" s="21">
         <v>124346</v>
       </c>
-      <c r="C15" s="20">
+      <c r="C15" s="21">
         <v>149215</v>
       </c>
-      <c r="D15" s="20">
+      <c r="D15" s="21">
         <v>149215</v>
       </c>
-      <c r="E15" s="20">
+      <c r="E15" s="21">
         <v>149215</v>
       </c>
-      <c r="F15" s="20">
+      <c r="F15" s="21">
         <v>149215</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="12" t="s">
-        <v>149</v>
-      </c>
-      <c r="B16" s="20">
+      <c r="A16" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="B16" s="21">
         <v>101738</v>
       </c>
-      <c r="C16" s="20">
+      <c r="C16" s="21">
         <v>122085</v>
       </c>
-      <c r="D16" s="20">
+      <c r="D16" s="21">
         <v>122085</v>
       </c>
-      <c r="E16" s="20">
+      <c r="E16" s="21">
         <v>122085</v>
       </c>
-      <c r="F16" s="20">
+      <c r="F16" s="21">
         <v>122085</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="B17" s="20">
+      <c r="A17" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="B17" s="21">
         <v>81390</v>
       </c>
-      <c r="C17" s="20">
+      <c r="C17" s="21">
         <v>97668</v>
       </c>
-      <c r="D17" s="20">
+      <c r="D17" s="21">
         <v>97668</v>
       </c>
-      <c r="E17" s="20">
+      <c r="E17" s="21">
         <v>97668</v>
       </c>
-      <c r="F17" s="20">
+      <c r="F17" s="21">
         <v>97668</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="12" t="s">
-        <v>151</v>
-      </c>
-      <c r="B18" s="20">
+      <c r="A18" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="B18" s="21">
         <v>352690</v>
       </c>
-      <c r="C18" s="20">
+      <c r="C18" s="21">
         <v>423228</v>
       </c>
-      <c r="D18" s="20">
+      <c r="D18" s="21">
         <v>423228</v>
       </c>
-      <c r="E18" s="20">
+      <c r="E18" s="21">
         <v>423228</v>
       </c>
-      <c r="F18" s="20">
+      <c r="F18" s="21">
         <v>423228</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="12" t="s">
-        <v>152</v>
-      </c>
-      <c r="B19" s="20">
+      <c r="A19" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="B19" s="21">
         <v>62173</v>
       </c>
-      <c r="C19" s="20">
+      <c r="C19" s="21">
         <v>74608</v>
       </c>
-      <c r="D19" s="20">
+      <c r="D19" s="21">
         <v>74608</v>
       </c>
-      <c r="E19" s="20">
+      <c r="E19" s="21">
         <v>74608</v>
       </c>
-      <c r="F19" s="20">
+      <c r="F19" s="21">
         <v>74608</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="12" t="s">
-        <v>153</v>
-      </c>
-      <c r="B20" s="20">
+      <c r="A20" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="B20" s="21">
         <v>95738</v>
       </c>
-      <c r="C20" s="20">
+      <c r="C20" s="21">
         <v>114885</v>
       </c>
-      <c r="D20" s="20">
+      <c r="D20" s="21">
         <v>114885</v>
       </c>
-      <c r="E20" s="20">
+      <c r="E20" s="21">
         <v>114885</v>
       </c>
-      <c r="F20" s="20">
+      <c r="F20" s="21">
         <v>114885</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="12" t="s">
-        <v>154</v>
-      </c>
-      <c r="B21" s="20">
+      <c r="A21" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="B21" s="21">
         <v>62173</v>
       </c>
-      <c r="C21" s="20">
+      <c r="C21" s="21">
         <v>74608</v>
       </c>
-      <c r="D21" s="20">
+      <c r="D21" s="21">
         <v>74608</v>
       </c>
-      <c r="E21" s="20">
+      <c r="E21" s="21">
         <v>74608</v>
       </c>
-      <c r="F21" s="20">
+      <c r="F21" s="21">
         <v>74608</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="B22" s="20">
+      <c r="A22" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="B22" s="21">
         <v>84012</v>
       </c>
-      <c r="C22" s="20">
+      <c r="C22" s="21">
         <v>100814</v>
       </c>
-      <c r="D22" s="20">
+      <c r="D22" s="21">
         <v>100814</v>
       </c>
-      <c r="E22" s="20">
+      <c r="E22" s="21">
         <v>100814</v>
       </c>
-      <c r="F22" s="20">
+      <c r="F22" s="21">
         <v>100814</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="12" t="s">
-        <v>156</v>
-      </c>
-      <c r="B23" s="20">
+      <c r="A23" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="B23" s="21">
         <v>62173</v>
       </c>
-      <c r="C23" s="20">
+      <c r="C23" s="21">
         <v>74608</v>
       </c>
-      <c r="D23" s="20">
+      <c r="D23" s="21">
         <v>74608</v>
       </c>
-      <c r="E23" s="20">
+      <c r="E23" s="21">
         <v>74608</v>
       </c>
-      <c r="F23" s="20">
+      <c r="F23" s="21">
         <v>74608</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="11" t="s">
-        <v>157</v>
-      </c>
-      <c r="B24" s="27">
+      <c r="A24" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="B24" s="28">
         <f>SUM(B15:B23)</f>
         <v>1026431</v>
       </c>
-      <c r="C24" s="27">
+      <c r="C24" s="28">
         <f>SUM(C15:C23)</f>
         <v>1231718</v>
       </c>
-      <c r="D24" s="27">
+      <c r="D24" s="28">
         <f>SUM(D15:D23)</f>
         <v>1231718</v>
       </c>
-      <c r="E24" s="27">
+      <c r="E24" s="28">
         <f>SUM(E15:E23)</f>
         <v>1231718</v>
       </c>
-      <c r="F24" s="27">
+      <c r="F24" s="28">
         <f>SUM(F15:F23)</f>
         <v>1231718</v>
       </c>
     </row>
     <row r="26" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="11" t="s">
-        <v>110</v>
-      </c>
-      <c r="B26" s="11"/>
-      <c r="C26" s="11"/>
-      <c r="D26" s="11"/>
-      <c r="E26" s="11"/>
-      <c r="F26" s="11"/>
+      <c r="A26" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="B26" s="12"/>
+      <c r="C26" s="12"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="12"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="B27" s="12"/>
-      <c r="C27" s="12"/>
-      <c r="D27" s="12"/>
-      <c r="E27" s="12"/>
-      <c r="F27" s="12"/>
+      <c r="A27" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="B27" s="13"/>
+      <c r="C27" s="13"/>
+      <c r="D27" s="13"/>
+      <c r="E27" s="13"/>
+      <c r="F27" s="13"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="B28" s="20">
+      <c r="A28" s="13" t="s">
+        <v>159</v>
+      </c>
+      <c r="B28" s="21">
         <v>70000</v>
       </c>
-      <c r="C28" s="20">
+      <c r="C28" s="21">
         <v>144200</v>
       </c>
-      <c r="D28" s="20">
+      <c r="D28" s="21">
         <v>222900</v>
       </c>
-      <c r="E28" s="20">
+      <c r="E28" s="21">
         <v>286875</v>
       </c>
-      <c r="F28" s="20">
+      <c r="F28" s="21">
         <v>315200</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="28" t="s">
-        <v>159</v>
-      </c>
-      <c r="B29" s="29">
+      <c r="A29" s="29" t="s">
+        <v>160</v>
+      </c>
+      <c r="B29" s="30">
         <v>70000</v>
       </c>
-      <c r="C29" s="29">
+      <c r="C29" s="30">
         <v>144200</v>
       </c>
-      <c r="D29" s="29">
+      <c r="D29" s="30">
         <v>222900</v>
       </c>
-      <c r="E29" s="29">
+      <c r="E29" s="30">
         <v>286875</v>
       </c>
-      <c r="F29" s="29">
+      <c r="F29" s="30">
         <v>315200</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="12" t="s">
-        <v>119</v>
-      </c>
-      <c r="B30" s="12"/>
-      <c r="C30" s="12"/>
-      <c r="D30" s="12"/>
-      <c r="E30" s="12"/>
-      <c r="F30" s="12"/>
+      <c r="A30" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="B30" s="13"/>
+      <c r="C30" s="13"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="13"/>
+      <c r="F30" s="13"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="12" t="s">
-        <v>160</v>
-      </c>
-      <c r="B31" s="20">
+      <c r="A31" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="B31" s="21">
         <v>50000</v>
       </c>
-      <c r="C31" s="20">
+      <c r="C31" s="21">
         <v>103000</v>
       </c>
-      <c r="D31" s="20">
+      <c r="D31" s="21">
         <v>159000</v>
       </c>
-      <c r="E31" s="20">
+      <c r="E31" s="21">
         <v>204750</v>
       </c>
-      <c r="F31" s="20">
+      <c r="F31" s="21">
         <v>224800</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="28" t="s">
-        <v>161</v>
-      </c>
-      <c r="B32" s="29">
+      <c r="A32" s="29" t="s">
+        <v>162</v>
+      </c>
+      <c r="B32" s="30">
         <v>50000</v>
       </c>
-      <c r="C32" s="29">
+      <c r="C32" s="30">
         <v>103000</v>
       </c>
-      <c r="D32" s="29">
+      <c r="D32" s="30">
         <v>159000</v>
       </c>
-      <c r="E32" s="29">
+      <c r="E32" s="30">
         <v>204750</v>
       </c>
-      <c r="F32" s="29">
+      <c r="F32" s="30">
         <v>224800</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="B33" s="12"/>
-      <c r="C33" s="12"/>
-      <c r="D33" s="12"/>
-      <c r="E33" s="12"/>
-      <c r="F33" s="12"/>
+      <c r="A33" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="B33" s="13"/>
+      <c r="C33" s="13"/>
+      <c r="D33" s="13"/>
+      <c r="E33" s="13"/>
+      <c r="F33" s="13"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="12" t="s">
-        <v>162</v>
-      </c>
-      <c r="B34" s="20">
+      <c r="A34" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="B34" s="21">
         <v>180000</v>
       </c>
-      <c r="C34" s="20">
+      <c r="C34" s="21">
         <v>222480</v>
       </c>
-      <c r="D34" s="20">
+      <c r="D34" s="21">
         <v>229154</v>
       </c>
-      <c r="E34" s="20">
+      <c r="E34" s="21">
         <v>236029</v>
       </c>
-      <c r="F34" s="20">
+      <c r="F34" s="21">
         <v>243110</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="B35" s="20">
+      <c r="A35" s="13" t="s">
+        <v>164</v>
+      </c>
+      <c r="B35" s="21">
         <v>25000</v>
       </c>
-      <c r="C35" s="20">
+      <c r="C35" s="21">
         <v>30900</v>
       </c>
-      <c r="D35" s="20">
+      <c r="D35" s="21">
         <v>31824</v>
       </c>
-      <c r="E35" s="20">
+      <c r="E35" s="21">
         <v>32784</v>
       </c>
-      <c r="F35" s="20">
+      <c r="F35" s="21">
         <v>33768</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="12" t="s">
-        <v>164</v>
-      </c>
-      <c r="B36" s="20">
+      <c r="A36" s="13" t="s">
+        <v>165</v>
+      </c>
+      <c r="B36" s="21">
         <v>15000</v>
       </c>
-      <c r="C36" s="20">
+      <c r="C36" s="21">
         <v>18540</v>
       </c>
-      <c r="D36" s="20">
+      <c r="D36" s="21">
         <v>19096</v>
       </c>
-      <c r="E36" s="20">
+      <c r="E36" s="21">
         <v>19669</v>
       </c>
-      <c r="F36" s="20">
+      <c r="F36" s="21">
         <v>20259</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="12" t="s">
-        <v>165</v>
-      </c>
-      <c r="B37" s="20">
+      <c r="A37" s="13" t="s">
+        <v>166</v>
+      </c>
+      <c r="B37" s="21">
         <v>15000</v>
       </c>
-      <c r="C37" s="20">
+      <c r="C37" s="21">
         <v>18540</v>
       </c>
-      <c r="D37" s="20">
+      <c r="D37" s="21">
         <v>19092</v>
       </c>
-      <c r="E37" s="20">
+      <c r="E37" s="21">
         <v>19668</v>
       </c>
-      <c r="F37" s="20">
+      <c r="F37" s="21">
         <v>20256</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="28" t="s">
-        <v>166</v>
-      </c>
-      <c r="B38" s="29">
+      <c r="A38" s="29" t="s">
+        <v>167</v>
+      </c>
+      <c r="B38" s="30">
         <v>235000</v>
       </c>
-      <c r="C38" s="29">
+      <c r="C38" s="30">
         <v>290460</v>
       </c>
-      <c r="D38" s="29">
+      <c r="D38" s="30">
         <v>299166</v>
       </c>
-      <c r="E38" s="29">
+      <c r="E38" s="30">
         <v>308150</v>
       </c>
-      <c r="F38" s="29">
+      <c r="F38" s="30">
         <v>317393</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="B39" s="12"/>
-      <c r="C39" s="12"/>
-      <c r="D39" s="12"/>
-      <c r="E39" s="12"/>
-      <c r="F39" s="12"/>
+      <c r="A39" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="B39" s="13"/>
+      <c r="C39" s="13"/>
+      <c r="D39" s="13"/>
+      <c r="E39" s="13"/>
+      <c r="F39" s="13"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="12" t="s">
-        <v>167</v>
-      </c>
-      <c r="B40" s="20">
+      <c r="A40" s="13" t="s">
+        <v>168</v>
+      </c>
+      <c r="B40" s="21">
         <v>20833</v>
       </c>
-      <c r="C40" s="20">
+      <c r="C40" s="21">
         <v>25750</v>
       </c>
-      <c r="D40" s="20">
+      <c r="D40" s="21">
         <v>26523</v>
       </c>
-      <c r="E40" s="20">
+      <c r="E40" s="21">
         <v>27318</v>
       </c>
-      <c r="F40" s="20">
+      <c r="F40" s="21">
         <v>28138</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="12" t="s">
-        <v>168</v>
-      </c>
-      <c r="B41" s="20">
+      <c r="A41" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="B41" s="21">
         <v>12500</v>
       </c>
-      <c r="C41" s="20">
+      <c r="C41" s="21">
         <v>15450</v>
       </c>
-      <c r="D41" s="20">
+      <c r="D41" s="21">
         <v>15914</v>
       </c>
-      <c r="E41" s="20">
+      <c r="E41" s="21">
         <v>16391</v>
       </c>
-      <c r="F41" s="20">
+      <c r="F41" s="21">
         <v>16883</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="12" t="s">
-        <v>169</v>
-      </c>
-      <c r="B42" s="20">
+      <c r="A42" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="B42" s="21">
         <v>16667</v>
       </c>
-      <c r="C42" s="20">
+      <c r="C42" s="21">
         <v>20600</v>
       </c>
-      <c r="D42" s="20">
+      <c r="D42" s="21">
         <v>21218</v>
       </c>
-      <c r="E42" s="20">
+      <c r="E42" s="21">
         <v>21855</v>
       </c>
-      <c r="F42" s="20">
+      <c r="F42" s="21">
         <v>22510</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="12" t="s">
-        <v>170</v>
-      </c>
-      <c r="B43" s="20">
+      <c r="A43" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="B43" s="21">
         <v>80000</v>
       </c>
-      <c r="C43" s="20">
+      <c r="C43" s="21">
         <v>164800</v>
       </c>
-      <c r="D43" s="20">
+      <c r="D43" s="21">
         <v>254700</v>
       </c>
-      <c r="E43" s="20">
+      <c r="E43" s="21">
         <v>327750</v>
       </c>
-      <c r="F43" s="20">
+      <c r="F43" s="21">
         <v>360000</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="12" t="s">
-        <v>171</v>
-      </c>
-      <c r="B44" s="20">
+      <c r="A44" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="B44" s="21">
         <v>60000</v>
       </c>
-      <c r="C44" s="20">
+      <c r="C44" s="21">
         <v>123600</v>
       </c>
-      <c r="D44" s="20">
+      <c r="D44" s="21">
         <v>191100</v>
       </c>
-      <c r="E44" s="20">
+      <c r="E44" s="21">
         <v>246000</v>
       </c>
-      <c r="F44" s="20">
+      <c r="F44" s="21">
         <v>270000</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="28" t="s">
-        <v>172</v>
-      </c>
-      <c r="B45" s="29">
+      <c r="A45" s="29" t="s">
+        <v>173</v>
+      </c>
+      <c r="B45" s="30">
         <v>190000</v>
       </c>
-      <c r="C45" s="29">
+      <c r="C45" s="30">
         <v>350200</v>
       </c>
-      <c r="D45" s="29">
+      <c r="D45" s="30">
         <v>509455</v>
       </c>
-      <c r="E45" s="29">
+      <c r="E45" s="30">
         <v>639314</v>
       </c>
-      <c r="F45" s="29">
+      <c r="F45" s="30">
         <v>697531</v>
       </c>
     </row>
     <row r="46" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="B46" s="27">
+      <c r="A46" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="B46" s="28">
         <f>B29+B32+B38+B45</f>
         <v>545000</v>
       </c>
-      <c r="C46" s="27">
+      <c r="C46" s="28">
         <f>C29+C32+C38+C45</f>
         <v>887860</v>
       </c>
-      <c r="D46" s="27">
+      <c r="D46" s="28">
         <f>D29+D32+D38+D45</f>
         <v>1190521</v>
       </c>
-      <c r="E46" s="27">
+      <c r="E46" s="28">
         <f>E29+E32+E38+E45</f>
         <v>1439089</v>
       </c>
-      <c r="F46" s="27">
+      <c r="F46" s="28">
         <f>F29+F32+F38+F45</f>
         <v>1554924</v>
       </c>
     </row>
     <row r="48" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="11" t="s">
-        <v>174</v>
-      </c>
-      <c r="B48" s="11"/>
-      <c r="C48" s="11"/>
-      <c r="D48" s="11"/>
-      <c r="E48" s="11"/>
-      <c r="F48" s="11"/>
+      <c r="A48" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="B48" s="12"/>
+      <c r="C48" s="12"/>
+      <c r="D48" s="12"/>
+      <c r="E48" s="12"/>
+      <c r="F48" s="12"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="12" t="s">
-        <v>131</v>
-      </c>
-      <c r="B49" s="20">
+      <c r="A49" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="B49" s="21">
         <v>49825</v>
       </c>
-      <c r="C49" s="20">
+      <c r="C49" s="21">
         <v>49825</v>
       </c>
-      <c r="D49" s="20">
+      <c r="D49" s="21">
         <v>49825</v>
       </c>
-      <c r="E49" s="20">
+      <c r="E49" s="21">
         <v>49825</v>
       </c>
-      <c r="F49" s="20">
+      <c r="F49" s="21">
         <v>49825</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="12" t="s">
-        <v>132</v>
-      </c>
-      <c r="B50" s="20">
+      <c r="A50" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="B50" s="21">
         <v>75000</v>
       </c>
-      <c r="C50" s="20">
+      <c r="C50" s="21">
         <v>25000</v>
       </c>
-      <c r="D50" s="20">
+      <c r="D50" s="21">
         <v>30000</v>
       </c>
-      <c r="E50" s="20">
+      <c r="E50" s="21">
         <v>15000</v>
       </c>
-      <c r="F50" s="20">
+      <c r="F50" s="21">
         <v>10000</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="12" t="s">
-        <v>134</v>
-      </c>
-      <c r="B51" s="20">
+      <c r="A51" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="B51" s="21">
         <v>40000</v>
       </c>
-      <c r="C51" s="20">
+      <c r="C51" s="21">
         <v>15000</v>
       </c>
-      <c r="D51" s="20">
+      <c r="D51" s="21">
         <v>10000</v>
       </c>
-      <c r="E51" s="20">
+      <c r="E51" s="21">
         <v>10000</v>
       </c>
-      <c r="F51" s="20">
+      <c r="F51" s="21">
         <v>10000</v>
       </c>
     </row>
     <row r="52" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="11" t="s">
-        <v>175</v>
-      </c>
-      <c r="B52" s="27">
+      <c r="A52" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="B52" s="28">
         <f>SUM(B49:B51)</f>
         <v>164825</v>
       </c>
-      <c r="C52" s="27">
+      <c r="C52" s="28">
         <f>SUM(C49:C51)</f>
         <v>89825</v>
       </c>
-      <c r="D52" s="27">
+      <c r="D52" s="28">
         <f>SUM(D49:D51)</f>
         <v>89825</v>
       </c>
-      <c r="E52" s="27">
+      <c r="E52" s="28">
         <f>SUM(E49:E51)</f>
         <v>74825</v>
       </c>
-      <c r="F52" s="27">
+      <c r="F52" s="28">
         <f>SUM(F49:F51)</f>
         <v>69825</v>
       </c>
     </row>
     <row r="54" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="B54" s="11"/>
-      <c r="C54" s="11"/>
-      <c r="D54" s="11"/>
-      <c r="E54" s="11"/>
-      <c r="F54" s="11"/>
+      <c r="A54" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="B54" s="12"/>
+      <c r="C54" s="12"/>
+      <c r="D54" s="12"/>
+      <c r="E54" s="12"/>
+      <c r="F54" s="12"/>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="25" t="s">
-        <v>177</v>
-      </c>
-      <c r="B55" s="29">
+      <c r="A55" s="26" t="s">
+        <v>178</v>
+      </c>
+      <c r="B55" s="30">
         <f>B12</f>
         <v>1288333</v>
       </c>
-      <c r="C55" s="29">
+      <c r="C55" s="30">
         <f>C12</f>
         <v>2522800</v>
       </c>
-      <c r="D55" s="29">
+      <c r="D55" s="30">
         <f>D12</f>
         <v>3784600</v>
       </c>
-      <c r="E55" s="29">
+      <c r="E55" s="30">
         <f>E12</f>
         <v>4759125</v>
       </c>
-      <c r="F55" s="29">
+      <c r="F55" s="30">
         <f>F12</f>
         <v>5184400</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="B56" s="20">
+      <c r="A56" s="13" t="s">
+        <v>179</v>
+      </c>
+      <c r="B56" s="21">
         <f>B24</f>
         <v>1026431</v>
       </c>
-      <c r="C56" s="20">
+      <c r="C56" s="21">
         <f>C24</f>
         <v>1231718</v>
       </c>
-      <c r="D56" s="20">
+      <c r="D56" s="21">
         <f>D24</f>
         <v>1231718</v>
       </c>
-      <c r="E56" s="20">
+      <c r="E56" s="21">
         <f>E24</f>
         <v>1231718</v>
       </c>
-      <c r="F56" s="20">
+      <c r="F56" s="21">
         <f>F24</f>
         <v>1231718</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="12" t="s">
-        <v>179</v>
-      </c>
-      <c r="B57" s="20">
+      <c r="A57" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="B57" s="21">
         <f>B46</f>
         <v>545000</v>
       </c>
-      <c r="C57" s="20">
+      <c r="C57" s="21">
         <f>C46</f>
         <v>887860</v>
       </c>
-      <c r="D57" s="20">
+      <c r="D57" s="21">
         <f>D46</f>
         <v>1190521</v>
       </c>
-      <c r="E57" s="20">
+      <c r="E57" s="21">
         <f>E46</f>
         <v>1439089</v>
       </c>
-      <c r="F57" s="20">
+      <c r="F57" s="21">
         <f>F46</f>
         <v>1554924</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="12" t="s">
-        <v>180</v>
-      </c>
-      <c r="B58" s="20">
+      <c r="A58" s="13" t="s">
+        <v>181</v>
+      </c>
+      <c r="B58" s="21">
         <f>B52</f>
         <v>164825</v>
       </c>
-      <c r="C58" s="20">
+      <c r="C58" s="21">
         <f>C52</f>
         <v>89825</v>
       </c>
-      <c r="D58" s="20">
+      <c r="D58" s="21">
         <f>D52</f>
         <v>89825</v>
       </c>
-      <c r="E58" s="20">
+      <c r="E58" s="21">
         <f>E52</f>
         <v>74825</v>
       </c>
-      <c r="F58" s="20">
+      <c r="F58" s="21">
         <f>F52</f>
         <v>69825</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="25" t="s">
-        <v>181</v>
-      </c>
-      <c r="B59" s="29">
+      <c r="A59" s="26" t="s">
+        <v>182</v>
+      </c>
+      <c r="B59" s="30">
         <f>B56+B57+B58</f>
         <v>1736256</v>
       </c>
-      <c r="C59" s="29">
+      <c r="C59" s="30">
         <f>C56+C57+C58</f>
         <v>2209403</v>
       </c>
-      <c r="D59" s="29">
+      <c r="D59" s="30">
         <f>D56+D57+D58</f>
         <v>2512064</v>
       </c>
-      <c r="E59" s="29">
+      <c r="E59" s="30">
         <f>E56+E57+E58</f>
         <v>2745632</v>
       </c>
-      <c r="F59" s="29">
+      <c r="F59" s="30">
         <f>F56+F57+F58</f>
         <v>2856467</v>
       </c>
@@ -4007,569 +4031,569 @@
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="30" t="s">
-        <v>182</v>
-      </c>
-      <c r="B61" s="31">
+      <c r="A61" s="31" t="s">
+        <v>183</v>
+      </c>
+      <c r="B61" s="32">
         <f>B55-B59</f>
         <v>-447923</v>
       </c>
-      <c r="C61" s="32">
+      <c r="C61" s="33">
         <f>C55-C59</f>
         <v>313397</v>
       </c>
-      <c r="D61" s="32">
+      <c r="D61" s="33">
         <f>D55-D59</f>
         <v>1272536</v>
       </c>
-      <c r="E61" s="32">
+      <c r="E61" s="33">
         <f>E55-E59</f>
         <v>2013493</v>
       </c>
-      <c r="F61" s="32">
+      <c r="F61" s="33">
         <f>F55-F59</f>
         <v>2327933</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="12" t="s">
-        <v>183</v>
-      </c>
-      <c r="B62" s="33">
+      <c r="A62" s="13" t="s">
+        <v>184</v>
+      </c>
+      <c r="B62" s="34">
         <f>IF(B55=0,"",B61/B55)</f>
         <v>-0.35</v>
       </c>
-      <c r="C62" s="33">
+      <c r="C62" s="34">
         <f>IF(C55=0,"",C61/C55)</f>
         <v>0.12</v>
       </c>
-      <c r="D62" s="33">
+      <c r="D62" s="34">
         <f>IF(D55=0,"",D61/D55)</f>
         <v>0.34</v>
       </c>
-      <c r="E62" s="33">
+      <c r="E62" s="34">
         <f>IF(E55=0,"",E61/E55)</f>
         <v>0.42</v>
       </c>
-      <c r="F62" s="33">
+      <c r="F62" s="34">
         <f>IF(F55=0,"",F61/F55)</f>
         <v>0.45</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" s="12" t="s">
-        <v>184</v>
-      </c>
-      <c r="B63" s="20">
+      <c r="A63" s="13" t="s">
+        <v>185</v>
+      </c>
+      <c r="B63" s="21">
         <f>B61</f>
         <v>-447923</v>
       </c>
-      <c r="C63" s="20">
+      <c r="C63" s="21">
         <f>B63+C61</f>
         <v>-134526</v>
       </c>
-      <c r="D63" s="20">
+      <c r="D63" s="21">
         <f>C63+D61</f>
         <v>1138010</v>
       </c>
-      <c r="E63" s="20">
+      <c r="E63" s="21">
         <f>D63+E61</f>
         <v>3151503</v>
       </c>
-      <c r="F63" s="20">
+      <c r="F63" s="21">
         <f>E63+F61</f>
         <v>5479436</v>
       </c>
     </row>
     <row r="65" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A65" s="11" t="s">
-        <v>185</v>
-      </c>
-      <c r="B65" s="11"/>
-      <c r="C65" s="11"/>
-      <c r="D65" s="11"/>
-      <c r="E65" s="11"/>
-      <c r="F65" s="11"/>
+      <c r="A65" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="B65" s="12"/>
+      <c r="C65" s="12"/>
+      <c r="D65" s="12"/>
+      <c r="E65" s="12"/>
+      <c r="F65" s="12"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A66" s="25" t="s">
-        <v>186</v>
-      </c>
-      <c r="B66" s="29">
+      <c r="A66" s="26" t="s">
+        <v>187</v>
+      </c>
+      <c r="B66" s="30">
         <f>B55-B56-B57</f>
         <v>-283098</v>
       </c>
-      <c r="C66" s="29">
+      <c r="C66" s="30">
         <f>C55-C56-C57</f>
         <v>403222</v>
       </c>
-      <c r="D66" s="29">
+      <c r="D66" s="30">
         <f>D55-D56-D57</f>
         <v>1362361</v>
       </c>
-      <c r="E66" s="29">
+      <c r="E66" s="30">
         <f>E55-E56-E57</f>
         <v>2088318</v>
       </c>
-      <c r="F66" s="29">
+      <c r="F66" s="30">
         <f>F55-F56-F57</f>
         <v>2397758</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A67" s="12" t="s">
-        <v>187</v>
-      </c>
-      <c r="B67" s="20">
+      <c r="A67" s="13" t="s">
+        <v>188</v>
+      </c>
+      <c r="B67" s="21">
         <f>B58</f>
         <v>164825</v>
       </c>
-      <c r="C67" s="20">
+      <c r="C67" s="21">
         <f>C58</f>
         <v>89825</v>
       </c>
-      <c r="D67" s="20">
+      <c r="D67" s="21">
         <f>D58</f>
         <v>89825</v>
       </c>
-      <c r="E67" s="20">
+      <c r="E67" s="21">
         <f>E58</f>
         <v>74825</v>
       </c>
-      <c r="F67" s="20">
+      <c r="F67" s="21">
         <f>F58</f>
         <v>69825</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A68" s="25" t="s">
-        <v>188</v>
-      </c>
-      <c r="B68" s="34">
+      <c r="A68" s="26" t="s">
+        <v>189</v>
+      </c>
+      <c r="B68" s="35">
         <f>IF(B67=0,"N/A",B66/B67)</f>
         <v>-1.72</v>
       </c>
-      <c r="C68" s="34">
+      <c r="C68" s="35">
         <f>IF(C67=0,"N/A",C66/C67)</f>
         <v>4.49</v>
       </c>
-      <c r="D68" s="34">
+      <c r="D68" s="35">
         <f>IF(D67=0,"N/A",D66/D67)</f>
         <v>15.17</v>
       </c>
-      <c r="E68" s="34">
+      <c r="E68" s="35">
         <f>IF(E67=0,"N/A",E66/E67)</f>
         <v>27.91</v>
       </c>
-      <c r="F68" s="34">
+      <c r="F68" s="35">
         <f>IF(F67=0,"N/A",F66/F67)</f>
         <v>34.34</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A69" s="12" t="s">
-        <v>142</v>
-      </c>
-      <c r="B69" s="20" t="str">
+      <c r="A69" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="B69" s="21" t="str">
         <f>Assumptions!B68</f>
         <v>0</v>
       </c>
-      <c r="C69" s="20">
+      <c r="C69" s="21">
         <f>B70</f>
         <v>-447923</v>
       </c>
-      <c r="D69" s="20">
+      <c r="D69" s="21">
         <f>C70</f>
         <v>-134526</v>
       </c>
-      <c r="E69" s="20">
+      <c r="E69" s="21">
         <f>D70</f>
         <v>1138010</v>
       </c>
-      <c r="F69" s="20">
+      <c r="F69" s="21">
         <f>E70</f>
         <v>3151503</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A70" s="25" t="s">
-        <v>189</v>
-      </c>
-      <c r="B70" s="29">
+      <c r="A70" s="26" t="s">
+        <v>190</v>
+      </c>
+      <c r="B70" s="30">
         <f>B69+B61</f>
         <v>-447923</v>
       </c>
-      <c r="C70" s="29">
+      <c r="C70" s="30">
         <f>C69+C61</f>
         <v>-134526</v>
       </c>
-      <c r="D70" s="29">
+      <c r="D70" s="30">
         <f>D69+D61</f>
         <v>1138010</v>
       </c>
-      <c r="E70" s="29">
+      <c r="E70" s="30">
         <f>E69+E61</f>
         <v>3151503</v>
       </c>
-      <c r="F70" s="29">
+      <c r="F70" s="30">
         <f>F69+F61</f>
         <v>5479436</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A71" s="12" t="s">
-        <v>190</v>
-      </c>
-      <c r="B71" s="35">
+      <c r="A71" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="B71" s="36">
         <f>IF(B59=0,"",B70/B59*365)</f>
         <v>-94</v>
       </c>
-      <c r="C71" s="35">
+      <c r="C71" s="36">
         <f>IF(C59=0,"",C70/C59*365)</f>
         <v>-22</v>
       </c>
-      <c r="D71" s="35">
+      <c r="D71" s="36">
         <f>IF(D59=0,"",D70/D59*365)</f>
         <v>165</v>
       </c>
-      <c r="E71" s="35">
+      <c r="E71" s="36">
         <f>IF(E59=0,"",E70/E59*365)</f>
         <v>419</v>
       </c>
-      <c r="F71" s="35">
+      <c r="F71" s="36">
         <f>IF(F59=0,"",F70/F59*365)</f>
         <v>700</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A72" s="12" t="s">
-        <v>191</v>
-      </c>
-      <c r="B72" s="36">
+      <c r="A72" s="13" t="s">
+        <v>192</v>
+      </c>
+      <c r="B72" s="37">
         <f>IF(B59=0,"",B70/(B59/12))</f>
         <v>-3.1</v>
       </c>
-      <c r="C72" s="36">
+      <c r="C72" s="37">
         <f>IF(C59=0,"",C70/(C59/12))</f>
         <v>-0.7</v>
       </c>
-      <c r="D72" s="36">
+      <c r="D72" s="37">
         <f>IF(D59=0,"",D70/(D59/12))</f>
         <v>5.4</v>
       </c>
-      <c r="E72" s="36">
+      <c r="E72" s="37">
         <f>IF(E59=0,"",E70/(E59/12))</f>
         <v>13.8</v>
       </c>
-      <c r="F72" s="36">
+      <c r="F72" s="37">
         <f>IF(F59=0,"",F70/(F59/12))</f>
         <v>23</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A73" s="12" t="s">
-        <v>192</v>
-      </c>
-      <c r="B73" s="33">
+      <c r="A73" s="13" t="s">
+        <v>193</v>
+      </c>
+      <c r="B73" s="34">
         <f>IF(Assumptions!B12=0,"",B3/Assumptions!B12)</f>
         <v>0.3</v>
       </c>
-      <c r="C73" s="33">
+      <c r="C73" s="34">
         <f>IF(Assumptions!B12=0,"",C3/Assumptions!B12)</f>
         <v>0.5</v>
       </c>
-      <c r="D73" s="33">
+      <c r="D73" s="34">
         <f>IF(Assumptions!B12=0,"",D3/Assumptions!B12)</f>
         <v>0.75</v>
       </c>
-      <c r="E73" s="33">
+      <c r="E73" s="34">
         <f>IF(Assumptions!B12=0,"",E3/Assumptions!B12)</f>
         <v>0.94</v>
       </c>
-      <c r="F73" s="33">
+      <c r="F73" s="34">
         <f>IF(Assumptions!B12=0,"",F3/Assumptions!B12)</f>
         <v>1</v>
       </c>
     </row>
     <row r="75" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A75" s="11" t="s">
-        <v>193</v>
-      </c>
-      <c r="B75" s="11"/>
-      <c r="C75" s="11"/>
-      <c r="D75" s="11"/>
-      <c r="E75" s="11"/>
-      <c r="F75" s="11"/>
+      <c r="A75" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="B75" s="12"/>
+      <c r="C75" s="12"/>
+      <c r="D75" s="12"/>
+      <c r="E75" s="12"/>
+      <c r="F75" s="12"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A76" s="12" t="s">
-        <v>194</v>
-      </c>
-      <c r="B76" s="12" t="str">
+      <c r="A76" s="13" t="s">
+        <v>195</v>
+      </c>
+      <c r="B76" s="13" t="str">
         <f>IF(B67=0,"N/A",IF(B68&gt;=1.2,"PASS","FAIL"))</f>
         <v>FAIL</v>
       </c>
-      <c r="C76" s="12" t="str">
+      <c r="C76" s="13" t="str">
         <f>IF(C67=0,"N/A",IF(C68&gt;=1.2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="D76" s="12" t="str">
+      <c r="D76" s="13" t="str">
         <f>IF(D67=0,"N/A",IF(D68&gt;=1.2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="E76" s="12" t="str">
+      <c r="E76" s="13" t="str">
         <f>IF(E67=0,"N/A",IF(E68&gt;=1.2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="F76" s="12" t="str">
+      <c r="F76" s="13" t="str">
         <f>IF(F67=0,"N/A",IF(F68&gt;=1.2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A77" s="12" t="s">
-        <v>195</v>
-      </c>
-      <c r="B77" s="12" t="str">
+      <c r="A77" s="13" t="s">
+        <v>196</v>
+      </c>
+      <c r="B77" s="13" t="str">
         <f>IF(B61&gt;0,"PASS","FAIL")</f>
         <v>FAIL</v>
       </c>
-      <c r="C77" s="12" t="str">
+      <c r="C77" s="13" t="str">
         <f>IF(C61&gt;0,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-      <c r="D77" s="12" t="str">
+      <c r="D77" s="13" t="str">
         <f>IF(D61&gt;0,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-      <c r="E77" s="12" t="str">
+      <c r="E77" s="13" t="str">
         <f>IF(E61&gt;0,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-      <c r="F77" s="12" t="str">
+      <c r="F77" s="13" t="str">
         <f>IF(F61&gt;0,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A78" s="12" t="s">
-        <v>196</v>
-      </c>
-      <c r="B78" s="12" t="str">
+      <c r="A78" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="B78" s="13" t="str">
         <f>IF(Assumptions!B12=0,"N/A",IF(B3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
         <v>FAIL</v>
       </c>
-      <c r="C78" s="12" t="str">
+      <c r="C78" s="13" t="str">
         <f>IF(Assumptions!B12=0,"N/A",IF(C3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
         <v>FAIL</v>
       </c>
-      <c r="D78" s="12" t="str">
+      <c r="D78" s="13" t="str">
         <f>IF(Assumptions!B12=0,"N/A",IF(D3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="E78" s="12" t="str">
+      <c r="E78" s="13" t="str">
         <f>IF(Assumptions!B12=0,"N/A",IF(E3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="F78" s="12" t="str">
+      <c r="F78" s="13" t="str">
         <f>IF(Assumptions!B12=0,"N/A",IF(F3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A79" s="12" t="s">
-        <v>197</v>
-      </c>
-      <c r="B79" s="12" t="str">
+      <c r="A79" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="B79" s="13" t="str">
         <f>IF(B59=0,"N/A",IF(B70/(B59/12)&gt;=2,"PASS","FAIL"))</f>
         <v>FAIL</v>
       </c>
-      <c r="C79" s="12" t="str">
+      <c r="C79" s="13" t="str">
         <f>IF(C59=0,"N/A",IF(C70/(C59/12)&gt;=2,"PASS","FAIL"))</f>
         <v>FAIL</v>
       </c>
-      <c r="D79" s="12" t="str">
+      <c r="D79" s="13" t="str">
         <f>IF(D59=0,"N/A",IF(D70/(D59/12)&gt;=2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="E79" s="12" t="str">
+      <c r="E79" s="13" t="str">
         <f>IF(E59=0,"N/A",IF(E70/(E59/12)&gt;=2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="F79" s="12" t="str">
+      <c r="F79" s="13" t="str">
         <f>IF(F59=0,"N/A",IF(F70/(F59/12)&gt;=2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="81" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A81" s="11" t="s">
-        <v>198</v>
-      </c>
-      <c r="B81" s="11"/>
-      <c r="C81" s="11"/>
-      <c r="D81" s="11"/>
-      <c r="E81" s="11"/>
-      <c r="F81" s="11"/>
+      <c r="A81" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="B81" s="12"/>
+      <c r="C81" s="12"/>
+      <c r="D81" s="12"/>
+      <c r="E81" s="12"/>
+      <c r="F81" s="12"/>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A82" s="12" t="s">
-        <v>199</v>
-      </c>
-      <c r="B82" s="20">
+      <c r="A82" s="13" t="s">
+        <v>200</v>
+      </c>
+      <c r="B82" s="21">
         <f>IF(B3=0,"",B12/B3)</f>
         <v>10736</v>
       </c>
-      <c r="C82" s="20">
+      <c r="C82" s="21">
         <f>IF(C3=0,"",C12/C3)</f>
         <v>12614</v>
       </c>
-      <c r="D82" s="20">
+      <c r="D82" s="21">
         <f>IF(D3=0,"",D12/D3)</f>
         <v>12615</v>
       </c>
-      <c r="E82" s="20">
+      <c r="E82" s="21">
         <f>IF(E3=0,"",E12/E3)</f>
         <v>12691</v>
       </c>
-      <c r="F82" s="20">
+      <c r="F82" s="21">
         <f>IF(F3=0,"",F12/F3)</f>
         <v>12961</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A83" s="12" t="s">
-        <v>200</v>
-      </c>
-      <c r="B83" s="20">
+      <c r="A83" s="13" t="s">
+        <v>201</v>
+      </c>
+      <c r="B83" s="21">
         <f>IF(B3=0,"",B59/B3)</f>
         <v>14469</v>
       </c>
-      <c r="C83" s="20">
+      <c r="C83" s="21">
         <f>IF(C3=0,"",C59/C3)</f>
         <v>11047</v>
       </c>
-      <c r="D83" s="20">
+      <c r="D83" s="21">
         <f>IF(D3=0,"",D59/D3)</f>
         <v>8374</v>
       </c>
-      <c r="E83" s="20">
+      <c r="E83" s="21">
         <f>IF(E3=0,"",E59/E3)</f>
         <v>7322</v>
       </c>
-      <c r="F83" s="20">
+      <c r="F83" s="21">
         <f>IF(F3=0,"",F59/F3)</f>
         <v>7141</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A84" s="12" t="s">
-        <v>201</v>
-      </c>
-      <c r="B84" s="20">
+      <c r="A84" s="13" t="s">
+        <v>202</v>
+      </c>
+      <c r="B84" s="21">
         <f>B56+B58</f>
         <v>1191256</v>
       </c>
-      <c r="C84" s="20">
+      <c r="C84" s="21">
         <f>C56+C58</f>
         <v>1321543</v>
       </c>
-      <c r="D84" s="20">
+      <c r="D84" s="21">
         <f>D56+D58</f>
         <v>1321543</v>
       </c>
-      <c r="E84" s="20">
+      <c r="E84" s="21">
         <f>E56+E58</f>
         <v>1306543</v>
       </c>
-      <c r="F84" s="20">
+      <c r="F84" s="21">
         <f>F56+F58</f>
         <v>1301543</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A85" s="12" t="s">
-        <v>202</v>
-      </c>
-      <c r="B85" s="20">
+      <c r="A85" s="13" t="s">
+        <v>203</v>
+      </c>
+      <c r="B85" s="21">
         <f>IF(B3=0,"",B57/B3)</f>
         <v>4542</v>
       </c>
-      <c r="C85" s="20">
+      <c r="C85" s="21">
         <f>IF(C3=0,"",C57/C3)</f>
         <v>4439</v>
       </c>
-      <c r="D85" s="20">
+      <c r="D85" s="21">
         <f>IF(D3=0,"",D57/D3)</f>
         <v>3968</v>
       </c>
-      <c r="E85" s="20">
+      <c r="E85" s="21">
         <f>IF(E3=0,"",E57/E3)</f>
         <v>3838</v>
       </c>
-      <c r="F85" s="20">
+      <c r="F85" s="21">
         <f>IF(F3=0,"",F57/F3)</f>
         <v>3887</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A86" s="12" t="s">
-        <v>203</v>
-      </c>
-      <c r="B86" s="20">
+      <c r="A86" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="B86" s="21">
         <f>IF(B3=0,"",B82-B85)</f>
         <v>6194</v>
       </c>
-      <c r="C86" s="20">
+      <c r="C86" s="21">
         <f>IF(C3=0,"",C82-C85)</f>
         <v>8175</v>
       </c>
-      <c r="D86" s="20">
+      <c r="D86" s="21">
         <f>IF(D3=0,"",D82-D85)</f>
         <v>8647</v>
       </c>
-      <c r="E86" s="20">
+      <c r="E86" s="21">
         <f>IF(E3=0,"",E82-E85)</f>
         <v>8853</v>
       </c>
-      <c r="F86" s="20">
+      <c r="F86" s="21">
         <f>IF(F3=0,"",F82-F85)</f>
         <v>9074</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A87" s="37" t="s">
-        <v>204</v>
-      </c>
-      <c r="B87" s="38">
+      <c r="A87" s="38" t="s">
+        <v>205</v>
+      </c>
+      <c r="B87" s="39">
         <f>IF(B86&lt;=0,"N/A",ROUNDUP(B84/B86,0))</f>
         <v>193</v>
       </c>
-      <c r="C87" s="38">
+      <c r="C87" s="39">
         <f>IF(C86&lt;=0,"N/A",ROUNDUP(C84/C86,0))</f>
         <v>162</v>
       </c>
-      <c r="D87" s="38">
+      <c r="D87" s="39">
         <f>IF(D86&lt;=0,"N/A",ROUNDUP(D84/D86,0))</f>
         <v>153</v>
       </c>
-      <c r="E87" s="38">
+      <c r="E87" s="39">
         <f>IF(E86&lt;=0,"N/A",ROUNDUP(E84/E86,0))</f>
         <v>148</v>
       </c>
-      <c r="F87" s="38">
+      <c r="F87" s="39">
         <f>IF(F86&lt;=0,"N/A",ROUNDUP(F84/F86,0))</f>
         <v>144</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A89" s="23" t="s">
-        <v>143</v>
-      </c>
-      <c r="B89" s="23"/>
-      <c r="C89" s="23"/>
-      <c r="D89" s="23"/>
-      <c r="E89" s="23"/>
-      <c r="F89" s="23"/>
+      <c r="A89" s="24" t="s">
+        <v>144</v>
+      </c>
+      <c r="B89" s="24"/>
+      <c r="C89" s="24"/>
+      <c r="D89" s="24"/>
+      <c r="E89" s="24"/>
+      <c r="F89" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -4600,7 +4624,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -4617,390 +4641,390 @@
       <c r="N1" s="8"/>
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="24" t="s">
-        <v>45</v>
-      </c>
-      <c r="C2" s="24" t="s">
-        <v>206</v>
-      </c>
-      <c r="D2" s="24" t="s">
+      <c r="B2" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" s="25" t="s">
         <v>207</v>
       </c>
-      <c r="E2" s="24" t="s">
+      <c r="D2" s="25" t="s">
         <v>208</v>
       </c>
-      <c r="F2" s="24" t="s">
+      <c r="E2" s="25" t="s">
         <v>209</v>
       </c>
-      <c r="G2" s="24" t="s">
+      <c r="F2" s="25" t="s">
         <v>210</v>
       </c>
-      <c r="H2" s="24" t="s">
+      <c r="G2" s="25" t="s">
         <v>211</v>
       </c>
-      <c r="I2" s="24" t="s">
+      <c r="H2" s="25" t="s">
         <v>212</v>
       </c>
-      <c r="J2" s="24" t="s">
+      <c r="I2" s="25" t="s">
         <v>213</v>
       </c>
-      <c r="K2" s="24" t="s">
+      <c r="J2" s="25" t="s">
         <v>214</v>
       </c>
-      <c r="L2" s="24" t="s">
+      <c r="K2" s="25" t="s">
         <v>215</v>
       </c>
-      <c r="M2" s="24" t="s">
+      <c r="L2" s="25" t="s">
         <v>216</v>
       </c>
-      <c r="N2" s="24" t="s">
+      <c r="M2" s="25" t="s">
         <v>217</v>
       </c>
+      <c r="N2" s="25" t="s">
+        <v>218</v>
+      </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="11" t="s">
-        <v>145</v>
-      </c>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11"/>
-      <c r="H3" s="11"/>
-      <c r="I3" s="11"/>
-      <c r="J3" s="11"/>
-      <c r="K3" s="11"/>
-      <c r="L3" s="11"/>
-      <c r="M3" s="11"/>
-      <c r="N3" s="11"/>
+      <c r="A3" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="B3" s="12"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="12"/>
+      <c r="J3" s="12"/>
+      <c r="K3" s="12"/>
+      <c r="L3" s="12"/>
+      <c r="M3" s="12"/>
+      <c r="N3" s="12"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="B4" s="20">
+      <c r="A4" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="B4" s="21">
         <v>114000</v>
       </c>
-      <c r="C4" s="20">
+      <c r="C4" s="21">
         <v>114000</v>
       </c>
-      <c r="D4" s="20">
+      <c r="D4" s="21">
         <v>114000</v>
       </c>
-      <c r="E4" s="20">
+      <c r="E4" s="21">
         <v>114000</v>
       </c>
-      <c r="F4" s="20">
+      <c r="F4" s="21">
         <v>114000</v>
       </c>
-      <c r="G4" s="20">
+      <c r="G4" s="21">
         <v>114000</v>
       </c>
-      <c r="H4" s="20">
+      <c r="H4" s="21">
         <v>114000</v>
       </c>
-      <c r="I4" s="20">
+      <c r="I4" s="21">
         <v>114000</v>
       </c>
-      <c r="J4" s="20">
+      <c r="J4" s="21">
         <v>114000</v>
       </c>
-      <c r="K4" s="20">
+      <c r="K4" s="21">
         <v>114000</v>
       </c>
-      <c r="L4" s="20">
-        <v>0</v>
-      </c>
-      <c r="M4" s="20">
-        <v>0</v>
-      </c>
-      <c r="N4" s="20">
+      <c r="L4" s="21">
+        <v>0</v>
+      </c>
+      <c r="M4" s="21">
+        <v>0</v>
+      </c>
+      <c r="N4" s="21">
         <f>SUM(B4:M4)</f>
         <v>950000</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="B5" s="20">
+      <c r="A5" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="B5" s="21">
         <v>9600</v>
       </c>
-      <c r="C5" s="20">
+      <c r="C5" s="21">
         <v>9600</v>
       </c>
-      <c r="D5" s="20">
+      <c r="D5" s="21">
         <v>9600</v>
       </c>
-      <c r="E5" s="20">
+      <c r="E5" s="21">
         <v>9600</v>
       </c>
-      <c r="F5" s="20">
+      <c r="F5" s="21">
         <v>9600</v>
       </c>
-      <c r="G5" s="20">
+      <c r="G5" s="21">
         <v>9600</v>
       </c>
-      <c r="H5" s="20">
+      <c r="H5" s="21">
         <v>9600</v>
       </c>
-      <c r="I5" s="20">
+      <c r="I5" s="21">
         <v>9600</v>
       </c>
-      <c r="J5" s="20">
+      <c r="J5" s="21">
         <v>9600</v>
       </c>
-      <c r="K5" s="20">
+      <c r="K5" s="21">
         <v>9600</v>
       </c>
-      <c r="L5" s="20">
-        <v>0</v>
-      </c>
-      <c r="M5" s="20">
-        <v>0</v>
-      </c>
-      <c r="N5" s="20">
+      <c r="L5" s="21">
+        <v>0</v>
+      </c>
+      <c r="M5" s="21">
+        <v>0</v>
+      </c>
+      <c r="N5" s="21">
         <f>SUM(B5:M5)</f>
         <v>80000</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="B6" s="20">
+      <c r="A6" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="B6" s="21">
         <v>14400</v>
       </c>
-      <c r="C6" s="20">
+      <c r="C6" s="21">
         <v>14400</v>
       </c>
-      <c r="D6" s="20">
+      <c r="D6" s="21">
         <v>14400</v>
       </c>
-      <c r="E6" s="20">
+      <c r="E6" s="21">
         <v>14400</v>
       </c>
-      <c r="F6" s="20">
+      <c r="F6" s="21">
         <v>14400</v>
       </c>
-      <c r="G6" s="20">
+      <c r="G6" s="21">
         <v>14400</v>
       </c>
-      <c r="H6" s="20">
+      <c r="H6" s="21">
         <v>14400</v>
       </c>
-      <c r="I6" s="20">
+      <c r="I6" s="21">
         <v>14400</v>
       </c>
-      <c r="J6" s="20">
+      <c r="J6" s="21">
         <v>14400</v>
       </c>
-      <c r="K6" s="20">
+      <c r="K6" s="21">
         <v>14400</v>
       </c>
-      <c r="L6" s="20">
-        <v>0</v>
-      </c>
-      <c r="M6" s="20">
-        <v>0</v>
-      </c>
-      <c r="N6" s="20">
+      <c r="L6" s="21">
+        <v>0</v>
+      </c>
+      <c r="M6" s="21">
+        <v>0</v>
+      </c>
+      <c r="N6" s="21">
         <f>SUM(B6:M6)</f>
         <v>120000</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="B7" s="20">
+      <c r="A7" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="B7" s="21">
         <v>10000</v>
       </c>
-      <c r="C7" s="20">
+      <c r="C7" s="21">
         <v>10000</v>
       </c>
-      <c r="D7" s="20">
+      <c r="D7" s="21">
         <v>10000</v>
       </c>
-      <c r="E7" s="20">
+      <c r="E7" s="21">
         <v>10000</v>
       </c>
-      <c r="F7" s="20">
+      <c r="F7" s="21">
         <v>10000</v>
       </c>
-      <c r="G7" s="20">
+      <c r="G7" s="21">
         <v>10000</v>
       </c>
-      <c r="H7" s="20">
+      <c r="H7" s="21">
         <v>10000</v>
       </c>
-      <c r="I7" s="20">
+      <c r="I7" s="21">
         <v>10000</v>
       </c>
-      <c r="J7" s="20">
+      <c r="J7" s="21">
         <v>10000</v>
       </c>
-      <c r="K7" s="20">
+      <c r="K7" s="21">
         <v>10000</v>
       </c>
-      <c r="L7" s="20">
-        <v>0</v>
-      </c>
-      <c r="M7" s="20">
-        <v>0</v>
-      </c>
-      <c r="N7" s="20">
+      <c r="L7" s="21">
+        <v>0</v>
+      </c>
+      <c r="M7" s="21">
+        <v>0</v>
+      </c>
+      <c r="N7" s="21">
         <f>SUM(B7:M7)</f>
         <v>83333</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="B8" s="20">
+      <c r="A8" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="B8" s="21">
         <v>3000</v>
       </c>
-      <c r="C8" s="20">
+      <c r="C8" s="21">
         <v>3000</v>
       </c>
-      <c r="D8" s="20">
+      <c r="D8" s="21">
         <v>3000</v>
       </c>
-      <c r="E8" s="20">
+      <c r="E8" s="21">
         <v>3000</v>
       </c>
-      <c r="F8" s="20">
+      <c r="F8" s="21">
         <v>3000</v>
       </c>
-      <c r="G8" s="20">
+      <c r="G8" s="21">
         <v>3000</v>
       </c>
-      <c r="H8" s="20">
+      <c r="H8" s="21">
         <v>3000</v>
       </c>
-      <c r="I8" s="20">
+      <c r="I8" s="21">
         <v>3000</v>
       </c>
-      <c r="J8" s="20">
+      <c r="J8" s="21">
         <v>3000</v>
       </c>
-      <c r="K8" s="20">
+      <c r="K8" s="21">
         <v>3000</v>
       </c>
-      <c r="L8" s="20">
-        <v>0</v>
-      </c>
-      <c r="M8" s="20">
-        <v>0</v>
-      </c>
-      <c r="N8" s="20">
+      <c r="L8" s="21">
+        <v>0</v>
+      </c>
+      <c r="M8" s="21">
+        <v>0</v>
+      </c>
+      <c r="N8" s="21">
         <f>SUM(B8:M8)</f>
         <v>25000</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="B9" s="20">
+      <c r="A9" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="B9" s="21">
         <v>3600</v>
       </c>
-      <c r="C9" s="20">
+      <c r="C9" s="21">
         <v>3600</v>
       </c>
-      <c r="D9" s="20">
+      <c r="D9" s="21">
         <v>3600</v>
       </c>
-      <c r="E9" s="20">
+      <c r="E9" s="21">
         <v>3600</v>
       </c>
-      <c r="F9" s="20">
+      <c r="F9" s="21">
         <v>3600</v>
       </c>
-      <c r="G9" s="20">
+      <c r="G9" s="21">
         <v>3600</v>
       </c>
-      <c r="H9" s="20">
+      <c r="H9" s="21">
         <v>3600</v>
       </c>
-      <c r="I9" s="20">
+      <c r="I9" s="21">
         <v>3600</v>
       </c>
-      <c r="J9" s="20">
+      <c r="J9" s="21">
         <v>3600</v>
       </c>
-      <c r="K9" s="20">
+      <c r="K9" s="21">
         <v>3600</v>
       </c>
-      <c r="L9" s="20">
-        <v>0</v>
-      </c>
-      <c r="M9" s="20">
-        <v>0</v>
-      </c>
-      <c r="N9" s="20">
+      <c r="L9" s="21">
+        <v>0</v>
+      </c>
+      <c r="M9" s="21">
+        <v>0</v>
+      </c>
+      <c r="N9" s="21">
         <f>SUM(B9:M9)</f>
         <v>30000</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="B10" s="27">
+      <c r="A10" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="B10" s="28">
         <f>SUM(B4:B9)</f>
         <v>154600</v>
       </c>
-      <c r="C10" s="27">
+      <c r="C10" s="28">
         <f>SUM(C4:C9)</f>
         <v>154600</v>
       </c>
-      <c r="D10" s="27">
+      <c r="D10" s="28">
         <f>SUM(D4:D9)</f>
         <v>154600</v>
       </c>
-      <c r="E10" s="27">
+      <c r="E10" s="28">
         <f>SUM(E4:E9)</f>
         <v>154600</v>
       </c>
-      <c r="F10" s="27">
+      <c r="F10" s="28">
         <f>SUM(F4:F9)</f>
         <v>154600</v>
       </c>
-      <c r="G10" s="27">
+      <c r="G10" s="28">
         <f>SUM(G4:G9)</f>
         <v>154600</v>
       </c>
-      <c r="H10" s="27">
+      <c r="H10" s="28">
         <f>SUM(H4:H9)</f>
         <v>154600</v>
       </c>
-      <c r="I10" s="27">
+      <c r="I10" s="28">
         <f>SUM(I4:I9)</f>
         <v>154600</v>
       </c>
-      <c r="J10" s="27">
+      <c r="J10" s="28">
         <f>SUM(J4:J9)</f>
         <v>154600</v>
       </c>
-      <c r="K10" s="27">
+      <c r="K10" s="28">
         <f>SUM(K4:K9)</f>
         <v>154600</v>
       </c>
-      <c r="L10" s="27" t="str">
+      <c r="L10" s="28" t="str">
         <f>SUM(L4:L9)</f>
         <v>0</v>
       </c>
-      <c r="M10" s="27" t="str">
+      <c r="M10" s="28" t="str">
         <f>SUM(M4:M9)</f>
         <v>0</v>
       </c>
-      <c r="N10" s="27">
+      <c r="N10" s="28">
         <f>SUM(B10:M10)</f>
         <v>1546000</v>
       </c>
@@ -5011,481 +5035,481 @@
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" s="11" t="s">
-        <v>147</v>
-      </c>
-      <c r="B12" s="11"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
-      <c r="J12" s="11"/>
-      <c r="K12" s="11"/>
-      <c r="L12" s="11"/>
-      <c r="M12" s="11"/>
-      <c r="N12" s="11"/>
+      <c r="A12" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="B12" s="12"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="12"/>
+      <c r="H12" s="12"/>
+      <c r="I12" s="12"/>
+      <c r="J12" s="12"/>
+      <c r="K12" s="12"/>
+      <c r="L12" s="12"/>
+      <c r="M12" s="12"/>
+      <c r="N12" s="12"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="B13" s="20">
+      <c r="A13" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="B13" s="21">
         <v>12435</v>
       </c>
-      <c r="C13" s="20">
+      <c r="C13" s="21">
         <v>12435</v>
       </c>
-      <c r="D13" s="20">
+      <c r="D13" s="21">
         <v>12435</v>
       </c>
-      <c r="E13" s="20">
+      <c r="E13" s="21">
         <v>12435</v>
       </c>
-      <c r="F13" s="20">
+      <c r="F13" s="21">
         <v>12435</v>
       </c>
-      <c r="G13" s="20">
+      <c r="G13" s="21">
         <v>12435</v>
       </c>
-      <c r="H13" s="20">
+      <c r="H13" s="21">
         <v>12435</v>
       </c>
-      <c r="I13" s="20">
+      <c r="I13" s="21">
         <v>12435</v>
       </c>
-      <c r="J13" s="20">
+      <c r="J13" s="21">
         <v>12435</v>
       </c>
-      <c r="K13" s="20">
+      <c r="K13" s="21">
         <v>12435</v>
       </c>
-      <c r="L13" s="20">
-        <v>0</v>
-      </c>
-      <c r="M13" s="20">
-        <v>0</v>
-      </c>
-      <c r="N13" s="20">
+      <c r="L13" s="21">
+        <v>0</v>
+      </c>
+      <c r="M13" s="21">
+        <v>0</v>
+      </c>
+      <c r="N13" s="21">
         <f>SUM(B13:M13)</f>
         <v>124346</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A14" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="B14" s="20">
+      <c r="A14" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="B14" s="21">
         <v>10174</v>
       </c>
-      <c r="C14" s="20">
+      <c r="C14" s="21">
         <v>10174</v>
       </c>
-      <c r="D14" s="20">
+      <c r="D14" s="21">
         <v>10174</v>
       </c>
-      <c r="E14" s="20">
+      <c r="E14" s="21">
         <v>10174</v>
       </c>
-      <c r="F14" s="20">
+      <c r="F14" s="21">
         <v>10174</v>
       </c>
-      <c r="G14" s="20">
+      <c r="G14" s="21">
         <v>10174</v>
       </c>
-      <c r="H14" s="20">
+      <c r="H14" s="21">
         <v>10174</v>
       </c>
-      <c r="I14" s="20">
+      <c r="I14" s="21">
         <v>10174</v>
       </c>
-      <c r="J14" s="20">
+      <c r="J14" s="21">
         <v>10174</v>
       </c>
-      <c r="K14" s="20">
+      <c r="K14" s="21">
         <v>10174</v>
       </c>
-      <c r="L14" s="20">
-        <v>0</v>
-      </c>
-      <c r="M14" s="20">
-        <v>0</v>
-      </c>
-      <c r="N14" s="20">
+      <c r="L14" s="21">
+        <v>0</v>
+      </c>
+      <c r="M14" s="21">
+        <v>0</v>
+      </c>
+      <c r="N14" s="21">
         <f>SUM(B14:M14)</f>
         <v>101738</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="B15" s="20">
+      <c r="A15" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="B15" s="21">
         <v>8139</v>
       </c>
-      <c r="C15" s="20">
+      <c r="C15" s="21">
         <v>8139</v>
       </c>
-      <c r="D15" s="20">
+      <c r="D15" s="21">
         <v>8139</v>
       </c>
-      <c r="E15" s="20">
+      <c r="E15" s="21">
         <v>8139</v>
       </c>
-      <c r="F15" s="20">
+      <c r="F15" s="21">
         <v>8139</v>
       </c>
-      <c r="G15" s="20">
+      <c r="G15" s="21">
         <v>8139</v>
       </c>
-      <c r="H15" s="20">
+      <c r="H15" s="21">
         <v>8139</v>
       </c>
-      <c r="I15" s="20">
+      <c r="I15" s="21">
         <v>8139</v>
       </c>
-      <c r="J15" s="20">
+      <c r="J15" s="21">
         <v>8139</v>
       </c>
-      <c r="K15" s="20">
+      <c r="K15" s="21">
         <v>8139</v>
       </c>
-      <c r="L15" s="20">
-        <v>0</v>
-      </c>
-      <c r="M15" s="20">
-        <v>0</v>
-      </c>
-      <c r="N15" s="20">
+      <c r="L15" s="21">
+        <v>0</v>
+      </c>
+      <c r="M15" s="21">
+        <v>0</v>
+      </c>
+      <c r="N15" s="21">
         <f>SUM(B15:M15)</f>
         <v>81390</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A16" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="B16" s="20">
+      <c r="A16" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="B16" s="21">
         <v>35269</v>
       </c>
-      <c r="C16" s="20">
+      <c r="C16" s="21">
         <v>35269</v>
       </c>
-      <c r="D16" s="20">
+      <c r="D16" s="21">
         <v>35269</v>
       </c>
-      <c r="E16" s="20">
+      <c r="E16" s="21">
         <v>35269</v>
       </c>
-      <c r="F16" s="20">
+      <c r="F16" s="21">
         <v>35269</v>
       </c>
-      <c r="G16" s="20">
+      <c r="G16" s="21">
         <v>35269</v>
       </c>
-      <c r="H16" s="20">
+      <c r="H16" s="21">
         <v>35269</v>
       </c>
-      <c r="I16" s="20">
+      <c r="I16" s="21">
         <v>35269</v>
       </c>
-      <c r="J16" s="20">
+      <c r="J16" s="21">
         <v>35269</v>
       </c>
-      <c r="K16" s="20">
+      <c r="K16" s="21">
         <v>35269</v>
       </c>
-      <c r="L16" s="20">
-        <v>0</v>
-      </c>
-      <c r="M16" s="20">
-        <v>0</v>
-      </c>
-      <c r="N16" s="20">
+      <c r="L16" s="21">
+        <v>0</v>
+      </c>
+      <c r="M16" s="21">
+        <v>0</v>
+      </c>
+      <c r="N16" s="21">
         <f>SUM(B16:M16)</f>
         <v>352690</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A17" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="B17" s="20">
+      <c r="A17" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="B17" s="21">
         <v>6217</v>
       </c>
-      <c r="C17" s="20">
+      <c r="C17" s="21">
         <v>6217</v>
       </c>
-      <c r="D17" s="20">
+      <c r="D17" s="21">
         <v>6217</v>
       </c>
-      <c r="E17" s="20">
+      <c r="E17" s="21">
         <v>6217</v>
       </c>
-      <c r="F17" s="20">
+      <c r="F17" s="21">
         <v>6217</v>
       </c>
-      <c r="G17" s="20">
+      <c r="G17" s="21">
         <v>6217</v>
       </c>
-      <c r="H17" s="20">
+      <c r="H17" s="21">
         <v>6217</v>
       </c>
-      <c r="I17" s="20">
+      <c r="I17" s="21">
         <v>6217</v>
       </c>
-      <c r="J17" s="20">
+      <c r="J17" s="21">
         <v>6217</v>
       </c>
-      <c r="K17" s="20">
+      <c r="K17" s="21">
         <v>6217</v>
       </c>
-      <c r="L17" s="20">
-        <v>0</v>
-      </c>
-      <c r="M17" s="20">
-        <v>0</v>
-      </c>
-      <c r="N17" s="20">
+      <c r="L17" s="21">
+        <v>0</v>
+      </c>
+      <c r="M17" s="21">
+        <v>0</v>
+      </c>
+      <c r="N17" s="21">
         <f>SUM(B17:M17)</f>
         <v>62173</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="B18" s="20">
+      <c r="A18" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="B18" s="21">
         <v>9574</v>
       </c>
-      <c r="C18" s="20">
+      <c r="C18" s="21">
         <v>9574</v>
       </c>
-      <c r="D18" s="20">
+      <c r="D18" s="21">
         <v>9574</v>
       </c>
-      <c r="E18" s="20">
+      <c r="E18" s="21">
         <v>9574</v>
       </c>
-      <c r="F18" s="20">
+      <c r="F18" s="21">
         <v>9574</v>
       </c>
-      <c r="G18" s="20">
+      <c r="G18" s="21">
         <v>9574</v>
       </c>
-      <c r="H18" s="20">
+      <c r="H18" s="21">
         <v>9574</v>
       </c>
-      <c r="I18" s="20">
+      <c r="I18" s="21">
         <v>9574</v>
       </c>
-      <c r="J18" s="20">
+      <c r="J18" s="21">
         <v>9574</v>
       </c>
-      <c r="K18" s="20">
+      <c r="K18" s="21">
         <v>9574</v>
       </c>
-      <c r="L18" s="20">
-        <v>0</v>
-      </c>
-      <c r="M18" s="20">
-        <v>0</v>
-      </c>
-      <c r="N18" s="20">
+      <c r="L18" s="21">
+        <v>0</v>
+      </c>
+      <c r="M18" s="21">
+        <v>0</v>
+      </c>
+      <c r="N18" s="21">
         <f>SUM(B18:M18)</f>
         <v>95738</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A19" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="B19" s="20">
+      <c r="A19" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="B19" s="21">
         <v>6217</v>
       </c>
-      <c r="C19" s="20">
+      <c r="C19" s="21">
         <v>6217</v>
       </c>
-      <c r="D19" s="20">
+      <c r="D19" s="21">
         <v>6217</v>
       </c>
-      <c r="E19" s="20">
+      <c r="E19" s="21">
         <v>6217</v>
       </c>
-      <c r="F19" s="20">
+      <c r="F19" s="21">
         <v>6217</v>
       </c>
-      <c r="G19" s="20">
+      <c r="G19" s="21">
         <v>6217</v>
       </c>
-      <c r="H19" s="20">
+      <c r="H19" s="21">
         <v>6217</v>
       </c>
-      <c r="I19" s="20">
+      <c r="I19" s="21">
         <v>6217</v>
       </c>
-      <c r="J19" s="20">
+      <c r="J19" s="21">
         <v>6217</v>
       </c>
-      <c r="K19" s="20">
+      <c r="K19" s="21">
         <v>6217</v>
       </c>
-      <c r="L19" s="20">
-        <v>0</v>
-      </c>
-      <c r="M19" s="20">
-        <v>0</v>
-      </c>
-      <c r="N19" s="20">
+      <c r="L19" s="21">
+        <v>0</v>
+      </c>
+      <c r="M19" s="21">
+        <v>0</v>
+      </c>
+      <c r="N19" s="21">
         <f>SUM(B19:M19)</f>
         <v>62173</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A20" s="12" t="s">
-        <v>98</v>
-      </c>
-      <c r="B20" s="20">
+      <c r="A20" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="B20" s="21">
         <v>8401</v>
       </c>
-      <c r="C20" s="20">
+      <c r="C20" s="21">
         <v>8401</v>
       </c>
-      <c r="D20" s="20">
+      <c r="D20" s="21">
         <v>8401</v>
       </c>
-      <c r="E20" s="20">
+      <c r="E20" s="21">
         <v>8401</v>
       </c>
-      <c r="F20" s="20">
+      <c r="F20" s="21">
         <v>8401</v>
       </c>
-      <c r="G20" s="20">
+      <c r="G20" s="21">
         <v>8401</v>
       </c>
-      <c r="H20" s="20">
+      <c r="H20" s="21">
         <v>8401</v>
       </c>
-      <c r="I20" s="20">
+      <c r="I20" s="21">
         <v>8401</v>
       </c>
-      <c r="J20" s="20">
+      <c r="J20" s="21">
         <v>8401</v>
       </c>
-      <c r="K20" s="20">
+      <c r="K20" s="21">
         <v>8401</v>
       </c>
-      <c r="L20" s="20">
-        <v>0</v>
-      </c>
-      <c r="M20" s="20">
-        <v>0</v>
-      </c>
-      <c r="N20" s="20">
+      <c r="L20" s="21">
+        <v>0</v>
+      </c>
+      <c r="M20" s="21">
+        <v>0</v>
+      </c>
+      <c r="N20" s="21">
         <f>SUM(B20:M20)</f>
         <v>84012</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A21" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="B21" s="20">
+      <c r="A21" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="B21" s="21">
         <v>6217</v>
       </c>
-      <c r="C21" s="20">
+      <c r="C21" s="21">
         <v>6217</v>
       </c>
-      <c r="D21" s="20">
+      <c r="D21" s="21">
         <v>6217</v>
       </c>
-      <c r="E21" s="20">
+      <c r="E21" s="21">
         <v>6217</v>
       </c>
-      <c r="F21" s="20">
+      <c r="F21" s="21">
         <v>6217</v>
       </c>
-      <c r="G21" s="20">
+      <c r="G21" s="21">
         <v>6217</v>
       </c>
-      <c r="H21" s="20">
+      <c r="H21" s="21">
         <v>6217</v>
       </c>
-      <c r="I21" s="20">
+      <c r="I21" s="21">
         <v>6217</v>
       </c>
-      <c r="J21" s="20">
+      <c r="J21" s="21">
         <v>6217</v>
       </c>
-      <c r="K21" s="20">
+      <c r="K21" s="21">
         <v>6217</v>
       </c>
-      <c r="L21" s="20">
-        <v>0</v>
-      </c>
-      <c r="M21" s="20">
-        <v>0</v>
-      </c>
-      <c r="N21" s="20">
+      <c r="L21" s="21">
+        <v>0</v>
+      </c>
+      <c r="M21" s="21">
+        <v>0</v>
+      </c>
+      <c r="N21" s="21">
         <f>SUM(B21:M21)</f>
         <v>62173</v>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A22" s="11" t="s">
-        <v>157</v>
-      </c>
-      <c r="B22" s="27">
+      <c r="A22" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="B22" s="28">
         <f>SUM(B13:B21)</f>
         <v>102643</v>
       </c>
-      <c r="C22" s="27">
+      <c r="C22" s="28">
         <f>SUM(C13:C21)</f>
         <v>102643</v>
       </c>
-      <c r="D22" s="27">
+      <c r="D22" s="28">
         <f>SUM(D13:D21)</f>
         <v>102643</v>
       </c>
-      <c r="E22" s="27">
+      <c r="E22" s="28">
         <f>SUM(E13:E21)</f>
         <v>102643</v>
       </c>
-      <c r="F22" s="27">
+      <c r="F22" s="28">
         <f>SUM(F13:F21)</f>
         <v>102643</v>
       </c>
-      <c r="G22" s="27">
+      <c r="G22" s="28">
         <f>SUM(G13:G21)</f>
         <v>102643</v>
       </c>
-      <c r="H22" s="27">
+      <c r="H22" s="28">
         <f>SUM(H13:H21)</f>
         <v>102643</v>
       </c>
-      <c r="I22" s="27">
+      <c r="I22" s="28">
         <f>SUM(I13:I21)</f>
         <v>102643</v>
       </c>
-      <c r="J22" s="27">
+      <c r="J22" s="28">
         <f>SUM(J13:J21)</f>
         <v>102643</v>
       </c>
-      <c r="K22" s="27">
+      <c r="K22" s="28">
         <f>SUM(K13:K21)</f>
         <v>102643</v>
       </c>
-      <c r="L22" s="27" t="str">
+      <c r="L22" s="28" t="str">
         <f>SUM(L13:L21)</f>
         <v>0</v>
       </c>
-      <c r="M22" s="27" t="str">
+      <c r="M22" s="28" t="str">
         <f>SUM(M13:M21)</f>
         <v>0</v>
       </c>
-      <c r="N22" s="27">
+      <c r="N22" s="28">
         <f>SUM(B22:M22)</f>
         <v>1026431</v>
       </c>
@@ -5496,823 +5520,823 @@
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A24" s="11" t="s">
-        <v>110</v>
-      </c>
-      <c r="B24" s="11"/>
-      <c r="C24" s="11"/>
-      <c r="D24" s="11"/>
-      <c r="E24" s="11"/>
-      <c r="F24" s="11"/>
-      <c r="G24" s="11"/>
-      <c r="H24" s="11"/>
-      <c r="I24" s="11"/>
-      <c r="J24" s="11"/>
-      <c r="K24" s="11"/>
-      <c r="L24" s="11"/>
-      <c r="M24" s="11"/>
-      <c r="N24" s="11"/>
+      <c r="A24" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="B24" s="12"/>
+      <c r="C24" s="12"/>
+      <c r="D24" s="12"/>
+      <c r="E24" s="12"/>
+      <c r="F24" s="12"/>
+      <c r="G24" s="12"/>
+      <c r="H24" s="12"/>
+      <c r="I24" s="12"/>
+      <c r="J24" s="12"/>
+      <c r="K24" s="12"/>
+      <c r="L24" s="12"/>
+      <c r="M24" s="12"/>
+      <c r="N24" s="12"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A25" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="B25" s="12"/>
-      <c r="C25" s="12"/>
-      <c r="D25" s="12"/>
-      <c r="E25" s="12"/>
-      <c r="F25" s="12"/>
-      <c r="G25" s="12"/>
-      <c r="H25" s="12"/>
-      <c r="I25" s="12"/>
-      <c r="J25" s="12"/>
-      <c r="K25" s="12"/>
-      <c r="L25" s="12"/>
-      <c r="M25" s="12"/>
-      <c r="N25" s="12"/>
+      <c r="A25" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="B25" s="13"/>
+      <c r="C25" s="13"/>
+      <c r="D25" s="13"/>
+      <c r="E25" s="13"/>
+      <c r="F25" s="13"/>
+      <c r="G25" s="13"/>
+      <c r="H25" s="13"/>
+      <c r="I25" s="13"/>
+      <c r="J25" s="13"/>
+      <c r="K25" s="13"/>
+      <c r="L25" s="13"/>
+      <c r="M25" s="13"/>
+      <c r="N25" s="13"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A26" s="12" t="s">
-        <v>218</v>
-      </c>
-      <c r="B26" s="20">
+      <c r="A26" s="13" t="s">
+        <v>219</v>
+      </c>
+      <c r="B26" s="21">
         <v>7000</v>
       </c>
-      <c r="C26" s="20">
+      <c r="C26" s="21">
         <v>7000</v>
       </c>
-      <c r="D26" s="20">
+      <c r="D26" s="21">
         <v>7000</v>
       </c>
-      <c r="E26" s="20">
+      <c r="E26" s="21">
         <v>7000</v>
       </c>
-      <c r="F26" s="20">
+      <c r="F26" s="21">
         <v>7000</v>
       </c>
-      <c r="G26" s="20">
+      <c r="G26" s="21">
         <v>7000</v>
       </c>
-      <c r="H26" s="20">
+      <c r="H26" s="21">
         <v>7000</v>
       </c>
-      <c r="I26" s="20">
+      <c r="I26" s="21">
         <v>7000</v>
       </c>
-      <c r="J26" s="20">
+      <c r="J26" s="21">
         <v>7000</v>
       </c>
-      <c r="K26" s="20">
+      <c r="K26" s="21">
         <v>7000</v>
       </c>
-      <c r="L26" s="20">
-        <v>0</v>
-      </c>
-      <c r="M26" s="20">
-        <v>0</v>
-      </c>
-      <c r="N26" s="20">
+      <c r="L26" s="21">
+        <v>0</v>
+      </c>
+      <c r="M26" s="21">
+        <v>0</v>
+      </c>
+      <c r="N26" s="21">
         <f>SUM(B26:M26)</f>
         <v>70000</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A27" s="28" t="s">
-        <v>159</v>
-      </c>
-      <c r="B27" s="29">
+      <c r="A27" s="29" t="s">
+        <v>160</v>
+      </c>
+      <c r="B27" s="30">
         <v>7000</v>
       </c>
-      <c r="C27" s="29">
+      <c r="C27" s="30">
         <v>7000</v>
       </c>
-      <c r="D27" s="29">
+      <c r="D27" s="30">
         <v>7000</v>
       </c>
-      <c r="E27" s="29">
+      <c r="E27" s="30">
         <v>7000</v>
       </c>
-      <c r="F27" s="29">
+      <c r="F27" s="30">
         <v>7000</v>
       </c>
-      <c r="G27" s="29">
+      <c r="G27" s="30">
         <v>7000</v>
       </c>
-      <c r="H27" s="29">
+      <c r="H27" s="30">
         <v>7000</v>
       </c>
-      <c r="I27" s="29">
+      <c r="I27" s="30">
         <v>7000</v>
       </c>
-      <c r="J27" s="29">
+      <c r="J27" s="30">
         <v>7000</v>
       </c>
-      <c r="K27" s="29">
+      <c r="K27" s="30">
         <v>7000</v>
       </c>
-      <c r="L27" s="29">
-        <v>0</v>
-      </c>
-      <c r="M27" s="29">
-        <v>0</v>
-      </c>
-      <c r="N27" s="29">
+      <c r="L27" s="30">
+        <v>0</v>
+      </c>
+      <c r="M27" s="30">
+        <v>0</v>
+      </c>
+      <c r="N27" s="30">
         <f>SUM(B27:M27)</f>
         <v>70000</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A28" s="12" t="s">
-        <v>119</v>
-      </c>
-      <c r="B28" s="12"/>
-      <c r="C28" s="12"/>
-      <c r="D28" s="12"/>
-      <c r="E28" s="12"/>
-      <c r="F28" s="12"/>
-      <c r="G28" s="12"/>
-      <c r="H28" s="12"/>
-      <c r="I28" s="12"/>
-      <c r="J28" s="12"/>
-      <c r="K28" s="12"/>
-      <c r="L28" s="12"/>
-      <c r="M28" s="12"/>
-      <c r="N28" s="12"/>
+      <c r="A28" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="B28" s="13"/>
+      <c r="C28" s="13"/>
+      <c r="D28" s="13"/>
+      <c r="E28" s="13"/>
+      <c r="F28" s="13"/>
+      <c r="G28" s="13"/>
+      <c r="H28" s="13"/>
+      <c r="I28" s="13"/>
+      <c r="J28" s="13"/>
+      <c r="K28" s="13"/>
+      <c r="L28" s="13"/>
+      <c r="M28" s="13"/>
+      <c r="N28" s="13"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A29" s="12" t="s">
-        <v>219</v>
-      </c>
-      <c r="B29" s="20">
+      <c r="A29" s="13" t="s">
+        <v>220</v>
+      </c>
+      <c r="B29" s="21">
         <v>5000</v>
       </c>
-      <c r="C29" s="20">
+      <c r="C29" s="21">
         <v>5000</v>
       </c>
-      <c r="D29" s="20">
+      <c r="D29" s="21">
         <v>5000</v>
       </c>
-      <c r="E29" s="20">
+      <c r="E29" s="21">
         <v>5000</v>
       </c>
-      <c r="F29" s="20">
+      <c r="F29" s="21">
         <v>5000</v>
       </c>
-      <c r="G29" s="20">
+      <c r="G29" s="21">
         <v>5000</v>
       </c>
-      <c r="H29" s="20">
+      <c r="H29" s="21">
         <v>5000</v>
       </c>
-      <c r="I29" s="20">
+      <c r="I29" s="21">
         <v>5000</v>
       </c>
-      <c r="J29" s="20">
+      <c r="J29" s="21">
         <v>5000</v>
       </c>
-      <c r="K29" s="20">
+      <c r="K29" s="21">
         <v>5000</v>
       </c>
-      <c r="L29" s="20">
-        <v>0</v>
-      </c>
-      <c r="M29" s="20">
-        <v>0</v>
-      </c>
-      <c r="N29" s="20">
+      <c r="L29" s="21">
+        <v>0</v>
+      </c>
+      <c r="M29" s="21">
+        <v>0</v>
+      </c>
+      <c r="N29" s="21">
         <f>SUM(B29:M29)</f>
         <v>50000</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A30" s="28" t="s">
-        <v>161</v>
-      </c>
-      <c r="B30" s="29">
+      <c r="A30" s="29" t="s">
+        <v>162</v>
+      </c>
+      <c r="B30" s="30">
         <v>5000</v>
       </c>
-      <c r="C30" s="29">
+      <c r="C30" s="30">
         <v>5000</v>
       </c>
-      <c r="D30" s="29">
+      <c r="D30" s="30">
         <v>5000</v>
       </c>
-      <c r="E30" s="29">
+      <c r="E30" s="30">
         <v>5000</v>
       </c>
-      <c r="F30" s="29">
+      <c r="F30" s="30">
         <v>5000</v>
       </c>
-      <c r="G30" s="29">
+      <c r="G30" s="30">
         <v>5000</v>
       </c>
-      <c r="H30" s="29">
+      <c r="H30" s="30">
         <v>5000</v>
       </c>
-      <c r="I30" s="29">
+      <c r="I30" s="30">
         <v>5000</v>
       </c>
-      <c r="J30" s="29">
+      <c r="J30" s="30">
         <v>5000</v>
       </c>
-      <c r="K30" s="29">
+      <c r="K30" s="30">
         <v>5000</v>
       </c>
-      <c r="L30" s="29">
-        <v>0</v>
-      </c>
-      <c r="M30" s="29">
-        <v>0</v>
-      </c>
-      <c r="N30" s="29">
+      <c r="L30" s="30">
+        <v>0</v>
+      </c>
+      <c r="M30" s="30">
+        <v>0</v>
+      </c>
+      <c r="N30" s="30">
         <f>SUM(B30:M30)</f>
         <v>50000</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A31" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="B31" s="12"/>
-      <c r="C31" s="12"/>
-      <c r="D31" s="12"/>
-      <c r="E31" s="12"/>
-      <c r="F31" s="12"/>
-      <c r="G31" s="12"/>
-      <c r="H31" s="12"/>
-      <c r="I31" s="12"/>
-      <c r="J31" s="12"/>
-      <c r="K31" s="12"/>
-      <c r="L31" s="12"/>
-      <c r="M31" s="12"/>
-      <c r="N31" s="12"/>
+      <c r="A31" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="B31" s="13"/>
+      <c r="C31" s="13"/>
+      <c r="D31" s="13"/>
+      <c r="E31" s="13"/>
+      <c r="F31" s="13"/>
+      <c r="G31" s="13"/>
+      <c r="H31" s="13"/>
+      <c r="I31" s="13"/>
+      <c r="J31" s="13"/>
+      <c r="K31" s="13"/>
+      <c r="L31" s="13"/>
+      <c r="M31" s="13"/>
+      <c r="N31" s="13"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A32" s="12" t="s">
-        <v>220</v>
-      </c>
-      <c r="B32" s="20">
+      <c r="A32" s="13" t="s">
+        <v>221</v>
+      </c>
+      <c r="B32" s="21">
         <v>18000</v>
       </c>
-      <c r="C32" s="20">
+      <c r="C32" s="21">
         <v>18000</v>
       </c>
-      <c r="D32" s="20">
+      <c r="D32" s="21">
         <v>18000</v>
       </c>
-      <c r="E32" s="20">
+      <c r="E32" s="21">
         <v>18000</v>
       </c>
-      <c r="F32" s="20">
+      <c r="F32" s="21">
         <v>18000</v>
       </c>
-      <c r="G32" s="20">
+      <c r="G32" s="21">
         <v>18000</v>
       </c>
-      <c r="H32" s="20">
+      <c r="H32" s="21">
         <v>18000</v>
       </c>
-      <c r="I32" s="20">
+      <c r="I32" s="21">
         <v>18000</v>
       </c>
-      <c r="J32" s="20">
+      <c r="J32" s="21">
         <v>18000</v>
       </c>
-      <c r="K32" s="20">
+      <c r="K32" s="21">
         <v>18000</v>
       </c>
-      <c r="L32" s="20">
-        <v>0</v>
-      </c>
-      <c r="M32" s="20">
-        <v>0</v>
-      </c>
-      <c r="N32" s="20">
+      <c r="L32" s="21">
+        <v>0</v>
+      </c>
+      <c r="M32" s="21">
+        <v>0</v>
+      </c>
+      <c r="N32" s="21">
         <f>SUM(B32:M32)</f>
         <v>180000</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A33" s="12" t="s">
-        <v>221</v>
-      </c>
-      <c r="B33" s="20">
+      <c r="A33" s="13" t="s">
+        <v>222</v>
+      </c>
+      <c r="B33" s="21">
         <v>2500</v>
       </c>
-      <c r="C33" s="20">
+      <c r="C33" s="21">
         <v>2500</v>
       </c>
-      <c r="D33" s="20">
+      <c r="D33" s="21">
         <v>2500</v>
       </c>
-      <c r="E33" s="20">
+      <c r="E33" s="21">
         <v>2500</v>
       </c>
-      <c r="F33" s="20">
+      <c r="F33" s="21">
         <v>2500</v>
       </c>
-      <c r="G33" s="20">
+      <c r="G33" s="21">
         <v>2500</v>
       </c>
-      <c r="H33" s="20">
+      <c r="H33" s="21">
         <v>2500</v>
       </c>
-      <c r="I33" s="20">
+      <c r="I33" s="21">
         <v>2500</v>
       </c>
-      <c r="J33" s="20">
+      <c r="J33" s="21">
         <v>2500</v>
       </c>
-      <c r="K33" s="20">
+      <c r="K33" s="21">
         <v>2500</v>
       </c>
-      <c r="L33" s="20">
-        <v>0</v>
-      </c>
-      <c r="M33" s="20">
-        <v>0</v>
-      </c>
-      <c r="N33" s="20">
+      <c r="L33" s="21">
+        <v>0</v>
+      </c>
+      <c r="M33" s="21">
+        <v>0</v>
+      </c>
+      <c r="N33" s="21">
         <f>SUM(B33:M33)</f>
         <v>25000</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A34" s="12" t="s">
-        <v>222</v>
-      </c>
-      <c r="B34" s="20">
+      <c r="A34" s="13" t="s">
+        <v>223</v>
+      </c>
+      <c r="B34" s="21">
         <v>1500</v>
       </c>
-      <c r="C34" s="20">
+      <c r="C34" s="21">
         <v>1500</v>
       </c>
-      <c r="D34" s="20">
+      <c r="D34" s="21">
         <v>1500</v>
       </c>
-      <c r="E34" s="20">
+      <c r="E34" s="21">
         <v>1500</v>
       </c>
-      <c r="F34" s="20">
+      <c r="F34" s="21">
         <v>1500</v>
       </c>
-      <c r="G34" s="20">
+      <c r="G34" s="21">
         <v>1500</v>
       </c>
-      <c r="H34" s="20">
+      <c r="H34" s="21">
         <v>1500</v>
       </c>
-      <c r="I34" s="20">
+      <c r="I34" s="21">
         <v>1500</v>
       </c>
-      <c r="J34" s="20">
+      <c r="J34" s="21">
         <v>1500</v>
       </c>
-      <c r="K34" s="20">
+      <c r="K34" s="21">
         <v>1500</v>
       </c>
-      <c r="L34" s="20">
-        <v>0</v>
-      </c>
-      <c r="M34" s="20">
-        <v>0</v>
-      </c>
-      <c r="N34" s="20">
+      <c r="L34" s="21">
+        <v>0</v>
+      </c>
+      <c r="M34" s="21">
+        <v>0</v>
+      </c>
+      <c r="N34" s="21">
         <f>SUM(B34:M34)</f>
         <v>15000</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A35" s="12" t="s">
-        <v>223</v>
-      </c>
-      <c r="B35" s="20">
+      <c r="A35" s="13" t="s">
+        <v>224</v>
+      </c>
+      <c r="B35" s="21">
         <v>1500</v>
       </c>
-      <c r="C35" s="20">
+      <c r="C35" s="21">
         <v>1500</v>
       </c>
-      <c r="D35" s="20">
+      <c r="D35" s="21">
         <v>1500</v>
       </c>
-      <c r="E35" s="20">
+      <c r="E35" s="21">
         <v>1500</v>
       </c>
-      <c r="F35" s="20">
+      <c r="F35" s="21">
         <v>1500</v>
       </c>
-      <c r="G35" s="20">
+      <c r="G35" s="21">
         <v>1500</v>
       </c>
-      <c r="H35" s="20">
+      <c r="H35" s="21">
         <v>1500</v>
       </c>
-      <c r="I35" s="20">
+      <c r="I35" s="21">
         <v>1500</v>
       </c>
-      <c r="J35" s="20">
+      <c r="J35" s="21">
         <v>1500</v>
       </c>
-      <c r="K35" s="20">
+      <c r="K35" s="21">
         <v>1500</v>
       </c>
-      <c r="L35" s="20">
-        <v>0</v>
-      </c>
-      <c r="M35" s="20">
-        <v>0</v>
-      </c>
-      <c r="N35" s="20">
+      <c r="L35" s="21">
+        <v>0</v>
+      </c>
+      <c r="M35" s="21">
+        <v>0</v>
+      </c>
+      <c r="N35" s="21">
         <f>SUM(B35:M35)</f>
         <v>15000</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A36" s="28" t="s">
-        <v>166</v>
-      </c>
-      <c r="B36" s="29">
+      <c r="A36" s="29" t="s">
+        <v>167</v>
+      </c>
+      <c r="B36" s="30">
         <v>23500</v>
       </c>
-      <c r="C36" s="29">
+      <c r="C36" s="30">
         <v>23500</v>
       </c>
-      <c r="D36" s="29">
+      <c r="D36" s="30">
         <v>23500</v>
       </c>
-      <c r="E36" s="29">
+      <c r="E36" s="30">
         <v>23500</v>
       </c>
-      <c r="F36" s="29">
+      <c r="F36" s="30">
         <v>23500</v>
       </c>
-      <c r="G36" s="29">
+      <c r="G36" s="30">
         <v>23500</v>
       </c>
-      <c r="H36" s="29">
+      <c r="H36" s="30">
         <v>23500</v>
       </c>
-      <c r="I36" s="29">
+      <c r="I36" s="30">
         <v>23500</v>
       </c>
-      <c r="J36" s="29">
+      <c r="J36" s="30">
         <v>23500</v>
       </c>
-      <c r="K36" s="29">
+      <c r="K36" s="30">
         <v>23500</v>
       </c>
-      <c r="L36" s="29">
-        <v>0</v>
-      </c>
-      <c r="M36" s="29">
-        <v>0</v>
-      </c>
-      <c r="N36" s="29">
+      <c r="L36" s="30">
+        <v>0</v>
+      </c>
+      <c r="M36" s="30">
+        <v>0</v>
+      </c>
+      <c r="N36" s="30">
         <f>SUM(B36:M36)</f>
         <v>235000</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A37" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="B37" s="12"/>
-      <c r="C37" s="12"/>
-      <c r="D37" s="12"/>
-      <c r="E37" s="12"/>
-      <c r="F37" s="12"/>
-      <c r="G37" s="12"/>
-      <c r="H37" s="12"/>
-      <c r="I37" s="12"/>
-      <c r="J37" s="12"/>
-      <c r="K37" s="12"/>
-      <c r="L37" s="12"/>
-      <c r="M37" s="12"/>
-      <c r="N37" s="12"/>
+      <c r="A37" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="B37" s="13"/>
+      <c r="C37" s="13"/>
+      <c r="D37" s="13"/>
+      <c r="E37" s="13"/>
+      <c r="F37" s="13"/>
+      <c r="G37" s="13"/>
+      <c r="H37" s="13"/>
+      <c r="I37" s="13"/>
+      <c r="J37" s="13"/>
+      <c r="K37" s="13"/>
+      <c r="L37" s="13"/>
+      <c r="M37" s="13"/>
+      <c r="N37" s="13"/>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A38" s="12" t="s">
-        <v>224</v>
-      </c>
-      <c r="B38" s="20">
+      <c r="A38" s="13" t="s">
+        <v>225</v>
+      </c>
+      <c r="B38" s="21">
         <v>2083</v>
       </c>
-      <c r="C38" s="20">
+      <c r="C38" s="21">
         <v>2083</v>
       </c>
-      <c r="D38" s="20">
+      <c r="D38" s="21">
         <v>2083</v>
       </c>
-      <c r="E38" s="20">
+      <c r="E38" s="21">
         <v>2083</v>
       </c>
-      <c r="F38" s="20">
+      <c r="F38" s="21">
         <v>2083</v>
       </c>
-      <c r="G38" s="20">
+      <c r="G38" s="21">
         <v>2083</v>
       </c>
-      <c r="H38" s="20">
+      <c r="H38" s="21">
         <v>2083</v>
       </c>
-      <c r="I38" s="20">
+      <c r="I38" s="21">
         <v>2083</v>
       </c>
-      <c r="J38" s="20">
+      <c r="J38" s="21">
         <v>2083</v>
       </c>
-      <c r="K38" s="20">
+      <c r="K38" s="21">
         <v>2083</v>
       </c>
-      <c r="L38" s="20">
-        <v>0</v>
-      </c>
-      <c r="M38" s="20">
-        <v>0</v>
-      </c>
-      <c r="N38" s="20">
+      <c r="L38" s="21">
+        <v>0</v>
+      </c>
+      <c r="M38" s="21">
+        <v>0</v>
+      </c>
+      <c r="N38" s="21">
         <f>SUM(B38:M38)</f>
         <v>20833</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A39" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="B39" s="20">
+      <c r="A39" s="13" t="s">
+        <v>226</v>
+      </c>
+      <c r="B39" s="21">
         <v>1250</v>
       </c>
-      <c r="C39" s="20">
+      <c r="C39" s="21">
         <v>1250</v>
       </c>
-      <c r="D39" s="20">
+      <c r="D39" s="21">
         <v>1250</v>
       </c>
-      <c r="E39" s="20">
+      <c r="E39" s="21">
         <v>1250</v>
       </c>
-      <c r="F39" s="20">
+      <c r="F39" s="21">
         <v>1250</v>
       </c>
-      <c r="G39" s="20">
+      <c r="G39" s="21">
         <v>1250</v>
       </c>
-      <c r="H39" s="20">
+      <c r="H39" s="21">
         <v>1250</v>
       </c>
-      <c r="I39" s="20">
+      <c r="I39" s="21">
         <v>1250</v>
       </c>
-      <c r="J39" s="20">
+      <c r="J39" s="21">
         <v>1250</v>
       </c>
-      <c r="K39" s="20">
+      <c r="K39" s="21">
         <v>1250</v>
       </c>
-      <c r="L39" s="20">
-        <v>0</v>
-      </c>
-      <c r="M39" s="20">
-        <v>0</v>
-      </c>
-      <c r="N39" s="20">
+      <c r="L39" s="21">
+        <v>0</v>
+      </c>
+      <c r="M39" s="21">
+        <v>0</v>
+      </c>
+      <c r="N39" s="21">
         <f>SUM(B39:M39)</f>
         <v>12500</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A40" s="12" t="s">
-        <v>226</v>
-      </c>
-      <c r="B40" s="20">
+      <c r="A40" s="13" t="s">
+        <v>227</v>
+      </c>
+      <c r="B40" s="21">
         <v>1667</v>
       </c>
-      <c r="C40" s="20">
+      <c r="C40" s="21">
         <v>1667</v>
       </c>
-      <c r="D40" s="20">
+      <c r="D40" s="21">
         <v>1667</v>
       </c>
-      <c r="E40" s="20">
+      <c r="E40" s="21">
         <v>1667</v>
       </c>
-      <c r="F40" s="20">
+      <c r="F40" s="21">
         <v>1667</v>
       </c>
-      <c r="G40" s="20">
+      <c r="G40" s="21">
         <v>1667</v>
       </c>
-      <c r="H40" s="20">
+      <c r="H40" s="21">
         <v>1667</v>
       </c>
-      <c r="I40" s="20">
+      <c r="I40" s="21">
         <v>1667</v>
       </c>
-      <c r="J40" s="20">
+      <c r="J40" s="21">
         <v>1667</v>
       </c>
-      <c r="K40" s="20">
+      <c r="K40" s="21">
         <v>1667</v>
       </c>
-      <c r="L40" s="20">
-        <v>0</v>
-      </c>
-      <c r="M40" s="20">
-        <v>0</v>
-      </c>
-      <c r="N40" s="20">
+      <c r="L40" s="21">
+        <v>0</v>
+      </c>
+      <c r="M40" s="21">
+        <v>0</v>
+      </c>
+      <c r="N40" s="21">
         <f>SUM(B40:M40)</f>
         <v>16667</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A41" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="B41" s="20">
+      <c r="A41" s="13" t="s">
+        <v>228</v>
+      </c>
+      <c r="B41" s="21">
         <v>8000</v>
       </c>
-      <c r="C41" s="20">
+      <c r="C41" s="21">
         <v>8000</v>
       </c>
-      <c r="D41" s="20">
+      <c r="D41" s="21">
         <v>8000</v>
       </c>
-      <c r="E41" s="20">
+      <c r="E41" s="21">
         <v>8000</v>
       </c>
-      <c r="F41" s="20">
+      <c r="F41" s="21">
         <v>8000</v>
       </c>
-      <c r="G41" s="20">
+      <c r="G41" s="21">
         <v>8000</v>
       </c>
-      <c r="H41" s="20">
+      <c r="H41" s="21">
         <v>8000</v>
       </c>
-      <c r="I41" s="20">
+      <c r="I41" s="21">
         <v>8000</v>
       </c>
-      <c r="J41" s="20">
+      <c r="J41" s="21">
         <v>8000</v>
       </c>
-      <c r="K41" s="20">
+      <c r="K41" s="21">
         <v>8000</v>
       </c>
-      <c r="L41" s="20">
-        <v>0</v>
-      </c>
-      <c r="M41" s="20">
-        <v>0</v>
-      </c>
-      <c r="N41" s="20">
+      <c r="L41" s="21">
+        <v>0</v>
+      </c>
+      <c r="M41" s="21">
+        <v>0</v>
+      </c>
+      <c r="N41" s="21">
         <f>SUM(B41:M41)</f>
         <v>80000</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A42" s="12" t="s">
-        <v>228</v>
-      </c>
-      <c r="B42" s="20">
+      <c r="A42" s="13" t="s">
+        <v>229</v>
+      </c>
+      <c r="B42" s="21">
         <v>6000</v>
       </c>
-      <c r="C42" s="20">
+      <c r="C42" s="21">
         <v>6000</v>
       </c>
-      <c r="D42" s="20">
+      <c r="D42" s="21">
         <v>6000</v>
       </c>
-      <c r="E42" s="20">
+      <c r="E42" s="21">
         <v>6000</v>
       </c>
-      <c r="F42" s="20">
+      <c r="F42" s="21">
         <v>6000</v>
       </c>
-      <c r="G42" s="20">
+      <c r="G42" s="21">
         <v>6000</v>
       </c>
-      <c r="H42" s="20">
+      <c r="H42" s="21">
         <v>6000</v>
       </c>
-      <c r="I42" s="20">
+      <c r="I42" s="21">
         <v>6000</v>
       </c>
-      <c r="J42" s="20">
+      <c r="J42" s="21">
         <v>6000</v>
       </c>
-      <c r="K42" s="20">
+      <c r="K42" s="21">
         <v>6000</v>
       </c>
-      <c r="L42" s="20">
-        <v>0</v>
-      </c>
-      <c r="M42" s="20">
-        <v>0</v>
-      </c>
-      <c r="N42" s="20">
+      <c r="L42" s="21">
+        <v>0</v>
+      </c>
+      <c r="M42" s="21">
+        <v>0</v>
+      </c>
+      <c r="N42" s="21">
         <f>SUM(B42:M42)</f>
         <v>60000</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A43" s="28" t="s">
-        <v>172</v>
-      </c>
-      <c r="B43" s="29">
+      <c r="A43" s="29" t="s">
+        <v>173</v>
+      </c>
+      <c r="B43" s="30">
         <v>19000</v>
       </c>
-      <c r="C43" s="29">
+      <c r="C43" s="30">
         <v>19000</v>
       </c>
-      <c r="D43" s="29">
+      <c r="D43" s="30">
         <v>19000</v>
       </c>
-      <c r="E43" s="29">
+      <c r="E43" s="30">
         <v>19000</v>
       </c>
-      <c r="F43" s="29">
+      <c r="F43" s="30">
         <v>19000</v>
       </c>
-      <c r="G43" s="29">
+      <c r="G43" s="30">
         <v>19000</v>
       </c>
-      <c r="H43" s="29">
+      <c r="H43" s="30">
         <v>19000</v>
       </c>
-      <c r="I43" s="29">
+      <c r="I43" s="30">
         <v>19000</v>
       </c>
-      <c r="J43" s="29">
+      <c r="J43" s="30">
         <v>19000</v>
       </c>
-      <c r="K43" s="29">
+      <c r="K43" s="30">
         <v>19000</v>
       </c>
-      <c r="L43" s="29">
-        <v>0</v>
-      </c>
-      <c r="M43" s="29">
-        <v>0</v>
-      </c>
-      <c r="N43" s="29">
+      <c r="L43" s="30">
+        <v>0</v>
+      </c>
+      <c r="M43" s="30">
+        <v>0</v>
+      </c>
+      <c r="N43" s="30">
         <f>SUM(B43:M43)</f>
         <v>190000</v>
       </c>
     </row>
     <row r="44" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A44" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="B44" s="27">
+      <c r="A44" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="B44" s="28">
         <f>B27+B30+B36+B43</f>
         <v>54500</v>
       </c>
-      <c r="C44" s="27">
+      <c r="C44" s="28">
         <f>C27+C30+C36+C43</f>
         <v>54500</v>
       </c>
-      <c r="D44" s="27">
+      <c r="D44" s="28">
         <f>D27+D30+D36+D43</f>
         <v>54500</v>
       </c>
-      <c r="E44" s="27">
+      <c r="E44" s="28">
         <f>E27+E30+E36+E43</f>
         <v>54500</v>
       </c>
-      <c r="F44" s="27">
+      <c r="F44" s="28">
         <f>F27+F30+F36+F43</f>
         <v>54500</v>
       </c>
-      <c r="G44" s="27">
+      <c r="G44" s="28">
         <f>G27+G30+G36+G43</f>
         <v>54500</v>
       </c>
-      <c r="H44" s="27">
+      <c r="H44" s="28">
         <f>H27+H30+H36+H43</f>
         <v>54500</v>
       </c>
-      <c r="I44" s="27">
+      <c r="I44" s="28">
         <f>I27+I30+I36+I43</f>
         <v>54500</v>
       </c>
-      <c r="J44" s="27">
+      <c r="J44" s="28">
         <f>J27+J30+J36+J43</f>
         <v>54500</v>
       </c>
-      <c r="K44" s="27">
+      <c r="K44" s="28">
         <f>K27+K30+K36+K43</f>
         <v>54500</v>
       </c>
-      <c r="L44" s="27" t="str">
+      <c r="L44" s="28" t="str">
         <f>L27+L30+L36+L43</f>
         <v>0</v>
       </c>
-      <c r="M44" s="27" t="str">
+      <c r="M44" s="28" t="str">
         <f>M27+M30+M36+M43</f>
         <v>0</v>
       </c>
-      <c r="N44" s="27">
+      <c r="N44" s="28">
         <f>SUM(B44:M44)</f>
         <v>545000</v>
       </c>
@@ -6323,46 +6347,46 @@
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A46" s="25" t="s">
-        <v>229</v>
-      </c>
-      <c r="B46" s="20">
+      <c r="A46" s="26" t="s">
+        <v>230</v>
+      </c>
+      <c r="B46" s="21">
         <v>13735</v>
       </c>
-      <c r="C46" s="20">
+      <c r="C46" s="21">
         <v>13735</v>
       </c>
-      <c r="D46" s="20">
+      <c r="D46" s="21">
         <v>13735</v>
       </c>
-      <c r="E46" s="20">
+      <c r="E46" s="21">
         <v>13735</v>
       </c>
-      <c r="F46" s="20">
+      <c r="F46" s="21">
         <v>13735</v>
       </c>
-      <c r="G46" s="20">
+      <c r="G46" s="21">
         <v>13735</v>
       </c>
-      <c r="H46" s="20">
+      <c r="H46" s="21">
         <v>13735</v>
       </c>
-      <c r="I46" s="20">
+      <c r="I46" s="21">
         <v>13735</v>
       </c>
-      <c r="J46" s="20">
+      <c r="J46" s="21">
         <v>13735</v>
       </c>
-      <c r="K46" s="20">
+      <c r="K46" s="21">
         <v>13735</v>
       </c>
-      <c r="L46" s="20">
+      <c r="L46" s="21">
         <v>13735</v>
       </c>
-      <c r="M46" s="20">
+      <c r="M46" s="21">
         <v>13735</v>
       </c>
-      <c r="N46" s="20">
+      <c r="N46" s="21">
         <f>SUM(B46:M46)</f>
         <v>164825</v>
       </c>
@@ -6373,244 +6397,244 @@
       </c>
     </row>
     <row r="48" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A48" s="11" t="s">
-        <v>230</v>
-      </c>
-      <c r="B48" s="11"/>
-      <c r="C48" s="11"/>
-      <c r="D48" s="11"/>
-      <c r="E48" s="11"/>
-      <c r="F48" s="11"/>
-      <c r="G48" s="11"/>
-      <c r="H48" s="11"/>
-      <c r="I48" s="11"/>
-      <c r="J48" s="11"/>
-      <c r="K48" s="11"/>
-      <c r="L48" s="11"/>
-      <c r="M48" s="11"/>
-      <c r="N48" s="11"/>
+      <c r="A48" s="12" t="s">
+        <v>231</v>
+      </c>
+      <c r="B48" s="12"/>
+      <c r="C48" s="12"/>
+      <c r="D48" s="12"/>
+      <c r="E48" s="12"/>
+      <c r="F48" s="12"/>
+      <c r="G48" s="12"/>
+      <c r="H48" s="12"/>
+      <c r="I48" s="12"/>
+      <c r="J48" s="12"/>
+      <c r="K48" s="12"/>
+      <c r="L48" s="12"/>
+      <c r="M48" s="12"/>
+      <c r="N48" s="12"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A49" s="25" t="s">
-        <v>181</v>
-      </c>
-      <c r="B49" s="29">
+      <c r="A49" s="26" t="s">
+        <v>182</v>
+      </c>
+      <c r="B49" s="30">
         <f>B22+B44+B46</f>
         <v>170878</v>
       </c>
-      <c r="C49" s="29">
+      <c r="C49" s="30">
         <f>C22+C44+C46</f>
         <v>170878</v>
       </c>
-      <c r="D49" s="29">
+      <c r="D49" s="30">
         <f>D22+D44+D46</f>
         <v>170878</v>
       </c>
-      <c r="E49" s="29">
+      <c r="E49" s="30">
         <f>E22+E44+E46</f>
         <v>170878</v>
       </c>
-      <c r="F49" s="29">
+      <c r="F49" s="30">
         <f>F22+F44+F46</f>
         <v>170878</v>
       </c>
-      <c r="G49" s="29">
+      <c r="G49" s="30">
         <f>G22+G44+G46</f>
         <v>170878</v>
       </c>
-      <c r="H49" s="29">
+      <c r="H49" s="30">
         <f>H22+H44+H46</f>
         <v>170878</v>
       </c>
-      <c r="I49" s="29">
+      <c r="I49" s="30">
         <f>I22+I44+I46</f>
         <v>170878</v>
       </c>
-      <c r="J49" s="29">
+      <c r="J49" s="30">
         <f>J22+J44+J46</f>
         <v>170878</v>
       </c>
-      <c r="K49" s="29">
+      <c r="K49" s="30">
         <f>K22+K44+K46</f>
         <v>170878</v>
       </c>
-      <c r="L49" s="29">
+      <c r="L49" s="30">
         <f>L22+L44+L46</f>
         <v>13735</v>
       </c>
-      <c r="M49" s="29">
+      <c r="M49" s="30">
         <f>M22+M44+M46</f>
         <v>13735</v>
       </c>
-      <c r="N49" s="29">
+      <c r="N49" s="30">
         <f>SUM(B49:M49)</f>
         <v>1736250</v>
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A50" s="25" t="s">
-        <v>231</v>
-      </c>
-      <c r="B50" s="29">
+      <c r="A50" s="26" t="s">
+        <v>232</v>
+      </c>
+      <c r="B50" s="30">
         <f>B10-B49</f>
         <v>-16278</v>
       </c>
-      <c r="C50" s="29">
+      <c r="C50" s="30">
         <f>C10-C49</f>
         <v>-16278</v>
       </c>
-      <c r="D50" s="29">
+      <c r="D50" s="30">
         <f>D10-D49</f>
         <v>-16278</v>
       </c>
-      <c r="E50" s="29">
+      <c r="E50" s="30">
         <f>E10-E49</f>
         <v>-16278</v>
       </c>
-      <c r="F50" s="29">
+      <c r="F50" s="30">
         <f>F10-F49</f>
         <v>-16278</v>
       </c>
-      <c r="G50" s="29">
+      <c r="G50" s="30">
         <f>G10-G49</f>
         <v>-16278</v>
       </c>
-      <c r="H50" s="29">
+      <c r="H50" s="30">
         <f>H10-H49</f>
         <v>-16278</v>
       </c>
-      <c r="I50" s="29">
+      <c r="I50" s="30">
         <f>I10-I49</f>
         <v>-16278</v>
       </c>
-      <c r="J50" s="29">
+      <c r="J50" s="30">
         <f>J10-J49</f>
         <v>-16278</v>
       </c>
-      <c r="K50" s="29">
+      <c r="K50" s="30">
         <f>K10-K49</f>
         <v>-16278</v>
       </c>
-      <c r="L50" s="29">
+      <c r="L50" s="30">
         <f>L10-L49</f>
         <v>-13735</v>
       </c>
-      <c r="M50" s="29">
+      <c r="M50" s="30">
         <f>M10-M49</f>
         <v>-13735</v>
       </c>
-      <c r="N50" s="29">
+      <c r="N50" s="30">
         <f>SUM(B50:M50)</f>
         <v>-190250</v>
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A51" s="25" t="s">
-        <v>232</v>
-      </c>
-      <c r="B51" s="29">
+      <c r="A51" s="26" t="s">
+        <v>233</v>
+      </c>
+      <c r="B51" s="30">
         <f>0+B50</f>
         <v>-16278</v>
       </c>
-      <c r="C51" s="29">
+      <c r="C51" s="30">
         <f>B51+C50</f>
         <v>-32556</v>
       </c>
-      <c r="D51" s="29">
+      <c r="D51" s="30">
         <f>C51+D50</f>
         <v>-48834</v>
       </c>
-      <c r="E51" s="29">
+      <c r="E51" s="30">
         <f>D51+E50</f>
         <v>-65112</v>
       </c>
-      <c r="F51" s="29">
+      <c r="F51" s="30">
         <f>E51+F50</f>
         <v>-81390</v>
       </c>
-      <c r="G51" s="29">
+      <c r="G51" s="30">
         <f>F51+G50</f>
         <v>-97668</v>
       </c>
-      <c r="H51" s="29">
+      <c r="H51" s="30">
         <f>G51+H50</f>
         <v>-113946</v>
       </c>
-      <c r="I51" s="29">
+      <c r="I51" s="30">
         <f>H51+I50</f>
         <v>-130224</v>
       </c>
-      <c r="J51" s="29">
+      <c r="J51" s="30">
         <f>I51+J50</f>
         <v>-146502</v>
       </c>
-      <c r="K51" s="29">
+      <c r="K51" s="30">
         <f>J51+K50</f>
         <v>-162780</v>
       </c>
-      <c r="L51" s="29">
+      <c r="L51" s="30">
         <f>K51+L50</f>
         <v>-176515</v>
       </c>
-      <c r="M51" s="29">
+      <c r="M51" s="30">
         <f>L51+M50</f>
         <v>-190250</v>
       </c>
-      <c r="N51" s="29">
+      <c r="N51" s="30">
         <f>M51</f>
         <v>-190250</v>
       </c>
     </row>
     <row r="53" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" s="11" t="s">
-        <v>233</v>
-      </c>
-      <c r="B53" s="11"/>
-      <c r="C53" s="11"/>
+      <c r="A53" s="12" t="s">
+        <v>234</v>
+      </c>
+      <c r="B53" s="12"/>
+      <c r="C53" s="12"/>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" s="12" t="s">
-        <v>142</v>
-      </c>
-      <c r="B54" s="20">
+      <c r="A54" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="B54" s="21">
         <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A55" s="12" t="s">
-        <v>234</v>
-      </c>
-      <c r="B55" s="29">
+      <c r="A55" s="13" t="s">
+        <v>235</v>
+      </c>
+      <c r="B55" s="30">
         <f>M51</f>
         <v>-190250</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A56" s="12" t="s">
-        <v>235</v>
-      </c>
-      <c r="B56" s="20">
+      <c r="A56" s="13" t="s">
+        <v>236</v>
+      </c>
+      <c r="B56" s="21">
         <f>MIN(B51:M51)</f>
         <v>-190250</v>
       </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A58" s="23" t="s">
-        <v>143</v>
-      </c>
-      <c r="B58" s="23"/>
-      <c r="C58" s="23"/>
-      <c r="D58" s="23"/>
-      <c r="E58" s="23"/>
-      <c r="F58" s="23"/>
-      <c r="G58" s="23"/>
-      <c r="H58" s="23"/>
-      <c r="I58" s="23"/>
-      <c r="J58" s="23"/>
-      <c r="K58" s="23"/>
-      <c r="L58" s="23"/>
-      <c r="M58" s="23"/>
-      <c r="N58" s="23"/>
+      <c r="A58" s="24" t="s">
+        <v>144</v>
+      </c>
+      <c r="B58" s="24"/>
+      <c r="C58" s="24"/>
+      <c r="D58" s="24"/>
+      <c r="E58" s="24"/>
+      <c r="F58" s="24"/>
+      <c r="G58" s="24"/>
+      <c r="H58" s="24"/>
+      <c r="I58" s="24"/>
+      <c r="J58" s="24"/>
+      <c r="K58" s="24"/>
+      <c r="L58" s="24"/>
+      <c r="M58" s="24"/>
+      <c r="N58" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -6643,7 +6667,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -6652,466 +6676,466 @@
       <c r="G2" s="1"/>
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="39" t="s">
-        <v>237</v>
-      </c>
-      <c r="C3" s="39"/>
-      <c r="D3" s="39"/>
-      <c r="E3" s="39"/>
-      <c r="F3" s="39"/>
-      <c r="G3" s="39"/>
+      <c r="B3" s="40" t="s">
+        <v>238</v>
+      </c>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
+      <c r="G3" s="40"/>
     </row>
     <row r="5" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="11" t="s">
-        <v>238</v>
-      </c>
-      <c r="C5" s="15" t="s">
+      <c r="B5" s="12" t="s">
         <v>239</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="C5" s="16" t="s">
         <v>240</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="D5" s="16" t="s">
         <v>241</v>
       </c>
-      <c r="F5" s="15" t="s">
+      <c r="E5" s="16" t="s">
         <v>242</v>
       </c>
-      <c r="G5" s="15" t="s">
+      <c r="F5" s="16" t="s">
         <v>243</v>
       </c>
+      <c r="G5" s="16" t="s">
+        <v>244</v>
+      </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="12" t="s">
-        <v>244</v>
-      </c>
-      <c r="C6" s="40">
+      <c r="B6" s="13" t="s">
+        <v>245</v>
+      </c>
+      <c r="C6" s="41">
         <v>120</v>
       </c>
-      <c r="D6" s="40">
+      <c r="D6" s="41">
         <v>200</v>
       </c>
-      <c r="E6" s="40">
+      <c r="E6" s="41">
         <v>300</v>
       </c>
-      <c r="F6" s="40">
+      <c r="F6" s="41">
         <v>375</v>
       </c>
-      <c r="G6" s="40">
+      <c r="G6" s="41">
         <v>400</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="12" t="s">
-        <v>245</v>
-      </c>
-      <c r="C7" s="41">
+      <c r="B7" s="13" t="s">
+        <v>246</v>
+      </c>
+      <c r="C7" s="42">
         <v>1546000</v>
       </c>
-      <c r="D7" s="41">
+      <c r="D7" s="42">
         <v>2522800</v>
       </c>
-      <c r="E7" s="41">
+      <c r="E7" s="42">
         <v>3784600</v>
       </c>
-      <c r="F7" s="41">
+      <c r="F7" s="42">
         <v>4759125</v>
       </c>
-      <c r="G7" s="41">
+      <c r="G7" s="42">
         <v>5184400</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="12" t="s">
-        <v>246</v>
-      </c>
-      <c r="C8" s="41">
+      <c r="B8" s="13" t="s">
+        <v>247</v>
+      </c>
+      <c r="C8" s="42">
         <v>1026431.25</v>
       </c>
-      <c r="D8" s="41">
+      <c r="D8" s="42">
         <v>1231717.5</v>
       </c>
-      <c r="E8" s="41">
+      <c r="E8" s="42">
         <v>1231717.5</v>
       </c>
-      <c r="F8" s="41">
+      <c r="F8" s="42">
         <v>1231717.5</v>
       </c>
-      <c r="G8" s="41">
+      <c r="G8" s="42">
         <v>1231717.5</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="C9" s="41">
+      <c r="B9" s="13" t="s">
+        <v>248</v>
+      </c>
+      <c r="C9" s="42">
         <v>654000</v>
       </c>
-      <c r="D9" s="41">
+      <c r="D9" s="42">
         <v>887860</v>
       </c>
-      <c r="E9" s="41">
+      <c r="E9" s="42">
         <v>1190521.4</v>
       </c>
-      <c r="F9" s="41">
+      <c r="F9" s="42">
         <v>1439089.0320000001</v>
       </c>
-      <c r="G9" s="41">
+      <c r="G9" s="42">
         <v>1554923.90296</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="12" t="s">
-        <v>187</v>
-      </c>
-      <c r="C10" s="41">
+      <c r="B10" s="13" t="s">
+        <v>188</v>
+      </c>
+      <c r="C10" s="42">
         <v>49824.605221179416</v>
       </c>
-      <c r="D10" s="41">
+      <c r="D10" s="42">
         <v>49824.605221179416</v>
       </c>
-      <c r="E10" s="41">
+      <c r="E10" s="42">
         <v>49824.605221179416</v>
       </c>
-      <c r="F10" s="41">
+      <c r="F10" s="42">
         <v>49824.605221179416</v>
       </c>
-      <c r="G10" s="41">
+      <c r="G10" s="42">
         <v>49824.605221179416</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B11" s="25" t="s">
-        <v>182</v>
-      </c>
-      <c r="C11" s="42">
+      <c r="B11" s="26" t="s">
+        <v>183</v>
+      </c>
+      <c r="C11" s="43">
         <v>-184255.85522117943</v>
       </c>
-      <c r="D11" s="43">
+      <c r="D11" s="44">
         <v>353397.89477882057</v>
       </c>
-      <c r="E11" s="43">
+      <c r="E11" s="44">
         <v>1312536.4947788208</v>
       </c>
-      <c r="F11" s="43">
+      <c r="F11" s="44">
         <v>2038493.8627788206</v>
       </c>
-      <c r="G11" s="43">
+      <c r="G11" s="44">
         <v>2347933.9918188206</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="25" t="s">
-        <v>189</v>
-      </c>
-      <c r="C12" s="42">
+      <c r="B12" s="26" t="s">
+        <v>190</v>
+      </c>
+      <c r="C12" s="43">
         <v>-184255.85522117943</v>
       </c>
-      <c r="D12" s="43">
+      <c r="D12" s="44">
         <v>169142.03955764114</v>
       </c>
-      <c r="E12" s="43">
+      <c r="E12" s="44">
         <v>1481678.534336462</v>
       </c>
-      <c r="F12" s="43">
+      <c r="F12" s="44">
         <v>3520172.3971152827</v>
       </c>
-      <c r="G12" s="43">
+      <c r="G12" s="44">
         <v>5868106.388934104</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="25" t="s">
-        <v>248</v>
-      </c>
-      <c r="C13" s="44">
+      <c r="B13" s="26" t="s">
+        <v>249</v>
+      </c>
+      <c r="C13" s="45">
         <v>-0.11918231256221179</v>
       </c>
-      <c r="D13" s="45">
+      <c r="D13" s="46">
         <v>0.14008161359553692</v>
       </c>
-      <c r="E13" s="45">
+      <c r="E13" s="46">
         <v>0.34680983321323805</v>
       </c>
-      <c r="F13" s="45">
+      <c r="F13" s="46">
         <v>0.4283337510107048</v>
       </c>
-      <c r="G13" s="45">
+      <c r="G13" s="46">
         <v>0.4528844209202262</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="25" t="s">
-        <v>249</v>
-      </c>
-      <c r="C14" s="41">
+      <c r="B14" s="26" t="s">
+        <v>250</v>
+      </c>
+      <c r="C14" s="42">
         <v>12883.333333333334</v>
       </c>
-      <c r="D14" s="41">
+      <c r="D14" s="42">
         <v>12614</v>
       </c>
-      <c r="E14" s="41">
+      <c r="E14" s="42">
         <v>12615.333333333334</v>
       </c>
-      <c r="F14" s="41">
+      <c r="F14" s="42">
         <v>12691</v>
       </c>
-      <c r="G14" s="41">
+      <c r="G14" s="42">
         <v>12961</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="25" t="s">
-        <v>250</v>
-      </c>
-      <c r="C15" s="44">
+      <c r="B15" s="26" t="s">
+        <v>251</v>
+      </c>
+      <c r="C15" s="45">
         <v>0.6639270698576973</v>
       </c>
-      <c r="D15" s="45">
+      <c r="D15" s="46">
         <v>0.48823430315522437</v>
       </c>
-      <c r="E15" s="45">
+      <c r="E15" s="46">
         <v>0.3254551339639592</v>
       </c>
-      <c r="F15" s="45">
+      <c r="F15" s="46">
         <v>0.25881175636277676</v>
       </c>
-      <c r="G15" s="45">
+      <c r="G15" s="46">
         <v>0.23758149448345034</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="25" t="s">
-        <v>251</v>
-      </c>
-      <c r="C16" s="45">
+      <c r="B16" s="26" t="s">
+        <v>252</v>
+      </c>
+      <c r="C16" s="46">
         <v>0.12690815006468306</v>
       </c>
-      <c r="D16" s="45">
+      <c r="D16" s="46">
         <v>0.10558030759473601</v>
       </c>
-      <c r="E16" s="45">
+      <c r="E16" s="46">
         <v>0.09437098240236748</v>
       </c>
-      <c r="F16" s="45">
+      <c r="F16" s="46">
         <v>0.09071556422661729</v>
       </c>
-      <c r="G16" s="45">
+      <c r="G16" s="46">
         <v>0.08997707948615076</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="25" t="s">
-        <v>252</v>
-      </c>
-      <c r="C17" s="44">
+      <c r="B17" s="26" t="s">
+        <v>253</v>
+      </c>
+      <c r="C17" s="45">
         <v>-0.08695423673997413</v>
       </c>
-      <c r="D17" s="45">
+      <c r="D17" s="46">
         <v>0.15983133819565562</v>
       </c>
-      <c r="E17" s="45">
+      <c r="E17" s="46">
         <v>0.35997492469481585</v>
       </c>
-      <c r="F17" s="45">
+      <c r="F17" s="46">
         <v>0.4388030295484989</v>
       </c>
-      <c r="G17" s="45">
+      <c r="G17" s="46">
         <v>0.4624949072293804</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B18" s="25" t="s">
-        <v>253</v>
-      </c>
-      <c r="C18" s="46">
+      <c r="B18" s="26" t="s">
+        <v>254</v>
+      </c>
+      <c r="C18" s="47">
         <v>-2.698089616630942</v>
       </c>
-      <c r="D18" s="47">
+      <c r="D18" s="48">
         <v>8.092838833544805</v>
       </c>
-      <c r="E18" s="47">
+      <c r="E18" s="48">
         <v>27.34313887590801</v>
       </c>
-      <c r="F18" s="47">
+      <c r="F18" s="48">
         <v>41.91339718056208</v>
       </c>
-      <c r="G18" s="47">
+      <c r="G18" s="48">
         <v>48.12398585791026</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="25" t="s">
-        <v>254</v>
-      </c>
-      <c r="C19" s="48" t="s">
-        <v>240</v>
-      </c>
-      <c r="D19" s="48"/>
-      <c r="E19" s="48"/>
-      <c r="F19" s="48"/>
-      <c r="G19" s="48"/>
+      <c r="B19" s="26" t="s">
+        <v>255</v>
+      </c>
+      <c r="C19" s="49" t="s">
+        <v>241</v>
+      </c>
+      <c r="D19" s="49"/>
+      <c r="E19" s="49"/>
+      <c r="F19" s="49"/>
+      <c r="G19" s="49"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B20" s="25" t="s">
-        <v>255</v>
-      </c>
-      <c r="C20" s="49" t="s">
+      <c r="B20" s="26" t="s">
         <v>256</v>
       </c>
-      <c r="D20" s="49"/>
-      <c r="E20" s="49"/>
-      <c r="F20" s="49"/>
-      <c r="G20" s="49"/>
+      <c r="C20" s="50" t="s">
+        <v>257</v>
+      </c>
+      <c r="D20" s="50"/>
+      <c r="E20" s="50"/>
+      <c r="F20" s="50"/>
+      <c r="G20" s="50"/>
     </row>
     <row r="22" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B22" s="11" t="s">
-        <v>257</v>
-      </c>
-      <c r="C22" s="11" t="s">
+      <c r="B22" s="12" t="s">
         <v>258</v>
       </c>
-      <c r="D22" s="11" t="s">
+      <c r="C22" s="12" t="s">
         <v>259</v>
       </c>
-      <c r="E22" s="11"/>
-      <c r="F22" s="11" t="s">
+      <c r="D22" s="12" t="s">
         <v>260</v>
       </c>
-      <c r="G22" s="11"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="12" t="s">
+        <v>261</v>
+      </c>
+      <c r="G22" s="12"/>
     </row>
     <row r="23" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B23" s="50" t="s">
-        <v>261</v>
-      </c>
-      <c r="C23" s="51" t="s">
+      <c r="B23" s="51" t="s">
         <v>262</v>
       </c>
-      <c r="D23" s="52" t="s">
+      <c r="C23" s="52" t="s">
         <v>263</v>
       </c>
-      <c r="E23" s="52"/>
-      <c r="F23" s="53" t="s">
+      <c r="D23" s="53" t="s">
         <v>264</v>
       </c>
-      <c r="G23" s="53"/>
+      <c r="E23" s="53"/>
+      <c r="F23" s="54" t="s">
+        <v>265</v>
+      </c>
+      <c r="G23" s="54"/>
     </row>
     <row r="24" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B24" s="50" t="s">
-        <v>265</v>
-      </c>
-      <c r="C24" s="54" t="s">
+      <c r="B24" s="51" t="s">
         <v>266</v>
       </c>
-      <c r="D24" s="52" t="s">
+      <c r="C24" s="55" t="s">
         <v>267</v>
       </c>
-      <c r="E24" s="52"/>
-      <c r="F24" s="53" t="s">
+      <c r="D24" s="53" t="s">
         <v>268</v>
       </c>
-      <c r="G24" s="53"/>
+      <c r="E24" s="53"/>
+      <c r="F24" s="54" t="s">
+        <v>269</v>
+      </c>
+      <c r="G24" s="54"/>
     </row>
     <row r="25" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B25" s="50" t="s">
-        <v>269</v>
-      </c>
-      <c r="C25" s="51" t="s">
-        <v>262</v>
-      </c>
-      <c r="D25" s="52" t="s">
+      <c r="B25" s="51" t="s">
         <v>270</v>
       </c>
-      <c r="E25" s="52"/>
-      <c r="F25" s="53" t="s">
+      <c r="C25" s="52" t="s">
+        <v>263</v>
+      </c>
+      <c r="D25" s="53" t="s">
         <v>271</v>
       </c>
-      <c r="G25" s="53"/>
+      <c r="E25" s="53"/>
+      <c r="F25" s="54" t="s">
+        <v>272</v>
+      </c>
+      <c r="G25" s="54"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B26" s="50" t="s">
-        <v>272</v>
-      </c>
-      <c r="C26" s="51" t="s">
-        <v>262</v>
-      </c>
-      <c r="D26" s="52" t="s">
+      <c r="B26" s="51" t="s">
         <v>273</v>
       </c>
-      <c r="E26" s="52"/>
-      <c r="F26" s="53" t="s">
+      <c r="C26" s="52" t="s">
+        <v>263</v>
+      </c>
+      <c r="D26" s="53" t="s">
         <v>274</v>
       </c>
-      <c r="G26" s="53"/>
+      <c r="E26" s="53"/>
+      <c r="F26" s="54" t="s">
+        <v>275</v>
+      </c>
+      <c r="G26" s="54"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B27" s="50" t="s">
-        <v>275</v>
-      </c>
-      <c r="C27" s="51" t="s">
-        <v>262</v>
-      </c>
-      <c r="D27" s="52" t="s">
+      <c r="B27" s="51" t="s">
         <v>276</v>
       </c>
-      <c r="E27" s="52"/>
-      <c r="F27" s="53" t="s">
+      <c r="C27" s="52" t="s">
+        <v>263</v>
+      </c>
+      <c r="D27" s="53" t="s">
         <v>277</v>
       </c>
-      <c r="G27" s="53"/>
+      <c r="E27" s="53"/>
+      <c r="F27" s="54" t="s">
+        <v>278</v>
+      </c>
+      <c r="G27" s="54"/>
     </row>
     <row r="28" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B28" s="50" t="s">
-        <v>278</v>
-      </c>
-      <c r="C28" s="51" t="s">
-        <v>262</v>
-      </c>
-      <c r="D28" s="52" t="s">
+      <c r="B28" s="51" t="s">
         <v>279</v>
       </c>
-      <c r="E28" s="52"/>
-      <c r="F28" s="53" t="s">
+      <c r="C28" s="52" t="s">
+        <v>263</v>
+      </c>
+      <c r="D28" s="53" t="s">
         <v>280</v>
       </c>
-      <c r="G28" s="53"/>
+      <c r="E28" s="53"/>
+      <c r="F28" s="54" t="s">
+        <v>281</v>
+      </c>
+      <c r="G28" s="54"/>
     </row>
     <row r="29" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B29" s="50" t="s">
-        <v>281</v>
-      </c>
-      <c r="C29" s="51" t="s">
-        <v>262</v>
-      </c>
-      <c r="D29" s="52" t="s">
+      <c r="B29" s="51" t="s">
         <v>282</v>
       </c>
-      <c r="E29" s="52"/>
-      <c r="F29" s="53" t="s">
+      <c r="C29" s="52" t="s">
+        <v>263</v>
+      </c>
+      <c r="D29" s="53" t="s">
         <v>283</v>
       </c>
-      <c r="G29" s="53"/>
+      <c r="E29" s="53"/>
+      <c r="F29" s="54" t="s">
+        <v>284</v>
+      </c>
+      <c r="G29" s="54"/>
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B31" s="50" t="s">
-        <v>284</v>
-      </c>
-      <c r="C31" s="25" t="s">
+      <c r="B31" s="51" t="s">
         <v>285</v>
       </c>
-      <c r="D31" s="25"/>
-      <c r="E31" s="25"/>
+      <c r="C31" s="26" t="s">
+        <v>286</v>
+      </c>
+      <c r="D31" s="26"/>
+      <c r="E31" s="26"/>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B33" s="55" t="s">
-        <v>143</v>
-      </c>
-      <c r="C33" s="55"/>
-      <c r="D33" s="55"/>
-      <c r="E33" s="55"/>
-      <c r="F33" s="55"/>
-      <c r="G33" s="55"/>
+      <c r="B33" s="56" t="s">
+        <v>144</v>
+      </c>
+      <c r="C33" s="56"/>
+      <c r="D33" s="56"/>
+      <c r="E33" s="56"/>
+      <c r="F33" s="56"/>
+      <c r="G33" s="56"/>
     </row>
   </sheetData>
   <mergeCells count="22">

--- a/artifacts/api-server/qa-output/Formula_Export_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Formula_Export_Charter_Public_Funding.xlsx
@@ -19,7 +19,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'5-Year Model'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Year 1 Pro Forma'!$A1:$N58</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Year 1 Pro Forma'!$1:$2</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'Financial Health'!$A1:$G33</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Financial Health'!$A1:$H35</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Financial Health'!$1:$2</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="299">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -746,6 +746,15 @@
     <t>Generated March 26, 2026</t>
   </si>
   <si>
+    <t>● Green = healthy</t>
+  </si>
+  <si>
+    <t>◐ Yellow = monitor</t>
+  </si>
+  <si>
+    <t>○ Red = action needed</t>
+  </si>
+  <si>
     <t>Metric</t>
   </si>
   <si>
@@ -764,6 +773,9 @@
     <t>Year 5</t>
   </si>
   <si>
+    <t>Benchmark</t>
+  </si>
+  <si>
     <t>Enrollment</t>
   </si>
   <si>
@@ -782,18 +794,39 @@
     <t>Revenue per Student</t>
   </si>
   <si>
+    <t>≥ $10,000</t>
+  </si>
+  <si>
     <t>Payroll %</t>
   </si>
   <si>
+    <t>≤ 55%</t>
+  </si>
+  <si>
     <t>Facility %</t>
   </si>
   <si>
+    <t>≤ 15%</t>
+  </si>
+  <si>
     <t>Operating Margin</t>
   </si>
   <si>
+    <t>≥ 10%</t>
+  </si>
+  <si>
+    <t>Revenue Sources</t>
+  </si>
+  <si>
+    <t>≥ 3 sources</t>
+  </si>
+  <si>
     <t>DSCR</t>
   </si>
   <si>
+    <t>≥ 1.25x</t>
+  </si>
+  <si>
     <t>Break-even Year</t>
   </si>
   <si>
@@ -801,6 +834,9 @@
   </si>
   <si>
     <t>0 months</t>
+  </si>
+  <si>
+    <t>60+ months</t>
   </si>
   <si>
     <t>FINANCIAL HEALTH SIGNALS</t>
@@ -901,7 +937,7 @@
     <numFmt numFmtId="167" formatCode="0.00x"/>
     <numFmt numFmtId="168" formatCode="0.0"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -1000,6 +1036,12 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <color rgb="FFD97706"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -1090,7 +1132,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1140,6 +1182,9 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1158,6 +1203,11 @@
     <xf numFmtId="166" fontId="12" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="12" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1186,7 +1236,28 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="21">
+  <dxfs count="24">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -6653,19 +6724,20 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
-    <tabColor rgb="FF0D9488"/>
+    <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:G33"/>
+  <dimension ref="B2:H35"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
     <col min="3" max="7" width="16" customWidth="1"/>
-    <col min="8" max="8" width="40" customWidth="1"/>
+    <col min="8" max="8" width="20" customWidth="1"/>
+    <col min="9" max="9" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" ht="30" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>237</v>
       </c>
@@ -6674,8 +6746,9 @@
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
-    </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="H2" s="1"/>
+    </row>
+    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B3" s="40" t="s">
         <v>238</v>
       </c>
@@ -6684,559 +6757,632 @@
       <c r="E3" s="40"/>
       <c r="F3" s="40"/>
       <c r="G3" s="40"/>
-    </row>
-    <row r="5" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="12" t="s">
+      <c r="H3" s="40"/>
+    </row>
+    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B4" s="41" t="s">
         <v>239</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="D4" s="42" t="s">
         <v>240</v>
       </c>
-      <c r="D5" s="16" t="s">
+      <c r="F4" s="43" t="s">
         <v>241</v>
       </c>
-      <c r="E5" s="16" t="s">
+    </row>
+    <row r="6" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B6" s="12" t="s">
         <v>242</v>
       </c>
-      <c r="F5" s="16" t="s">
+      <c r="C6" s="16" t="s">
         <v>243</v>
       </c>
-      <c r="G5" s="16" t="s">
+      <c r="D6" s="16" t="s">
         <v>244</v>
       </c>
-    </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="13" t="s">
+      <c r="E6" s="16" t="s">
         <v>245</v>
       </c>
-      <c r="C6" s="41">
-        <v>120</v>
-      </c>
-      <c r="D6" s="41">
-        <v>200</v>
-      </c>
-      <c r="E6" s="41">
-        <v>300</v>
-      </c>
-      <c r="F6" s="41">
-        <v>375</v>
-      </c>
-      <c r="G6" s="41">
-        <v>400</v>
+      <c r="F6" s="16" t="s">
+        <v>246</v>
+      </c>
+      <c r="G6" s="16" t="s">
+        <v>247</v>
+      </c>
+      <c r="H6" s="16" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="13" t="s">
-        <v>246</v>
-      </c>
-      <c r="C7" s="42">
-        <v>1546000</v>
-      </c>
-      <c r="D7" s="42">
-        <v>2522800</v>
-      </c>
-      <c r="E7" s="42">
-        <v>3784600</v>
-      </c>
-      <c r="F7" s="42">
-        <v>4759125</v>
-      </c>
-      <c r="G7" s="42">
-        <v>5184400</v>
+        <v>249</v>
+      </c>
+      <c r="C7" s="44">
+        <v>120</v>
+      </c>
+      <c r="D7" s="44">
+        <v>200</v>
+      </c>
+      <c r="E7" s="44">
+        <v>300</v>
+      </c>
+      <c r="F7" s="44">
+        <v>375</v>
+      </c>
+      <c r="G7" s="44">
+        <v>400</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="13" t="s">
-        <v>247</v>
-      </c>
-      <c r="C8" s="42">
-        <v>1026431.25</v>
-      </c>
-      <c r="D8" s="42">
-        <v>1231717.5</v>
-      </c>
-      <c r="E8" s="42">
-        <v>1231717.5</v>
-      </c>
-      <c r="F8" s="42">
-        <v>1231717.5</v>
-      </c>
-      <c r="G8" s="42">
-        <v>1231717.5</v>
+        <v>250</v>
+      </c>
+      <c r="C8" s="45">
+        <v>1546000</v>
+      </c>
+      <c r="D8" s="45">
+        <v>2522800</v>
+      </c>
+      <c r="E8" s="45">
+        <v>3784600</v>
+      </c>
+      <c r="F8" s="45">
+        <v>4759125</v>
+      </c>
+      <c r="G8" s="45">
+        <v>5184400</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="13" t="s">
-        <v>248</v>
-      </c>
-      <c r="C9" s="42">
-        <v>654000</v>
-      </c>
-      <c r="D9" s="42">
-        <v>887860</v>
-      </c>
-      <c r="E9" s="42">
-        <v>1190521.4</v>
-      </c>
-      <c r="F9" s="42">
-        <v>1439089.0320000001</v>
-      </c>
-      <c r="G9" s="42">
-        <v>1554923.90296</v>
+        <v>251</v>
+      </c>
+      <c r="C9" s="45">
+        <v>1026431.25</v>
+      </c>
+      <c r="D9" s="45">
+        <v>1231717.5</v>
+      </c>
+      <c r="E9" s="45">
+        <v>1231717.5</v>
+      </c>
+      <c r="F9" s="45">
+        <v>1231717.5</v>
+      </c>
+      <c r="G9" s="45">
+        <v>1231717.5</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="13" t="s">
+        <v>252</v>
+      </c>
+      <c r="C10" s="45">
+        <v>654000</v>
+      </c>
+      <c r="D10" s="45">
+        <v>887860</v>
+      </c>
+      <c r="E10" s="45">
+        <v>1190521.4</v>
+      </c>
+      <c r="F10" s="45">
+        <v>1439089.0320000001</v>
+      </c>
+      <c r="G10" s="45">
+        <v>1554923.90296</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B11" s="13" t="s">
         <v>188</v>
       </c>
-      <c r="C10" s="42">
+      <c r="C11" s="45">
         <v>49824.605221179416</v>
       </c>
-      <c r="D10" s="42">
+      <c r="D11" s="45">
         <v>49824.605221179416</v>
       </c>
-      <c r="E10" s="42">
+      <c r="E11" s="45">
         <v>49824.605221179416</v>
       </c>
-      <c r="F10" s="42">
+      <c r="F11" s="45">
         <v>49824.605221179416</v>
       </c>
-      <c r="G10" s="42">
+      <c r="G11" s="45">
         <v>49824.605221179416</v>
-      </c>
-    </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B11" s="26" t="s">
-        <v>183</v>
-      </c>
-      <c r="C11" s="43">
-        <v>-184255.85522117943</v>
-      </c>
-      <c r="D11" s="44">
-        <v>353397.89477882057</v>
-      </c>
-      <c r="E11" s="44">
-        <v>1312536.4947788208</v>
-      </c>
-      <c r="F11" s="44">
-        <v>2038493.8627788206</v>
-      </c>
-      <c r="G11" s="44">
-        <v>2347933.9918188206</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="26" t="s">
-        <v>190</v>
-      </c>
-      <c r="C12" s="43">
+        <v>183</v>
+      </c>
+      <c r="C12" s="46">
         <v>-184255.85522117943</v>
       </c>
-      <c r="D12" s="44">
-        <v>169142.03955764114</v>
-      </c>
-      <c r="E12" s="44">
-        <v>1481678.534336462</v>
-      </c>
-      <c r="F12" s="44">
-        <v>3520172.3971152827</v>
-      </c>
-      <c r="G12" s="44">
-        <v>5868106.388934104</v>
+      <c r="D12" s="47">
+        <v>353397.89477882057</v>
+      </c>
+      <c r="E12" s="47">
+        <v>1312536.4947788208</v>
+      </c>
+      <c r="F12" s="47">
+        <v>2038493.8627788206</v>
+      </c>
+      <c r="G12" s="47">
+        <v>2347933.9918188206</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="26" t="s">
-        <v>249</v>
-      </c>
-      <c r="C13" s="45">
-        <v>-0.11918231256221179</v>
-      </c>
-      <c r="D13" s="46">
-        <v>0.14008161359553692</v>
-      </c>
-      <c r="E13" s="46">
-        <v>0.34680983321323805</v>
-      </c>
-      <c r="F13" s="46">
-        <v>0.4283337510107048</v>
-      </c>
-      <c r="G13" s="46">
-        <v>0.4528844209202262</v>
+        <v>190</v>
+      </c>
+      <c r="C13" s="46">
+        <v>-184255.85522117943</v>
+      </c>
+      <c r="D13" s="47">
+        <v>169142.03955764114</v>
+      </c>
+      <c r="E13" s="47">
+        <v>1481678.534336462</v>
+      </c>
+      <c r="F13" s="47">
+        <v>3520172.3971152827</v>
+      </c>
+      <c r="G13" s="47">
+        <v>5868106.388934104</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="26" t="s">
-        <v>250</v>
-      </c>
-      <c r="C14" s="42">
+        <v>253</v>
+      </c>
+      <c r="C14" s="48">
+        <v>-0.11918231256221179</v>
+      </c>
+      <c r="D14" s="49">
+        <v>0.14008161359553692</v>
+      </c>
+      <c r="E14" s="49">
+        <v>0.34680983321323805</v>
+      </c>
+      <c r="F14" s="49">
+        <v>0.4283337510107048</v>
+      </c>
+      <c r="G14" s="49">
+        <v>0.4528844209202262</v>
+      </c>
+    </row>
+    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B15" s="26" t="s">
+        <v>254</v>
+      </c>
+      <c r="C15" s="50">
         <v>12883.333333333334</v>
       </c>
-      <c r="D14" s="42">
+      <c r="D15" s="50">
         <v>12614</v>
       </c>
-      <c r="E14" s="42">
+      <c r="E15" s="50">
         <v>12615.333333333334</v>
       </c>
-      <c r="F14" s="42">
+      <c r="F15" s="50">
         <v>12691</v>
       </c>
-      <c r="G14" s="42">
+      <c r="G15" s="50">
         <v>12961</v>
       </c>
-    </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="26" t="s">
-        <v>251</v>
-      </c>
-      <c r="C15" s="45">
+      <c r="H15" s="51" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B16" s="26" t="s">
+        <v>256</v>
+      </c>
+      <c r="C16" s="48">
         <v>0.6639270698576973</v>
       </c>
-      <c r="D15" s="46">
+      <c r="D16" s="49">
         <v>0.48823430315522437</v>
       </c>
-      <c r="E15" s="46">
+      <c r="E16" s="49">
         <v>0.3254551339639592</v>
       </c>
-      <c r="F15" s="46">
+      <c r="F16" s="49">
         <v>0.25881175636277676</v>
       </c>
-      <c r="G15" s="46">
+      <c r="G16" s="49">
         <v>0.23758149448345034</v>
       </c>
-    </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="26" t="s">
-        <v>252</v>
-      </c>
-      <c r="C16" s="46">
+      <c r="H16" s="51" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B17" s="26" t="s">
+        <v>258</v>
+      </c>
+      <c r="C17" s="49">
         <v>0.12690815006468306</v>
       </c>
-      <c r="D16" s="46">
+      <c r="D17" s="49">
         <v>0.10558030759473601</v>
       </c>
-      <c r="E16" s="46">
+      <c r="E17" s="49">
         <v>0.09437098240236748</v>
       </c>
-      <c r="F16" s="46">
+      <c r="F17" s="49">
         <v>0.09071556422661729</v>
       </c>
-      <c r="G16" s="46">
+      <c r="G17" s="49">
         <v>0.08997707948615076</v>
       </c>
-    </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="26" t="s">
-        <v>253</v>
-      </c>
-      <c r="C17" s="45">
+      <c r="H17" s="51" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="26" t="s">
+        <v>260</v>
+      </c>
+      <c r="C18" s="48">
         <v>-0.08695423673997413</v>
       </c>
-      <c r="D17" s="46">
+      <c r="D18" s="49">
         <v>0.15983133819565562</v>
       </c>
-      <c r="E17" s="46">
+      <c r="E18" s="49">
         <v>0.35997492469481585</v>
       </c>
-      <c r="F17" s="46">
+      <c r="F18" s="49">
         <v>0.4388030295484989</v>
       </c>
-      <c r="G17" s="46">
+      <c r="G18" s="49">
         <v>0.4624949072293804</v>
       </c>
-    </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B18" s="26" t="s">
-        <v>254</v>
-      </c>
-      <c r="C18" s="47">
+      <c r="H18" s="51" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B19" s="26" t="s">
+        <v>262</v>
+      </c>
+      <c r="C19" s="52">
+        <v>1</v>
+      </c>
+      <c r="D19" s="52"/>
+      <c r="E19" s="52"/>
+      <c r="F19" s="52"/>
+      <c r="G19" s="52"/>
+      <c r="H19" s="51" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B20" s="26" t="s">
+        <v>264</v>
+      </c>
+      <c r="C20" s="53">
         <v>-2.698089616630942</v>
       </c>
-      <c r="D18" s="48">
+      <c r="D20" s="54">
         <v>8.092838833544805</v>
       </c>
-      <c r="E18" s="48">
+      <c r="E20" s="54">
         <v>27.34313887590801</v>
       </c>
-      <c r="F18" s="48">
+      <c r="F20" s="54">
         <v>41.91339718056208</v>
       </c>
-      <c r="G18" s="48">
+      <c r="G20" s="54">
         <v>48.12398585791026</v>
       </c>
-    </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="26" t="s">
-        <v>255</v>
-      </c>
-      <c r="C19" s="49" t="s">
-        <v>241</v>
-      </c>
-      <c r="D19" s="49"/>
-      <c r="E19" s="49"/>
-      <c r="F19" s="49"/>
-      <c r="G19" s="49"/>
-    </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B20" s="26" t="s">
-        <v>256</v>
-      </c>
-      <c r="C20" s="50" t="s">
-        <v>257</v>
-      </c>
-      <c r="D20" s="50"/>
-      <c r="E20" s="50"/>
-      <c r="F20" s="50"/>
-      <c r="G20" s="50"/>
-    </row>
-    <row r="22" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B22" s="12" t="s">
-        <v>258</v>
-      </c>
-      <c r="C22" s="12" t="s">
-        <v>259</v>
-      </c>
-      <c r="D22" s="12" t="s">
-        <v>260</v>
-      </c>
-      <c r="E22" s="12"/>
-      <c r="F22" s="12" t="s">
-        <v>261</v>
-      </c>
-      <c r="G22" s="12"/>
-    </row>
-    <row r="23" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B23" s="51" t="s">
-        <v>262</v>
-      </c>
-      <c r="C23" s="52" t="s">
-        <v>263</v>
-      </c>
-      <c r="D23" s="53" t="s">
-        <v>264</v>
-      </c>
-      <c r="E23" s="53"/>
-      <c r="F23" s="54" t="s">
+      <c r="H20" s="51" t="s">
         <v>265</v>
       </c>
-      <c r="G23" s="54"/>
-    </row>
-    <row r="24" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B24" s="51" t="s">
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B21" s="26" t="s">
         <v>266</v>
       </c>
-      <c r="C24" s="55" t="s">
+      <c r="C21" s="55" t="s">
+        <v>244</v>
+      </c>
+      <c r="D21" s="55"/>
+      <c r="E21" s="55"/>
+      <c r="F21" s="55"/>
+      <c r="G21" s="55"/>
+      <c r="H21" s="51" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B22" s="26" t="s">
         <v>267</v>
       </c>
-      <c r="D24" s="53" t="s">
+      <c r="C22" s="56" t="s">
         <v>268</v>
       </c>
-      <c r="E24" s="53"/>
-      <c r="F24" s="54" t="s">
+      <c r="D22" s="56"/>
+      <c r="E22" s="56"/>
+      <c r="F22" s="56"/>
+      <c r="G22" s="56"/>
+      <c r="H22" s="51" t="s">
         <v>269</v>
       </c>
-      <c r="G24" s="54"/>
-    </row>
-    <row r="25" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B25" s="51" t="s">
+    </row>
+    <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="12" t="s">
         <v>270</v>
       </c>
-      <c r="C25" s="52" t="s">
-        <v>263</v>
-      </c>
-      <c r="D25" s="53" t="s">
+      <c r="C24" s="12" t="s">
         <v>271</v>
       </c>
-      <c r="E25" s="53"/>
-      <c r="F25" s="54" t="s">
+      <c r="D24" s="12" t="s">
         <v>272</v>
       </c>
-      <c r="G25" s="54"/>
-    </row>
-    <row r="26" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B26" s="51" t="s">
+      <c r="E24" s="12"/>
+      <c r="F24" s="12" t="s">
         <v>273</v>
       </c>
-      <c r="C26" s="52" t="s">
-        <v>263</v>
-      </c>
-      <c r="D26" s="53" t="s">
+      <c r="G24" s="12"/>
+      <c r="H24" s="12"/>
+    </row>
+    <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="57" t="s">
         <v>274</v>
       </c>
-      <c r="E26" s="53"/>
-      <c r="F26" s="54" t="s">
+      <c r="C25" s="58" t="s">
         <v>275</v>
       </c>
-      <c r="G26" s="54"/>
-    </row>
-    <row r="27" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B27" s="51" t="s">
+      <c r="D25" s="59" t="s">
         <v>276</v>
       </c>
-      <c r="C27" s="52" t="s">
-        <v>263</v>
-      </c>
-      <c r="D27" s="53" t="s">
+      <c r="E25" s="59"/>
+      <c r="F25" s="60" t="s">
         <v>277</v>
       </c>
-      <c r="E27" s="53"/>
-      <c r="F27" s="54" t="s">
+      <c r="G25" s="60"/>
+      <c r="H25" s="60"/>
+    </row>
+    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="57" t="s">
         <v>278</v>
       </c>
-      <c r="G27" s="54"/>
-    </row>
-    <row r="28" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B28" s="51" t="s">
+      <c r="C26" s="61" t="s">
         <v>279</v>
       </c>
-      <c r="C28" s="52" t="s">
-        <v>263</v>
-      </c>
-      <c r="D28" s="53" t="s">
+      <c r="D26" s="59" t="s">
         <v>280</v>
       </c>
-      <c r="E28" s="53"/>
-      <c r="F28" s="54" t="s">
+      <c r="E26" s="59"/>
+      <c r="F26" s="60" t="s">
         <v>281</v>
       </c>
-      <c r="G28" s="54"/>
-    </row>
-    <row r="29" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B29" s="51" t="s">
+      <c r="G26" s="60"/>
+      <c r="H26" s="60"/>
+    </row>
+    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="57" t="s">
         <v>282</v>
       </c>
-      <c r="C29" s="52" t="s">
-        <v>263</v>
-      </c>
-      <c r="D29" s="53" t="s">
+      <c r="C27" s="58" t="s">
+        <v>275</v>
+      </c>
+      <c r="D27" s="59" t="s">
         <v>283</v>
       </c>
-      <c r="E29" s="53"/>
-      <c r="F29" s="54" t="s">
+      <c r="E27" s="59"/>
+      <c r="F27" s="60" t="s">
         <v>284</v>
       </c>
-      <c r="G29" s="54"/>
-    </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B31" s="51" t="s">
+      <c r="G27" s="60"/>
+      <c r="H27" s="60"/>
+    </row>
+    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B28" s="57" t="s">
         <v>285</v>
       </c>
-      <c r="C31" s="26" t="s">
+      <c r="C28" s="58" t="s">
+        <v>275</v>
+      </c>
+      <c r="D28" s="59" t="s">
         <v>286</v>
       </c>
-      <c r="D31" s="26"/>
-      <c r="E31" s="26"/>
-    </row>
-    <row r="33" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B33" s="56" t="s">
+      <c r="E28" s="59"/>
+      <c r="F28" s="60" t="s">
+        <v>287</v>
+      </c>
+      <c r="G28" s="60"/>
+      <c r="H28" s="60"/>
+    </row>
+    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="57" t="s">
+        <v>288</v>
+      </c>
+      <c r="C29" s="58" t="s">
+        <v>275</v>
+      </c>
+      <c r="D29" s="59" t="s">
+        <v>289</v>
+      </c>
+      <c r="E29" s="59"/>
+      <c r="F29" s="60" t="s">
+        <v>290</v>
+      </c>
+      <c r="G29" s="60"/>
+      <c r="H29" s="60"/>
+    </row>
+    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B30" s="57" t="s">
+        <v>291</v>
+      </c>
+      <c r="C30" s="58" t="s">
+        <v>275</v>
+      </c>
+      <c r="D30" s="59" t="s">
+        <v>292</v>
+      </c>
+      <c r="E30" s="59"/>
+      <c r="F30" s="60" t="s">
+        <v>293</v>
+      </c>
+      <c r="G30" s="60"/>
+      <c r="H30" s="60"/>
+    </row>
+    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B31" s="57" t="s">
+        <v>294</v>
+      </c>
+      <c r="C31" s="58" t="s">
+        <v>275</v>
+      </c>
+      <c r="D31" s="59" t="s">
+        <v>295</v>
+      </c>
+      <c r="E31" s="59"/>
+      <c r="F31" s="60" t="s">
+        <v>296</v>
+      </c>
+      <c r="G31" s="60"/>
+      <c r="H31" s="60"/>
+    </row>
+    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B33" s="57" t="s">
+        <v>297</v>
+      </c>
+      <c r="C33" s="26" t="s">
+        <v>298</v>
+      </c>
+      <c r="D33" s="26"/>
+      <c r="E33" s="26"/>
+      <c r="F33" s="26"/>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B35" s="62" t="s">
         <v>144</v>
       </c>
-      <c r="C33" s="56"/>
-      <c r="D33" s="56"/>
-      <c r="E33" s="56"/>
-      <c r="F33" s="56"/>
-      <c r="G33" s="56"/>
+      <c r="C35" s="62"/>
+      <c r="D35" s="62"/>
+      <c r="E35" s="62"/>
+      <c r="F35" s="62"/>
+      <c r="G35" s="62"/>
+      <c r="H35" s="62"/>
     </row>
   </sheetData>
-  <mergeCells count="22">
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B3:G3"/>
+  <mergeCells count="23">
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B3:H3"/>
     <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="C22:G22"/>
     <mergeCell ref="D24:E24"/>
-    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F24:H24"/>
     <mergeCell ref="D25:E25"/>
-    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="F25:H25"/>
     <mergeCell ref="D26:E26"/>
-    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F26:H26"/>
     <mergeCell ref="D27:E27"/>
-    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="F27:H27"/>
     <mergeCell ref="D28:E28"/>
-    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="F28:H28"/>
     <mergeCell ref="D29:E29"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="C31:E31"/>
-    <mergeCell ref="B33:G33"/>
+    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="B35:H35"/>
   </mergeCells>
-  <conditionalFormatting sqref="C11:G11">
+  <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">
-      <formula>C11&gt;=0</formula>
+      <formula>C12&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="1" priority="2">
-      <formula>C11&gt;=-1</formula>
+      <formula>C12&gt;=-1</formula>
     </cfRule>
     <cfRule type="expression" dxfId="2" priority="3">
-      <formula>C11&lt;-1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C12:G12">
-    <cfRule type="expression" dxfId="3" priority="1">
-      <formula>C12&gt;=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="4" priority="2">
-      <formula>C12&gt;=-1</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="5" priority="3">
       <formula>C12&lt;-1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C13:G13">
+    <cfRule type="expression" dxfId="3" priority="1">
+      <formula>C13&gt;=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="4" priority="2">
+      <formula>C13&gt;=-1</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="5" priority="3">
+      <formula>C13&lt;-1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C14:G14">
     <cfRule type="expression" dxfId="6" priority="1">
-      <formula>C13&gt;=0.05</formula>
+      <formula>C14&gt;=0.05</formula>
     </cfRule>
     <cfRule type="expression" dxfId="7" priority="2">
-      <formula>C13&gt;=0</formula>
+      <formula>C14&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="8" priority="3">
-      <formula>C13&lt;0</formula>
+      <formula>C14&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:G15">
     <cfRule type="expression" dxfId="9" priority="1">
-      <formula>C15&lt;=0.55</formula>
+      <formula>C15&gt;=10000</formula>
     </cfRule>
     <cfRule type="expression" dxfId="10" priority="2">
-      <formula>C15&lt;=0.65</formula>
+      <formula>C15&gt;=7000</formula>
     </cfRule>
     <cfRule type="expression" dxfId="11" priority="3">
-      <formula>C15&gt;0.65</formula>
+      <formula>C15&lt;7000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C16:G16">
     <cfRule type="expression" dxfId="12" priority="1">
-      <formula>C16&lt;=0.15</formula>
+      <formula>C16&lt;=0.55</formula>
     </cfRule>
     <cfRule type="expression" dxfId="13" priority="2">
-      <formula>C16&lt;=0.25</formula>
+      <formula>C16&lt;=0.65</formula>
     </cfRule>
     <cfRule type="expression" dxfId="14" priority="3">
-      <formula>C16&gt;0.25</formula>
+      <formula>C16&gt;0.65</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C17:G17">
     <cfRule type="expression" dxfId="15" priority="1">
-      <formula>C17&gt;=0.10</formula>
+      <formula>C17&lt;=0.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="16" priority="2">
-      <formula>C17&gt;=0</formula>
+      <formula>C17&lt;=0.25</formula>
     </cfRule>
     <cfRule type="expression" dxfId="17" priority="3">
-      <formula>C17&lt;0</formula>
+      <formula>C17&gt;0.25</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C18:G18">
     <cfRule type="expression" dxfId="18" priority="1">
-      <formula>C18&gt;=1.25</formula>
+      <formula>C18&gt;=0.10</formula>
     </cfRule>
     <cfRule type="expression" dxfId="19" priority="2">
-      <formula>C18&gt;=1.0</formula>
+      <formula>C18&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="20" priority="3">
-      <formula>C18&lt;1.0</formula>
+      <formula>C18&lt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C20:G20">
+    <cfRule type="expression" dxfId="21" priority="1">
+      <formula>C20&gt;=1.25</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="22" priority="2">
+      <formula>C20&gt;=1.0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="23" priority="3">
+      <formula>C20&lt;1.0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>

--- a/artifacts/api-server/qa-output/Formula_Export_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Formula_Export_Charter_Public_Funding.xlsx
@@ -15,7 +15,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Instructions'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Assumptions'!$A1:$J70</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Assumptions'!$1:$3</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'5-Year Model'!$A1:$F89</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'5-Year Model'!$A1:$F90</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'5-Year Model'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Year 1 Pro Forma'!$A1:$N58</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Year 1 Pro Forma'!$1:$2</definedName>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="301">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -585,6 +585,12 @@
   </si>
   <si>
     <t>Cumulative Net Income</t>
+  </si>
+  <si>
+    <t>Break-even</t>
+  </si>
+  <si>
+    <t>✓ Break-even</t>
   </si>
   <si>
     <t>CASH FLOW &amp; DEBT COVERAGE</t>
@@ -1025,14 +1031,14 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <i/>
-      <color rgb="FF6B7280"/>
+      <b/>
+      <color rgb="FF16A34A"/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b/>
-      <color rgb="FF16A34A"/>
+      <i/>
+      <color rgb="FF6B7280"/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
@@ -1132,7 +1138,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1176,13 +1182,19 @@
     <xf numFmtId="165" fontId="14" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="167" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="168" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1206,24 +1218,21 @@
     <xf numFmtId="165" fontId="6" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="12" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="167" fontId="12" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3059,7 +3068,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F89"/>
+  <dimension ref="A1:F90"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
@@ -4176,500 +4185,520 @@
         <v>5479436</v>
       </c>
     </row>
-    <row r="65" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A65" s="12" t="s">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" s="29" t="s">
         <v>186</v>
       </c>
-      <c r="B65" s="12"/>
-      <c r="C65" s="12"/>
-      <c r="D65" s="12"/>
-      <c r="E65" s="12"/>
-      <c r="F65" s="12"/>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A66" s="26" t="s">
+      <c r="B64" s="35" t="s">
+        <v>7</v>
+      </c>
+      <c r="C64" s="35" t="s">
+        <v>7</v>
+      </c>
+      <c r="D64" s="36" t="s">
         <v>187</v>
       </c>
-      <c r="B66" s="30">
+      <c r="E64" s="35" t="s">
+        <v>7</v>
+      </c>
+      <c r="F64" s="35" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="66" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="B66" s="12"/>
+      <c r="C66" s="12"/>
+      <c r="D66" s="12"/>
+      <c r="E66" s="12"/>
+      <c r="F66" s="12"/>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" s="26" t="s">
+        <v>189</v>
+      </c>
+      <c r="B67" s="30">
         <f>B55-B56-B57</f>
         <v>-283098</v>
       </c>
-      <c r="C66" s="30">
+      <c r="C67" s="30">
         <f>C55-C56-C57</f>
         <v>403222</v>
       </c>
-      <c r="D66" s="30">
+      <c r="D67" s="30">
         <f>D55-D56-D57</f>
         <v>1362361</v>
       </c>
-      <c r="E66" s="30">
+      <c r="E67" s="30">
         <f>E55-E56-E57</f>
         <v>2088318</v>
       </c>
-      <c r="F66" s="30">
+      <c r="F67" s="30">
         <f>F55-F56-F57</f>
         <v>2397758</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A67" s="13" t="s">
-        <v>188</v>
-      </c>
-      <c r="B67" s="21">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68" s="13" t="s">
+        <v>190</v>
+      </c>
+      <c r="B68" s="21">
         <f>B58</f>
         <v>164825</v>
       </c>
-      <c r="C67" s="21">
+      <c r="C68" s="21">
         <f>C58</f>
         <v>89825</v>
       </c>
-      <c r="D67" s="21">
+      <c r="D68" s="21">
         <f>D58</f>
         <v>89825</v>
       </c>
-      <c r="E67" s="21">
+      <c r="E68" s="21">
         <f>E58</f>
         <v>74825</v>
       </c>
-      <c r="F67" s="21">
+      <c r="F68" s="21">
         <f>F58</f>
         <v>69825</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A68" s="26" t="s">
-        <v>189</v>
-      </c>
-      <c r="B68" s="35">
-        <f>IF(B67=0,"N/A",B66/B67)</f>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" s="26" t="s">
+        <v>191</v>
+      </c>
+      <c r="B69" s="37">
+        <f>IF(B68=0,"N/A",B67/B68)</f>
         <v>-1.72</v>
       </c>
-      <c r="C68" s="35">
-        <f>IF(C67=0,"N/A",C66/C67)</f>
+      <c r="C69" s="37">
+        <f>IF(C68=0,"N/A",C67/C68)</f>
         <v>4.49</v>
       </c>
-      <c r="D68" s="35">
-        <f>IF(D67=0,"N/A",D66/D67)</f>
+      <c r="D69" s="37">
+        <f>IF(D68=0,"N/A",D67/D68)</f>
         <v>15.17</v>
       </c>
-      <c r="E68" s="35">
-        <f>IF(E67=0,"N/A",E66/E67)</f>
+      <c r="E69" s="37">
+        <f>IF(E68=0,"N/A",E67/E68)</f>
         <v>27.91</v>
       </c>
-      <c r="F68" s="35">
-        <f>IF(F67=0,"N/A",F66/F67)</f>
+      <c r="F69" s="37">
+        <f>IF(F68=0,"N/A",F67/F68)</f>
         <v>34.34</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A69" s="13" t="s">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70" s="13" t="s">
         <v>143</v>
       </c>
-      <c r="B69" s="21" t="str">
+      <c r="B70" s="21" t="str">
         <f>Assumptions!B68</f>
         <v>0</v>
       </c>
-      <c r="C69" s="21">
-        <f>B70</f>
+      <c r="C70" s="21">
+        <f>B71</f>
         <v>-447923</v>
       </c>
-      <c r="D69" s="21">
-        <f>C70</f>
+      <c r="D70" s="21">
+        <f>C71</f>
         <v>-134526</v>
       </c>
-      <c r="E69" s="21">
-        <f>D70</f>
+      <c r="E70" s="21">
+        <f>D71</f>
         <v>1138010</v>
       </c>
-      <c r="F69" s="21">
-        <f>E70</f>
+      <c r="F70" s="21">
+        <f>E71</f>
         <v>3151503</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A70" s="26" t="s">
-        <v>190</v>
-      </c>
-      <c r="B70" s="30">
-        <f>B69+B61</f>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A71" s="26" t="s">
+        <v>192</v>
+      </c>
+      <c r="B71" s="30">
+        <f>B70+B61</f>
         <v>-447923</v>
       </c>
-      <c r="C70" s="30">
-        <f>C69+C61</f>
+      <c r="C71" s="30">
+        <f>C70+C61</f>
         <v>-134526</v>
       </c>
-      <c r="D70" s="30">
-        <f>D69+D61</f>
+      <c r="D71" s="30">
+        <f>D70+D61</f>
         <v>1138010</v>
       </c>
-      <c r="E70" s="30">
-        <f>E69+E61</f>
+      <c r="E71" s="30">
+        <f>E70+E61</f>
         <v>3151503</v>
       </c>
-      <c r="F70" s="30">
-        <f>F69+F61</f>
+      <c r="F71" s="30">
+        <f>F70+F61</f>
         <v>5479436</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A71" s="13" t="s">
-        <v>191</v>
-      </c>
-      <c r="B71" s="36">
-        <f>IF(B59=0,"",B70/B59*365)</f>
-        <v>-94</v>
-      </c>
-      <c r="C71" s="36">
-        <f>IF(C59=0,"",C70/C59*365)</f>
-        <v>-22</v>
-      </c>
-      <c r="D71" s="36">
-        <f>IF(D59=0,"",D70/D59*365)</f>
-        <v>165</v>
-      </c>
-      <c r="E71" s="36">
-        <f>IF(E59=0,"",E70/E59*365)</f>
-        <v>419</v>
-      </c>
-      <c r="F71" s="36">
-        <f>IF(F59=0,"",F70/F59*365)</f>
-        <v>700</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="13" t="s">
-        <v>192</v>
-      </c>
-      <c r="B72" s="37">
-        <f>IF(B59=0,"",B70/(B59/12))</f>
-        <v>-3.1</v>
-      </c>
-      <c r="C72" s="37">
-        <f>IF(C59=0,"",C70/(C59/12))</f>
-        <v>-0.7</v>
-      </c>
-      <c r="D72" s="37">
-        <f>IF(D59=0,"",D70/(D59/12))</f>
-        <v>5.4</v>
-      </c>
-      <c r="E72" s="37">
-        <f>IF(E59=0,"",E70/(E59/12))</f>
-        <v>13.8</v>
-      </c>
-      <c r="F72" s="37">
-        <f>IF(F59=0,"",F70/(F59/12))</f>
-        <v>23</v>
+        <v>193</v>
+      </c>
+      <c r="B72" s="38">
+        <f>IF(B59=0,"",B71/B59*365)</f>
+        <v>-94</v>
+      </c>
+      <c r="C72" s="38">
+        <f>IF(C59=0,"",C71/C59*365)</f>
+        <v>-22</v>
+      </c>
+      <c r="D72" s="38">
+        <f>IF(D59=0,"",D71/D59*365)</f>
+        <v>165</v>
+      </c>
+      <c r="E72" s="38">
+        <f>IF(E59=0,"",E71/E59*365)</f>
+        <v>419</v>
+      </c>
+      <c r="F72" s="38">
+        <f>IF(F59=0,"",F71/F59*365)</f>
+        <v>700</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="13" t="s">
-        <v>193</v>
-      </c>
-      <c r="B73" s="34">
+        <v>194</v>
+      </c>
+      <c r="B73" s="39">
+        <f>IF(B59=0,"",B71/(B59/12))</f>
+        <v>-3.1</v>
+      </c>
+      <c r="C73" s="39">
+        <f>IF(C59=0,"",C71/(C59/12))</f>
+        <v>-0.7</v>
+      </c>
+      <c r="D73" s="39">
+        <f>IF(D59=0,"",D71/(D59/12))</f>
+        <v>5.4</v>
+      </c>
+      <c r="E73" s="39">
+        <f>IF(E59=0,"",E71/(E59/12))</f>
+        <v>13.8</v>
+      </c>
+      <c r="F73" s="39">
+        <f>IF(F59=0,"",F71/(F59/12))</f>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A74" s="13" t="s">
+        <v>195</v>
+      </c>
+      <c r="B74" s="34">
         <f>IF(Assumptions!B12=0,"",B3/Assumptions!B12)</f>
         <v>0.3</v>
       </c>
-      <c r="C73" s="34">
+      <c r="C74" s="34">
         <f>IF(Assumptions!B12=0,"",C3/Assumptions!B12)</f>
         <v>0.5</v>
       </c>
-      <c r="D73" s="34">
+      <c r="D74" s="34">
         <f>IF(Assumptions!B12=0,"",D3/Assumptions!B12)</f>
         <v>0.75</v>
       </c>
-      <c r="E73" s="34">
+      <c r="E74" s="34">
         <f>IF(Assumptions!B12=0,"",E3/Assumptions!B12)</f>
         <v>0.94</v>
       </c>
-      <c r="F73" s="34">
+      <c r="F74" s="34">
         <f>IF(Assumptions!B12=0,"",F3/Assumptions!B12)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="75" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A75" s="12" t="s">
-        <v>194</v>
-      </c>
-      <c r="B75" s="12"/>
-      <c r="C75" s="12"/>
-      <c r="D75" s="12"/>
-      <c r="E75" s="12"/>
-      <c r="F75" s="12"/>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A76" s="13" t="s">
-        <v>195</v>
-      </c>
-      <c r="B76" s="13" t="str">
-        <f>IF(B67=0,"N/A",IF(B68&gt;=1.2,"PASS","FAIL"))</f>
-        <v>FAIL</v>
-      </c>
-      <c r="C76" s="13" t="str">
-        <f>IF(C67=0,"N/A",IF(C68&gt;=1.2,"PASS","FAIL"))</f>
-        <v>PASS</v>
-      </c>
-      <c r="D76" s="13" t="str">
-        <f>IF(D67=0,"N/A",IF(D68&gt;=1.2,"PASS","FAIL"))</f>
-        <v>PASS</v>
-      </c>
-      <c r="E76" s="13" t="str">
-        <f>IF(E67=0,"N/A",IF(E68&gt;=1.2,"PASS","FAIL"))</f>
-        <v>PASS</v>
-      </c>
-      <c r="F76" s="13" t="str">
-        <f>IF(F67=0,"N/A",IF(F68&gt;=1.2,"PASS","FAIL"))</f>
-        <v>PASS</v>
-      </c>
+    <row r="76" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A76" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="B76" s="12"/>
+      <c r="C76" s="12"/>
+      <c r="D76" s="12"/>
+      <c r="E76" s="12"/>
+      <c r="F76" s="12"/>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="13" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B77" s="13" t="str">
+        <f>IF(B68=0,"N/A",IF(B69&gt;=1.2,"PASS","FAIL"))</f>
+        <v>FAIL</v>
+      </c>
+      <c r="C77" s="13" t="str">
+        <f>IF(C68=0,"N/A",IF(C69&gt;=1.2,"PASS","FAIL"))</f>
+        <v>PASS</v>
+      </c>
+      <c r="D77" s="13" t="str">
+        <f>IF(D68=0,"N/A",IF(D69&gt;=1.2,"PASS","FAIL"))</f>
+        <v>PASS</v>
+      </c>
+      <c r="E77" s="13" t="str">
+        <f>IF(E68=0,"N/A",IF(E69&gt;=1.2,"PASS","FAIL"))</f>
+        <v>PASS</v>
+      </c>
+      <c r="F77" s="13" t="str">
+        <f>IF(F68=0,"N/A",IF(F69&gt;=1.2,"PASS","FAIL"))</f>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="B78" s="13" t="str">
         <f>IF(B61&gt;0,"PASS","FAIL")</f>
         <v>FAIL</v>
       </c>
-      <c r="C77" s="13" t="str">
+      <c r="C78" s="13" t="str">
         <f>IF(C61&gt;0,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-      <c r="D77" s="13" t="str">
+      <c r="D78" s="13" t="str">
         <f>IF(D61&gt;0,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-      <c r="E77" s="13" t="str">
+      <c r="E78" s="13" t="str">
         <f>IF(E61&gt;0,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-      <c r="F77" s="13" t="str">
+      <c r="F78" s="13" t="str">
         <f>IF(F61&gt;0,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A78" s="13" t="s">
-        <v>197</v>
-      </c>
-      <c r="B78" s="13" t="str">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A79" s="13" t="s">
+        <v>199</v>
+      </c>
+      <c r="B79" s="13" t="str">
         <f>IF(Assumptions!B12=0,"N/A",IF(B3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
         <v>FAIL</v>
       </c>
-      <c r="C78" s="13" t="str">
+      <c r="C79" s="13" t="str">
         <f>IF(Assumptions!B12=0,"N/A",IF(C3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
         <v>FAIL</v>
       </c>
-      <c r="D78" s="13" t="str">
+      <c r="D79" s="13" t="str">
         <f>IF(Assumptions!B12=0,"N/A",IF(D3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="E78" s="13" t="str">
+      <c r="E79" s="13" t="str">
         <f>IF(Assumptions!B12=0,"N/A",IF(E3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="F78" s="13" t="str">
+      <c r="F79" s="13" t="str">
         <f>IF(Assumptions!B12=0,"N/A",IF(F3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A79" s="13" t="s">
-        <v>198</v>
-      </c>
-      <c r="B79" s="13" t="str">
-        <f>IF(B59=0,"N/A",IF(B70/(B59/12)&gt;=2,"PASS","FAIL"))</f>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A80" s="13" t="s">
+        <v>200</v>
+      </c>
+      <c r="B80" s="13" t="str">
+        <f>IF(B59=0,"N/A",IF(B71/(B59/12)&gt;=2,"PASS","FAIL"))</f>
         <v>FAIL</v>
       </c>
-      <c r="C79" s="13" t="str">
-        <f>IF(C59=0,"N/A",IF(C70/(C59/12)&gt;=2,"PASS","FAIL"))</f>
+      <c r="C80" s="13" t="str">
+        <f>IF(C59=0,"N/A",IF(C71/(C59/12)&gt;=2,"PASS","FAIL"))</f>
         <v>FAIL</v>
       </c>
-      <c r="D79" s="13" t="str">
-        <f>IF(D59=0,"N/A",IF(D70/(D59/12)&gt;=2,"PASS","FAIL"))</f>
+      <c r="D80" s="13" t="str">
+        <f>IF(D59=0,"N/A",IF(D71/(D59/12)&gt;=2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="E79" s="13" t="str">
-        <f>IF(E59=0,"N/A",IF(E70/(E59/12)&gt;=2,"PASS","FAIL"))</f>
+      <c r="E80" s="13" t="str">
+        <f>IF(E59=0,"N/A",IF(E71/(E59/12)&gt;=2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="F79" s="13" t="str">
-        <f>IF(F59=0,"N/A",IF(F70/(F59/12)&gt;=2,"PASS","FAIL"))</f>
+      <c r="F80" s="13" t="str">
+        <f>IF(F59=0,"N/A",IF(F71/(F59/12)&gt;=2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
-    <row r="81" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A81" s="12" t="s">
-        <v>199</v>
-      </c>
-      <c r="B81" s="12"/>
-      <c r="C81" s="12"/>
-      <c r="D81" s="12"/>
-      <c r="E81" s="12"/>
-      <c r="F81" s="12"/>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A82" s="13" t="s">
-        <v>200</v>
-      </c>
-      <c r="B82" s="21">
+    <row r="82" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A82" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="B82" s="12"/>
+      <c r="C82" s="12"/>
+      <c r="D82" s="12"/>
+      <c r="E82" s="12"/>
+      <c r="F82" s="12"/>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A83" s="13" t="s">
+        <v>202</v>
+      </c>
+      <c r="B83" s="21">
         <f>IF(B3=0,"",B12/B3)</f>
         <v>10736</v>
       </c>
-      <c r="C82" s="21">
+      <c r="C83" s="21">
         <f>IF(C3=0,"",C12/C3)</f>
         <v>12614</v>
       </c>
-      <c r="D82" s="21">
+      <c r="D83" s="21">
         <f>IF(D3=0,"",D12/D3)</f>
         <v>12615</v>
       </c>
-      <c r="E82" s="21">
+      <c r="E83" s="21">
         <f>IF(E3=0,"",E12/E3)</f>
         <v>12691</v>
       </c>
-      <c r="F82" s="21">
+      <c r="F83" s="21">
         <f>IF(F3=0,"",F12/F3)</f>
         <v>12961</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A83" s="13" t="s">
-        <v>201</v>
-      </c>
-      <c r="B83" s="21">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A84" s="13" t="s">
+        <v>203</v>
+      </c>
+      <c r="B84" s="21">
         <f>IF(B3=0,"",B59/B3)</f>
         <v>14469</v>
       </c>
-      <c r="C83" s="21">
+      <c r="C84" s="21">
         <f>IF(C3=0,"",C59/C3)</f>
         <v>11047</v>
       </c>
-      <c r="D83" s="21">
+      <c r="D84" s="21">
         <f>IF(D3=0,"",D59/D3)</f>
         <v>8374</v>
       </c>
-      <c r="E83" s="21">
+      <c r="E84" s="21">
         <f>IF(E3=0,"",E59/E3)</f>
         <v>7322</v>
       </c>
-      <c r="F83" s="21">
+      <c r="F84" s="21">
         <f>IF(F3=0,"",F59/F3)</f>
         <v>7141</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A84" s="13" t="s">
-        <v>202</v>
-      </c>
-      <c r="B84" s="21">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A85" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="B85" s="21">
         <f>B56+B58</f>
         <v>1191256</v>
       </c>
-      <c r="C84" s="21">
+      <c r="C85" s="21">
         <f>C56+C58</f>
         <v>1321543</v>
       </c>
-      <c r="D84" s="21">
+      <c r="D85" s="21">
         <f>D56+D58</f>
         <v>1321543</v>
       </c>
-      <c r="E84" s="21">
+      <c r="E85" s="21">
         <f>E56+E58</f>
         <v>1306543</v>
       </c>
-      <c r="F84" s="21">
+      <c r="F85" s="21">
         <f>F56+F58</f>
         <v>1301543</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A85" s="13" t="s">
-        <v>203</v>
-      </c>
-      <c r="B85" s="21">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A86" s="13" t="s">
+        <v>205</v>
+      </c>
+      <c r="B86" s="21">
         <f>IF(B3=0,"",B57/B3)</f>
         <v>4542</v>
       </c>
-      <c r="C85" s="21">
+      <c r="C86" s="21">
         <f>IF(C3=0,"",C57/C3)</f>
         <v>4439</v>
       </c>
-      <c r="D85" s="21">
+      <c r="D86" s="21">
         <f>IF(D3=0,"",D57/D3)</f>
         <v>3968</v>
       </c>
-      <c r="E85" s="21">
+      <c r="E86" s="21">
         <f>IF(E3=0,"",E57/E3)</f>
         <v>3838</v>
       </c>
-      <c r="F85" s="21">
+      <c r="F86" s="21">
         <f>IF(F3=0,"",F57/F3)</f>
         <v>3887</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A86" s="13" t="s">
-        <v>204</v>
-      </c>
-      <c r="B86" s="21">
-        <f>IF(B3=0,"",B82-B85)</f>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A87" s="13" t="s">
+        <v>206</v>
+      </c>
+      <c r="B87" s="21">
+        <f>IF(B3=0,"",B83-B86)</f>
         <v>6194</v>
       </c>
-      <c r="C86" s="21">
-        <f>IF(C3=0,"",C82-C85)</f>
+      <c r="C87" s="21">
+        <f>IF(C3=0,"",C83-C86)</f>
         <v>8175</v>
       </c>
-      <c r="D86" s="21">
-        <f>IF(D3=0,"",D82-D85)</f>
+      <c r="D87" s="21">
+        <f>IF(D3=0,"",D83-D86)</f>
         <v>8647</v>
       </c>
-      <c r="E86" s="21">
-        <f>IF(E3=0,"",E82-E85)</f>
+      <c r="E87" s="21">
+        <f>IF(E3=0,"",E83-E86)</f>
         <v>8853</v>
       </c>
-      <c r="F86" s="21">
-        <f>IF(F3=0,"",F82-F85)</f>
+      <c r="F87" s="21">
+        <f>IF(F3=0,"",F83-F86)</f>
         <v>9074</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A87" s="38" t="s">
-        <v>205</v>
-      </c>
-      <c r="B87" s="39">
-        <f>IF(B86&lt;=0,"N/A",ROUNDUP(B84/B86,0))</f>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A88" s="40" t="s">
+        <v>207</v>
+      </c>
+      <c r="B88" s="41">
+        <f>IF(B87&lt;=0,"N/A",ROUNDUP(B85/B87,0))</f>
         <v>193</v>
       </c>
-      <c r="C87" s="39">
-        <f>IF(C86&lt;=0,"N/A",ROUNDUP(C84/C86,0))</f>
+      <c r="C88" s="41">
+        <f>IF(C87&lt;=0,"N/A",ROUNDUP(C85/C87,0))</f>
         <v>162</v>
       </c>
-      <c r="D87" s="39">
-        <f>IF(D86&lt;=0,"N/A",ROUNDUP(D84/D86,0))</f>
+      <c r="D88" s="41">
+        <f>IF(D87&lt;=0,"N/A",ROUNDUP(D85/D87,0))</f>
         <v>153</v>
       </c>
-      <c r="E87" s="39">
-        <f>IF(E86&lt;=0,"N/A",ROUNDUP(E84/E86,0))</f>
+      <c r="E88" s="41">
+        <f>IF(E87&lt;=0,"N/A",ROUNDUP(E85/E87,0))</f>
         <v>148</v>
       </c>
-      <c r="F87" s="39">
-        <f>IF(F86&lt;=0,"N/A",ROUNDUP(F84/F86,0))</f>
+      <c r="F88" s="41">
+        <f>IF(F87&lt;=0,"N/A",ROUNDUP(F85/F87,0))</f>
         <v>144</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A89" s="24" t="s">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A90" s="24" t="s">
         <v>144</v>
       </c>
-      <c r="B89" s="24"/>
-      <c r="C89" s="24"/>
-      <c r="D89" s="24"/>
-      <c r="E89" s="24"/>
-      <c r="F89" s="24"/>
+      <c r="B90" s="24"/>
+      <c r="C90" s="24"/>
+      <c r="D90" s="24"/>
+      <c r="E90" s="24"/>
+      <c r="F90" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A89:F89"/>
+    <mergeCell ref="A90:F90"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>
@@ -4695,7 +4724,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -4719,40 +4748,40 @@
         <v>46</v>
       </c>
       <c r="C2" s="25" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D2" s="25" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="E2" s="25" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="F2" s="25" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G2" s="25" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H2" s="25" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="I2" s="25" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="J2" s="25" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="K2" s="25" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="L2" s="25" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="M2" s="25" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="N2" s="25" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -5628,7 +5657,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="13" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B26" s="21">
         <v>7000</v>
@@ -5736,7 +5765,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="13" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B29" s="21">
         <v>5000</v>
@@ -5844,7 +5873,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="13" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B32" s="21">
         <v>18000</v>
@@ -5889,7 +5918,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="13" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B33" s="21">
         <v>2500</v>
@@ -5934,7 +5963,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="13" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B34" s="21">
         <v>1500</v>
@@ -5979,7 +6008,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="13" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B35" s="21">
         <v>1500</v>
@@ -6087,7 +6116,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="13" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B38" s="21">
         <v>2083</v>
@@ -6132,7 +6161,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="13" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B39" s="21">
         <v>1250</v>
@@ -6177,7 +6206,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="13" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B40" s="21">
         <v>1667</v>
@@ -6222,7 +6251,7 @@
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" s="13" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B41" s="21">
         <v>8000</v>
@@ -6267,7 +6296,7 @@
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" s="13" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B42" s="21">
         <v>6000</v>
@@ -6419,7 +6448,7 @@
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" s="26" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B46" s="21">
         <v>13735</v>
@@ -6469,7 +6498,7 @@
     </row>
     <row r="48" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" s="12" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B48" s="12"/>
       <c r="C48" s="12"/>
@@ -6544,7 +6573,7 @@
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" s="26" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B50" s="30">
         <f>B10-B49</f>
@@ -6601,7 +6630,7 @@
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51" s="26" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B51" s="30">
         <f>0+B50</f>
@@ -6658,7 +6687,7 @@
     </row>
     <row r="53" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="12" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B53" s="12"/>
       <c r="C53" s="12"/>
@@ -6673,7 +6702,7 @@
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" s="13" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B55" s="30">
         <f>M51</f>
@@ -6682,7 +6711,7 @@
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" s="13" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B56" s="21">
         <f>MIN(B51:M51)</f>
@@ -6739,7 +6768,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -6749,147 +6778,147 @@
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="40" t="s">
-        <v>238</v>
-      </c>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="40"/>
-      <c r="G3" s="40"/>
-      <c r="H3" s="40"/>
+      <c r="B3" s="42" t="s">
+        <v>240</v>
+      </c>
+      <c r="C3" s="42"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="42"/>
+      <c r="F3" s="42"/>
+      <c r="G3" s="42"/>
+      <c r="H3" s="42"/>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="41" t="s">
-        <v>239</v>
-      </c>
-      <c r="D4" s="42" t="s">
-        <v>240</v>
-      </c>
-      <c r="F4" s="43" t="s">
+      <c r="B4" s="43" t="s">
         <v>241</v>
+      </c>
+      <c r="D4" s="44" t="s">
+        <v>242</v>
+      </c>
+      <c r="F4" s="45" t="s">
+        <v>243</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B6" s="12" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="E6" s="16" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="F6" s="16" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="G6" s="16" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="H6" s="16" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="13" t="s">
-        <v>249</v>
-      </c>
-      <c r="C7" s="44">
+        <v>251</v>
+      </c>
+      <c r="C7" s="46">
         <v>120</v>
       </c>
-      <c r="D7" s="44">
+      <c r="D7" s="46">
         <v>200</v>
       </c>
-      <c r="E7" s="44">
+      <c r="E7" s="46">
         <v>300</v>
       </c>
-      <c r="F7" s="44">
+      <c r="F7" s="46">
         <v>375</v>
       </c>
-      <c r="G7" s="44">
+      <c r="G7" s="46">
         <v>400</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="13" t="s">
-        <v>250</v>
-      </c>
-      <c r="C8" s="45">
+        <v>252</v>
+      </c>
+      <c r="C8" s="47">
         <v>1546000</v>
       </c>
-      <c r="D8" s="45">
+      <c r="D8" s="47">
         <v>2522800</v>
       </c>
-      <c r="E8" s="45">
+      <c r="E8" s="47">
         <v>3784600</v>
       </c>
-      <c r="F8" s="45">
+      <c r="F8" s="47">
         <v>4759125</v>
       </c>
-      <c r="G8" s="45">
+      <c r="G8" s="47">
         <v>5184400</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="13" t="s">
-        <v>251</v>
-      </c>
-      <c r="C9" s="45">
+        <v>253</v>
+      </c>
+      <c r="C9" s="47">
         <v>1026431.25</v>
       </c>
-      <c r="D9" s="45">
+      <c r="D9" s="47">
         <v>1231717.5</v>
       </c>
-      <c r="E9" s="45">
+      <c r="E9" s="47">
         <v>1231717.5</v>
       </c>
-      <c r="F9" s="45">
+      <c r="F9" s="47">
         <v>1231717.5</v>
       </c>
-      <c r="G9" s="45">
+      <c r="G9" s="47">
         <v>1231717.5</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="13" t="s">
-        <v>252</v>
-      </c>
-      <c r="C10" s="45">
+        <v>254</v>
+      </c>
+      <c r="C10" s="47">
         <v>654000</v>
       </c>
-      <c r="D10" s="45">
+      <c r="D10" s="47">
         <v>887860</v>
       </c>
-      <c r="E10" s="45">
+      <c r="E10" s="47">
         <v>1190521.4</v>
       </c>
-      <c r="F10" s="45">
+      <c r="F10" s="47">
         <v>1439089.0320000001</v>
       </c>
-      <c r="G10" s="45">
+      <c r="G10" s="47">
         <v>1554923.90296</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="13" t="s">
-        <v>188</v>
-      </c>
-      <c r="C11" s="45">
+        <v>190</v>
+      </c>
+      <c r="C11" s="47">
         <v>49824.605221179416</v>
       </c>
-      <c r="D11" s="45">
+      <c r="D11" s="47">
         <v>49824.605221179416</v>
       </c>
-      <c r="E11" s="45">
+      <c r="E11" s="47">
         <v>49824.605221179416</v>
       </c>
-      <c r="F11" s="45">
+      <c r="F11" s="47">
         <v>49824.605221179416</v>
       </c>
-      <c r="G11" s="45">
+      <c r="G11" s="47">
         <v>49824.605221179416</v>
       </c>
     </row>
@@ -6897,379 +6926,379 @@
       <c r="B12" s="26" t="s">
         <v>183</v>
       </c>
-      <c r="C12" s="46">
+      <c r="C12" s="48">
         <v>-184255.85522117943</v>
       </c>
-      <c r="D12" s="47">
+      <c r="D12" s="49">
         <v>353397.89477882057</v>
       </c>
-      <c r="E12" s="47">
+      <c r="E12" s="49">
         <v>1312536.4947788208</v>
       </c>
-      <c r="F12" s="47">
+      <c r="F12" s="49">
         <v>2038493.8627788206</v>
       </c>
-      <c r="G12" s="47">
+      <c r="G12" s="49">
         <v>2347933.9918188206</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="26" t="s">
-        <v>190</v>
-      </c>
-      <c r="C13" s="46">
+        <v>192</v>
+      </c>
+      <c r="C13" s="48">
         <v>-184255.85522117943</v>
       </c>
-      <c r="D13" s="47">
+      <c r="D13" s="49">
         <v>169142.03955764114</v>
       </c>
-      <c r="E13" s="47">
+      <c r="E13" s="49">
         <v>1481678.534336462</v>
       </c>
-      <c r="F13" s="47">
+      <c r="F13" s="49">
         <v>3520172.3971152827</v>
       </c>
-      <c r="G13" s="47">
+      <c r="G13" s="49">
         <v>5868106.388934104</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="26" t="s">
-        <v>253</v>
-      </c>
-      <c r="C14" s="48">
+        <v>255</v>
+      </c>
+      <c r="C14" s="50">
         <v>-0.11918231256221179</v>
       </c>
-      <c r="D14" s="49">
+      <c r="D14" s="51">
         <v>0.14008161359553692</v>
       </c>
-      <c r="E14" s="49">
+      <c r="E14" s="51">
         <v>0.34680983321323805</v>
       </c>
-      <c r="F14" s="49">
+      <c r="F14" s="51">
         <v>0.4283337510107048</v>
       </c>
-      <c r="G14" s="49">
+      <c r="G14" s="51">
         <v>0.4528844209202262</v>
       </c>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" s="26" t="s">
-        <v>254</v>
-      </c>
-      <c r="C15" s="50">
+        <v>256</v>
+      </c>
+      <c r="C15" s="52">
         <v>12883.333333333334</v>
       </c>
-      <c r="D15" s="50">
+      <c r="D15" s="52">
         <v>12614</v>
       </c>
-      <c r="E15" s="50">
+      <c r="E15" s="52">
         <v>12615.333333333334</v>
       </c>
-      <c r="F15" s="50">
+      <c r="F15" s="52">
         <v>12691</v>
       </c>
-      <c r="G15" s="50">
+      <c r="G15" s="52">
         <v>12961</v>
       </c>
-      <c r="H15" s="51" t="s">
-        <v>255</v>
+      <c r="H15" s="53" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B16" s="26" t="s">
-        <v>256</v>
-      </c>
-      <c r="C16" s="48">
+        <v>258</v>
+      </c>
+      <c r="C16" s="50">
         <v>0.6639270698576973</v>
       </c>
-      <c r="D16" s="49">
+      <c r="D16" s="51">
         <v>0.48823430315522437</v>
       </c>
-      <c r="E16" s="49">
+      <c r="E16" s="51">
         <v>0.3254551339639592</v>
       </c>
-      <c r="F16" s="49">
+      <c r="F16" s="51">
         <v>0.25881175636277676</v>
       </c>
-      <c r="G16" s="49">
+      <c r="G16" s="51">
         <v>0.23758149448345034</v>
       </c>
-      <c r="H16" s="51" t="s">
-        <v>257</v>
+      <c r="H16" s="53" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B17" s="26" t="s">
-        <v>258</v>
-      </c>
-      <c r="C17" s="49">
+        <v>260</v>
+      </c>
+      <c r="C17" s="51">
         <v>0.12690815006468306</v>
       </c>
-      <c r="D17" s="49">
+      <c r="D17" s="51">
         <v>0.10558030759473601</v>
       </c>
-      <c r="E17" s="49">
+      <c r="E17" s="51">
         <v>0.09437098240236748</v>
       </c>
-      <c r="F17" s="49">
+      <c r="F17" s="51">
         <v>0.09071556422661729</v>
       </c>
-      <c r="G17" s="49">
+      <c r="G17" s="51">
         <v>0.08997707948615076</v>
       </c>
-      <c r="H17" s="51" t="s">
-        <v>259</v>
+      <c r="H17" s="53" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" s="26" t="s">
-        <v>260</v>
-      </c>
-      <c r="C18" s="48">
+        <v>262</v>
+      </c>
+      <c r="C18" s="50">
         <v>-0.08695423673997413</v>
       </c>
-      <c r="D18" s="49">
+      <c r="D18" s="51">
         <v>0.15983133819565562</v>
       </c>
-      <c r="E18" s="49">
+      <c r="E18" s="51">
         <v>0.35997492469481585</v>
       </c>
-      <c r="F18" s="49">
+      <c r="F18" s="51">
         <v>0.4388030295484989</v>
       </c>
-      <c r="G18" s="49">
+      <c r="G18" s="51">
         <v>0.4624949072293804</v>
       </c>
-      <c r="H18" s="51" t="s">
-        <v>261</v>
+      <c r="H18" s="53" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B19" s="26" t="s">
-        <v>262</v>
-      </c>
-      <c r="C19" s="52">
-        <v>1</v>
-      </c>
-      <c r="D19" s="52"/>
-      <c r="E19" s="52"/>
-      <c r="F19" s="52"/>
-      <c r="G19" s="52"/>
-      <c r="H19" s="51" t="s">
-        <v>263</v>
+        <v>264</v>
+      </c>
+      <c r="C19" s="54">
+        <v>3</v>
+      </c>
+      <c r="D19" s="54"/>
+      <c r="E19" s="54"/>
+      <c r="F19" s="54"/>
+      <c r="G19" s="54"/>
+      <c r="H19" s="53" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="26" t="s">
-        <v>264</v>
-      </c>
-      <c r="C20" s="53">
+        <v>266</v>
+      </c>
+      <c r="C20" s="55">
         <v>-2.698089616630942</v>
       </c>
-      <c r="D20" s="54">
+      <c r="D20" s="56">
         <v>8.092838833544805</v>
       </c>
-      <c r="E20" s="54">
+      <c r="E20" s="56">
         <v>27.34313887590801</v>
       </c>
-      <c r="F20" s="54">
+      <c r="F20" s="56">
         <v>41.91339718056208</v>
       </c>
-      <c r="G20" s="54">
+      <c r="G20" s="56">
         <v>48.12398585791026</v>
       </c>
-      <c r="H20" s="51" t="s">
-        <v>265</v>
+      <c r="H20" s="53" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="26" t="s">
-        <v>266</v>
-      </c>
-      <c r="C21" s="55" t="s">
-        <v>244</v>
-      </c>
-      <c r="D21" s="55"/>
-      <c r="E21" s="55"/>
-      <c r="F21" s="55"/>
-      <c r="G21" s="55"/>
-      <c r="H21" s="51" t="s">
-        <v>243</v>
+        <v>268</v>
+      </c>
+      <c r="C21" s="57" t="s">
+        <v>246</v>
+      </c>
+      <c r="D21" s="57"/>
+      <c r="E21" s="57"/>
+      <c r="F21" s="57"/>
+      <c r="G21" s="57"/>
+      <c r="H21" s="53" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="26" t="s">
-        <v>267</v>
-      </c>
-      <c r="C22" s="56" t="s">
-        <v>268</v>
-      </c>
-      <c r="D22" s="56"/>
-      <c r="E22" s="56"/>
-      <c r="F22" s="56"/>
-      <c r="G22" s="56"/>
-      <c r="H22" s="51" t="s">
         <v>269</v>
+      </c>
+      <c r="C22" s="58" t="s">
+        <v>270</v>
+      </c>
+      <c r="D22" s="58"/>
+      <c r="E22" s="58"/>
+      <c r="F22" s="58"/>
+      <c r="G22" s="58"/>
+      <c r="H22" s="53" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B24" s="12" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E24" s="12"/>
       <c r="F24" s="12" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="G24" s="12"/>
       <c r="H24" s="12"/>
     </row>
     <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="57" t="s">
-        <v>274</v>
-      </c>
-      <c r="C25" s="58" t="s">
-        <v>275</v>
-      </c>
-      <c r="D25" s="59" t="s">
+      <c r="B25" s="59" t="s">
         <v>276</v>
       </c>
-      <c r="E25" s="59"/>
-      <c r="F25" s="60" t="s">
+      <c r="C25" s="36" t="s">
         <v>277</v>
       </c>
-      <c r="G25" s="60"/>
-      <c r="H25" s="60"/>
+      <c r="D25" s="60" t="s">
+        <v>278</v>
+      </c>
+      <c r="E25" s="60"/>
+      <c r="F25" s="61" t="s">
+        <v>279</v>
+      </c>
+      <c r="G25" s="61"/>
+      <c r="H25" s="61"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="57" t="s">
-        <v>278</v>
-      </c>
-      <c r="C26" s="61" t="s">
-        <v>279</v>
-      </c>
-      <c r="D26" s="59" t="s">
+      <c r="B26" s="59" t="s">
         <v>280</v>
       </c>
-      <c r="E26" s="59"/>
-      <c r="F26" s="60" t="s">
+      <c r="C26" s="62" t="s">
         <v>281</v>
       </c>
-      <c r="G26" s="60"/>
-      <c r="H26" s="60"/>
+      <c r="D26" s="60" t="s">
+        <v>282</v>
+      </c>
+      <c r="E26" s="60"/>
+      <c r="F26" s="61" t="s">
+        <v>283</v>
+      </c>
+      <c r="G26" s="61"/>
+      <c r="H26" s="61"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="57" t="s">
-        <v>282</v>
-      </c>
-      <c r="C27" s="58" t="s">
-        <v>275</v>
-      </c>
-      <c r="D27" s="59" t="s">
-        <v>283</v>
-      </c>
-      <c r="E27" s="59"/>
-      <c r="F27" s="60" t="s">
+      <c r="B27" s="59" t="s">
         <v>284</v>
       </c>
-      <c r="G27" s="60"/>
-      <c r="H27" s="60"/>
+      <c r="C27" s="36" t="s">
+        <v>277</v>
+      </c>
+      <c r="D27" s="60" t="s">
+        <v>285</v>
+      </c>
+      <c r="E27" s="60"/>
+      <c r="F27" s="61" t="s">
+        <v>286</v>
+      </c>
+      <c r="G27" s="61"/>
+      <c r="H27" s="61"/>
     </row>
     <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="57" t="s">
-        <v>285</v>
-      </c>
-      <c r="C28" s="58" t="s">
-        <v>275</v>
-      </c>
-      <c r="D28" s="59" t="s">
-        <v>286</v>
-      </c>
-      <c r="E28" s="59"/>
-      <c r="F28" s="60" t="s">
+      <c r="B28" s="59" t="s">
         <v>287</v>
       </c>
-      <c r="G28" s="60"/>
-      <c r="H28" s="60"/>
+      <c r="C28" s="36" t="s">
+        <v>277</v>
+      </c>
+      <c r="D28" s="60" t="s">
+        <v>288</v>
+      </c>
+      <c r="E28" s="60"/>
+      <c r="F28" s="61" t="s">
+        <v>289</v>
+      </c>
+      <c r="G28" s="61"/>
+      <c r="H28" s="61"/>
     </row>
     <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="57" t="s">
-        <v>288</v>
-      </c>
-      <c r="C29" s="58" t="s">
-        <v>275</v>
-      </c>
-      <c r="D29" s="59" t="s">
-        <v>289</v>
-      </c>
-      <c r="E29" s="59"/>
-      <c r="F29" s="60" t="s">
+      <c r="B29" s="59" t="s">
         <v>290</v>
       </c>
-      <c r="G29" s="60"/>
-      <c r="H29" s="60"/>
+      <c r="C29" s="36" t="s">
+        <v>277</v>
+      </c>
+      <c r="D29" s="60" t="s">
+        <v>291</v>
+      </c>
+      <c r="E29" s="60"/>
+      <c r="F29" s="61" t="s">
+        <v>292</v>
+      </c>
+      <c r="G29" s="61"/>
+      <c r="H29" s="61"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="57" t="s">
-        <v>291</v>
-      </c>
-      <c r="C30" s="58" t="s">
-        <v>275</v>
-      </c>
-      <c r="D30" s="59" t="s">
-        <v>292</v>
-      </c>
-      <c r="E30" s="59"/>
-      <c r="F30" s="60" t="s">
+      <c r="B30" s="59" t="s">
         <v>293</v>
       </c>
-      <c r="G30" s="60"/>
-      <c r="H30" s="60"/>
+      <c r="C30" s="36" t="s">
+        <v>277</v>
+      </c>
+      <c r="D30" s="60" t="s">
+        <v>294</v>
+      </c>
+      <c r="E30" s="60"/>
+      <c r="F30" s="61" t="s">
+        <v>295</v>
+      </c>
+      <c r="G30" s="61"/>
+      <c r="H30" s="61"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="57" t="s">
-        <v>294</v>
-      </c>
-      <c r="C31" s="58" t="s">
-        <v>275</v>
-      </c>
-      <c r="D31" s="59" t="s">
-        <v>295</v>
-      </c>
-      <c r="E31" s="59"/>
-      <c r="F31" s="60" t="s">
+      <c r="B31" s="59" t="s">
         <v>296</v>
       </c>
-      <c r="G31" s="60"/>
-      <c r="H31" s="60"/>
+      <c r="C31" s="36" t="s">
+        <v>277</v>
+      </c>
+      <c r="D31" s="60" t="s">
+        <v>297</v>
+      </c>
+      <c r="E31" s="60"/>
+      <c r="F31" s="61" t="s">
+        <v>298</v>
+      </c>
+      <c r="G31" s="61"/>
+      <c r="H31" s="61"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B33" s="57" t="s">
-        <v>297</v>
+      <c r="B33" s="59" t="s">
+        <v>299</v>
       </c>
       <c r="C33" s="26" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D33" s="26"/>
       <c r="E33" s="26"/>
       <c r="F33" s="26"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="62" t="s">
+      <c r="B35" s="63" t="s">
         <v>144</v>
       </c>
-      <c r="C35" s="62"/>
-      <c r="D35" s="62"/>
-      <c r="E35" s="62"/>
-      <c r="F35" s="62"/>
-      <c r="G35" s="62"/>
-      <c r="H35" s="62"/>
+      <c r="C35" s="63"/>
+      <c r="D35" s="63"/>
+      <c r="E35" s="63"/>
+      <c r="F35" s="63"/>
+      <c r="G35" s="63"/>
+      <c r="H35" s="63"/>
     </row>
   </sheetData>
   <mergeCells count="23">

--- a/artifacts/api-server/qa-output/Formula_Export_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Formula_Export_Charter_Public_Funding.xlsx
@@ -7408,10 +7408,10 @@
       <formula>C20&gt;=1.25</formula>
     </cfRule>
     <cfRule type="expression" dxfId="22" priority="2">
-      <formula>C20&gt;=1.0</formula>
+      <formula>C20&gt;=1</formula>
     </cfRule>
     <cfRule type="expression" dxfId="23" priority="3">
-      <formula>C20&lt;1.0</formula>
+      <formula>C20&lt;1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>

--- a/artifacts/api-server/qa-output/Formula_Export_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Formula_Export_Charter_Public_Funding.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="301">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -1226,7 +1226,9 @@
     <xf numFmtId="167" fontId="12" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -7116,13 +7118,26 @@
       <c r="B21" s="26" t="s">
         <v>268</v>
       </c>
-      <c r="C21" s="57" t="s">
-        <v>246</v>
-      </c>
-      <c r="D21" s="57"/>
-      <c r="E21" s="57"/>
-      <c r="F21" s="57"/>
-      <c r="G21" s="57"/>
+      <c r="C21" s="57" t="str">
+        <f>IF('5-Year Model'!B63&gt;=0,"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="D21" s="36" t="str">
+        <f>IF('5-Year Model'!C63&gt;=0,"✓ Break-even","")</f>
+        <v>✓ Break-even</v>
+      </c>
+      <c r="E21" s="57" t="str">
+        <f>IF('5-Year Model'!D63&gt;=0,"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="F21" s="57" t="str">
+        <f>IF('5-Year Model'!E63&gt;=0,"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="G21" s="57" t="str">
+        <f>IF('5-Year Model'!F63&gt;=0,"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
       <c r="H21" s="53" t="s">
         <v>245</v>
       </c>
@@ -7301,11 +7316,10 @@
       <c r="H35" s="63"/>
     </row>
   </sheetData>
-  <mergeCells count="23">
+  <mergeCells count="22">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
     <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C21:G21"/>
     <mergeCell ref="C22:G22"/>
     <mergeCell ref="D24:E24"/>
     <mergeCell ref="F24:H24"/>
@@ -7386,10 +7400,10 @@
       <formula>C17&lt;=0.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="16" priority="2">
-      <formula>C17&lt;=0.25</formula>
+      <formula>C17&lt;=0.22</formula>
     </cfRule>
     <cfRule type="expression" dxfId="17" priority="3">
-      <formula>C17&gt;0.25</formula>
+      <formula>C17&gt;0.22</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C18:G18">

--- a/artifacts/api-server/qa-output/Formula_Export_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Formula_Export_Charter_Public_Funding.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="300">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -836,13 +836,10 @@
     <t>Break-even Year</t>
   </si>
   <si>
-    <t>Cash Runway</t>
-  </si>
-  <si>
-    <t>0 months</t>
-  </si>
-  <si>
-    <t>60+ months</t>
+    <t>Cash Runway (Months)</t>
+  </si>
+  <si>
+    <t>≥ 24 months</t>
   </si>
   <si>
     <t>FINANCIAL HEALTH SIGNALS</t>
@@ -1049,7 +1046,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1084,6 +1081,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFCE4EC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF8E1"/>
       </patternFill>
     </fill>
   </fills>
@@ -1138,7 +1140,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1219,7 +1221,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="167" fontId="12" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1229,7 +1233,12 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="12" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -7083,10 +7092,18 @@
       <c r="C19" s="54">
         <v>3</v>
       </c>
-      <c r="D19" s="54"/>
-      <c r="E19" s="54"/>
-      <c r="F19" s="54"/>
-      <c r="G19" s="54"/>
+      <c r="D19" s="54">
+        <v>3</v>
+      </c>
+      <c r="E19" s="54">
+        <v>3</v>
+      </c>
+      <c r="F19" s="54">
+        <v>3</v>
+      </c>
+      <c r="G19" s="54">
+        <v>3</v>
+      </c>
       <c r="H19" s="53" t="s">
         <v>265</v>
       </c>
@@ -7123,19 +7140,19 @@
         <v>0</v>
       </c>
       <c r="D21" s="36" t="str">
-        <f>IF('5-Year Model'!C63&gt;=0,"✓ Break-even","")</f>
+        <f>IF(AND('5-Year Model'!C63&gt;=0,'5-Year Model'!B63&lt;0),"✓ Break-even","")</f>
         <v>✓ Break-even</v>
       </c>
       <c r="E21" s="57" t="str">
-        <f>IF('5-Year Model'!D63&gt;=0,"✓ Break-even","")</f>
+        <f>IF(AND('5-Year Model'!D63&gt;=0,'5-Year Model'!C63&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
       <c r="F21" s="57" t="str">
-        <f>IF('5-Year Model'!E63&gt;=0,"✓ Break-even","")</f>
+        <f>IF(AND('5-Year Model'!E63&gt;=0,'5-Year Model'!D63&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
       <c r="G21" s="57" t="str">
-        <f>IF('5-Year Model'!F63&gt;=0,"✓ Break-even","")</f>
+        <f>IF(AND('5-Year Model'!F63&gt;=0,'5-Year Model'!E63&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
       <c r="H21" s="53" t="s">
@@ -7146,181 +7163,187 @@
       <c r="B22" s="26" t="s">
         <v>269</v>
       </c>
-      <c r="C22" s="58" t="s">
+      <c r="C22" s="58">
+        <v>-1</v>
+      </c>
+      <c r="D22" s="58">
+        <v>1</v>
+      </c>
+      <c r="E22" s="58">
+        <v>7</v>
+      </c>
+      <c r="F22" s="59">
+        <v>16</v>
+      </c>
+      <c r="G22" s="54">
+        <v>25</v>
+      </c>
+      <c r="H22" s="53" t="s">
         <v>270</v>
-      </c>
-      <c r="D22" s="58"/>
-      <c r="E22" s="58"/>
-      <c r="F22" s="58"/>
-      <c r="G22" s="58"/>
-      <c r="H22" s="53" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B24" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="C24" s="12" t="s">
         <v>272</v>
       </c>
-      <c r="C24" s="12" t="s">
+      <c r="D24" s="12" t="s">
         <v>273</v>
-      </c>
-      <c r="D24" s="12" t="s">
-        <v>274</v>
       </c>
       <c r="E24" s="12"/>
       <c r="F24" s="12" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="G24" s="12"/>
       <c r="H24" s="12"/>
     </row>
     <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="59" t="s">
+      <c r="B25" s="60" t="s">
+        <v>275</v>
+      </c>
+      <c r="C25" s="36" t="s">
         <v>276</v>
       </c>
-      <c r="C25" s="36" t="s">
+      <c r="D25" s="61" t="s">
         <v>277</v>
       </c>
-      <c r="D25" s="60" t="s">
+      <c r="E25" s="61"/>
+      <c r="F25" s="62" t="s">
         <v>278</v>
       </c>
-      <c r="E25" s="60"/>
-      <c r="F25" s="61" t="s">
+      <c r="G25" s="62"/>
+      <c r="H25" s="62"/>
+    </row>
+    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="60" t="s">
         <v>279</v>
       </c>
-      <c r="G25" s="61"/>
-      <c r="H25" s="61"/>
-    </row>
-    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="59" t="s">
+      <c r="C26" s="63" t="s">
         <v>280</v>
       </c>
-      <c r="C26" s="62" t="s">
+      <c r="D26" s="61" t="s">
         <v>281</v>
       </c>
-      <c r="D26" s="60" t="s">
+      <c r="E26" s="61"/>
+      <c r="F26" s="62" t="s">
         <v>282</v>
       </c>
-      <c r="E26" s="60"/>
-      <c r="F26" s="61" t="s">
+      <c r="G26" s="62"/>
+      <c r="H26" s="62"/>
+    </row>
+    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="60" t="s">
         <v>283</v>
       </c>
-      <c r="G26" s="61"/>
-      <c r="H26" s="61"/>
-    </row>
-    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="59" t="s">
+      <c r="C27" s="36" t="s">
+        <v>276</v>
+      </c>
+      <c r="D27" s="61" t="s">
         <v>284</v>
       </c>
-      <c r="C27" s="36" t="s">
-        <v>277</v>
-      </c>
-      <c r="D27" s="60" t="s">
+      <c r="E27" s="61"/>
+      <c r="F27" s="62" t="s">
         <v>285</v>
       </c>
-      <c r="E27" s="60"/>
-      <c r="F27" s="61" t="s">
+      <c r="G27" s="62"/>
+      <c r="H27" s="62"/>
+    </row>
+    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B28" s="60" t="s">
         <v>286</v>
       </c>
-      <c r="G27" s="61"/>
-      <c r="H27" s="61"/>
-    </row>
-    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="59" t="s">
+      <c r="C28" s="36" t="s">
+        <v>276</v>
+      </c>
+      <c r="D28" s="61" t="s">
         <v>287</v>
       </c>
-      <c r="C28" s="36" t="s">
-        <v>277</v>
-      </c>
-      <c r="D28" s="60" t="s">
+      <c r="E28" s="61"/>
+      <c r="F28" s="62" t="s">
         <v>288</v>
       </c>
-      <c r="E28" s="60"/>
-      <c r="F28" s="61" t="s">
+      <c r="G28" s="62"/>
+      <c r="H28" s="62"/>
+    </row>
+    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="60" t="s">
         <v>289</v>
       </c>
-      <c r="G28" s="61"/>
-      <c r="H28" s="61"/>
-    </row>
-    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="59" t="s">
+      <c r="C29" s="36" t="s">
+        <v>276</v>
+      </c>
+      <c r="D29" s="61" t="s">
         <v>290</v>
       </c>
-      <c r="C29" s="36" t="s">
-        <v>277</v>
-      </c>
-      <c r="D29" s="60" t="s">
+      <c r="E29" s="61"/>
+      <c r="F29" s="62" t="s">
         <v>291</v>
       </c>
-      <c r="E29" s="60"/>
-      <c r="F29" s="61" t="s">
+      <c r="G29" s="62"/>
+      <c r="H29" s="62"/>
+    </row>
+    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B30" s="60" t="s">
         <v>292</v>
       </c>
-      <c r="G29" s="61"/>
-      <c r="H29" s="61"/>
-    </row>
-    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="59" t="s">
+      <c r="C30" s="36" t="s">
+        <v>276</v>
+      </c>
+      <c r="D30" s="61" t="s">
         <v>293</v>
       </c>
-      <c r="C30" s="36" t="s">
-        <v>277</v>
-      </c>
-      <c r="D30" s="60" t="s">
+      <c r="E30" s="61"/>
+      <c r="F30" s="62" t="s">
         <v>294</v>
       </c>
-      <c r="E30" s="60"/>
-      <c r="F30" s="61" t="s">
+      <c r="G30" s="62"/>
+      <c r="H30" s="62"/>
+    </row>
+    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B31" s="60" t="s">
         <v>295</v>
       </c>
-      <c r="G30" s="61"/>
-      <c r="H30" s="61"/>
-    </row>
-    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="59" t="s">
+      <c r="C31" s="36" t="s">
+        <v>276</v>
+      </c>
+      <c r="D31" s="61" t="s">
         <v>296</v>
       </c>
-      <c r="C31" s="36" t="s">
-        <v>277</v>
-      </c>
-      <c r="D31" s="60" t="s">
+      <c r="E31" s="61"/>
+      <c r="F31" s="62" t="s">
         <v>297</v>
       </c>
-      <c r="E31" s="60"/>
-      <c r="F31" s="61" t="s">
+      <c r="G31" s="62"/>
+      <c r="H31" s="62"/>
+    </row>
+    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B33" s="60" t="s">
         <v>298</v>
       </c>
-      <c r="G31" s="61"/>
-      <c r="H31" s="61"/>
-    </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B33" s="59" t="s">
+      <c r="C33" s="26" t="s">
         <v>299</v>
-      </c>
-      <c r="C33" s="26" t="s">
-        <v>300</v>
       </c>
       <c r="D33" s="26"/>
       <c r="E33" s="26"/>
       <c r="F33" s="26"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="63" t="s">
+      <c r="B35" s="64" t="s">
         <v>144</v>
       </c>
-      <c r="C35" s="63"/>
-      <c r="D35" s="63"/>
-      <c r="E35" s="63"/>
-      <c r="F35" s="63"/>
-      <c r="G35" s="63"/>
-      <c r="H35" s="63"/>
+      <c r="C35" s="64"/>
+      <c r="D35" s="64"/>
+      <c r="E35" s="64"/>
+      <c r="F35" s="64"/>
+      <c r="G35" s="64"/>
+      <c r="H35" s="64"/>
     </row>
   </sheetData>
-  <mergeCells count="22">
+  <mergeCells count="20">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C22:G22"/>
     <mergeCell ref="D24:E24"/>
     <mergeCell ref="F24:H24"/>
     <mergeCell ref="D25:E25"/>

--- a/artifacts/api-server/qa-output/Formula_Export_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Formula_Export_Charter_Public_Funding.xlsx
@@ -890,7 +890,7 @@
     <t>Facility Burden</t>
   </si>
   <si>
-    <t>Facility costs at 9% of revenue are well-managed and leave budget for programs.</t>
+    <t>Facility costs at 6% of revenue are well-managed and leave budget for programs.</t>
   </si>
   <si>
     <t>Watch for rent escalation clauses that could push this higher over time.</t>
@@ -1140,7 +1140,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1221,6 +1221,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="12" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="164" fontId="12" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -7043,20 +7046,20 @@
       <c r="B17" s="26" t="s">
         <v>260</v>
       </c>
-      <c r="C17" s="51">
-        <v>0.12690815006468306</v>
+      <c r="C17" s="54">
+        <v>0.18240620957309184</v>
       </c>
       <c r="D17" s="51">
-        <v>0.10558030759473601</v>
+        <v>0.1151339781195497</v>
       </c>
       <c r="E17" s="51">
-        <v>0.09437098240236748</v>
+        <v>0.07904835385509698</v>
       </c>
       <c r="F17" s="51">
-        <v>0.09071556422661729</v>
+        <v>0.06474930412628371</v>
       </c>
       <c r="G17" s="51">
-        <v>0.08997707948615076</v>
+        <v>0.06122075900007716</v>
       </c>
       <c r="H17" s="53" t="s">
         <v>261</v>
@@ -7089,19 +7092,19 @@
       <c r="B19" s="26" t="s">
         <v>264</v>
       </c>
-      <c r="C19" s="54">
+      <c r="C19" s="55">
         <v>3</v>
       </c>
-      <c r="D19" s="54">
+      <c r="D19" s="55">
         <v>3</v>
       </c>
-      <c r="E19" s="54">
+      <c r="E19" s="55">
         <v>3</v>
       </c>
-      <c r="F19" s="54">
+      <c r="F19" s="55">
         <v>3</v>
       </c>
-      <c r="G19" s="54">
+      <c r="G19" s="55">
         <v>3</v>
       </c>
       <c r="H19" s="53" t="s">
@@ -7112,19 +7115,19 @@
       <c r="B20" s="26" t="s">
         <v>266</v>
       </c>
-      <c r="C20" s="55">
+      <c r="C20" s="56">
         <v>-2.698089616630942</v>
       </c>
-      <c r="D20" s="56">
+      <c r="D20" s="57">
         <v>8.092838833544805</v>
       </c>
-      <c r="E20" s="56">
+      <c r="E20" s="57">
         <v>27.34313887590801</v>
       </c>
-      <c r="F20" s="56">
+      <c r="F20" s="57">
         <v>41.91339718056208</v>
       </c>
-      <c r="G20" s="56">
+      <c r="G20" s="57">
         <v>48.12398585791026</v>
       </c>
       <c r="H20" s="53" t="s">
@@ -7135,7 +7138,7 @@
       <c r="B21" s="26" t="s">
         <v>268</v>
       </c>
-      <c r="C21" s="57" t="str">
+      <c r="C21" s="58" t="str">
         <f>IF('5-Year Model'!B63&gt;=0,"✓ Break-even","")</f>
         <v>0</v>
       </c>
@@ -7143,15 +7146,15 @@
         <f>IF(AND('5-Year Model'!C63&gt;=0,'5-Year Model'!B63&lt;0),"✓ Break-even","")</f>
         <v>✓ Break-even</v>
       </c>
-      <c r="E21" s="57" t="str">
+      <c r="E21" s="58" t="str">
         <f>IF(AND('5-Year Model'!D63&gt;=0,'5-Year Model'!C63&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="F21" s="57" t="str">
+      <c r="F21" s="58" t="str">
         <f>IF(AND('5-Year Model'!E63&gt;=0,'5-Year Model'!D63&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="G21" s="57" t="str">
+      <c r="G21" s="58" t="str">
         <f>IF(AND('5-Year Model'!F63&gt;=0,'5-Year Model'!E63&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
@@ -7163,19 +7166,19 @@
       <c r="B22" s="26" t="s">
         <v>269</v>
       </c>
-      <c r="C22" s="58">
+      <c r="C22" s="59">
         <v>-1</v>
       </c>
-      <c r="D22" s="58">
+      <c r="D22" s="59">
         <v>1</v>
       </c>
-      <c r="E22" s="58">
+      <c r="E22" s="59">
         <v>7</v>
       </c>
-      <c r="F22" s="59">
+      <c r="F22" s="60">
         <v>16</v>
       </c>
-      <c r="G22" s="54">
+      <c r="G22" s="55">
         <v>25</v>
       </c>
       <c r="H22" s="53" t="s">
@@ -7200,126 +7203,126 @@
       <c r="H24" s="12"/>
     </row>
     <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="60" t="s">
+      <c r="B25" s="61" t="s">
         <v>275</v>
       </c>
       <c r="C25" s="36" t="s">
         <v>276</v>
       </c>
-      <c r="D25" s="61" t="s">
+      <c r="D25" s="62" t="s">
         <v>277</v>
       </c>
-      <c r="E25" s="61"/>
-      <c r="F25" s="62" t="s">
+      <c r="E25" s="62"/>
+      <c r="F25" s="63" t="s">
         <v>278</v>
       </c>
-      <c r="G25" s="62"/>
-      <c r="H25" s="62"/>
+      <c r="G25" s="63"/>
+      <c r="H25" s="63"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="60" t="s">
+      <c r="B26" s="61" t="s">
         <v>279</v>
       </c>
-      <c r="C26" s="63" t="s">
+      <c r="C26" s="64" t="s">
         <v>280</v>
       </c>
-      <c r="D26" s="61" t="s">
+      <c r="D26" s="62" t="s">
         <v>281</v>
       </c>
-      <c r="E26" s="61"/>
-      <c r="F26" s="62" t="s">
+      <c r="E26" s="62"/>
+      <c r="F26" s="63" t="s">
         <v>282</v>
       </c>
-      <c r="G26" s="62"/>
-      <c r="H26" s="62"/>
+      <c r="G26" s="63"/>
+      <c r="H26" s="63"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="60" t="s">
+      <c r="B27" s="61" t="s">
         <v>283</v>
       </c>
       <c r="C27" s="36" t="s">
         <v>276</v>
       </c>
-      <c r="D27" s="61" t="s">
+      <c r="D27" s="62" t="s">
         <v>284</v>
       </c>
-      <c r="E27" s="61"/>
-      <c r="F27" s="62" t="s">
+      <c r="E27" s="62"/>
+      <c r="F27" s="63" t="s">
         <v>285</v>
       </c>
-      <c r="G27" s="62"/>
-      <c r="H27" s="62"/>
+      <c r="G27" s="63"/>
+      <c r="H27" s="63"/>
     </row>
     <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="60" t="s">
+      <c r="B28" s="61" t="s">
         <v>286</v>
       </c>
       <c r="C28" s="36" t="s">
         <v>276</v>
       </c>
-      <c r="D28" s="61" t="s">
+      <c r="D28" s="62" t="s">
         <v>287</v>
       </c>
-      <c r="E28" s="61"/>
-      <c r="F28" s="62" t="s">
+      <c r="E28" s="62"/>
+      <c r="F28" s="63" t="s">
         <v>288</v>
       </c>
-      <c r="G28" s="62"/>
-      <c r="H28" s="62"/>
+      <c r="G28" s="63"/>
+      <c r="H28" s="63"/>
     </row>
     <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="60" t="s">
+      <c r="B29" s="61" t="s">
         <v>289</v>
       </c>
       <c r="C29" s="36" t="s">
         <v>276</v>
       </c>
-      <c r="D29" s="61" t="s">
+      <c r="D29" s="62" t="s">
         <v>290</v>
       </c>
-      <c r="E29" s="61"/>
-      <c r="F29" s="62" t="s">
+      <c r="E29" s="62"/>
+      <c r="F29" s="63" t="s">
         <v>291</v>
       </c>
-      <c r="G29" s="62"/>
-      <c r="H29" s="62"/>
+      <c r="G29" s="63"/>
+      <c r="H29" s="63"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="60" t="s">
+      <c r="B30" s="61" t="s">
         <v>292</v>
       </c>
       <c r="C30" s="36" t="s">
         <v>276</v>
       </c>
-      <c r="D30" s="61" t="s">
+      <c r="D30" s="62" t="s">
         <v>293</v>
       </c>
-      <c r="E30" s="61"/>
-      <c r="F30" s="62" t="s">
+      <c r="E30" s="62"/>
+      <c r="F30" s="63" t="s">
         <v>294</v>
       </c>
-      <c r="G30" s="62"/>
-      <c r="H30" s="62"/>
+      <c r="G30" s="63"/>
+      <c r="H30" s="63"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="60" t="s">
+      <c r="B31" s="61" t="s">
         <v>295</v>
       </c>
       <c r="C31" s="36" t="s">
         <v>276</v>
       </c>
-      <c r="D31" s="61" t="s">
+      <c r="D31" s="62" t="s">
         <v>296</v>
       </c>
-      <c r="E31" s="61"/>
-      <c r="F31" s="62" t="s">
+      <c r="E31" s="62"/>
+      <c r="F31" s="63" t="s">
         <v>297</v>
       </c>
-      <c r="G31" s="62"/>
-      <c r="H31" s="62"/>
+      <c r="G31" s="63"/>
+      <c r="H31" s="63"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B33" s="60" t="s">
+      <c r="B33" s="61" t="s">
         <v>298</v>
       </c>
       <c r="C33" s="26" t="s">
@@ -7330,15 +7333,15 @@
       <c r="F33" s="26"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="64" t="s">
+      <c r="B35" s="65" t="s">
         <v>144</v>
       </c>
-      <c r="C35" s="64"/>
-      <c r="D35" s="64"/>
-      <c r="E35" s="64"/>
-      <c r="F35" s="64"/>
-      <c r="G35" s="64"/>
-      <c r="H35" s="64"/>
+      <c r="C35" s="65"/>
+      <c r="D35" s="65"/>
+      <c r="E35" s="65"/>
+      <c r="F35" s="65"/>
+      <c r="G35" s="65"/>
+      <c r="H35" s="65"/>
     </row>
   </sheetData>
   <mergeCells count="20">

--- a/artifacts/api-server/qa-output/Formula_Export_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Formula_Export_Charter_Public_Funding.xlsx
@@ -35,7 +35,7 @@
     <t>Civic Scholars Charter</t>
   </si>
   <si>
-    <t>Generated March 26, 2026 · nonprofit_501c3</t>
+    <t>Generated March 27, 2026 · nonprofit_501c3</t>
   </si>
   <si>
     <t>Cell Color Legend</t>
@@ -749,7 +749,7 @@
     <t>Civic Scholars Charter — Financial Health Dashboard</t>
   </si>
   <si>
-    <t>Generated March 26, 2026</t>
+    <t>Generated March 27, 2026</t>
   </si>
   <si>
     <t>● Green = healthy</t>

--- a/artifacts/api-server/qa-output/Formula_Export_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Formula_Export_Charter_Public_Funding.xlsx
@@ -308,7 +308,7 @@
     <t>Dean of Students</t>
   </si>
   <si>
-    <t>Core Teachers</t>
+    <t>Core Teachers [1:22]</t>
   </si>
   <si>
     <t>Instructional</t>
@@ -485,7 +485,7 @@
     <t>Dean of Students (School Leadership)</t>
   </si>
   <si>
-    <t>Core Teachers (Instructional)</t>
+    <t>Core Teachers [1:22] (Instructional)</t>
   </si>
   <si>
     <t>Special Education Teacher (Instructional)</t>
@@ -3374,19 +3374,19 @@
         <v>152</v>
       </c>
       <c r="B18" s="21">
-        <v>352690</v>
+        <v>323299</v>
       </c>
       <c r="C18" s="21">
-        <v>423228</v>
+        <v>670111</v>
       </c>
       <c r="D18" s="21">
-        <v>423228</v>
+        <v>987532</v>
       </c>
       <c r="E18" s="21">
-        <v>423228</v>
+        <v>1234415</v>
       </c>
       <c r="F18" s="21">
-        <v>423228</v>
+        <v>1304953</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -3495,23 +3495,23 @@
       </c>
       <c r="B24" s="28">
         <f>SUM(B15:B23)</f>
-        <v>1026431</v>
+        <v>997040</v>
       </c>
       <c r="C24" s="28">
         <f>SUM(C15:C23)</f>
-        <v>1231718</v>
+        <v>1478601</v>
       </c>
       <c r="D24" s="28">
         <f>SUM(D15:D23)</f>
-        <v>1231718</v>
+        <v>1796022</v>
       </c>
       <c r="E24" s="28">
         <f>SUM(E15:E23)</f>
-        <v>1231718</v>
+        <v>2042905</v>
       </c>
       <c r="F24" s="28">
         <f>SUM(F15:F23)</f>
-        <v>1231718</v>
+        <v>2113443</v>
       </c>
     </row>
     <row r="26" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4025,23 +4025,23 @@
       </c>
       <c r="B56" s="21">
         <f>B24</f>
-        <v>1026431</v>
+        <v>997040</v>
       </c>
       <c r="C56" s="21">
         <f>C24</f>
-        <v>1231718</v>
+        <v>1478601</v>
       </c>
       <c r="D56" s="21">
         <f>D24</f>
-        <v>1231718</v>
+        <v>1796022</v>
       </c>
       <c r="E56" s="21">
         <f>E24</f>
-        <v>1231718</v>
+        <v>2042905</v>
       </c>
       <c r="F56" s="21">
         <f>F24</f>
-        <v>1231718</v>
+        <v>2113443</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -4100,23 +4100,23 @@
       </c>
       <c r="B59" s="30">
         <f>B56+B57+B58</f>
-        <v>1736256</v>
+        <v>1706865</v>
       </c>
       <c r="C59" s="30">
         <f>C56+C57+C58</f>
-        <v>2209403</v>
+        <v>2456286</v>
       </c>
       <c r="D59" s="30">
         <f>D56+D57+D58</f>
-        <v>2512064</v>
+        <v>3076368</v>
       </c>
       <c r="E59" s="30">
         <f>E56+E57+E58</f>
-        <v>2745632</v>
+        <v>3556819</v>
       </c>
       <c r="F59" s="30">
         <f>F56+F57+F58</f>
-        <v>2856467</v>
+        <v>3738192</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.25">
@@ -4130,23 +4130,23 @@
       </c>
       <c r="B61" s="32">
         <f>B55-B59</f>
-        <v>-447923</v>
+        <v>-418532</v>
       </c>
       <c r="C61" s="33">
         <f>C55-C59</f>
-        <v>313397</v>
+        <v>66514</v>
       </c>
       <c r="D61" s="33">
         <f>D55-D59</f>
-        <v>1272536</v>
+        <v>708232</v>
       </c>
       <c r="E61" s="33">
         <f>E55-E59</f>
-        <v>2013493</v>
+        <v>1202306</v>
       </c>
       <c r="F61" s="33">
         <f>F55-F59</f>
-        <v>2327933</v>
+        <v>1446208</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -4155,23 +4155,23 @@
       </c>
       <c r="B62" s="34">
         <f>IF(B55=0,"",B61/B55)</f>
-        <v>-0.35</v>
+        <v>-0.32</v>
       </c>
       <c r="C62" s="34">
         <f>IF(C55=0,"",C61/C55)</f>
-        <v>0.12</v>
+        <v>0.03</v>
       </c>
       <c r="D62" s="34">
         <f>IF(D55=0,"",D61/D55)</f>
-        <v>0.34</v>
+        <v>0.19</v>
       </c>
       <c r="E62" s="34">
         <f>IF(E55=0,"",E61/E55)</f>
-        <v>0.42</v>
+        <v>0.25</v>
       </c>
       <c r="F62" s="34">
         <f>IF(F55=0,"",F61/F55)</f>
-        <v>0.45</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
@@ -4180,23 +4180,23 @@
       </c>
       <c r="B63" s="21">
         <f>B61</f>
-        <v>-447923</v>
+        <v>-418532</v>
       </c>
       <c r="C63" s="21">
         <f>B63+C61</f>
-        <v>-134526</v>
+        <v>-352018</v>
       </c>
       <c r="D63" s="21">
         <f>C63+D61</f>
-        <v>1138010</v>
+        <v>356214</v>
       </c>
       <c r="E63" s="21">
         <f>D63+E61</f>
-        <v>3151503</v>
+        <v>1558520</v>
       </c>
       <c r="F63" s="21">
         <f>E63+F61</f>
-        <v>5479436</v>
+        <v>3004728</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
@@ -4235,23 +4235,23 @@
       </c>
       <c r="B67" s="30">
         <f>B55-B56-B57</f>
-        <v>-283098</v>
+        <v>-253707</v>
       </c>
       <c r="C67" s="30">
         <f>C55-C56-C57</f>
-        <v>403222</v>
+        <v>156339</v>
       </c>
       <c r="D67" s="30">
         <f>D55-D56-D57</f>
-        <v>1362361</v>
+        <v>798057</v>
       </c>
       <c r="E67" s="30">
         <f>E55-E56-E57</f>
-        <v>2088318</v>
+        <v>1277131</v>
       </c>
       <c r="F67" s="30">
         <f>F55-F56-F57</f>
-        <v>2397758</v>
+        <v>1516033</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
@@ -4285,23 +4285,23 @@
       </c>
       <c r="B69" s="37">
         <f>IF(B68=0,"N/A",B67/B68)</f>
-        <v>-1.72</v>
+        <v>-1.54</v>
       </c>
       <c r="C69" s="37">
         <f>IF(C68=0,"N/A",C67/C68)</f>
-        <v>4.49</v>
+        <v>1.74</v>
       </c>
       <c r="D69" s="37">
         <f>IF(D68=0,"N/A",D67/D68)</f>
-        <v>15.17</v>
+        <v>8.88</v>
       </c>
       <c r="E69" s="37">
         <f>IF(E68=0,"N/A",E67/E68)</f>
-        <v>27.91</v>
+        <v>17.07</v>
       </c>
       <c r="F69" s="37">
         <f>IF(F68=0,"N/A",F67/F68)</f>
-        <v>34.34</v>
+        <v>21.71</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
@@ -4314,19 +4314,19 @@
       </c>
       <c r="C70" s="21">
         <f>B71</f>
-        <v>-447923</v>
+        <v>-418532</v>
       </c>
       <c r="D70" s="21">
         <f>C71</f>
-        <v>-134526</v>
+        <v>-352018</v>
       </c>
       <c r="E70" s="21">
         <f>D71</f>
-        <v>1138010</v>
+        <v>356214</v>
       </c>
       <c r="F70" s="21">
         <f>E71</f>
-        <v>3151503</v>
+        <v>1558520</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
@@ -4335,23 +4335,23 @@
       </c>
       <c r="B71" s="30">
         <f>B70+B61</f>
-        <v>-447923</v>
+        <v>-418532</v>
       </c>
       <c r="C71" s="30">
         <f>C70+C61</f>
-        <v>-134526</v>
+        <v>-352018</v>
       </c>
       <c r="D71" s="30">
         <f>D70+D61</f>
-        <v>1138010</v>
+        <v>356214</v>
       </c>
       <c r="E71" s="30">
         <f>E70+E61</f>
-        <v>3151503</v>
+        <v>1558520</v>
       </c>
       <c r="F71" s="30">
         <f>F70+F61</f>
-        <v>5479436</v>
+        <v>3004728</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
@@ -4360,23 +4360,23 @@
       </c>
       <c r="B72" s="38">
         <f>IF(B59=0,"",B71/B59*365)</f>
-        <v>-94</v>
+        <v>-89</v>
       </c>
       <c r="C72" s="38">
         <f>IF(C59=0,"",C71/C59*365)</f>
-        <v>-22</v>
+        <v>-52</v>
       </c>
       <c r="D72" s="38">
         <f>IF(D59=0,"",D71/D59*365)</f>
-        <v>165</v>
+        <v>42</v>
       </c>
       <c r="E72" s="38">
         <f>IF(E59=0,"",E71/E59*365)</f>
-        <v>419</v>
+        <v>160</v>
       </c>
       <c r="F72" s="38">
         <f>IF(F59=0,"",F71/F59*365)</f>
-        <v>700</v>
+        <v>293</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -4385,23 +4385,23 @@
       </c>
       <c r="B73" s="39">
         <f>IF(B59=0,"",B71/(B59/12))</f>
-        <v>-3.1</v>
+        <v>-2.9</v>
       </c>
       <c r="C73" s="39">
         <f>IF(C59=0,"",C71/(C59/12))</f>
-        <v>-0.7</v>
+        <v>-1.7</v>
       </c>
       <c r="D73" s="39">
         <f>IF(D59=0,"",D71/(D59/12))</f>
-        <v>5.4</v>
+        <v>1.4</v>
       </c>
       <c r="E73" s="39">
         <f>IF(E59=0,"",E71/(E59/12))</f>
-        <v>13.8</v>
+        <v>5.3</v>
       </c>
       <c r="F73" s="39">
         <f>IF(F59=0,"",F71/(F59/12))</f>
-        <v>23</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
@@ -4528,7 +4528,7 @@
       </c>
       <c r="D80" s="13" t="str">
         <f>IF(D59=0,"N/A",IF(D71/(D59/12)&gt;=2,"PASS","FAIL"))</f>
-        <v>PASS</v>
+        <v>FAIL</v>
       </c>
       <c r="E80" s="13" t="str">
         <f>IF(E59=0,"N/A",IF(E71/(E59/12)&gt;=2,"PASS","FAIL"))</f>
@@ -4580,23 +4580,23 @@
       </c>
       <c r="B84" s="21">
         <f>IF(B3=0,"",B59/B3)</f>
-        <v>14469</v>
+        <v>14224</v>
       </c>
       <c r="C84" s="21">
         <f>IF(C3=0,"",C59/C3)</f>
-        <v>11047</v>
+        <v>12281</v>
       </c>
       <c r="D84" s="21">
         <f>IF(D3=0,"",D59/D3)</f>
-        <v>8374</v>
+        <v>10255</v>
       </c>
       <c r="E84" s="21">
         <f>IF(E3=0,"",E59/E3)</f>
-        <v>7322</v>
+        <v>9485</v>
       </c>
       <c r="F84" s="21">
         <f>IF(F3=0,"",F59/F3)</f>
-        <v>7141</v>
+        <v>9345</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
@@ -4605,23 +4605,23 @@
       </c>
       <c r="B85" s="21">
         <f>B56+B58</f>
-        <v>1191256</v>
+        <v>1161865</v>
       </c>
       <c r="C85" s="21">
         <f>C56+C58</f>
-        <v>1321543</v>
+        <v>1568426</v>
       </c>
       <c r="D85" s="21">
         <f>D56+D58</f>
-        <v>1321543</v>
+        <v>1885847</v>
       </c>
       <c r="E85" s="21">
         <f>E56+E58</f>
-        <v>1306543</v>
+        <v>2117730</v>
       </c>
       <c r="F85" s="21">
         <f>F56+F58</f>
-        <v>1301543</v>
+        <v>2183268</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
@@ -4680,23 +4680,23 @@
       </c>
       <c r="B88" s="41">
         <f>IF(B87&lt;=0,"N/A",ROUNDUP(B85/B87,0))</f>
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="C88" s="41">
         <f>IF(C87&lt;=0,"N/A",ROUNDUP(C85/C87,0))</f>
-        <v>162</v>
+        <v>192</v>
       </c>
       <c r="D88" s="41">
         <f>IF(D87&lt;=0,"N/A",ROUNDUP(D85/D87,0))</f>
-        <v>153</v>
+        <v>219</v>
       </c>
       <c r="E88" s="41">
         <f>IF(E87&lt;=0,"N/A",ROUNDUP(E85/E87,0))</f>
-        <v>148</v>
+        <v>240</v>
       </c>
       <c r="F88" s="41">
         <f>IF(F87&lt;=0,"N/A",ROUNDUP(F85/F87,0))</f>
-        <v>144</v>
+        <v>241</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
@@ -5306,34 +5306,34 @@
         <v>93</v>
       </c>
       <c r="B16" s="21">
-        <v>35269</v>
+        <v>32330</v>
       </c>
       <c r="C16" s="21">
-        <v>35269</v>
+        <v>32330</v>
       </c>
       <c r="D16" s="21">
-        <v>35269</v>
+        <v>32330</v>
       </c>
       <c r="E16" s="21">
-        <v>35269</v>
+        <v>32330</v>
       </c>
       <c r="F16" s="21">
-        <v>35269</v>
+        <v>32330</v>
       </c>
       <c r="G16" s="21">
-        <v>35269</v>
+        <v>32330</v>
       </c>
       <c r="H16" s="21">
-        <v>35269</v>
+        <v>32330</v>
       </c>
       <c r="I16" s="21">
-        <v>35269</v>
+        <v>32330</v>
       </c>
       <c r="J16" s="21">
-        <v>35269</v>
+        <v>32330</v>
       </c>
       <c r="K16" s="21">
-        <v>35269</v>
+        <v>32330</v>
       </c>
       <c r="L16" s="21">
         <v>0</v>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="N16" s="21">
         <f>SUM(B16:M16)</f>
-        <v>352690</v>
+        <v>323299</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
@@ -5577,43 +5577,43 @@
       </c>
       <c r="B22" s="28">
         <f>SUM(B13:B21)</f>
-        <v>102643</v>
+        <v>99704</v>
       </c>
       <c r="C22" s="28">
         <f>SUM(C13:C21)</f>
-        <v>102643</v>
+        <v>99704</v>
       </c>
       <c r="D22" s="28">
         <f>SUM(D13:D21)</f>
-        <v>102643</v>
+        <v>99704</v>
       </c>
       <c r="E22" s="28">
         <f>SUM(E13:E21)</f>
-        <v>102643</v>
+        <v>99704</v>
       </c>
       <c r="F22" s="28">
         <f>SUM(F13:F21)</f>
-        <v>102643</v>
+        <v>99704</v>
       </c>
       <c r="G22" s="28">
         <f>SUM(G13:G21)</f>
-        <v>102643</v>
+        <v>99704</v>
       </c>
       <c r="H22" s="28">
         <f>SUM(H13:H21)</f>
-        <v>102643</v>
+        <v>99704</v>
       </c>
       <c r="I22" s="28">
         <f>SUM(I13:I21)</f>
-        <v>102643</v>
+        <v>99704</v>
       </c>
       <c r="J22" s="28">
         <f>SUM(J13:J21)</f>
-        <v>102643</v>
+        <v>99704</v>
       </c>
       <c r="K22" s="28">
         <f>SUM(K13:K21)</f>
-        <v>102643</v>
+        <v>99704</v>
       </c>
       <c r="L22" s="28" t="str">
         <f>SUM(L13:L21)</f>
@@ -5625,7 +5625,7 @@
       </c>
       <c r="N22" s="28">
         <f>SUM(B22:M22)</f>
-        <v>1026431</v>
+        <v>997040</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
@@ -6534,43 +6534,43 @@
       </c>
       <c r="B49" s="30">
         <f>B22+B44+B46</f>
-        <v>170878</v>
+        <v>167939</v>
       </c>
       <c r="C49" s="30">
         <f>C22+C44+C46</f>
-        <v>170878</v>
+        <v>167939</v>
       </c>
       <c r="D49" s="30">
         <f>D22+D44+D46</f>
-        <v>170878</v>
+        <v>167939</v>
       </c>
       <c r="E49" s="30">
         <f>E22+E44+E46</f>
-        <v>170878</v>
+        <v>167939</v>
       </c>
       <c r="F49" s="30">
         <f>F22+F44+F46</f>
-        <v>170878</v>
+        <v>167939</v>
       </c>
       <c r="G49" s="30">
         <f>G22+G44+G46</f>
-        <v>170878</v>
+        <v>167939</v>
       </c>
       <c r="H49" s="30">
         <f>H22+H44+H46</f>
-        <v>170878</v>
+        <v>167939</v>
       </c>
       <c r="I49" s="30">
         <f>I22+I44+I46</f>
-        <v>170878</v>
+        <v>167939</v>
       </c>
       <c r="J49" s="30">
         <f>J22+J44+J46</f>
-        <v>170878</v>
+        <v>167939</v>
       </c>
       <c r="K49" s="30">
         <f>K22+K44+K46</f>
-        <v>170878</v>
+        <v>167939</v>
       </c>
       <c r="L49" s="30">
         <f>L22+L44+L46</f>
@@ -6582,7 +6582,7 @@
       </c>
       <c r="N49" s="30">
         <f>SUM(B49:M49)</f>
-        <v>1736250</v>
+        <v>1706860</v>
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
@@ -6591,43 +6591,43 @@
       </c>
       <c r="B50" s="30">
         <f>B10-B49</f>
-        <v>-16278</v>
+        <v>-13339</v>
       </c>
       <c r="C50" s="30">
         <f>C10-C49</f>
-        <v>-16278</v>
+        <v>-13339</v>
       </c>
       <c r="D50" s="30">
         <f>D10-D49</f>
-        <v>-16278</v>
+        <v>-13339</v>
       </c>
       <c r="E50" s="30">
         <f>E10-E49</f>
-        <v>-16278</v>
+        <v>-13339</v>
       </c>
       <c r="F50" s="30">
         <f>F10-F49</f>
-        <v>-16278</v>
+        <v>-13339</v>
       </c>
       <c r="G50" s="30">
         <f>G10-G49</f>
-        <v>-16278</v>
+        <v>-13339</v>
       </c>
       <c r="H50" s="30">
         <f>H10-H49</f>
-        <v>-16278</v>
+        <v>-13339</v>
       </c>
       <c r="I50" s="30">
         <f>I10-I49</f>
-        <v>-16278</v>
+        <v>-13339</v>
       </c>
       <c r="J50" s="30">
         <f>J10-J49</f>
-        <v>-16278</v>
+        <v>-13339</v>
       </c>
       <c r="K50" s="30">
         <f>K10-K49</f>
-        <v>-16278</v>
+        <v>-13339</v>
       </c>
       <c r="L50" s="30">
         <f>L10-L49</f>
@@ -6639,7 +6639,7 @@
       </c>
       <c r="N50" s="30">
         <f>SUM(B50:M50)</f>
-        <v>-190250</v>
+        <v>-160860</v>
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
@@ -6648,55 +6648,55 @@
       </c>
       <c r="B51" s="30">
         <f>0+B50</f>
-        <v>-16278</v>
+        <v>-13339</v>
       </c>
       <c r="C51" s="30">
         <f>B51+C50</f>
-        <v>-32556</v>
+        <v>-26678</v>
       </c>
       <c r="D51" s="30">
         <f>C51+D50</f>
-        <v>-48834</v>
+        <v>-40017</v>
       </c>
       <c r="E51" s="30">
         <f>D51+E50</f>
-        <v>-65112</v>
+        <v>-53356</v>
       </c>
       <c r="F51" s="30">
         <f>E51+F50</f>
-        <v>-81390</v>
+        <v>-66695</v>
       </c>
       <c r="G51" s="30">
         <f>F51+G50</f>
-        <v>-97668</v>
+        <v>-80034</v>
       </c>
       <c r="H51" s="30">
         <f>G51+H50</f>
-        <v>-113946</v>
+        <v>-93373</v>
       </c>
       <c r="I51" s="30">
         <f>H51+I50</f>
-        <v>-130224</v>
+        <v>-106712</v>
       </c>
       <c r="J51" s="30">
         <f>I51+J50</f>
-        <v>-146502</v>
+        <v>-120051</v>
       </c>
       <c r="K51" s="30">
         <f>J51+K50</f>
-        <v>-162780</v>
+        <v>-133390</v>
       </c>
       <c r="L51" s="30">
         <f>K51+L50</f>
-        <v>-176515</v>
+        <v>-147125</v>
       </c>
       <c r="M51" s="30">
         <f>L51+M50</f>
-        <v>-190250</v>
+        <v>-160860</v>
       </c>
       <c r="N51" s="30">
         <f>M51</f>
-        <v>-190250</v>
+        <v>-160860</v>
       </c>
     </row>
     <row r="53" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -6720,7 +6720,7 @@
       </c>
       <c r="B55" s="30">
         <f>M51</f>
-        <v>-190250</v>
+        <v>-160860</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
@@ -6729,7 +6729,7 @@
       </c>
       <c r="B56" s="21">
         <f>MIN(B51:M51)</f>
-        <v>-190250</v>
+        <v>-160860</v>
       </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.25">

--- a/artifacts/api-server/qa-output/Formula_Export_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Formula_Export_Charter_Public_Funding.xlsx
@@ -19,7 +19,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'5-Year Model'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Year 1 Pro Forma'!$A1:$N58</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Year 1 Pro Forma'!$1:$2</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'Financial Health'!$A1:$H35</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Financial Health'!$A1:$H36</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Financial Health'!$1:$2</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="301">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -840,6 +840,9 @@
   </si>
   <si>
     <t>≥ 24 months</t>
+  </si>
+  <si>
+    <t>≥ 90 days</t>
   </si>
   <si>
     <t>FINANCIAL HEALTH SIGNALS</t>
@@ -6770,7 +6773,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H35"/>
+  <dimension ref="B2:H36"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -7185,170 +7188,191 @@
         <v>270</v>
       </c>
     </row>
-    <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B24" s="12" t="s">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="26" t="s">
+        <v>193</v>
+      </c>
+      <c r="C23" s="59">
+        <v>0</v>
+      </c>
+      <c r="D23" s="59">
+        <v>28</v>
+      </c>
+      <c r="E23" s="55">
+        <v>219</v>
+      </c>
+      <c r="F23" s="55">
+        <v>472</v>
+      </c>
+      <c r="G23" s="55">
+        <v>755</v>
+      </c>
+      <c r="H23" s="53" t="s">
         <v>271</v>
       </c>
-      <c r="C24" s="12" t="s">
+    </row>
+    <row r="25" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="12" t="s">
         <v>272</v>
       </c>
-      <c r="D24" s="12" t="s">
+      <c r="C25" s="12" t="s">
         <v>273</v>
       </c>
-      <c r="E24" s="12"/>
-      <c r="F24" s="12" t="s">
+      <c r="D25" s="12" t="s">
         <v>274</v>
       </c>
-      <c r="G24" s="12"/>
-      <c r="H24" s="12"/>
-    </row>
-    <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="61" t="s">
+      <c r="E25" s="12"/>
+      <c r="F25" s="12" t="s">
         <v>275</v>
       </c>
-      <c r="C25" s="36" t="s">
-        <v>276</v>
-      </c>
-      <c r="D25" s="62" t="s">
-        <v>277</v>
-      </c>
-      <c r="E25" s="62"/>
-      <c r="F25" s="63" t="s">
-        <v>278</v>
-      </c>
-      <c r="G25" s="63"/>
-      <c r="H25" s="63"/>
+      <c r="G25" s="12"/>
+      <c r="H25" s="12"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B26" s="61" t="s">
-        <v>279</v>
-      </c>
-      <c r="C26" s="64" t="s">
-        <v>280</v>
+        <v>276</v>
+      </c>
+      <c r="C26" s="36" t="s">
+        <v>277</v>
       </c>
       <c r="D26" s="62" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="E26" s="62"/>
       <c r="F26" s="63" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="G26" s="63"/>
       <c r="H26" s="63"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B27" s="61" t="s">
-        <v>283</v>
-      </c>
-      <c r="C27" s="36" t="s">
-        <v>276</v>
+        <v>280</v>
+      </c>
+      <c r="C27" s="64" t="s">
+        <v>281</v>
       </c>
       <c r="D27" s="62" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="E27" s="62"/>
       <c r="F27" s="63" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G27" s="63"/>
       <c r="H27" s="63"/>
     </row>
     <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B28" s="61" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C28" s="36" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D28" s="62" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="E28" s="62"/>
       <c r="F28" s="63" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="G28" s="63"/>
       <c r="H28" s="63"/>
     </row>
     <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B29" s="61" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C29" s="36" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D29" s="62" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="E29" s="62"/>
       <c r="F29" s="63" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="G29" s="63"/>
       <c r="H29" s="63"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B30" s="61" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C30" s="36" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D30" s="62" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="E30" s="62"/>
       <c r="F30" s="63" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="G30" s="63"/>
       <c r="H30" s="63"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B31" s="61" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C31" s="36" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D31" s="62" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="E31" s="62"/>
       <c r="F31" s="63" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="G31" s="63"/>
       <c r="H31" s="63"/>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B33" s="61" t="s">
+    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B32" s="61" t="s">
+        <v>296</v>
+      </c>
+      <c r="C32" s="36" t="s">
+        <v>277</v>
+      </c>
+      <c r="D32" s="62" t="s">
+        <v>297</v>
+      </c>
+      <c r="E32" s="62"/>
+      <c r="F32" s="63" t="s">
         <v>298</v>
       </c>
-      <c r="C33" s="26" t="s">
+      <c r="G32" s="63"/>
+      <c r="H32" s="63"/>
+    </row>
+    <row r="34" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B34" s="61" t="s">
         <v>299</v>
       </c>
-      <c r="D33" s="26"/>
-      <c r="E33" s="26"/>
-      <c r="F33" s="26"/>
-    </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="65" t="s">
+      <c r="C34" s="26" t="s">
+        <v>300</v>
+      </c>
+      <c r="D34" s="26"/>
+      <c r="E34" s="26"/>
+      <c r="F34" s="26"/>
+    </row>
+    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B36" s="65" t="s">
         <v>144</v>
       </c>
-      <c r="C35" s="65"/>
-      <c r="D35" s="65"/>
-      <c r="E35" s="65"/>
-      <c r="F35" s="65"/>
-      <c r="G35" s="65"/>
-      <c r="H35" s="65"/>
+      <c r="C36" s="65"/>
+      <c r="D36" s="65"/>
+      <c r="E36" s="65"/>
+      <c r="F36" s="65"/>
+      <c r="G36" s="65"/>
+      <c r="H36" s="65"/>
     </row>
   </sheetData>
   <mergeCells count="20">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="F24:H24"/>
     <mergeCell ref="D25:E25"/>
     <mergeCell ref="F25:H25"/>
     <mergeCell ref="D26:E26"/>
@@ -7363,8 +7387,10 @@
     <mergeCell ref="F30:H30"/>
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="F31:H31"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="B35:H35"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="B36:H36"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">

--- a/artifacts/api-server/qa-output/Formula_Export_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Formula_Export_Charter_Public_Funding.xlsx
@@ -19,7 +19,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'5-Year Model'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Year 1 Pro Forma'!$A1:$N58</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Year 1 Pro Forma'!$1:$2</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'Financial Health'!$A1:$H36</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Financial Health'!$A1:$H40</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Financial Health'!$1:$2</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="306">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -801,6 +801,21 @@
   </si>
   <si>
     <t>≥ $10,000</t>
+  </si>
+  <si>
+    <t>Cost per Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Instructional / Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Facility / Student</t>
+  </si>
+  <si>
+    <t>≤ $2,000 / $2k–$3.5k / &gt; $3,500</t>
+  </si>
+  <si>
+    <t>Surplus per Student</t>
   </si>
   <si>
     <t>Payroll %</t>
@@ -1143,7 +1158,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1224,6 +1239,18 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="166" fontId="12" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -6773,7 +6800,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H36"/>
+  <dimension ref="B2:H40"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -7022,365 +7049,440 @@
         <v>257</v>
       </c>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="26" t="s">
         <v>258</v>
       </c>
-      <c r="C16" s="50">
-        <v>0.6639270698576973</v>
-      </c>
-      <c r="D16" s="51">
-        <v>0.48823430315522437</v>
-      </c>
-      <c r="E16" s="51">
-        <v>0.3254551339639592</v>
-      </c>
-      <c r="F16" s="51">
-        <v>0.25881175636277676</v>
-      </c>
-      <c r="G16" s="51">
-        <v>0.23758149448345034</v>
-      </c>
-      <c r="H16" s="53" t="s">
+      <c r="C16" s="54">
+        <v>14418.798793509828</v>
+      </c>
+      <c r="D16" s="54">
+        <v>10847.010526105896</v>
+      </c>
+      <c r="E16" s="54">
+        <v>8240.211684070597</v>
+      </c>
+      <c r="F16" s="54">
+        <v>7255.016365923145</v>
+      </c>
+      <c r="G16" s="54">
+        <v>7091.165020452949</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="13" t="s">
         <v>259</v>
       </c>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B17" s="26" t="s">
+      <c r="C17" s="47">
+        <v>700</v>
+      </c>
+      <c r="D17" s="47">
+        <v>721</v>
+      </c>
+      <c r="E17" s="47">
+        <v>743</v>
+      </c>
+      <c r="F17" s="47">
+        <v>765</v>
+      </c>
+      <c r="G17" s="47">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="13" t="s">
         <v>260</v>
       </c>
-      <c r="C17" s="54">
-        <v>0.18240620957309184</v>
-      </c>
-      <c r="D17" s="51">
-        <v>0.1151339781195497</v>
-      </c>
-      <c r="E17" s="51">
-        <v>0.07904835385509698</v>
-      </c>
-      <c r="F17" s="51">
-        <v>0.06474930412628371</v>
-      </c>
-      <c r="G17" s="51">
-        <v>0.06122075900007716</v>
-      </c>
-      <c r="H17" s="53" t="s">
+      <c r="C18" s="55">
+        <v>2350</v>
+      </c>
+      <c r="D18" s="52">
+        <v>1452.3</v>
+      </c>
+      <c r="E18" s="52">
+        <v>997.2213333333334</v>
+      </c>
+      <c r="F18" s="52">
+        <v>821.7334186666667</v>
+      </c>
+      <c r="G18" s="52">
+        <v>793.4822574000001</v>
+      </c>
+      <c r="H18" s="53" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="26" t="s">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B19" s="26" t="s">
         <v>262</v>
       </c>
-      <c r="C18" s="50">
-        <v>-0.08695423673997413</v>
-      </c>
-      <c r="D18" s="51">
-        <v>0.15983133819565562</v>
-      </c>
-      <c r="E18" s="51">
-        <v>0.35997492469481585</v>
-      </c>
-      <c r="F18" s="51">
-        <v>0.4388030295484989</v>
-      </c>
-      <c r="G18" s="51">
-        <v>0.4624949072293804</v>
-      </c>
-      <c r="H18" s="53" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B19" s="26" t="s">
-        <v>264</v>
-      </c>
-      <c r="C19" s="55">
-        <v>3</v>
-      </c>
-      <c r="D19" s="55">
-        <v>3</v>
-      </c>
-      <c r="E19" s="55">
-        <v>3</v>
-      </c>
-      <c r="F19" s="55">
-        <v>3</v>
-      </c>
-      <c r="G19" s="55">
-        <v>3</v>
-      </c>
-      <c r="H19" s="53" t="s">
-        <v>265</v>
+      <c r="C19" s="56">
+        <v>-1535.4654601764953</v>
+      </c>
+      <c r="D19" s="57">
+        <v>1766.989473894103</v>
+      </c>
+      <c r="E19" s="57">
+        <v>4375.121649262736</v>
+      </c>
+      <c r="F19" s="57">
+        <v>5435.983634076855</v>
+      </c>
+      <c r="G19" s="57">
+        <v>5869.834979547051</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="26" t="s">
-        <v>266</v>
-      </c>
-      <c r="C20" s="56">
-        <v>-2.698089616630942</v>
-      </c>
-      <c r="D20" s="57">
-        <v>8.092838833544805</v>
-      </c>
-      <c r="E20" s="57">
-        <v>27.34313887590801</v>
-      </c>
-      <c r="F20" s="57">
-        <v>41.91339718056208</v>
-      </c>
-      <c r="G20" s="57">
-        <v>48.12398585791026</v>
+        <v>263</v>
+      </c>
+      <c r="C20" s="50">
+        <v>0.6639270698576973</v>
+      </c>
+      <c r="D20" s="51">
+        <v>0.48823430315522437</v>
+      </c>
+      <c r="E20" s="51">
+        <v>0.3254551339639592</v>
+      </c>
+      <c r="F20" s="51">
+        <v>0.25881175636277676</v>
+      </c>
+      <c r="G20" s="51">
+        <v>0.23758149448345034</v>
       </c>
       <c r="H20" s="53" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="26" t="s">
+        <v>265</v>
+      </c>
+      <c r="C21" s="58">
+        <v>0.18240620957309184</v>
+      </c>
+      <c r="D21" s="51">
+        <v>0.1151339781195497</v>
+      </c>
+      <c r="E21" s="51">
+        <v>0.07904835385509698</v>
+      </c>
+      <c r="F21" s="51">
+        <v>0.06474930412628371</v>
+      </c>
+      <c r="G21" s="51">
+        <v>0.06122075900007716</v>
+      </c>
+      <c r="H21" s="53" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B22" s="26" t="s">
+        <v>267</v>
+      </c>
+      <c r="C22" s="50">
+        <v>-0.08695423673997413</v>
+      </c>
+      <c r="D22" s="51">
+        <v>0.15983133819565562</v>
+      </c>
+      <c r="E22" s="51">
+        <v>0.35997492469481585</v>
+      </c>
+      <c r="F22" s="51">
+        <v>0.4388030295484989</v>
+      </c>
+      <c r="G22" s="51">
+        <v>0.4624949072293804</v>
+      </c>
+      <c r="H22" s="53" t="s">
         <v>268</v>
       </c>
-      <c r="C21" s="58" t="str">
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="26" t="s">
+        <v>269</v>
+      </c>
+      <c r="C23" s="59">
+        <v>3</v>
+      </c>
+      <c r="D23" s="59">
+        <v>3</v>
+      </c>
+      <c r="E23" s="59">
+        <v>3</v>
+      </c>
+      <c r="F23" s="59">
+        <v>3</v>
+      </c>
+      <c r="G23" s="59">
+        <v>3</v>
+      </c>
+      <c r="H23" s="53" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="26" t="s">
+        <v>271</v>
+      </c>
+      <c r="C24" s="60">
+        <v>-2.698089616630942</v>
+      </c>
+      <c r="D24" s="61">
+        <v>8.092838833544805</v>
+      </c>
+      <c r="E24" s="61">
+        <v>27.34313887590801</v>
+      </c>
+      <c r="F24" s="61">
+        <v>41.91339718056208</v>
+      </c>
+      <c r="G24" s="61">
+        <v>48.12398585791026</v>
+      </c>
+      <c r="H24" s="53" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="26" t="s">
+        <v>273</v>
+      </c>
+      <c r="C25" s="62" t="str">
         <f>IF('5-Year Model'!B63&gt;=0,"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="D21" s="36" t="str">
+      <c r="D25" s="36" t="str">
         <f>IF(AND('5-Year Model'!C63&gt;=0,'5-Year Model'!B63&lt;0),"✓ Break-even","")</f>
         <v>✓ Break-even</v>
       </c>
-      <c r="E21" s="58" t="str">
+      <c r="E25" s="62" t="str">
         <f>IF(AND('5-Year Model'!D63&gt;=0,'5-Year Model'!C63&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="F21" s="58" t="str">
+      <c r="F25" s="62" t="str">
         <f>IF(AND('5-Year Model'!E63&gt;=0,'5-Year Model'!D63&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="G21" s="58" t="str">
+      <c r="G25" s="62" t="str">
         <f>IF(AND('5-Year Model'!F63&gt;=0,'5-Year Model'!E63&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="H21" s="53" t="s">
+      <c r="H25" s="53" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B22" s="26" t="s">
-        <v>269</v>
-      </c>
-      <c r="C22" s="59">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="26" t="s">
+        <v>274</v>
+      </c>
+      <c r="C26" s="63">
         <v>-1</v>
       </c>
-      <c r="D22" s="59">
+      <c r="D26" s="63">
         <v>1</v>
       </c>
-      <c r="E22" s="59">
+      <c r="E26" s="63">
         <v>7</v>
       </c>
-      <c r="F22" s="60">
+      <c r="F26" s="64">
         <v>16</v>
       </c>
-      <c r="G22" s="55">
+      <c r="G26" s="59">
         <v>25</v>
       </c>
-      <c r="H22" s="53" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B23" s="26" t="s">
+      <c r="H26" s="53" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="26" t="s">
         <v>193</v>
       </c>
-      <c r="C23" s="59">
-        <v>0</v>
-      </c>
-      <c r="D23" s="59">
+      <c r="C27" s="63">
+        <v>0</v>
+      </c>
+      <c r="D27" s="63">
         <v>28</v>
       </c>
-      <c r="E23" s="55">
+      <c r="E27" s="59">
         <v>219</v>
       </c>
-      <c r="F23" s="55">
+      <c r="F27" s="59">
         <v>472</v>
       </c>
-      <c r="G23" s="55">
+      <c r="G27" s="59">
         <v>755</v>
       </c>
-      <c r="H23" s="53" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="25" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="12" t="s">
-        <v>272</v>
-      </c>
-      <c r="C25" s="12" t="s">
-        <v>273</v>
-      </c>
-      <c r="D25" s="12" t="s">
-        <v>274</v>
-      </c>
-      <c r="E25" s="12"/>
-      <c r="F25" s="12" t="s">
-        <v>275</v>
-      </c>
-      <c r="G25" s="12"/>
-      <c r="H25" s="12"/>
-    </row>
-    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="61" t="s">
+      <c r="H27" s="53" t="s">
         <v>276</v>
       </c>
-      <c r="C26" s="36" t="s">
+    </row>
+    <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="12" t="s">
         <v>277</v>
       </c>
-      <c r="D26" s="62" t="s">
+      <c r="C29" s="12" t="s">
         <v>278</v>
       </c>
-      <c r="E26" s="62"/>
-      <c r="F26" s="63" t="s">
+      <c r="D29" s="12" t="s">
         <v>279</v>
       </c>
-      <c r="G26" s="63"/>
-      <c r="H26" s="63"/>
-    </row>
-    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="61" t="s">
+      <c r="E29" s="12"/>
+      <c r="F29" s="12" t="s">
         <v>280</v>
       </c>
-      <c r="C27" s="64" t="s">
+      <c r="G29" s="12"/>
+      <c r="H29" s="12"/>
+    </row>
+    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B30" s="65" t="s">
         <v>281</v>
       </c>
-      <c r="D27" s="62" t="s">
+      <c r="C30" s="36" t="s">
         <v>282</v>
       </c>
-      <c r="E27" s="62"/>
-      <c r="F27" s="63" t="s">
+      <c r="D30" s="66" t="s">
         <v>283</v>
       </c>
-      <c r="G27" s="63"/>
-      <c r="H27" s="63"/>
-    </row>
-    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="61" t="s">
+      <c r="E30" s="66"/>
+      <c r="F30" s="67" t="s">
         <v>284</v>
       </c>
-      <c r="C28" s="36" t="s">
-        <v>277</v>
-      </c>
-      <c r="D28" s="62" t="s">
+      <c r="G30" s="67"/>
+      <c r="H30" s="67"/>
+    </row>
+    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B31" s="65" t="s">
         <v>285</v>
       </c>
-      <c r="E28" s="62"/>
-      <c r="F28" s="63" t="s">
+      <c r="C31" s="68" t="s">
         <v>286</v>
       </c>
-      <c r="G28" s="63"/>
-      <c r="H28" s="63"/>
-    </row>
-    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="61" t="s">
+      <c r="D31" s="66" t="s">
         <v>287</v>
       </c>
-      <c r="C29" s="36" t="s">
-        <v>277</v>
-      </c>
-      <c r="D29" s="62" t="s">
+      <c r="E31" s="66"/>
+      <c r="F31" s="67" t="s">
         <v>288</v>
       </c>
-      <c r="E29" s="62"/>
-      <c r="F29" s="63" t="s">
+      <c r="G31" s="67"/>
+      <c r="H31" s="67"/>
+    </row>
+    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B32" s="65" t="s">
         <v>289</v>
       </c>
-      <c r="G29" s="63"/>
-      <c r="H29" s="63"/>
-    </row>
-    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="61" t="s">
+      <c r="C32" s="36" t="s">
+        <v>282</v>
+      </c>
+      <c r="D32" s="66" t="s">
         <v>290</v>
       </c>
-      <c r="C30" s="36" t="s">
-        <v>277</v>
-      </c>
-      <c r="D30" s="62" t="s">
+      <c r="E32" s="66"/>
+      <c r="F32" s="67" t="s">
         <v>291</v>
       </c>
-      <c r="E30" s="62"/>
-      <c r="F30" s="63" t="s">
+      <c r="G32" s="67"/>
+      <c r="H32" s="67"/>
+    </row>
+    <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B33" s="65" t="s">
         <v>292</v>
       </c>
-      <c r="G30" s="63"/>
-      <c r="H30" s="63"/>
-    </row>
-    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="61" t="s">
+      <c r="C33" s="36" t="s">
+        <v>282</v>
+      </c>
+      <c r="D33" s="66" t="s">
         <v>293</v>
       </c>
-      <c r="C31" s="36" t="s">
-        <v>277</v>
-      </c>
-      <c r="D31" s="62" t="s">
+      <c r="E33" s="66"/>
+      <c r="F33" s="67" t="s">
         <v>294</v>
       </c>
-      <c r="E31" s="62"/>
-      <c r="F31" s="63" t="s">
+      <c r="G33" s="67"/>
+      <c r="H33" s="67"/>
+    </row>
+    <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B34" s="65" t="s">
         <v>295</v>
       </c>
-      <c r="G31" s="63"/>
-      <c r="H31" s="63"/>
-    </row>
-    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B32" s="61" t="s">
+      <c r="C34" s="36" t="s">
+        <v>282</v>
+      </c>
+      <c r="D34" s="66" t="s">
         <v>296</v>
       </c>
-      <c r="C32" s="36" t="s">
-        <v>277</v>
-      </c>
-      <c r="D32" s="62" t="s">
+      <c r="E34" s="66"/>
+      <c r="F34" s="67" t="s">
         <v>297</v>
       </c>
-      <c r="E32" s="62"/>
-      <c r="F32" s="63" t="s">
+      <c r="G34" s="67"/>
+      <c r="H34" s="67"/>
+    </row>
+    <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B35" s="65" t="s">
         <v>298</v>
       </c>
-      <c r="G32" s="63"/>
-      <c r="H32" s="63"/>
-    </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B34" s="61" t="s">
+      <c r="C35" s="36" t="s">
+        <v>282</v>
+      </c>
+      <c r="D35" s="66" t="s">
         <v>299</v>
       </c>
-      <c r="C34" s="26" t="s">
+      <c r="E35" s="66"/>
+      <c r="F35" s="67" t="s">
         <v>300</v>
       </c>
-      <c r="D34" s="26"/>
-      <c r="E34" s="26"/>
-      <c r="F34" s="26"/>
-    </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="G35" s="67"/>
+      <c r="H35" s="67"/>
+    </row>
+    <row r="36" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B36" s="65" t="s">
+        <v>301</v>
+      </c>
+      <c r="C36" s="36" t="s">
+        <v>282</v>
+      </c>
+      <c r="D36" s="66" t="s">
+        <v>302</v>
+      </c>
+      <c r="E36" s="66"/>
+      <c r="F36" s="67" t="s">
+        <v>303</v>
+      </c>
+      <c r="G36" s="67"/>
+      <c r="H36" s="67"/>
+    </row>
+    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B38" s="65" t="s">
+        <v>304</v>
+      </c>
+      <c r="C38" s="26" t="s">
+        <v>305</v>
+      </c>
+      <c r="D38" s="26"/>
+      <c r="E38" s="26"/>
+      <c r="F38" s="26"/>
+    </row>
+    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B40" s="69" t="s">
         <v>144</v>
       </c>
-      <c r="C36" s="65"/>
-      <c r="D36" s="65"/>
-      <c r="E36" s="65"/>
-      <c r="F36" s="65"/>
-      <c r="G36" s="65"/>
-      <c r="H36" s="65"/>
+      <c r="C40" s="69"/>
+      <c r="D40" s="69"/>
+      <c r="E40" s="69"/>
+      <c r="F40" s="69"/>
+      <c r="G40" s="69"/>
+      <c r="H40" s="69"/>
     </row>
   </sheetData>
   <mergeCells count="20">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="F25:H25"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="F26:H26"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="F28:H28"/>
     <mergeCell ref="D29:E29"/>
     <mergeCell ref="F29:H29"/>
     <mergeCell ref="D30:E30"/>
@@ -7389,8 +7491,16 @@
     <mergeCell ref="F31:H31"/>
     <mergeCell ref="D32:E32"/>
     <mergeCell ref="F32:H32"/>
-    <mergeCell ref="C34:F34"/>
-    <mergeCell ref="B36:H36"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="C38:F38"/>
+    <mergeCell ref="B40:H40"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">
@@ -7436,48 +7546,48 @@
       <formula>C15&lt;7000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C16:G16">
+  <conditionalFormatting sqref="C20:G20">
     <cfRule type="expression" dxfId="12" priority="1">
-      <formula>C16&lt;=0.55</formula>
+      <formula>C20&lt;=0.55</formula>
     </cfRule>
     <cfRule type="expression" dxfId="13" priority="2">
-      <formula>C16&lt;=0.65</formula>
+      <formula>C20&lt;=0.65</formula>
     </cfRule>
     <cfRule type="expression" dxfId="14" priority="3">
-      <formula>C16&gt;0.65</formula>
+      <formula>C20&gt;0.65</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C17:G17">
+  <conditionalFormatting sqref="C21:G21">
     <cfRule type="expression" dxfId="15" priority="1">
-      <formula>C17&lt;=0.15</formula>
+      <formula>C21&lt;=0.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="16" priority="2">
-      <formula>C17&lt;=0.22</formula>
+      <formula>C21&lt;=0.22</formula>
     </cfRule>
     <cfRule type="expression" dxfId="17" priority="3">
-      <formula>C17&gt;0.22</formula>
+      <formula>C21&gt;0.22</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C18:G18">
+  <conditionalFormatting sqref="C22:G22">
     <cfRule type="expression" dxfId="18" priority="1">
-      <formula>C18&gt;=0.10</formula>
+      <formula>C22&gt;=0.10</formula>
     </cfRule>
     <cfRule type="expression" dxfId="19" priority="2">
-      <formula>C18&gt;=0</formula>
+      <formula>C22&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="20" priority="3">
-      <formula>C18&lt;0</formula>
+      <formula>C22&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C20:G20">
+  <conditionalFormatting sqref="C24:G24">
     <cfRule type="expression" dxfId="21" priority="1">
-      <formula>C20&gt;=1.25</formula>
+      <formula>C24&gt;=1.25</formula>
     </cfRule>
     <cfRule type="expression" dxfId="22" priority="2">
-      <formula>C20&gt;=1</formula>
+      <formula>C24&gt;=1</formula>
     </cfRule>
     <cfRule type="expression" dxfId="23" priority="3">
-      <formula>C20&lt;1</formula>
+      <formula>C24&lt;1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>

--- a/artifacts/api-server/qa-output/Formula_Export_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Formula_Export_Charter_Public_Funding.xlsx
@@ -19,7 +19,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'5-Year Model'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Year 1 Pro Forma'!$A1:$N58</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Year 1 Pro Forma'!$1:$2</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'Financial Health'!$A1:$H40</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Financial Health'!$A1:$H35</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Financial Health'!$1:$2</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="300">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -803,21 +803,6 @@
     <t>≥ $10,000</t>
   </si>
   <si>
-    <t>Cost per Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Instructional / Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Facility / Student</t>
-  </si>
-  <si>
-    <t>≤ $2,000 / $2k–$3.5k / &gt; $3,500</t>
-  </si>
-  <si>
-    <t>Surplus per Student</t>
-  </si>
-  <si>
     <t>Payroll %</t>
   </si>
   <si>
@@ -855,9 +840,6 @@
   </si>
   <si>
     <t>≥ 24 months</t>
-  </si>
-  <si>
-    <t>≥ 90 days</t>
   </si>
   <si>
     <t>FINANCIAL HEALTH SIGNALS</t>
@@ -1158,7 +1140,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1239,18 +1221,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="12" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="12" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="166" fontId="12" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -6800,7 +6770,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H40"/>
+  <dimension ref="B2:H35"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -7049,458 +7019,352 @@
         <v>257</v>
       </c>
     </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B16" s="26" t="s">
         <v>258</v>
       </c>
-      <c r="C16" s="54">
-        <v>14418.798793509828</v>
-      </c>
-      <c r="D16" s="54">
-        <v>10847.010526105896</v>
-      </c>
-      <c r="E16" s="54">
-        <v>8240.211684070597</v>
-      </c>
-      <c r="F16" s="54">
-        <v>7255.016365923145</v>
-      </c>
-      <c r="G16" s="54">
-        <v>7091.165020452949</v>
-      </c>
-    </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="13" t="s">
+      <c r="C16" s="50">
+        <v>0.6639270698576973</v>
+      </c>
+      <c r="D16" s="51">
+        <v>0.48823430315522437</v>
+      </c>
+      <c r="E16" s="51">
+        <v>0.3254551339639592</v>
+      </c>
+      <c r="F16" s="51">
+        <v>0.25881175636277676</v>
+      </c>
+      <c r="G16" s="51">
+        <v>0.23758149448345034</v>
+      </c>
+      <c r="H16" s="53" t="s">
         <v>259</v>
       </c>
-      <c r="C17" s="47">
-        <v>700</v>
-      </c>
-      <c r="D17" s="47">
-        <v>721</v>
-      </c>
-      <c r="E17" s="47">
-        <v>743</v>
-      </c>
-      <c r="F17" s="47">
-        <v>765</v>
-      </c>
-      <c r="G17" s="47">
-        <v>788</v>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B17" s="26" t="s">
+        <v>260</v>
+      </c>
+      <c r="C17" s="54">
+        <v>0.18240620957309184</v>
+      </c>
+      <c r="D17" s="51">
+        <v>0.1151339781195497</v>
+      </c>
+      <c r="E17" s="51">
+        <v>0.07904835385509698</v>
+      </c>
+      <c r="F17" s="51">
+        <v>0.06474930412628371</v>
+      </c>
+      <c r="G17" s="51">
+        <v>0.06122075900007716</v>
+      </c>
+      <c r="H17" s="53" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="13" t="s">
-        <v>260</v>
-      </c>
-      <c r="C18" s="55">
-        <v>2350</v>
-      </c>
-      <c r="D18" s="52">
-        <v>1452.3</v>
-      </c>
-      <c r="E18" s="52">
-        <v>997.2213333333334</v>
-      </c>
-      <c r="F18" s="52">
-        <v>821.7334186666667</v>
-      </c>
-      <c r="G18" s="52">
-        <v>793.4822574000001</v>
+      <c r="B18" s="26" t="s">
+        <v>262</v>
+      </c>
+      <c r="C18" s="50">
+        <v>-0.08695423673997413</v>
+      </c>
+      <c r="D18" s="51">
+        <v>0.15983133819565562</v>
+      </c>
+      <c r="E18" s="51">
+        <v>0.35997492469481585</v>
+      </c>
+      <c r="F18" s="51">
+        <v>0.4388030295484989</v>
+      </c>
+      <c r="G18" s="51">
+        <v>0.4624949072293804</v>
       </c>
       <c r="H18" s="53" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B19" s="26" t="s">
-        <v>262</v>
-      </c>
-      <c r="C19" s="56">
-        <v>-1535.4654601764953</v>
-      </c>
-      <c r="D19" s="57">
-        <v>1766.989473894103</v>
-      </c>
-      <c r="E19" s="57">
-        <v>4375.121649262736</v>
-      </c>
-      <c r="F19" s="57">
-        <v>5435.983634076855</v>
-      </c>
-      <c r="G19" s="57">
-        <v>5869.834979547051</v>
+        <v>264</v>
+      </c>
+      <c r="C19" s="55">
+        <v>3</v>
+      </c>
+      <c r="D19" s="55">
+        <v>3</v>
+      </c>
+      <c r="E19" s="55">
+        <v>3</v>
+      </c>
+      <c r="F19" s="55">
+        <v>3</v>
+      </c>
+      <c r="G19" s="55">
+        <v>3</v>
+      </c>
+      <c r="H19" s="53" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="26" t="s">
-        <v>263</v>
-      </c>
-      <c r="C20" s="50">
-        <v>0.6639270698576973</v>
-      </c>
-      <c r="D20" s="51">
-        <v>0.48823430315522437</v>
-      </c>
-      <c r="E20" s="51">
-        <v>0.3254551339639592</v>
-      </c>
-      <c r="F20" s="51">
-        <v>0.25881175636277676</v>
-      </c>
-      <c r="G20" s="51">
-        <v>0.23758149448345034</v>
+        <v>266</v>
+      </c>
+      <c r="C20" s="56">
+        <v>-2.698089616630942</v>
+      </c>
+      <c r="D20" s="57">
+        <v>8.092838833544805</v>
+      </c>
+      <c r="E20" s="57">
+        <v>27.34313887590801</v>
+      </c>
+      <c r="F20" s="57">
+        <v>41.91339718056208</v>
+      </c>
+      <c r="G20" s="57">
+        <v>48.12398585791026</v>
       </c>
       <c r="H20" s="53" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="26" t="s">
-        <v>265</v>
-      </c>
-      <c r="C21" s="58">
-        <v>0.18240620957309184</v>
-      </c>
-      <c r="D21" s="51">
-        <v>0.1151339781195497</v>
-      </c>
-      <c r="E21" s="51">
-        <v>0.07904835385509698</v>
-      </c>
-      <c r="F21" s="51">
-        <v>0.06474930412628371</v>
-      </c>
-      <c r="G21" s="51">
-        <v>0.06122075900007716</v>
+        <v>268</v>
+      </c>
+      <c r="C21" s="58" t="str">
+        <f>IF('5-Year Model'!B63&gt;=0,"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="D21" s="36" t="str">
+        <f>IF(AND('5-Year Model'!C63&gt;=0,'5-Year Model'!B63&lt;0),"✓ Break-even","")</f>
+        <v>✓ Break-even</v>
+      </c>
+      <c r="E21" s="58" t="str">
+        <f>IF(AND('5-Year Model'!D63&gt;=0,'5-Year Model'!C63&lt;0),"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="F21" s="58" t="str">
+        <f>IF(AND('5-Year Model'!E63&gt;=0,'5-Year Model'!D63&lt;0),"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="G21" s="58" t="str">
+        <f>IF(AND('5-Year Model'!F63&gt;=0,'5-Year Model'!E63&lt;0),"✓ Break-even","")</f>
+        <v>0</v>
       </c>
       <c r="H21" s="53" t="s">
-        <v>266</v>
+        <v>245</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="26" t="s">
-        <v>267</v>
-      </c>
-      <c r="C22" s="50">
-        <v>-0.08695423673997413</v>
-      </c>
-      <c r="D22" s="51">
-        <v>0.15983133819565562</v>
-      </c>
-      <c r="E22" s="51">
-        <v>0.35997492469481585</v>
-      </c>
-      <c r="F22" s="51">
-        <v>0.4388030295484989</v>
-      </c>
-      <c r="G22" s="51">
-        <v>0.4624949072293804</v>
+        <v>269</v>
+      </c>
+      <c r="C22" s="59">
+        <v>-1</v>
+      </c>
+      <c r="D22" s="59">
+        <v>1</v>
+      </c>
+      <c r="E22" s="59">
+        <v>7</v>
+      </c>
+      <c r="F22" s="60">
+        <v>16</v>
+      </c>
+      <c r="G22" s="55">
+        <v>25</v>
       </c>
       <c r="H22" s="53" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B23" s="26" t="s">
-        <v>269</v>
-      </c>
-      <c r="C23" s="59">
-        <v>3</v>
-      </c>
-      <c r="D23" s="59">
-        <v>3</v>
-      </c>
-      <c r="E23" s="59">
-        <v>3</v>
-      </c>
-      <c r="F23" s="59">
-        <v>3</v>
-      </c>
-      <c r="G23" s="59">
-        <v>3</v>
-      </c>
-      <c r="H23" s="53" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B24" s="26" t="s">
+    <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="12" t="s">
         <v>271</v>
       </c>
-      <c r="C24" s="60">
-        <v>-2.698089616630942</v>
-      </c>
-      <c r="D24" s="61">
-        <v>8.092838833544805</v>
-      </c>
-      <c r="E24" s="61">
-        <v>27.34313887590801</v>
-      </c>
-      <c r="F24" s="61">
-        <v>41.91339718056208</v>
-      </c>
-      <c r="G24" s="61">
-        <v>48.12398585791026</v>
-      </c>
-      <c r="H24" s="53" t="s">
+      <c r="C24" s="12" t="s">
         <v>272</v>
       </c>
-    </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="26" t="s">
+      <c r="D24" s="12" t="s">
         <v>273</v>
       </c>
-      <c r="C25" s="62" t="str">
-        <f>IF('5-Year Model'!B63&gt;=0,"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="D25" s="36" t="str">
-        <f>IF(AND('5-Year Model'!C63&gt;=0,'5-Year Model'!B63&lt;0),"✓ Break-even","")</f>
-        <v>✓ Break-even</v>
-      </c>
-      <c r="E25" s="62" t="str">
-        <f>IF(AND('5-Year Model'!D63&gt;=0,'5-Year Model'!C63&lt;0),"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="F25" s="62" t="str">
-        <f>IF(AND('5-Year Model'!E63&gt;=0,'5-Year Model'!D63&lt;0),"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="G25" s="62" t="str">
-        <f>IF(AND('5-Year Model'!F63&gt;=0,'5-Year Model'!E63&lt;0),"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="H25" s="53" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="26" t="s">
+      <c r="E24" s="12"/>
+      <c r="F24" s="12" t="s">
         <v>274</v>
       </c>
-      <c r="C26" s="63">
-        <v>-1</v>
-      </c>
-      <c r="D26" s="63">
-        <v>1</v>
-      </c>
-      <c r="E26" s="63">
-        <v>7</v>
-      </c>
-      <c r="F26" s="64">
-        <v>16</v>
-      </c>
-      <c r="G26" s="59">
-        <v>25</v>
-      </c>
-      <c r="H26" s="53" t="s">
+      <c r="G24" s="12"/>
+      <c r="H24" s="12"/>
+    </row>
+    <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="61" t="s">
         <v>275</v>
       </c>
-    </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="26" t="s">
-        <v>193</v>
-      </c>
-      <c r="C27" s="63">
-        <v>0</v>
-      </c>
-      <c r="D27" s="63">
-        <v>28</v>
-      </c>
-      <c r="E27" s="59">
-        <v>219</v>
-      </c>
-      <c r="F27" s="59">
-        <v>472</v>
-      </c>
-      <c r="G27" s="59">
-        <v>755</v>
-      </c>
-      <c r="H27" s="53" t="s">
+      <c r="C25" s="36" t="s">
         <v>276</v>
       </c>
-    </row>
-    <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="12" t="s">
+      <c r="D25" s="62" t="s">
         <v>277</v>
       </c>
-      <c r="C29" s="12" t="s">
+      <c r="E25" s="62"/>
+      <c r="F25" s="63" t="s">
         <v>278</v>
       </c>
-      <c r="D29" s="12" t="s">
+      <c r="G25" s="63"/>
+      <c r="H25" s="63"/>
+    </row>
+    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="61" t="s">
         <v>279</v>
       </c>
-      <c r="E29" s="12"/>
-      <c r="F29" s="12" t="s">
+      <c r="C26" s="64" t="s">
         <v>280</v>
       </c>
-      <c r="G29" s="12"/>
-      <c r="H29" s="12"/>
+      <c r="D26" s="62" t="s">
+        <v>281</v>
+      </c>
+      <c r="E26" s="62"/>
+      <c r="F26" s="63" t="s">
+        <v>282</v>
+      </c>
+      <c r="G26" s="63"/>
+      <c r="H26" s="63"/>
+    </row>
+    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="61" t="s">
+        <v>283</v>
+      </c>
+      <c r="C27" s="36" t="s">
+        <v>276</v>
+      </c>
+      <c r="D27" s="62" t="s">
+        <v>284</v>
+      </c>
+      <c r="E27" s="62"/>
+      <c r="F27" s="63" t="s">
+        <v>285</v>
+      </c>
+      <c r="G27" s="63"/>
+      <c r="H27" s="63"/>
+    </row>
+    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B28" s="61" t="s">
+        <v>286</v>
+      </c>
+      <c r="C28" s="36" t="s">
+        <v>276</v>
+      </c>
+      <c r="D28" s="62" t="s">
+        <v>287</v>
+      </c>
+      <c r="E28" s="62"/>
+      <c r="F28" s="63" t="s">
+        <v>288</v>
+      </c>
+      <c r="G28" s="63"/>
+      <c r="H28" s="63"/>
+    </row>
+    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="61" t="s">
+        <v>289</v>
+      </c>
+      <c r="C29" s="36" t="s">
+        <v>276</v>
+      </c>
+      <c r="D29" s="62" t="s">
+        <v>290</v>
+      </c>
+      <c r="E29" s="62"/>
+      <c r="F29" s="63" t="s">
+        <v>291</v>
+      </c>
+      <c r="G29" s="63"/>
+      <c r="H29" s="63"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="65" t="s">
-        <v>281</v>
+      <c r="B30" s="61" t="s">
+        <v>292</v>
       </c>
       <c r="C30" s="36" t="s">
-        <v>282</v>
-      </c>
-      <c r="D30" s="66" t="s">
-        <v>283</v>
-      </c>
-      <c r="E30" s="66"/>
-      <c r="F30" s="67" t="s">
-        <v>284</v>
-      </c>
-      <c r="G30" s="67"/>
-      <c r="H30" s="67"/>
+        <v>276</v>
+      </c>
+      <c r="D30" s="62" t="s">
+        <v>293</v>
+      </c>
+      <c r="E30" s="62"/>
+      <c r="F30" s="63" t="s">
+        <v>294</v>
+      </c>
+      <c r="G30" s="63"/>
+      <c r="H30" s="63"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="65" t="s">
-        <v>285</v>
-      </c>
-      <c r="C31" s="68" t="s">
-        <v>286</v>
-      </c>
-      <c r="D31" s="66" t="s">
-        <v>287</v>
-      </c>
-      <c r="E31" s="66"/>
-      <c r="F31" s="67" t="s">
-        <v>288</v>
-      </c>
-      <c r="G31" s="67"/>
-      <c r="H31" s="67"/>
-    </row>
-    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B32" s="65" t="s">
-        <v>289</v>
-      </c>
-      <c r="C32" s="36" t="s">
-        <v>282</v>
-      </c>
-      <c r="D32" s="66" t="s">
-        <v>290</v>
-      </c>
-      <c r="E32" s="66"/>
-      <c r="F32" s="67" t="s">
-        <v>291</v>
-      </c>
-      <c r="G32" s="67"/>
-      <c r="H32" s="67"/>
-    </row>
-    <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B33" s="65" t="s">
-        <v>292</v>
-      </c>
-      <c r="C33" s="36" t="s">
-        <v>282</v>
-      </c>
-      <c r="D33" s="66" t="s">
-        <v>293</v>
-      </c>
-      <c r="E33" s="66"/>
-      <c r="F33" s="67" t="s">
-        <v>294</v>
-      </c>
-      <c r="G33" s="67"/>
-      <c r="H33" s="67"/>
-    </row>
-    <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B34" s="65" t="s">
+      <c r="B31" s="61" t="s">
         <v>295</v>
       </c>
-      <c r="C34" s="36" t="s">
-        <v>282</v>
-      </c>
-      <c r="D34" s="66" t="s">
+      <c r="C31" s="36" t="s">
+        <v>276</v>
+      </c>
+      <c r="D31" s="62" t="s">
         <v>296</v>
       </c>
-      <c r="E34" s="66"/>
-      <c r="F34" s="67" t="s">
+      <c r="E31" s="62"/>
+      <c r="F31" s="63" t="s">
         <v>297</v>
       </c>
-      <c r="G34" s="67"/>
-      <c r="H34" s="67"/>
-    </row>
-    <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="G31" s="63"/>
+      <c r="H31" s="63"/>
+    </row>
+    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B33" s="61" t="s">
+        <v>298</v>
+      </c>
+      <c r="C33" s="26" t="s">
+        <v>299</v>
+      </c>
+      <c r="D33" s="26"/>
+      <c r="E33" s="26"/>
+      <c r="F33" s="26"/>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B35" s="65" t="s">
-        <v>298</v>
-      </c>
-      <c r="C35" s="36" t="s">
-        <v>282</v>
-      </c>
-      <c r="D35" s="66" t="s">
-        <v>299</v>
-      </c>
-      <c r="E35" s="66"/>
-      <c r="F35" s="67" t="s">
-        <v>300</v>
-      </c>
-      <c r="G35" s="67"/>
-      <c r="H35" s="67"/>
-    </row>
-    <row r="36" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B36" s="65" t="s">
-        <v>301</v>
-      </c>
-      <c r="C36" s="36" t="s">
-        <v>282</v>
-      </c>
-      <c r="D36" s="66" t="s">
-        <v>302</v>
-      </c>
-      <c r="E36" s="66"/>
-      <c r="F36" s="67" t="s">
-        <v>303</v>
-      </c>
-      <c r="G36" s="67"/>
-      <c r="H36" s="67"/>
-    </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B38" s="65" t="s">
-        <v>304</v>
-      </c>
-      <c r="C38" s="26" t="s">
-        <v>305</v>
-      </c>
-      <c r="D38" s="26"/>
-      <c r="E38" s="26"/>
-      <c r="F38" s="26"/>
-    </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B40" s="69" t="s">
         <v>144</v>
       </c>
-      <c r="C40" s="69"/>
-      <c r="D40" s="69"/>
-      <c r="E40" s="69"/>
-      <c r="F40" s="69"/>
-      <c r="G40" s="69"/>
-      <c r="H40" s="69"/>
+      <c r="C35" s="65"/>
+      <c r="D35" s="65"/>
+      <c r="E35" s="65"/>
+      <c r="F35" s="65"/>
+      <c r="G35" s="65"/>
+      <c r="H35" s="65"/>
     </row>
   </sheetData>
   <mergeCells count="20">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="F24:H24"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="F25:H25"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="F26:H26"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="F28:H28"/>
     <mergeCell ref="D29:E29"/>
     <mergeCell ref="F29:H29"/>
     <mergeCell ref="D30:E30"/>
     <mergeCell ref="F30:H30"/>
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="F31:H31"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="F32:H32"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="F33:H33"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="F34:H34"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="F36:H36"/>
-    <mergeCell ref="C38:F38"/>
-    <mergeCell ref="B40:H40"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="B35:H35"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">
@@ -7546,48 +7410,48 @@
       <formula>C15&lt;7000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C20:G20">
+  <conditionalFormatting sqref="C16:G16">
     <cfRule type="expression" dxfId="12" priority="1">
-      <formula>C20&lt;=0.55</formula>
+      <formula>C16&lt;=0.55</formula>
     </cfRule>
     <cfRule type="expression" dxfId="13" priority="2">
-      <formula>C20&lt;=0.65</formula>
+      <formula>C16&lt;=0.65</formula>
     </cfRule>
     <cfRule type="expression" dxfId="14" priority="3">
-      <formula>C20&gt;0.65</formula>
+      <formula>C16&gt;0.65</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C21:G21">
+  <conditionalFormatting sqref="C17:G17">
     <cfRule type="expression" dxfId="15" priority="1">
-      <formula>C21&lt;=0.15</formula>
+      <formula>C17&lt;=0.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="16" priority="2">
-      <formula>C21&lt;=0.22</formula>
+      <formula>C17&lt;=0.22</formula>
     </cfRule>
     <cfRule type="expression" dxfId="17" priority="3">
-      <formula>C21&gt;0.22</formula>
+      <formula>C17&gt;0.22</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C22:G22">
+  <conditionalFormatting sqref="C18:G18">
     <cfRule type="expression" dxfId="18" priority="1">
-      <formula>C22&gt;=0.10</formula>
+      <formula>C18&gt;=0.10</formula>
     </cfRule>
     <cfRule type="expression" dxfId="19" priority="2">
-      <formula>C22&gt;=0</formula>
+      <formula>C18&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="20" priority="3">
-      <formula>C22&lt;0</formula>
+      <formula>C18&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C24:G24">
+  <conditionalFormatting sqref="C20:G20">
     <cfRule type="expression" dxfId="21" priority="1">
-      <formula>C24&gt;=1.25</formula>
+      <formula>C20&gt;=1.25</formula>
     </cfRule>
     <cfRule type="expression" dxfId="22" priority="2">
-      <formula>C24&gt;=1</formula>
+      <formula>C20&gt;=1</formula>
     </cfRule>
     <cfRule type="expression" dxfId="23" priority="3">
-      <formula>C24&lt;1</formula>
+      <formula>C20&lt;1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>

--- a/artifacts/api-server/qa-output/Formula_Export_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Formula_Export_Charter_Public_Funding.xlsx
@@ -19,7 +19,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'5-Year Model'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Year 1 Pro Forma'!$A1:$N58</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Year 1 Pro Forma'!$1:$2</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'Financial Health'!$A1:$H35</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Financial Health'!$A1:$H40</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Financial Health'!$1:$2</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="306">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -803,6 +803,21 @@
     <t>≥ $10,000</t>
   </si>
   <si>
+    <t>Cost per Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Instructional / Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Facility / Student</t>
+  </si>
+  <si>
+    <t>≤ $2,000 / $2k–$3.5k / &gt; $3,500</t>
+  </si>
+  <si>
+    <t>Surplus per Student</t>
+  </si>
+  <si>
     <t>Payroll %</t>
   </si>
   <si>
@@ -840,6 +855,9 @@
   </si>
   <si>
     <t>≥ 24 months</t>
+  </si>
+  <si>
+    <t>≥ 90 days</t>
   </si>
   <si>
     <t>FINANCIAL HEALTH SIGNALS</t>
@@ -1140,7 +1158,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1221,6 +1239,18 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="166" fontId="12" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -6770,7 +6800,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H35"/>
+  <dimension ref="B2:H40"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -7019,352 +7049,458 @@
         <v>257</v>
       </c>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="26" t="s">
         <v>258</v>
       </c>
-      <c r="C16" s="50">
-        <v>0.6639270698576973</v>
-      </c>
-      <c r="D16" s="51">
-        <v>0.48823430315522437</v>
-      </c>
-      <c r="E16" s="51">
-        <v>0.3254551339639592</v>
-      </c>
-      <c r="F16" s="51">
-        <v>0.25881175636277676</v>
-      </c>
-      <c r="G16" s="51">
-        <v>0.23758149448345034</v>
-      </c>
-      <c r="H16" s="53" t="s">
+      <c r="C16" s="54">
+        <v>14418.798793509828</v>
+      </c>
+      <c r="D16" s="54">
+        <v>10847.010526105896</v>
+      </c>
+      <c r="E16" s="54">
+        <v>8240.211684070597</v>
+      </c>
+      <c r="F16" s="54">
+        <v>7255.016365923145</v>
+      </c>
+      <c r="G16" s="54">
+        <v>7091.165020452949</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="13" t="s">
         <v>259</v>
       </c>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B17" s="26" t="s">
+      <c r="C17" s="47">
+        <v>700</v>
+      </c>
+      <c r="D17" s="47">
+        <v>721</v>
+      </c>
+      <c r="E17" s="47">
+        <v>743</v>
+      </c>
+      <c r="F17" s="47">
+        <v>765</v>
+      </c>
+      <c r="G17" s="47">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="13" t="s">
         <v>260</v>
       </c>
-      <c r="C17" s="54">
-        <v>0.18240620957309184</v>
-      </c>
-      <c r="D17" s="51">
-        <v>0.1151339781195497</v>
-      </c>
-      <c r="E17" s="51">
-        <v>0.07904835385509698</v>
-      </c>
-      <c r="F17" s="51">
-        <v>0.06474930412628371</v>
-      </c>
-      <c r="G17" s="51">
-        <v>0.06122075900007716</v>
-      </c>
-      <c r="H17" s="53" t="s">
+      <c r="C18" s="55">
+        <v>2350</v>
+      </c>
+      <c r="D18" s="52">
+        <v>1452.3</v>
+      </c>
+      <c r="E18" s="52">
+        <v>997.2213333333334</v>
+      </c>
+      <c r="F18" s="52">
+        <v>821.7334186666667</v>
+      </c>
+      <c r="G18" s="52">
+        <v>793.4822574000001</v>
+      </c>
+      <c r="H18" s="53" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="26" t="s">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B19" s="26" t="s">
         <v>262</v>
       </c>
-      <c r="C18" s="50">
-        <v>-0.08695423673997413</v>
-      </c>
-      <c r="D18" s="51">
-        <v>0.15983133819565562</v>
-      </c>
-      <c r="E18" s="51">
-        <v>0.35997492469481585</v>
-      </c>
-      <c r="F18" s="51">
-        <v>0.4388030295484989</v>
-      </c>
-      <c r="G18" s="51">
-        <v>0.4624949072293804</v>
-      </c>
-      <c r="H18" s="53" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B19" s="26" t="s">
-        <v>264</v>
-      </c>
-      <c r="C19" s="55">
-        <v>3</v>
-      </c>
-      <c r="D19" s="55">
-        <v>3</v>
-      </c>
-      <c r="E19" s="55">
-        <v>3</v>
-      </c>
-      <c r="F19" s="55">
-        <v>3</v>
-      </c>
-      <c r="G19" s="55">
-        <v>3</v>
-      </c>
-      <c r="H19" s="53" t="s">
-        <v>265</v>
+      <c r="C19" s="56">
+        <v>-1535.4654601764953</v>
+      </c>
+      <c r="D19" s="57">
+        <v>1766.989473894103</v>
+      </c>
+      <c r="E19" s="57">
+        <v>4375.121649262736</v>
+      </c>
+      <c r="F19" s="57">
+        <v>5435.983634076855</v>
+      </c>
+      <c r="G19" s="57">
+        <v>5869.834979547051</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="26" t="s">
-        <v>266</v>
-      </c>
-      <c r="C20" s="56">
-        <v>-2.698089616630942</v>
-      </c>
-      <c r="D20" s="57">
-        <v>8.092838833544805</v>
-      </c>
-      <c r="E20" s="57">
-        <v>27.34313887590801</v>
-      </c>
-      <c r="F20" s="57">
-        <v>41.91339718056208</v>
-      </c>
-      <c r="G20" s="57">
-        <v>48.12398585791026</v>
+        <v>263</v>
+      </c>
+      <c r="C20" s="50">
+        <v>0.6639270698576973</v>
+      </c>
+      <c r="D20" s="51">
+        <v>0.48823430315522437</v>
+      </c>
+      <c r="E20" s="51">
+        <v>0.3254551339639592</v>
+      </c>
+      <c r="F20" s="51">
+        <v>0.25881175636277676</v>
+      </c>
+      <c r="G20" s="51">
+        <v>0.23758149448345034</v>
       </c>
       <c r="H20" s="53" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="26" t="s">
+        <v>265</v>
+      </c>
+      <c r="C21" s="58">
+        <v>0.18240620957309184</v>
+      </c>
+      <c r="D21" s="51">
+        <v>0.1151339781195497</v>
+      </c>
+      <c r="E21" s="51">
+        <v>0.07904835385509698</v>
+      </c>
+      <c r="F21" s="51">
+        <v>0.06474930412628371</v>
+      </c>
+      <c r="G21" s="51">
+        <v>0.06122075900007716</v>
+      </c>
+      <c r="H21" s="53" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B22" s="26" t="s">
+        <v>267</v>
+      </c>
+      <c r="C22" s="50">
+        <v>-0.08695423673997413</v>
+      </c>
+      <c r="D22" s="51">
+        <v>0.15983133819565562</v>
+      </c>
+      <c r="E22" s="51">
+        <v>0.35997492469481585</v>
+      </c>
+      <c r="F22" s="51">
+        <v>0.4388030295484989</v>
+      </c>
+      <c r="G22" s="51">
+        <v>0.4624949072293804</v>
+      </c>
+      <c r="H22" s="53" t="s">
         <v>268</v>
       </c>
-      <c r="C21" s="58" t="str">
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="26" t="s">
+        <v>269</v>
+      </c>
+      <c r="C23" s="59">
+        <v>3</v>
+      </c>
+      <c r="D23" s="59">
+        <v>3</v>
+      </c>
+      <c r="E23" s="59">
+        <v>3</v>
+      </c>
+      <c r="F23" s="59">
+        <v>3</v>
+      </c>
+      <c r="G23" s="59">
+        <v>3</v>
+      </c>
+      <c r="H23" s="53" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="26" t="s">
+        <v>271</v>
+      </c>
+      <c r="C24" s="60">
+        <v>-2.698089616630942</v>
+      </c>
+      <c r="D24" s="61">
+        <v>8.092838833544805</v>
+      </c>
+      <c r="E24" s="61">
+        <v>27.34313887590801</v>
+      </c>
+      <c r="F24" s="61">
+        <v>41.91339718056208</v>
+      </c>
+      <c r="G24" s="61">
+        <v>48.12398585791026</v>
+      </c>
+      <c r="H24" s="53" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="26" t="s">
+        <v>273</v>
+      </c>
+      <c r="C25" s="62" t="str">
         <f>IF('5-Year Model'!B63&gt;=0,"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="D21" s="36" t="str">
+      <c r="D25" s="36" t="str">
         <f>IF(AND('5-Year Model'!C63&gt;=0,'5-Year Model'!B63&lt;0),"✓ Break-even","")</f>
         <v>✓ Break-even</v>
       </c>
-      <c r="E21" s="58" t="str">
+      <c r="E25" s="62" t="str">
         <f>IF(AND('5-Year Model'!D63&gt;=0,'5-Year Model'!C63&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="F21" s="58" t="str">
+      <c r="F25" s="62" t="str">
         <f>IF(AND('5-Year Model'!E63&gt;=0,'5-Year Model'!D63&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="G21" s="58" t="str">
+      <c r="G25" s="62" t="str">
         <f>IF(AND('5-Year Model'!F63&gt;=0,'5-Year Model'!E63&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="H21" s="53" t="s">
+      <c r="H25" s="53" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B22" s="26" t="s">
-        <v>269</v>
-      </c>
-      <c r="C22" s="59">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="26" t="s">
+        <v>274</v>
+      </c>
+      <c r="C26" s="63">
         <v>-1</v>
       </c>
-      <c r="D22" s="59">
+      <c r="D26" s="63">
         <v>1</v>
       </c>
-      <c r="E22" s="59">
+      <c r="E26" s="63">
         <v>7</v>
       </c>
-      <c r="F22" s="60">
+      <c r="F26" s="64">
         <v>16</v>
       </c>
-      <c r="G22" s="55">
+      <c r="G26" s="59">
         <v>25</v>
       </c>
-      <c r="H22" s="53" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B24" s="12" t="s">
-        <v>271</v>
-      </c>
-      <c r="C24" s="12" t="s">
-        <v>272</v>
-      </c>
-      <c r="D24" s="12" t="s">
-        <v>273</v>
-      </c>
-      <c r="E24" s="12"/>
-      <c r="F24" s="12" t="s">
-        <v>274</v>
-      </c>
-      <c r="G24" s="12"/>
-      <c r="H24" s="12"/>
-    </row>
-    <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="61" t="s">
+      <c r="H26" s="53" t="s">
         <v>275</v>
       </c>
-      <c r="C25" s="36" t="s">
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="26" t="s">
+        <v>193</v>
+      </c>
+      <c r="C27" s="63">
+        <v>0</v>
+      </c>
+      <c r="D27" s="63">
+        <v>28</v>
+      </c>
+      <c r="E27" s="59">
+        <v>219</v>
+      </c>
+      <c r="F27" s="59">
+        <v>472</v>
+      </c>
+      <c r="G27" s="59">
+        <v>755</v>
+      </c>
+      <c r="H27" s="53" t="s">
         <v>276</v>
       </c>
-      <c r="D25" s="62" t="s">
+    </row>
+    <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="12" t="s">
         <v>277</v>
       </c>
-      <c r="E25" s="62"/>
-      <c r="F25" s="63" t="s">
+      <c r="C29" s="12" t="s">
         <v>278</v>
       </c>
-      <c r="G25" s="63"/>
-      <c r="H25" s="63"/>
-    </row>
-    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="61" t="s">
+      <c r="D29" s="12" t="s">
         <v>279</v>
       </c>
-      <c r="C26" s="64" t="s">
+      <c r="E29" s="12"/>
+      <c r="F29" s="12" t="s">
         <v>280</v>
       </c>
-      <c r="D26" s="62" t="s">
+      <c r="G29" s="12"/>
+      <c r="H29" s="12"/>
+    </row>
+    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B30" s="65" t="s">
         <v>281</v>
       </c>
-      <c r="E26" s="62"/>
-      <c r="F26" s="63" t="s">
+      <c r="C30" s="36" t="s">
         <v>282</v>
       </c>
-      <c r="G26" s="63"/>
-      <c r="H26" s="63"/>
-    </row>
-    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="61" t="s">
+      <c r="D30" s="66" t="s">
         <v>283</v>
       </c>
-      <c r="C27" s="36" t="s">
-        <v>276</v>
-      </c>
-      <c r="D27" s="62" t="s">
+      <c r="E30" s="66"/>
+      <c r="F30" s="67" t="s">
         <v>284</v>
       </c>
-      <c r="E27" s="62"/>
-      <c r="F27" s="63" t="s">
+      <c r="G30" s="67"/>
+      <c r="H30" s="67"/>
+    </row>
+    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B31" s="65" t="s">
         <v>285</v>
       </c>
-      <c r="G27" s="63"/>
-      <c r="H27" s="63"/>
-    </row>
-    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="61" t="s">
+      <c r="C31" s="68" t="s">
         <v>286</v>
       </c>
-      <c r="C28" s="36" t="s">
-        <v>276</v>
-      </c>
-      <c r="D28" s="62" t="s">
+      <c r="D31" s="66" t="s">
         <v>287</v>
       </c>
-      <c r="E28" s="62"/>
-      <c r="F28" s="63" t="s">
+      <c r="E31" s="66"/>
+      <c r="F31" s="67" t="s">
         <v>288</v>
       </c>
-      <c r="G28" s="63"/>
-      <c r="H28" s="63"/>
-    </row>
-    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="61" t="s">
+      <c r="G31" s="67"/>
+      <c r="H31" s="67"/>
+    </row>
+    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B32" s="65" t="s">
         <v>289</v>
       </c>
-      <c r="C29" s="36" t="s">
-        <v>276</v>
-      </c>
-      <c r="D29" s="62" t="s">
+      <c r="C32" s="36" t="s">
+        <v>282</v>
+      </c>
+      <c r="D32" s="66" t="s">
         <v>290</v>
       </c>
-      <c r="E29" s="62"/>
-      <c r="F29" s="63" t="s">
+      <c r="E32" s="66"/>
+      <c r="F32" s="67" t="s">
         <v>291</v>
       </c>
-      <c r="G29" s="63"/>
-      <c r="H29" s="63"/>
-    </row>
-    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="61" t="s">
+      <c r="G32" s="67"/>
+      <c r="H32" s="67"/>
+    </row>
+    <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B33" s="65" t="s">
         <v>292</v>
       </c>
-      <c r="C30" s="36" t="s">
-        <v>276</v>
-      </c>
-      <c r="D30" s="62" t="s">
+      <c r="C33" s="36" t="s">
+        <v>282</v>
+      </c>
+      <c r="D33" s="66" t="s">
         <v>293</v>
       </c>
-      <c r="E30" s="62"/>
-      <c r="F30" s="63" t="s">
+      <c r="E33" s="66"/>
+      <c r="F33" s="67" t="s">
         <v>294</v>
       </c>
-      <c r="G30" s="63"/>
-      <c r="H30" s="63"/>
-    </row>
-    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="61" t="s">
+      <c r="G33" s="67"/>
+      <c r="H33" s="67"/>
+    </row>
+    <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B34" s="65" t="s">
         <v>295</v>
       </c>
-      <c r="C31" s="36" t="s">
-        <v>276</v>
-      </c>
-      <c r="D31" s="62" t="s">
+      <c r="C34" s="36" t="s">
+        <v>282</v>
+      </c>
+      <c r="D34" s="66" t="s">
         <v>296</v>
       </c>
-      <c r="E31" s="62"/>
-      <c r="F31" s="63" t="s">
+      <c r="E34" s="66"/>
+      <c r="F34" s="67" t="s">
         <v>297</v>
       </c>
-      <c r="G31" s="63"/>
-      <c r="H31" s="63"/>
-    </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B33" s="61" t="s">
+      <c r="G34" s="67"/>
+      <c r="H34" s="67"/>
+    </row>
+    <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B35" s="65" t="s">
         <v>298</v>
       </c>
-      <c r="C33" s="26" t="s">
+      <c r="C35" s="36" t="s">
+        <v>282</v>
+      </c>
+      <c r="D35" s="66" t="s">
         <v>299</v>
       </c>
-      <c r="D33" s="26"/>
-      <c r="E33" s="26"/>
-      <c r="F33" s="26"/>
-    </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="65" t="s">
+      <c r="E35" s="66"/>
+      <c r="F35" s="67" t="s">
+        <v>300</v>
+      </c>
+      <c r="G35" s="67"/>
+      <c r="H35" s="67"/>
+    </row>
+    <row r="36" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B36" s="65" t="s">
+        <v>301</v>
+      </c>
+      <c r="C36" s="36" t="s">
+        <v>282</v>
+      </c>
+      <c r="D36" s="66" t="s">
+        <v>302</v>
+      </c>
+      <c r="E36" s="66"/>
+      <c r="F36" s="67" t="s">
+        <v>303</v>
+      </c>
+      <c r="G36" s="67"/>
+      <c r="H36" s="67"/>
+    </row>
+    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B38" s="65" t="s">
+        <v>304</v>
+      </c>
+      <c r="C38" s="26" t="s">
+        <v>305</v>
+      </c>
+      <c r="D38" s="26"/>
+      <c r="E38" s="26"/>
+      <c r="F38" s="26"/>
+    </row>
+    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B40" s="69" t="s">
         <v>144</v>
       </c>
-      <c r="C35" s="65"/>
-      <c r="D35" s="65"/>
-      <c r="E35" s="65"/>
-      <c r="F35" s="65"/>
-      <c r="G35" s="65"/>
-      <c r="H35" s="65"/>
+      <c r="C40" s="69"/>
+      <c r="D40" s="69"/>
+      <c r="E40" s="69"/>
+      <c r="F40" s="69"/>
+      <c r="G40" s="69"/>
+      <c r="H40" s="69"/>
     </row>
   </sheetData>
   <mergeCells count="20">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="F24:H24"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="F25:H25"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="F26:H26"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="F28:H28"/>
     <mergeCell ref="D29:E29"/>
     <mergeCell ref="F29:H29"/>
     <mergeCell ref="D30:E30"/>
     <mergeCell ref="F30:H30"/>
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="F31:H31"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="B35:H35"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="C38:F38"/>
+    <mergeCell ref="B40:H40"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">
@@ -7410,48 +7546,48 @@
       <formula>C15&lt;7000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C16:G16">
+  <conditionalFormatting sqref="C20:G20">
     <cfRule type="expression" dxfId="12" priority="1">
-      <formula>C16&lt;=0.55</formula>
+      <formula>C20&lt;=0.55</formula>
     </cfRule>
     <cfRule type="expression" dxfId="13" priority="2">
-      <formula>C16&lt;=0.65</formula>
+      <formula>C20&lt;=0.65</formula>
     </cfRule>
     <cfRule type="expression" dxfId="14" priority="3">
-      <formula>C16&gt;0.65</formula>
+      <formula>C20&gt;0.65</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C17:G17">
+  <conditionalFormatting sqref="C21:G21">
     <cfRule type="expression" dxfId="15" priority="1">
-      <formula>C17&lt;=0.15</formula>
+      <formula>C21&lt;=0.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="16" priority="2">
-      <formula>C17&lt;=0.22</formula>
+      <formula>C21&lt;=0.22</formula>
     </cfRule>
     <cfRule type="expression" dxfId="17" priority="3">
-      <formula>C17&gt;0.22</formula>
+      <formula>C21&gt;0.22</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C18:G18">
+  <conditionalFormatting sqref="C22:G22">
     <cfRule type="expression" dxfId="18" priority="1">
-      <formula>C18&gt;=0.10</formula>
+      <formula>C22&gt;=0.10</formula>
     </cfRule>
     <cfRule type="expression" dxfId="19" priority="2">
-      <formula>C18&gt;=0</formula>
+      <formula>C22&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="20" priority="3">
-      <formula>C18&lt;0</formula>
+      <formula>C22&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C20:G20">
+  <conditionalFormatting sqref="C24:G24">
     <cfRule type="expression" dxfId="21" priority="1">
-      <formula>C20&gt;=1.25</formula>
+      <formula>C24&gt;=1.25</formula>
     </cfRule>
     <cfRule type="expression" dxfId="22" priority="2">
-      <formula>C20&gt;=1</formula>
+      <formula>C24&gt;=1</formula>
     </cfRule>
     <cfRule type="expression" dxfId="23" priority="3">
-      <formula>C20&lt;1</formula>
+      <formula>C24&lt;1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>

--- a/artifacts/api-server/qa-output/Formula_Export_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Formula_Export_Charter_Public_Funding.xlsx
@@ -15,7 +15,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Instructions'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Assumptions'!$A1:$J70</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Assumptions'!$1:$3</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'5-Year Model'!$A1:$F90</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'5-Year Model'!$A1:$F91</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'5-Year Model'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Year 1 Pro Forma'!$A1:$N58</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Year 1 Pro Forma'!$1:$2</definedName>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="307">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -35,7 +35,7 @@
     <t>Civic Scholars Charter</t>
   </si>
   <si>
-    <t>Generated March 27, 2026 · nonprofit_501c3</t>
+    <t>Generated April 29, 2026 · nonprofit_501c3</t>
   </si>
   <si>
     <t>Cell Color Legend</t>
@@ -467,6 +467,9 @@
     <t>Civic Scholars Charter - 5-Year Financial Model</t>
   </si>
   <si>
+    <t>Projections prepared on an accrual basis. School currently keeps books on a undetermined basis.</t>
+  </si>
+  <si>
     <t>REVENUE</t>
   </si>
   <si>
@@ -620,7 +623,7 @@
     <t>COVENANT &amp; HEALTH CHECKS</t>
   </si>
   <si>
-    <t>DSCR ≥ 1.20x</t>
+    <t>DSCR ≥ 1.25x</t>
   </si>
   <si>
     <t>Positive Net Income</t>
@@ -749,7 +752,7 @@
     <t>Civic Scholars Charter — Financial Health Dashboard</t>
   </si>
   <si>
-    <t>Generated March 27, 2026</t>
+    <t>Generated April 29, 2026</t>
   </si>
   <si>
     <t>● Green = healthy</t>
@@ -890,7 +893,7 @@
     <t>○ Needs attention</t>
   </si>
   <si>
-    <t>Cash goes negative in month 0. The school will need outside funding to continue operating.</t>
+    <t>Cash goes negative in month 1. The school will need outside funding to continue operating.</t>
   </si>
   <si>
     <t>Secure a line of credit or bridge funding before operations begin.</t>
@@ -908,7 +911,7 @@
     <t>Facility Burden</t>
   </si>
   <si>
-    <t>Facility costs at 6% of revenue are well-managed and leave budget for programs.</t>
+    <t>Facility costs at 5% of revenue are well-managed and leave budget for programs.</t>
   </si>
   <si>
     <t>Watch for rent escalation clauses that could push this higher over time.</t>
@@ -917,7 +920,7 @@
     <t>Debt Affordability</t>
   </si>
   <si>
-    <t>DSCR of 48.12x provides comfortable coverage of debt payments with room to spare.</t>
+    <t>DSCR of 49.61x provides comfortable coverage of debt payments with room to spare.</t>
   </si>
   <si>
     <t>Maintain this ratio as you take on any additional debt.</t>
@@ -935,7 +938,7 @@
     <t>Reserve Strength</t>
   </si>
   <si>
-    <t>24.8 months of reserves by Year 5 — a strong buffer for unexpected costs.</t>
+    <t>27.2 months of reserves by Year 5 — a strong buffer for unexpected costs.</t>
   </si>
   <si>
     <t>Continue growing reserves toward 6 months for best-in-class financial health.</t>
@@ -958,7 +961,7 @@
     <numFmt numFmtId="167" formatCode="0.00x"/>
     <numFmt numFmtId="168" formatCode="0.0"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -1020,6 +1023,12 @@
       <i/>
       <color rgb="FF9CA3AF"/>
       <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="FF64748B"/>
+      <sz val="10"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -1158,7 +1167,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1190,96 +1199,91 @@
     <xf numFmtId="10" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="12" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="13" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="168" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="13" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="13" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="13" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="13" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="6" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="13" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="13" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="13" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="13" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="167" fontId="12" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="167" fontId="12" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="13" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="13" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="13" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3112,7 +3116,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F90"/>
+  <dimension ref="A1:F91"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
@@ -3129,254 +3133,244 @@
       <c r="E1" s="8"/>
       <c r="F1" s="8"/>
     </row>
-    <row r="2" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
+        <v>146</v>
+      </c>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+    </row>
+    <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="25" t="s">
+      <c r="B3" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="C2" s="25" t="s">
+      <c r="C3" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="D2" s="25" t="s">
+      <c r="D3" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="E2" s="25" t="s">
+      <c r="E3" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="F2" s="25" t="s">
+      <c r="F3" s="26" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="26" t="s">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="27" t="s">
         <v>58</v>
       </c>
-      <c r="B3" s="27">
+      <c r="B4" s="28">
         <f>Assumptions!B17</f>
         <v>120</v>
       </c>
-      <c r="C3" s="27">
+      <c r="C4" s="28">
         <f>Assumptions!C17</f>
         <v>200</v>
       </c>
-      <c r="D3" s="27">
+      <c r="D4" s="28">
         <f>Assumptions!D17</f>
         <v>300</v>
       </c>
-      <c r="E3" s="27">
+      <c r="E4" s="28">
         <f>Assumptions!E17</f>
         <v>375</v>
       </c>
-      <c r="F3" s="27">
+      <c r="F4" s="28">
         <f>Assumptions!F17</f>
         <v>400</v>
       </c>
     </row>
-    <row r="5" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="B5" s="12"/>
-      <c r="C5" s="12"/>
-      <c r="D5" s="12"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="B6" s="21">
-        <v>950000</v>
-      </c>
-      <c r="C6" s="21">
-        <v>1938000</v>
-      </c>
-      <c r="D6" s="21">
-        <v>2965200</v>
-      </c>
-      <c r="E6" s="21">
-        <v>3780375</v>
-      </c>
-      <c r="F6" s="21">
-        <v>4113200</v>
-      </c>
+    <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="B6" s="12"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B7" s="21">
-        <v>80000</v>
+        <v>950000</v>
       </c>
       <c r="C7" s="21">
-        <v>163200</v>
+        <v>1938000</v>
       </c>
       <c r="D7" s="21">
-        <v>249600</v>
+        <v>2965200</v>
       </c>
       <c r="E7" s="21">
-        <v>318375</v>
+        <v>3780375</v>
       </c>
       <c r="F7" s="21">
-        <v>346400</v>
+        <v>4113200</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B8" s="21">
-        <v>120000</v>
+        <v>80000</v>
       </c>
       <c r="C8" s="21">
-        <v>244800</v>
+        <v>163200</v>
       </c>
       <c r="D8" s="21">
-        <v>374400</v>
+        <v>249600</v>
       </c>
       <c r="E8" s="21">
-        <v>477375</v>
+        <v>318375</v>
       </c>
       <c r="F8" s="21">
-        <v>519600</v>
+        <v>346400</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B9" s="21">
-        <v>83333</v>
+        <v>120000</v>
       </c>
       <c r="C9" s="21">
-        <v>75000</v>
+        <v>244800</v>
       </c>
       <c r="D9" s="21">
-        <v>50000</v>
+        <v>374400</v>
       </c>
       <c r="E9" s="21">
-        <v>0</v>
+        <v>477375</v>
       </c>
       <c r="F9" s="21">
-        <v>0</v>
+        <v>519600</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B10" s="21">
-        <v>25000</v>
+        <v>83333</v>
       </c>
       <c r="C10" s="21">
-        <v>40000</v>
+        <v>75000</v>
       </c>
       <c r="D10" s="21">
         <v>50000</v>
       </c>
       <c r="E10" s="21">
-        <v>60000</v>
+        <v>0</v>
       </c>
       <c r="F10" s="21">
-        <v>70000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="B11" s="21">
+        <v>25000</v>
+      </c>
+      <c r="C11" s="21">
+        <v>40000</v>
+      </c>
+      <c r="D11" s="21">
+        <v>50000</v>
+      </c>
+      <c r="E11" s="21">
+        <v>60000</v>
+      </c>
+      <c r="F11" s="21">
+        <v>70000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="B11" s="21">
+      <c r="B12" s="21">
         <v>30000</v>
       </c>
-      <c r="C11" s="21">
+      <c r="C12" s="21">
         <v>61800</v>
       </c>
-      <c r="D11" s="21">
+      <c r="D12" s="21">
         <v>95400</v>
       </c>
-      <c r="E11" s="21">
+      <c r="E12" s="21">
         <v>123000</v>
       </c>
-      <c r="F11" s="21">
+      <c r="F12" s="21">
         <v>135200</v>
       </c>
     </row>
-    <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="12" t="s">
-        <v>147</v>
-      </c>
-      <c r="B12" s="28">
-        <f>SUM(B6:B11)</f>
+    <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="B13" s="29">
+        <f>SUM(B7:B12)</f>
         <v>1288333</v>
       </c>
-      <c r="C12" s="28">
-        <f>SUM(C6:C11)</f>
+      <c r="C13" s="29">
+        <f>SUM(C7:C12)</f>
         <v>2522800</v>
       </c>
-      <c r="D12" s="28">
-        <f>SUM(D6:D11)</f>
+      <c r="D13" s="29">
+        <f>SUM(D7:D12)</f>
         <v>3784600</v>
       </c>
-      <c r="E12" s="28">
-        <f>SUM(E6:E11)</f>
+      <c r="E13" s="29">
+        <f>SUM(E7:E12)</f>
         <v>4759125</v>
       </c>
-      <c r="F12" s="28">
-        <f>SUM(F6:F11)</f>
+      <c r="F13" s="29">
+        <f>SUM(F7:F12)</f>
         <v>5184400</v>
       </c>
     </row>
-    <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="12" t="s">
-        <v>148</v>
-      </c>
-      <c r="B14" s="12"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="13" t="s">
+    <row r="15" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="B15" s="21">
-        <v>124346</v>
-      </c>
-      <c r="C15" s="21">
-        <v>149215</v>
-      </c>
-      <c r="D15" s="21">
-        <v>149215</v>
-      </c>
-      <c r="E15" s="21">
-        <v>149215</v>
-      </c>
-      <c r="F15" s="21">
-        <v>149215</v>
-      </c>
+      <c r="B15" s="12"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="12"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
         <v>150</v>
       </c>
       <c r="B16" s="21">
-        <v>101738</v>
+        <v>124346</v>
       </c>
       <c r="C16" s="21">
-        <v>122085</v>
+        <v>149215</v>
       </c>
       <c r="D16" s="21">
-        <v>122085</v>
+        <v>149215</v>
       </c>
       <c r="E16" s="21">
-        <v>122085</v>
+        <v>149215</v>
       </c>
       <c r="F16" s="21">
-        <v>122085</v>
+        <v>149215</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -3384,19 +3378,19 @@
         <v>151</v>
       </c>
       <c r="B17" s="21">
-        <v>81390</v>
+        <v>101738</v>
       </c>
       <c r="C17" s="21">
-        <v>97668</v>
+        <v>122085</v>
       </c>
       <c r="D17" s="21">
-        <v>97668</v>
+        <v>122085</v>
       </c>
       <c r="E17" s="21">
-        <v>97668</v>
+        <v>122085</v>
       </c>
       <c r="F17" s="21">
-        <v>97668</v>
+        <v>122085</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -3404,19 +3398,19 @@
         <v>152</v>
       </c>
       <c r="B18" s="21">
-        <v>323299</v>
+        <v>81390</v>
       </c>
       <c r="C18" s="21">
-        <v>670111</v>
+        <v>97668</v>
       </c>
       <c r="D18" s="21">
-        <v>987532</v>
+        <v>97668</v>
       </c>
       <c r="E18" s="21">
-        <v>1234415</v>
+        <v>97668</v>
       </c>
       <c r="F18" s="21">
-        <v>1304953</v>
+        <v>97668</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -3424,19 +3418,19 @@
         <v>153</v>
       </c>
       <c r="B19" s="21">
-        <v>62173</v>
+        <v>323299</v>
       </c>
       <c r="C19" s="21">
-        <v>74608</v>
+        <v>670111</v>
       </c>
       <c r="D19" s="21">
-        <v>74608</v>
+        <v>987532</v>
       </c>
       <c r="E19" s="21">
-        <v>74608</v>
+        <v>1234415</v>
       </c>
       <c r="F19" s="21">
-        <v>74608</v>
+        <v>1304953</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -3444,19 +3438,19 @@
         <v>154</v>
       </c>
       <c r="B20" s="21">
-        <v>95738</v>
+        <v>62173</v>
       </c>
       <c r="C20" s="21">
-        <v>114885</v>
+        <v>74608</v>
       </c>
       <c r="D20" s="21">
-        <v>114885</v>
+        <v>74608</v>
       </c>
       <c r="E20" s="21">
-        <v>114885</v>
+        <v>74608</v>
       </c>
       <c r="F20" s="21">
-        <v>114885</v>
+        <v>74608</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -3464,19 +3458,19 @@
         <v>155</v>
       </c>
       <c r="B21" s="21">
-        <v>62173</v>
+        <v>95738</v>
       </c>
       <c r="C21" s="21">
-        <v>74608</v>
+        <v>114885</v>
       </c>
       <c r="D21" s="21">
-        <v>74608</v>
+        <v>114885</v>
       </c>
       <c r="E21" s="21">
-        <v>74608</v>
+        <v>114885</v>
       </c>
       <c r="F21" s="21">
-        <v>74608</v>
+        <v>114885</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -3484,19 +3478,19 @@
         <v>156</v>
       </c>
       <c r="B22" s="21">
-        <v>84012</v>
+        <v>62173</v>
       </c>
       <c r="C22" s="21">
-        <v>100814</v>
+        <v>74608</v>
       </c>
       <c r="D22" s="21">
-        <v>100814</v>
+        <v>74608</v>
       </c>
       <c r="E22" s="21">
-        <v>100814</v>
+        <v>74608</v>
       </c>
       <c r="F22" s="21">
-        <v>100814</v>
+        <v>74608</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -3504,204 +3498,204 @@
         <v>157</v>
       </c>
       <c r="B23" s="21">
+        <v>84012</v>
+      </c>
+      <c r="C23" s="21">
+        <v>100814</v>
+      </c>
+      <c r="D23" s="21">
+        <v>100814</v>
+      </c>
+      <c r="E23" s="21">
+        <v>100814</v>
+      </c>
+      <c r="F23" s="21">
+        <v>100814</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="B24" s="21">
         <v>62173</v>
       </c>
-      <c r="C23" s="21">
+      <c r="C24" s="21">
         <v>74608</v>
       </c>
-      <c r="D23" s="21">
+      <c r="D24" s="21">
         <v>74608</v>
       </c>
-      <c r="E23" s="21">
+      <c r="E24" s="21">
         <v>74608</v>
       </c>
-      <c r="F23" s="21">
+      <c r="F24" s="21">
         <v>74608</v>
       </c>
     </row>
-    <row r="24" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="B24" s="28">
-        <f>SUM(B15:B23)</f>
+    <row r="25" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="B25" s="29">
+        <f>SUM(B16:B24)</f>
         <v>997040</v>
       </c>
-      <c r="C24" s="28">
-        <f>SUM(C15:C23)</f>
+      <c r="C25" s="29">
+        <f>SUM(C16:C24)</f>
         <v>1478601</v>
       </c>
-      <c r="D24" s="28">
-        <f>SUM(D15:D23)</f>
+      <c r="D25" s="29">
+        <f>SUM(D16:D24)</f>
         <v>1796022</v>
       </c>
-      <c r="E24" s="28">
-        <f>SUM(E15:E23)</f>
+      <c r="E25" s="29">
+        <f>SUM(E16:E24)</f>
         <v>2042905</v>
       </c>
-      <c r="F24" s="28">
-        <f>SUM(F15:F23)</f>
+      <c r="F25" s="29">
+        <f>SUM(F16:F24)</f>
         <v>2113443</v>
       </c>
     </row>
-    <row r="26" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="12" t="s">
+    <row r="27" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="B26" s="12"/>
-      <c r="C26" s="12"/>
-      <c r="D26" s="12"/>
-      <c r="E26" s="12"/>
-      <c r="F26" s="12"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="B27" s="13"/>
-      <c r="C27" s="13"/>
-      <c r="D27" s="13"/>
-      <c r="E27" s="13"/>
-      <c r="F27" s="13"/>
+      <c r="B27" s="12"/>
+      <c r="C27" s="12"/>
+      <c r="D27" s="12"/>
+      <c r="E27" s="12"/>
+      <c r="F27" s="12"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>159</v>
-      </c>
-      <c r="B28" s="21">
+        <v>118</v>
+      </c>
+      <c r="B28" s="13"/>
+      <c r="C28" s="13"/>
+      <c r="D28" s="13"/>
+      <c r="E28" s="13"/>
+      <c r="F28" s="13"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="B29" s="21">
         <v>70000</v>
       </c>
-      <c r="C28" s="21">
+      <c r="C29" s="21">
         <v>144200</v>
       </c>
-      <c r="D28" s="21">
+      <c r="D29" s="21">
         <v>222900</v>
       </c>
-      <c r="E28" s="21">
+      <c r="E29" s="21">
         <v>286875</v>
       </c>
-      <c r="F28" s="21">
+      <c r="F29" s="21">
         <v>315200</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="29" t="s">
-        <v>160</v>
-      </c>
-      <c r="B29" s="30">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="B30" s="31">
         <v>70000</v>
       </c>
-      <c r="C29" s="30">
+      <c r="C30" s="31">
         <v>144200</v>
       </c>
-      <c r="D29" s="30">
+      <c r="D30" s="31">
         <v>222900</v>
       </c>
-      <c r="E29" s="30">
+      <c r="E30" s="31">
         <v>286875</v>
       </c>
-      <c r="F29" s="30">
+      <c r="F30" s="31">
         <v>315200</v>
       </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="13" t="s">
-        <v>120</v>
-      </c>
-      <c r="B30" s="13"/>
-      <c r="C30" s="13"/>
-      <c r="D30" s="13"/>
-      <c r="E30" s="13"/>
-      <c r="F30" s="13"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="13" t="s">
-        <v>161</v>
-      </c>
-      <c r="B31" s="21">
+        <v>120</v>
+      </c>
+      <c r="B31" s="13"/>
+      <c r="C31" s="13"/>
+      <c r="D31" s="13"/>
+      <c r="E31" s="13"/>
+      <c r="F31" s="13"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="B32" s="21">
         <v>50000</v>
       </c>
-      <c r="C31" s="21">
+      <c r="C32" s="21">
         <v>103000</v>
       </c>
-      <c r="D31" s="21">
+      <c r="D32" s="21">
         <v>159000</v>
       </c>
-      <c r="E31" s="21">
+      <c r="E32" s="21">
         <v>204750</v>
       </c>
-      <c r="F31" s="21">
+      <c r="F32" s="21">
         <v>224800</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="29" t="s">
-        <v>162</v>
-      </c>
-      <c r="B32" s="30">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="30" t="s">
+        <v>163</v>
+      </c>
+      <c r="B33" s="31">
         <v>50000</v>
       </c>
-      <c r="C32" s="30">
+      <c r="C33" s="31">
         <v>103000</v>
       </c>
-      <c r="D32" s="30">
+      <c r="D33" s="31">
         <v>159000</v>
       </c>
-      <c r="E32" s="30">
+      <c r="E33" s="31">
         <v>204750</v>
       </c>
-      <c r="F32" s="30">
+      <c r="F33" s="31">
         <v>224800</v>
       </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="B33" s="13"/>
-      <c r="C33" s="13"/>
-      <c r="D33" s="13"/>
-      <c r="E33" s="13"/>
-      <c r="F33" s="13"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="13" t="s">
-        <v>163</v>
-      </c>
-      <c r="B34" s="21">
-        <v>180000</v>
-      </c>
-      <c r="C34" s="21">
-        <v>222480</v>
-      </c>
-      <c r="D34" s="21">
-        <v>229154</v>
-      </c>
-      <c r="E34" s="21">
-        <v>236029</v>
-      </c>
-      <c r="F34" s="21">
-        <v>243110</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="B34" s="13"/>
+      <c r="C34" s="13"/>
+      <c r="D34" s="13"/>
+      <c r="E34" s="13"/>
+      <c r="F34" s="13"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="13" t="s">
         <v>164</v>
       </c>
       <c r="B35" s="21">
-        <v>25000</v>
+        <v>180000</v>
       </c>
       <c r="C35" s="21">
-        <v>30900</v>
+        <v>222480</v>
       </c>
       <c r="D35" s="21">
-        <v>31824</v>
+        <v>229154</v>
       </c>
       <c r="E35" s="21">
-        <v>32784</v>
+        <v>236029</v>
       </c>
       <c r="F35" s="21">
-        <v>33768</v>
+        <v>243110</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -3709,19 +3703,19 @@
         <v>165</v>
       </c>
       <c r="B36" s="21">
-        <v>15000</v>
+        <v>25000</v>
       </c>
       <c r="C36" s="21">
-        <v>18540</v>
+        <v>30900</v>
       </c>
       <c r="D36" s="21">
-        <v>19096</v>
+        <v>31824</v>
       </c>
       <c r="E36" s="21">
-        <v>19669</v>
+        <v>32784</v>
       </c>
       <c r="F36" s="21">
-        <v>20259</v>
+        <v>33768</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -3735,83 +3729,83 @@
         <v>18540</v>
       </c>
       <c r="D37" s="21">
+        <v>19096</v>
+      </c>
+      <c r="E37" s="21">
+        <v>19669</v>
+      </c>
+      <c r="F37" s="21">
+        <v>20259</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="B38" s="21">
+        <v>15000</v>
+      </c>
+      <c r="C38" s="21">
+        <v>18540</v>
+      </c>
+      <c r="D38" s="21">
         <v>19092</v>
       </c>
-      <c r="E37" s="21">
+      <c r="E38" s="21">
         <v>19668</v>
       </c>
-      <c r="F37" s="21">
+      <c r="F38" s="21">
         <v>20256</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="29" t="s">
-        <v>167</v>
-      </c>
-      <c r="B38" s="30">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="30" t="s">
+        <v>168</v>
+      </c>
+      <c r="B39" s="31">
         <v>235000</v>
       </c>
-      <c r="C38" s="30">
+      <c r="C39" s="31">
         <v>290460</v>
       </c>
-      <c r="D38" s="30">
+      <c r="D39" s="31">
         <v>299166</v>
       </c>
-      <c r="E38" s="30">
+      <c r="E39" s="31">
         <v>308150</v>
       </c>
-      <c r="F38" s="30">
+      <c r="F39" s="31">
         <v>317393</v>
       </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="B39" s="13"/>
-      <c r="C39" s="13"/>
-      <c r="D39" s="13"/>
-      <c r="E39" s="13"/>
-      <c r="F39" s="13"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="13" t="s">
-        <v>168</v>
-      </c>
-      <c r="B40" s="21">
-        <v>20833</v>
-      </c>
-      <c r="C40" s="21">
-        <v>25750</v>
-      </c>
-      <c r="D40" s="21">
-        <v>26523</v>
-      </c>
-      <c r="E40" s="21">
-        <v>27318</v>
-      </c>
-      <c r="F40" s="21">
-        <v>28138</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="B40" s="13"/>
+      <c r="C40" s="13"/>
+      <c r="D40" s="13"/>
+      <c r="E40" s="13"/>
+      <c r="F40" s="13"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="13" t="s">
         <v>169</v>
       </c>
       <c r="B41" s="21">
-        <v>12500</v>
+        <v>20833</v>
       </c>
       <c r="C41" s="21">
-        <v>15450</v>
+        <v>25750</v>
       </c>
       <c r="D41" s="21">
-        <v>15914</v>
+        <v>26523</v>
       </c>
       <c r="E41" s="21">
-        <v>16391</v>
+        <v>27318</v>
       </c>
       <c r="F41" s="21">
-        <v>16883</v>
+        <v>28138</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -3819,19 +3813,19 @@
         <v>170</v>
       </c>
       <c r="B42" s="21">
-        <v>16667</v>
+        <v>12500</v>
       </c>
       <c r="C42" s="21">
-        <v>20600</v>
+        <v>15450</v>
       </c>
       <c r="D42" s="21">
-        <v>21218</v>
+        <v>15914</v>
       </c>
       <c r="E42" s="21">
-        <v>21855</v>
+        <v>16391</v>
       </c>
       <c r="F42" s="21">
-        <v>22510</v>
+        <v>16883</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -3839,19 +3833,19 @@
         <v>171</v>
       </c>
       <c r="B43" s="21">
-        <v>80000</v>
+        <v>16667</v>
       </c>
       <c r="C43" s="21">
-        <v>164800</v>
+        <v>20600</v>
       </c>
       <c r="D43" s="21">
-        <v>254700</v>
+        <v>21218</v>
       </c>
       <c r="E43" s="21">
-        <v>327750</v>
+        <v>21855</v>
       </c>
       <c r="F43" s="21">
-        <v>360000</v>
+        <v>22510</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -3859,219 +3853,214 @@
         <v>172</v>
       </c>
       <c r="B44" s="21">
+        <v>80000</v>
+      </c>
+      <c r="C44" s="21">
+        <v>164800</v>
+      </c>
+      <c r="D44" s="21">
+        <v>254700</v>
+      </c>
+      <c r="E44" s="21">
+        <v>327750</v>
+      </c>
+      <c r="F44" s="21">
+        <v>360000</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="B45" s="21">
         <v>60000</v>
       </c>
-      <c r="C44" s="21">
+      <c r="C45" s="21">
         <v>123600</v>
       </c>
-      <c r="D44" s="21">
+      <c r="D45" s="21">
         <v>191100</v>
       </c>
-      <c r="E44" s="21">
+      <c r="E45" s="21">
         <v>246000</v>
       </c>
-      <c r="F44" s="21">
+      <c r="F45" s="21">
         <v>270000</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="29" t="s">
-        <v>173</v>
-      </c>
-      <c r="B45" s="30">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="30" t="s">
+        <v>174</v>
+      </c>
+      <c r="B46" s="31">
         <v>190000</v>
       </c>
-      <c r="C45" s="30">
+      <c r="C46" s="31">
         <v>350200</v>
       </c>
-      <c r="D45" s="30">
+      <c r="D46" s="31">
         <v>509455</v>
       </c>
-      <c r="E45" s="30">
+      <c r="E46" s="31">
         <v>639314</v>
       </c>
-      <c r="F45" s="30">
+      <c r="F46" s="31">
         <v>697531</v>
       </c>
     </row>
-    <row r="46" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="12" t="s">
-        <v>174</v>
-      </c>
-      <c r="B46" s="28">
-        <f>B29+B32+B38+B45</f>
+    <row r="47" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="B47" s="29">
+        <f>B30+B33+B39+B46</f>
         <v>545000</v>
       </c>
-      <c r="C46" s="28">
-        <f>C29+C32+C38+C45</f>
+      <c r="C47" s="29">
+        <f>C30+C33+C39+C46</f>
         <v>887860</v>
       </c>
-      <c r="D46" s="28">
-        <f>D29+D32+D38+D45</f>
+      <c r="D47" s="29">
+        <f>D30+D33+D39+D46</f>
         <v>1190521</v>
       </c>
-      <c r="E46" s="28">
-        <f>E29+E32+E38+E45</f>
+      <c r="E47" s="29">
+        <f>E30+E33+E39+E46</f>
         <v>1439089</v>
       </c>
-      <c r="F46" s="28">
-        <f>F29+F32+F38+F45</f>
+      <c r="F47" s="29">
+        <f>F30+F33+F39+F46</f>
         <v>1554924</v>
       </c>
     </row>
-    <row r="48" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="12" t="s">
-        <v>175</v>
-      </c>
-      <c r="B48" s="12"/>
-      <c r="C48" s="12"/>
-      <c r="D48" s="12"/>
-      <c r="E48" s="12"/>
-      <c r="F48" s="12"/>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="B49" s="21">
-        <v>49825</v>
-      </c>
-      <c r="C49" s="21">
-        <v>49825</v>
-      </c>
-      <c r="D49" s="21">
-        <v>49825</v>
-      </c>
-      <c r="E49" s="21">
-        <v>49825</v>
-      </c>
-      <c r="F49" s="21">
-        <v>49825</v>
-      </c>
+    <row r="49" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="B49" s="12"/>
+      <c r="C49" s="12"/>
+      <c r="D49" s="12"/>
+      <c r="E49" s="12"/>
+      <c r="F49" s="12"/>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="13" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B50" s="21">
-        <v>75000</v>
+        <v>49825</v>
       </c>
       <c r="C50" s="21">
-        <v>25000</v>
+        <v>49825</v>
       </c>
       <c r="D50" s="21">
-        <v>30000</v>
+        <v>49825</v>
       </c>
       <c r="E50" s="21">
-        <v>15000</v>
+        <v>49825</v>
       </c>
       <c r="F50" s="21">
-        <v>10000</v>
+        <v>49825</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="13" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B51" s="21">
-        <v>40000</v>
+        <v>75000</v>
       </c>
       <c r="C51" s="21">
+        <v>25000</v>
+      </c>
+      <c r="D51" s="21">
+        <v>30000</v>
+      </c>
+      <c r="E51" s="21">
         <v>15000</v>
-      </c>
-      <c r="D51" s="21">
-        <v>10000</v>
-      </c>
-      <c r="E51" s="21">
-        <v>10000</v>
       </c>
       <c r="F51" s="21">
         <v>10000</v>
       </c>
     </row>
-    <row r="52" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="12" t="s">
-        <v>176</v>
-      </c>
-      <c r="B52" s="28">
-        <f>SUM(B49:B51)</f>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="B52" s="21">
+        <v>40000</v>
+      </c>
+      <c r="C52" s="21">
+        <v>15000</v>
+      </c>
+      <c r="D52" s="21">
+        <v>10000</v>
+      </c>
+      <c r="E52" s="21">
+        <v>10000</v>
+      </c>
+      <c r="F52" s="21">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="53" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="B53" s="29">
+        <f>SUM(B50:B52)</f>
         <v>164825</v>
       </c>
-      <c r="C52" s="28">
-        <f>SUM(C49:C51)</f>
+      <c r="C53" s="29">
+        <f>SUM(C50:C52)</f>
         <v>89825</v>
       </c>
-      <c r="D52" s="28">
-        <f>SUM(D49:D51)</f>
+      <c r="D53" s="29">
+        <f>SUM(D50:D52)</f>
         <v>89825</v>
       </c>
-      <c r="E52" s="28">
-        <f>SUM(E49:E51)</f>
+      <c r="E53" s="29">
+        <f>SUM(E50:E52)</f>
         <v>74825</v>
       </c>
-      <c r="F52" s="28">
-        <f>SUM(F49:F51)</f>
+      <c r="F53" s="29">
+        <f>SUM(F50:F52)</f>
         <v>69825</v>
       </c>
     </row>
-    <row r="54" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="12" t="s">
-        <v>177</v>
-      </c>
-      <c r="B54" s="12"/>
-      <c r="C54" s="12"/>
-      <c r="D54" s="12"/>
-      <c r="E54" s="12"/>
-      <c r="F54" s="12"/>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="26" t="s">
+    <row r="55" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="12" t="s">
         <v>178</v>
       </c>
-      <c r="B55" s="30">
-        <f>B12</f>
+      <c r="B55" s="12"/>
+      <c r="C55" s="12"/>
+      <c r="D55" s="12"/>
+      <c r="E55" s="12"/>
+      <c r="F55" s="12"/>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="27" t="s">
+        <v>179</v>
+      </c>
+      <c r="B56" s="31">
+        <f>B13</f>
         <v>1288333</v>
       </c>
-      <c r="C55" s="30">
-        <f>C12</f>
+      <c r="C56" s="31">
+        <f>C13</f>
         <v>2522800</v>
       </c>
-      <c r="D55" s="30">
-        <f>D12</f>
+      <c r="D56" s="31">
+        <f>D13</f>
         <v>3784600</v>
       </c>
-      <c r="E55" s="30">
-        <f>E12</f>
+      <c r="E56" s="31">
+        <f>E13</f>
         <v>4759125</v>
       </c>
-      <c r="F55" s="30">
-        <f>F12</f>
+      <c r="F56" s="31">
+        <f>F13</f>
         <v>5184400</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="13" t="s">
-        <v>179</v>
-      </c>
-      <c r="B56" s="21">
-        <f>B24</f>
-        <v>997040</v>
-      </c>
-      <c r="C56" s="21">
-        <f>C24</f>
-        <v>1478601</v>
-      </c>
-      <c r="D56" s="21">
-        <f>D24</f>
-        <v>1796022</v>
-      </c>
-      <c r="E56" s="21">
-        <f>E24</f>
-        <v>2042905</v>
-      </c>
-      <c r="F56" s="21">
-        <f>F24</f>
-        <v>2113443</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -4079,24 +4068,24 @@
         <v>180</v>
       </c>
       <c r="B57" s="21">
-        <f>B46</f>
-        <v>545000</v>
+        <f>B25</f>
+        <v>997040</v>
       </c>
       <c r="C57" s="21">
-        <f>C46</f>
-        <v>887860</v>
+        <f>C25</f>
+        <v>1478601</v>
       </c>
       <c r="D57" s="21">
-        <f>D46</f>
-        <v>1190521</v>
+        <f>D25</f>
+        <v>1796022</v>
       </c>
       <c r="E57" s="21">
-        <f>E46</f>
-        <v>1439089</v>
+        <f>E25</f>
+        <v>2042905</v>
       </c>
       <c r="F57" s="21">
-        <f>F46</f>
-        <v>1554924</v>
+        <f>F25</f>
+        <v>2113443</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
@@ -4104,309 +4093,309 @@
         <v>181</v>
       </c>
       <c r="B58" s="21">
-        <f>B52</f>
+        <f>B47</f>
+        <v>545000</v>
+      </c>
+      <c r="C58" s="21">
+        <f>C47</f>
+        <v>887860</v>
+      </c>
+      <c r="D58" s="21">
+        <f>D47</f>
+        <v>1190521</v>
+      </c>
+      <c r="E58" s="21">
+        <f>E47</f>
+        <v>1439089</v>
+      </c>
+      <c r="F58" s="21">
+        <f>F47</f>
+        <v>1554924</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="B59" s="21">
+        <f>B53</f>
         <v>164825</v>
       </c>
-      <c r="C58" s="21">
-        <f>C52</f>
+      <c r="C59" s="21">
+        <f>C53</f>
         <v>89825</v>
       </c>
-      <c r="D58" s="21">
-        <f>D52</f>
+      <c r="D59" s="21">
+        <f>D53</f>
         <v>89825</v>
       </c>
-      <c r="E58" s="21">
-        <f>E52</f>
+      <c r="E59" s="21">
+        <f>E53</f>
         <v>74825</v>
       </c>
-      <c r="F58" s="21">
-        <f>F52</f>
+      <c r="F59" s="21">
+        <f>F53</f>
         <v>69825</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="26" t="s">
-        <v>182</v>
-      </c>
-      <c r="B59" s="30">
-        <f>B56+B57+B58</f>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="27" t="s">
+        <v>183</v>
+      </c>
+      <c r="B60" s="31">
+        <f>B57+B58+B59</f>
         <v>1706865</v>
       </c>
-      <c r="C59" s="30">
-        <f>C56+C57+C58</f>
+      <c r="C60" s="31">
+        <f>C57+C58+C59</f>
         <v>2456286</v>
       </c>
-      <c r="D59" s="30">
-        <f>D56+D57+D58</f>
+      <c r="D60" s="31">
+        <f>D57+D58+D59</f>
         <v>3076368</v>
       </c>
-      <c r="E59" s="30">
-        <f>E56+E57+E58</f>
+      <c r="E60" s="31">
+        <f>E57+E58+E59</f>
         <v>3556819</v>
       </c>
-      <c r="F59" s="30">
-        <f>F56+F57+F58</f>
+      <c r="F60" s="31">
+        <f>F57+F58+F59</f>
         <v>3738192</v>
       </c>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="31" t="s">
-        <v>183</v>
-      </c>
-      <c r="B61" s="32">
-        <f>B55-B59</f>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" s="32" t="s">
+        <v>184</v>
+      </c>
+      <c r="B62" s="33">
+        <f>B56-B60</f>
         <v>-418532</v>
       </c>
-      <c r="C61" s="33">
-        <f>C55-C59</f>
+      <c r="C62" s="34">
+        <f>C56-C60</f>
         <v>66514</v>
       </c>
-      <c r="D61" s="33">
-        <f>D55-D59</f>
+      <c r="D62" s="34">
+        <f>D56-D60</f>
         <v>708232</v>
       </c>
-      <c r="E61" s="33">
-        <f>E55-E59</f>
+      <c r="E62" s="34">
+        <f>E56-E60</f>
         <v>1202306</v>
       </c>
-      <c r="F61" s="33">
-        <f>F55-F59</f>
+      <c r="F62" s="34">
+        <f>F56-F60</f>
         <v>1446208</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="13" t="s">
-        <v>184</v>
-      </c>
-      <c r="B62" s="34">
-        <f>IF(B55=0,"",B61/B55)</f>
-        <v>-0.32</v>
-      </c>
-      <c r="C62" s="34">
-        <f>IF(C55=0,"",C61/C55)</f>
-        <v>0.03</v>
-      </c>
-      <c r="D62" s="34">
-        <f>IF(D55=0,"",D61/D55)</f>
-        <v>0.19</v>
-      </c>
-      <c r="E62" s="34">
-        <f>IF(E55=0,"",E61/E55)</f>
-        <v>0.25</v>
-      </c>
-      <c r="F62" s="34">
-        <f>IF(F55=0,"",F61/F55)</f>
-        <v>0.28</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="13" t="s">
         <v>185</v>
       </c>
-      <c r="B63" s="21">
-        <f>B61</f>
+      <c r="B63" s="35">
+        <f>IF(B56=0,"",B62/B56)</f>
+        <v>-0.32486321</v>
+      </c>
+      <c r="C63" s="35">
+        <f>IF(C56=0,"",C62/C56)</f>
+        <v>0.02636515</v>
+      </c>
+      <c r="D63" s="35">
+        <f>IF(D56=0,"",D62/D56)</f>
+        <v>0.18713523</v>
+      </c>
+      <c r="E63" s="35">
+        <f>IF(E56=0,"",E62/E56)</f>
+        <v>0.25263173</v>
+      </c>
+      <c r="F63" s="35">
+        <f>IF(F56=0,"",F62/F56)</f>
+        <v>0.27895378</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" s="13" t="s">
+        <v>186</v>
+      </c>
+      <c r="B64" s="21">
+        <f>B62</f>
         <v>-418532</v>
       </c>
-      <c r="C63" s="21">
-        <f>B63+C61</f>
+      <c r="C64" s="21">
+        <f>B64+C62</f>
         <v>-352018</v>
       </c>
-      <c r="D63" s="21">
-        <f>C63+D61</f>
+      <c r="D64" s="21">
+        <f>C64+D62</f>
         <v>356214</v>
       </c>
-      <c r="E63" s="21">
-        <f>D63+E61</f>
+      <c r="E64" s="21">
+        <f>D64+E62</f>
         <v>1558520</v>
       </c>
-      <c r="F63" s="21">
-        <f>E63+F61</f>
+      <c r="F64" s="21">
+        <f>E64+F62</f>
         <v>3004728</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64" s="29" t="s">
-        <v>186</v>
-      </c>
-      <c r="B64" s="35" t="s">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65" s="30" t="s">
+        <v>187</v>
+      </c>
+      <c r="B65" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="C64" s="35" t="s">
+      <c r="C65" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="D64" s="36" t="s">
-        <v>187</v>
-      </c>
-      <c r="E64" s="35" t="s">
+      <c r="D65" s="37" t="s">
+        <v>188</v>
+      </c>
+      <c r="E65" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="F64" s="35" t="s">
+      <c r="F65" s="36" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="66" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A66" s="12" t="s">
-        <v>188</v>
-      </c>
-      <c r="B66" s="12"/>
-      <c r="C66" s="12"/>
-      <c r="D66" s="12"/>
-      <c r="E66" s="12"/>
-      <c r="F66" s="12"/>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A67" s="26" t="s">
+    <row r="67" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" s="12" t="s">
         <v>189</v>
       </c>
-      <c r="B67" s="30">
-        <f>B55-B56-B57</f>
+      <c r="B67" s="12"/>
+      <c r="C67" s="12"/>
+      <c r="D67" s="12"/>
+      <c r="E67" s="12"/>
+      <c r="F67" s="12"/>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68" s="27" t="s">
+        <v>190</v>
+      </c>
+      <c r="B68" s="31">
+        <f>B56-B57-B58</f>
         <v>-253707</v>
       </c>
-      <c r="C67" s="30">
-        <f>C55-C56-C57</f>
+      <c r="C68" s="31">
+        <f>C56-C57-C58</f>
         <v>156339</v>
       </c>
-      <c r="D67" s="30">
-        <f>D55-D56-D57</f>
+      <c r="D68" s="31">
+        <f>D56-D57-D58</f>
         <v>798057</v>
       </c>
-      <c r="E67" s="30">
-        <f>E55-E56-E57</f>
+      <c r="E68" s="31">
+        <f>E56-E57-E58</f>
         <v>1277131</v>
       </c>
-      <c r="F67" s="30">
-        <f>F55-F56-F57</f>
+      <c r="F68" s="31">
+        <f>F56-F57-F58</f>
         <v>1516033</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A68" s="13" t="s">
-        <v>190</v>
-      </c>
-      <c r="B68" s="21">
-        <f>B58</f>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="B69" s="21">
+        <f>B59</f>
         <v>164825</v>
       </c>
-      <c r="C68" s="21">
-        <f>C58</f>
+      <c r="C69" s="21">
+        <f>C59</f>
         <v>89825</v>
       </c>
-      <c r="D68" s="21">
-        <f>D58</f>
+      <c r="D69" s="21">
+        <f>D59</f>
         <v>89825</v>
       </c>
-      <c r="E68" s="21">
-        <f>E58</f>
+      <c r="E69" s="21">
+        <f>E59</f>
         <v>74825</v>
       </c>
-      <c r="F68" s="21">
-        <f>F58</f>
+      <c r="F69" s="21">
+        <f>F59</f>
         <v>69825</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A69" s="26" t="s">
-        <v>191</v>
-      </c>
-      <c r="B69" s="37">
-        <f>IF(B68=0,"N/A",B67/B68)</f>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70" s="27" t="s">
+        <v>192</v>
+      </c>
+      <c r="B70" s="38">
+        <f>IF(B69=0,"N/A",B68/B69)</f>
         <v>-1.54</v>
       </c>
-      <c r="C69" s="37">
-        <f>IF(C68=0,"N/A",C67/C68)</f>
+      <c r="C70" s="38">
+        <f>IF(C69=0,"N/A",C68/C69)</f>
         <v>1.74</v>
       </c>
-      <c r="D69" s="37">
-        <f>IF(D68=0,"N/A",D67/D68)</f>
+      <c r="D70" s="38">
+        <f>IF(D69=0,"N/A",D68/D69)</f>
         <v>8.88</v>
       </c>
-      <c r="E69" s="37">
-        <f>IF(E68=0,"N/A",E67/E68)</f>
+      <c r="E70" s="38">
+        <f>IF(E69=0,"N/A",E68/E69)</f>
         <v>17.07</v>
       </c>
-      <c r="F69" s="37">
-        <f>IF(F68=0,"N/A",F67/F68)</f>
+      <c r="F70" s="38">
+        <f>IF(F69=0,"N/A",F68/F69)</f>
         <v>21.71</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A70" s="13" t="s">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A71" s="13" t="s">
         <v>143</v>
       </c>
-      <c r="B70" s="21" t="str">
+      <c r="B71" s="21" t="str">
         <f>Assumptions!B68</f>
         <v>0</v>
       </c>
-      <c r="C70" s="21">
-        <f>B71</f>
+      <c r="C71" s="21">
+        <f>B72</f>
         <v>-418532</v>
       </c>
-      <c r="D70" s="21">
-        <f>C71</f>
+      <c r="D71" s="21">
+        <f>C72</f>
         <v>-352018</v>
       </c>
-      <c r="E70" s="21">
-        <f>D71</f>
+      <c r="E71" s="21">
+        <f>D72</f>
         <v>356214</v>
       </c>
-      <c r="F70" s="21">
-        <f>E71</f>
+      <c r="F71" s="21">
+        <f>E72</f>
         <v>1558520</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A71" s="26" t="s">
-        <v>192</v>
-      </c>
-      <c r="B71" s="30">
-        <f>B70+B61</f>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72" s="27" t="s">
+        <v>193</v>
+      </c>
+      <c r="B72" s="31">
+        <f>B71+B62</f>
         <v>-418532</v>
       </c>
-      <c r="C71" s="30">
-        <f>C70+C61</f>
+      <c r="C72" s="31">
+        <f>C71+C62</f>
         <v>-352018</v>
       </c>
-      <c r="D71" s="30">
-        <f>D70+D61</f>
+      <c r="D72" s="31">
+        <f>D71+D62</f>
         <v>356214</v>
       </c>
-      <c r="E71" s="30">
-        <f>E70+E61</f>
+      <c r="E72" s="31">
+        <f>E71+E62</f>
         <v>1558520</v>
       </c>
-      <c r="F71" s="30">
-        <f>F70+F61</f>
+      <c r="F72" s="31">
+        <f>F71+F62</f>
         <v>3004728</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A72" s="13" t="s">
-        <v>193</v>
-      </c>
-      <c r="B72" s="38">
-        <f>IF(B59=0,"",B71/B59*365)</f>
-        <v>-89</v>
-      </c>
-      <c r="C72" s="38">
-        <f>IF(C59=0,"",C71/C59*365)</f>
-        <v>-52</v>
-      </c>
-      <c r="D72" s="38">
-        <f>IF(D59=0,"",D71/D59*365)</f>
-        <v>42</v>
-      </c>
-      <c r="E72" s="38">
-        <f>IF(E59=0,"",E71/E59*365)</f>
-        <v>160</v>
-      </c>
-      <c r="F72" s="38">
-        <f>IF(F59=0,"",F71/F59*365)</f>
-        <v>293</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -4414,108 +4403,108 @@
         <v>194</v>
       </c>
       <c r="B73" s="39">
-        <f>IF(B59=0,"",B71/(B59/12))</f>
-        <v>-2.9</v>
+        <f>IF(B60=0,"",B72/B60*365)</f>
+        <v>-89</v>
       </c>
       <c r="C73" s="39">
-        <f>IF(C59=0,"",C71/(C59/12))</f>
-        <v>-1.7</v>
+        <f>IF(C60=0,"",C72/C60*365)</f>
+        <v>-52</v>
       </c>
       <c r="D73" s="39">
-        <f>IF(D59=0,"",D71/(D59/12))</f>
-        <v>1.4</v>
+        <f>IF(D60=0,"",D72/D60*365)</f>
+        <v>42</v>
       </c>
       <c r="E73" s="39">
-        <f>IF(E59=0,"",E71/(E59/12))</f>
-        <v>5.3</v>
+        <f>IF(E60=0,"",E72/E60*365)</f>
+        <v>160</v>
       </c>
       <c r="F73" s="39">
-        <f>IF(F59=0,"",F71/(F59/12))</f>
-        <v>9.6</v>
+        <f>IF(F60=0,"",F72/F60*365)</f>
+        <v>293</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="13" t="s">
         <v>195</v>
       </c>
-      <c r="B74" s="34">
-        <f>IF(Assumptions!B12=0,"",B3/Assumptions!B12)</f>
+      <c r="B74" s="40">
+        <f>IF(B60=0,"",B72/(B60/12))</f>
+        <v>-2.9</v>
+      </c>
+      <c r="C74" s="40">
+        <f>IF(C60=0,"",C72/(C60/12))</f>
+        <v>-1.7</v>
+      </c>
+      <c r="D74" s="40">
+        <f>IF(D60=0,"",D72/(D60/12))</f>
+        <v>1.4</v>
+      </c>
+      <c r="E74" s="40">
+        <f>IF(E60=0,"",E72/(E60/12))</f>
+        <v>5.3</v>
+      </c>
+      <c r="F74" s="40">
+        <f>IF(F60=0,"",F72/(F60/12))</f>
+        <v>9.6</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A75" s="13" t="s">
+        <v>196</v>
+      </c>
+      <c r="B75" s="35">
+        <f>IF(Assumptions!B12=0,"",B4/Assumptions!B12)</f>
         <v>0.3</v>
       </c>
-      <c r="C74" s="34">
-        <f>IF(Assumptions!B12=0,"",C3/Assumptions!B12)</f>
+      <c r="C75" s="35">
+        <f>IF(Assumptions!B12=0,"",C4/Assumptions!B12)</f>
         <v>0.5</v>
       </c>
-      <c r="D74" s="34">
-        <f>IF(Assumptions!B12=0,"",D3/Assumptions!B12)</f>
+      <c r="D75" s="35">
+        <f>IF(Assumptions!B12=0,"",D4/Assumptions!B12)</f>
         <v>0.75</v>
       </c>
-      <c r="E74" s="34">
-        <f>IF(Assumptions!B12=0,"",E3/Assumptions!B12)</f>
-        <v>0.94</v>
-      </c>
-      <c r="F74" s="34">
-        <f>IF(Assumptions!B12=0,"",F3/Assumptions!B12)</f>
+      <c r="E75" s="35">
+        <f>IF(Assumptions!B12=0,"",E4/Assumptions!B12)</f>
+        <v>0.9375</v>
+      </c>
+      <c r="F75" s="35">
+        <f>IF(Assumptions!B12=0,"",F4/Assumptions!B12)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="76" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A76" s="12" t="s">
-        <v>196</v>
-      </c>
-      <c r="B76" s="12"/>
-      <c r="C76" s="12"/>
-      <c r="D76" s="12"/>
-      <c r="E76" s="12"/>
-      <c r="F76" s="12"/>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A77" s="13" t="s">
+    <row r="77" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A77" s="12" t="s">
         <v>197</v>
       </c>
-      <c r="B77" s="13" t="str">
-        <f>IF(B68=0,"N/A",IF(B69&gt;=1.2,"PASS","FAIL"))</f>
-        <v>FAIL</v>
-      </c>
-      <c r="C77" s="13" t="str">
-        <f>IF(C68=0,"N/A",IF(C69&gt;=1.2,"PASS","FAIL"))</f>
-        <v>PASS</v>
-      </c>
-      <c r="D77" s="13" t="str">
-        <f>IF(D68=0,"N/A",IF(D69&gt;=1.2,"PASS","FAIL"))</f>
-        <v>PASS</v>
-      </c>
-      <c r="E77" s="13" t="str">
-        <f>IF(E68=0,"N/A",IF(E69&gt;=1.2,"PASS","FAIL"))</f>
-        <v>PASS</v>
-      </c>
-      <c r="F77" s="13" t="str">
-        <f>IF(F68=0,"N/A",IF(F69&gt;=1.2,"PASS","FAIL"))</f>
-        <v>PASS</v>
-      </c>
+      <c r="B77" s="12"/>
+      <c r="C77" s="12"/>
+      <c r="D77" s="12"/>
+      <c r="E77" s="12"/>
+      <c r="F77" s="12"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="13" t="s">
         <v>198</v>
       </c>
       <c r="B78" s="13" t="str">
-        <f>IF(B61&gt;0,"PASS","FAIL")</f>
+        <f>IF(B69=0,"N/A",IF(B70&gt;=1.25,"PASS","FAIL"))</f>
         <v>FAIL</v>
       </c>
       <c r="C78" s="13" t="str">
-        <f>IF(C61&gt;0,"PASS","FAIL")</f>
+        <f>IF(C69=0,"N/A",IF(C70&gt;=1.25,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
       <c r="D78" s="13" t="str">
-        <f>IF(D61&gt;0,"PASS","FAIL")</f>
+        <f>IF(D69=0,"N/A",IF(D70&gt;=1.25,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
       <c r="E78" s="13" t="str">
-        <f>IF(E61&gt;0,"PASS","FAIL")</f>
+        <f>IF(E69=0,"N/A",IF(E70&gt;=1.25,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
       <c r="F78" s="13" t="str">
-        <f>IF(F61&gt;0,"PASS","FAIL")</f>
+        <f>IF(F69=0,"N/A",IF(F70&gt;=1.25,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
@@ -4524,23 +4513,23 @@
         <v>199</v>
       </c>
       <c r="B79" s="13" t="str">
-        <f>IF(Assumptions!B12=0,"N/A",IF(B3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
+        <f>IF(B62&gt;0,"PASS","FAIL")</f>
         <v>FAIL</v>
       </c>
       <c r="C79" s="13" t="str">
-        <f>IF(Assumptions!B12=0,"N/A",IF(C3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
-        <v>FAIL</v>
+        <f>IF(C62&gt;0,"PASS","FAIL")</f>
+        <v>PASS</v>
       </c>
       <c r="D79" s="13" t="str">
-        <f>IF(Assumptions!B12=0,"N/A",IF(D3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
+        <f>IF(D62&gt;0,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="E79" s="13" t="str">
-        <f>IF(Assumptions!B12=0,"N/A",IF(E3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
+        <f>IF(E62&gt;0,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="F79" s="13" t="str">
-        <f>IF(Assumptions!B12=0,"N/A",IF(F3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
+        <f>IF(F62&gt;0,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
@@ -4549,84 +4538,84 @@
         <v>200</v>
       </c>
       <c r="B80" s="13" t="str">
-        <f>IF(B59=0,"N/A",IF(B71/(B59/12)&gt;=2,"PASS","FAIL"))</f>
+        <f>IF(Assumptions!B12=0,"N/A",IF(B4/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
         <v>FAIL</v>
       </c>
       <c r="C80" s="13" t="str">
-        <f>IF(C59=0,"N/A",IF(C71/(C59/12)&gt;=2,"PASS","FAIL"))</f>
+        <f>IF(Assumptions!B12=0,"N/A",IF(C4/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
         <v>FAIL</v>
       </c>
       <c r="D80" s="13" t="str">
-        <f>IF(D59=0,"N/A",IF(D71/(D59/12)&gt;=2,"PASS","FAIL"))</f>
+        <f>IF(Assumptions!B12=0,"N/A",IF(D4/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
+        <v>PASS</v>
+      </c>
+      <c r="E80" s="13" t="str">
+        <f>IF(Assumptions!B12=0,"N/A",IF(E4/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
+        <v>PASS</v>
+      </c>
+      <c r="F80" s="13" t="str">
+        <f>IF(Assumptions!B12=0,"N/A",IF(F4/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A81" s="13" t="s">
+        <v>201</v>
+      </c>
+      <c r="B81" s="13" t="str">
+        <f>IF(B60=0,"N/A",IF(B72/(B60/12)&gt;=2,"PASS","FAIL"))</f>
         <v>FAIL</v>
       </c>
-      <c r="E80" s="13" t="str">
-        <f>IF(E59=0,"N/A",IF(E71/(E59/12)&gt;=2,"PASS","FAIL"))</f>
+      <c r="C81" s="13" t="str">
+        <f>IF(C60=0,"N/A",IF(C72/(C60/12)&gt;=2,"PASS","FAIL"))</f>
+        <v>FAIL</v>
+      </c>
+      <c r="D81" s="13" t="str">
+        <f>IF(D60=0,"N/A",IF(D72/(D60/12)&gt;=2,"PASS","FAIL"))</f>
+        <v>FAIL</v>
+      </c>
+      <c r="E81" s="13" t="str">
+        <f>IF(E60=0,"N/A",IF(E72/(E60/12)&gt;=2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="F80" s="13" t="str">
-        <f>IF(F59=0,"N/A",IF(F71/(F59/12)&gt;=2,"PASS","FAIL"))</f>
+      <c r="F81" s="13" t="str">
+        <f>IF(F60=0,"N/A",IF(F72/(F60/12)&gt;=2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
-    <row r="82" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A82" s="12" t="s">
-        <v>201</v>
-      </c>
-      <c r="B82" s="12"/>
-      <c r="C82" s="12"/>
-      <c r="D82" s="12"/>
-      <c r="E82" s="12"/>
-      <c r="F82" s="12"/>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A83" s="13" t="s">
+    <row r="83" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A83" s="12" t="s">
         <v>202</v>
       </c>
-      <c r="B83" s="21">
-        <f>IF(B3=0,"",B12/B3)</f>
-        <v>10736</v>
-      </c>
-      <c r="C83" s="21">
-        <f>IF(C3=0,"",C12/C3)</f>
-        <v>12614</v>
-      </c>
-      <c r="D83" s="21">
-        <f>IF(D3=0,"",D12/D3)</f>
-        <v>12615</v>
-      </c>
-      <c r="E83" s="21">
-        <f>IF(E3=0,"",E12/E3)</f>
-        <v>12691</v>
-      </c>
-      <c r="F83" s="21">
-        <f>IF(F3=0,"",F12/F3)</f>
-        <v>12961</v>
-      </c>
+      <c r="B83" s="12"/>
+      <c r="C83" s="12"/>
+      <c r="D83" s="12"/>
+      <c r="E83" s="12"/>
+      <c r="F83" s="12"/>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="13" t="s">
         <v>203</v>
       </c>
       <c r="B84" s="21">
-        <f>IF(B3=0,"",B59/B3)</f>
-        <v>14224</v>
+        <f>IF(B4=0,"",B13/B4)</f>
+        <v>10736</v>
       </c>
       <c r="C84" s="21">
-        <f>IF(C3=0,"",C59/C3)</f>
-        <v>12281</v>
+        <f>IF(C4=0,"",C13/C4)</f>
+        <v>12614</v>
       </c>
       <c r="D84" s="21">
-        <f>IF(D3=0,"",D59/D3)</f>
-        <v>10255</v>
+        <f>IF(D4=0,"",D13/D4)</f>
+        <v>12615</v>
       </c>
       <c r="E84" s="21">
-        <f>IF(E3=0,"",E59/E3)</f>
-        <v>9485</v>
+        <f>IF(E4=0,"",E13/E4)</f>
+        <v>12691</v>
       </c>
       <c r="F84" s="21">
-        <f>IF(F3=0,"",F59/F3)</f>
-        <v>9345</v>
+        <f>IF(F4=0,"",F13/F4)</f>
+        <v>12961</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
@@ -4634,24 +4623,24 @@
         <v>204</v>
       </c>
       <c r="B85" s="21">
-        <f>B56+B58</f>
-        <v>1161865</v>
+        <f>IF(B4=0,"",B60/B4)</f>
+        <v>14224</v>
       </c>
       <c r="C85" s="21">
-        <f>C56+C58</f>
-        <v>1568426</v>
+        <f>IF(C4=0,"",C60/C4)</f>
+        <v>12281</v>
       </c>
       <c r="D85" s="21">
-        <f>D56+D58</f>
-        <v>1885847</v>
+        <f>IF(D4=0,"",D60/D4)</f>
+        <v>10255</v>
       </c>
       <c r="E85" s="21">
-        <f>E56+E58</f>
-        <v>2117730</v>
+        <f>IF(E4=0,"",E60/E4)</f>
+        <v>9485</v>
       </c>
       <c r="F85" s="21">
-        <f>F56+F58</f>
-        <v>2183268</v>
+        <f>IF(F4=0,"",F60/F4)</f>
+        <v>9345</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
@@ -4659,24 +4648,24 @@
         <v>205</v>
       </c>
       <c r="B86" s="21">
-        <f>IF(B3=0,"",B57/B3)</f>
-        <v>4542</v>
+        <f>B57+B59</f>
+        <v>1161865</v>
       </c>
       <c r="C86" s="21">
-        <f>IF(C3=0,"",C57/C3)</f>
-        <v>4439</v>
+        <f>C57+C59</f>
+        <v>1568426</v>
       </c>
       <c r="D86" s="21">
-        <f>IF(D3=0,"",D57/D3)</f>
-        <v>3968</v>
+        <f>D57+D59</f>
+        <v>1885847</v>
       </c>
       <c r="E86" s="21">
-        <f>IF(E3=0,"",E57/E3)</f>
-        <v>3838</v>
+        <f>E57+E59</f>
+        <v>2117730</v>
       </c>
       <c r="F86" s="21">
-        <f>IF(F3=0,"",F57/F3)</f>
-        <v>3887</v>
+        <f>F57+F59</f>
+        <v>2183268</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
@@ -4684,65 +4673,91 @@
         <v>206</v>
       </c>
       <c r="B87" s="21">
-        <f>IF(B3=0,"",B83-B86)</f>
+        <f>IF(B4=0,"",B58/B4)</f>
+        <v>4542</v>
+      </c>
+      <c r="C87" s="21">
+        <f>IF(C4=0,"",C58/C4)</f>
+        <v>4439</v>
+      </c>
+      <c r="D87" s="21">
+        <f>IF(D4=0,"",D58/D4)</f>
+        <v>3968</v>
+      </c>
+      <c r="E87" s="21">
+        <f>IF(E4=0,"",E58/E4)</f>
+        <v>3838</v>
+      </c>
+      <c r="F87" s="21">
+        <f>IF(F4=0,"",F58/F4)</f>
+        <v>3887</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A88" s="13" t="s">
+        <v>207</v>
+      </c>
+      <c r="B88" s="21">
+        <f>IF(B4=0,"",B84-B87)</f>
         <v>6194</v>
       </c>
-      <c r="C87" s="21">
-        <f>IF(C3=0,"",C83-C86)</f>
+      <c r="C88" s="21">
+        <f>IF(C4=0,"",C84-C87)</f>
         <v>8175</v>
       </c>
-      <c r="D87" s="21">
-        <f>IF(D3=0,"",D83-D86)</f>
+      <c r="D88" s="21">
+        <f>IF(D4=0,"",D84-D87)</f>
         <v>8647</v>
       </c>
-      <c r="E87" s="21">
-        <f>IF(E3=0,"",E83-E86)</f>
+      <c r="E88" s="21">
+        <f>IF(E4=0,"",E84-E87)</f>
         <v>8853</v>
       </c>
-      <c r="F87" s="21">
-        <f>IF(F3=0,"",F83-F86)</f>
+      <c r="F88" s="21">
+        <f>IF(F4=0,"",F84-F87)</f>
         <v>9074</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A88" s="40" t="s">
-        <v>207</v>
-      </c>
-      <c r="B88" s="41">
-        <f>IF(B87&lt;=0,"N/A",ROUNDUP(B85/B87,0))</f>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A89" s="41" t="s">
+        <v>208</v>
+      </c>
+      <c r="B89" s="42">
+        <f>IF(B88&lt;=0,"N/A",ROUNDUP(B86/B88,0))</f>
         <v>188</v>
       </c>
-      <c r="C88" s="41">
-        <f>IF(C87&lt;=0,"N/A",ROUNDUP(C85/C87,0))</f>
+      <c r="C89" s="42">
+        <f>IF(C88&lt;=0,"N/A",ROUNDUP(C86/C88,0))</f>
         <v>192</v>
       </c>
-      <c r="D88" s="41">
-        <f>IF(D87&lt;=0,"N/A",ROUNDUP(D85/D87,0))</f>
+      <c r="D89" s="42">
+        <f>IF(D88&lt;=0,"N/A",ROUNDUP(D86/D88,0))</f>
         <v>219</v>
       </c>
-      <c r="E88" s="41">
-        <f>IF(E87&lt;=0,"N/A",ROUNDUP(E85/E87,0))</f>
+      <c r="E89" s="42">
+        <f>IF(E88&lt;=0,"N/A",ROUNDUP(E86/E88,0))</f>
         <v>240</v>
       </c>
-      <c r="F88" s="41">
-        <f>IF(F87&lt;=0,"N/A",ROUNDUP(F85/F87,0))</f>
+      <c r="F89" s="42">
+        <f>IF(F88&lt;=0,"N/A",ROUNDUP(F86/F88,0))</f>
         <v>241</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A90" s="24" t="s">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A91" s="24" t="s">
         <v>144</v>
       </c>
-      <c r="B90" s="24"/>
-      <c r="C90" s="24"/>
-      <c r="D90" s="24"/>
-      <c r="E90" s="24"/>
-      <c r="F90" s="24"/>
+      <c r="B91" s="24"/>
+      <c r="C91" s="24"/>
+      <c r="D91" s="24"/>
+      <c r="E91" s="24"/>
+      <c r="F91" s="24"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A90:F90"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A91:F91"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>
@@ -4768,7 +4783,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -4785,52 +4800,52 @@
       <c r="N1" s="8"/>
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="25" t="s">
+      <c r="B2" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="C2" s="25" t="s">
-        <v>209</v>
-      </c>
-      <c r="D2" s="25" t="s">
+      <c r="C2" s="26" t="s">
         <v>210</v>
       </c>
-      <c r="E2" s="25" t="s">
+      <c r="D2" s="26" t="s">
         <v>211</v>
       </c>
-      <c r="F2" s="25" t="s">
+      <c r="E2" s="26" t="s">
         <v>212</v>
       </c>
-      <c r="G2" s="25" t="s">
+      <c r="F2" s="26" t="s">
         <v>213</v>
       </c>
-      <c r="H2" s="25" t="s">
+      <c r="G2" s="26" t="s">
         <v>214</v>
       </c>
-      <c r="I2" s="25" t="s">
+      <c r="H2" s="26" t="s">
         <v>215</v>
       </c>
-      <c r="J2" s="25" t="s">
+      <c r="I2" s="26" t="s">
         <v>216</v>
       </c>
-      <c r="K2" s="25" t="s">
+      <c r="J2" s="26" t="s">
         <v>217</v>
       </c>
-      <c r="L2" s="25" t="s">
+      <c r="K2" s="26" t="s">
         <v>218</v>
       </c>
-      <c r="M2" s="25" t="s">
+      <c r="L2" s="26" t="s">
         <v>219</v>
       </c>
-      <c r="N2" s="25" t="s">
+      <c r="M2" s="26" t="s">
         <v>220</v>
+      </c>
+      <c r="N2" s="26" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B3" s="12"/>
       <c r="C3" s="12"/>
@@ -5118,57 +5133,57 @@
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
-        <v>147</v>
-      </c>
-      <c r="B10" s="28">
+        <v>148</v>
+      </c>
+      <c r="B10" s="29">
         <f>SUM(B4:B9)</f>
         <v>154600</v>
       </c>
-      <c r="C10" s="28">
+      <c r="C10" s="29">
         <f>SUM(C4:C9)</f>
         <v>154600</v>
       </c>
-      <c r="D10" s="28">
+      <c r="D10" s="29">
         <f>SUM(D4:D9)</f>
         <v>154600</v>
       </c>
-      <c r="E10" s="28">
+      <c r="E10" s="29">
         <f>SUM(E4:E9)</f>
         <v>154600</v>
       </c>
-      <c r="F10" s="28">
+      <c r="F10" s="29">
         <f>SUM(F4:F9)</f>
         <v>154600</v>
       </c>
-      <c r="G10" s="28">
+      <c r="G10" s="29">
         <f>SUM(G4:G9)</f>
         <v>154600</v>
       </c>
-      <c r="H10" s="28">
+      <c r="H10" s="29">
         <f>SUM(H4:H9)</f>
         <v>154600</v>
       </c>
-      <c r="I10" s="28">
+      <c r="I10" s="29">
         <f>SUM(I4:I9)</f>
         <v>154600</v>
       </c>
-      <c r="J10" s="28">
+      <c r="J10" s="29">
         <f>SUM(J4:J9)</f>
         <v>154600</v>
       </c>
-      <c r="K10" s="28">
+      <c r="K10" s="29">
         <f>SUM(K4:K9)</f>
         <v>154600</v>
       </c>
-      <c r="L10" s="28" t="str">
+      <c r="L10" s="29" t="str">
         <f>SUM(L4:L9)</f>
         <v>0</v>
       </c>
-      <c r="M10" s="28" t="str">
+      <c r="M10" s="29" t="str">
         <f>SUM(M4:M9)</f>
         <v>0</v>
       </c>
-      <c r="N10" s="28">
+      <c r="N10" s="29">
         <f>SUM(B10:M10)</f>
         <v>1546000</v>
       </c>
@@ -5180,7 +5195,7 @@
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B12" s="12"/>
       <c r="C12" s="12"/>
@@ -5603,57 +5618,57 @@
     </row>
     <row r="22" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="B22" s="28">
+        <v>159</v>
+      </c>
+      <c r="B22" s="29">
         <f>SUM(B13:B21)</f>
         <v>99704</v>
       </c>
-      <c r="C22" s="28">
+      <c r="C22" s="29">
         <f>SUM(C13:C21)</f>
         <v>99704</v>
       </c>
-      <c r="D22" s="28">
+      <c r="D22" s="29">
         <f>SUM(D13:D21)</f>
         <v>99704</v>
       </c>
-      <c r="E22" s="28">
+      <c r="E22" s="29">
         <f>SUM(E13:E21)</f>
         <v>99704</v>
       </c>
-      <c r="F22" s="28">
+      <c r="F22" s="29">
         <f>SUM(F13:F21)</f>
         <v>99704</v>
       </c>
-      <c r="G22" s="28">
+      <c r="G22" s="29">
         <f>SUM(G13:G21)</f>
         <v>99704</v>
       </c>
-      <c r="H22" s="28">
+      <c r="H22" s="29">
         <f>SUM(H13:H21)</f>
         <v>99704</v>
       </c>
-      <c r="I22" s="28">
+      <c r="I22" s="29">
         <f>SUM(I13:I21)</f>
         <v>99704</v>
       </c>
-      <c r="J22" s="28">
+      <c r="J22" s="29">
         <f>SUM(J13:J21)</f>
         <v>99704</v>
       </c>
-      <c r="K22" s="28">
+      <c r="K22" s="29">
         <f>SUM(K13:K21)</f>
         <v>99704</v>
       </c>
-      <c r="L22" s="28" t="str">
+      <c r="L22" s="29" t="str">
         <f>SUM(L13:L21)</f>
         <v>0</v>
       </c>
-      <c r="M22" s="28" t="str">
+      <c r="M22" s="29" t="str">
         <f>SUM(M13:M21)</f>
         <v>0</v>
       </c>
-      <c r="N22" s="28">
+      <c r="N22" s="29">
         <f>SUM(B22:M22)</f>
         <v>997040</v>
       </c>
@@ -5701,7 +5716,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="13" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B26" s="21">
         <v>7000</v>
@@ -5745,46 +5760,46 @@
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A27" s="29" t="s">
-        <v>160</v>
-      </c>
-      <c r="B27" s="30">
+      <c r="A27" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="B27" s="31">
         <v>7000</v>
       </c>
-      <c r="C27" s="30">
+      <c r="C27" s="31">
         <v>7000</v>
       </c>
-      <c r="D27" s="30">
+      <c r="D27" s="31">
         <v>7000</v>
       </c>
-      <c r="E27" s="30">
+      <c r="E27" s="31">
         <v>7000</v>
       </c>
-      <c r="F27" s="30">
+      <c r="F27" s="31">
         <v>7000</v>
       </c>
-      <c r="G27" s="30">
+      <c r="G27" s="31">
         <v>7000</v>
       </c>
-      <c r="H27" s="30">
+      <c r="H27" s="31">
         <v>7000</v>
       </c>
-      <c r="I27" s="30">
+      <c r="I27" s="31">
         <v>7000</v>
       </c>
-      <c r="J27" s="30">
+      <c r="J27" s="31">
         <v>7000</v>
       </c>
-      <c r="K27" s="30">
+      <c r="K27" s="31">
         <v>7000</v>
       </c>
-      <c r="L27" s="30">
-        <v>0</v>
-      </c>
-      <c r="M27" s="30">
-        <v>0</v>
-      </c>
-      <c r="N27" s="30">
+      <c r="L27" s="31">
+        <v>0</v>
+      </c>
+      <c r="M27" s="31">
+        <v>0</v>
+      </c>
+      <c r="N27" s="31">
         <f>SUM(B27:M27)</f>
         <v>70000</v>
       </c>
@@ -5809,7 +5824,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="13" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B29" s="21">
         <v>5000</v>
@@ -5853,46 +5868,46 @@
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A30" s="29" t="s">
-        <v>162</v>
-      </c>
-      <c r="B30" s="30">
+      <c r="A30" s="30" t="s">
+        <v>163</v>
+      </c>
+      <c r="B30" s="31">
         <v>5000</v>
       </c>
-      <c r="C30" s="30">
+      <c r="C30" s="31">
         <v>5000</v>
       </c>
-      <c r="D30" s="30">
+      <c r="D30" s="31">
         <v>5000</v>
       </c>
-      <c r="E30" s="30">
+      <c r="E30" s="31">
         <v>5000</v>
       </c>
-      <c r="F30" s="30">
+      <c r="F30" s="31">
         <v>5000</v>
       </c>
-      <c r="G30" s="30">
+      <c r="G30" s="31">
         <v>5000</v>
       </c>
-      <c r="H30" s="30">
+      <c r="H30" s="31">
         <v>5000</v>
       </c>
-      <c r="I30" s="30">
+      <c r="I30" s="31">
         <v>5000</v>
       </c>
-      <c r="J30" s="30">
+      <c r="J30" s="31">
         <v>5000</v>
       </c>
-      <c r="K30" s="30">
+      <c r="K30" s="31">
         <v>5000</v>
       </c>
-      <c r="L30" s="30">
-        <v>0</v>
-      </c>
-      <c r="M30" s="30">
-        <v>0</v>
-      </c>
-      <c r="N30" s="30">
+      <c r="L30" s="31">
+        <v>0</v>
+      </c>
+      <c r="M30" s="31">
+        <v>0</v>
+      </c>
+      <c r="N30" s="31">
         <f>SUM(B30:M30)</f>
         <v>50000</v>
       </c>
@@ -5917,7 +5932,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="13" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B32" s="21">
         <v>18000</v>
@@ -5962,7 +5977,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="13" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B33" s="21">
         <v>2500</v>
@@ -6007,7 +6022,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="13" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B34" s="21">
         <v>1500</v>
@@ -6052,7 +6067,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="13" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B35" s="21">
         <v>1500</v>
@@ -6096,46 +6111,46 @@
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A36" s="29" t="s">
-        <v>167</v>
-      </c>
-      <c r="B36" s="30">
+      <c r="A36" s="30" t="s">
+        <v>168</v>
+      </c>
+      <c r="B36" s="31">
         <v>23500</v>
       </c>
-      <c r="C36" s="30">
+      <c r="C36" s="31">
         <v>23500</v>
       </c>
-      <c r="D36" s="30">
+      <c r="D36" s="31">
         <v>23500</v>
       </c>
-      <c r="E36" s="30">
+      <c r="E36" s="31">
         <v>23500</v>
       </c>
-      <c r="F36" s="30">
+      <c r="F36" s="31">
         <v>23500</v>
       </c>
-      <c r="G36" s="30">
+      <c r="G36" s="31">
         <v>23500</v>
       </c>
-      <c r="H36" s="30">
+      <c r="H36" s="31">
         <v>23500</v>
       </c>
-      <c r="I36" s="30">
+      <c r="I36" s="31">
         <v>23500</v>
       </c>
-      <c r="J36" s="30">
+      <c r="J36" s="31">
         <v>23500</v>
       </c>
-      <c r="K36" s="30">
+      <c r="K36" s="31">
         <v>23500</v>
       </c>
-      <c r="L36" s="30">
-        <v>0</v>
-      </c>
-      <c r="M36" s="30">
-        <v>0</v>
-      </c>
-      <c r="N36" s="30">
+      <c r="L36" s="31">
+        <v>0</v>
+      </c>
+      <c r="M36" s="31">
+        <v>0</v>
+      </c>
+      <c r="N36" s="31">
         <f>SUM(B36:M36)</f>
         <v>235000</v>
       </c>
@@ -6160,7 +6175,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="13" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B38" s="21">
         <v>2083</v>
@@ -6205,7 +6220,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="13" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B39" s="21">
         <v>1250</v>
@@ -6250,7 +6265,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="13" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B40" s="21">
         <v>1667</v>
@@ -6295,7 +6310,7 @@
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" s="13" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B41" s="21">
         <v>8000</v>
@@ -6340,7 +6355,7 @@
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" s="13" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B42" s="21">
         <v>6000</v>
@@ -6384,103 +6399,103 @@
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A43" s="29" t="s">
-        <v>173</v>
-      </c>
-      <c r="B43" s="30">
+      <c r="A43" s="30" t="s">
+        <v>174</v>
+      </c>
+      <c r="B43" s="31">
         <v>19000</v>
       </c>
-      <c r="C43" s="30">
+      <c r="C43" s="31">
         <v>19000</v>
       </c>
-      <c r="D43" s="30">
+      <c r="D43" s="31">
         <v>19000</v>
       </c>
-      <c r="E43" s="30">
+      <c r="E43" s="31">
         <v>19000</v>
       </c>
-      <c r="F43" s="30">
+      <c r="F43" s="31">
         <v>19000</v>
       </c>
-      <c r="G43" s="30">
+      <c r="G43" s="31">
         <v>19000</v>
       </c>
-      <c r="H43" s="30">
+      <c r="H43" s="31">
         <v>19000</v>
       </c>
-      <c r="I43" s="30">
+      <c r="I43" s="31">
         <v>19000</v>
       </c>
-      <c r="J43" s="30">
+      <c r="J43" s="31">
         <v>19000</v>
       </c>
-      <c r="K43" s="30">
+      <c r="K43" s="31">
         <v>19000</v>
       </c>
-      <c r="L43" s="30">
-        <v>0</v>
-      </c>
-      <c r="M43" s="30">
-        <v>0</v>
-      </c>
-      <c r="N43" s="30">
+      <c r="L43" s="31">
+        <v>0</v>
+      </c>
+      <c r="M43" s="31">
+        <v>0</v>
+      </c>
+      <c r="N43" s="31">
         <f>SUM(B43:M43)</f>
         <v>190000</v>
       </c>
     </row>
     <row r="44" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" s="12" t="s">
-        <v>174</v>
-      </c>
-      <c r="B44" s="28">
+        <v>175</v>
+      </c>
+      <c r="B44" s="29">
         <f>B27+B30+B36+B43</f>
         <v>54500</v>
       </c>
-      <c r="C44" s="28">
+      <c r="C44" s="29">
         <f>C27+C30+C36+C43</f>
         <v>54500</v>
       </c>
-      <c r="D44" s="28">
+      <c r="D44" s="29">
         <f>D27+D30+D36+D43</f>
         <v>54500</v>
       </c>
-      <c r="E44" s="28">
+      <c r="E44" s="29">
         <f>E27+E30+E36+E43</f>
         <v>54500</v>
       </c>
-      <c r="F44" s="28">
+      <c r="F44" s="29">
         <f>F27+F30+F36+F43</f>
         <v>54500</v>
       </c>
-      <c r="G44" s="28">
+      <c r="G44" s="29">
         <f>G27+G30+G36+G43</f>
         <v>54500</v>
       </c>
-      <c r="H44" s="28">
+      <c r="H44" s="29">
         <f>H27+H30+H36+H43</f>
         <v>54500</v>
       </c>
-      <c r="I44" s="28">
+      <c r="I44" s="29">
         <f>I27+I30+I36+I43</f>
         <v>54500</v>
       </c>
-      <c r="J44" s="28">
+      <c r="J44" s="29">
         <f>J27+J30+J36+J43</f>
         <v>54500</v>
       </c>
-      <c r="K44" s="28">
+      <c r="K44" s="29">
         <f>K27+K30+K36+K43</f>
         <v>54500</v>
       </c>
-      <c r="L44" s="28" t="str">
+      <c r="L44" s="29" t="str">
         <f>L27+L30+L36+L43</f>
         <v>0</v>
       </c>
-      <c r="M44" s="28" t="str">
+      <c r="M44" s="29" t="str">
         <f>M27+M30+M36+M43</f>
         <v>0</v>
       </c>
-      <c r="N44" s="28">
+      <c r="N44" s="29">
         <f>SUM(B44:M44)</f>
         <v>545000</v>
       </c>
@@ -6491,8 +6506,8 @@
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A46" s="26" t="s">
-        <v>232</v>
+      <c r="A46" s="27" t="s">
+        <v>233</v>
       </c>
       <c r="B46" s="21">
         <v>13735</v>
@@ -6542,7 +6557,7 @@
     </row>
     <row r="48" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" s="12" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B48" s="12"/>
       <c r="C48" s="12"/>
@@ -6559,179 +6574,179 @@
       <c r="N48" s="12"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A49" s="26" t="s">
-        <v>182</v>
-      </c>
-      <c r="B49" s="30">
+      <c r="A49" s="27" t="s">
+        <v>183</v>
+      </c>
+      <c r="B49" s="31">
         <f>B22+B44+B46</f>
         <v>167939</v>
       </c>
-      <c r="C49" s="30">
+      <c r="C49" s="31">
         <f>C22+C44+C46</f>
         <v>167939</v>
       </c>
-      <c r="D49" s="30">
+      <c r="D49" s="31">
         <f>D22+D44+D46</f>
         <v>167939</v>
       </c>
-      <c r="E49" s="30">
+      <c r="E49" s="31">
         <f>E22+E44+E46</f>
         <v>167939</v>
       </c>
-      <c r="F49" s="30">
+      <c r="F49" s="31">
         <f>F22+F44+F46</f>
         <v>167939</v>
       </c>
-      <c r="G49" s="30">
+      <c r="G49" s="31">
         <f>G22+G44+G46</f>
         <v>167939</v>
       </c>
-      <c r="H49" s="30">
+      <c r="H49" s="31">
         <f>H22+H44+H46</f>
         <v>167939</v>
       </c>
-      <c r="I49" s="30">
+      <c r="I49" s="31">
         <f>I22+I44+I46</f>
         <v>167939</v>
       </c>
-      <c r="J49" s="30">
+      <c r="J49" s="31">
         <f>J22+J44+J46</f>
         <v>167939</v>
       </c>
-      <c r="K49" s="30">
+      <c r="K49" s="31">
         <f>K22+K44+K46</f>
         <v>167939</v>
       </c>
-      <c r="L49" s="30">
+      <c r="L49" s="31">
         <f>L22+L44+L46</f>
         <v>13735</v>
       </c>
-      <c r="M49" s="30">
+      <c r="M49" s="31">
         <f>M22+M44+M46</f>
         <v>13735</v>
       </c>
-      <c r="N49" s="30">
+      <c r="N49" s="31">
         <f>SUM(B49:M49)</f>
         <v>1706860</v>
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A50" s="26" t="s">
-        <v>234</v>
-      </c>
-      <c r="B50" s="30">
+      <c r="A50" s="27" t="s">
+        <v>235</v>
+      </c>
+      <c r="B50" s="31">
         <f>B10-B49</f>
         <v>-13339</v>
       </c>
-      <c r="C50" s="30">
+      <c r="C50" s="31">
         <f>C10-C49</f>
         <v>-13339</v>
       </c>
-      <c r="D50" s="30">
+      <c r="D50" s="31">
         <f>D10-D49</f>
         <v>-13339</v>
       </c>
-      <c r="E50" s="30">
+      <c r="E50" s="31">
         <f>E10-E49</f>
         <v>-13339</v>
       </c>
-      <c r="F50" s="30">
+      <c r="F50" s="31">
         <f>F10-F49</f>
         <v>-13339</v>
       </c>
-      <c r="G50" s="30">
+      <c r="G50" s="31">
         <f>G10-G49</f>
         <v>-13339</v>
       </c>
-      <c r="H50" s="30">
+      <c r="H50" s="31">
         <f>H10-H49</f>
         <v>-13339</v>
       </c>
-      <c r="I50" s="30">
+      <c r="I50" s="31">
         <f>I10-I49</f>
         <v>-13339</v>
       </c>
-      <c r="J50" s="30">
+      <c r="J50" s="31">
         <f>J10-J49</f>
         <v>-13339</v>
       </c>
-      <c r="K50" s="30">
+      <c r="K50" s="31">
         <f>K10-K49</f>
         <v>-13339</v>
       </c>
-      <c r="L50" s="30">
+      <c r="L50" s="31">
         <f>L10-L49</f>
         <v>-13735</v>
       </c>
-      <c r="M50" s="30">
+      <c r="M50" s="31">
         <f>M10-M49</f>
         <v>-13735</v>
       </c>
-      <c r="N50" s="30">
+      <c r="N50" s="31">
         <f>SUM(B50:M50)</f>
         <v>-160860</v>
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A51" s="26" t="s">
-        <v>235</v>
-      </c>
-      <c r="B51" s="30">
+      <c r="A51" s="27" t="s">
+        <v>236</v>
+      </c>
+      <c r="B51" s="31">
         <f>0+B50</f>
         <v>-13339</v>
       </c>
-      <c r="C51" s="30">
+      <c r="C51" s="31">
         <f>B51+C50</f>
         <v>-26678</v>
       </c>
-      <c r="D51" s="30">
+      <c r="D51" s="31">
         <f>C51+D50</f>
         <v>-40017</v>
       </c>
-      <c r="E51" s="30">
+      <c r="E51" s="31">
         <f>D51+E50</f>
         <v>-53356</v>
       </c>
-      <c r="F51" s="30">
+      <c r="F51" s="31">
         <f>E51+F50</f>
         <v>-66695</v>
       </c>
-      <c r="G51" s="30">
+      <c r="G51" s="31">
         <f>F51+G50</f>
         <v>-80034</v>
       </c>
-      <c r="H51" s="30">
+      <c r="H51" s="31">
         <f>G51+H50</f>
         <v>-93373</v>
       </c>
-      <c r="I51" s="30">
+      <c r="I51" s="31">
         <f>H51+I50</f>
         <v>-106712</v>
       </c>
-      <c r="J51" s="30">
+      <c r="J51" s="31">
         <f>I51+J50</f>
         <v>-120051</v>
       </c>
-      <c r="K51" s="30">
+      <c r="K51" s="31">
         <f>J51+K50</f>
         <v>-133390</v>
       </c>
-      <c r="L51" s="30">
+      <c r="L51" s="31">
         <f>K51+L50</f>
         <v>-147125</v>
       </c>
-      <c r="M51" s="30">
+      <c r="M51" s="31">
         <f>L51+M50</f>
         <v>-160860</v>
       </c>
-      <c r="N51" s="30">
+      <c r="N51" s="31">
         <f>M51</f>
         <v>-160860</v>
       </c>
     </row>
     <row r="53" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="12" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B53" s="12"/>
       <c r="C53" s="12"/>
@@ -6746,16 +6761,16 @@
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" s="13" t="s">
-        <v>237</v>
-      </c>
-      <c r="B55" s="30">
+        <v>238</v>
+      </c>
+      <c r="B55" s="31">
         <f>M51</f>
         <v>-160860</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" s="13" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B56" s="21">
         <f>MIN(B51:M51)</f>
@@ -6812,7 +6827,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -6822,662 +6837,662 @@
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="42" t="s">
-        <v>240</v>
-      </c>
-      <c r="C3" s="42"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="42"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="42"/>
-      <c r="H3" s="42"/>
+      <c r="B3" s="43" t="s">
+        <v>241</v>
+      </c>
+      <c r="C3" s="43"/>
+      <c r="D3" s="43"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="43"/>
+      <c r="G3" s="43"/>
+      <c r="H3" s="43"/>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="43" t="s">
-        <v>241</v>
-      </c>
-      <c r="D4" s="44" t="s">
+      <c r="B4" s="44" t="s">
         <v>242</v>
       </c>
-      <c r="F4" s="45" t="s">
+      <c r="D4" s="45" t="s">
         <v>243</v>
+      </c>
+      <c r="F4" s="46" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B6" s="12" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E6" s="16" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F6" s="16" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G6" s="16" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H6" s="16" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="13" t="s">
-        <v>251</v>
-      </c>
-      <c r="C7" s="46">
+        <v>252</v>
+      </c>
+      <c r="C7" s="47">
         <v>120</v>
       </c>
-      <c r="D7" s="46">
+      <c r="D7" s="47">
         <v>200</v>
       </c>
-      <c r="E7" s="46">
+      <c r="E7" s="47">
         <v>300</v>
       </c>
-      <c r="F7" s="46">
+      <c r="F7" s="47">
         <v>375</v>
       </c>
-      <c r="G7" s="46">
+      <c r="G7" s="47">
         <v>400</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="13" t="s">
-        <v>252</v>
-      </c>
-      <c r="C8" s="47">
+        <v>253</v>
+      </c>
+      <c r="C8" s="48">
         <v>1546000</v>
       </c>
-      <c r="D8" s="47">
+      <c r="D8" s="48">
         <v>2522800</v>
       </c>
-      <c r="E8" s="47">
+      <c r="E8" s="48">
         <v>3784600</v>
       </c>
-      <c r="F8" s="47">
+      <c r="F8" s="48">
         <v>4759125</v>
       </c>
-      <c r="G8" s="47">
+      <c r="G8" s="48">
         <v>5184400</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="13" t="s">
-        <v>253</v>
-      </c>
-      <c r="C9" s="47">
+        <v>254</v>
+      </c>
+      <c r="C9" s="48">
         <v>1026431.25</v>
       </c>
-      <c r="D9" s="47">
+      <c r="D9" s="48">
         <v>1231717.5</v>
       </c>
-      <c r="E9" s="47">
+      <c r="E9" s="48">
         <v>1231717.5</v>
       </c>
-      <c r="F9" s="47">
+      <c r="F9" s="48">
         <v>1231717.5</v>
       </c>
-      <c r="G9" s="47">
+      <c r="G9" s="48">
         <v>1231717.5</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="13" t="s">
-        <v>254</v>
-      </c>
-      <c r="C10" s="47">
-        <v>654000</v>
-      </c>
-      <c r="D10" s="47">
-        <v>887860</v>
-      </c>
-      <c r="E10" s="47">
-        <v>1190521.4</v>
-      </c>
-      <c r="F10" s="47">
-        <v>1439089.0320000001</v>
-      </c>
-      <c r="G10" s="47">
-        <v>1554923.90296</v>
+        <v>255</v>
+      </c>
+      <c r="C10" s="48">
+        <v>552000</v>
+      </c>
+      <c r="D10" s="48">
+        <v>819880</v>
+      </c>
+      <c r="E10" s="48">
+        <v>1120509.4</v>
+      </c>
+      <c r="F10" s="48">
+        <v>1366968.0320000001</v>
+      </c>
+      <c r="G10" s="48">
+        <v>1480640.90296</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="13" t="s">
-        <v>190</v>
-      </c>
-      <c r="C11" s="47">
+        <v>191</v>
+      </c>
+      <c r="C11" s="48">
         <v>49824.605221179416</v>
       </c>
-      <c r="D11" s="47">
+      <c r="D11" s="48">
         <v>49824.605221179416</v>
       </c>
-      <c r="E11" s="47">
+      <c r="E11" s="48">
         <v>49824.605221179416</v>
       </c>
-      <c r="F11" s="47">
+      <c r="F11" s="48">
         <v>49824.605221179416</v>
       </c>
-      <c r="G11" s="47">
+      <c r="G11" s="48">
         <v>49824.605221179416</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="26" t="s">
-        <v>183</v>
-      </c>
-      <c r="C12" s="48">
-        <v>-184255.85522117943</v>
-      </c>
-      <c r="D12" s="49">
-        <v>353397.89477882057</v>
-      </c>
-      <c r="E12" s="49">
-        <v>1312536.4947788208</v>
-      </c>
-      <c r="F12" s="49">
-        <v>2038493.8627788206</v>
-      </c>
-      <c r="G12" s="49">
-        <v>2347933.9918188206</v>
+      <c r="B12" s="27" t="s">
+        <v>184</v>
+      </c>
+      <c r="C12" s="49">
+        <v>-82255.85522117942</v>
+      </c>
+      <c r="D12" s="50">
+        <v>421377.89477882057</v>
+      </c>
+      <c r="E12" s="50">
+        <v>1382548.4947788208</v>
+      </c>
+      <c r="F12" s="50">
+        <v>2110614.8627788206</v>
+      </c>
+      <c r="G12" s="50">
+        <v>2422216.9918188206</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="26" t="s">
-        <v>192</v>
-      </c>
-      <c r="C13" s="48">
-        <v>-184255.85522117943</v>
-      </c>
-      <c r="D13" s="49">
-        <v>169142.03955764114</v>
-      </c>
-      <c r="E13" s="49">
-        <v>1481678.534336462</v>
-      </c>
-      <c r="F13" s="49">
-        <v>3520172.3971152827</v>
-      </c>
-      <c r="G13" s="49">
-        <v>5868106.388934104</v>
+      <c r="B13" s="27" t="s">
+        <v>193</v>
+      </c>
+      <c r="C13" s="49">
+        <v>-82255.85522117942</v>
+      </c>
+      <c r="D13" s="50">
+        <v>339122.03955764114</v>
+      </c>
+      <c r="E13" s="50">
+        <v>1721670.534336462</v>
+      </c>
+      <c r="F13" s="50">
+        <v>3832285.3971152827</v>
+      </c>
+      <c r="G13" s="50">
+        <v>6254502.388934104</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="26" t="s">
-        <v>255</v>
-      </c>
-      <c r="C14" s="50">
-        <v>-0.11918231256221179</v>
-      </c>
-      <c r="D14" s="51">
-        <v>0.14008161359553692</v>
-      </c>
-      <c r="E14" s="51">
-        <v>0.34680983321323805</v>
-      </c>
-      <c r="F14" s="51">
-        <v>0.4283337510107048</v>
-      </c>
-      <c r="G14" s="51">
-        <v>0.4528844209202262</v>
+      <c r="B14" s="27" t="s">
+        <v>256</v>
+      </c>
+      <c r="C14" s="51">
+        <v>-0.05320559846130622</v>
+      </c>
+      <c r="D14" s="52">
+        <v>0.16702786379372941</v>
+      </c>
+      <c r="E14" s="52">
+        <v>0.3653090141042173</v>
+      </c>
+      <c r="F14" s="52">
+        <v>0.44348800730781823</v>
+      </c>
+      <c r="G14" s="52">
+        <v>0.4672125977584331</v>
       </c>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B15" s="26" t="s">
-        <v>256</v>
-      </c>
-      <c r="C15" s="52">
+      <c r="B15" s="27" t="s">
+        <v>257</v>
+      </c>
+      <c r="C15" s="53">
         <v>12883.333333333334</v>
       </c>
-      <c r="D15" s="52">
+      <c r="D15" s="53">
         <v>12614</v>
       </c>
-      <c r="E15" s="52">
+      <c r="E15" s="53">
         <v>12615.333333333334</v>
       </c>
-      <c r="F15" s="52">
+      <c r="F15" s="53">
         <v>12691</v>
       </c>
-      <c r="G15" s="52">
+      <c r="G15" s="53">
         <v>12961</v>
       </c>
-      <c r="H15" s="53" t="s">
-        <v>257</v>
+      <c r="H15" s="54" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="26" t="s">
-        <v>258</v>
-      </c>
-      <c r="C16" s="54">
-        <v>14418.798793509828</v>
-      </c>
-      <c r="D16" s="54">
-        <v>10847.010526105896</v>
-      </c>
-      <c r="E16" s="54">
-        <v>8240.211684070597</v>
-      </c>
-      <c r="F16" s="54">
-        <v>7255.016365923145</v>
-      </c>
-      <c r="G16" s="54">
-        <v>7091.165020452949</v>
+      <c r="B16" s="27" t="s">
+        <v>259</v>
+      </c>
+      <c r="C16" s="55">
+        <v>13568.798793509828</v>
+      </c>
+      <c r="D16" s="55">
+        <v>10507.110526105896</v>
+      </c>
+      <c r="E16" s="55">
+        <v>8006.838350737264</v>
+      </c>
+      <c r="F16" s="55">
+        <v>7062.693699256479</v>
+      </c>
+      <c r="G16" s="55">
+        <v>6905.457520452948</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="13" t="s">
-        <v>259</v>
-      </c>
-      <c r="C17" s="47">
+        <v>260</v>
+      </c>
+      <c r="C17" s="48">
         <v>700</v>
       </c>
-      <c r="D17" s="47">
+      <c r="D17" s="48">
         <v>721</v>
       </c>
-      <c r="E17" s="47">
+      <c r="E17" s="48">
         <v>743</v>
       </c>
-      <c r="F17" s="47">
+      <c r="F17" s="48">
         <v>765</v>
       </c>
-      <c r="G17" s="47">
+      <c r="G17" s="48">
         <v>788</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" s="13" t="s">
-        <v>260</v>
-      </c>
-      <c r="C18" s="55">
-        <v>2350</v>
-      </c>
-      <c r="D18" s="52">
-        <v>1452.3</v>
-      </c>
-      <c r="E18" s="52">
-        <v>997.2213333333334</v>
-      </c>
-      <c r="F18" s="52">
-        <v>821.7334186666667</v>
-      </c>
-      <c r="G18" s="52">
-        <v>793.4822574000001</v>
-      </c>
-      <c r="H18" s="53" t="s">
         <v>261</v>
       </c>
+      <c r="C18" s="53">
+        <v>1500</v>
+      </c>
+      <c r="D18" s="53">
+        <v>1112.4</v>
+      </c>
+      <c r="E18" s="53">
+        <v>763.848</v>
+      </c>
+      <c r="F18" s="53">
+        <v>629.410752</v>
+      </c>
+      <c r="G18" s="53">
+        <v>607.7747574000001</v>
+      </c>
+      <c r="H18" s="54" t="s">
+        <v>262</v>
+      </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="26" t="s">
+      <c r="B19" s="27" t="s">
+        <v>263</v>
+      </c>
+      <c r="C19" s="56">
+        <v>-685.4654601764952</v>
+      </c>
+      <c r="D19" s="57">
+        <v>2106.889473894103</v>
+      </c>
+      <c r="E19" s="57">
+        <v>4608.494982596069</v>
+      </c>
+      <c r="F19" s="57">
+        <v>5628.306300743521</v>
+      </c>
+      <c r="G19" s="57">
+        <v>6055.542479547052</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B20" s="27" t="s">
+        <v>264</v>
+      </c>
+      <c r="C20" s="51">
+        <v>0.6639270698576973</v>
+      </c>
+      <c r="D20" s="52">
+        <v>0.48823430315522437</v>
+      </c>
+      <c r="E20" s="52">
+        <v>0.3254551339639592</v>
+      </c>
+      <c r="F20" s="52">
+        <v>0.25881175636277676</v>
+      </c>
+      <c r="G20" s="52">
+        <v>0.23758149448345034</v>
+      </c>
+      <c r="H20" s="54" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B21" s="27" t="s">
+        <v>266</v>
+      </c>
+      <c r="C21" s="52">
+        <v>0.11642949547218628</v>
+      </c>
+      <c r="D21" s="52">
+        <v>0.08818772792135722</v>
+      </c>
+      <c r="E21" s="52">
+        <v>0.060549172964117735</v>
+      </c>
+      <c r="F21" s="52">
+        <v>0.04959504782917028</v>
+      </c>
+      <c r="G21" s="52">
+        <v>0.046892582161870235</v>
+      </c>
+      <c r="H21" s="54" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B22" s="27" t="s">
+        <v>268</v>
+      </c>
+      <c r="C22" s="51">
+        <v>-0.020977522639068564</v>
+      </c>
+      <c r="D22" s="52">
+        <v>0.18677758839384812</v>
+      </c>
+      <c r="E22" s="52">
+        <v>0.3784741055857951</v>
+      </c>
+      <c r="F22" s="52">
+        <v>0.45395728584561235</v>
+      </c>
+      <c r="G22" s="52">
+        <v>0.47682308406758733</v>
+      </c>
+      <c r="H22" s="54" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="27" t="s">
+        <v>270</v>
+      </c>
+      <c r="C23" s="58">
+        <v>3</v>
+      </c>
+      <c r="D23" s="58">
+        <v>3</v>
+      </c>
+      <c r="E23" s="58">
+        <v>3</v>
+      </c>
+      <c r="F23" s="58">
+        <v>3</v>
+      </c>
+      <c r="G23" s="58">
+        <v>3</v>
+      </c>
+      <c r="H23" s="54" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="27" t="s">
+        <v>272</v>
+      </c>
+      <c r="C24" s="59">
+        <v>-0.6509083184108029</v>
+      </c>
+      <c r="D24" s="60">
+        <v>9.457224957593874</v>
+      </c>
+      <c r="E24" s="60">
+        <v>28.748308062682405</v>
+      </c>
+      <c r="F24" s="60">
+        <v>43.36089485123791</v>
+      </c>
+      <c r="G24" s="60">
+        <v>49.614875743946406</v>
+      </c>
+      <c r="H24" s="54" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="27" t="s">
+        <v>274</v>
+      </c>
+      <c r="C25" s="61" t="str">
+        <f>IF('5-Year Model'!B64&gt;=0,"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="D25" s="37" t="str">
+        <f>IF(AND('5-Year Model'!C64&gt;=0,'5-Year Model'!B64&lt;0),"✓ Break-even","")</f>
+        <v>✓ Break-even</v>
+      </c>
+      <c r="E25" s="61" t="str">
+        <f>IF(AND('5-Year Model'!D64&gt;=0,'5-Year Model'!C64&lt;0),"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="F25" s="61" t="str">
+        <f>IF(AND('5-Year Model'!E64&gt;=0,'5-Year Model'!D64&lt;0),"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="G25" s="61" t="str">
+        <f>IF(AND('5-Year Model'!F64&gt;=0,'5-Year Model'!E64&lt;0),"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="H25" s="54" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="27" t="s">
+        <v>275</v>
+      </c>
+      <c r="C26" s="62">
+        <v>-1</v>
+      </c>
+      <c r="D26" s="62">
+        <v>2</v>
+      </c>
+      <c r="E26" s="62">
+        <v>9</v>
+      </c>
+      <c r="F26" s="63">
+        <v>17</v>
+      </c>
+      <c r="G26" s="58">
+        <v>27</v>
+      </c>
+      <c r="H26" s="54" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="27" t="s">
+        <v>194</v>
+      </c>
+      <c r="C27" s="62">
+        <v>0</v>
+      </c>
+      <c r="D27" s="63">
+        <v>59</v>
+      </c>
+      <c r="E27" s="58">
         <v>262</v>
       </c>
-      <c r="C19" s="56">
-        <v>-1535.4654601764953</v>
-      </c>
-      <c r="D19" s="57">
-        <v>1766.989473894103</v>
-      </c>
-      <c r="E19" s="57">
-        <v>4375.121649262736</v>
-      </c>
-      <c r="F19" s="57">
-        <v>5435.983634076855</v>
-      </c>
-      <c r="G19" s="57">
-        <v>5869.834979547051</v>
-      </c>
-    </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B20" s="26" t="s">
-        <v>263</v>
-      </c>
-      <c r="C20" s="50">
-        <v>0.6639270698576973</v>
-      </c>
-      <c r="D20" s="51">
-        <v>0.48823430315522437</v>
-      </c>
-      <c r="E20" s="51">
-        <v>0.3254551339639592</v>
-      </c>
-      <c r="F20" s="51">
-        <v>0.25881175636277676</v>
-      </c>
-      <c r="G20" s="51">
-        <v>0.23758149448345034</v>
-      </c>
-      <c r="H20" s="53" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B21" s="26" t="s">
-        <v>265</v>
-      </c>
-      <c r="C21" s="58">
-        <v>0.18240620957309184</v>
-      </c>
-      <c r="D21" s="51">
-        <v>0.1151339781195497</v>
-      </c>
-      <c r="E21" s="51">
-        <v>0.07904835385509698</v>
-      </c>
-      <c r="F21" s="51">
-        <v>0.06474930412628371</v>
-      </c>
-      <c r="G21" s="51">
-        <v>0.06122075900007716</v>
-      </c>
-      <c r="H21" s="53" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B22" s="26" t="s">
-        <v>267</v>
-      </c>
-      <c r="C22" s="50">
-        <v>-0.08695423673997413</v>
-      </c>
-      <c r="D22" s="51">
-        <v>0.15983133819565562</v>
-      </c>
-      <c r="E22" s="51">
-        <v>0.35997492469481585</v>
-      </c>
-      <c r="F22" s="51">
-        <v>0.4388030295484989</v>
-      </c>
-      <c r="G22" s="51">
-        <v>0.4624949072293804</v>
-      </c>
-      <c r="H22" s="53" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B23" s="26" t="s">
-        <v>269</v>
-      </c>
-      <c r="C23" s="59">
-        <v>3</v>
-      </c>
-      <c r="D23" s="59">
-        <v>3</v>
-      </c>
-      <c r="E23" s="59">
-        <v>3</v>
-      </c>
-      <c r="F23" s="59">
-        <v>3</v>
-      </c>
-      <c r="G23" s="59">
-        <v>3</v>
-      </c>
-      <c r="H23" s="53" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B24" s="26" t="s">
-        <v>271</v>
-      </c>
-      <c r="C24" s="60">
-        <v>-2.698089616630942</v>
-      </c>
-      <c r="D24" s="61">
-        <v>8.092838833544805</v>
-      </c>
-      <c r="E24" s="61">
-        <v>27.34313887590801</v>
-      </c>
-      <c r="F24" s="61">
-        <v>41.91339718056208</v>
-      </c>
-      <c r="G24" s="61">
-        <v>48.12398585791026</v>
-      </c>
-      <c r="H24" s="53" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="26" t="s">
-        <v>273</v>
-      </c>
-      <c r="C25" s="62" t="str">
-        <f>IF('5-Year Model'!B63&gt;=0,"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="D25" s="36" t="str">
-        <f>IF(AND('5-Year Model'!C63&gt;=0,'5-Year Model'!B63&lt;0),"✓ Break-even","")</f>
-        <v>✓ Break-even</v>
-      </c>
-      <c r="E25" s="62" t="str">
-        <f>IF(AND('5-Year Model'!D63&gt;=0,'5-Year Model'!C63&lt;0),"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="F25" s="62" t="str">
-        <f>IF(AND('5-Year Model'!E63&gt;=0,'5-Year Model'!D63&lt;0),"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="G25" s="62" t="str">
-        <f>IF(AND('5-Year Model'!F63&gt;=0,'5-Year Model'!E63&lt;0),"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="H25" s="53" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="26" t="s">
-        <v>274</v>
-      </c>
-      <c r="C26" s="63">
-        <v>-1</v>
-      </c>
-      <c r="D26" s="63">
-        <v>1</v>
-      </c>
-      <c r="E26" s="63">
-        <v>7</v>
-      </c>
-      <c r="F26" s="64">
-        <v>16</v>
-      </c>
-      <c r="G26" s="59">
-        <v>25</v>
-      </c>
-      <c r="H26" s="53" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="26" t="s">
-        <v>193</v>
-      </c>
-      <c r="C27" s="63">
-        <v>0</v>
-      </c>
-      <c r="D27" s="63">
-        <v>28</v>
-      </c>
-      <c r="E27" s="59">
-        <v>219</v>
-      </c>
-      <c r="F27" s="59">
-        <v>472</v>
-      </c>
-      <c r="G27" s="59">
-        <v>755</v>
-      </c>
-      <c r="H27" s="53" t="s">
-        <v>276</v>
+      <c r="F27" s="58">
+        <v>528</v>
+      </c>
+      <c r="G27" s="58">
+        <v>826</v>
+      </c>
+      <c r="H27" s="54" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B29" s="12" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E29" s="12"/>
       <c r="F29" s="12" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="G29" s="12"/>
       <c r="H29" s="12"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="65" t="s">
-        <v>281</v>
-      </c>
-      <c r="C30" s="36" t="s">
+      <c r="B30" s="64" t="s">
         <v>282</v>
       </c>
-      <c r="D30" s="66" t="s">
+      <c r="C30" s="37" t="s">
         <v>283</v>
       </c>
-      <c r="E30" s="66"/>
-      <c r="F30" s="67" t="s">
+      <c r="D30" s="65" t="s">
         <v>284</v>
       </c>
-      <c r="G30" s="67"/>
-      <c r="H30" s="67"/>
+      <c r="E30" s="65"/>
+      <c r="F30" s="66" t="s">
+        <v>285</v>
+      </c>
+      <c r="G30" s="66"/>
+      <c r="H30" s="66"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="65" t="s">
-        <v>285</v>
-      </c>
-      <c r="C31" s="68" t="s">
+      <c r="B31" s="64" t="s">
         <v>286</v>
       </c>
-      <c r="D31" s="66" t="s">
+      <c r="C31" s="67" t="s">
         <v>287</v>
       </c>
-      <c r="E31" s="66"/>
-      <c r="F31" s="67" t="s">
+      <c r="D31" s="65" t="s">
         <v>288</v>
       </c>
-      <c r="G31" s="67"/>
-      <c r="H31" s="67"/>
+      <c r="E31" s="65"/>
+      <c r="F31" s="66" t="s">
+        <v>289</v>
+      </c>
+      <c r="G31" s="66"/>
+      <c r="H31" s="66"/>
     </row>
     <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B32" s="65" t="s">
-        <v>289</v>
-      </c>
-      <c r="C32" s="36" t="s">
-        <v>282</v>
-      </c>
-      <c r="D32" s="66" t="s">
+      <c r="B32" s="64" t="s">
         <v>290</v>
       </c>
-      <c r="E32" s="66"/>
-      <c r="F32" s="67" t="s">
+      <c r="C32" s="37" t="s">
+        <v>283</v>
+      </c>
+      <c r="D32" s="65" t="s">
         <v>291</v>
       </c>
-      <c r="G32" s="67"/>
-      <c r="H32" s="67"/>
+      <c r="E32" s="65"/>
+      <c r="F32" s="66" t="s">
+        <v>292</v>
+      </c>
+      <c r="G32" s="66"/>
+      <c r="H32" s="66"/>
     </row>
     <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B33" s="65" t="s">
-        <v>292</v>
-      </c>
-      <c r="C33" s="36" t="s">
-        <v>282</v>
-      </c>
-      <c r="D33" s="66" t="s">
+      <c r="B33" s="64" t="s">
         <v>293</v>
       </c>
-      <c r="E33" s="66"/>
-      <c r="F33" s="67" t="s">
+      <c r="C33" s="37" t="s">
+        <v>283</v>
+      </c>
+      <c r="D33" s="65" t="s">
         <v>294</v>
       </c>
-      <c r="G33" s="67"/>
-      <c r="H33" s="67"/>
+      <c r="E33" s="65"/>
+      <c r="F33" s="66" t="s">
+        <v>295</v>
+      </c>
+      <c r="G33" s="66"/>
+      <c r="H33" s="66"/>
     </row>
     <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B34" s="65" t="s">
-        <v>295</v>
-      </c>
-      <c r="C34" s="36" t="s">
-        <v>282</v>
-      </c>
-      <c r="D34" s="66" t="s">
+      <c r="B34" s="64" t="s">
         <v>296</v>
       </c>
-      <c r="E34" s="66"/>
-      <c r="F34" s="67" t="s">
+      <c r="C34" s="37" t="s">
+        <v>283</v>
+      </c>
+      <c r="D34" s="65" t="s">
         <v>297</v>
       </c>
-      <c r="G34" s="67"/>
-      <c r="H34" s="67"/>
+      <c r="E34" s="65"/>
+      <c r="F34" s="66" t="s">
+        <v>298</v>
+      </c>
+      <c r="G34" s="66"/>
+      <c r="H34" s="66"/>
     </row>
     <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="65" t="s">
-        <v>298</v>
-      </c>
-      <c r="C35" s="36" t="s">
-        <v>282</v>
-      </c>
-      <c r="D35" s="66" t="s">
+      <c r="B35" s="64" t="s">
         <v>299</v>
       </c>
-      <c r="E35" s="66"/>
-      <c r="F35" s="67" t="s">
+      <c r="C35" s="37" t="s">
+        <v>283</v>
+      </c>
+      <c r="D35" s="65" t="s">
         <v>300</v>
       </c>
-      <c r="G35" s="67"/>
-      <c r="H35" s="67"/>
+      <c r="E35" s="65"/>
+      <c r="F35" s="66" t="s">
+        <v>301</v>
+      </c>
+      <c r="G35" s="66"/>
+      <c r="H35" s="66"/>
     </row>
     <row r="36" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B36" s="65" t="s">
-        <v>301</v>
-      </c>
-      <c r="C36" s="36" t="s">
-        <v>282</v>
-      </c>
-      <c r="D36" s="66" t="s">
+      <c r="B36" s="64" t="s">
         <v>302</v>
       </c>
-      <c r="E36" s="66"/>
-      <c r="F36" s="67" t="s">
+      <c r="C36" s="37" t="s">
+        <v>283</v>
+      </c>
+      <c r="D36" s="65" t="s">
         <v>303</v>
       </c>
-      <c r="G36" s="67"/>
-      <c r="H36" s="67"/>
+      <c r="E36" s="65"/>
+      <c r="F36" s="66" t="s">
+        <v>304</v>
+      </c>
+      <c r="G36" s="66"/>
+      <c r="H36" s="66"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B38" s="65" t="s">
-        <v>304</v>
-      </c>
-      <c r="C38" s="26" t="s">
+      <c r="B38" s="64" t="s">
         <v>305</v>
       </c>
-      <c r="D38" s="26"/>
-      <c r="E38" s="26"/>
-      <c r="F38" s="26"/>
+      <c r="C38" s="27" t="s">
+        <v>306</v>
+      </c>
+      <c r="D38" s="27"/>
+      <c r="E38" s="27"/>
+      <c r="F38" s="27"/>
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B40" s="69" t="s">
+      <c r="B40" s="68" t="s">
         <v>144</v>
       </c>
-      <c r="C40" s="69"/>
-      <c r="D40" s="69"/>
-      <c r="E40" s="69"/>
-      <c r="F40" s="69"/>
-      <c r="G40" s="69"/>
-      <c r="H40" s="69"/>
+      <c r="C40" s="68"/>
+      <c r="D40" s="68"/>
+      <c r="E40" s="68"/>
+      <c r="F40" s="68"/>
+      <c r="G40" s="68"/>
+      <c r="H40" s="68"/>
     </row>
   </sheetData>
   <mergeCells count="20">
@@ -7584,10 +7599,10 @@
       <formula>C24&gt;=1.25</formula>
     </cfRule>
     <cfRule type="expression" dxfId="22" priority="2">
-      <formula>C24&gt;=1</formula>
+      <formula>C24&gt;=1.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="23" priority="3">
-      <formula>C24&lt;1</formula>
+      <formula>C24&lt;1.15</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>

--- a/artifacts/api-server/qa-output/Formula_Export_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Formula_Export_Charter_Public_Funding.xlsx
@@ -8,7 +8,8 @@
     <sheet sheetId="2" name="Assumptions" state="visible" r:id="rId5"/>
     <sheet sheetId="3" name="5-Year Model" state="visible" r:id="rId6"/>
     <sheet sheetId="4" name="Year 1 Pro Forma" state="visible" r:id="rId7"/>
-    <sheet sheetId="5" name="Financial Health" state="visible" r:id="rId8"/>
+    <sheet sheetId="5" name="Decision History" state="visible" r:id="rId8"/>
+    <sheet sheetId="6" name="Financial Health" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Instructions'!$A1:$B37</definedName>
@@ -19,15 +20,17 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'5-Year Model'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Year 1 Pro Forma'!$A1:$N58</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Year 1 Pro Forma'!$1:$2</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'Financial Health'!$A1:$H40</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Financial Health'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Decision History'!$A1:$H4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Decision History'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'Financial Health'!$A1:$H40</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Financial Health'!$1:$2</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="310">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -747,6 +750,15 @@
   </si>
   <si>
     <t>Minimum Cash Month</t>
+  </si>
+  <si>
+    <t>Decision History</t>
+  </si>
+  <si>
+    <t>No decisions have been tracked with an outcome yet. As the team marks saved scenarios as Pursued, Declined, or On hold, those outcomes (and any retrospective notes) will appear here so reviewers can see what actually happened versus what was modeled.</t>
+  </si>
+  <si>
+    <t>Once decisions are saved with a Pursued / Declined / On hold outcome inside the planner, they will be summarized here.</t>
   </si>
   <si>
     <t>Civic Scholars Charter — Financial Health Dashboard</t>
@@ -1167,7 +1179,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1223,6 +1235,13 @@
     <xf numFmtId="168" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -6815,6 +6834,73 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="B1:H4"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="3" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="30" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="7" max="7" width="38" customWidth="1"/>
+    <col min="8" max="8" width="50" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B1" s="43" t="s">
+        <v>240</v>
+      </c>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
+    </row>
+    <row r="2" ht="60" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B2" s="44" t="s">
+        <v>241</v>
+      </c>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="44"/>
+      <c r="H2" s="44"/>
+    </row>
+    <row r="4" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B4" s="45" t="s">
+        <v>242</v>
+      </c>
+      <c r="C4" s="45"/>
+      <c r="D4" s="45"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="45"/>
+      <c r="G4" s="45"/>
+      <c r="H4" s="45"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B4:H4"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddHeader>&amp;L&amp;10&amp;BCivic Scholars Charter&amp;R&amp;8&amp;IDecision History</oddHeader>
+    <oddFooter>&amp;L&amp;8Built by SchoolStack Budget  •  budget.schoolstack.ai&amp;C&amp;8Page &amp;P of &amp;N&amp;R&amp;8&amp;D</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF328555"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="B2:H40"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
@@ -6827,7 +6913,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -6837,127 +6923,127 @@
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="43" t="s">
-        <v>241</v>
-      </c>
-      <c r="C3" s="43"/>
-      <c r="D3" s="43"/>
-      <c r="E3" s="43"/>
-      <c r="F3" s="43"/>
-      <c r="G3" s="43"/>
-      <c r="H3" s="43"/>
+      <c r="B3" s="46" t="s">
+        <v>244</v>
+      </c>
+      <c r="C3" s="46"/>
+      <c r="D3" s="46"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="46"/>
+      <c r="G3" s="46"/>
+      <c r="H3" s="46"/>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="44" t="s">
-        <v>242</v>
-      </c>
-      <c r="D4" s="45" t="s">
-        <v>243</v>
-      </c>
-      <c r="F4" s="46" t="s">
-        <v>244</v>
+      <c r="B4" s="47" t="s">
+        <v>245</v>
+      </c>
+      <c r="D4" s="48" t="s">
+        <v>246</v>
+      </c>
+      <c r="F4" s="49" t="s">
+        <v>247</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B6" s="12" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="E6" s="16" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="F6" s="16" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G6" s="16" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="H6" s="16" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="13" t="s">
-        <v>252</v>
-      </c>
-      <c r="C7" s="47">
+        <v>255</v>
+      </c>
+      <c r="C7" s="50">
         <v>120</v>
       </c>
-      <c r="D7" s="47">
+      <c r="D7" s="50">
         <v>200</v>
       </c>
-      <c r="E7" s="47">
+      <c r="E7" s="50">
         <v>300</v>
       </c>
-      <c r="F7" s="47">
+      <c r="F7" s="50">
         <v>375</v>
       </c>
-      <c r="G7" s="47">
+      <c r="G7" s="50">
         <v>400</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="13" t="s">
-        <v>253</v>
-      </c>
-      <c r="C8" s="48">
+        <v>256</v>
+      </c>
+      <c r="C8" s="51">
         <v>1546000</v>
       </c>
-      <c r="D8" s="48">
+      <c r="D8" s="51">
         <v>2522800</v>
       </c>
-      <c r="E8" s="48">
+      <c r="E8" s="51">
         <v>3784600</v>
       </c>
-      <c r="F8" s="48">
+      <c r="F8" s="51">
         <v>4759125</v>
       </c>
-      <c r="G8" s="48">
+      <c r="G8" s="51">
         <v>5184400</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="13" t="s">
-        <v>254</v>
-      </c>
-      <c r="C9" s="48">
+        <v>257</v>
+      </c>
+      <c r="C9" s="51">
         <v>1026431.25</v>
       </c>
-      <c r="D9" s="48">
+      <c r="D9" s="51">
         <v>1231717.5</v>
       </c>
-      <c r="E9" s="48">
+      <c r="E9" s="51">
         <v>1231717.5</v>
       </c>
-      <c r="F9" s="48">
+      <c r="F9" s="51">
         <v>1231717.5</v>
       </c>
-      <c r="G9" s="48">
+      <c r="G9" s="51">
         <v>1231717.5</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="13" t="s">
-        <v>255</v>
-      </c>
-      <c r="C10" s="48">
+        <v>258</v>
+      </c>
+      <c r="C10" s="51">
         <v>552000</v>
       </c>
-      <c r="D10" s="48">
+      <c r="D10" s="51">
         <v>819880</v>
       </c>
-      <c r="E10" s="48">
+      <c r="E10" s="51">
         <v>1120509.4</v>
       </c>
-      <c r="F10" s="48">
+      <c r="F10" s="51">
         <v>1366968.0320000001</v>
       </c>
-      <c r="G10" s="48">
+      <c r="G10" s="51">
         <v>1480640.90296</v>
       </c>
     </row>
@@ -6965,19 +7051,19 @@
       <c r="B11" s="13" t="s">
         <v>191</v>
       </c>
-      <c r="C11" s="48">
+      <c r="C11" s="51">
         <v>49824.605221179416</v>
       </c>
-      <c r="D11" s="48">
+      <c r="D11" s="51">
         <v>49824.605221179416</v>
       </c>
-      <c r="E11" s="48">
+      <c r="E11" s="51">
         <v>49824.605221179416</v>
       </c>
-      <c r="F11" s="48">
+      <c r="F11" s="51">
         <v>49824.605221179416</v>
       </c>
-      <c r="G11" s="48">
+      <c r="G11" s="51">
         <v>49824.605221179416</v>
       </c>
     </row>
@@ -6985,19 +7071,19 @@
       <c r="B12" s="27" t="s">
         <v>184</v>
       </c>
-      <c r="C12" s="49">
+      <c r="C12" s="52">
         <v>-82255.85522117942</v>
       </c>
-      <c r="D12" s="50">
+      <c r="D12" s="53">
         <v>421377.89477882057</v>
       </c>
-      <c r="E12" s="50">
+      <c r="E12" s="53">
         <v>1382548.4947788208</v>
       </c>
-      <c r="F12" s="50">
+      <c r="F12" s="53">
         <v>2110614.8627788206</v>
       </c>
-      <c r="G12" s="50">
+      <c r="G12" s="53">
         <v>2422216.9918188206</v>
       </c>
     </row>
@@ -7005,268 +7091,268 @@
       <c r="B13" s="27" t="s">
         <v>193</v>
       </c>
-      <c r="C13" s="49">
+      <c r="C13" s="52">
         <v>-82255.85522117942</v>
       </c>
-      <c r="D13" s="50">
+      <c r="D13" s="53">
         <v>339122.03955764114</v>
       </c>
-      <c r="E13" s="50">
+      <c r="E13" s="53">
         <v>1721670.534336462</v>
       </c>
-      <c r="F13" s="50">
+      <c r="F13" s="53">
         <v>3832285.3971152827</v>
       </c>
-      <c r="G13" s="50">
+      <c r="G13" s="53">
         <v>6254502.388934104</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="27" t="s">
-        <v>256</v>
-      </c>
-      <c r="C14" s="51">
+        <v>259</v>
+      </c>
+      <c r="C14" s="54">
         <v>-0.05320559846130622</v>
       </c>
-      <c r="D14" s="52">
+      <c r="D14" s="55">
         <v>0.16702786379372941</v>
       </c>
-      <c r="E14" s="52">
+      <c r="E14" s="55">
         <v>0.3653090141042173</v>
       </c>
-      <c r="F14" s="52">
+      <c r="F14" s="55">
         <v>0.44348800730781823</v>
       </c>
-      <c r="G14" s="52">
+      <c r="G14" s="55">
         <v>0.4672125977584331</v>
       </c>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" s="27" t="s">
-        <v>257</v>
-      </c>
-      <c r="C15" s="53">
+        <v>260</v>
+      </c>
+      <c r="C15" s="56">
         <v>12883.333333333334</v>
       </c>
-      <c r="D15" s="53">
+      <c r="D15" s="56">
         <v>12614</v>
       </c>
-      <c r="E15" s="53">
+      <c r="E15" s="56">
         <v>12615.333333333334</v>
       </c>
-      <c r="F15" s="53">
+      <c r="F15" s="56">
         <v>12691</v>
       </c>
-      <c r="G15" s="53">
+      <c r="G15" s="56">
         <v>12961</v>
       </c>
-      <c r="H15" s="54" t="s">
-        <v>258</v>
+      <c r="H15" s="57" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="27" t="s">
-        <v>259</v>
-      </c>
-      <c r="C16" s="55">
+        <v>262</v>
+      </c>
+      <c r="C16" s="58">
         <v>13568.798793509828</v>
       </c>
-      <c r="D16" s="55">
+      <c r="D16" s="58">
         <v>10507.110526105896</v>
       </c>
-      <c r="E16" s="55">
+      <c r="E16" s="58">
         <v>8006.838350737264</v>
       </c>
-      <c r="F16" s="55">
+      <c r="F16" s="58">
         <v>7062.693699256479</v>
       </c>
-      <c r="G16" s="55">
+      <c r="G16" s="58">
         <v>6905.457520452948</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="13" t="s">
-        <v>260</v>
-      </c>
-      <c r="C17" s="48">
+        <v>263</v>
+      </c>
+      <c r="C17" s="51">
         <v>700</v>
       </c>
-      <c r="D17" s="48">
+      <c r="D17" s="51">
         <v>721</v>
       </c>
-      <c r="E17" s="48">
+      <c r="E17" s="51">
         <v>743</v>
       </c>
-      <c r="F17" s="48">
+      <c r="F17" s="51">
         <v>765</v>
       </c>
-      <c r="G17" s="48">
+      <c r="G17" s="51">
         <v>788</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" s="13" t="s">
-        <v>261</v>
-      </c>
-      <c r="C18" s="53">
+        <v>264</v>
+      </c>
+      <c r="C18" s="56">
         <v>1500</v>
       </c>
-      <c r="D18" s="53">
+      <c r="D18" s="56">
         <v>1112.4</v>
       </c>
-      <c r="E18" s="53">
+      <c r="E18" s="56">
         <v>763.848</v>
       </c>
-      <c r="F18" s="53">
+      <c r="F18" s="56">
         <v>629.410752</v>
       </c>
-      <c r="G18" s="53">
+      <c r="G18" s="56">
         <v>607.7747574000001</v>
       </c>
-      <c r="H18" s="54" t="s">
-        <v>262</v>
+      <c r="H18" s="57" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" s="27" t="s">
-        <v>263</v>
-      </c>
-      <c r="C19" s="56">
+        <v>266</v>
+      </c>
+      <c r="C19" s="59">
         <v>-685.4654601764952</v>
       </c>
-      <c r="D19" s="57">
+      <c r="D19" s="60">
         <v>2106.889473894103</v>
       </c>
-      <c r="E19" s="57">
+      <c r="E19" s="60">
         <v>4608.494982596069</v>
       </c>
-      <c r="F19" s="57">
+      <c r="F19" s="60">
         <v>5628.306300743521</v>
       </c>
-      <c r="G19" s="57">
+      <c r="G19" s="60">
         <v>6055.542479547052</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="27" t="s">
-        <v>264</v>
-      </c>
-      <c r="C20" s="51">
+        <v>267</v>
+      </c>
+      <c r="C20" s="54">
         <v>0.6639270698576973</v>
       </c>
-      <c r="D20" s="52">
+      <c r="D20" s="55">
         <v>0.48823430315522437</v>
       </c>
-      <c r="E20" s="52">
+      <c r="E20" s="55">
         <v>0.3254551339639592</v>
       </c>
-      <c r="F20" s="52">
+      <c r="F20" s="55">
         <v>0.25881175636277676</v>
       </c>
-      <c r="G20" s="52">
+      <c r="G20" s="55">
         <v>0.23758149448345034</v>
       </c>
-      <c r="H20" s="54" t="s">
-        <v>265</v>
+      <c r="H20" s="57" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="27" t="s">
-        <v>266</v>
-      </c>
-      <c r="C21" s="52">
+        <v>269</v>
+      </c>
+      <c r="C21" s="55">
         <v>0.11642949547218628</v>
       </c>
-      <c r="D21" s="52">
+      <c r="D21" s="55">
         <v>0.08818772792135722</v>
       </c>
-      <c r="E21" s="52">
+      <c r="E21" s="55">
         <v>0.060549172964117735</v>
       </c>
-      <c r="F21" s="52">
+      <c r="F21" s="55">
         <v>0.04959504782917028</v>
       </c>
-      <c r="G21" s="52">
+      <c r="G21" s="55">
         <v>0.046892582161870235</v>
       </c>
-      <c r="H21" s="54" t="s">
-        <v>267</v>
+      <c r="H21" s="57" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="27" t="s">
-        <v>268</v>
-      </c>
-      <c r="C22" s="51">
+        <v>271</v>
+      </c>
+      <c r="C22" s="54">
         <v>-0.020977522639068564</v>
       </c>
-      <c r="D22" s="52">
+      <c r="D22" s="55">
         <v>0.18677758839384812</v>
       </c>
-      <c r="E22" s="52">
+      <c r="E22" s="55">
         <v>0.3784741055857951</v>
       </c>
-      <c r="F22" s="52">
+      <c r="F22" s="55">
         <v>0.45395728584561235</v>
       </c>
-      <c r="G22" s="52">
+      <c r="G22" s="55">
         <v>0.47682308406758733</v>
       </c>
-      <c r="H22" s="54" t="s">
-        <v>269</v>
+      <c r="H22" s="57" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B23" s="27" t="s">
-        <v>270</v>
-      </c>
-      <c r="C23" s="58">
+        <v>273</v>
+      </c>
+      <c r="C23" s="61">
         <v>3</v>
       </c>
-      <c r="D23" s="58">
+      <c r="D23" s="61">
         <v>3</v>
       </c>
-      <c r="E23" s="58">
+      <c r="E23" s="61">
         <v>3</v>
       </c>
-      <c r="F23" s="58">
+      <c r="F23" s="61">
         <v>3</v>
       </c>
-      <c r="G23" s="58">
+      <c r="G23" s="61">
         <v>3</v>
       </c>
-      <c r="H23" s="54" t="s">
-        <v>271</v>
+      <c r="H23" s="57" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B24" s="27" t="s">
-        <v>272</v>
-      </c>
-      <c r="C24" s="59">
+        <v>275</v>
+      </c>
+      <c r="C24" s="62">
         <v>-0.6509083184108029</v>
       </c>
-      <c r="D24" s="60">
+      <c r="D24" s="63">
         <v>9.457224957593874</v>
       </c>
-      <c r="E24" s="60">
+      <c r="E24" s="63">
         <v>28.748308062682405</v>
       </c>
-      <c r="F24" s="60">
+      <c r="F24" s="63">
         <v>43.36089485123791</v>
       </c>
-      <c r="G24" s="60">
+      <c r="G24" s="63">
         <v>49.614875743946406</v>
       </c>
-      <c r="H24" s="54" t="s">
-        <v>273</v>
+      <c r="H24" s="57" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B25" s="27" t="s">
-        <v>274</v>
-      </c>
-      <c r="C25" s="61" t="str">
+        <v>277</v>
+      </c>
+      <c r="C25" s="64" t="str">
         <f>IF('5-Year Model'!B64&gt;=0,"✓ Break-even","")</f>
         <v>0</v>
       </c>
@@ -7274,225 +7360,225 @@
         <f>IF(AND('5-Year Model'!C64&gt;=0,'5-Year Model'!B64&lt;0),"✓ Break-even","")</f>
         <v>✓ Break-even</v>
       </c>
-      <c r="E25" s="61" t="str">
+      <c r="E25" s="64" t="str">
         <f>IF(AND('5-Year Model'!D64&gt;=0,'5-Year Model'!C64&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="F25" s="61" t="str">
+      <c r="F25" s="64" t="str">
         <f>IF(AND('5-Year Model'!E64&gt;=0,'5-Year Model'!D64&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="G25" s="61" t="str">
+      <c r="G25" s="64" t="str">
         <f>IF(AND('5-Year Model'!F64&gt;=0,'5-Year Model'!E64&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="H25" s="54" t="s">
-        <v>246</v>
+      <c r="H25" s="57" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B26" s="27" t="s">
-        <v>275</v>
-      </c>
-      <c r="C26" s="62">
+        <v>278</v>
+      </c>
+      <c r="C26" s="65">
         <v>-1</v>
       </c>
-      <c r="D26" s="62">
+      <c r="D26" s="65">
         <v>2</v>
       </c>
-      <c r="E26" s="62">
+      <c r="E26" s="65">
         <v>9</v>
       </c>
-      <c r="F26" s="63">
+      <c r="F26" s="66">
         <v>17</v>
       </c>
-      <c r="G26" s="58">
+      <c r="G26" s="61">
         <v>27</v>
       </c>
-      <c r="H26" s="54" t="s">
-        <v>276</v>
+      <c r="H26" s="57" t="s">
+        <v>279</v>
       </c>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B27" s="27" t="s">
         <v>194</v>
       </c>
-      <c r="C27" s="62">
-        <v>0</v>
-      </c>
-      <c r="D27" s="63">
+      <c r="C27" s="65">
+        <v>0</v>
+      </c>
+      <c r="D27" s="66">
         <v>59</v>
       </c>
-      <c r="E27" s="58">
+      <c r="E27" s="61">
         <v>262</v>
       </c>
-      <c r="F27" s="58">
+      <c r="F27" s="61">
         <v>528</v>
       </c>
-      <c r="G27" s="58">
+      <c r="G27" s="61">
         <v>826</v>
       </c>
-      <c r="H27" s="54" t="s">
-        <v>277</v>
+      <c r="H27" s="57" t="s">
+        <v>280</v>
       </c>
     </row>
     <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B29" s="12" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="E29" s="12"/>
       <c r="F29" s="12" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="G29" s="12"/>
       <c r="H29" s="12"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="64" t="s">
-        <v>282</v>
+      <c r="B30" s="67" t="s">
+        <v>285</v>
       </c>
       <c r="C30" s="37" t="s">
-        <v>283</v>
-      </c>
-      <c r="D30" s="65" t="s">
-        <v>284</v>
-      </c>
-      <c r="E30" s="65"/>
-      <c r="F30" s="66" t="s">
-        <v>285</v>
-      </c>
-      <c r="G30" s="66"/>
-      <c r="H30" s="66"/>
+        <v>286</v>
+      </c>
+      <c r="D30" s="68" t="s">
+        <v>287</v>
+      </c>
+      <c r="E30" s="68"/>
+      <c r="F30" s="69" t="s">
+        <v>288</v>
+      </c>
+      <c r="G30" s="69"/>
+      <c r="H30" s="69"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="64" t="s">
+      <c r="B31" s="67" t="s">
+        <v>289</v>
+      </c>
+      <c r="C31" s="70" t="s">
+        <v>290</v>
+      </c>
+      <c r="D31" s="68" t="s">
+        <v>291</v>
+      </c>
+      <c r="E31" s="68"/>
+      <c r="F31" s="69" t="s">
+        <v>292</v>
+      </c>
+      <c r="G31" s="69"/>
+      <c r="H31" s="69"/>
+    </row>
+    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B32" s="67" t="s">
+        <v>293</v>
+      </c>
+      <c r="C32" s="37" t="s">
         <v>286</v>
       </c>
-      <c r="C31" s="67" t="s">
-        <v>287</v>
-      </c>
-      <c r="D31" s="65" t="s">
-        <v>288</v>
-      </c>
-      <c r="E31" s="65"/>
-      <c r="F31" s="66" t="s">
-        <v>289</v>
-      </c>
-      <c r="G31" s="66"/>
-      <c r="H31" s="66"/>
-    </row>
-    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B32" s="64" t="s">
-        <v>290</v>
-      </c>
-      <c r="C32" s="37" t="s">
-        <v>283</v>
-      </c>
-      <c r="D32" s="65" t="s">
-        <v>291</v>
-      </c>
-      <c r="E32" s="65"/>
-      <c r="F32" s="66" t="s">
-        <v>292</v>
-      </c>
-      <c r="G32" s="66"/>
-      <c r="H32" s="66"/>
+      <c r="D32" s="68" t="s">
+        <v>294</v>
+      </c>
+      <c r="E32" s="68"/>
+      <c r="F32" s="69" t="s">
+        <v>295</v>
+      </c>
+      <c r="G32" s="69"/>
+      <c r="H32" s="69"/>
     </row>
     <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B33" s="64" t="s">
-        <v>293</v>
+      <c r="B33" s="67" t="s">
+        <v>296</v>
       </c>
       <c r="C33" s="37" t="s">
-        <v>283</v>
-      </c>
-      <c r="D33" s="65" t="s">
-        <v>294</v>
-      </c>
-      <c r="E33" s="65"/>
-      <c r="F33" s="66" t="s">
-        <v>295</v>
-      </c>
-      <c r="G33" s="66"/>
-      <c r="H33" s="66"/>
+        <v>286</v>
+      </c>
+      <c r="D33" s="68" t="s">
+        <v>297</v>
+      </c>
+      <c r="E33" s="68"/>
+      <c r="F33" s="69" t="s">
+        <v>298</v>
+      </c>
+      <c r="G33" s="69"/>
+      <c r="H33" s="69"/>
     </row>
     <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B34" s="64" t="s">
-        <v>296</v>
+      <c r="B34" s="67" t="s">
+        <v>299</v>
       </c>
       <c r="C34" s="37" t="s">
-        <v>283</v>
-      </c>
-      <c r="D34" s="65" t="s">
-        <v>297</v>
-      </c>
-      <c r="E34" s="65"/>
-      <c r="F34" s="66" t="s">
-        <v>298</v>
-      </c>
-      <c r="G34" s="66"/>
-      <c r="H34" s="66"/>
+        <v>286</v>
+      </c>
+      <c r="D34" s="68" t="s">
+        <v>300</v>
+      </c>
+      <c r="E34" s="68"/>
+      <c r="F34" s="69" t="s">
+        <v>301</v>
+      </c>
+      <c r="G34" s="69"/>
+      <c r="H34" s="69"/>
     </row>
     <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="64" t="s">
-        <v>299</v>
+      <c r="B35" s="67" t="s">
+        <v>302</v>
       </c>
       <c r="C35" s="37" t="s">
-        <v>283</v>
-      </c>
-      <c r="D35" s="65" t="s">
-        <v>300</v>
-      </c>
-      <c r="E35" s="65"/>
-      <c r="F35" s="66" t="s">
-        <v>301</v>
-      </c>
-      <c r="G35" s="66"/>
-      <c r="H35" s="66"/>
+        <v>286</v>
+      </c>
+      <c r="D35" s="68" t="s">
+        <v>303</v>
+      </c>
+      <c r="E35" s="68"/>
+      <c r="F35" s="69" t="s">
+        <v>304</v>
+      </c>
+      <c r="G35" s="69"/>
+      <c r="H35" s="69"/>
     </row>
     <row r="36" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B36" s="64" t="s">
-        <v>302</v>
+      <c r="B36" s="67" t="s">
+        <v>305</v>
       </c>
       <c r="C36" s="37" t="s">
-        <v>283</v>
-      </c>
-      <c r="D36" s="65" t="s">
-        <v>303</v>
-      </c>
-      <c r="E36" s="65"/>
-      <c r="F36" s="66" t="s">
-        <v>304</v>
-      </c>
-      <c r="G36" s="66"/>
-      <c r="H36" s="66"/>
+        <v>286</v>
+      </c>
+      <c r="D36" s="68" t="s">
+        <v>306</v>
+      </c>
+      <c r="E36" s="68"/>
+      <c r="F36" s="69" t="s">
+        <v>307</v>
+      </c>
+      <c r="G36" s="69"/>
+      <c r="H36" s="69"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B38" s="64" t="s">
-        <v>305</v>
+      <c r="B38" s="67" t="s">
+        <v>308</v>
       </c>
       <c r="C38" s="27" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="D38" s="27"/>
       <c r="E38" s="27"/>
       <c r="F38" s="27"/>
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B40" s="68" t="s">
+      <c r="B40" s="71" t="s">
         <v>144</v>
       </c>
-      <c r="C40" s="68"/>
-      <c r="D40" s="68"/>
-      <c r="E40" s="68"/>
-      <c r="F40" s="68"/>
-      <c r="G40" s="68"/>
-      <c r="H40" s="68"/>
+      <c r="C40" s="71"/>
+      <c r="D40" s="71"/>
+      <c r="E40" s="71"/>
+      <c r="F40" s="71"/>
+      <c r="G40" s="71"/>
+      <c r="H40" s="71"/>
     </row>
   </sheetData>
   <mergeCells count="20">

--- a/artifacts/api-server/qa-output/Formula_Export_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Formula_Export_Charter_Public_Funding.xlsx
@@ -38,7 +38,7 @@
     <t>Civic Scholars Charter</t>
   </si>
   <si>
-    <t>Generated April 29, 2026 · nonprofit_501c3</t>
+    <t>Generated May 1, 2026 · nonprofit_501c3</t>
   </si>
   <si>
     <t>Cell Color Legend</t>
@@ -764,7 +764,7 @@
     <t>Civic Scholars Charter — Financial Health Dashboard</t>
   </si>
   <si>
-    <t>Generated April 29, 2026</t>
+    <t>Generated May 1, 2026</t>
   </si>
   <si>
     <t>● Green = healthy</t>

--- a/artifacts/api-server/qa-output/Formula_Export_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Formula_Export_Charter_Public_Funding.xlsx
@@ -22,7 +22,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Year 1 Pro Forma'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'Decision History'!$A1:$H4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Decision History'!$1:$2</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">'Financial Health'!$A1:$H40</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'Financial Health'!$A1:$I40</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'Financial Health'!$1:$2</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
@@ -38,7 +38,7 @@
     <t>Civic Scholars Charter</t>
   </si>
   <si>
-    <t>Generated May 1, 2026 · nonprofit_501c3</t>
+    <t>Generated May 7, 2026 · nonprofit_501c3</t>
   </si>
   <si>
     <t>Cell Color Legend</t>
@@ -764,7 +764,7 @@
     <t>Civic Scholars Charter — Financial Health Dashboard</t>
   </si>
   <si>
-    <t>Generated May 1, 2026</t>
+    <t>Generated May 7, 2026</t>
   </si>
   <si>
     <t>● Green = healthy</t>
@@ -896,7 +896,7 @@
     <t>The model reaches net income early and sustains strong margins through Year 5.</t>
   </si>
   <si>
-    <t>Monitor enrollment actuals vs. projections in Year 1.</t>
+    <t>Compare your real Year 1 enrollment against this projection as students enroll.</t>
   </si>
   <si>
     <t>Liquidity</t>
@@ -6901,7 +6901,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H40"/>
+  <dimension ref="B2:I40"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -6911,7 +6911,7 @@
     <col min="9" max="9" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="2" ht="30" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>243</v>
       </c>
@@ -6921,8 +6921,9 @@
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
-    </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I2" s="1"/>
+    </row>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B3" s="46" t="s">
         <v>244</v>
       </c>
@@ -6932,6 +6933,7 @@
       <c r="F3" s="46"/>
       <c r="G3" s="46"/>
       <c r="H3" s="46"/>
+      <c r="I3" s="46"/>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B4" s="47" t="s">
@@ -7422,7 +7424,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="29" ht="24" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B29" s="12" t="s">
         <v>281</v>
       </c>
@@ -7438,8 +7440,9 @@
       </c>
       <c r="G29" s="12"/>
       <c r="H29" s="12"/>
-    </row>
-    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I29" s="12"/>
+    </row>
+    <row r="30" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B30" s="67" t="s">
         <v>285</v>
       </c>
@@ -7455,8 +7458,9 @@
       </c>
       <c r="G30" s="69"/>
       <c r="H30" s="69"/>
-    </row>
-    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I30" s="69"/>
+    </row>
+    <row r="31" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B31" s="67" t="s">
         <v>289</v>
       </c>
@@ -7472,8 +7476,9 @@
       </c>
       <c r="G31" s="69"/>
       <c r="H31" s="69"/>
-    </row>
-    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I31" s="69"/>
+    </row>
+    <row r="32" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B32" s="67" t="s">
         <v>293</v>
       </c>
@@ -7489,8 +7494,9 @@
       </c>
       <c r="G32" s="69"/>
       <c r="H32" s="69"/>
-    </row>
-    <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I32" s="69"/>
+    </row>
+    <row r="33" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B33" s="67" t="s">
         <v>296</v>
       </c>
@@ -7506,8 +7512,9 @@
       </c>
       <c r="G33" s="69"/>
       <c r="H33" s="69"/>
-    </row>
-    <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I33" s="69"/>
+    </row>
+    <row r="34" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B34" s="67" t="s">
         <v>299</v>
       </c>
@@ -7523,8 +7530,9 @@
       </c>
       <c r="G34" s="69"/>
       <c r="H34" s="69"/>
-    </row>
-    <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I34" s="69"/>
+    </row>
+    <row r="35" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B35" s="67" t="s">
         <v>302</v>
       </c>
@@ -7540,8 +7548,9 @@
       </c>
       <c r="G35" s="69"/>
       <c r="H35" s="69"/>
-    </row>
-    <row r="36" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I35" s="69"/>
+    </row>
+    <row r="36" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B36" s="67" t="s">
         <v>305</v>
       </c>
@@ -7557,6 +7566,7 @@
       </c>
       <c r="G36" s="69"/>
       <c r="H36" s="69"/>
+      <c r="I36" s="69"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B38" s="67" t="s">
@@ -7569,7 +7579,7 @@
       <c r="E38" s="27"/>
       <c r="F38" s="27"/>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B40" s="71" t="s">
         <v>144</v>
       </c>
@@ -7579,29 +7589,30 @@
       <c r="F40" s="71"/>
       <c r="G40" s="71"/>
       <c r="H40" s="71"/>
+      <c r="I40" s="71"/>
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="B3:I3"/>
     <mergeCell ref="D29:E29"/>
-    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="F29:I29"/>
     <mergeCell ref="D30:E30"/>
-    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="F30:I30"/>
     <mergeCell ref="D31:E31"/>
-    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="F31:I31"/>
     <mergeCell ref="D32:E32"/>
-    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="F32:I32"/>
     <mergeCell ref="D33:E33"/>
-    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="F33:I33"/>
     <mergeCell ref="D34:E34"/>
-    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="F34:I34"/>
     <mergeCell ref="D35:E35"/>
-    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="F35:I35"/>
     <mergeCell ref="D36:E36"/>
-    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="F36:I36"/>
     <mergeCell ref="C38:F38"/>
-    <mergeCell ref="B40:H40"/>
+    <mergeCell ref="B40:I40"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">

--- a/artifacts/api-server/qa-output/Formula_Export_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Formula_Export_Charter_Public_Funding.xlsx
@@ -38,7 +38,7 @@
     <t>Civic Scholars Charter</t>
   </si>
   <si>
-    <t>Generated May 7, 2026 · nonprofit_501c3</t>
+    <t>Generated May 9, 2026 · nonprofit_501c3</t>
   </si>
   <si>
     <t>Cell Color Legend</t>
@@ -764,7 +764,7 @@
     <t>Civic Scholars Charter — Financial Health Dashboard</t>
   </si>
   <si>
-    <t>Generated May 7, 2026</t>
+    <t>Generated May 9, 2026</t>
   </si>
   <si>
     <t>● Green = healthy</t>
